--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="1427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="1426">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,19 +44,19 @@
     <t xml:space="preserve">CE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52814483642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46432209014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30644083023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26613092422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31315946578979</t>
+    <t xml:space="preserve">4.52814435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46432113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30644035339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26613140106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31315898895264</t>
   </si>
   <si>
     <t xml:space="preserve">4.31987762451172</t>
@@ -65,100 +65,100 @@
     <t xml:space="preserve">4.36690521240234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27285003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2358980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05114507675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08473634719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74210238456726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91677832603455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03099060058594</t>
+    <t xml:space="preserve">4.27284955978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23589849472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05114555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08473587036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74210214614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91677808761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03098964691162</t>
   </si>
   <si>
     <t xml:space="preserve">4.1552791595459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12840557098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01419353485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12504625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12168788909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9470112323761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80256724357605</t>
+    <t xml:space="preserve">4.12840461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01419401168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12504577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1216869354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94701099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80256700515747</t>
   </si>
   <si>
     <t xml:space="preserve">3.83615946769714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86975073814392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58086276054382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42970085144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7521800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6077356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84959554672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670132637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96716594696045</t>
+    <t xml:space="preserve">3.86974954605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58086228370667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42970108985901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75217962265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60773587226868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84959578514099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96716618537903</t>
   </si>
   <si>
     <t xml:space="preserve">4.06458187103271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82944083213806</t>
+    <t xml:space="preserve">3.82944059371948</t>
   </si>
   <si>
     <t xml:space="preserve">3.77233457565308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90334224700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87982773780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72866582870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79584908485413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88318705558777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95708799362183</t>
+    <t xml:space="preserve">3.90334177017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87982869148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72866535186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79584836959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88318753242493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95708823204041</t>
   </si>
   <si>
     <t xml:space="preserve">4.13176488876343</t>
@@ -167,34 +167,34 @@
     <t xml:space="preserve">4.1955885887146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18551111221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13848257064819</t>
+    <t xml:space="preserve">4.18551063537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13848304748535</t>
   </si>
   <si>
     <t xml:space="preserve">4.22246265411377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29972267150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3568286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25605392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2795672416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14856100082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32659578323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26949024200439</t>
+    <t xml:space="preserve">4.29972314834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35682821273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25605344772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27956771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14856004714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32659673690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26949071884155</t>
   </si>
   <si>
     <t xml:space="preserve">4.16535615921021</t>
@@ -203,19 +203,19 @@
     <t xml:space="preserve">4.09817314147949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04778528213501</t>
+    <t xml:space="preserve">4.04778623580933</t>
   </si>
   <si>
     <t xml:space="preserve">4.04106712341309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93021583557129</t>
+    <t xml:space="preserve">3.93021535873413</t>
   </si>
   <si>
     <t xml:space="preserve">3.91006016731262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81936240196228</t>
+    <t xml:space="preserve">3.81936311721802</t>
   </si>
   <si>
     <t xml:space="preserve">3.75889801979065</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">3.71187043190002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93357443809509</t>
+    <t xml:space="preserve">3.93357467651367</t>
   </si>
   <si>
     <t xml:space="preserve">3.82608151435852</t>
@@ -233,79 +233,79 @@
     <t xml:space="preserve">4.08137702941895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15863752365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17879247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21238422393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21574401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28292655944824</t>
+    <t xml:space="preserve">4.15863847732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17879343032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21238470077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21574354171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2829270362854</t>
   </si>
   <si>
     <t xml:space="preserve">4.30308151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3534688949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1989483833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07465839385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08809471130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06122255325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02427196502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693375587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21648931503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14420700073242</t>
+    <t xml:space="preserve">4.35346937179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19894742965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07465934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08809566497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06122303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0242714881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21648979187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14420652389526</t>
   </si>
   <si>
     <t xml:space="preserve">4.19927930831909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2543511390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23370027542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23714208602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49185228347778</t>
+    <t xml:space="preserve">4.25435209274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23369979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23714160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49185180664062</t>
   </si>
   <si>
     <t xml:space="preserve">4.49873638153076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47120046615601</t>
+    <t xml:space="preserve">4.47119998931885</t>
   </si>
   <si>
     <t xml:space="preserve">4.45743179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46431589126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37826585769653</t>
+    <t xml:space="preserve">4.46431636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37826490402222</t>
   </si>
   <si>
     <t xml:space="preserve">4.31975078582764</t>
@@ -317,73 +317,73 @@
     <t xml:space="preserve">4.28188800811768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42989587783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34040212631226</t>
+    <t xml:space="preserve">4.42989540100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34040307998657</t>
   </si>
   <si>
     <t xml:space="preserve">4.35072898864746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25091028213501</t>
+    <t xml:space="preserve">4.25090980529785</t>
   </si>
   <si>
     <t xml:space="preserve">4.03750371932983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91703271865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98243141174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884379386902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13732290267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33696126937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38170623779297</t>
+    <t xml:space="preserve">3.91703319549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98243165016174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884427070618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13732242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3369607925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38170671463013</t>
   </si>
   <si>
     <t xml:space="preserve">4.423011302948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52971458435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74148917198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181460380554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73116302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84130811691284</t>
+    <t xml:space="preserve">4.52971363067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74148941040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181555747986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73116374015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84130764007568</t>
   </si>
   <si>
     <t xml:space="preserve">3.65199613571167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52464127540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42826437950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50743103027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65887999534607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75525760650635</t>
+    <t xml:space="preserve">3.5246410369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42826390266418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50743079185486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65888047218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75525665283203</t>
   </si>
   <si>
     <t xml:space="preserve">3.82065606117249</t>
@@ -392,61 +392,61 @@
     <t xml:space="preserve">3.78623533248901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90670680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96522164344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95145344734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0409460067749</t>
+    <t xml:space="preserve">3.90670657157898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9652214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95145297050476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04094552993774</t>
   </si>
   <si>
     <t xml:space="preserve">4.01340961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94456887245178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98931550979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95833706855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79656147956848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90326428413391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80000400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68641662597656</t>
+    <t xml:space="preserve">3.94456934928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98931622505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95833683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79656195640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90326476097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80000352859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68641638755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.70018482208252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76558327674866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362710952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66576385498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66920638084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55217671394348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48677849769592</t>
+    <t xml:space="preserve">3.76558303833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362687110901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66576409339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6692066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55217742919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4867787361145</t>
   </si>
   <si>
     <t xml:space="preserve">3.47989463806152</t>
@@ -455,31 +455,31 @@
     <t xml:space="preserve">3.37319135665894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3718147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5005464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68985915184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561947822571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45235800743103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47645282745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64511227607727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72083711624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7070689201355</t>
+    <t xml:space="preserve">3.37181448936462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50054740905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68985843658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561900138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45235848426819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47645258903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64511203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72083616256714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706939697266</t>
   </si>
   <si>
     <t xml:space="preserve">3.77935123443604</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">3.61413359642029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61757564544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57971334457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5659453868866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49366211891174</t>
+    <t xml:space="preserve">3.61757612228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57971358299255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56594562530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49366307258606</t>
   </si>
   <si>
     <t xml:space="preserve">3.49022102355957</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">3.63822865486145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49710440635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38695979118347</t>
+    <t xml:space="preserve">3.49710488319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38696026802063</t>
   </si>
   <si>
     <t xml:space="preserve">3.35804653167725</t>
@@ -524,85 +524,85 @@
     <t xml:space="preserve">3.37456846237183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31123542785645</t>
+    <t xml:space="preserve">3.31123495101929</t>
   </si>
   <si>
     <t xml:space="preserve">3.32637977600098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35529327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41587281227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.514315366745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48333644866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51087284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51775717735291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47301077842712</t>
+    <t xml:space="preserve">3.35529351234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41587257385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51431512832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48333621025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51087260246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51775670051575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47301054000854</t>
   </si>
   <si>
     <t xml:space="preserve">3.57627129554749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53496742248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64855480194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.679532289505</t>
+    <t xml:space="preserve">3.53496789932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64855408668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67953276634216</t>
   </si>
   <si>
     <t xml:space="preserve">3.596923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64167070388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63134407997131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56250381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5315248966217</t>
+    <t xml:space="preserve">3.64167046546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63134360313416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56250309944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53152537345886</t>
   </si>
   <si>
     <t xml:space="preserve">3.45580053329468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41174221038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42964100837708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45924210548401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4420325756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52808332443237</t>
+    <t xml:space="preserve">3.41174244880676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42964148521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45924305915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44203186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52808356285095</t>
   </si>
   <si>
     <t xml:space="preserve">3.63478636741638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67609119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62790179252625</t>
+    <t xml:space="preserve">3.67609024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62790203094482</t>
   </si>
   <si>
     <t xml:space="preserve">3.58659768104553</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">3.54529333114624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55906128883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56938791275024</t>
+    <t xml:space="preserve">3.5590615272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56938767433167</t>
   </si>
   <si>
     <t xml:space="preserve">3.71739482879639</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">3.94112658500671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00996780395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88605427742004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97210550308228</t>
+    <t xml:space="preserve">4.00996732711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88605451583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97210502624512</t>
   </si>
   <si>
     <t xml:space="preserve">3.83442401885986</t>
@@ -638,13 +638,13 @@
     <t xml:space="preserve">3.92735862731934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98587322235107</t>
+    <t xml:space="preserve">3.9858729839325</t>
   </si>
   <si>
     <t xml:space="preserve">4.0547137260437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93080139160156</t>
+    <t xml:space="preserve">3.9308009147644</t>
   </si>
   <si>
     <t xml:space="preserve">4.04438781738281</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">4.06159782409668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91014909744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.899822473526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05815553665161</t>
+    <t xml:space="preserve">3.91014838218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89982295036316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05815601348877</t>
   </si>
   <si>
     <t xml:space="preserve">4.07192468643188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07880878448486</t>
+    <t xml:space="preserve">4.07880830764771</t>
   </si>
   <si>
     <t xml:space="preserve">4.03061962127686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19583702087402</t>
+    <t xml:space="preserve">4.19583749771118</t>
   </si>
   <si>
     <t xml:space="preserve">4.20960521697998</t>
@@ -680,31 +680,31 @@
     <t xml:space="preserve">4.29565620422363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27844619750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24746751785278</t>
+    <t xml:space="preserve">4.27844572067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24746799468994</t>
   </si>
   <si>
     <t xml:space="preserve">4.30254077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12699699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13043928146362</t>
+    <t xml:space="preserve">4.12699747085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13043880462646</t>
   </si>
   <si>
     <t xml:space="preserve">4.202721118927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10634469985962</t>
+    <t xml:space="preserve">4.10634422302246</t>
   </si>
   <si>
     <t xml:space="preserve">4.12011289596558</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17862701416016</t>
+    <t xml:space="preserve">4.17862749099731</t>
   </si>
   <si>
     <t xml:space="preserve">4.2405834197998</t>
@@ -716,43 +716,43 @@
     <t xml:space="preserve">4.16141748428345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04782962799072</t>
+    <t xml:space="preserve">4.04783010482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.14076471328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1510910987854</t>
+    <t xml:space="preserve">4.15109062194824</t>
   </si>
   <si>
     <t xml:space="preserve">4.15453243255615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18206882476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15797519683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21304702758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32319211959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449718475342</t>
+    <t xml:space="preserve">4.18206930160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15797472000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21304750442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32319164276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449766159058</t>
   </si>
   <si>
     <t xml:space="preserve">4.43333768844604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44022130966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38514852523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4746413230896</t>
+    <t xml:space="preserve">4.44022178649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38514947891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47464179992676</t>
   </si>
   <si>
     <t xml:space="preserve">4.41956996917725</t>
@@ -761,22 +761,22 @@
     <t xml:space="preserve">4.37482357025146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41268539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34384489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30942440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36793899536133</t>
+    <t xml:space="preserve">4.41268491744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34384441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30942487716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36793851852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.35417079925537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2853307723999</t>
+    <t xml:space="preserve">4.28532981872559</t>
   </si>
   <si>
     <t xml:space="preserve">4.52627229690552</t>
@@ -785,22 +785,22 @@
     <t xml:space="preserve">4.40580129623413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48841047286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50906229019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53659868240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54348182678223</t>
+    <t xml:space="preserve">4.48840951919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50906276702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53659820556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54348278045654</t>
   </si>
   <si>
     <t xml:space="preserve">4.447105884552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67083740234375</t>
+    <t xml:space="preserve">4.67083787918091</t>
   </si>
   <si>
     <t xml:space="preserve">4.69899654388428</t>
@@ -809,22 +809,22 @@
     <t xml:space="preserve">4.80107259750366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7165961265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83627080917358</t>
+    <t xml:space="preserve">4.71659564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83627128601074</t>
   </si>
   <si>
     <t xml:space="preserve">4.86090993881226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85034942626953</t>
+    <t xml:space="preserve">4.85035085678101</t>
   </si>
   <si>
     <t xml:space="preserve">4.87850904464722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78347301483154</t>
+    <t xml:space="preserve">4.78347253799438</t>
   </si>
   <si>
     <t xml:space="preserve">4.72011566162109</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">4.7306752204895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75179433822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81515121459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81163215637207</t>
+    <t xml:space="preserve">4.75179481506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81515169143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81163167953491</t>
   </si>
   <si>
     <t xml:space="preserve">4.9277868270874</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">4.87498903274536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80811166763306</t>
+    <t xml:space="preserve">4.80811214447021</t>
   </si>
   <si>
     <t xml:space="preserve">4.80459213256836</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">4.7869930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95946502685547</t>
+    <t xml:space="preserve">4.95946550369263</t>
   </si>
   <si>
     <t xml:space="preserve">4.86442947387695</t>
@@ -872,58 +872,58 @@
     <t xml:space="preserve">4.89258813858032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89610815048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91370725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97354412078857</t>
+    <t xml:space="preserve">4.89610767364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91370677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97354459762573</t>
   </si>
   <si>
     <t xml:space="preserve">4.97706460952759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94538593292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11081886291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25865268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0615406036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08618068695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10377931594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09673881530762</t>
+    <t xml:space="preserve">4.94538545608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1108193397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2586522102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06154108047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08617973327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10377883911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09673976898193</t>
   </si>
   <si>
     <t xml:space="preserve">5.0509819984436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08969974517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01930236816406</t>
+    <t xml:space="preserve">5.08969926834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01930284500122</t>
   </si>
   <si>
     <t xml:space="preserve">5.04746150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96650505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91018724441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00874328613281</t>
+    <t xml:space="preserve">4.96650552749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91018772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00874376296997</t>
   </si>
   <si>
     <t xml:space="preserve">5.10025930404663</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.06858015060425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13193845748901</t>
+    <t xml:space="preserve">5.13193798065186</t>
   </si>
   <si>
     <t xml:space="preserve">5.04042196273804</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">5.03690242767334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16361713409424</t>
+    <t xml:space="preserve">5.16361665725708</t>
   </si>
   <si>
     <t xml:space="preserve">5.27273178100586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23049354553223</t>
+    <t xml:space="preserve">5.23049402236938</t>
   </si>
   <si>
     <t xml:space="preserve">5.15305757522583</t>
@@ -971,43 +971,43 @@
     <t xml:space="preserve">5.11433839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10729885101318</t>
+    <t xml:space="preserve">5.10729932785034</t>
   </si>
   <si>
     <t xml:space="preserve">5.00522375106812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99818420410156</t>
+    <t xml:space="preserve">4.99818325042725</t>
   </si>
   <si>
     <t xml:space="preserve">5.01226282119751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04394245147705</t>
+    <t xml:space="preserve">5.04394149780273</t>
   </si>
   <si>
     <t xml:space="preserve">5.06506109237671</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15657615661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34312915802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30089092254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27977085113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30792999267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25161266326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29385042190552</t>
+    <t xml:space="preserve">5.15657711029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3431282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30089044570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27977228164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30793046951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2516131401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29385089874268</t>
   </si>
   <si>
     <t xml:space="preserve">5.29033136367798</t>
@@ -1016,25 +1016,25 @@
     <t xml:space="preserve">5.33608913421631</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34664821624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36776828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35368824005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38536643981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39944648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26569175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31145000457764</t>
+    <t xml:space="preserve">5.34664869308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36776781082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35368871688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38536691665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3994460105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26569271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31145048141479</t>
   </si>
   <si>
     <t xml:space="preserve">5.3255295753479</t>
@@ -1052,22 +1052,22 @@
     <t xml:space="preserve">5.14249706268311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16713714599609</t>
+    <t xml:space="preserve">5.16713619232178</t>
   </si>
   <si>
     <t xml:space="preserve">5.31497001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29737138748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19177484512329</t>
+    <t xml:space="preserve">5.29736995697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19177532196045</t>
   </si>
   <si>
     <t xml:space="preserve">5.35720825195312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07210063934326</t>
+    <t xml:space="preserve">5.0721001625061</t>
   </si>
   <si>
     <t xml:space="preserve">4.9841046333313</t>
@@ -1079,16 +1079,16 @@
     <t xml:space="preserve">4.86794900894165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92426681518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98058414459229</t>
+    <t xml:space="preserve">4.92426729202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98058462142944</t>
   </si>
   <si>
     <t xml:space="preserve">5.03338241577148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05450057983398</t>
+    <t xml:space="preserve">5.0545015335083</t>
   </si>
   <si>
     <t xml:space="preserve">5.18473529815674</t>
@@ -1097,58 +1097,58 @@
     <t xml:space="preserve">5.17417573928833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21993350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17769575119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22697305679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28681182861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02282190322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0017032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02986288070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.058021068573</t>
+    <t xml:space="preserve">5.21993398666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17769622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22697401046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28681135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02282333374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00170373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02986240386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05802154541016</t>
   </si>
   <si>
     <t xml:space="preserve">4.92074680328369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99114418029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37128734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47688341140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48392200469971</t>
+    <t xml:space="preserve">4.99114370346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37128686904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47688293457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48392295837402</t>
   </si>
   <si>
     <t xml:space="preserve">5.44168472290039</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43464469909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52616024017334</t>
+    <t xml:space="preserve">5.43464517593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5261607170105</t>
   </si>
   <si>
     <t xml:space="preserve">5.51208114624023</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46984338760376</t>
+    <t xml:space="preserve">5.4698429107666</t>
   </si>
   <si>
     <t xml:space="preserve">5.40648603439331</t>
@@ -1157,40 +1157,40 @@
     <t xml:space="preserve">5.37832736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18825531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13897752761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3290491104126</t>
+    <t xml:space="preserve">5.18825578689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13897800445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32904958724976</t>
   </si>
   <si>
     <t xml:space="preserve">5.14601707458496</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19529581069946</t>
+    <t xml:space="preserve">5.1952953338623</t>
   </si>
   <si>
     <t xml:space="preserve">5.24457311630249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22345352172852</t>
+    <t xml:space="preserve">5.22345399856567</t>
   </si>
   <si>
     <t xml:space="preserve">5.23753356933594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16009664535522</t>
+    <t xml:space="preserve">5.16009616851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.11785840988159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97002506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2189998626709</t>
+    <t xml:space="preserve">4.97002410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21899938583374</t>
   </si>
   <si>
     <t xml:space="preserve">5.14661407470703</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">4.98012685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94393491744995</t>
+    <t xml:space="preserve">4.94393444061279</t>
   </si>
   <si>
     <t xml:space="preserve">4.81364011764526</t>
@@ -1211,58 +1211,58 @@
     <t xml:space="preserve">4.85707187652588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82087850570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8064022064209</t>
+    <t xml:space="preserve">4.82087898254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80640125274658</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029081344604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46618986129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21283960342407</t>
+    <t xml:space="preserve">4.46618938446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21284103393555</t>
   </si>
   <si>
     <t xml:space="preserve">4.4517126083374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37208890914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52409887313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40828132629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34313440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29246425628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39380407333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45895147323608</t>
+    <t xml:space="preserve">4.37208843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52409839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4082818031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3431339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29246377944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3938045501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45895099639893</t>
   </si>
   <si>
     <t xml:space="preserve">4.43723583221436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53133678436279</t>
+    <t xml:space="preserve">4.53133726119995</t>
   </si>
   <si>
     <t xml:space="preserve">4.61096096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64715385437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69058513641357</t>
+    <t xml:space="preserve">4.64715337753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69058465957642</t>
   </si>
   <si>
     <t xml:space="preserve">4.57476806640625</t>
@@ -1277,13 +1277,13 @@
     <t xml:space="preserve">4.545814037323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58924579620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60372257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68334627151489</t>
+    <t xml:space="preserve">4.5892448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6037220954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68334674835205</t>
   </si>
   <si>
     <t xml:space="preserve">4.69782304763794</t>
@@ -1298,43 +1298,43 @@
     <t xml:space="preserve">4.61819934844971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56752872467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44447422027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42999601364136</t>
+    <t xml:space="preserve">4.56752967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44447374343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42999696731567</t>
   </si>
   <si>
     <t xml:space="preserve">4.59648323059082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47342777252197</t>
+    <t xml:space="preserve">4.47342824935913</t>
   </si>
   <si>
     <t xml:space="preserve">4.51685905456543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50962162017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17664766311646</t>
+    <t xml:space="preserve">4.50962066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1766471862793</t>
   </si>
   <si>
     <t xml:space="preserve">4.10426187515259</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04635286331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0246376991272</t>
+    <t xml:space="preserve">4.04635381698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02463722229004</t>
   </si>
   <si>
     <t xml:space="preserve">4.03187656402588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05359172821045</t>
+    <t xml:space="preserve">4.05359220504761</t>
   </si>
   <si>
     <t xml:space="preserve">4.0680685043335</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">4.00292253494263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85091304779053</t>
+    <t xml:space="preserve">3.85091257095337</t>
   </si>
   <si>
     <t xml:space="preserve">3.87262773513794</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">3.9232976436615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11149978637695</t>
+    <t xml:space="preserve">4.11150026321411</t>
   </si>
   <si>
     <t xml:space="preserve">4.22731733322144</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">4.20560169219971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22007846832275</t>
+    <t xml:space="preserve">4.22007894515991</t>
   </si>
   <si>
     <t xml:space="preserve">4.23455572128296</t>
@@ -1385,16 +1385,16 @@
     <t xml:space="preserve">4.36485004425049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35761165618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26350975036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09702348709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06083011627197</t>
+    <t xml:space="preserve">4.35761117935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26351070404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09702301025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06083106994629</t>
   </si>
   <si>
     <t xml:space="preserve">4.12597751617432</t>
@@ -1403,34 +1403,34 @@
     <t xml:space="preserve">3.90882062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84367370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78576493263245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87986660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94501328468323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80748128890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72061800956726</t>
+    <t xml:space="preserve">3.84367418289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7857654094696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87986707687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94501376152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80748081207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72061848640442</t>
   </si>
   <si>
     <t xml:space="preserve">3.68442606925964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57946681976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45641112327576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55051279067993</t>
+    <t xml:space="preserve">3.57946634292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45641136169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55051231384277</t>
   </si>
   <si>
     <t xml:space="preserve">3.81471967697144</t>
@@ -1442,85 +1442,85 @@
     <t xml:space="preserve">3.82919645309448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83643555641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85815048217773</t>
+    <t xml:space="preserve">3.83643579483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85815095901489</t>
   </si>
   <si>
     <t xml:space="preserve">3.74233412742615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75681114196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70614099502563</t>
+    <t xml:space="preserve">3.75681090354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70614123344421</t>
   </si>
   <si>
     <t xml:space="preserve">3.67718696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63375616073608</t>
+    <t xml:space="preserve">3.63375544548035</t>
   </si>
   <si>
     <t xml:space="preserve">3.66994833946228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6192786693573</t>
+    <t xml:space="preserve">3.61927819252014</t>
   </si>
   <si>
     <t xml:space="preserve">3.64099431037903</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77128863334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80024242401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6627094745636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72785687446594</t>
+    <t xml:space="preserve">3.7712881565094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80024266242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66270971298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72785758972168</t>
   </si>
   <si>
     <t xml:space="preserve">3.86538982391357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60480165481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58670473098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57584691047668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54327321052551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547132492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82195854187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71337985992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69890308380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69166374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62651681900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64823269844055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52517771720886</t>
+    <t xml:space="preserve">3.60480117797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58670496940613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57584714889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54327392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547108650208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8219587802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7133800983429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69890284538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69166398048401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62651705741882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64823246002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52517700195312</t>
   </si>
   <si>
     <t xml:space="preserve">3.60118222236633</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">3.54689335823059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5034613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6084201335907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79300332069397</t>
+    <t xml:space="preserve">3.50346183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60842084884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79300379753113</t>
   </si>
   <si>
     <t xml:space="preserve">3.88710498809814</t>
@@ -1544,184 +1544,184 @@
     <t xml:space="preserve">3.56498980522156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59394359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77852654457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58308506011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53965401649475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48174619674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49622297286987</t>
+    <t xml:space="preserve">3.59394383430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77852702140808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58308529853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53965377807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48174548149109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49622273445129</t>
   </si>
   <si>
     <t xml:space="preserve">3.45279145240784</t>
   </si>
   <si>
+    <t xml:space="preserve">3.42021799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43155574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43533563613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41265940666199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33329558372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38620495796204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3710880279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36352920532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38242602348328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31062054634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32573699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29172420501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393128395081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3143994808197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33707499504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.276606798172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28038668632507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23503565788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20480108261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21613907814026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23125600814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21235990524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24259376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18212556838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13677501678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1518919467926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18968415260315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20102214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25015234947205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39376330375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59784340858459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65831065177917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55627107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55249166488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56760907173157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57516717910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60540151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53359603881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4769070148468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59028434753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58272552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57138824462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5260374546051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50336170196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43911457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4277765750885</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.42021822929382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43155598640442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43533515930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41265964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3332953453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841251373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38620495796204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3710880279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36352920532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38242530822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31062030792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32573699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29172372817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393080711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31439971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33707523345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27660703659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28038644790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23503565788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20480108261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21613883972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23125624656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21235966682434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24259352684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18212580680847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13677501678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15189170837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18968439102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20102214813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25015234947205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39376330375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59784293174744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65831065177917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55627083778381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55249190330505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56760859489441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57516741752625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60540103912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53359603881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4769070148468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59028434753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58272552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57138824462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52603721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50336170196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4391143321991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42777633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42021870613098</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.40132188796997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36730885505676</t>
+    <t xml:space="preserve">3.36730861663818</t>
   </si>
   <si>
     <t xml:space="preserve">3.40888071060181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34085392951965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42399764060974</t>
+    <t xml:space="preserve">3.34085416793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4239981174469</t>
   </si>
   <si>
     <t xml:space="preserve">3.51469945907593</t>
@@ -1730,28 +1730,28 @@
     <t xml:space="preserve">3.49958252906799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54871296882629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63941407203674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65453171730042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68098664283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67342758178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73011660575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78680491447449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285823822021</t>
+    <t xml:space="preserve">3.54871273040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63941431045532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65453195571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68098592758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67342782020569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73011636734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78680539131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285776138306</t>
   </si>
   <si>
     <t xml:space="preserve">3.86239051818848</t>
@@ -1760,76 +1760,76 @@
     <t xml:space="preserve">3.74523329734802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76790833473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83971452713013</t>
+    <t xml:space="preserve">3.76790928840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83971500396729</t>
   </si>
   <si>
     <t xml:space="preserve">3.83215618133545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77168846130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7376754283905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69232416152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70366215705872</t>
+    <t xml:space="preserve">3.77168798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73767471313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69232392311096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70366191864014</t>
   </si>
   <si>
     <t xml:space="preserve">3.77924680709839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68854522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66586971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69610285758972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66964864730835</t>
+    <t xml:space="preserve">3.68854475021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66586947441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6961030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66964840888977</t>
   </si>
   <si>
     <t xml:space="preserve">3.73389554023743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81703925132751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84727358818054</t>
+    <t xml:space="preserve">3.81703972816467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84727311134338</t>
   </si>
   <si>
     <t xml:space="preserve">3.90018248558044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98332619667053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9606499671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95309162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93041658401489</t>
+    <t xml:space="preserve">3.98332571983337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96065020561218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9530918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93041634559631</t>
   </si>
   <si>
     <t xml:space="preserve">3.94553327560425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99088501930237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91529965400696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02111911773682</t>
+    <t xml:space="preserve">3.99088454246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91529941558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0211181640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.09670305252075</t>
@@ -1841,16 +1841,16 @@
     <t xml:space="preserve">4.06646966934204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0815863609314</t>
+    <t xml:space="preserve">4.08158683776855</t>
   </si>
   <si>
     <t xml:space="preserve">4.13449573516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05135250091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02867650985718</t>
+    <t xml:space="preserve">4.05135297775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02867746353149</t>
   </si>
   <si>
     <t xml:space="preserve">4.0060019493103</t>
@@ -1859,82 +1859,82 @@
     <t xml:space="preserve">4.04379367828369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11937856674194</t>
+    <t xml:space="preserve">4.1193790435791</t>
   </si>
   <si>
     <t xml:space="preserve">4.01355981826782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96820902824402</t>
+    <t xml:space="preserve">3.96820831298828</t>
   </si>
   <si>
     <t xml:space="preserve">3.93797540664673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97576785087585</t>
+    <t xml:space="preserve">3.97576761245728</t>
   </si>
   <si>
     <t xml:space="preserve">3.90774130821228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89262413978577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88506531715393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87750720977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85483121871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80192232131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5940637588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60162210464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6507523059845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877908706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99844288825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72255849838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63185620307922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46556949615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44667315483093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28416514396667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1103196144104</t>
+    <t xml:space="preserve">3.89262390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88506555557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87750697135925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85483193397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80192255973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59406352043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6016218662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65075182914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877884864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99844312667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72255802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63185596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46556925773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44667291641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28416562080383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11032009124756</t>
   </si>
   <si>
     <t xml:space="preserve">3.0649688243866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.838214635849</t>
+    <t xml:space="preserve">2.83821415901184</t>
   </si>
   <si>
     <t xml:space="preserve">2.8344349861145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95915031433105</t>
+    <t xml:space="preserve">2.9591498374939</t>
   </si>
   <si>
     <t xml:space="preserve">2.70971989631653</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">2.93269562721252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00450110435486</t>
+    <t xml:space="preserve">3.00450134277344</t>
   </si>
   <si>
     <t xml:space="preserve">2.97426724433899</t>
@@ -1952,46 +1952,46 @@
     <t xml:space="preserve">2.94403314590454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91001963615417</t>
+    <t xml:space="preserve">2.91001987457275</t>
   </si>
   <si>
     <t xml:space="preserve">2.96292924880981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85333132743835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89490270614624</t>
+    <t xml:space="preserve">2.85333156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89490294456482</t>
   </si>
   <si>
     <t xml:space="preserve">2.88734436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92135763168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85711026191711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90246152877808</t>
+    <t xml:space="preserve">2.92135787010193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85711073875427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9024612903595</t>
   </si>
   <si>
     <t xml:space="preserve">2.82687664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89112377166748</t>
+    <t xml:space="preserve">2.8911235332489</t>
   </si>
   <si>
     <t xml:space="preserve">2.9969425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95159149169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97804641723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99316334724426</t>
+    <t xml:space="preserve">2.9515917301178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97804665565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99316358566284</t>
   </si>
   <si>
     <t xml:space="preserve">3.05363130569458</t>
@@ -2003,31 +2003,31 @@
     <t xml:space="preserve">3.02717661857605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12165760993958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06119012832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09898209571838</t>
+    <t xml:space="preserve">3.12165784835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06118988990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09898233413696</t>
   </si>
   <si>
     <t xml:space="preserve">3.16700887680054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14433336257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19346332550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2199182510376</t>
+    <t xml:space="preserve">3.14433312416077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19346356391907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21991848945618</t>
   </si>
   <si>
     <t xml:space="preserve">3.26904821395874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32195806503296</t>
+    <t xml:space="preserve">3.32195782661438</t>
   </si>
   <si>
     <t xml:space="preserve">3.1594500541687</t>
@@ -2039,37 +2039,37 @@
     <t xml:space="preserve">3.06874823570251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10654067993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16322922706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27282762527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28794455528259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40510153770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51092004776001</t>
+    <t xml:space="preserve">3.10654091835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16322946548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27282786369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28794479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40510129928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51092028617859</t>
   </si>
   <si>
     <t xml:space="preserve">3.48824453353882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45801067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29550290107727</t>
+    <t xml:space="preserve">3.45801019668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29550337791443</t>
   </si>
   <si>
     <t xml:space="preserve">3.34463357925415</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29928207397461</t>
+    <t xml:space="preserve">3.29928255081177</t>
   </si>
   <si>
     <t xml:space="preserve">3.30684089660645</t>
@@ -2087,58 +2087,58 @@
     <t xml:space="preserve">3.37486743927002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26526927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39754247665405</t>
+    <t xml:space="preserve">3.26526880264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39754295349121</t>
   </si>
   <si>
     <t xml:space="preserve">3.48068618774414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38998460769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31817865371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25771045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22747659683228</t>
+    <t xml:space="preserve">3.38998436927795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31817841529846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25771069526672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2274763584137</t>
   </si>
   <si>
     <t xml:space="preserve">3.18590497970581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24637293815613</t>
+    <t xml:space="preserve">3.24637317657471</t>
   </si>
   <si>
     <t xml:space="preserve">3.17456698417664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14055418968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17834663391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09142422676086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08008599281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04607319831848</t>
+    <t xml:space="preserve">3.14055442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17834639549255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09142398834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08008575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0460729598999</t>
   </si>
   <si>
     <t xml:space="preserve">3.01583886146545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9402539730072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95537066459656</t>
+    <t xml:space="preserve">2.94025373458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95537090301514</t>
   </si>
   <si>
     <t xml:space="preserve">2.92513704299927</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">2.7890841960907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77018761634827</t>
+    <t xml:space="preserve">2.77018785476685</t>
   </si>
   <si>
     <t xml:space="preserve">2.75129151344299</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">2.71727848052979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72105765342712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67948579788208</t>
+    <t xml:space="preserve">2.72105741500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67948603630066</t>
   </si>
   <si>
     <t xml:space="preserve">2.55477094650269</t>
@@ -2177,43 +2177,43 @@
     <t xml:space="preserve">2.55099153518677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61523914337158</t>
+    <t xml:space="preserve">2.61523866653442</t>
   </si>
   <si>
     <t xml:space="preserve">2.69838213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98938393592834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5373752117157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62807679176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63563561439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57894730567932</t>
+    <t xml:space="preserve">2.98938417434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53737473487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62807703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63563537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57894706726074</t>
   </si>
   <si>
     <t xml:space="preserve">3.56382966041565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50714111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48446559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52225780487061</t>
+    <t xml:space="preserve">3.50714039802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48446536064148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52225828170776</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643881797791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12543749809265</t>
+    <t xml:space="preserve">3.12543725967407</t>
   </si>
   <si>
     <t xml:space="preserve">3.80948066711426</t>
@@ -2222,16 +2222,16 @@
     <t xml:space="preserve">3.76035046577454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64319396018982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68476557731628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74901294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79436421394348</t>
+    <t xml:space="preserve">3.64319372177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68476533889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74901247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79436373710632</t>
   </si>
   <si>
     <t xml:space="preserve">3.7565712928772</t>
@@ -2240,10 +2240,10 @@
     <t xml:space="preserve">3.77546739578247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76412987709045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15717077255249</t>
+    <t xml:space="preserve">3.76413011550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15717124938965</t>
   </si>
   <si>
     <t xml:space="preserve">4.11182022094727</t>
@@ -2258,28 +2258,28 @@
     <t xml:space="preserve">4.22718667984009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1252326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07817649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09386157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20365905761719</t>
+    <t xml:space="preserve">4.12523221969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07817602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08601903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09386110305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20365953445435</t>
   </si>
   <si>
     <t xml:space="preserve">4.26639986038208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27424240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25855731964111</t>
+    <t xml:space="preserve">4.27424192428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25855779647827</t>
   </si>
   <si>
     <t xml:space="preserve">4.36835479736328</t>
@@ -2300,22 +2300,22 @@
     <t xml:space="preserve">4.28992795944214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28208589553833</t>
+    <t xml:space="preserve">4.28208541870117</t>
   </si>
   <si>
     <t xml:space="preserve">4.19581604003906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03896331787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02327823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99974966049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00759315490723</t>
+    <t xml:space="preserve">4.03896379470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02327871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9997501373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00759267807007</t>
   </si>
   <si>
     <t xml:space="preserve">3.96053695678711</t>
@@ -2327,22 +2327,22 @@
     <t xml:space="preserve">4.05464887619019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93700933456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92132377624512</t>
+    <t xml:space="preserve">3.93700885772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92132329940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.01543521881104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07033395767212</t>
+    <t xml:space="preserve">4.07033443450928</t>
   </si>
   <si>
     <t xml:space="preserve">3.97622227668762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18797397613525</t>
+    <t xml:space="preserve">4.1879734992981</t>
   </si>
   <si>
     <t xml:space="preserve">4.24287223815918</t>
@@ -2351,397 +2351,397 @@
     <t xml:space="preserve">4.21150159835815</t>
   </si>
   <si>
+    <t xml:space="preserve">4.39188289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45462322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43109607696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42325305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38404035568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39972543716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33698415756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.360511302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46246576309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44678115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4389386177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47815179824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48599433898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50167942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56442070007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60363388061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62716150283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6350040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49383687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59579133987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66637516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68206024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72911643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64284658432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74480152130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8624415397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90949726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05850696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03497982025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99576616287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95655345916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94871091842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97223854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87028360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98008108139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0741925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05066537857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02713680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08987760543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19183254241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18399000167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10556316375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14477682113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23888826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21536064147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19967460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25457334518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30162954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01929378509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93302488327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79970026016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76048707962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76833009719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68990278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69774580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61147689819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53305053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50952196121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47030830383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55657768249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54873561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57226371765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52520751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54089260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51736497879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58010625839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8232274055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87812662124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8859691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78401470184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65853214263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77617216110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85459899902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94086837768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52122354507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66239070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73297500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89767026901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68591928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70160484313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59965038299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5369086265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906608581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17614698410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29378700256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7134313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4154109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89381170272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81538534164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9251823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84675598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72127389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5879487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61931943893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558786392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77163219451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.738609790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69733238220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63954496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79639768600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98627233505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95325088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07708168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11835956573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97801733016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06057119369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90371799468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96976184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87069654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82941961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62303447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40839338302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50745820999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56524658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58175754547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6478009223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61477947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57350158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51571369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3340950012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30932760238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38362693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16898632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2680516242981</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.39188241958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45462322235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43109560012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42325305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38403940200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39972496032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33698415756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36051177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46246671676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44678115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4389386177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47815179824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48599433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50167989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56442022323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60363388061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62716197967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63500452041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49383640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59579133987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66637468338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68206024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72911643981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64284706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74480199813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86244106292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90949726104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05850744247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03497982025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99576616287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95655298233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9487099647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97223901748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87028360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98008060455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0741925239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0506649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02713680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08987760543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19183254241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18399000167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10556364059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14477634429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23888778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21536016464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1996750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25457334518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3016300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01929426193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93302440643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79969930648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76048707962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76832962036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68990278244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69774580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61147689819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53305053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50952243804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47030878067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55657815933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54873514175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57226324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52520751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54089260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51736497879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58010625839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82322788238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87812662124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88596963882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7840142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70558834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65853261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77617216110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85459899902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94086790084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52122402191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66239070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73297500610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89767026901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68591928482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70160484313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59964990615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53690910339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906608581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17614698410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29378700256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71343088150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41541051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89381122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81538534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92518281936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84675550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72127389907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5879487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61931896209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77163219451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73861026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69733333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63954496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7963981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98627328872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95325088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312601089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07708215713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11835908889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97801733016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06057214736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9037184715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96976184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87069702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82942008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62303400039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40839385986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50745868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56524658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48269176483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58175754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64780044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54873561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61477851867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5735011100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51571369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33409452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30932807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38362693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16898632049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2680516242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39188289642334</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.46618127822876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42490434646606</t>
+    <t xml:space="preserve">4.42490482330322</t>
   </si>
   <si>
     <t xml:space="preserve">4.3753719329834</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">4.44967031478882</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34235048294067</t>
+    <t xml:space="preserve">4.34235000610352</t>
   </si>
   <si>
     <t xml:space="preserve">4.41664838790894</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">4.77988719940186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73035430908203</t>
+    <t xml:space="preserve">4.73035478591919</t>
   </si>
   <si>
     <t xml:space="preserve">4.82116460800171</t>
@@ -2804,22 +2804,22 @@
     <t xml:space="preserve">4.83767509460449</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78814220428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87895202636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60652351379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66431140899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81290864944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88720750808716</t>
+    <t xml:space="preserve">4.78814268112183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87895154953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60652303695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66431188583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81290912628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88720703125</t>
   </si>
   <si>
     <t xml:space="preserve">4.93673992156982</t>
@@ -2834,19 +2834,19 @@
     <t xml:space="preserve">5.16789197921753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23393583297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19265747070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22567939758301</t>
+    <t xml:space="preserve">5.23393535614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19265794754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22567987442017</t>
   </si>
   <si>
     <t xml:space="preserve">5.26695680618286</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27521228790283</t>
+    <t xml:space="preserve">5.27521181106567</t>
   </si>
   <si>
     <t xml:space="preserve">5.29172277450562</t>
@@ -2855,22 +2855,22 @@
     <t xml:space="preserve">5.30823373794556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36602163314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4320650100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47334241867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55589628219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41555404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48985290527344</t>
+    <t xml:space="preserve">5.36602210998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43206548690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4733419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5558967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41555452346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4898533821106</t>
   </si>
   <si>
     <t xml:space="preserve">5.46508693695068</t>
@@ -2888,16 +2888,16 @@
     <t xml:space="preserve">5.52287483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51461887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58891820907593</t>
+    <t xml:space="preserve">5.51461935043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58891868591309</t>
   </si>
   <si>
     <t xml:space="preserve">5.45683145523071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54764127731323</t>
+    <t xml:space="preserve">5.54764080047607</t>
   </si>
   <si>
     <t xml:space="preserve">5.68798303604126</t>
@@ -2909,13 +2909,13 @@
     <t xml:space="preserve">5.61368465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5971736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58066320419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65496158599854</t>
+    <t xml:space="preserve">5.59717416763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58066272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65496110916138</t>
   </si>
   <si>
     <t xml:space="preserve">5.77879285812378</t>
@@ -2927,22 +2927,22 @@
     <t xml:space="preserve">5.84483575820923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86134719848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89436817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81181478500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90262413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80355882644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73751592636108</t>
+    <t xml:space="preserve">5.86134624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89436864852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8118143081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90262460708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80355978012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73751544952393</t>
   </si>
   <si>
     <t xml:space="preserve">6.00168943405151</t>
@@ -2951,28 +2951,28 @@
     <t xml:space="preserve">6.30713939666748</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38969373703003</t>
+    <t xml:space="preserve">6.38969421386719</t>
   </si>
   <si>
     <t xml:space="preserve">6.39794874191284</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47224760055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43922662734985</t>
+    <t xml:space="preserve">6.47224807739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4392261505127</t>
   </si>
   <si>
     <t xml:space="preserve">6.45573663711548</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59607934951782</t>
+    <t xml:space="preserve">6.59607839584351</t>
   </si>
   <si>
     <t xml:space="preserve">6.52178049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57956886291504</t>
+    <t xml:space="preserve">6.57956838607788</t>
   </si>
   <si>
     <t xml:space="preserve">6.58782386779785</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">6.72816562652588</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67037773132324</t>
+    <t xml:space="preserve">6.6703782081604</t>
   </si>
   <si>
     <t xml:space="preserve">6.63735628128052</t>
@@ -2999,10 +2999,10 @@
     <t xml:space="preserve">6.79420852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73642158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68688917160034</t>
+    <t xml:space="preserve">6.73642110824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6868896484375</t>
   </si>
   <si>
     <t xml:space="preserve">6.53829145431519</t>
@@ -3023,10 +3023,10 @@
     <t xml:space="preserve">6.75293254852295</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78595352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96866750717163</t>
+    <t xml:space="preserve">6.78595399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96866703033447</t>
   </si>
   <si>
     <t xml:space="preserve">6.05122137069702</t>
@@ -3035,25 +3035,25 @@
     <t xml:space="preserve">5.64670610427856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8530912399292</t>
+    <t xml:space="preserve">5.85309171676636</t>
   </si>
   <si>
     <t xml:space="preserve">5.67972755432129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39904356002808</t>
+    <t xml:space="preserve">5.39904403686523</t>
   </si>
   <si>
     <t xml:space="preserve">5.38253259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66321706771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60542869567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7457709312439</t>
+    <t xml:space="preserve">5.66321659088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60542964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74577140808105</t>
   </si>
   <si>
     <t xml:space="preserve">5.83658075332642</t>
@@ -3068,19 +3068,19 @@
     <t xml:space="preserve">5.87785768508911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97692251205444</t>
+    <t xml:space="preserve">5.9769229888916</t>
   </si>
   <si>
     <t xml:space="preserve">5.91087913513184</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91913461685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63845109939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78704833984375</t>
+    <t xml:space="preserve">5.91913509368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63845014572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78704881668091</t>
   </si>
   <si>
     <t xml:space="preserve">5.94390106201172</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">5.9604115486145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8696026802063</t>
+    <t xml:space="preserve">5.86960220336914</t>
   </si>
   <si>
     <t xml:space="preserve">5.98917293548584</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">5.79011058807373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78145551681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57373857498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67759704589844</t>
+    <t xml:space="preserve">5.78145599365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57373905181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6775975227356</t>
   </si>
   <si>
     <t xml:space="preserve">5.76414585113525</t>
@@ -3134,76 +3134,76 @@
     <t xml:space="preserve">5.82472991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80742073059082</t>
+    <t xml:space="preserve">5.80742025375366</t>
   </si>
   <si>
     <t xml:space="preserve">5.86800479888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88531398773193</t>
+    <t xml:space="preserve">5.88531446456909</t>
   </si>
   <si>
     <t xml:space="preserve">5.87665939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9285888671875</t>
+    <t xml:space="preserve">5.92858839035034</t>
   </si>
   <si>
     <t xml:space="preserve">5.96320819854736</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94589805603027</t>
+    <t xml:space="preserve">5.94589853286743</t>
   </si>
   <si>
     <t xml:space="preserve">5.91993379592896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15361547470093</t>
+    <t xml:space="preserve">6.15361499786377</t>
   </si>
   <si>
     <t xml:space="preserve">6.22285461425781</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17092561721802</t>
+    <t xml:space="preserve">6.17092514038086</t>
   </si>
   <si>
     <t xml:space="preserve">6.28343868255615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25747394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24881839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24016427993774</t>
+    <t xml:space="preserve">6.25747346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24881887435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24016380310059</t>
   </si>
   <si>
     <t xml:space="preserve">6.2315092086792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2661280632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46519041061401</t>
+    <t xml:space="preserve">6.26612901687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46519088745117</t>
   </si>
   <si>
     <t xml:space="preserve">6.54308462142944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58635950088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56904935836792</t>
+    <t xml:space="preserve">6.58635902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56904983520508</t>
   </si>
   <si>
     <t xml:space="preserve">6.6382884979248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56039428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57770395278931</t>
+    <t xml:space="preserve">6.56039381027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57770442962646</t>
   </si>
   <si>
     <t xml:space="preserve">6.62097835540771</t>
@@ -3218,19 +3218,19 @@
     <t xml:space="preserve">6.73349189758301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64694309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50846481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66425275802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11034107208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30940294265747</t>
+    <t xml:space="preserve">6.64694261550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50846529006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66425228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11034059524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30940341949463</t>
   </si>
   <si>
     <t xml:space="preserve">6.37864208221436</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">6.49115562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49981069564819</t>
+    <t xml:space="preserve">6.49981021881104</t>
   </si>
   <si>
     <t xml:space="preserve">6.55173969268799</t>
@@ -3254,16 +3254,16 @@
     <t xml:space="preserve">6.70752716064453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68156242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60366916656494</t>
+    <t xml:space="preserve">6.68156290054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60366868972778</t>
   </si>
   <si>
     <t xml:space="preserve">6.51712036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6296329498291</t>
+    <t xml:space="preserve">6.62963342666626</t>
   </si>
   <si>
     <t xml:space="preserve">6.74214696884155</t>
@@ -3275,28 +3275,28 @@
     <t xml:space="preserve">6.79407596588135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85466051101685</t>
+    <t xml:space="preserve">6.85466003417969</t>
   </si>
   <si>
     <t xml:space="preserve">6.61232376098633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7854208946228</t>
+    <t xml:space="preserve">6.78542137145996</t>
   </si>
   <si>
     <t xml:space="preserve">6.77676630020142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7508020401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52577447891235</t>
+    <t xml:space="preserve">6.75080156326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52577495574951</t>
   </si>
   <si>
     <t xml:space="preserve">6.42191648483276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45653629302979</t>
+    <t xml:space="preserve">6.45653581619263</t>
   </si>
   <si>
     <t xml:space="preserve">6.71618270874023</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">6.92389917373657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01044845581055</t>
+    <t xml:space="preserve">7.01044797897339</t>
   </si>
   <si>
     <t xml:space="preserve">7.05372142791748</t>
@@ -3326,16 +3326,16 @@
     <t xml:space="preserve">6.9931378364563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00179290771484</t>
+    <t xml:space="preserve">7.001793384552</t>
   </si>
   <si>
     <t xml:space="preserve">7.02775764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97582912445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95851898193359</t>
+    <t xml:space="preserve">6.97582864761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95851850509644</t>
   </si>
   <si>
     <t xml:space="preserve">6.94986343383789</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">7.07103204727173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06237745285034</t>
+    <t xml:space="preserve">7.06237697601318</t>
   </si>
   <si>
     <t xml:space="preserve">7.11430644989014</t>
@@ -3359,28 +3359,28 @@
     <t xml:space="preserve">7.04506778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13161563873291</t>
+    <t xml:space="preserve">7.13161611557007</t>
   </si>
   <si>
     <t xml:space="preserve">7.18354558944702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1575813293457</t>
+    <t xml:space="preserve">7.15758085250854</t>
   </si>
   <si>
     <t xml:space="preserve">7.07968711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88927936553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86331510543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93255376815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91524457931519</t>
+    <t xml:space="preserve">6.88927984237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86331462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93255424499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91524410247803</t>
   </si>
   <si>
     <t xml:space="preserve">6.94120931625366</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">6.96717357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17489051818848</t>
+    <t xml:space="preserve">7.17489004135132</t>
   </si>
   <si>
     <t xml:space="preserve">7.27009391784668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20085477828979</t>
+    <t xml:space="preserve">7.20085430145264</t>
   </si>
   <si>
     <t xml:space="preserve">7.22681999206543</t>
@@ -3404,13 +3404,13 @@
     <t xml:space="preserve">7.16623544692993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0883412361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14027118682861</t>
+    <t xml:space="preserve">7.14892625808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08834171295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14027070999146</t>
   </si>
   <si>
     <t xml:space="preserve">7.26143932342529</t>
@@ -3419,31 +3419,31 @@
     <t xml:space="preserve">7.31336784362793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33933305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42588186264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44319248199463</t>
+    <t xml:space="preserve">7.33933258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42588138580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44319200515747</t>
   </si>
   <si>
     <t xml:space="preserve">7.48646545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23547410964966</t>
+    <t xml:space="preserve">7.23547458648682</t>
   </si>
   <si>
     <t xml:space="preserve">7.29605865478516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19220066070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45184564590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38260793685913</t>
+    <t xml:space="preserve">7.19220113754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4518461227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38260746002197</t>
   </si>
   <si>
     <t xml:space="preserve">7.3566427230835</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">7.52108478546143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84997034072876</t>
+    <t xml:space="preserve">7.84997081756592</t>
   </si>
   <si>
     <t xml:space="preserve">7.72880268096924</t>
@@ -3461,40 +3461,40 @@
     <t xml:space="preserve">7.76342248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53839540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55570411682129</t>
+    <t xml:space="preserve">7.53839588165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55570507049561</t>
   </si>
   <si>
     <t xml:space="preserve">7.46050119400024</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40857267379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63359880447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72014760971069</t>
+    <t xml:space="preserve">7.40857219696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63359785079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72014713287354</t>
   </si>
   <si>
     <t xml:space="preserve">7.88458967208862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77207660675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65090847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66821813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78073072433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83266162872314</t>
+    <t xml:space="preserve">7.77207612991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65090894699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6682186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78073120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83266115188599</t>
   </si>
   <si>
     <t xml:space="preserve">7.82400560379028</t>
@@ -3503,16 +3503,16 @@
     <t xml:space="preserve">7.75476741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7028374671936</t>
+    <t xml:space="preserve">7.70283794403076</t>
   </si>
   <si>
     <t xml:space="preserve">7.69418334960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67687320709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94517374038696</t>
+    <t xml:space="preserve">7.67687273025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94517469406128</t>
   </si>
   <si>
     <t xml:space="preserve">8.01441287994385</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">8.11827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05768775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12692737579346</t>
+    <t xml:space="preserve">8.05768871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12692642211914</t>
   </si>
   <si>
     <t xml:space="preserve">8.0663423538208</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">8.10961627960205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17885494232178</t>
+    <t xml:space="preserve">8.17885589599609</t>
   </si>
   <si>
     <t xml:space="preserve">8.17020034790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20481967926025</t>
+    <t xml:space="preserve">8.20482063293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.07499694824219</t>
@@ -3554,13 +3554,13 @@
     <t xml:space="preserve">8.00575828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99710369110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87593555450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30867862701416</t>
+    <t xml:space="preserve">7.99710321426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87593650817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30867958068848</t>
   </si>
   <si>
     <t xml:space="preserve">8.24809455871582</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">8.27406024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41253757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.576979637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5856351852417</t>
+    <t xml:space="preserve">8.41253662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57698059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58563423156738</t>
   </si>
   <si>
     <t xml:space="preserve">8.65487384796143</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">8.54236030578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62025451660156</t>
+    <t xml:space="preserve">8.62025356292725</t>
   </si>
   <si>
     <t xml:space="preserve">8.81066226959229</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">8.70680332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87990188598633</t>
+    <t xml:space="preserve">8.87990093231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.834641456604</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">8.93421173095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86179637908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.753173828125</t>
+    <t xml:space="preserve">8.86179733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75317478179932</t>
   </si>
   <si>
     <t xml:space="preserve">8.72601890563965</t>
@@ -3629,22 +3629,22 @@
     <t xml:space="preserve">8.80748558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85274410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77127742767334</t>
+    <t xml:space="preserve">8.85274505615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77127838134766</t>
   </si>
   <si>
     <t xml:space="preserve">8.68981170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69886302947998</t>
+    <t xml:space="preserve">8.69886207580566</t>
   </si>
   <si>
     <t xml:space="preserve">8.73507022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59929275512695</t>
+    <t xml:space="preserve">8.59929180145264</t>
   </si>
   <si>
     <t xml:space="preserve">8.56308460235596</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">8.08333492279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27342414855957</t>
+    <t xml:space="preserve">8.27342510223389</t>
   </si>
   <si>
     <t xml:space="preserve">8.42730712890625</t>
@@ -3683,10 +3683,10 @@
     <t xml:space="preserve">8.4906702041626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40015125274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58118724822998</t>
+    <t xml:space="preserve">8.40015029907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5811882019043</t>
   </si>
   <si>
     <t xml:space="preserve">8.40920257568359</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">8.41825485229492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60834503173828</t>
+    <t xml:space="preserve">8.60834407806396</t>
   </si>
   <si>
     <t xml:space="preserve">8.48161697387695</t>
@@ -3710,16 +3710,16 @@
     <t xml:space="preserve">8.68075942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65360355377197</t>
+    <t xml:space="preserve">8.65360450744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.870849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02473068237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91610908508301</t>
+    <t xml:space="preserve">9.02473163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91610813140869</t>
   </si>
   <si>
     <t xml:space="preserve">8.98852348327637</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">9.08809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01567935943604</t>
+    <t xml:space="preserve">9.01567840576172</t>
   </si>
   <si>
     <t xml:space="preserve">9.04283428192139</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">9.16050910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79843425750732</t>
+    <t xml:space="preserve">8.79843330383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.36394309997559</t>
@@ -3752,16 +3752,16 @@
     <t xml:space="preserve">8.29152774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23721694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26437282562256</t>
+    <t xml:space="preserve">8.23721790313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26437187194824</t>
   </si>
   <si>
     <t xml:space="preserve">8.47256565093994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97947216033936</t>
+    <t xml:space="preserve">8.97947120666504</t>
   </si>
   <si>
     <t xml:space="preserve">8.89800453186035</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">9.14240550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34154605865479</t>
+    <t xml:space="preserve">9.3415470123291</t>
   </si>
   <si>
     <t xml:space="preserve">9.28723621368408</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">9.19671630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2510290145874</t>
+    <t xml:space="preserve">9.25102806091309</t>
   </si>
   <si>
     <t xml:space="preserve">9.12430191040039</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">9.21482086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35965156555176</t>
+    <t xml:space="preserve">9.35965061187744</t>
   </si>
   <si>
     <t xml:space="preserve">9.17861366271973</t>
@@ -3818,10 +3818,10 @@
     <t xml:space="preserve">9.10619831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30533885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50448036193848</t>
+    <t xml:space="preserve">9.30533981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50448131561279</t>
   </si>
   <si>
     <t xml:space="preserve">9.65504741668701</t>
@@ -3897,9 +3897,6 @@
   </si>
   <si>
     <t xml:space="preserve">9.5797643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50448131561279</t>
   </si>
   <si>
     <t xml:space="preserve">9.46683979034424</t>
@@ -46743,7 +46740,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1620" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46769,7 +46766,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1621" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46795,7 +46792,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1622" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46821,7 +46818,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1623" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46847,7 +46844,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1624" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46873,7 +46870,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1625" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46899,7 +46896,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1626" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46925,7 +46922,7 @@
         <v>6</v>
       </c>
       <c r="G1627" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46951,7 +46948,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1628" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46977,7 +46974,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1629" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47003,7 +47000,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1630" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -47029,7 +47026,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1631" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47055,7 +47052,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1632" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47081,7 +47078,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1633" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47107,7 +47104,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1634" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47133,7 +47130,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1635" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47159,7 +47156,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1636" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47185,7 +47182,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1637" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47211,7 +47208,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1638" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47237,7 +47234,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1639" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47263,7 +47260,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1640" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47289,7 +47286,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1641" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47315,7 +47312,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1642" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47341,7 +47338,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1643" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47367,7 +47364,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1644" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47393,7 +47390,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1645" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47419,7 +47416,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1646" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47445,7 +47442,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1647" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47471,7 +47468,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1648" t="s">
-        <v>898</v>
+        <v>840</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47549,7 +47546,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1651" t="s">
-        <v>898</v>
+        <v>840</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47913,7 +47910,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1665" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47939,7 +47936,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1666" t="s">
-        <v>898</v>
+        <v>840</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47965,7 +47962,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1667" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47991,7 +47988,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1668" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48173,7 +48170,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1675" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48199,7 +48196,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1676" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48277,7 +48274,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1679" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48303,7 +48300,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1680" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48381,7 +48378,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1683" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48459,7 +48456,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1686" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48485,7 +48482,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1687" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48641,7 +48638,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1693" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -48693,7 +48690,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1695" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48745,7 +48742,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1697" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48823,7 +48820,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1700" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48927,7 +48924,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1704" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48953,7 +48950,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1705" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -49031,7 +49028,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1708" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -49083,7 +49080,7 @@
         <v>6</v>
       </c>
       <c r="G1710" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49161,7 +49158,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1713" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49265,7 +49262,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1717" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49369,7 +49366,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1721" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49473,7 +49470,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1725" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49551,7 +49548,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1728" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49603,7 +49600,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1730" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -49733,7 +49730,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1735" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49759,7 +49756,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1736" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -49837,7 +49834,7 @@
         <v>6</v>
       </c>
       <c r="G1739" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -63591,7 +63588,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>1295</v>
+        <v>1269</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63617,7 +63614,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2269" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63643,7 +63640,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2270" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63669,7 +63666,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2271" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63695,7 +63692,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2272" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63747,7 +63744,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2274" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63877,7 +63874,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2279" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63903,7 +63900,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2280" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63929,7 +63926,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2281" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63955,7 +63952,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2282" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63981,7 +63978,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2283" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64007,7 +64004,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64059,7 +64056,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2286" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64111,7 +64108,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2288" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64137,7 +64134,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2289" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64163,7 +64160,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2290" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64215,7 +64212,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2292" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64241,7 +64238,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2293" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64267,7 +64264,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2294" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64293,7 +64290,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2295" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64319,7 +64316,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2296" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64345,7 +64342,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2297" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64371,7 +64368,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2298" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64397,7 +64394,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2299" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64423,7 +64420,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2300" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64449,7 +64446,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2301" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64475,7 +64472,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2302" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64501,7 +64498,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2303" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64527,7 +64524,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2304" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64553,7 +64550,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2305" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64579,7 +64576,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2306" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64605,7 +64602,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64631,7 +64628,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2308" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64657,7 +64654,7 @@
         <v>11.5</v>
       </c>
       <c r="G2309" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64683,7 +64680,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2310" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64709,7 +64706,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2311" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64735,7 +64732,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2312" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64761,7 +64758,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2313" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64787,7 +64784,7 @@
         <v>11.5</v>
       </c>
       <c r="G2314" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64813,7 +64810,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2315" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64839,7 +64836,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2316" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64865,7 +64862,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2317" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64891,7 +64888,7 @@
         <v>12</v>
       </c>
       <c r="G2318" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64917,7 +64914,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2319" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64943,7 +64940,7 @@
         <v>12</v>
       </c>
       <c r="G2320" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64969,7 +64966,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2321" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64995,7 +64992,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2322" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65021,7 +65018,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2323" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65047,7 +65044,7 @@
         <v>12</v>
       </c>
       <c r="G2324" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65073,7 +65070,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2325" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65099,7 +65096,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2326" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65125,7 +65122,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2327" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65151,7 +65148,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2328" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65177,7 +65174,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2329" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65203,7 +65200,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2330" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65229,7 +65226,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2331" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65255,7 +65252,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2332" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65281,7 +65278,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2333" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65307,7 +65304,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2334" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65333,7 +65330,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65359,7 +65356,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65385,7 +65382,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2337" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65411,7 +65408,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2338" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65437,7 +65434,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2339" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65463,7 +65460,7 @@
         <v>12.5</v>
       </c>
       <c r="G2340" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65489,7 +65486,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2341" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65515,7 +65512,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65541,7 +65538,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2343" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65567,7 +65564,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2344" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65593,7 +65590,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2345" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65619,7 +65616,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2346" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65645,7 +65642,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2347" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65671,7 +65668,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2348" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65697,7 +65694,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2349" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65723,7 +65720,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2350" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65749,7 +65746,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2351" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65775,7 +65772,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2352" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65801,7 +65798,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2353" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65827,7 +65824,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2354" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65853,7 +65850,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2355" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65879,7 +65876,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2356" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65905,7 +65902,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2357" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65931,7 +65928,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2358" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65957,7 +65954,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2359" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65983,7 +65980,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2360" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66009,7 +66006,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2361" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66035,7 +66032,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2362" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66061,7 +66058,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2363" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66087,7 +66084,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2364" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66113,7 +66110,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2365" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66139,7 +66136,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2366" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66165,7 +66162,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2367" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66191,7 +66188,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G2368" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66217,7 +66214,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2369" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66243,7 +66240,7 @@
         <v>12</v>
       </c>
       <c r="G2370" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66269,7 +66266,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2371" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66295,7 +66292,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2372" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66321,7 +66318,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2373" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66347,7 +66344,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2374" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66373,7 +66370,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2375" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66399,7 +66396,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2376" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66425,7 +66422,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66451,7 +66448,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2378" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66477,7 +66474,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2379" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66503,7 +66500,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2380" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66529,7 +66526,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2381" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66555,7 +66552,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2382" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66581,7 +66578,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2383" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66607,7 +66604,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2384" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66633,7 +66630,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2385" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66659,7 +66656,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2386" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66685,7 +66682,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2387" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66711,7 +66708,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2388" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66737,7 +66734,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2389" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66763,7 +66760,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2390" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66789,7 +66786,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2391" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66815,7 +66812,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2392" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66841,7 +66838,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2393" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66867,7 +66864,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2394" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66893,7 +66890,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2395" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66919,7 +66916,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2396" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66945,7 +66942,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2397" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66971,7 +66968,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2398" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66997,7 +66994,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2399" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67023,7 +67020,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2400" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67049,7 +67046,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2401" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67075,7 +67072,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2402" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67101,7 +67098,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67127,7 +67124,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67153,7 +67150,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2405" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67179,7 +67176,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2406" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67205,7 +67202,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67231,7 +67228,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2408" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67257,7 +67254,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67283,7 +67280,7 @@
         <v>12.5</v>
       </c>
       <c r="G2410" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67309,7 +67306,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2411" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67335,7 +67332,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67361,7 +67358,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2413" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67387,7 +67384,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2414" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67413,7 +67410,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2415" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67439,7 +67436,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67465,7 +67462,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2417" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67491,7 +67488,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2418" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67517,7 +67514,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67543,7 +67540,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2420" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67569,7 +67566,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2421" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67595,7 +67592,7 @@
         <v>13</v>
       </c>
       <c r="G2422" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67621,7 +67618,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67647,7 +67644,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G2424" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67673,7 +67670,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2425" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67699,7 +67696,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2426" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67725,7 +67722,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67751,7 +67748,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2428" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67777,7 +67774,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2429" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67803,7 +67800,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2430" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67829,7 +67826,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2431" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67855,7 +67852,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2432" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67881,7 +67878,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2433" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67907,7 +67904,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2434" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67933,7 +67930,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2435" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67959,7 +67956,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2436" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67985,7 +67982,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2437" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68011,7 +68008,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2438" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68037,7 +68034,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2439" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68063,7 +68060,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2440" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68089,7 +68086,7 @@
         <v>13.5</v>
       </c>
       <c r="G2441" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68115,7 +68112,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2442" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68141,7 +68138,7 @@
         <v>13.5</v>
       </c>
       <c r="G2443" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68167,7 +68164,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2444" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68193,7 +68190,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68219,7 +68216,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2446" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68245,7 +68242,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2447" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68271,7 +68268,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2448" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68297,7 +68294,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2449" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68323,7 +68320,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2450" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68349,7 +68346,7 @@
         <v>14</v>
       </c>
       <c r="G2451" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68375,7 +68372,7 @@
         <v>14</v>
       </c>
       <c r="G2452" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68401,7 +68398,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2453" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68427,7 +68424,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2454" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68453,7 +68450,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2455" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68479,7 +68476,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2456" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68505,7 +68502,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2457" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68531,7 +68528,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2458" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68557,7 +68554,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G2459" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68583,7 +68580,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2460" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68609,7 +68606,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G2461" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68635,7 +68632,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2462" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68661,7 +68658,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G2463" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68687,7 +68684,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2464" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68713,7 +68710,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G2465" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68739,7 +68736,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2466" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68765,7 +68762,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2467" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68791,7 +68788,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68817,7 +68814,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2469" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68843,7 +68840,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68869,7 +68866,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68895,7 +68892,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2472" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68921,7 +68918,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2473" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68947,7 +68944,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2474" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68973,7 +68970,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68999,7 +68996,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G2476" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69025,7 +69022,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69051,7 +69048,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69077,7 +69074,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69103,7 +69100,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2480" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69129,7 +69126,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2481" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69155,7 +69152,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69181,7 +69178,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2483" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69207,7 +69204,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2484" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69233,7 +69230,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2485" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69259,7 +69256,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2486" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69267,7 +69264,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6493981481</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>489641</v>
@@ -69285,9 +69282,35 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G2487" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6496412037</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>97738</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>13.5799999237061</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>13.3199996948242</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>13.460000038147</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>13.3199996948242</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="1428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1429" uniqueCount="1429">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49119520187378</t>
+    <t xml:space="preserve">4.49119472503662</t>
   </si>
   <si>
     <t xml:space="preserve">CE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52814531326294</t>
+    <t xml:space="preserve">4.52814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">4.46432113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30644035339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26613092422485</t>
+    <t xml:space="preserve">4.30644083023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26613140106201</t>
   </si>
   <si>
     <t xml:space="preserve">4.31315898895264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31987762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36690616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27284955978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2358980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05114603042603</t>
+    <t xml:space="preserve">4.3198766708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3669056892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27284908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23589849472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05114507675171</t>
   </si>
   <si>
     <t xml:space="preserve">4.08473634719849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74210166931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9167788028717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03099012374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15527963638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12840557098389</t>
+    <t xml:space="preserve">3.74210262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91677904129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03098964691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15527868270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12840509414673</t>
   </si>
   <si>
     <t xml:space="preserve">4.01419401168823</t>
@@ -98,136 +98,136 @@
     <t xml:space="preserve">4.12504625320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12168741226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9470112323761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80256748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83615899085999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86975026130676</t>
+    <t xml:space="preserve">4.12168788909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94701099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80256700515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83615946769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86975073814392</t>
   </si>
   <si>
     <t xml:space="preserve">3.58086252212524</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42970037460327</t>
+    <t xml:space="preserve">3.42970108985901</t>
   </si>
   <si>
     <t xml:space="preserve">3.75217986106873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60773611068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84959506988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670132637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96716547012329</t>
+    <t xml:space="preserve">3.60773587226868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84959483146667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9067006111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96716642379761</t>
   </si>
   <si>
     <t xml:space="preserve">4.06458139419556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8294403553009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7723343372345</t>
+    <t xml:space="preserve">3.82944059371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77233457565308</t>
   </si>
   <si>
     <t xml:space="preserve">3.90334177017212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87982773780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72866582870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79584932327271</t>
+    <t xml:space="preserve">3.87982821464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72866606712341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79584884643555</t>
   </si>
   <si>
     <t xml:space="preserve">3.88318705558777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95708799362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13176488876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19558811187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18551111221313</t>
+    <t xml:space="preserve">3.95708823204041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13176441192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1955885887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18551206588745</t>
   </si>
   <si>
     <t xml:space="preserve">4.13848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22246217727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29972219467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35682916641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25605392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27956819534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14856052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32659578323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26949024200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16535615921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09817266464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04778575897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04106760025024</t>
+    <t xml:space="preserve">4.22246265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29972267150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35682821273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25605297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27956771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14856100082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3265962600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26949071884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16535711288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09817314147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04778528213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0410680770874</t>
   </si>
   <si>
     <t xml:space="preserve">3.93021535873413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91006016731262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81936311721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75889778137207</t>
+    <t xml:space="preserve">3.91006064414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81936287879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75889801979065</t>
   </si>
   <si>
     <t xml:space="preserve">3.71186995506287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93357419967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82608199119568</t>
+    <t xml:space="preserve">3.93357467651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82608151435852</t>
   </si>
   <si>
     <t xml:space="preserve">4.08137702941895</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">4.15863847732544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17879295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21238422393799</t>
+    <t xml:space="preserve">4.17879247665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21238374710083</t>
   </si>
   <si>
     <t xml:space="preserve">4.21574354171753</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">4.30308151245117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3534688949585</t>
+    <t xml:space="preserve">4.35346937179565</t>
   </si>
   <si>
     <t xml:space="preserve">4.19894790649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07465887069702</t>
+    <t xml:space="preserve">4.07465934753418</t>
   </si>
   <si>
     <t xml:space="preserve">4.08809566497803</t>
@@ -266,76 +266,76 @@
     <t xml:space="preserve">4.06122255325317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02427101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693375587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21649026870728</t>
+    <t xml:space="preserve">4.0242714881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693327903748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21648931503296</t>
   </si>
   <si>
     <t xml:space="preserve">4.14420700073242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19927930831909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25435209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23370027542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23714208602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49185276031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49873685836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47119998931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45743131637573</t>
+    <t xml:space="preserve">4.19927883148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25435161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23369979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23714160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49185228347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4987359046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47120046615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45743179321289</t>
   </si>
   <si>
     <t xml:space="preserve">4.46431636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37826538085938</t>
+    <t xml:space="preserve">4.37826490402222</t>
   </si>
   <si>
     <t xml:space="preserve">4.31975030899048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3713812828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28188848495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42989540100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34040212631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35072898864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25090980529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03750419616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91703271865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98243141174316</t>
+    <t xml:space="preserve">4.37138080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28188800811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42989635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34040260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3507285118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25091028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03750276565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91703319549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98243117332458</t>
   </si>
   <si>
     <t xml:space="preserve">3.86884427070618</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">4.13732290267944</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3369607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38170719146729</t>
+    <t xml:space="preserve">4.33696126937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38170671463013</t>
   </si>
   <si>
     <t xml:space="preserve">4.42301177978516</t>
@@ -356,103 +356,103 @@
     <t xml:space="preserve">4.52971410751343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74148917198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7518150806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73116254806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84130764007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65199613571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52464079856873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42826414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50743126869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65887999534607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75525760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82065582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78623604774475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96522116661072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9514524936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04094552993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01341009140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94456887245178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98931550979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95833706855774</t>
+    <t xml:space="preserve">3.74148941040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181484222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73116326332092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84130811691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65199637413025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52464032173157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42826461791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50743079185486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65888094902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75525736808777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82065653800964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78623509407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670704841614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9652214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95145344734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0409460067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01340961456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94456839561462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98931527137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95833730697632</t>
   </si>
   <si>
     <t xml:space="preserve">3.79656171798706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90326452255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80000329017639</t>
+    <t xml:space="preserve">3.90326476097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80000305175781</t>
   </si>
   <si>
     <t xml:space="preserve">3.68641662597656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70018458366394</t>
+    <t xml:space="preserve">3.70018482208252</t>
   </si>
   <si>
     <t xml:space="preserve">3.76558327674866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70362710952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66576457023621</t>
+    <t xml:space="preserve">3.70362687110901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66576409339905</t>
   </si>
   <si>
     <t xml:space="preserve">3.66920638084412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55217695236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48677897453308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47989392280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37319183349609</t>
+    <t xml:space="preserve">3.5521776676178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48677849769592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47989439964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37319207191467</t>
   </si>
   <si>
     <t xml:space="preserve">3.37181448936462</t>
@@ -461,52 +461,52 @@
     <t xml:space="preserve">3.50054693222046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68985939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561923980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45235824584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47645258903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64511275291443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72083687782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7070689201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77935171127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80688786506653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61413431167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757564544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57971358299255</t>
+    <t xml:space="preserve">3.68985867500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561947822571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45235848426819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47645235061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64511227607727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72083711624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706915855408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77935147285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80688762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61413383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757636070251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57971334457397</t>
   </si>
   <si>
     <t xml:space="preserve">3.56594562530518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49366235733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49022078514099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4489164352417</t>
+    <t xml:space="preserve">3.4936625957489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49022126197815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44891667366028</t>
   </si>
   <si>
     <t xml:space="preserve">3.63822793960571</t>
@@ -515,133 +515,133 @@
     <t xml:space="preserve">3.49710488319397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38695979118347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35804629325867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37456870079041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31123495101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3263795375824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35529255867004</t>
+    <t xml:space="preserve">3.38696026802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35804653167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37456893920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31123518943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32637977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3552930355072</t>
   </si>
   <si>
     <t xml:space="preserve">3.41587257385254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51431465148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48333692550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51087284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51775670051575</t>
+    <t xml:space="preserve">3.51431512832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48333644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51087260246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51775693893433</t>
   </si>
   <si>
     <t xml:space="preserve">3.47301054000854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57627201080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53496718406677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64855480194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67953252792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59692358970642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6416699886322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63134384155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56250333786011</t>
+    <t xml:space="preserve">3.57627177238464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53496742248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64855432510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67953276634216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59692430496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64166951179504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63134431838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56250357627869</t>
   </si>
   <si>
     <t xml:space="preserve">3.53152561187744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4558002948761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41174221038818</t>
+    <t xml:space="preserve">3.45580077171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41174244880676</t>
   </si>
   <si>
     <t xml:space="preserve">3.4296407699585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45924258232117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44203233718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52808308601379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63478589057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67609047889709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62790155410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58659720420837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54529333114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55906128883362</t>
+    <t xml:space="preserve">3.45924305915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4420325756073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52808284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63478636741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67609071731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62790250778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58659768104553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54529309272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55906200408936</t>
   </si>
   <si>
     <t xml:space="preserve">3.56938743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71739506721497</t>
+    <t xml:space="preserve">3.71739482879639</t>
   </si>
   <si>
     <t xml:space="preserve">3.94112658500671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00996828079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88605427742004</t>
+    <t xml:space="preserve">4.00996780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88605451583862</t>
   </si>
   <si>
     <t xml:space="preserve">3.97210550308228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83442330360413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92735862731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98587322235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0547137260437</t>
+    <t xml:space="preserve">3.83442449569702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92735815048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98587346076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05471420288086</t>
   </si>
   <si>
     <t xml:space="preserve">3.93080139160156</t>
@@ -650,58 +650,58 @@
     <t xml:space="preserve">4.04438781738281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06159830093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91014814376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89982271194458</t>
+    <t xml:space="preserve">4.06159782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91014838218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89982295036316</t>
   </si>
   <si>
     <t xml:space="preserve">4.05815601348877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07192373275757</t>
+    <t xml:space="preserve">4.07192420959473</t>
   </si>
   <si>
     <t xml:space="preserve">4.07880878448486</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0306191444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19583702087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20960521697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29565572738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27844619750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24746751785278</t>
+    <t xml:space="preserve">4.03061962127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19583749771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20960569381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29565620422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27844572067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2474684715271</t>
   </si>
   <si>
     <t xml:space="preserve">4.30254077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1269965171814</t>
+    <t xml:space="preserve">4.12699699401855</t>
   </si>
   <si>
     <t xml:space="preserve">4.13043880462646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.202721118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10634422302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12011289596558</t>
+    <t xml:space="preserve">4.20272159576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10634469985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12011337280273</t>
   </si>
   <si>
     <t xml:space="preserve">4.17862749099731</t>
@@ -710,70 +710,70 @@
     <t xml:space="preserve">4.2405834197998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14764928817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16141748428345</t>
+    <t xml:space="preserve">4.14764881134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16141700744629</t>
   </si>
   <si>
     <t xml:space="preserve">4.04783010482788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14076519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15109205245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15453338623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18206834793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15797472000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21304750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32319211959839</t>
+    <t xml:space="preserve">4.14076471328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15109062194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15453290939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18206930160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15797519683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21304655075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32319259643555</t>
   </si>
   <si>
     <t xml:space="preserve">4.36449718475342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43333768844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44022226333618</t>
+    <t xml:space="preserve">4.4333381652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44022130966187</t>
   </si>
   <si>
     <t xml:space="preserve">4.38514947891235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47464227676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41956949234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37482357025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41268444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34384489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30942440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36793899536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35417032241821</t>
+    <t xml:space="preserve">4.4746413230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4195704460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37482309341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41268491744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34384441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30942487716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36793947219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35417079925537</t>
   </si>
   <si>
     <t xml:space="preserve">4.28532981872559</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">4.52627229690552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40580081939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48841047286987</t>
+    <t xml:space="preserve">4.40580129623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48840999603271</t>
   </si>
   <si>
     <t xml:space="preserve">4.50906324386597</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">4.53659820556641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54348230361938</t>
+    <t xml:space="preserve">4.54348278045654</t>
   </si>
   <si>
     <t xml:space="preserve">4.447105884552</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">4.67083787918091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69899654388428</t>
+    <t xml:space="preserve">4.69899702072144</t>
   </si>
   <si>
     <t xml:space="preserve">4.80107259750366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7165961265564</t>
+    <t xml:space="preserve">4.71659517288208</t>
   </si>
   <si>
     <t xml:space="preserve">4.83627033233643</t>
@@ -827,22 +827,22 @@
     <t xml:space="preserve">4.78347301483154</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72011613845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68491744995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73067474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75179433822632</t>
+    <t xml:space="preserve">4.72011518478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68491697311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7306752204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75179481506348</t>
   </si>
   <si>
     <t xml:space="preserve">4.81515216827393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81163263320923</t>
+    <t xml:space="preserve">4.81163167953491</t>
   </si>
   <si>
     <t xml:space="preserve">4.9277868270874</t>
@@ -851,49 +851,49 @@
     <t xml:space="preserve">4.93834638595581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8749885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80811166763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80459213256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7869930267334</t>
+    <t xml:space="preserve">4.87498950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80811214447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8045916557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78699254989624</t>
   </si>
   <si>
     <t xml:space="preserve">4.95946502685547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86442947387695</t>
+    <t xml:space="preserve">4.86442995071411</t>
   </si>
   <si>
     <t xml:space="preserve">4.89258813858032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89610815048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97354555130005</t>
+    <t xml:space="preserve">4.89610767364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91370725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97354459762573</t>
   </si>
   <si>
     <t xml:space="preserve">4.97706460952759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94538593292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11081886291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25865316390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0615406036377</t>
+    <t xml:space="preserve">4.94538640975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1108193397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25865173339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06154155731201</t>
   </si>
   <si>
     <t xml:space="preserve">5.08618021011353</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">5.10377931594849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09673929214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05098152160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08969926834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01930284500122</t>
+    <t xml:space="preserve">5.09673881530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0509819984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08969974517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01930332183838</t>
   </si>
   <si>
     <t xml:space="preserve">5.04746150970459</t>
@@ -935,22 +935,22 @@
     <t xml:space="preserve">5.13193798065186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0404224395752</t>
+    <t xml:space="preserve">5.04042148590088</t>
   </si>
   <si>
     <t xml:space="preserve">5.1248984336853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20937442779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36424827575684</t>
+    <t xml:space="preserve">5.20937490463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36424732208252</t>
   </si>
   <si>
     <t xml:space="preserve">5.21289396286011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03690195083618</t>
+    <t xml:space="preserve">5.0369029045105</t>
   </si>
   <si>
     <t xml:space="preserve">5.16361665725708</t>
@@ -962,49 +962,49 @@
     <t xml:space="preserve">5.23049354553223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15305757522583</t>
+    <t xml:space="preserve">5.15305709838867</t>
   </si>
   <si>
     <t xml:space="preserve">5.20233488082886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11433887481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10729932785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00522327423096</t>
+    <t xml:space="preserve">5.11433839797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10729885101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00522375106812</t>
   </si>
   <si>
     <t xml:space="preserve">4.9981837272644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01226329803467</t>
+    <t xml:space="preserve">5.01226282119751</t>
   </si>
   <si>
     <t xml:space="preserve">5.04394197463989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06506109237671</t>
+    <t xml:space="preserve">5.06506061553955</t>
   </si>
   <si>
     <t xml:space="preserve">5.15657663345337</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34312915802002</t>
+    <t xml:space="preserve">5.34312868118286</t>
   </si>
   <si>
     <t xml:space="preserve">5.30089092254639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27977085113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30792951583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25161218643188</t>
+    <t xml:space="preserve">5.27977180480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30792999267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2516131401062</t>
   </si>
   <si>
     <t xml:space="preserve">5.29385089874268</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">5.29033088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33608865737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3466477394104</t>
+    <t xml:space="preserve">5.33608913421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34664869308472</t>
   </si>
   <si>
     <t xml:space="preserve">5.36776828765869</t>
@@ -1031,40 +1031,40 @@
     <t xml:space="preserve">5.39944648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26569223403931</t>
+    <t xml:space="preserve">5.26569271087646</t>
   </si>
   <si>
     <t xml:space="preserve">5.31145000457764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32553005218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28329086303711</t>
+    <t xml:space="preserve">5.3255295753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28329133987427</t>
   </si>
   <si>
     <t xml:space="preserve">5.23401355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21641397476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14249753952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16713666915894</t>
+    <t xml:space="preserve">5.21641445159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14249706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16713714599609</t>
   </si>
   <si>
     <t xml:space="preserve">5.31497001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29737091064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19177532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35720825195312</t>
+    <t xml:space="preserve">5.29737138748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19177484512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35720777511597</t>
   </si>
   <si>
     <t xml:space="preserve">5.07210063934326</t>
@@ -1073,88 +1073,88 @@
     <t xml:space="preserve">4.98410415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94186592102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86794948577881</t>
+    <t xml:space="preserve">4.94186639785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86794900894165</t>
   </si>
   <si>
     <t xml:space="preserve">4.92426681518555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98058414459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03338241577148</t>
+    <t xml:space="preserve">4.98058462142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03338193893433</t>
   </si>
   <si>
     <t xml:space="preserve">5.05450105667114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18473482131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17417573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21993446350098</t>
+    <t xml:space="preserve">5.18473529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17417621612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21993398666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.17769575119019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22697448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28681230545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02282190322876</t>
+    <t xml:space="preserve">5.22697401046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28681182861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02282285690308</t>
   </si>
   <si>
     <t xml:space="preserve">5.00170373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02986240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.058021068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92074632644653</t>
+    <t xml:space="preserve">5.02986288070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05802154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92074680328369</t>
   </si>
   <si>
     <t xml:space="preserve">4.99114370346069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37128734588623</t>
+    <t xml:space="preserve">5.37128782272339</t>
   </si>
   <si>
     <t xml:space="preserve">5.47688341140747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48392248153687</t>
+    <t xml:space="preserve">5.48392295837402</t>
   </si>
   <si>
     <t xml:space="preserve">5.44168424606323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43464517593384</t>
+    <t xml:space="preserve">5.43464469909668</t>
   </si>
   <si>
     <t xml:space="preserve">5.5261607170105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51208162307739</t>
+    <t xml:space="preserve">5.51208114624023</t>
   </si>
   <si>
     <t xml:space="preserve">5.46984338760376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40648555755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3783278465271</t>
+    <t xml:space="preserve">5.40648603439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37832736968994</t>
   </si>
   <si>
     <t xml:space="preserve">5.18825531005859</t>
@@ -1175,16 +1175,16 @@
     <t xml:space="preserve">5.24457263946533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22345352172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23753309249878</t>
+    <t xml:space="preserve">5.22345447540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23753356933594</t>
   </si>
   <si>
     <t xml:space="preserve">5.16009664535522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11785840988159</t>
+    <t xml:space="preserve">5.11785888671875</t>
   </si>
   <si>
     <t xml:space="preserve">4.97002506256104</t>
@@ -1193,43 +1193,43 @@
     <t xml:space="preserve">5.21899938583374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14661359786987</t>
+    <t xml:space="preserve">5.14661407470703</t>
   </si>
   <si>
     <t xml:space="preserve">4.98012685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94393444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81364107131958</t>
+    <t xml:space="preserve">4.94393491744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81364011764526</t>
   </si>
   <si>
     <t xml:space="preserve">4.84259510040283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85707187652588</t>
+    <t xml:space="preserve">4.85707235336304</t>
   </si>
   <si>
     <t xml:space="preserve">4.82087898254395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80640125274658</t>
+    <t xml:space="preserve">4.8064022064209</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029081344604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46618938446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21284055709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4517126083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37208795547485</t>
+    <t xml:space="preserve">4.46618986129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21284008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45171308517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37208843231201</t>
   </si>
   <si>
     <t xml:space="preserve">4.52409839630127</t>
@@ -1247,19 +1247,19 @@
     <t xml:space="preserve">4.39380407333374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45895099639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4372353553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53133678436279</t>
+    <t xml:space="preserve">4.45895147323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43723583221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53133726119995</t>
   </si>
   <si>
     <t xml:space="preserve">4.61096096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64715385437012</t>
+    <t xml:space="preserve">4.64715433120728</t>
   </si>
   <si>
     <t xml:space="preserve">4.69058513641357</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">4.57476806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58200693130493</t>
+    <t xml:space="preserve">4.58200645446777</t>
   </si>
   <si>
     <t xml:space="preserve">4.48790502548218</t>
@@ -1277,10 +1277,10 @@
     <t xml:space="preserve">4.54581356048584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58924531936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60372257232666</t>
+    <t xml:space="preserve">4.58924579620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6037220954895</t>
   </si>
   <si>
     <t xml:space="preserve">4.68334579467773</t>
@@ -1289,79 +1289,79 @@
     <t xml:space="preserve">4.6978235244751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62543821334839</t>
+    <t xml:space="preserve">4.62543773651123</t>
   </si>
   <si>
     <t xml:space="preserve">4.63267660140991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61819934844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56752967834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44447422027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42999696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59648370742798</t>
+    <t xml:space="preserve">4.61819982528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56752920150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44447374343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42999649047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59648323059082</t>
   </si>
   <si>
     <t xml:space="preserve">4.47342824935913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51685953140259</t>
+    <t xml:space="preserve">4.51685905456543</t>
   </si>
   <si>
     <t xml:space="preserve">4.50962162017822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1766471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10426187515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04635381698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0246376991272</t>
+    <t xml:space="preserve">4.17664766311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10426235198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04635334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02463817596436</t>
   </si>
   <si>
     <t xml:space="preserve">4.03187656402588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05359172821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0680685043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97396731376648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00292253494263</t>
+    <t xml:space="preserve">4.05359220504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06806898117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97396779060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00292205810547</t>
   </si>
   <si>
     <t xml:space="preserve">3.85091257095337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87262725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93053650856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92329835891724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11149978637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22731733322144</t>
+    <t xml:space="preserve">3.87262773513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93053603172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9232976436615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11150026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22731781005859</t>
   </si>
   <si>
     <t xml:space="preserve">4.20560169219971</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">4.22007894515991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23455572128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25627136230469</t>
+    <t xml:space="preserve">4.23455667495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25627183914185</t>
   </si>
   <si>
     <t xml:space="preserve">4.27798700332642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29970264434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36485004425049</t>
+    <t xml:space="preserve">4.2997031211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36484956741333</t>
   </si>
   <si>
     <t xml:space="preserve">4.35761117935181</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">4.26351022720337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09702348709106</t>
+    <t xml:space="preserve">4.09702301025391</t>
   </si>
   <si>
     <t xml:space="preserve">4.06083059310913</t>
@@ -1400,34 +1400,34 @@
     <t xml:space="preserve">4.12597703933716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90882158279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84367418289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78576493263245</t>
+    <t xml:space="preserve">3.90882062911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84367322921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78576517105103</t>
   </si>
   <si>
     <t xml:space="preserve">3.87986660003662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94501280784607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80748128890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72061848640442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68442535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57946634292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45641112327576</t>
+    <t xml:space="preserve">3.94501376152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80748152732849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72061800956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68442583084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57946681976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45641088485718</t>
   </si>
   <si>
     <t xml:space="preserve">3.55051231384277</t>
@@ -1436,76 +1436,76 @@
     <t xml:space="preserve">3.81471967697144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76404929161072</t>
+    <t xml:space="preserve">3.7640495300293</t>
   </si>
   <si>
     <t xml:space="preserve">3.82919645309448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83643555641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85815095901489</t>
+    <t xml:space="preserve">3.83643579483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85815048217773</t>
   </si>
   <si>
     <t xml:space="preserve">3.74233412742615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75681114196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70614147186279</t>
+    <t xml:space="preserve">3.75681161880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70614099502563</t>
   </si>
   <si>
     <t xml:space="preserve">3.6771867275238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63375568389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6699481010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61927819252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64099431037903</t>
+    <t xml:space="preserve">3.6337559223175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66994905471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61927890777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64099407196045</t>
   </si>
   <si>
     <t xml:space="preserve">3.7712881565094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80024290084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66270971298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7278573513031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86538934707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60480141639709</t>
+    <t xml:space="preserve">3.80024218559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66270923614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72785663604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86539030075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60480165481567</t>
   </si>
   <si>
     <t xml:space="preserve">3.58670496940613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57584691047668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54327344894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547132492065</t>
+    <t xml:space="preserve">3.57584714889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54327321052551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547108650208</t>
   </si>
   <si>
     <t xml:space="preserve">3.82195806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71338033676147</t>
+    <t xml:space="preserve">3.7133800983429</t>
   </si>
   <si>
     <t xml:space="preserve">3.69890260696411</t>
@@ -1517,121 +1517,121 @@
     <t xml:space="preserve">3.6265172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64823293685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52517747879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60118246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54689311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50346159934998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60842108726501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79300379753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88710451126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56498908996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59394407272339</t>
+    <t xml:space="preserve">3.64823269844055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5251772403717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60118222236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54689335823059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50346183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60842037200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79300355911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88710498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56499004364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59394311904907</t>
   </si>
   <si>
     <t xml:space="preserve">3.77852606773376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58308506011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53965449333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48174571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49622297286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45279169082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42021822929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43155574798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43533515930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41265988349915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33329510688782</t>
+    <t xml:space="preserve">3.58308529853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53965401649475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48174619674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49622321128845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45279145240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42021799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43155598640442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43533539772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41265964508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3332953453064</t>
   </si>
   <si>
     <t xml:space="preserve">3.34841251373291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38620519638062</t>
+    <t xml:space="preserve">3.38620495796204</t>
   </si>
   <si>
     <t xml:space="preserve">3.37108826637268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36352968215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3824257850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31062006950378</t>
+    <t xml:space="preserve">3.36352920532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38242530822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31062030792236</t>
   </si>
   <si>
     <t xml:space="preserve">3.32573699951172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29172396659851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393128395081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31439995765686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33707451820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.276606798172</t>
+    <t xml:space="preserve">3.29172372817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393080711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3143994808197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33707523345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27660703659058</t>
   </si>
   <si>
     <t xml:space="preserve">3.28038644790649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23503518104553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2048008441925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21613883972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23125600814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21235942840576</t>
+    <t xml:space="preserve">3.23503565788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20480132102966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21613907814026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23125624656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21235966682434</t>
   </si>
   <si>
     <t xml:space="preserve">3.24259352684021</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">3.18212580680847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13677501678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15189170837402</t>
+    <t xml:space="preserve">3.13677477836609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1518919467926</t>
   </si>
   <si>
     <t xml:space="preserve">3.18968415260315</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">3.20102190971375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25015258789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39376330375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59784245491028</t>
+    <t xml:space="preserve">3.25015234947205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39376354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59784293174744</t>
   </si>
   <si>
     <t xml:space="preserve">3.65831089019775</t>
@@ -1667,52 +1667,52 @@
     <t xml:space="preserve">3.55627083778381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55249190330505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56760859489441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57516765594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60540127754211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53359532356262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47690677642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59028387069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58272576332092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57138824462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52603673934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50336146354675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4391143321991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4277765750885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4202184677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40132212638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3673083782196</t>
+    <t xml:space="preserve">3.55249214172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56760835647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57516717910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60540103912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53359580039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4769070148468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5902841091156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58272552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57138800621033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52603721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50336170196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43911457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42777633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42021870613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40132164955139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36730885505676</t>
   </si>
   <si>
     <t xml:space="preserve">3.40888071060181</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">3.34085416793823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42399740219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51469969749451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49958229064941</t>
+    <t xml:space="preserve">3.42399764060974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51469945907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49958252906799</t>
   </si>
   <si>
     <t xml:space="preserve">3.54871273040771</t>
@@ -1745,64 +1745,64 @@
     <t xml:space="preserve">3.67342782020569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73011589050293</t>
+    <t xml:space="preserve">3.73011660575867</t>
   </si>
   <si>
     <t xml:space="preserve">3.78680539131165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92285823822021</t>
+    <t xml:space="preserve">3.92285871505737</t>
   </si>
   <si>
     <t xml:space="preserve">3.86239004135132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7452335357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76790928840637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83971428871155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83215594291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168774604797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73767495155334</t>
+    <t xml:space="preserve">3.74523329734802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76790857315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83971452713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83215665817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168822288513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7376754283905</t>
   </si>
   <si>
     <t xml:space="preserve">3.69232416152954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70366191864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77924633026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68854475021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66586923599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69610333442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66964840888977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73389554023743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81703925132751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8472728729248</t>
+    <t xml:space="preserve">3.70366215705872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77924704551697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6885449886322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66586971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6961030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66964864730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73389577865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81703901290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84727358818054</t>
   </si>
   <si>
     <t xml:space="preserve">3.90018248558044</t>
@@ -1811,13 +1811,13 @@
     <t xml:space="preserve">3.98332619667053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96065044403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95309162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93041610717773</t>
+    <t xml:space="preserve">3.96065020561218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9530918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93041634559631</t>
   </si>
   <si>
     <t xml:space="preserve">3.94553279876709</t>
@@ -1826,22 +1826,22 @@
     <t xml:space="preserve">3.99088454246521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9152991771698</t>
+    <t xml:space="preserve">3.91529989242554</t>
   </si>
   <si>
     <t xml:space="preserve">4.02111864089966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09670400619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03623533248901</t>
+    <t xml:space="preserve">4.09670305252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03623628616333</t>
   </si>
   <si>
     <t xml:space="preserve">4.06646966934204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08158731460571</t>
+    <t xml:space="preserve">4.0815863609314</t>
   </si>
   <si>
     <t xml:space="preserve">4.13449573516846</t>
@@ -1850,91 +1850,91 @@
     <t xml:space="preserve">4.05135250091553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02867698669434</t>
+    <t xml:space="preserve">4.02867650985718</t>
   </si>
   <si>
     <t xml:space="preserve">4.0060019493103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04379320144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11937808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01356029510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96820950508118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93797492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97576785087585</t>
+    <t xml:space="preserve">4.04379367828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1193790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01355981826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96820878982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93797516822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97576808929443</t>
   </si>
   <si>
     <t xml:space="preserve">3.90774130821228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89262461662292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88506579399109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87750768661499</t>
+    <t xml:space="preserve">3.89262390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88506531715393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87750744819641</t>
   </si>
   <si>
     <t xml:space="preserve">3.85483145713806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80192232131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5940637588501</t>
+    <t xml:space="preserve">3.801922082901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59406399726868</t>
   </si>
   <si>
     <t xml:space="preserve">3.60162210464478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6507523059845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877884864807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99844288825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72255778312683</t>
+    <t xml:space="preserve">3.65075254440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877932548523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99844264984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72255873680115</t>
   </si>
   <si>
     <t xml:space="preserve">3.63185572624207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46556925773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44667315483093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2841649055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1103196144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06496906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83821439743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83443546295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95915007591248</t>
+    <t xml:space="preserve">3.46556949615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44667291641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28416514396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11031985282898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0649688243866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.838214635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8344349861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95915031433105</t>
   </si>
   <si>
     <t xml:space="preserve">2.70971989631653</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">2.93269562721252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00450134277344</t>
+    <t xml:space="preserve">3.00450110435486</t>
   </si>
   <si>
     <t xml:space="preserve">2.97426700592041</t>
@@ -1952,13 +1952,13 @@
     <t xml:space="preserve">2.94403314590454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91001963615417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96292972564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85333108901978</t>
+    <t xml:space="preserve">2.91001987457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96292948722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85333132743835</t>
   </si>
   <si>
     <t xml:space="preserve">2.89490270614624</t>
@@ -1967,37 +1967,37 @@
     <t xml:space="preserve">2.88734436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92135787010193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85711026191711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9024612903595</t>
+    <t xml:space="preserve">2.92135763168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85711050033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90246152877808</t>
   </si>
   <si>
     <t xml:space="preserve">2.82687664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89112377166748</t>
+    <t xml:space="preserve">2.8911235332489</t>
   </si>
   <si>
     <t xml:space="preserve">2.9969425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95159149169922</t>
+    <t xml:space="preserve">2.9515917301178</t>
   </si>
   <si>
     <t xml:space="preserve">2.97804641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99316358566284</t>
+    <t xml:space="preserve">2.99316334724426</t>
   </si>
   <si>
     <t xml:space="preserve">3.05363130569458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03473496437073</t>
+    <t xml:space="preserve">3.03473472595215</t>
   </si>
   <si>
     <t xml:space="preserve">3.02717661857605</t>
@@ -2006,10 +2006,10 @@
     <t xml:space="preserve">3.12165784835815</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06119012832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09898257255554</t>
+    <t xml:space="preserve">3.06118988990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09898209571838</t>
   </si>
   <si>
     <t xml:space="preserve">3.16700887680054</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">3.14433312416077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19346356391907</t>
+    <t xml:space="preserve">3.19346332550049</t>
   </si>
   <si>
     <t xml:space="preserve">3.2199182510376</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">3.32195782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15945029258728</t>
+    <t xml:space="preserve">3.15944981575012</t>
   </si>
   <si>
     <t xml:space="preserve">3.07252764701843</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">3.06874823570251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10654091835022</t>
+    <t xml:space="preserve">3.10654067993164</t>
   </si>
   <si>
     <t xml:space="preserve">3.16322946548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27282786369324</t>
+    <t xml:space="preserve">3.27282762527466</t>
   </si>
   <si>
     <t xml:space="preserve">3.28794455528259</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">3.40510153770447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51091980934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4882447719574</t>
+    <t xml:space="preserve">3.51092004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48824429512024</t>
   </si>
   <si>
     <t xml:space="preserve">3.45801067352295</t>
@@ -2069,49 +2069,49 @@
     <t xml:space="preserve">3.34463334083557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29928255081177</t>
+    <t xml:space="preserve">3.29928207397461</t>
   </si>
   <si>
     <t xml:space="preserve">3.30684113502502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30306124687195</t>
+    <t xml:space="preserve">3.30306172370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.26148986816406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37864661216736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37486720085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26526951789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39754271507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48068642616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38998436927795</t>
+    <t xml:space="preserve">3.37864637374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3748676776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26526927947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39754247665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48068618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38998460769653</t>
   </si>
   <si>
     <t xml:space="preserve">3.31817841529846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2577109336853</t>
+    <t xml:space="preserve">3.25771045684814</t>
   </si>
   <si>
     <t xml:space="preserve">3.22747659683228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18590521812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24637293815613</t>
+    <t xml:space="preserve">3.18590497970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24637317657471</t>
   </si>
   <si>
     <t xml:space="preserve">3.17456698417664</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">3.17834639549255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09142422676086</t>
+    <t xml:space="preserve">3.09142398834229</t>
   </si>
   <si>
     <t xml:space="preserve">3.08008575439453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0460729598999</t>
+    <t xml:space="preserve">3.04607319831848</t>
   </si>
   <si>
     <t xml:space="preserve">3.01583886146545</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">2.95537066459656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92513680458069</t>
+    <t xml:space="preserve">2.92513704299927</t>
   </si>
   <si>
     <t xml:space="preserve">2.8835654258728</t>
@@ -2153,13 +2153,13 @@
     <t xml:space="preserve">2.7890841960907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77018785476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75129151344299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71727824211121</t>
+    <t xml:space="preserve">2.77018761634827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75129127502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71727848052979</t>
   </si>
   <si>
     <t xml:space="preserve">2.72105765342712</t>
@@ -2168,43 +2168,43 @@
     <t xml:space="preserve">2.67948603630066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55477070808411</t>
+    <t xml:space="preserve">2.55477118492126</t>
   </si>
   <si>
     <t xml:space="preserve">2.44895195960999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55099129676819</t>
+    <t xml:space="preserve">2.55099153518677</t>
   </si>
   <si>
     <t xml:space="preserve">2.615238904953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69838213920593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98938393592834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5373752117157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62807703018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63563513755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57894706726074</t>
+    <t xml:space="preserve">2.69838190078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98938417434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53737497329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62807679176331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63563561439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57894730567932</t>
   </si>
   <si>
     <t xml:space="preserve">3.56382989883423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50714063644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48446559906006</t>
+    <t xml:space="preserve">3.50714087486267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48446536064148</t>
   </si>
   <si>
     <t xml:space="preserve">3.52225780487061</t>
@@ -2213,34 +2213,34 @@
     <t xml:space="preserve">3.41643881797791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12543702125549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80948090553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76035070419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6431941986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68476557731628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7490131855011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79436373710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75657153129578</t>
+    <t xml:space="preserve">3.12543749809265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80948066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76035046577454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64319372177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68476533889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74901247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7943639755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7565712928772</t>
   </si>
   <si>
     <t xml:space="preserve">3.77546739578247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76412963867188</t>
+    <t xml:space="preserve">3.76412987709045</t>
   </si>
   <si>
     <t xml:space="preserve">4.15717124938965</t>
@@ -2252,22 +2252,22 @@
     <t xml:space="preserve">4.17228841781616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3134560585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22718715667725</t>
+    <t xml:space="preserve">4.31345558166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22718667984009</t>
   </si>
   <si>
     <t xml:space="preserve">4.1252326965332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07817602157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08601903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09386110305786</t>
+    <t xml:space="preserve">4.07817649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09386157989502</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365905761719</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">4.26639986038208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27424192428589</t>
+    <t xml:space="preserve">4.27424240112305</t>
   </si>
   <si>
     <t xml:space="preserve">4.25855731964111</t>
@@ -2294,61 +2294,61 @@
     <t xml:space="preserve">4.35266971588135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30561304092407</t>
+    <t xml:space="preserve">4.30561351776123</t>
   </si>
   <si>
     <t xml:space="preserve">4.28992795944214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28208541870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1958155632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03896379470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02327871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99974989891052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00759267807007</t>
+    <t xml:space="preserve">4.28208589553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19581604003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03896331787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02327823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99974966049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00759315490723</t>
   </si>
   <si>
     <t xml:space="preserve">3.96053695678711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03112077713013</t>
+    <t xml:space="preserve">4.03112030029297</t>
   </si>
   <si>
     <t xml:space="preserve">4.05464887619019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93700885772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92132329940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01543569564819</t>
+    <t xml:space="preserve">3.93700933456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92132377624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01543521881104</t>
   </si>
   <si>
     <t xml:space="preserve">4.07033395767212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97622203826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1879734992981</t>
+    <t xml:space="preserve">3.97622227668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18797397613525</t>
   </si>
   <si>
     <t xml:space="preserve">4.24287223815918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.211501121521</t>
+    <t xml:space="preserve">4.21150159835815</t>
   </si>
   <si>
     <t xml:space="preserve">4.39188241958618</t>
@@ -2357,16 +2357,16 @@
     <t xml:space="preserve">4.45462322235107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43109607696533</t>
+    <t xml:space="preserve">4.43109560012817</t>
   </si>
   <si>
     <t xml:space="preserve">4.42325305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38404035568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39972543716431</t>
+    <t xml:space="preserve">4.38403940200806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39972496032715</t>
   </si>
   <si>
     <t xml:space="preserve">4.33698415756226</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">4.36051177978516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4624662399292</t>
+    <t xml:space="preserve">4.46246671676636</t>
   </si>
   <si>
     <t xml:space="preserve">4.44678115844727</t>
@@ -2384,46 +2384,46 @@
     <t xml:space="preserve">4.4389386177063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47815132141113</t>
+    <t xml:space="preserve">4.47815179824829</t>
   </si>
   <si>
     <t xml:space="preserve">4.48599433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50167942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5644211769104</t>
+    <t xml:space="preserve">4.50167989730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56442022323608</t>
   </si>
   <si>
     <t xml:space="preserve">4.60363388061523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62716150283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6350040435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49383687973022</t>
+    <t xml:space="preserve">4.62716197967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63500452041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49383640289307</t>
   </si>
   <si>
     <t xml:space="preserve">4.59579133987427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66637516021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68206071853638</t>
+    <t xml:space="preserve">4.66637468338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68206024169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.72911643981934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64284658432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74480104446411</t>
+    <t xml:space="preserve">4.64284706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74480199813843</t>
   </si>
   <si>
     <t xml:space="preserve">4.86244106292725</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">4.90949726104736</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05850696563721</t>
+    <t xml:space="preserve">5.05850744247437</t>
   </si>
   <si>
     <t xml:space="preserve">5.03497982025146</t>
@@ -2441,37 +2441,37 @@
     <t xml:space="preserve">4.99576616287231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95655345916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94871091842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97223854064941</t>
+    <t xml:space="preserve">4.95655298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9487099647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97223901748657</t>
   </si>
   <si>
     <t xml:space="preserve">4.87028360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98008108139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07419204711914</t>
+    <t xml:space="preserve">4.98008060455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0741925239563</t>
   </si>
   <si>
     <t xml:space="preserve">5.0506649017334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02713632583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08987808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19183158874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18398952484131</t>
+    <t xml:space="preserve">5.02713680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08987760543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19183254241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18399000167847</t>
   </si>
   <si>
     <t xml:space="preserve">5.16830444335938</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">5.10556364059448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14477682113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23888826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21536111831665</t>
+    <t xml:space="preserve">5.14477634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23888778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21536016464233</t>
   </si>
   <si>
     <t xml:space="preserve">5.1996750831604</t>
@@ -2495,235 +2495,235 @@
     <t xml:space="preserve">5.25457334518433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30162954330444</t>
+    <t xml:space="preserve">5.3016300201416</t>
   </si>
   <si>
     <t xml:space="preserve">5.01929426193237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93302488327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79970026016235</t>
+    <t xml:space="preserve">4.93302440643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79969930648804</t>
   </si>
   <si>
     <t xml:space="preserve">4.76048707962036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76833009719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68990325927734</t>
+    <t xml:space="preserve">4.76832962036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68990278244019</t>
   </si>
   <si>
     <t xml:space="preserve">4.69774580001831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6114764213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53305006027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50952196121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47030830383301</t>
+    <t xml:space="preserve">4.61147689819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53305053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50952243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47030878067017</t>
   </si>
   <si>
     <t xml:space="preserve">4.55657815933228</t>
   </si>
   <si>
+    <t xml:space="preserve">4.54873514175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57226324081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52520751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54089260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51736497879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58010625839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82322788238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87812662124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88596963882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7840142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65853261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77617216110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85459899902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94086790084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52122402191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66239070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73297500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89767026901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68591928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70160484313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59964990615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53690910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906608581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17614698410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29378700256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71343088150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41541051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89381122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81538534164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92518281936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84675550460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72127389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5879487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61931896209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77163219451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73861026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69733333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63954496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7963981628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98627328872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95325088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312601089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07708215713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11835908889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97801733016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06057214736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9037184715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96976184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87069702148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82942008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62303400039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40839385986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50745868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56524658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48269176483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58175754547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64780044555664</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.54873561859131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57226371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52520704269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54089212417603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51736497879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58010625839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82322788238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87812662124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88596963882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78401517868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70558834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65853214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77617263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85459852218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94086790084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52122354507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6623911857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73297452926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89767074584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68591976165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70160484313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59964990615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5369086265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906656265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17614650726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29378652572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7134313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41541051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89381170272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81538534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9251823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84675598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72127342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5879487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61931943893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70558786392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77163171768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.738609790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69733285903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63954496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7963981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98627233505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95325088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312553405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07708215713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11835908889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97801733016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06057119369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9037184715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96976184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87069654464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82942008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62303447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40839338302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50745820999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56524658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58175754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64780044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61477899551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57350158691406</t>
+    <t xml:space="preserve">4.61477851867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5735011100769</t>
   </si>
   <si>
     <t xml:space="preserve">4.51571369171143</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3340950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30932760238647</t>
+    <t xml:space="preserve">4.33409452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30932807922363</t>
   </si>
   <si>
     <t xml:space="preserve">4.38362693786621</t>
@@ -2735,6 +2735,9 @@
     <t xml:space="preserve">4.2680516242981</t>
   </si>
   <si>
+    <t xml:space="preserve">4.39188289642334</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.46618127822876</t>
   </si>
   <si>
@@ -2747,7 +2750,7 @@
     <t xml:space="preserve">4.27630662918091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44967079162598</t>
+    <t xml:space="preserve">4.44967031478882</t>
   </si>
   <si>
     <t xml:space="preserve">4.34235048294067</t>
@@ -2756,7 +2759,7 @@
     <t xml:space="preserve">4.41664838790894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55699110031128</t>
+    <t xml:space="preserve">4.55699062347412</t>
   </si>
   <si>
     <t xml:space="preserve">4.67256689071655</t>
@@ -2774,19 +2777,16 @@
     <t xml:space="preserve">4.85418605804443</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8624415397644</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.72209930419922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75512075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7798867225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73035478591919</t>
+    <t xml:space="preserve">4.7551212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77988719940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73035430908203</t>
   </si>
   <si>
     <t xml:space="preserve">4.82116460800171</t>
@@ -2801,28 +2801,28 @@
     <t xml:space="preserve">4.94499540328979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83767557144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78814268112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87895154953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60652303695679</t>
+    <t xml:space="preserve">4.83767509460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78814220428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87895202636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60652351379395</t>
   </si>
   <si>
     <t xml:space="preserve">4.66431140899658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81290912628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93674039840698</t>
+    <t xml:space="preserve">4.81290864944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88720750808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93673992156982</t>
   </si>
   <si>
     <t xml:space="preserve">5.01103925704956</t>
@@ -2834,19 +2834,19 @@
     <t xml:space="preserve">5.16789197921753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23393535614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19265794754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22567987442017</t>
+    <t xml:space="preserve">5.23393583297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19265747070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22567939758301</t>
   </si>
   <si>
     <t xml:space="preserve">5.26695680618286</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27521181106567</t>
+    <t xml:space="preserve">5.27521228790283</t>
   </si>
   <si>
     <t xml:space="preserve">5.29172277450562</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">5.30823373794556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36602210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43206548690796</t>
+    <t xml:space="preserve">5.36602163314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4320650100708</t>
   </si>
   <si>
     <t xml:space="preserve">5.47334241867065</t>
@@ -2867,19 +2867,19 @@
     <t xml:space="preserve">5.55589628219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41555452346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4898533821106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46508646011353</t>
+    <t xml:space="preserve">5.41555404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48985290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46508693695068</t>
   </si>
   <si>
     <t xml:space="preserve">5.57240724563599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44857549667358</t>
+    <t xml:space="preserve">5.44857597351074</t>
   </si>
   <si>
     <t xml:space="preserve">5.49810838699341</t>
@@ -2888,16 +2888,16 @@
     <t xml:space="preserve">5.52287483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51461935043335</t>
+    <t xml:space="preserve">5.51461887359619</t>
   </si>
   <si>
     <t xml:space="preserve">5.58891820907593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45683097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54764080047607</t>
+    <t xml:space="preserve">5.45683145523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54764127731323</t>
   </si>
   <si>
     <t xml:space="preserve">5.68798303604126</t>
@@ -2906,43 +2906,43 @@
     <t xml:space="preserve">5.63019514083862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.613685131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59717416763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58066272735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65496110916138</t>
+    <t xml:space="preserve">5.61368465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5971736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58066320419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65496158599854</t>
   </si>
   <si>
     <t xml:space="preserve">5.77879285812378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82007026672363</t>
+    <t xml:space="preserve">5.82006978988647</t>
   </si>
   <si>
     <t xml:space="preserve">5.84483575820923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86134672164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89436864852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8118143081665</t>
+    <t xml:space="preserve">5.86134719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89436817169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81181478500366</t>
   </si>
   <si>
     <t xml:space="preserve">5.90262413024902</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80355930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73751544952393</t>
+    <t xml:space="preserve">5.80355882644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73751592636108</t>
   </si>
   <si>
     <t xml:space="preserve">6.00168943405151</t>
@@ -2954,43 +2954,43 @@
     <t xml:space="preserve">6.38969373703003</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47224807739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4392261505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45573711395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59607887268066</t>
+    <t xml:space="preserve">6.39794874191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47224760055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43922662734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45573663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59607934951782</t>
   </si>
   <si>
     <t xml:space="preserve">6.52178049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57956838607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58782339096069</t>
+    <t xml:space="preserve">6.57956886291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58782386779785</t>
   </si>
   <si>
     <t xml:space="preserve">6.51352500915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5630578994751</t>
+    <t xml:space="preserve">6.56305742263794</t>
   </si>
   <si>
     <t xml:space="preserve">6.67863368988037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72816514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6703782081604</t>
+    <t xml:space="preserve">6.72816562652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67037773132324</t>
   </si>
   <si>
     <t xml:space="preserve">6.63735628128052</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">6.79420852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73642110824585</t>
+    <t xml:space="preserve">6.73642158508301</t>
   </si>
   <si>
     <t xml:space="preserve">6.68688917160034</t>
@@ -3008,22 +3008,22 @@
     <t xml:space="preserve">6.53829145431519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62084531784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64561176300049</t>
+    <t xml:space="preserve">6.62084579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64561128616333</t>
   </si>
   <si>
     <t xml:space="preserve">6.71991062164307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74467706680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75293302536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78595399856567</t>
+    <t xml:space="preserve">6.74467658996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75293254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78595352172852</t>
   </si>
   <si>
     <t xml:space="preserve">5.96866750717163</t>
@@ -3035,22 +3035,22 @@
     <t xml:space="preserve">5.64670610427856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85309171676636</t>
+    <t xml:space="preserve">5.8530912399292</t>
   </si>
   <si>
     <t xml:space="preserve">5.67972755432129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39904403686523</t>
+    <t xml:space="preserve">5.39904356002808</t>
   </si>
   <si>
     <t xml:space="preserve">5.38253259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66321659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60542917251587</t>
+    <t xml:space="preserve">5.66321706771851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60542869567871</t>
   </si>
   <si>
     <t xml:space="preserve">5.7457709312439</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">5.83658075332642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88611316680908</t>
+    <t xml:space="preserve">5.88611364364624</t>
   </si>
   <si>
     <t xml:space="preserve">5.79530382156372</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">5.87785768508911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9769229888916</t>
+    <t xml:space="preserve">5.97692251205444</t>
   </si>
   <si>
     <t xml:space="preserve">5.91087913513184</t>
@@ -3077,19 +3077,19 @@
     <t xml:space="preserve">5.91913461685181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63845062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78704881668091</t>
+    <t xml:space="preserve">5.63845109939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78704833984375</t>
   </si>
   <si>
     <t xml:space="preserve">5.94390106201172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96041202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86960220336914</t>
+    <t xml:space="preserve">5.9604115486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8696026802063</t>
   </si>
   <si>
     <t xml:space="preserve">5.98917293548584</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">5.79011058807373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78145599365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57373905181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6775975227356</t>
+    <t xml:space="preserve">5.78145551681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57373857498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67759704589844</t>
   </si>
   <si>
     <t xml:space="preserve">5.76414585113525</t>
@@ -3140,13 +3140,13 @@
     <t xml:space="preserve">5.86800479888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88531446456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87665987014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92858839035034</t>
+    <t xml:space="preserve">5.88531398773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87665939331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9285888671875</t>
   </si>
   <si>
     <t xml:space="preserve">5.96320819854736</t>
@@ -3167,25 +3167,25 @@
     <t xml:space="preserve">6.17092561721802</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28343915939331</t>
+    <t xml:space="preserve">6.28343868255615</t>
   </si>
   <si>
     <t xml:space="preserve">6.25747394561768</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24881887435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24016380310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23150873184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26612854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46519088745117</t>
+    <t xml:space="preserve">6.24881839752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24016427993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2315092086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2661280632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46519041061401</t>
   </si>
   <si>
     <t xml:space="preserve">6.54308462142944</t>
@@ -3197,22 +3197,22 @@
     <t xml:space="preserve">6.56904935836792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63828802108765</t>
+    <t xml:space="preserve">6.6382884979248</t>
   </si>
   <si>
     <t xml:space="preserve">6.56039428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57770442962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62097883224487</t>
+    <t xml:space="preserve">6.57770395278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62097835540771</t>
   </si>
   <si>
     <t xml:space="preserve">6.65559816360474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69021797180176</t>
+    <t xml:space="preserve">6.6902174949646</t>
   </si>
   <si>
     <t xml:space="preserve">6.73349189758301</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">6.64694309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50846529006958</t>
+    <t xml:space="preserve">6.50846481323242</t>
   </si>
   <si>
     <t xml:space="preserve">6.66425275802612</t>
@@ -3257,58 +3257,58 @@
     <t xml:space="preserve">6.68156242370605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60366868972778</t>
+    <t xml:space="preserve">6.60366916656494</t>
   </si>
   <si>
     <t xml:space="preserve">6.51712036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62963342666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74214649200439</t>
+    <t xml:space="preserve">6.6296329498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74214696884155</t>
   </si>
   <si>
     <t xml:space="preserve">6.87196969985962</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79407644271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85466003417969</t>
+    <t xml:space="preserve">6.79407596588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85466051101685</t>
   </si>
   <si>
     <t xml:space="preserve">6.61232376098633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78542137145996</t>
+    <t xml:space="preserve">6.7854208946228</t>
   </si>
   <si>
     <t xml:space="preserve">6.77676630020142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75080156326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52577495574951</t>
+    <t xml:space="preserve">6.7508020401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52577447891235</t>
   </si>
   <si>
     <t xml:space="preserve">6.42191648483276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45653581619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71618223190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72483730316162</t>
+    <t xml:space="preserve">6.45653629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71618270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72483682632446</t>
   </si>
   <si>
     <t xml:space="preserve">6.75945663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82869577407837</t>
+    <t xml:space="preserve">6.82869529724121</t>
   </si>
   <si>
     <t xml:space="preserve">6.82004070281982</t>
@@ -3317,25 +3317,25 @@
     <t xml:space="preserve">6.92389917373657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01044797897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05372190475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99313831329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.001793384552</t>
+    <t xml:space="preserve">7.01044845581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05372142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9931378364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00179290771484</t>
   </si>
   <si>
     <t xml:space="preserve">7.02775764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97582864761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95851850509644</t>
+    <t xml:space="preserve">6.97582912445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95851898193359</t>
   </si>
   <si>
     <t xml:space="preserve">6.94986343383789</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">7.07103204727173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06237697601318</t>
+    <t xml:space="preserve">7.06237745285034</t>
   </si>
   <si>
     <t xml:space="preserve">7.11430644989014</t>
@@ -3356,31 +3356,31 @@
     <t xml:space="preserve">7.01910257339478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04506731033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13161611557007</t>
+    <t xml:space="preserve">7.04506778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13161563873291</t>
   </si>
   <si>
     <t xml:space="preserve">7.18354558944702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15758085250854</t>
+    <t xml:space="preserve">7.1575813293457</t>
   </si>
   <si>
     <t xml:space="preserve">7.07968711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88927984237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86331462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93255424499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91524410247803</t>
+    <t xml:space="preserve">6.88927936553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86331510543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93255376815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91524457931519</t>
   </si>
   <si>
     <t xml:space="preserve">6.94120931625366</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">6.96717357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17489004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27009439468384</t>
+    <t xml:space="preserve">7.17489051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27009391784668</t>
   </si>
   <si>
     <t xml:space="preserve">7.20085477828979</t>
@@ -3407,10 +3407,10 @@
     <t xml:space="preserve">7.14892578125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08834171295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14027070999146</t>
+    <t xml:space="preserve">7.0883412361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14027118682861</t>
   </si>
   <si>
     <t xml:space="preserve">7.26143932342529</t>
@@ -3422,16 +3422,16 @@
     <t xml:space="preserve">7.33933305740356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42588138580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44319200515747</t>
+    <t xml:space="preserve">7.42588186264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44319248199463</t>
   </si>
   <si>
     <t xml:space="preserve">7.48646545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23547506332397</t>
+    <t xml:space="preserve">7.23547410964966</t>
   </si>
   <si>
     <t xml:space="preserve">7.29605865478516</t>
@@ -3440,10 +3440,10 @@
     <t xml:space="preserve">7.19220066070557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4518461227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38260746002197</t>
+    <t xml:space="preserve">7.45184564590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38260793685913</t>
   </si>
   <si>
     <t xml:space="preserve">7.3566427230835</t>
@@ -3452,55 +3452,55 @@
     <t xml:space="preserve">7.52108478546143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84997081756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72880220413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7634220123291</t>
+    <t xml:space="preserve">7.84997034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72880268096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76342248916626</t>
   </si>
   <si>
     <t xml:space="preserve">7.53839540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55570507049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4605016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40857219696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63359785079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72014713287354</t>
+    <t xml:space="preserve">7.55570411682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46050119400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40857267379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63359880447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72014760971069</t>
   </si>
   <si>
     <t xml:space="preserve">7.88458967208862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77207612991333</t>
+    <t xml:space="preserve">7.77207660675049</t>
   </si>
   <si>
     <t xml:space="preserve">7.65090847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6682186126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78073215484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83266067504883</t>
+    <t xml:space="preserve">7.66821813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78073072433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83266162872314</t>
   </si>
   <si>
     <t xml:space="preserve">7.82400560379028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75476694107056</t>
+    <t xml:space="preserve">7.75476741790771</t>
   </si>
   <si>
     <t xml:space="preserve">7.7028374671936</t>
@@ -3509,10 +3509,10 @@
     <t xml:space="preserve">7.69418334960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67687273025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94517421722412</t>
+    <t xml:space="preserve">7.67687320709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94517374038696</t>
   </si>
   <si>
     <t xml:space="preserve">8.01441287994385</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">8.11827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05768871307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12692642211914</t>
+    <t xml:space="preserve">8.05768775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12692737579346</t>
   </si>
   <si>
     <t xml:space="preserve">8.0663423538208</t>
@@ -3536,10 +3536,10 @@
     <t xml:space="preserve">8.10961627960205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17885589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17020130157471</t>
+    <t xml:space="preserve">8.17885494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17020034790039</t>
   </si>
   <si>
     <t xml:space="preserve">8.20481967926025</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">8.00575828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99710273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87593650817871</t>
+    <t xml:space="preserve">7.99710369110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87593555450439</t>
   </si>
   <si>
     <t xml:space="preserve">8.30867862701416</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">8.41253757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57698059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58563423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65487289428711</t>
+    <t xml:space="preserve">8.576979637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5856351852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65487384796143</t>
   </si>
   <si>
     <t xml:space="preserve">8.54236030578613</t>
@@ -3587,16 +3587,16 @@
     <t xml:space="preserve">8.62025451660156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81066131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82797145843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7068042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87990093231201</t>
+    <t xml:space="preserve">8.81066226959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82797050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70680332183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87990188598633</t>
   </si>
   <si>
     <t xml:space="preserve">8.834641456604</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">8.93421173095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86179733276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75317478179932</t>
+    <t xml:space="preserve">8.86179637908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.753173828125</t>
   </si>
   <si>
     <t xml:space="preserve">8.72601890563965</t>
@@ -3629,22 +3629,22 @@
     <t xml:space="preserve">8.80748558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85274505615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77127838134766</t>
+    <t xml:space="preserve">8.85274410247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77127742767334</t>
   </si>
   <si>
     <t xml:space="preserve">8.68981170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69886207580566</t>
+    <t xml:space="preserve">8.69886302947998</t>
   </si>
   <si>
     <t xml:space="preserve">8.73507022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59929180145264</t>
+    <t xml:space="preserve">8.59929275512695</t>
   </si>
   <si>
     <t xml:space="preserve">8.56308460235596</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">8.08333492279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27342510223389</t>
+    <t xml:space="preserve">8.27342414855957</t>
   </si>
   <si>
     <t xml:space="preserve">8.42730712890625</t>
@@ -3683,10 +3683,10 @@
     <t xml:space="preserve">8.4906702041626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40015029907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5811882019043</t>
+    <t xml:space="preserve">8.40015125274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58118724822998</t>
   </si>
   <si>
     <t xml:space="preserve">8.40920257568359</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">8.41825485229492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60834407806396</t>
+    <t xml:space="preserve">8.60834503173828</t>
   </si>
   <si>
     <t xml:space="preserve">8.48161697387695</t>
@@ -3710,16 +3710,16 @@
     <t xml:space="preserve">8.68075942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65360450744629</t>
+    <t xml:space="preserve">8.65360355377197</t>
   </si>
   <si>
     <t xml:space="preserve">8.870849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02473163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91610813140869</t>
+    <t xml:space="preserve">9.02473068237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91610908508301</t>
   </si>
   <si>
     <t xml:space="preserve">8.98852348327637</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">9.08809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01567840576172</t>
+    <t xml:space="preserve">9.01567935943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.04283428192139</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">9.16050910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79843330383301</t>
+    <t xml:space="preserve">8.79843425750732</t>
   </si>
   <si>
     <t xml:space="preserve">8.36394309997559</t>
@@ -3752,16 +3752,16 @@
     <t xml:space="preserve">8.29152774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23721790313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26437187194824</t>
+    <t xml:space="preserve">8.23721694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26437282562256</t>
   </si>
   <si>
     <t xml:space="preserve">8.47256565093994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97947120666504</t>
+    <t xml:space="preserve">8.97947216033936</t>
   </si>
   <si>
     <t xml:space="preserve">8.89800453186035</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">9.14240550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3415470123291</t>
+    <t xml:space="preserve">9.34154605865479</t>
   </si>
   <si>
     <t xml:space="preserve">9.28723621368408</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">9.19671630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25102806091309</t>
+    <t xml:space="preserve">9.2510290145874</t>
   </si>
   <si>
     <t xml:space="preserve">9.12430191040039</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">9.21482086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35965061187744</t>
+    <t xml:space="preserve">9.35965156555176</t>
   </si>
   <si>
     <t xml:space="preserve">9.17861366271973</t>
@@ -3818,85 +3818,88 @@
     <t xml:space="preserve">9.10619831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30533981323242</t>
+    <t xml:space="preserve">9.30533885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50448036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65504741668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78679180145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73033046722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67386722564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52330112457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48566055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40096664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34450435638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29745292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35391426086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38214588165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26922225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41037750244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39155578613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91853713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93735885620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80561351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0314617156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84325408935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95617866516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97500038146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89971733093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61740589141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69268894195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5797643661499</t>
   </si>
   <si>
     <t xml:space="preserve">9.50448131561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65504741668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78679180145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73033046722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67386722564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52330112457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48566055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40096664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34450435638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29745292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35391426086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38214588165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26922225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41037750244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39155578613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91853713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93735885620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80561351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0314617156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84325408935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95617866516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97500038146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89971733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61740589141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69268894195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5797643661499</t>
   </si>
   <si>
     <t xml:space="preserve">9.46683979034424</t>
@@ -46746,7 +46749,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1620" t="s">
-        <v>875</v>
+        <v>850</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46772,7 +46775,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1621" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46798,7 +46801,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1622" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46824,7 +46827,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1623" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46850,7 +46853,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1624" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46876,7 +46879,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1625" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46902,7 +46905,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1626" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46928,7 +46931,7 @@
         <v>6</v>
       </c>
       <c r="G1627" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46954,7 +46957,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1628" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46980,7 +46983,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1629" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47006,7 +47009,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1630" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -47032,7 +47035,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1631" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47058,7 +47061,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1632" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47084,7 +47087,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1633" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47110,7 +47113,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1634" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47136,7 +47139,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1635" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47162,7 +47165,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1636" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47188,7 +47191,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1637" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47214,7 +47217,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1638" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47240,7 +47243,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1639" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47266,7 +47269,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1640" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47292,7 +47295,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1641" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47318,7 +47321,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1642" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47344,7 +47347,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1643" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47370,7 +47373,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1644" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47396,7 +47399,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1645" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47422,7 +47425,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1646" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47448,7 +47451,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1647" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47474,7 +47477,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1648" t="s">
-        <v>840</v>
+        <v>898</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47552,7 +47555,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1651" t="s">
-        <v>840</v>
+        <v>898</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47734,7 +47737,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1658" t="s">
-        <v>779</v>
+        <v>907</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47760,7 +47763,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1659" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47786,7 +47789,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1660" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47812,7 +47815,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1661" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47838,7 +47841,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1662" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47864,7 +47867,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1663" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47890,7 +47893,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1664" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47916,7 +47919,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1665" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47942,7 +47945,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1666" t="s">
-        <v>840</v>
+        <v>898</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47968,7 +47971,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1667" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47994,7 +47997,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1668" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48046,7 +48049,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1670" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48072,7 +48075,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1671" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48098,7 +48101,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1672" t="s">
-        <v>779</v>
+        <v>907</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48124,7 +48127,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1673" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48150,7 +48153,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1674" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48176,7 +48179,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1675" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48202,7 +48205,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1676" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48228,7 +48231,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1677" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48254,7 +48257,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1678" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48280,7 +48283,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1679" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48306,7 +48309,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1680" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48332,7 +48335,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48358,7 +48361,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1682" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48384,7 +48387,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1683" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48410,7 +48413,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1684" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48436,7 +48439,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G1685" t="s">
-        <v>920</v>
+        <v>804</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48462,7 +48465,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1686" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48488,7 +48491,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1687" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48514,7 +48517,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48644,7 +48647,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1693" t="s">
-        <v>875</v>
+        <v>850</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -48670,7 +48673,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48696,7 +48699,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1695" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48722,7 +48725,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -48748,7 +48751,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1697" t="s">
-        <v>875</v>
+        <v>850</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48774,7 +48777,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1698" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48800,7 +48803,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48826,7 +48829,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1700" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48852,7 +48855,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48930,7 +48933,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1704" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48956,7 +48959,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1705" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -49034,7 +49037,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1708" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -49086,7 +49089,7 @@
         <v>6</v>
       </c>
       <c r="G1710" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49164,7 +49167,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1713" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49268,7 +49271,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1717" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49320,7 +49323,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1719" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49372,7 +49375,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1721" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49398,7 +49401,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1722" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49424,7 +49427,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1723" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49476,7 +49479,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1725" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49554,7 +49557,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1728" t="s">
-        <v>875</v>
+        <v>850</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49580,7 +49583,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1729" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49606,7 +49609,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1730" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -49736,7 +49739,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1735" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49762,7 +49765,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1736" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -49840,7 +49843,7 @@
         <v>6</v>
       </c>
       <c r="G1739" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -63594,7 +63597,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>1269</v>
+        <v>1295</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63620,7 +63623,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2269" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63646,7 +63649,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2270" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63672,7 +63675,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2271" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63698,7 +63701,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2272" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63750,7 +63753,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2274" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63880,7 +63883,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2279" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63906,7 +63909,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2280" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63932,7 +63935,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2281" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63958,7 +63961,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2282" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63984,7 +63987,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2283" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64010,7 +64013,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64062,7 +64065,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2286" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64114,7 +64117,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2288" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64140,7 +64143,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2289" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64166,7 +64169,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2290" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64218,7 +64221,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2292" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64244,7 +64247,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2293" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64270,7 +64273,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2294" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64296,7 +64299,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2295" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64322,7 +64325,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2296" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64348,7 +64351,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2297" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64374,7 +64377,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2298" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64400,7 +64403,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2299" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64426,7 +64429,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2300" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64452,7 +64455,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2301" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64478,7 +64481,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2302" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64504,7 +64507,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2303" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64530,7 +64533,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2304" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64556,7 +64559,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2305" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64582,7 +64585,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2306" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64608,7 +64611,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64634,7 +64637,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2308" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64660,7 +64663,7 @@
         <v>11.5</v>
       </c>
       <c r="G2309" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64686,7 +64689,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2310" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64712,7 +64715,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2311" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64738,7 +64741,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2312" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64764,7 +64767,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2313" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64790,7 +64793,7 @@
         <v>11.5</v>
       </c>
       <c r="G2314" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64816,7 +64819,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2315" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64842,7 +64845,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2316" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64868,7 +64871,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2317" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64894,7 +64897,7 @@
         <v>12</v>
       </c>
       <c r="G2318" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64920,7 +64923,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2319" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64946,7 +64949,7 @@
         <v>12</v>
       </c>
       <c r="G2320" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64972,7 +64975,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2321" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64998,7 +65001,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2322" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65024,7 +65027,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2323" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65050,7 +65053,7 @@
         <v>12</v>
       </c>
       <c r="G2324" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65076,7 +65079,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2325" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65102,7 +65105,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2326" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65128,7 +65131,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2327" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65154,7 +65157,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2328" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65180,7 +65183,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2329" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65206,7 +65209,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2330" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65232,7 +65235,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2331" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65258,7 +65261,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2332" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65284,7 +65287,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2333" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65310,7 +65313,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2334" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65336,7 +65339,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65362,7 +65365,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65388,7 +65391,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2337" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65414,7 +65417,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2338" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65440,7 +65443,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2339" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65466,7 +65469,7 @@
         <v>12.5</v>
       </c>
       <c r="G2340" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65492,7 +65495,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2341" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65518,7 +65521,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65544,7 +65547,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2343" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65570,7 +65573,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2344" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65596,7 +65599,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2345" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65622,7 +65625,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2346" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65648,7 +65651,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2347" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65674,7 +65677,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2348" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65700,7 +65703,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2349" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65726,7 +65729,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2350" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65752,7 +65755,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2351" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65778,7 +65781,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2352" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65804,7 +65807,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2353" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65830,7 +65833,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2354" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65856,7 +65859,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2355" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65882,7 +65885,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2356" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65908,7 +65911,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2357" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65934,7 +65937,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2358" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65960,7 +65963,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2359" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65986,7 +65989,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2360" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66012,7 +66015,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2361" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66038,7 +66041,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2362" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66064,7 +66067,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2363" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66090,7 +66093,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2364" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66116,7 +66119,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2365" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66142,7 +66145,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2366" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66168,7 +66171,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2367" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66194,7 +66197,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G2368" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66220,7 +66223,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2369" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66246,7 +66249,7 @@
         <v>12</v>
       </c>
       <c r="G2370" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66272,7 +66275,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2371" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66298,7 +66301,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2372" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66324,7 +66327,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2373" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66350,7 +66353,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2374" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66376,7 +66379,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2375" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66402,7 +66405,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2376" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66428,7 +66431,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66454,7 +66457,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2378" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66480,7 +66483,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2379" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66506,7 +66509,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2380" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66532,7 +66535,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2381" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66558,7 +66561,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2382" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66584,7 +66587,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2383" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66610,7 +66613,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2384" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66636,7 +66639,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2385" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66662,7 +66665,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2386" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66688,7 +66691,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2387" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66714,7 +66717,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2388" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66740,7 +66743,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2389" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66766,7 +66769,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2390" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66792,7 +66795,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2391" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66818,7 +66821,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2392" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66844,7 +66847,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2393" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66870,7 +66873,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2394" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66896,7 +66899,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2395" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66922,7 +66925,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2396" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66948,7 +66951,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2397" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66974,7 +66977,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2398" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67000,7 +67003,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2399" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67026,7 +67029,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2400" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67052,7 +67055,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2401" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67078,7 +67081,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2402" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67104,7 +67107,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67130,7 +67133,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67156,7 +67159,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2405" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67182,7 +67185,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2406" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67208,7 +67211,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67234,7 +67237,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2408" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67260,7 +67263,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67286,7 +67289,7 @@
         <v>12.5</v>
       </c>
       <c r="G2410" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67312,7 +67315,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2411" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67338,7 +67341,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67364,7 +67367,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2413" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67390,7 +67393,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2414" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67416,7 +67419,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2415" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67442,7 +67445,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67468,7 +67471,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2417" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67494,7 +67497,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2418" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67520,7 +67523,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67546,7 +67549,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2420" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67572,7 +67575,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2421" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67598,7 +67601,7 @@
         <v>13</v>
       </c>
       <c r="G2422" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67624,7 +67627,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67650,7 +67653,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G2424" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67676,7 +67679,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2425" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67702,7 +67705,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2426" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67728,7 +67731,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67754,7 +67757,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2428" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67780,7 +67783,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2429" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67806,7 +67809,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2430" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67832,7 +67835,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2431" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67858,7 +67861,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2432" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67884,7 +67887,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2433" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67910,7 +67913,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2434" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67936,7 +67939,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2435" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67962,7 +67965,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2436" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67988,7 +67991,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2437" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68014,7 +68017,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2438" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68040,7 +68043,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2439" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68066,7 +68069,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2440" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68092,7 +68095,7 @@
         <v>13.5</v>
       </c>
       <c r="G2441" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68118,7 +68121,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2442" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68144,7 +68147,7 @@
         <v>13.5</v>
       </c>
       <c r="G2443" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68170,7 +68173,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2444" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68196,7 +68199,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68222,7 +68225,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2446" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68248,7 +68251,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2447" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68274,7 +68277,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2448" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68300,7 +68303,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2449" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68326,7 +68329,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2450" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68352,7 +68355,7 @@
         <v>14</v>
       </c>
       <c r="G2451" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68378,7 +68381,7 @@
         <v>14</v>
       </c>
       <c r="G2452" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68404,7 +68407,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2453" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68430,7 +68433,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2454" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68456,7 +68459,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2455" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68482,7 +68485,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2456" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68508,7 +68511,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2457" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68534,7 +68537,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2458" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68560,7 +68563,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G2459" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68586,7 +68589,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2460" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68612,7 +68615,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G2461" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68638,7 +68641,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2462" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68664,7 +68667,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G2463" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68690,7 +68693,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2464" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68716,7 +68719,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G2465" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68742,7 +68745,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2466" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68768,7 +68771,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2467" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68794,7 +68797,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68820,7 +68823,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2469" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68846,7 +68849,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68872,7 +68875,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68898,7 +68901,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2472" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68924,7 +68927,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2473" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68950,7 +68953,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2474" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68976,7 +68979,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69002,7 +69005,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G2476" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69028,7 +69031,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69054,7 +69057,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69080,7 +69083,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69106,7 +69109,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2480" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69132,7 +69135,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2481" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69158,7 +69161,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69184,7 +69187,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2483" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69210,7 +69213,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2484" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69236,7 +69239,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2485" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69262,7 +69265,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2486" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69288,7 +69291,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G2487" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69314,7 +69317,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2488" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69340,7 +69343,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2489" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69366,7 +69369,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2490" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69392,7 +69395,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2491" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69418,7 +69421,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2492" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69444,7 +69447,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2493" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69470,7 +69473,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69478,7 +69481,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6494560185</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>226887</v>
@@ -69496,9 +69499,35 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6495717593</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>119484</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>13.4200000762939</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>13.2799997329712</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>13.3599996566772</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1422</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">CE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52814483642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46432113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30644035339355</t>
+    <t xml:space="preserve">4.52814531326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46432161331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3064398765564</t>
   </si>
   <si>
     <t xml:space="preserve">4.26613092422485</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">4.31315898895264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3198766708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3669056892395</t>
+    <t xml:space="preserve">4.31987762451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36690521240234</t>
   </si>
   <si>
     <t xml:space="preserve">4.27284908294678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23589754104614</t>
+    <t xml:space="preserve">4.23589897155762</t>
   </si>
   <si>
     <t xml:space="preserve">4.05114507675171</t>
@@ -77,31 +77,31 @@
     <t xml:space="preserve">4.08473634719849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74210214614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9167788028717</t>
+    <t xml:space="preserve">3.74210286140442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91677808761597</t>
   </si>
   <si>
     <t xml:space="preserve">4.03099012374878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15527868270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12840509414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01419401168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12504625320435</t>
+    <t xml:space="preserve">4.15527820587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12840557098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01419448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12504577636719</t>
   </si>
   <si>
     <t xml:space="preserve">4.1216869354248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94701075553894</t>
+    <t xml:space="preserve">3.94701099395752</t>
   </si>
   <si>
     <t xml:space="preserve">3.80256748199463</t>
@@ -110,94 +110,94 @@
     <t xml:space="preserve">3.83615875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86975073814392</t>
+    <t xml:space="preserve">3.86975049972534</t>
   </si>
   <si>
     <t xml:space="preserve">3.58086276054382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42970037460327</t>
+    <t xml:space="preserve">3.42970061302185</t>
   </si>
   <si>
     <t xml:space="preserve">3.75217986106873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6077356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84959530830383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670037269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96716570854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06458234786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82943987846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77233529090881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90334153175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87982845306396</t>
+    <t xml:space="preserve">3.60773611068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84959554672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670156478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96716642379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06458139419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82944011688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77233505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90334177017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87982702255249</t>
   </si>
   <si>
     <t xml:space="preserve">3.72866559028625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79584884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88318729400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95708870887756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13176441192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19558763504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18551158905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13848257064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22246074676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29972219467163</t>
+    <t xml:space="preserve">3.79584860801697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88318681716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95708847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13176488876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19558811187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18551111221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13848304748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22246217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29972267150879</t>
   </si>
   <si>
     <t xml:space="preserve">4.3568286895752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25605297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27956771850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14856052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32659578323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26949024200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16535615921021</t>
+    <t xml:space="preserve">4.25605344772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2795672416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14856100082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32659530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26948976516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16535663604736</t>
   </si>
   <si>
     <t xml:space="preserve">4.09817266464233</t>
@@ -209,67 +209,67 @@
     <t xml:space="preserve">4.04106712341309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93021464347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91006064414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81936264038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75889778137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7118706703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93357443809509</t>
+    <t xml:space="preserve">3.93021583557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91006088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81936287879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75889801979065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71186995506287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93357419967651</t>
   </si>
   <si>
     <t xml:space="preserve">3.82608151435852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0813775062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15863800048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17879247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21238422393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21574354171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28292608261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30308103561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35346984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19894790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07465887069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08809566497803</t>
+    <t xml:space="preserve">4.08137655258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15863752365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17879295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21238470077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21574401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28292655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30308198928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3534688949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19894695281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07465934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08809614181519</t>
   </si>
   <si>
     <t xml:space="preserve">4.06122255325317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02427196502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693327903748</t>
+    <t xml:space="preserve">4.02427101135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693351745605</t>
   </si>
   <si>
     <t xml:space="preserve">4.21648979187012</t>
@@ -278,19 +278,19 @@
     <t xml:space="preserve">4.14420652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19927978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2543511390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23370027542114</t>
+    <t xml:space="preserve">4.19927883148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25435209274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23369979858398</t>
   </si>
   <si>
     <t xml:space="preserve">4.23714160919189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49185180664062</t>
+    <t xml:space="preserve">4.49185276031494</t>
   </si>
   <si>
     <t xml:space="preserve">4.4987359046936</t>
@@ -299,40 +299,40 @@
     <t xml:space="preserve">4.47119998931885</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45743131637573</t>
+    <t xml:space="preserve">4.45743179321289</t>
   </si>
   <si>
     <t xml:space="preserve">4.46431636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37826490402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31975030899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37138080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28188753128052</t>
+    <t xml:space="preserve">4.37826538085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31975078582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3713812828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28188848495483</t>
   </si>
   <si>
     <t xml:space="preserve">4.42989587783813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34040212631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35072994232178</t>
+    <t xml:space="preserve">4.34040355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35072898864746</t>
   </si>
   <si>
     <t xml:space="preserve">4.25090980529785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03750371932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91703248023987</t>
+    <t xml:space="preserve">4.03750324249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91703271865845</t>
   </si>
   <si>
     <t xml:space="preserve">3.98243093490601</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">3.8688440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1373233795166</t>
+    <t xml:space="preserve">4.13732290267944</t>
   </si>
   <si>
     <t xml:space="preserve">4.33696031570435</t>
@@ -350,16 +350,16 @@
     <t xml:space="preserve">4.38170671463013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42301177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52971458435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74148917198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181579589844</t>
+    <t xml:space="preserve">4.423011302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52971410751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74148941040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7518150806427</t>
   </si>
   <si>
     <t xml:space="preserve">3.73116302490234</t>
@@ -368,226 +368,226 @@
     <t xml:space="preserve">3.84130787849426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65199613571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52464056015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42826437950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50743126869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65887975692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75525712966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82065606117249</t>
+    <t xml:space="preserve">3.65199589729309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52464079856873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42826414108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50743055343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65888094902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75525689125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82065558433533</t>
   </si>
   <si>
     <t xml:space="preserve">3.78623580932617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90670704841614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96522164344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95145297050476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04094552993774</t>
+    <t xml:space="preserve">3.90670657157898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96522116661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95145273208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04094505310059</t>
   </si>
   <si>
     <t xml:space="preserve">4.01340961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94456887245178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98931527137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95833706855774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79656219482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90326499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80000400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6864161491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70018458366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76558303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362710952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66576433181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66920590400696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55217719078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48677849769592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47989463806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37319183349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37181496620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50054717063904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68985867500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561947822571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45235848426819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47645258903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64511251449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72083711624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70706915855408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77935123443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80688762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61413383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757636070251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57971358299255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56594514846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49366211891174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49022030830383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4489164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63822770118713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49710512161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38695955276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35804653167725</t>
+    <t xml:space="preserve">3.94456911087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98931574821472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95833730697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79656147956848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90326476097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80000305175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68641662597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70018529891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76558351516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362687110901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66576457023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66920638084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55217671394348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48677825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47989439964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37319159507751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37181448936462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50054693222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68985891342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561876296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45235872268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47645235061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64511227607727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72083759307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706868171692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77935147285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80688810348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61413407325745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6175754070282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57971382141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56594491004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49366283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49022078514099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44891619682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63822817802429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49710488319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38696026802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35804605484009</t>
   </si>
   <si>
     <t xml:space="preserve">3.37456822395325</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31123495101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32638049125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35529279708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41587281227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51431465148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48333716392517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51087307929993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51775670051575</t>
+    <t xml:space="preserve">3.31123447418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32637977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35529327392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41587233543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51431488990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48333692550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51087260246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51775765419006</t>
   </si>
   <si>
     <t xml:space="preserve">3.4730110168457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57627129554749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53496694564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64855456352234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67953324317932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59692406654358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64167022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63134384155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56250357627869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5315248966217</t>
+    <t xml:space="preserve">3.57627153396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53496718406677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64855432510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67953252792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.596923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64166975021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63134407997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56250333786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53152561187744</t>
   </si>
   <si>
     <t xml:space="preserve">3.45580053329468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41174244880676</t>
+    <t xml:space="preserve">3.41174268722534</t>
   </si>
   <si>
     <t xml:space="preserve">3.42964100837708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45924282073975</t>
+    <t xml:space="preserve">3.45924258232117</t>
   </si>
   <si>
     <t xml:space="preserve">3.44203233718872</t>
@@ -596,55 +596,55 @@
     <t xml:space="preserve">3.52808308601379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6347861289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67609119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6279022693634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58659768104553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5452938079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55906128883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56938791275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71739435195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94112634658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00996780395508</t>
+    <t xml:space="preserve">3.63478684425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67609024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62790203094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58659791946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54529333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5590615272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56938743591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71739482879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94112753868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00996732711792</t>
   </si>
   <si>
     <t xml:space="preserve">3.88605427742004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97210550308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83442378044128</t>
+    <t xml:space="preserve">3.9721052646637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83442449569702</t>
   </si>
   <si>
     <t xml:space="preserve">3.92735862731934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9858729839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0547137260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93080139160156</t>
+    <t xml:space="preserve">3.98587322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05471420288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93080115318298</t>
   </si>
   <si>
     <t xml:space="preserve">4.04438734054565</t>
@@ -653,16 +653,16 @@
     <t xml:space="preserve">4.06159830093384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91014885902405</t>
+    <t xml:space="preserve">3.91014838218689</t>
   </si>
   <si>
     <t xml:space="preserve">3.89982223510742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05815553665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07192420959473</t>
+    <t xml:space="preserve">4.05815601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07192468643188</t>
   </si>
   <si>
     <t xml:space="preserve">4.07880878448486</t>
@@ -671,67 +671,67 @@
     <t xml:space="preserve">4.03061962127686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19583702087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20960474014282</t>
+    <t xml:space="preserve">4.19583749771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20960521697998</t>
   </si>
   <si>
     <t xml:space="preserve">4.29565620422363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27844667434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24746799468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30254077911377</t>
+    <t xml:space="preserve">4.27844619750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24746751785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30253982543945</t>
   </si>
   <si>
     <t xml:space="preserve">4.1269965171814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13043880462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20272159576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10634469985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12011241912842</t>
+    <t xml:space="preserve">4.13043832778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20272207260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1063437461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12011289596558</t>
   </si>
   <si>
     <t xml:space="preserve">4.17862749099731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24058389663696</t>
+    <t xml:space="preserve">4.2405834197998</t>
   </si>
   <si>
     <t xml:space="preserve">4.14764881134033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16141748428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04783058166504</t>
+    <t xml:space="preserve">4.16141700744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04782962799072</t>
   </si>
   <si>
     <t xml:space="preserve">4.14076471328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1510910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15453338623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18206930160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15797472000122</t>
+    <t xml:space="preserve">4.15109062194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15453290939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18206882476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15797519683838</t>
   </si>
   <si>
     <t xml:space="preserve">4.21304702758789</t>
@@ -740,70 +740,70 @@
     <t xml:space="preserve">4.32319259643555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36449718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43333768844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44022178649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38514947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47464275360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41956901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37482261657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41268539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34384441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30942487716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36793899536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35417127609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28532981872559</t>
+    <t xml:space="preserve">4.36449670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43333721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44022130966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3851490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47464179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41956949234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37482309341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41268491744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34384489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30942440032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36793851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35417079925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28533029556274</t>
   </si>
   <si>
     <t xml:space="preserve">4.52627229690552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40580129623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48840999603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50906276702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53659868240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54348230361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.447105884552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67083740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69899606704712</t>
+    <t xml:space="preserve">4.40580177307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48841047286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50906229019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53659820556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54348182678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44710540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67083835601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69899654388428</t>
   </si>
   <si>
     <t xml:space="preserve">4.80107259750366</t>
@@ -815,10 +815,10 @@
     <t xml:space="preserve">4.83627080917358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86090993881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85034942626953</t>
+    <t xml:space="preserve">4.8609094619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85035037994385</t>
   </si>
   <si>
     <t xml:space="preserve">4.87850904464722</t>
@@ -827,19 +827,19 @@
     <t xml:space="preserve">4.78347301483154</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72011613845825</t>
+    <t xml:space="preserve">4.72011518478394</t>
   </si>
   <si>
     <t xml:space="preserve">4.68491792678833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73067474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75179433822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81515169143677</t>
+    <t xml:space="preserve">4.7306752204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75179481506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81515216827393</t>
   </si>
   <si>
     <t xml:space="preserve">4.81163167953491</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">4.92778635025024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93834590911865</t>
+    <t xml:space="preserve">4.93834638595581</t>
   </si>
   <si>
     <t xml:space="preserve">4.87498950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80811214447021</t>
+    <t xml:space="preserve">4.80811166763306</t>
   </si>
   <si>
     <t xml:space="preserve">4.80459213256836</t>
@@ -863,22 +863,22 @@
     <t xml:space="preserve">4.7869930267334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95946550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86442899703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89258813858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89610815048218</t>
+    <t xml:space="preserve">4.95946502685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86442947387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89258861541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89610767364502</t>
   </si>
   <si>
     <t xml:space="preserve">4.91370725631714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97354459762573</t>
+    <t xml:space="preserve">4.97354507446289</t>
   </si>
   <si>
     <t xml:space="preserve">4.97706460952759</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.1108193397522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2586522102356</t>
+    <t xml:space="preserve">5.25865268707275</t>
   </si>
   <si>
     <t xml:space="preserve">5.0615406036377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08617925643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10377931594849</t>
+    <t xml:space="preserve">5.08618021011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10377979278564</t>
   </si>
   <si>
     <t xml:space="preserve">5.09673976898193</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0509819984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08969926834106</t>
+    <t xml:space="preserve">5.05098152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08969974517822</t>
   </si>
   <si>
     <t xml:space="preserve">5.01930284500122</t>
@@ -917,31 +917,31 @@
     <t xml:space="preserve">5.04746150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96650505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91018724441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00874280929565</t>
+    <t xml:space="preserve">4.96650457382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91018772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00874328613281</t>
   </si>
   <si>
     <t xml:space="preserve">5.10025882720947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06858062744141</t>
+    <t xml:space="preserve">5.06858015060425</t>
   </si>
   <si>
     <t xml:space="preserve">5.13193798065186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04042196273804</t>
+    <t xml:space="preserve">5.04042148590088</t>
   </si>
   <si>
     <t xml:space="preserve">5.1248984336853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20937442779541</t>
+    <t xml:space="preserve">5.20937490463257</t>
   </si>
   <si>
     <t xml:space="preserve">5.36424779891968</t>
@@ -950,64 +950,64 @@
     <t xml:space="preserve">5.21289443969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03690195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16361618041992</t>
+    <t xml:space="preserve">5.03690242767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16361665725708</t>
   </si>
   <si>
     <t xml:space="preserve">5.27273225784302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23049354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15305757522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2023344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11433839797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10729932785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00522327423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99818420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01226234436035</t>
+    <t xml:space="preserve">5.23049306869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15305662155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20233488082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11433887481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10729885101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00522422790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99818325042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01226377487183</t>
   </si>
   <si>
     <t xml:space="preserve">5.04394197463989</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06506061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15657663345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34312868118286</t>
+    <t xml:space="preserve">5.06506109237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15657711029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34312963485718</t>
   </si>
   <si>
     <t xml:space="preserve">5.30089092254639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27977228164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30793046951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25161266326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29385089874268</t>
+    <t xml:space="preserve">5.27977132797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30792999267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25161361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29385042190552</t>
   </si>
   <si>
     <t xml:space="preserve">5.29033088684082</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">5.33608913421631</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34664869308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36776828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35368919372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38536691665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39944648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26569271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31145000457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3255295753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28329086303711</t>
+    <t xml:space="preserve">5.34664821624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36776781082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35368871688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38536739349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3994460105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26569223403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31145095825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32552909851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28329181671143</t>
   </si>
   <si>
     <t xml:space="preserve">5.23401355743408</t>
@@ -1058,28 +1058,28 @@
     <t xml:space="preserve">5.31497001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29737043380737</t>
+    <t xml:space="preserve">5.29737091064453</t>
   </si>
   <si>
     <t xml:space="preserve">5.19177579879761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35720777511597</t>
+    <t xml:space="preserve">5.35720825195312</t>
   </si>
   <si>
     <t xml:space="preserve">5.07210111618042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98410415649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94186639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86794948577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92426681518555</t>
+    <t xml:space="preserve">4.9841046333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94186687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86794900894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92426729202271</t>
   </si>
   <si>
     <t xml:space="preserve">4.98058414459229</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">5.05450105667114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1847357749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17417573928833</t>
+    <t xml:space="preserve">5.18473529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17417669296265</t>
   </si>
   <si>
     <t xml:space="preserve">5.21993398666382</t>
@@ -1103,82 +1103,82 @@
     <t xml:space="preserve">5.17769622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22697448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28681182861328</t>
+    <t xml:space="preserve">5.22697353363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28681087493896</t>
   </si>
   <si>
     <t xml:space="preserve">5.02282285690308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0017032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02986288070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05802154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92074728012085</t>
+    <t xml:space="preserve">5.00170421600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02986192703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05802059173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92074680328369</t>
   </si>
   <si>
     <t xml:space="preserve">4.99114418029785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37128734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47688245773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48392295837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44168519973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43464469909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5261607170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51208114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4698429107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40648555755615</t>
+    <t xml:space="preserve">5.37128782272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47688341140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48392248153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44168424606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43464517593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52616024017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51208162307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46984338760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40648603439331</t>
   </si>
   <si>
     <t xml:space="preserve">5.37832736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18825531005859</t>
+    <t xml:space="preserve">5.18825578689575</t>
   </si>
   <si>
     <t xml:space="preserve">5.13897800445557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32904958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14601755142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19529485702515</t>
+    <t xml:space="preserve">5.3290491104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14601707458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1952953338623</t>
   </si>
   <si>
     <t xml:space="preserve">5.24457263946533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22345447540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23753261566162</t>
+    <t xml:space="preserve">5.22345399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23753356933594</t>
   </si>
   <si>
     <t xml:space="preserve">5.16009616851807</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">4.97002553939819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21899938583374</t>
+    <t xml:space="preserve">5.21899890899658</t>
   </si>
   <si>
     <t xml:space="preserve">5.14661407470703</t>
@@ -1199,40 +1199,40 @@
     <t xml:space="preserve">4.98012781143188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94393444061279</t>
+    <t xml:space="preserve">4.94393396377563</t>
   </si>
   <si>
     <t xml:space="preserve">4.81364059448242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84259510040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85707187652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8208794593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80640172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56029081344604</t>
+    <t xml:space="preserve">4.84259462356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85707139968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82087898254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8064022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56029176712036</t>
   </si>
   <si>
     <t xml:space="preserve">4.46618986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21284055709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45171308517456</t>
+    <t xml:space="preserve">4.21284008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4517126083374</t>
   </si>
   <si>
     <t xml:space="preserve">4.37208843231201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52409839630127</t>
+    <t xml:space="preserve">4.52409887313843</t>
   </si>
   <si>
     <t xml:space="preserve">4.40828084945679</t>
@@ -1256,16 +1256,16 @@
     <t xml:space="preserve">4.53133678436279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61096143722534</t>
+    <t xml:space="preserve">4.61096000671387</t>
   </si>
   <si>
     <t xml:space="preserve">4.64715337753296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69058465957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57476854324341</t>
+    <t xml:space="preserve">4.69058513641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57476758956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.58200645446777</t>
@@ -1274,64 +1274,64 @@
     <t xml:space="preserve">4.48790550231934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.545814037323</t>
+    <t xml:space="preserve">4.54581451416016</t>
   </si>
   <si>
     <t xml:space="preserve">4.5892448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60372257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68334579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69782304763794</t>
+    <t xml:space="preserve">4.6037220954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68334627151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6978235244751</t>
   </si>
   <si>
     <t xml:space="preserve">4.62543773651123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63267660140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61820030212402</t>
+    <t xml:space="preserve">4.63267707824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61819934844971</t>
   </si>
   <si>
     <t xml:space="preserve">4.56752920150757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44447422027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42999649047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59648323059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47342777252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51685905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50962066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17664766311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10426187515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04635381698608</t>
+    <t xml:space="preserve">4.44447374343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42999696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59648370742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47342824935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51685953140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50962162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1766471862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10426139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04635334014893</t>
   </si>
   <si>
     <t xml:space="preserve">4.0246376991272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03187656402588</t>
+    <t xml:space="preserve">4.03187608718872</t>
   </si>
   <si>
     <t xml:space="preserve">4.05359172821045</t>
@@ -1340,28 +1340,28 @@
     <t xml:space="preserve">4.06806898117065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97396779060364</t>
+    <t xml:space="preserve">3.97396755218506</t>
   </si>
   <si>
     <t xml:space="preserve">4.00292205810547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85091257095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87262773513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93053603172302</t>
+    <t xml:space="preserve">3.85091233253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8726282119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93053650856018</t>
   </si>
   <si>
     <t xml:space="preserve">3.92329812049866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11149978637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22731733322144</t>
+    <t xml:space="preserve">4.11150026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22731781005859</t>
   </si>
   <si>
     <t xml:space="preserve">4.20560169219971</t>
@@ -1370,22 +1370,22 @@
     <t xml:space="preserve">4.22007846832275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23455572128296</t>
+    <t xml:space="preserve">4.23455619812012</t>
   </si>
   <si>
     <t xml:space="preserve">4.25627183914185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27798652648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29970359802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36485004425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35761117935181</t>
+    <t xml:space="preserve">4.27798748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2997031211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36484956741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35761070251465</t>
   </si>
   <si>
     <t xml:space="preserve">4.26351022720337</t>
@@ -1394,124 +1394,124 @@
     <t xml:space="preserve">4.09702348709106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06083011627197</t>
+    <t xml:space="preserve">4.06083106994629</t>
   </si>
   <si>
     <t xml:space="preserve">4.12597751617432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90882062911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84367370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78576588630676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87986660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94501423835754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80748081207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72061777114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68442559242249</t>
+    <t xml:space="preserve">3.90882110595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84367346763611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7857654094696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8798668384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94501304626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80748105049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72061824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68442583084106</t>
   </si>
   <si>
     <t xml:space="preserve">3.57946610450745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45641112327576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55051255226135</t>
+    <t xml:space="preserve">3.45641136169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55051231384277</t>
   </si>
   <si>
     <t xml:space="preserve">3.81471967697144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76405000686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82919669151306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83643531799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85815095901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74233365058899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75681114196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70614123344421</t>
+    <t xml:space="preserve">3.76404929161072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82919645309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83643507957458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85815119743347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74233388900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75681042671204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70614147186279</t>
   </si>
   <si>
     <t xml:space="preserve">3.67718720436096</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6337559223175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66994833946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6192786693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64099431037903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7712881565094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80024194717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66270995140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72785758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86538982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60480141639709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58670520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57584738731384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54327392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547108650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82195830345154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71337985992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69890284538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69166398048401</t>
+    <t xml:space="preserve">3.63375568389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66994857788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61927890777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64099478721619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77128767967224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80024218559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66270971298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72785687446594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86538934707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60480189323425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58670473098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57584691047668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54327321052551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547156333923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82195806503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7133800983429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69890332221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69166445732117</t>
   </si>
   <si>
     <t xml:space="preserve">3.62651705741882</t>
@@ -1520,46 +1520,46 @@
     <t xml:space="preserve">3.64823269844055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52517747879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60118246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54689335823059</t>
+    <t xml:space="preserve">3.5251772403717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60118269920349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54689264297485</t>
   </si>
   <si>
     <t xml:space="preserve">3.50346183776855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60842061042786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79300403594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88710498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56498908996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59394383430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77852702140808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58308529853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53965425491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48174571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49622273445129</t>
+    <t xml:space="preserve">3.60842084884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79300355911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88710522651672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5649893283844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59394407272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7785267829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58308506011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53965401649475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48174643516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49622297286987</t>
   </si>
   <si>
     <t xml:space="preserve">3.45279169082642</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">3.42021822929382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.431556224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43533539772034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41265964508057</t>
+    <t xml:space="preserve">3.43155598640442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43533515930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266012191772</t>
   </si>
   <si>
     <t xml:space="preserve">3.33329558372498</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">3.34841251373291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38620519638062</t>
+    <t xml:space="preserve">3.38620543479919</t>
   </si>
   <si>
     <t xml:space="preserve">3.3710880279541</t>
@@ -1592,46 +1592,46 @@
     <t xml:space="preserve">3.36352944374084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3824257850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31062006950378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32573699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29172420501709</t>
+    <t xml:space="preserve">3.38242530822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31062030792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3257372379303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29172348976135</t>
   </si>
   <si>
     <t xml:space="preserve">3.25393128395081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31439924240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33707499504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.276606798172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28038644790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23503541946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2048008441925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21613883972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23125576972961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21235966682434</t>
+    <t xml:space="preserve">3.31439971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33707475662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27660655975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28038597106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23503565788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20480108261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21613907814026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23125624656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21235990524292</t>
   </si>
   <si>
     <t xml:space="preserve">3.24259376525879</t>
@@ -1640,46 +1640,46 @@
     <t xml:space="preserve">3.18212556838989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13677501678467</t>
+    <t xml:space="preserve">3.13677477836609</t>
   </si>
   <si>
     <t xml:space="preserve">3.1518919467926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18968415260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20102214813232</t>
+    <t xml:space="preserve">3.18968391418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20102190971375</t>
   </si>
   <si>
     <t xml:space="preserve">3.25015234947205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39376330375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59784269332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65831112861633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55627083778381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5524914264679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56760883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57516765594482</t>
+    <t xml:space="preserve">3.39376306533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59784340858459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65831089019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55627107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55249190330505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56760907173157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57516741752625</t>
   </si>
   <si>
     <t xml:space="preserve">3.60540127754211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53359627723694</t>
+    <t xml:space="preserve">3.5335955619812</t>
   </si>
   <si>
     <t xml:space="preserve">3.4769070148468</t>
@@ -1688,94 +1688,94 @@
     <t xml:space="preserve">3.59028434753418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58272552490234</t>
+    <t xml:space="preserve">3.5827260017395</t>
   </si>
   <si>
     <t xml:space="preserve">3.57138824462891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52603697776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50336217880249</t>
+    <t xml:space="preserve">3.52603721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50336194038391</t>
   </si>
   <si>
     <t xml:space="preserve">3.43911480903625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42777681350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40132188796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36730861663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40888071060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34085440635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4239981174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51469945907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49958205223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54871273040771</t>
+    <t xml:space="preserve">3.4277765750885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40132236480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36730885505676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40888047218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34085416793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42399764060974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51469969749451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49958252906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54871249198914</t>
   </si>
   <si>
     <t xml:space="preserve">3.6394145488739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65453219413757</t>
+    <t xml:space="preserve">3.65453147888184</t>
   </si>
   <si>
     <t xml:space="preserve">3.68098640441895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67342805862427</t>
+    <t xml:space="preserve">3.67342758178711</t>
   </si>
   <si>
     <t xml:space="preserve">3.73011636734009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78680515289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285799980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8623902797699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74523377418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76790881156921</t>
+    <t xml:space="preserve">3.78680539131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285776138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86239051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74523305892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76790904998779</t>
   </si>
   <si>
     <t xml:space="preserve">3.83971476554871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83215618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73767471313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69232392311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70366215705872</t>
+    <t xml:space="preserve">3.83215641975403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168774604797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73767495155334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69232416152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70366168022156</t>
   </si>
   <si>
     <t xml:space="preserve">3.77924680709839</t>
@@ -1787,43 +1787,43 @@
     <t xml:space="preserve">3.66586923599243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6961030960083</t>
+    <t xml:space="preserve">3.69610285758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.66964840888977</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73389601707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81703901290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84727311134338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90018272399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98332619667053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96065068244934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95309257507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93041682243347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94553375244141</t>
+    <t xml:space="preserve">3.73389577865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81703948974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84727358818054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90018248558044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98332595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96065044403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95309162139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93041610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94553351402283</t>
   </si>
   <si>
     <t xml:space="preserve">3.99088478088379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9152991771698</t>
+    <t xml:space="preserve">3.91529941558838</t>
   </si>
   <si>
     <t xml:space="preserve">4.02111864089966</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">4.06646966934204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0815863609314</t>
+    <t xml:space="preserve">4.08158683776855</t>
   </si>
   <si>
     <t xml:space="preserve">4.1344952583313</t>
@@ -1850,22 +1850,22 @@
     <t xml:space="preserve">4.02867698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00600147247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04379367828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11937952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01355981826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96820855140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93797492980957</t>
+    <t xml:space="preserve">4.00600099563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04379463195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11937856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96820902824402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93797516822815</t>
   </si>
   <si>
     <t xml:space="preserve">3.9757673740387</t>
@@ -1874,61 +1874,61 @@
     <t xml:space="preserve">3.90774083137512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8926248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88506507873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87750720977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85483145713806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80192232131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5940637588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6016218662262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65075206756592</t>
+    <t xml:space="preserve">3.89262390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88506555557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87750697135925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85483169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80192255973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59406399726868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60162210464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6507523059845</t>
   </si>
   <si>
     <t xml:space="preserve">3.71877884864807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99844312667847</t>
+    <t xml:space="preserve">3.99844288825989</t>
   </si>
   <si>
     <t xml:space="preserve">3.72255778312683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63185572624207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46556949615479</t>
+    <t xml:space="preserve">3.63185596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46556901931763</t>
   </si>
   <si>
     <t xml:space="preserve">3.44667291641235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28416538238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11032009124756</t>
+    <t xml:space="preserve">3.28416514396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11031985282898</t>
   </si>
   <si>
     <t xml:space="preserve">3.0649688243866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83821439743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83443522453308</t>
+    <t xml:space="preserve">2.83821415901184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8344349861145</t>
   </si>
   <si>
     <t xml:space="preserve">2.95915007591248</t>
@@ -1937,100 +1937,100 @@
     <t xml:space="preserve">2.70971989631653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93269562721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00450086593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97426724433899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94403338432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91001987457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96292924880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85333132743835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89490294456482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88734459877014</t>
+    <t xml:space="preserve">2.93269538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00450110435486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97426700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94403290748596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91002011299133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96292972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85333108901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8949031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88734436035156</t>
   </si>
   <si>
     <t xml:space="preserve">2.92135787010193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85711026191711</t>
+    <t xml:space="preserve">2.85711050033569</t>
   </si>
   <si>
     <t xml:space="preserve">2.9024612903595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82687664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89112377166748</t>
+    <t xml:space="preserve">2.82687640190125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8911235332489</t>
   </si>
   <si>
     <t xml:space="preserve">2.9969425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9515917301178</t>
+    <t xml:space="preserve">2.95159149169922</t>
   </si>
   <si>
     <t xml:space="preserve">2.97804641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99316358566284</t>
+    <t xml:space="preserve">2.99316334724426</t>
   </si>
   <si>
     <t xml:space="preserve">3.05363130569458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03473520278931</t>
+    <t xml:space="preserve">3.03473496437073</t>
   </si>
   <si>
     <t xml:space="preserve">3.02717685699463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12165760993958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06119012832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09898233413696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16700887680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14433312416077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19346380233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21991848945618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26904773712158</t>
+    <t xml:space="preserve">3.12165784835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06118988990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09898209571838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16700863838196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14433336257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19346332550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21991872787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26904845237732</t>
   </si>
   <si>
     <t xml:space="preserve">3.32195782661438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15945029258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07252764701843</t>
+    <t xml:space="preserve">3.1594500541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07252740859985</t>
   </si>
   <si>
     <t xml:space="preserve">3.06874823570251</t>
@@ -2042,61 +2042,61 @@
     <t xml:space="preserve">3.16322946548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27282738685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28794479370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40510153770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51091980934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48824453353882</t>
+    <t xml:space="preserve">3.27282762527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28794407844543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40510129928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51092004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4882447719574</t>
   </si>
   <si>
     <t xml:space="preserve">3.45801043510437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29550313949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34463381767273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29928207397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30684113502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30306148529053</t>
+    <t xml:space="preserve">3.29550337791443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34463310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29928231239319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30684089660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30306172370911</t>
   </si>
   <si>
     <t xml:space="preserve">3.26149010658264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37864661216736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3748676776886</t>
+    <t xml:space="preserve">3.37864637374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37486743927002</t>
   </si>
   <si>
     <t xml:space="preserve">3.26526927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754271507263</t>
+    <t xml:space="preserve">3.39754319190979</t>
   </si>
   <si>
     <t xml:space="preserve">3.48068642616272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38998436927795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31817841529846</t>
+    <t xml:space="preserve">3.38998460769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31817865371704</t>
   </si>
   <si>
     <t xml:space="preserve">3.25771069526672</t>
@@ -2105,37 +2105,37 @@
     <t xml:space="preserve">3.22747659683228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18590474128723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24637293815613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17456698417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14055418968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17834639549255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09142398834229</t>
+    <t xml:space="preserve">3.18590497970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24637317657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17456674575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14055442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17834663391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09142374992371</t>
   </si>
   <si>
     <t xml:space="preserve">3.08008599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04607319831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01583909988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94025373458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95537090301514</t>
+    <t xml:space="preserve">3.0460729598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01583886146545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9402539730072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95537066459656</t>
   </si>
   <si>
     <t xml:space="preserve">2.92513680458069</t>
@@ -2156,22 +2156,22 @@
     <t xml:space="preserve">2.75129151344299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71727824211121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72105765342712</t>
+    <t xml:space="preserve">2.71727848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72105717658997</t>
   </si>
   <si>
     <t xml:space="preserve">2.67948603630066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55477118492126</t>
+    <t xml:space="preserve">2.55477070808411</t>
   </si>
   <si>
     <t xml:space="preserve">2.44895172119141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55099153518677</t>
+    <t xml:space="preserve">2.55099177360535</t>
   </si>
   <si>
     <t xml:space="preserve">2.61523866653442</t>
@@ -2186,31 +2186,31 @@
     <t xml:space="preserve">3.53737473487854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62807703018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63563513755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.578946352005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56382989883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50714087486267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48446536064148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52225804328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12543725967407</t>
+    <t xml:space="preserve">3.62807679176331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63563561439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57894706726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56382942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50714063644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48446583747864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52225780487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41643905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12543702125549</t>
   </si>
   <si>
     <t xml:space="preserve">3.80948066711426</t>
@@ -2219,82 +2219,82 @@
     <t xml:space="preserve">3.76035070419312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64319372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68476533889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74901247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7943639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75657153129578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77546715736389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76412963867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15717172622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11182022094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17228841781616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31345558166504</t>
+    <t xml:space="preserve">3.64319396018982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68476557731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74901294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79436349868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75657105445862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77546739578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76412987709045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15717124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11182069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.172287940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3134560585022</t>
   </si>
   <si>
     <t xml:space="preserve">4.22718667984009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12523221969604</t>
+    <t xml:space="preserve">4.12523317337036</t>
   </si>
   <si>
     <t xml:space="preserve">4.07817649841309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08601903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09386205673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20365905761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26639986038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27424240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25855731964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36835432052612</t>
+    <t xml:space="preserve">4.08601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09386157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20365858078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26640033721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27424287796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25855684280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36835479736328</t>
   </si>
   <si>
     <t xml:space="preserve">4.32914113998413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34482669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35267019271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30561351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28992748260498</t>
+    <t xml:space="preserve">4.34482622146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35266971588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30561256408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28992795944214</t>
   </si>
   <si>
     <t xml:space="preserve">4.28208541870117</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">4.03896331787109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02327823638916</t>
+    <t xml:space="preserve">4.02327871322632</t>
   </si>
   <si>
     <t xml:space="preserve">3.99974989891052</t>
@@ -2321,22 +2321,22 @@
     <t xml:space="preserve">4.03112077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05464887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93700933456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92132329940796</t>
+    <t xml:space="preserve">4.05464839935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93700861930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9213240146637</t>
   </si>
   <si>
     <t xml:space="preserve">4.01543521881104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07033395767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9762225151062</t>
+    <t xml:space="preserve">4.07033348083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97622203826904</t>
   </si>
   <si>
     <t xml:space="preserve">4.18797397613525</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">4.21150159835815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39188241958618</t>
+    <t xml:space="preserve">4.39188194274902</t>
   </si>
   <si>
     <t xml:space="preserve">4.45462369918823</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">4.43109560012817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42325353622437</t>
+    <t xml:space="preserve">4.42325258255005</t>
   </si>
   <si>
     <t xml:space="preserve">4.38403987884521</t>
@@ -2369,49 +2369,49 @@
     <t xml:space="preserve">4.33698463439941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.360511302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4624662399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44678115844727</t>
+    <t xml:space="preserve">4.36051177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46246671676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44678068161011</t>
   </si>
   <si>
     <t xml:space="preserve">4.4389386177063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47815132141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48599433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50167989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56442022323608</t>
+    <t xml:space="preserve">4.47815179824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4859938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50167942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5644211769104</t>
   </si>
   <si>
     <t xml:space="preserve">4.60363388061523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62716245651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63500452041626</t>
+    <t xml:space="preserve">4.62716197967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6350040435791</t>
   </si>
   <si>
     <t xml:space="preserve">4.49383640289307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59579133987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66637468338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68205976486206</t>
+    <t xml:space="preserve">4.59579086303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66637516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68206024169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.72911643981934</t>
@@ -2420,28 +2420,28 @@
     <t xml:space="preserve">4.64284753799438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74480199813843</t>
+    <t xml:space="preserve">4.74480152130127</t>
   </si>
   <si>
     <t xml:space="preserve">4.86244106292725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90949726104736</t>
+    <t xml:space="preserve">4.90949678421021</t>
   </si>
   <si>
     <t xml:space="preserve">5.05850696563721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03498029708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99576663970947</t>
+    <t xml:space="preserve">5.03497982025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99576616287231</t>
   </si>
   <si>
     <t xml:space="preserve">4.95655298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94871044158936</t>
+    <t xml:space="preserve">4.9487099647522</t>
   </si>
   <si>
     <t xml:space="preserve">4.97223854064941</t>
@@ -2450,16 +2450,16 @@
     <t xml:space="preserve">4.87028408050537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98008060455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07419204711914</t>
+    <t xml:space="preserve">4.98008108139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0741925239563</t>
   </si>
   <si>
     <t xml:space="preserve">5.05066442489624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02713632583618</t>
+    <t xml:space="preserve">5.02713680267334</t>
   </si>
   <si>
     <t xml:space="preserve">5.08987808227539</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">5.18399000167847</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16830492019653</t>
+    <t xml:space="preserve">5.16830444335938</t>
   </si>
   <si>
     <t xml:space="preserve">5.10556364059448</t>
@@ -2480,16 +2480,16 @@
     <t xml:space="preserve">5.14477634429932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23888826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21536016464233</t>
+    <t xml:space="preserve">5.23888778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21536064147949</t>
   </si>
   <si>
     <t xml:space="preserve">5.1996750831604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25457382202148</t>
+    <t xml:space="preserve">5.25457334518433</t>
   </si>
   <si>
     <t xml:space="preserve">5.30162954330444</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">5.01929473876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93302488327026</t>
+    <t xml:space="preserve">4.93302536010742</t>
   </si>
   <si>
     <t xml:space="preserve">4.7996997833252</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">4.53305006027222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50952243804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47030925750732</t>
+    <t xml:space="preserve">4.50952196121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47030878067017</t>
   </si>
   <si>
     <t xml:space="preserve">4.55657815933228</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">4.54089307785034</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51736450195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58010578155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82322788238525</t>
+    <t xml:space="preserve">4.51736497879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58010625839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8232274055481</t>
   </si>
   <si>
     <t xml:space="preserve">4.87812662124634</t>
@@ -2558,19 +2558,19 @@
     <t xml:space="preserve">4.8859691619873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7840142250061</t>
+    <t xml:space="preserve">4.78401470184326</t>
   </si>
   <si>
     <t xml:space="preserve">4.70558834075928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65853214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77617216110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85459852218628</t>
+    <t xml:space="preserve">4.65853261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77617263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85459899902344</t>
   </si>
   <si>
     <t xml:space="preserve">4.94086790084839</t>
@@ -2579,40 +2579,40 @@
     <t xml:space="preserve">5.52122354507446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6623911857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73297548294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89767074584961</t>
+    <t xml:space="preserve">5.66239070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73297500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89767026901245</t>
   </si>
   <si>
     <t xml:space="preserve">5.68591928482056</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70160484313965</t>
+    <t xml:space="preserve">5.70160436630249</t>
   </si>
   <si>
     <t xml:space="preserve">5.59964990615845</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5369086265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906703948975</t>
+    <t xml:space="preserve">5.53690910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906656265259</t>
   </si>
   <si>
     <t xml:space="preserve">5.17614698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29378700256348</t>
+    <t xml:space="preserve">5.29378747940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.7134313583374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41541004180908</t>
+    <t xml:space="preserve">4.41541051864624</t>
   </si>
   <si>
     <t xml:space="preserve">4.89381170272827</t>
@@ -2621,28 +2621,28 @@
     <t xml:space="preserve">4.81538534164429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92518281936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84675598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72127389907837</t>
+    <t xml:space="preserve">4.9251823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84675550460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72127294540405</t>
   </si>
   <si>
     <t xml:space="preserve">4.5879487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61931896209717</t>
+    <t xml:space="preserve">4.61931848526001</t>
   </si>
   <si>
     <t xml:space="preserve">4.77163171768188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73861026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69733285903931</t>
+    <t xml:space="preserve">4.738609790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69733333587646</t>
   </si>
   <si>
     <t xml:space="preserve">4.63954496383667</t>
@@ -2651,22 +2651,22 @@
     <t xml:space="preserve">4.7963981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98627233505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95325136184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312601089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07708215713501</t>
+    <t xml:space="preserve">4.98627281188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95325088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07708168029785</t>
   </si>
   <si>
     <t xml:space="preserve">5.11835908889771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97801685333252</t>
+    <t xml:space="preserve">4.97801733016968</t>
   </si>
   <si>
     <t xml:space="preserve">5.06057167053223</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">4.9037184715271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96976232528687</t>
+    <t xml:space="preserve">4.96976137161255</t>
   </si>
   <si>
     <t xml:space="preserve">4.87069702148438</t>
@@ -2684,31 +2684,31 @@
     <t xml:space="preserve">4.82941961288452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62303447723389</t>
+    <t xml:space="preserve">4.62303400039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.40839385986328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50745820999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56524705886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
+    <t xml:space="preserve">4.50745868682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56524658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48269176483154</t>
   </si>
   <si>
     <t xml:space="preserve">4.58175754547119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64779996871948</t>
+    <t xml:space="preserve">4.64780044555664</t>
   </si>
   <si>
     <t xml:space="preserve">4.61477899551392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57350206375122</t>
+    <t xml:space="preserve">4.5735011100769</t>
   </si>
   <si>
     <t xml:space="preserve">4.51571369171143</t>
@@ -2723,34 +2723,34 @@
     <t xml:space="preserve">4.38362693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16898632049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2680516242981</t>
+    <t xml:space="preserve">4.16898679733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26805114746094</t>
   </si>
   <si>
     <t xml:space="preserve">4.39188289642334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46618127822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42490434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3753719329834</t>
+    <t xml:space="preserve">4.4661808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42490386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37537145614624</t>
   </si>
   <si>
     <t xml:space="preserve">4.27630662918091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44967031478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34235000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41664838790894</t>
+    <t xml:space="preserve">4.44966983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34235048294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41664886474609</t>
   </si>
   <si>
     <t xml:space="preserve">4.55699062347412</t>
@@ -2771,34 +2771,34 @@
     <t xml:space="preserve">4.85418605804443</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8624415397644</t>
+    <t xml:space="preserve">4.86244058609009</t>
   </si>
   <si>
     <t xml:space="preserve">4.72209930419922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75512075424194</t>
+    <t xml:space="preserve">4.7551212310791</t>
   </si>
   <si>
     <t xml:space="preserve">4.77988719940186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73035478591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82116413116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9284839630127</t>
+    <t xml:space="preserve">4.73035430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82116460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92848443984985</t>
   </si>
   <si>
     <t xml:space="preserve">4.92022943496704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94499492645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83767509460449</t>
+    <t xml:space="preserve">4.94499540328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83767461776733</t>
   </si>
   <si>
     <t xml:space="preserve">4.78814268112183</t>
@@ -2810,13 +2810,13 @@
     <t xml:space="preserve">4.60652351379395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66431140899658</t>
+    <t xml:space="preserve">4.66431093215942</t>
   </si>
   <si>
     <t xml:space="preserve">4.81290864944458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88720750808716</t>
+    <t xml:space="preserve">4.88720798492432</t>
   </si>
   <si>
     <t xml:space="preserve">4.93673992156982</t>
@@ -2828,34 +2828,34 @@
     <t xml:space="preserve">5.11010408401489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16789197921753</t>
+    <t xml:space="preserve">5.16789150238037</t>
   </si>
   <si>
     <t xml:space="preserve">5.23393535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19265794754028</t>
+    <t xml:space="preserve">5.19265842437744</t>
   </si>
   <si>
     <t xml:space="preserve">5.22567939758301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26695728302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27521181106567</t>
+    <t xml:space="preserve">5.26695680618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27521228790283</t>
   </si>
   <si>
     <t xml:space="preserve">5.29172277450562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30823421478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36602210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4320650100708</t>
+    <t xml:space="preserve">5.30823373794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36602163314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43206548690796</t>
   </si>
   <si>
     <t xml:space="preserve">5.47334241867065</t>
@@ -2864,28 +2864,28 @@
     <t xml:space="preserve">5.55589628219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41555452346802</t>
+    <t xml:space="preserve">5.41555404663086</t>
   </si>
   <si>
     <t xml:space="preserve">5.48985290527344</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46508693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57240724563599</t>
+    <t xml:space="preserve">5.46508646011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57240772247314</t>
   </si>
   <si>
     <t xml:space="preserve">5.44857597351074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49810838699341</t>
+    <t xml:space="preserve">5.49810886383057</t>
   </si>
   <si>
     <t xml:space="preserve">5.52287483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51461935043335</t>
+    <t xml:space="preserve">5.51461887359619</t>
   </si>
   <si>
     <t xml:space="preserve">5.58891820907593</t>
@@ -2903,16 +2903,16 @@
     <t xml:space="preserve">5.63019514083862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61368417739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59717321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58066320419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65496158599854</t>
+    <t xml:space="preserve">5.61368465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5971736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58066272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65496110916138</t>
   </si>
   <si>
     <t xml:space="preserve">5.77879285812378</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">5.86134672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89436817169189</t>
+    <t xml:space="preserve">5.89436864852905</t>
   </si>
   <si>
     <t xml:space="preserve">5.8118143081665</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">6.38969373703003</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39794874191284</t>
+    <t xml:space="preserve">6.39794921875</t>
   </si>
   <si>
     <t xml:space="preserve">6.47224807739258</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">6.43922662734985</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45573663711548</t>
+    <t xml:space="preserve">6.45573711395264</t>
   </si>
   <si>
     <t xml:space="preserve">6.59607887268066</t>
@@ -2978,16 +2978,16 @@
     <t xml:space="preserve">6.51352500915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56305742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67863321304321</t>
+    <t xml:space="preserve">6.5630578994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67863368988037</t>
   </si>
   <si>
     <t xml:space="preserve">6.72816562652588</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67037773132324</t>
+    <t xml:space="preserve">6.6703782081604</t>
   </si>
   <si>
     <t xml:space="preserve">6.63735628128052</t>
@@ -2996,19 +2996,19 @@
     <t xml:space="preserve">6.79420852661133</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73642158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6868896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53829145431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62084579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64561176300049</t>
+    <t xml:space="preserve">6.73642110824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68688917160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53829097747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62084531784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64561128616333</t>
   </si>
   <si>
     <t xml:space="preserve">6.71991062164307</t>
@@ -3029,28 +3029,28 @@
     <t xml:space="preserve">6.05122137069702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64670658111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85309171676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67972755432129</t>
+    <t xml:space="preserve">5.64670610427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8530912399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67972803115845</t>
   </si>
   <si>
     <t xml:space="preserve">5.39904356002808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38253211975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66321659088135</t>
+    <t xml:space="preserve">5.38253259658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66321706771851</t>
   </si>
   <si>
     <t xml:space="preserve">5.60542917251587</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74577140808105</t>
+    <t xml:space="preserve">5.7457709312439</t>
   </si>
   <si>
     <t xml:space="preserve">5.83658075332642</t>
@@ -3059,25 +3059,25 @@
     <t xml:space="preserve">5.88611316680908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79530382156372</t>
+    <t xml:space="preserve">5.79530334472656</t>
   </si>
   <si>
     <t xml:space="preserve">5.87785768508911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97692251205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91087913513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91913509368896</t>
+    <t xml:space="preserve">5.9769229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91087961196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91913461685181</t>
   </si>
   <si>
     <t xml:space="preserve">5.63845062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78704833984375</t>
+    <t xml:space="preserve">5.78704881668091</t>
   </si>
   <si>
     <t xml:space="preserve">5.94390058517456</t>
@@ -3131,13 +3131,13 @@
     <t xml:space="preserve">5.82472991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80742025375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.868004322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88531446456909</t>
+    <t xml:space="preserve">5.80742073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86800479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88531398773193</t>
   </si>
   <si>
     <t xml:space="preserve">5.87665939331055</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">5.9285888671875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96320772171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94589853286743</t>
+    <t xml:space="preserve">5.96320819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94589805603027</t>
   </si>
   <si>
     <t xml:space="preserve">5.91993379592896</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">6.22285461425781</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17092514038086</t>
+    <t xml:space="preserve">6.17092561721802</t>
   </si>
   <si>
     <t xml:space="preserve">6.28343868255615</t>
@@ -3170,31 +3170,31 @@
     <t xml:space="preserve">6.25747394561768</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24881887435913</t>
+    <t xml:space="preserve">6.24881839752197</t>
   </si>
   <si>
     <t xml:space="preserve">6.24016427993774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23150873184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26612854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46519088745117</t>
+    <t xml:space="preserve">6.2315092086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2661280632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46519041061401</t>
   </si>
   <si>
     <t xml:space="preserve">6.54308462142944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58635902404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56904983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63828802108765</t>
+    <t xml:space="preserve">6.58635950088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56904935836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6382884979248</t>
   </si>
   <si>
     <t xml:space="preserve">6.56039428710938</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">6.64694309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50846529006958</t>
+    <t xml:space="preserve">6.50846481323242</t>
   </si>
   <si>
     <t xml:space="preserve">6.66425275802612</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">6.11034107208252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30940341949463</t>
+    <t xml:space="preserve">6.30940294265747</t>
   </si>
   <si>
     <t xml:space="preserve">6.37864208221436</t>
@@ -3236,16 +3236,16 @@
     <t xml:space="preserve">6.44788074493408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49115514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49981021881104</t>
+    <t xml:space="preserve">6.49115562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49981069564819</t>
   </si>
   <si>
     <t xml:space="preserve">6.55173969268799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59501361846924</t>
+    <t xml:space="preserve">6.5950140953064</t>
   </si>
   <si>
     <t xml:space="preserve">6.70752716064453</t>
@@ -3260,40 +3260,40 @@
     <t xml:space="preserve">6.51712036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62963342666626</t>
+    <t xml:space="preserve">6.6296329498291</t>
   </si>
   <si>
     <t xml:space="preserve">6.74214696884155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87197017669678</t>
+    <t xml:space="preserve">6.87196969985962</t>
   </si>
   <si>
     <t xml:space="preserve">6.79407596588135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85466003417969</t>
+    <t xml:space="preserve">6.85466051101685</t>
   </si>
   <si>
     <t xml:space="preserve">6.61232376098633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78542137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77676582336426</t>
+    <t xml:space="preserve">6.7854208946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77676630020142</t>
   </si>
   <si>
     <t xml:space="preserve">6.7508020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52577495574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42191696166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45653581619263</t>
+    <t xml:space="preserve">6.52577447891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42191648483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45653629302979</t>
   </si>
   <si>
     <t xml:space="preserve">6.71618270874023</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">6.75945663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82869577407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82004022598267</t>
+    <t xml:space="preserve">6.82869529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82004070281982</t>
   </si>
   <si>
     <t xml:space="preserve">6.92389917373657</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">7.01044845581055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05372190475464</t>
+    <t xml:space="preserve">7.05372142791748</t>
   </si>
   <si>
     <t xml:space="preserve">6.9931378364563</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">6.97582912445068</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95851850509644</t>
+    <t xml:space="preserve">6.95851898193359</t>
   </si>
   <si>
     <t xml:space="preserve">6.94986343383789</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">7.13161563873291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18354511260986</t>
+    <t xml:space="preserve">7.18354558944702</t>
   </si>
   <si>
     <t xml:space="preserve">7.1575813293457</t>
@@ -3368,16 +3368,16 @@
     <t xml:space="preserve">7.07968711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88927984237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86331462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93255424499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91524410247803</t>
+    <t xml:space="preserve">6.88927936553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86331510543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93255376815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91524457931519</t>
   </si>
   <si>
     <t xml:space="preserve">6.94120931625366</t>
@@ -3389,25 +3389,25 @@
     <t xml:space="preserve">7.17489051818848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27009344100952</t>
+    <t xml:space="preserve">7.27009391784668</t>
   </si>
   <si>
     <t xml:space="preserve">7.20085477828979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22681951522827</t>
+    <t xml:space="preserve">7.22681999206543</t>
   </si>
   <si>
     <t xml:space="preserve">7.16623544692993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14892625808716</t>
+    <t xml:space="preserve">7.14892578125</t>
   </si>
   <si>
     <t xml:space="preserve">7.0883412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14027070999146</t>
+    <t xml:space="preserve">7.14027118682861</t>
   </si>
   <si>
     <t xml:space="preserve">7.26143932342529</t>
@@ -3422,19 +3422,19 @@
     <t xml:space="preserve">7.42588186264038</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44319200515747</t>
+    <t xml:space="preserve">7.44319248199463</t>
   </si>
   <si>
     <t xml:space="preserve">7.48646545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23547458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29605913162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19220113754272</t>
+    <t xml:space="preserve">7.23547410964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29605865478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19220066070557</t>
   </si>
   <si>
     <t xml:space="preserve">7.45184564590454</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">7.52108478546143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84997081756592</t>
+    <t xml:space="preserve">7.84997034072876</t>
   </si>
   <si>
     <t xml:space="preserve">7.72880268096924</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">7.53839540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55570459365845</t>
+    <t xml:space="preserve">7.55570411682129</t>
   </si>
   <si>
     <t xml:space="preserve">7.46050119400024</t>
@@ -3470,28 +3470,28 @@
     <t xml:space="preserve">7.40857267379761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63359832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72014713287354</t>
+    <t xml:space="preserve">7.63359880447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72014760971069</t>
   </si>
   <si>
     <t xml:space="preserve">7.88458967208862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77207708358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65090799331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6682186126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78073120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83266115188599</t>
+    <t xml:space="preserve">7.77207660675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65090847015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66821813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78073072433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83266162872314</t>
   </si>
   <si>
     <t xml:space="preserve">7.82400560379028</t>
@@ -3500,16 +3500,16 @@
     <t xml:space="preserve">7.75476741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70283794403076</t>
+    <t xml:space="preserve">7.7028374671936</t>
   </si>
   <si>
     <t xml:space="preserve">7.69418334960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67687368392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94517469406128</t>
+    <t xml:space="preserve">7.67687320709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94517374038696</t>
   </si>
   <si>
     <t xml:space="preserve">8.01441287994385</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">8.11827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05768871307373</t>
+    <t xml:space="preserve">8.05768775939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.12692737579346</t>
@@ -3548,28 +3548,28 @@
     <t xml:space="preserve">8.18751049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00575733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99710321426392</t>
+    <t xml:space="preserve">8.00575828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99710369110107</t>
   </si>
   <si>
     <t xml:space="preserve">7.87593555450439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30867958068848</t>
+    <t xml:space="preserve">8.30867862701416</t>
   </si>
   <si>
     <t xml:space="preserve">8.24809455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2740592956543</t>
+    <t xml:space="preserve">8.27406024932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.41253757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57698059082031</t>
+    <t xml:space="preserve">8.576979637146</t>
   </si>
   <si>
     <t xml:space="preserve">8.5856351852417</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">8.70680332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87990093231201</t>
+    <t xml:space="preserve">8.87990188598633</t>
   </si>
   <si>
     <t xml:space="preserve">8.834641456604</t>
@@ -69530,7 +69530,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.649375</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>111904</v>
@@ -69551,6 +69551,32 @@
         <v>1396</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6910069444</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>211974</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>13.3000001907349</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>13.3599996566772</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>13.3800001144409</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49119472503662</t>
+    <t xml:space="preserve">4.49119424819946</t>
   </si>
   <si>
     <t xml:space="preserve">CE.MI</t>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">4.5281457901001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46432161331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30644130706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2661304473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31315851211548</t>
+    <t xml:space="preserve">4.46432113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30644083023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26613092422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31315898895264</t>
   </si>
   <si>
     <t xml:space="preserve">4.31987762451172</t>
@@ -65,100 +65,100 @@
     <t xml:space="preserve">4.3669056892395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27284955978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23589849472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05114555358887</t>
+    <t xml:space="preserve">4.27284908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23589897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05114603042603</t>
   </si>
   <si>
     <t xml:space="preserve">4.08473634719849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74210238456726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91677904129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03098964691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1552791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12840509414673</t>
+    <t xml:space="preserve">3.74210262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91677832603455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03099060058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15527868270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12840557098389</t>
   </si>
   <si>
     <t xml:space="preserve">4.01419401168823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12504625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1216869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9470112323761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80256700515747</t>
+    <t xml:space="preserve">4.1250467300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12168741226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94701075553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80256652832031</t>
   </si>
   <si>
     <t xml:space="preserve">3.83615851402283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86975049972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58086228370667</t>
+    <t xml:space="preserve">3.86975026130676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58086276054382</t>
   </si>
   <si>
     <t xml:space="preserve">3.42970061302185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75217962265015</t>
+    <t xml:space="preserve">3.7521800994873</t>
   </si>
   <si>
     <t xml:space="preserve">3.6077356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84959530830383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670084953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96716618537903</t>
+    <t xml:space="preserve">3.84959506988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670156478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96716666221619</t>
   </si>
   <si>
     <t xml:space="preserve">4.06458139419556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8294403553009</t>
+    <t xml:space="preserve">3.82944011688232</t>
   </si>
   <si>
     <t xml:space="preserve">3.77233457565308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9033420085907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87982773780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72866630554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79584932327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88318705558777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95708847045898</t>
+    <t xml:space="preserve">3.90334177017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87982797622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72866582870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79584860801697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88318729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95708799362183</t>
   </si>
   <si>
     <t xml:space="preserve">4.13176488876343</t>
@@ -173,73 +173,73 @@
     <t xml:space="preserve">4.13848257064819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22246265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29972362518311</t>
+    <t xml:space="preserve">4.22246170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29972267150879</t>
   </si>
   <si>
     <t xml:space="preserve">4.35682821273804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25605344772339</t>
+    <t xml:space="preserve">4.25605440139771</t>
   </si>
   <si>
     <t xml:space="preserve">4.27956771850586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14856052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3265962600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26949071884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16535568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09817266464233</t>
+    <t xml:space="preserve">4.14856004714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32659482955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26948976516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16535663604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09817314147949</t>
   </si>
   <si>
     <t xml:space="preserve">4.04778575897217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04106712341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93021488189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91006016731262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8193633556366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75889778137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71186995506287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93357467651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82608127593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08137655258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15863752365112</t>
+    <t xml:space="preserve">4.04106664657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93021535873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91006064414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81936264038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75889730453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71187019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93357372283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8260817527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08137798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15863847732544</t>
   </si>
   <si>
     <t xml:space="preserve">4.17879295349121</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21238374710083</t>
+    <t xml:space="preserve">4.21238470077515</t>
   </si>
   <si>
     <t xml:space="preserve">4.21574354171753</t>
@@ -251,25 +251,25 @@
     <t xml:space="preserve">4.30308198928833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3534688949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1989483833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07465887069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08809566497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06122207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02427101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693351745605</t>
+    <t xml:space="preserve">4.35346841812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19894790649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07465934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08809518814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06122255325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0242714881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693423271179</t>
   </si>
   <si>
     <t xml:space="preserve">4.21648931503296</t>
@@ -287,16 +287,16 @@
     <t xml:space="preserve">4.23369979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23714160919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49185180664062</t>
+    <t xml:space="preserve">4.23714256286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49185276031494</t>
   </si>
   <si>
     <t xml:space="preserve">4.4987359046936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47119951248169</t>
+    <t xml:space="preserve">4.47120046615601</t>
   </si>
   <si>
     <t xml:space="preserve">4.45743179321289</t>
@@ -305,43 +305,43 @@
     <t xml:space="preserve">4.46431589126587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37826538085938</t>
+    <t xml:space="preserve">4.37826490402222</t>
   </si>
   <si>
     <t xml:space="preserve">4.31975078582764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37138080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28188848495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42989587783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34040212631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35072946548462</t>
+    <t xml:space="preserve">4.3713812828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28188753128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42989540100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34040260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35072898864746</t>
   </si>
   <si>
     <t xml:space="preserve">4.25091028213501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03750324249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91703319549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98243093490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8688440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13732242584229</t>
+    <t xml:space="preserve">4.03750371932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91703271865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98243165016174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884427070618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13732290267944</t>
   </si>
   <si>
     <t xml:space="preserve">4.3369607925415</t>
@@ -353,172 +353,172 @@
     <t xml:space="preserve">4.423011302948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52971410751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74148917198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181531906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73116302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84130787849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65199589729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52464127540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42826414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50743055343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65888071060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75525712966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82065629959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78623580932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670680999756</t>
+    <t xml:space="preserve">4.52971458435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74148845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181555747986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73116278648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84130811691284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65199637413025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52464079856873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42826366424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50743103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65887999534607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75525736808777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82065558433533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78623485565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670657157898</t>
   </si>
   <si>
     <t xml:space="preserve">3.9652214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9514524936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04094648361206</t>
+    <t xml:space="preserve">3.95145273208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0409460067749</t>
   </si>
   <si>
     <t xml:space="preserve">4.01341009140015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94456911087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98931527137756</t>
+    <t xml:space="preserve">3.94456887245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98931503295898</t>
   </si>
   <si>
     <t xml:space="preserve">3.95833706855774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7965612411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90326428413391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80000376701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68641638755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70018458366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76558375358582</t>
+    <t xml:space="preserve">3.79656171798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90326404571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80000400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68641662597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70018410682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76558303833008</t>
   </si>
   <si>
     <t xml:space="preserve">3.70362639427185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66576433181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66920590400696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55217742919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48677897453308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4798948764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37319159507751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3718147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5005464553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68985843658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561995506287</t>
+    <t xml:space="preserve">3.66576480865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6692066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55217719078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4867787361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47989463806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37319207191467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37181496620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50054669380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68985891342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561923980713</t>
   </si>
   <si>
     <t xml:space="preserve">3.45235824584961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47645282745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64511227607727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72083687782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7070689201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77935099601746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80688786506653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61413407325745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757612228394</t>
+    <t xml:space="preserve">3.47645258903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64511203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72083735466003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706915855408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77935147285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80688810348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61413359642029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757588386536</t>
   </si>
   <si>
     <t xml:space="preserve">3.57971405982971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56594562530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49366235733032</t>
+    <t xml:space="preserve">3.5659453868866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4936625957489</t>
   </si>
   <si>
     <t xml:space="preserve">3.49022078514099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44891619682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63822770118713</t>
+    <t xml:space="preserve">3.4489164352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63822793960571</t>
   </si>
   <si>
     <t xml:space="preserve">3.49710464477539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38696002960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35804653167725</t>
+    <t xml:space="preserve">3.38695979118347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3580470085144</t>
   </si>
   <si>
     <t xml:space="preserve">3.37456870079041</t>
@@ -527,52 +527,52 @@
     <t xml:space="preserve">3.31123495101929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32638001441956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35529327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4158730506897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51431488990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48333644866943</t>
+    <t xml:space="preserve">3.32638025283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35529351234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41587281227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51431465148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48333668708801</t>
   </si>
   <si>
     <t xml:space="preserve">3.51087307929993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51775693893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47301077842712</t>
+    <t xml:space="preserve">3.51775741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47301030158997</t>
   </si>
   <si>
     <t xml:space="preserve">3.57627153396606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53496670722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64855432510376</t>
+    <t xml:space="preserve">3.53496742248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64855408668518</t>
   </si>
   <si>
     <t xml:space="preserve">3.679532289505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59692358970642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64166975021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63134431838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56250381469727</t>
+    <t xml:space="preserve">3.596923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64167022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63134407997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56250333786011</t>
   </si>
   <si>
     <t xml:space="preserve">3.53152537345886</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">3.45580053329468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41174173355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42964053153992</t>
+    <t xml:space="preserve">3.41174221038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42964100837708</t>
   </si>
   <si>
     <t xml:space="preserve">3.45924282073975</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">3.44203209877014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52808356285095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6347861289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67609047889709</t>
+    <t xml:space="preserve">3.52808284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63478660583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67609095573425</t>
   </si>
   <si>
     <t xml:space="preserve">3.62790203094482</t>
@@ -608,76 +608,76 @@
     <t xml:space="preserve">3.58659744262695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54529285430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55906176567078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56938695907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71739506721497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94112706184387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00996828079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8860547542572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97210454940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83442401885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92735862731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9858729839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0547137260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93080019950867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04438829421997</t>
+    <t xml:space="preserve">3.54529356956482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55906128883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56938743591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71739482879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94112730026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00996780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88605499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97210550308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83442378044128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92735910415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98587322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05471420288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93080115318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04438734054565</t>
   </si>
   <si>
     <t xml:space="preserve">4.06159830093384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91014862060547</t>
+    <t xml:space="preserve">3.91014885902405</t>
   </si>
   <si>
     <t xml:space="preserve">3.89982223510742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05815601348877</t>
+    <t xml:space="preserve">4.05815649032593</t>
   </si>
   <si>
     <t xml:space="preserve">4.07192420959473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07880878448486</t>
+    <t xml:space="preserve">4.07880830764771</t>
   </si>
   <si>
     <t xml:space="preserve">4.03061962127686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19583749771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20960569381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29565668106079</t>
+    <t xml:space="preserve">4.19583702087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20960474014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29565620422363</t>
   </si>
   <si>
     <t xml:space="preserve">4.27844619750977</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">4.1269965171814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13043832778931</t>
+    <t xml:space="preserve">4.13043880462646</t>
   </si>
   <si>
     <t xml:space="preserve">4.20272159576416</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">4.2405834197998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14764928817749</t>
+    <t xml:space="preserve">4.14764881134033</t>
   </si>
   <si>
     <t xml:space="preserve">4.16141700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04783058166504</t>
+    <t xml:space="preserve">4.04783010482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.14076471328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1510910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15453243255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18206882476807</t>
+    <t xml:space="preserve">4.15109205245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15453290939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18206977844238</t>
   </si>
   <si>
     <t xml:space="preserve">4.15797519683838</t>
@@ -737,37 +737,37 @@
     <t xml:space="preserve">4.21304750442505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32319211959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43333768844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44022130966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3851490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47464179992676</t>
+    <t xml:space="preserve">4.32319355010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43333721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44022178649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38514947891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4746413230896</t>
   </si>
   <si>
     <t xml:space="preserve">4.41956949234009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37482357025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41268587112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34384536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30942535400391</t>
+    <t xml:space="preserve">4.37482261657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41268539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34384441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30942487716675</t>
   </si>
   <si>
     <t xml:space="preserve">4.36793851852417</t>
@@ -779,37 +779,37 @@
     <t xml:space="preserve">4.28532981872559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52627182006836</t>
+    <t xml:space="preserve">4.52627229690552</t>
   </si>
   <si>
     <t xml:space="preserve">4.40580177307129</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48840999603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50906181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53659915924072</t>
+    <t xml:space="preserve">4.48841047286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50906229019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53659868240356</t>
   </si>
   <si>
     <t xml:space="preserve">4.54348230361938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44710540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67083740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69899702072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80107259750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71659517288208</t>
+    <t xml:space="preserve">4.44710636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67083787918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69899654388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8010721206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7165961265564</t>
   </si>
   <si>
     <t xml:space="preserve">4.83627080917358</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">4.86090993881226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85034990310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8785080909729</t>
+    <t xml:space="preserve">4.85034942626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87850904464722</t>
   </si>
   <si>
     <t xml:space="preserve">4.78347301483154</t>
@@ -830,31 +830,31 @@
     <t xml:space="preserve">4.72011566162109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68491744995117</t>
+    <t xml:space="preserve">4.68491792678833</t>
   </si>
   <si>
     <t xml:space="preserve">4.73067474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75179386138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81515169143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81163215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92778730392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93834590911865</t>
+    <t xml:space="preserve">4.75179433822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81515121459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81163167953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9277868270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93834638595581</t>
   </si>
   <si>
     <t xml:space="preserve">4.87498903274536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80811214447021</t>
+    <t xml:space="preserve">4.80811166763306</t>
   </si>
   <si>
     <t xml:space="preserve">4.80459260940552</t>
@@ -863,19 +863,19 @@
     <t xml:space="preserve">4.78699254989624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95946502685547</t>
+    <t xml:space="preserve">4.95946550369263</t>
   </si>
   <si>
     <t xml:space="preserve">4.86442947387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89258813858032</t>
+    <t xml:space="preserve">4.89258861541748</t>
   </si>
   <si>
     <t xml:space="preserve">4.89610815048218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91370677947998</t>
+    <t xml:space="preserve">4.91370725631714</t>
   </si>
   <si>
     <t xml:space="preserve">4.97354459762573</t>
@@ -884,73 +884,73 @@
     <t xml:space="preserve">4.97706460952759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94538640975952</t>
+    <t xml:space="preserve">4.94538593292236</t>
   </si>
   <si>
     <t xml:space="preserve">5.1108193397522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25865173339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06154155731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08617973327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10377979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09673976898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0509819984436</t>
+    <t xml:space="preserve">5.2586522102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06154108047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08617925643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10377931594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09673929214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05098104476929</t>
   </si>
   <si>
     <t xml:space="preserve">5.08969926834106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01930284500122</t>
+    <t xml:space="preserve">5.01930332183838</t>
   </si>
   <si>
     <t xml:space="preserve">5.04746198654175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96650457382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91018676757812</t>
+    <t xml:space="preserve">4.96650552749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91018772125244</t>
   </si>
   <si>
     <t xml:space="preserve">5.00874280929565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10025882720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06858015060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13193845748901</t>
+    <t xml:space="preserve">5.10026025772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06858062744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13193798065186</t>
   </si>
   <si>
     <t xml:space="preserve">5.04042196273804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1248984336853</t>
+    <t xml:space="preserve">5.12489795684814</t>
   </si>
   <si>
     <t xml:space="preserve">5.20937442779541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36424732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21289443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03690195083618</t>
+    <t xml:space="preserve">5.36424827575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21289396286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03690242767334</t>
   </si>
   <si>
     <t xml:space="preserve">5.16361665725708</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">5.2727313041687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23049306869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15305757522583</t>
+    <t xml:space="preserve">5.23049354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15305662155151</t>
   </si>
   <si>
     <t xml:space="preserve">5.20233488082886</t>
@@ -971,64 +971,64 @@
     <t xml:space="preserve">5.11433839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1072998046875</t>
+    <t xml:space="preserve">5.10729885101318</t>
   </si>
   <si>
     <t xml:space="preserve">5.00522327423096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9981837272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01226329803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04394197463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06506109237671</t>
+    <t xml:space="preserve">4.99818325042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01226377487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04394245147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06506061553955</t>
   </si>
   <si>
     <t xml:space="preserve">5.15657663345337</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34312868118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30089092254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27977132797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30792951583862</t>
+    <t xml:space="preserve">5.34312915802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30089044570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27977180480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30793046951294</t>
   </si>
   <si>
     <t xml:space="preserve">5.25161266326904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29385137557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29033136367798</t>
+    <t xml:space="preserve">5.29385042190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29033088684082</t>
   </si>
   <si>
     <t xml:space="preserve">5.33608913421631</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34664869308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36776733398438</t>
+    <t xml:space="preserve">5.34664821624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36776828765869</t>
   </si>
   <si>
     <t xml:space="preserve">5.35368871688843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38536691665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3994460105896</t>
+    <t xml:space="preserve">5.38536643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39944696426392</t>
   </si>
   <si>
     <t xml:space="preserve">5.26569175720215</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">5.31145048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32553005218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28329133987427</t>
+    <t xml:space="preserve">5.32552909851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28329181671143</t>
   </si>
   <si>
     <t xml:space="preserve">5.23401355743408</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">5.14249753952026</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16713666915894</t>
+    <t xml:space="preserve">5.16713619232178</t>
   </si>
   <si>
     <t xml:space="preserve">5.31497001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29737091064453</t>
+    <t xml:space="preserve">5.29737043380737</t>
   </si>
   <si>
     <t xml:space="preserve">5.19177532196045</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">5.07210063934326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98410415649414</t>
+    <t xml:space="preserve">4.9841046333313</t>
   </si>
   <si>
     <t xml:space="preserve">4.94186639785767</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">4.86794900894165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92426681518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98058462142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03338241577148</t>
+    <t xml:space="preserve">4.92426776885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9805850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03338193893433</t>
   </si>
   <si>
     <t xml:space="preserve">5.0545015335083</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">5.18473529815674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17417621612549</t>
+    <t xml:space="preserve">5.17417573928833</t>
   </si>
   <si>
     <t xml:space="preserve">5.21993398666382</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">5.28681135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02282285690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00170373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02986145019531</t>
+    <t xml:space="preserve">5.02282333374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0017032623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02986192703247</t>
   </si>
   <si>
     <t xml:space="preserve">5.058021068573</t>
@@ -1124,49 +1124,49 @@
     <t xml:space="preserve">4.92074728012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99114465713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37128734588623</t>
+    <t xml:space="preserve">4.99114418029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37128782272339</t>
   </si>
   <si>
     <t xml:space="preserve">5.47688293457031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48392295837402</t>
+    <t xml:space="preserve">5.48392248153687</t>
   </si>
   <si>
     <t xml:space="preserve">5.44168519973755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43464422225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5261607170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51208162307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4698429107666</t>
+    <t xml:space="preserve">5.43464469909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52616119384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51208114624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46984338760376</t>
   </si>
   <si>
     <t xml:space="preserve">5.40648603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37832689285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18825531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13897800445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32904958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14601755142212</t>
+    <t xml:space="preserve">5.37832736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18825578689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13897752761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3290491104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14601707458496</t>
   </si>
   <si>
     <t xml:space="preserve">5.1952953338623</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">5.24457263946533</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22345399856567</t>
+    <t xml:space="preserve">5.22345447540283</t>
   </si>
   <si>
     <t xml:space="preserve">5.23753309249878</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">5.2189998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14661407470703</t>
+    <t xml:space="preserve">5.14661455154419</t>
   </si>
   <si>
     <t xml:space="preserve">4.98012733459473</t>
@@ -1205,16 +1205,16 @@
     <t xml:space="preserve">4.81364011764526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84259414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85707139968872</t>
+    <t xml:space="preserve">4.84259462356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85707235336304</t>
   </si>
   <si>
     <t xml:space="preserve">4.82087898254395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80640125274658</t>
+    <t xml:space="preserve">4.80640172958374</t>
   </si>
   <si>
     <t xml:space="preserve">4.56029081344604</t>
@@ -1223,25 +1223,25 @@
     <t xml:space="preserve">4.46618938446045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21284008026123</t>
+    <t xml:space="preserve">4.21284055709839</t>
   </si>
   <si>
     <t xml:space="preserve">4.4517126083374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37208795547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52409791946411</t>
+    <t xml:space="preserve">4.37208843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52409839630127</t>
   </si>
   <si>
     <t xml:space="preserve">4.40828132629395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34313440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29246473312378</t>
+    <t xml:space="preserve">4.3431339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29246425628662</t>
   </si>
   <si>
     <t xml:space="preserve">4.3938045501709</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">4.43723583221436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53133678436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61096048355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64715337753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69058513641357</t>
+    <t xml:space="preserve">4.53133726119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61096143722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64715385437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69058465957642</t>
   </si>
   <si>
     <t xml:space="preserve">4.57476806640625</t>
@@ -1271,28 +1271,28 @@
     <t xml:space="preserve">4.58200645446777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48790502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54581356048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58924531936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6037220954895</t>
+    <t xml:space="preserve">4.48790550231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.545814037323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5892448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60372257232666</t>
   </si>
   <si>
     <t xml:space="preserve">4.68334674835205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69782257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62543773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63267612457275</t>
+    <t xml:space="preserve">4.69782304763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62543821334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63267660140991</t>
   </si>
   <si>
     <t xml:space="preserve">4.61819982528687</t>
@@ -1301,85 +1301,85 @@
     <t xml:space="preserve">4.56752967834473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44447374343872</t>
+    <t xml:space="preserve">4.44447422027588</t>
   </si>
   <si>
     <t xml:space="preserve">4.42999696731567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59648323059082</t>
+    <t xml:space="preserve">4.59648370742798</t>
   </si>
   <si>
     <t xml:space="preserve">4.47342777252197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51685953140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50962066650391</t>
+    <t xml:space="preserve">4.51685905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50962114334106</t>
   </si>
   <si>
     <t xml:space="preserve">4.1766471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10426235198975</t>
+    <t xml:space="preserve">4.10426187515259</t>
   </si>
   <si>
     <t xml:space="preserve">4.04635381698608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02463722229004</t>
+    <t xml:space="preserve">4.0246376991272</t>
   </si>
   <si>
     <t xml:space="preserve">4.03187656402588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05359220504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06806945800781</t>
+    <t xml:space="preserve">4.05359172821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0680685043335</t>
   </si>
   <si>
     <t xml:space="preserve">3.97396779060364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00292253494263</t>
+    <t xml:space="preserve">4.00292205810547</t>
   </si>
   <si>
     <t xml:space="preserve">3.85091233253479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8726282119751</t>
+    <t xml:space="preserve">3.87262773513794</t>
   </si>
   <si>
     <t xml:space="preserve">3.93053650856018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92329740524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11150074005127</t>
+    <t xml:space="preserve">3.92329788208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11150026321411</t>
   </si>
   <si>
     <t xml:space="preserve">4.22731733322144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20560169219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22007894515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23455572128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25627136230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27798700332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29970264434814</t>
+    <t xml:space="preserve">4.20560121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22007846832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2345552444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25627183914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27798748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2997031211853</t>
   </si>
   <si>
     <t xml:space="preserve">4.36485004425049</t>
@@ -1388,73 +1388,73 @@
     <t xml:space="preserve">4.35761117935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26351022720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09702348709106</t>
+    <t xml:space="preserve">4.26351070404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09702301025391</t>
   </si>
   <si>
     <t xml:space="preserve">4.06083059310913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12597751617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90882134437561</t>
+    <t xml:space="preserve">4.12597799301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90882110595703</t>
   </si>
   <si>
     <t xml:space="preserve">3.84367370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78576493263245</t>
+    <t xml:space="preserve">3.7857654094696</t>
   </si>
   <si>
     <t xml:space="preserve">3.87986660003662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94501399993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80748105049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.720618724823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68442559242249</t>
+    <t xml:space="preserve">3.94501376152039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80748081207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72061824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68442606925964</t>
   </si>
   <si>
     <t xml:space="preserve">3.5794665813446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45641088485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55051231384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81471967697144</t>
+    <t xml:space="preserve">3.45641112327576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55051255226135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81471943855286</t>
   </si>
   <si>
     <t xml:space="preserve">3.7640495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8291962146759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83643579483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85815119743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74233388900757</t>
+    <t xml:space="preserve">3.82919645309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83643555641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85815095901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74233412742615</t>
   </si>
   <si>
     <t xml:space="preserve">3.75681090354919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70614123344421</t>
+    <t xml:space="preserve">3.70614099502563</t>
   </si>
   <si>
     <t xml:space="preserve">3.67718696594238</t>
@@ -1463,31 +1463,31 @@
     <t xml:space="preserve">3.63375544548035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66994833946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6192786693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64099431037903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77128887176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80024266242981</t>
+    <t xml:space="preserve">3.66994881629944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61927795410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64099454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7712881565094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80024218559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.66270995140076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72785663604736</t>
+    <t xml:space="preserve">3.7278573513031</t>
   </si>
   <si>
     <t xml:space="preserve">3.865389585495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60480141639709</t>
+    <t xml:space="preserve">3.60480117797852</t>
   </si>
   <si>
     <t xml:space="preserve">3.58670496940613</t>
@@ -1496,22 +1496,22 @@
     <t xml:space="preserve">3.57584714889526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54327392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547108650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82195806503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7133800983429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69890213012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69166350364685</t>
+    <t xml:space="preserve">3.54327368736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82195830345154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71337962150574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69890284538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69166374206543</t>
   </si>
   <si>
     <t xml:space="preserve">3.62651705741882</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">3.64823269844055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52517700195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60118174552917</t>
+    <t xml:space="preserve">3.5251772403717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60118222236633</t>
   </si>
   <si>
     <t xml:space="preserve">3.54689335823059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50346159934998</t>
+    <t xml:space="preserve">3.50346183776855</t>
   </si>
   <si>
     <t xml:space="preserve">3.60842084884644</t>
@@ -1538,55 +1538,55 @@
     <t xml:space="preserve">3.79300355911255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88710522651672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5649893283844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59394359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77852654457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58308577537537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53965449333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48174571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49622344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.452791929245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42021822929382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43155574798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43533515930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41265988349915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3332953453064</t>
+    <t xml:space="preserve">3.88710474967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56498980522156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59394407272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7785267829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58308553695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53965425491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48174548149109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49622297286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45279169082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42021799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43155598640442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43533539772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41265940666199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33329558372498</t>
   </si>
   <si>
     <t xml:space="preserve">3.34841251373291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38620471954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37108826637268</t>
+    <t xml:space="preserve">3.38620519638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37108778953552</t>
   </si>
   <si>
     <t xml:space="preserve">3.36352944374084</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">3.32573699951172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29172372817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393152236938</t>
+    <t xml:space="preserve">3.29172420501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393128395081</t>
   </si>
   <si>
     <t xml:space="preserve">3.31439971923828</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">3.276606798172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28038620948792</t>
+    <t xml:space="preserve">3.28038668632507</t>
   </si>
   <si>
     <t xml:space="preserve">3.23503541946411</t>
@@ -1625,31 +1625,31 @@
     <t xml:space="preserve">3.2048008441925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2161386013031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23125624656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21235942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24259352684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18212604522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13677501678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1518919467926</t>
+    <t xml:space="preserve">3.21613907814026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23125600814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21235966682434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24259376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18212556838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13677477836609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15189170837402</t>
   </si>
   <si>
     <t xml:space="preserve">3.18968415260315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20102214813232</t>
+    <t xml:space="preserve">3.20102190971375</t>
   </si>
   <si>
     <t xml:space="preserve">3.25015234947205</t>
@@ -1658,142 +1658,142 @@
     <t xml:space="preserve">3.39376330375671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59784245491028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65831089019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55627083778381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55249166488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56760883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57516765594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60540175437927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53359627723694</t>
+    <t xml:space="preserve">3.59784293174744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65831065177917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55627107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55249190330505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56760859489441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57516741752625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60540151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53359603881836</t>
   </si>
   <si>
     <t xml:space="preserve">3.47690677642822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59028458595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58272576332092</t>
+    <t xml:space="preserve">3.5902841091156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58272552490234</t>
   </si>
   <si>
     <t xml:space="preserve">3.57138800621033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52603721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50336194038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4391143321991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4277765750885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42021870613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40132188796997</t>
+    <t xml:space="preserve">3.5260374546051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50336146354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43911480903625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42777681350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4202184677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40132212638855</t>
   </si>
   <si>
     <t xml:space="preserve">3.36730861663818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40888071060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34085416793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42399764060974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51469922065735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49958229064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54871273040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63941431045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65453171730042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68098616600037</t>
+    <t xml:space="preserve">3.40888047218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34085440635681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42399787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51469945907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49958205223083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54871296882629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6394145488739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65453147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68098568916321</t>
   </si>
   <si>
     <t xml:space="preserve">3.67342758178711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73011660575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78680539131165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285823822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86239004135132</t>
+    <t xml:space="preserve">3.73011636734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78680515289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285752296448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8623902797699</t>
   </si>
   <si>
     <t xml:space="preserve">3.74523329734802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76790881156921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83971500396729</t>
+    <t xml:space="preserve">3.76790928840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83971476554871</t>
   </si>
   <si>
     <t xml:space="preserve">3.83215594291687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77168846130371</t>
+    <t xml:space="preserve">3.77168798446655</t>
   </si>
   <si>
     <t xml:space="preserve">3.73767495155334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69232416152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70366191864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77924633026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68854522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66586923599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69610285758972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66964817047119</t>
+    <t xml:space="preserve">3.69232392311096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70366168022156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77924656867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68854451179504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66586875915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69610261917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66964840888977</t>
   </si>
   <si>
     <t xml:space="preserve">3.73389554023743</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">3.81703925132751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84727358818054</t>
+    <t xml:space="preserve">3.84727311134338</t>
   </si>
   <si>
     <t xml:space="preserve">3.90018248558044</t>
@@ -1811,16 +1811,16 @@
     <t xml:space="preserve">3.98332619667053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96065044403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95309162139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93041610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94553327560425</t>
+    <t xml:space="preserve">3.96065020561218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9530918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93041634559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94553303718567</t>
   </si>
   <si>
     <t xml:space="preserve">3.99088454246521</t>
@@ -1835,22 +1835,22 @@
     <t xml:space="preserve">4.09670352935791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03623533248901</t>
+    <t xml:space="preserve">4.03623628616333</t>
   </si>
   <si>
     <t xml:space="preserve">4.06646966934204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08158683776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1344952583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05135202407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02867698669434</t>
+    <t xml:space="preserve">4.08158731460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13449621200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05135297775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02867746353149</t>
   </si>
   <si>
     <t xml:space="preserve">4.0060019493103</t>
@@ -1859,22 +1859,22 @@
     <t xml:space="preserve">4.04379415512085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11937856674194</t>
+    <t xml:space="preserve">4.1193790435791</t>
   </si>
   <si>
     <t xml:space="preserve">4.01355981826782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96820950508118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93797492980957</t>
+    <t xml:space="preserve">3.96820855140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93797516822815</t>
   </si>
   <si>
     <t xml:space="preserve">3.9757673740387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90774083137512</t>
+    <t xml:space="preserve">3.90774130821228</t>
   </si>
   <si>
     <t xml:space="preserve">3.89262413978577</t>
@@ -1883,64 +1883,64 @@
     <t xml:space="preserve">3.88506579399109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87750720977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85483121871948</t>
+    <t xml:space="preserve">3.87750697135925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85483145713806</t>
   </si>
   <si>
     <t xml:space="preserve">3.80192255973816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5940637588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60162234306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6507523059845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877908706665</t>
+    <t xml:space="preserve">3.59406352043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6016218662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65075206756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877861022949</t>
   </si>
   <si>
     <t xml:space="preserve">3.99844336509705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72255802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63185620307922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46556925773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44667315483093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28416514396667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11031985282898</t>
+    <t xml:space="preserve">3.72255825996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63185596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46556949615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44667291641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28416538238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11032009124756</t>
   </si>
   <si>
     <t xml:space="preserve">3.0649688243866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83821439743042</t>
+    <t xml:space="preserve">2.83821415901184</t>
   </si>
   <si>
     <t xml:space="preserve">2.8344349861145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95915031433105</t>
+    <t xml:space="preserve">2.95915007591248</t>
   </si>
   <si>
     <t xml:space="preserve">2.70971989631653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93269562721252</t>
+    <t xml:space="preserve">2.93269538879395</t>
   </si>
   <si>
     <t xml:space="preserve">3.00450110435486</t>
@@ -1949,10 +1949,10 @@
     <t xml:space="preserve">2.97426724433899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94403338432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91001963615417</t>
+    <t xml:space="preserve">2.94403314590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91001987457275</t>
   </si>
   <si>
     <t xml:space="preserve">2.96292948722839</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">2.85333132743835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89490294456482</t>
+    <t xml:space="preserve">2.89490270614624</t>
   </si>
   <si>
     <t xml:space="preserve">2.88734436035156</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">2.92135787010193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85711026191711</t>
+    <t xml:space="preserve">2.85711050033569</t>
   </si>
   <si>
     <t xml:space="preserve">2.90246152877808</t>
@@ -1979,43 +1979,43 @@
     <t xml:space="preserve">2.82687664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89112377166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9969425201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95159125328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97804665565491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99316334724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05363154411316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03473496437073</t>
+    <t xml:space="preserve">2.8911235332489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99694275856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9515917301178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97804641723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99316358566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05363130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03473520278931</t>
   </si>
   <si>
     <t xml:space="preserve">3.02717661857605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12165784835815</t>
+    <t xml:space="preserve">3.12165808677673</t>
   </si>
   <si>
     <t xml:space="preserve">3.06119012832642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09898209571838</t>
+    <t xml:space="preserve">3.09898233413696</t>
   </si>
   <si>
     <t xml:space="preserve">3.16700863838196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14433312416077</t>
+    <t xml:space="preserve">3.14433336257935</t>
   </si>
   <si>
     <t xml:space="preserve">3.19346332550049</t>
@@ -2024,22 +2024,22 @@
     <t xml:space="preserve">3.21991848945618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26904821395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32195782661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15944981575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07252788543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06874799728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10654091835022</t>
+    <t xml:space="preserve">3.26904845237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3219575881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1594500541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07252764701843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06874823570251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1065411567688</t>
   </si>
   <si>
     <t xml:space="preserve">3.16322922706604</t>
@@ -2048,46 +2048,46 @@
     <t xml:space="preserve">3.27282762527466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28794431686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40510129928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51091980934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48824453353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45801067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29550361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34463334083557</t>
+    <t xml:space="preserve">3.28794479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40510153770447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51092004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48824429512024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45801043510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29550337791443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34463357925415</t>
   </si>
   <si>
     <t xml:space="preserve">3.29928231239319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30684065818787</t>
+    <t xml:space="preserve">3.30684113502502</t>
   </si>
   <si>
     <t xml:space="preserve">3.30306172370911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26149010658264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37864685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37486720085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26526927947998</t>
+    <t xml:space="preserve">3.26148962974548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37864661216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3748676776886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2652690410614</t>
   </si>
   <si>
     <t xml:space="preserve">3.39754271507263</t>
@@ -2096,46 +2096,46 @@
     <t xml:space="preserve">3.48068594932556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38998413085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31817817687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25771045684814</t>
+    <t xml:space="preserve">3.38998460769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31817865371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25771069526672</t>
   </si>
   <si>
     <t xml:space="preserve">3.22747659683228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18590521812439</t>
+    <t xml:space="preserve">3.18590474128723</t>
   </si>
   <si>
     <t xml:space="preserve">3.24637293815613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17456698417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14055418968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17834663391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09142422676086</t>
+    <t xml:space="preserve">3.17456674575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14055442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17834615707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09142398834229</t>
   </si>
   <si>
     <t xml:space="preserve">3.08008575439453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0460729598999</t>
+    <t xml:space="preserve">3.04607319831848</t>
   </si>
   <si>
     <t xml:space="preserve">3.01583886146545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9402539730072</t>
+    <t xml:space="preserve">2.94025373458862</t>
   </si>
   <si>
     <t xml:space="preserve">2.95537090301514</t>
@@ -2144,19 +2144,19 @@
     <t xml:space="preserve">2.92513704299927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8835654258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80042147636414</t>
+    <t xml:space="preserve">2.88356518745422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80042171478271</t>
   </si>
   <si>
     <t xml:space="preserve">2.7890841960907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77018761634827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75129151344299</t>
+    <t xml:space="preserve">2.77018785476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75129175186157</t>
   </si>
   <si>
     <t xml:space="preserve">2.71727848052979</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">2.67948603630066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55477070808411</t>
+    <t xml:space="preserve">2.55477094650269</t>
   </si>
   <si>
     <t xml:space="preserve">2.44895172119141</t>
@@ -2177,37 +2177,37 @@
     <t xml:space="preserve">2.55099153518677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61523914337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69838237762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98938393592834</t>
+    <t xml:space="preserve">2.615238904953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69838213920593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98938417434692</t>
   </si>
   <si>
     <t xml:space="preserve">3.53737497329712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62807679176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63563513755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57894706726074</t>
+    <t xml:space="preserve">3.62807703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63563537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57894659042358</t>
   </si>
   <si>
     <t xml:space="preserve">3.56382989883423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50714111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48446559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52225780487061</t>
+    <t xml:space="preserve">3.50714039802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4844651222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52225804328918</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643881797791</t>
@@ -2216,94 +2216,94 @@
     <t xml:space="preserve">3.12543702125549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80948066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76035094261169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6431941986084</t>
+    <t xml:space="preserve">3.80948090553284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76035070419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64319396018982</t>
   </si>
   <si>
     <t xml:space="preserve">3.68476533889771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74901294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79436373710632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7565712928772</t>
+    <t xml:space="preserve">3.74901247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7943639755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75657105445862</t>
   </si>
   <si>
     <t xml:space="preserve">3.77546739578247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76412987709045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15717077255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11182069778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17228841781616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31345558166504</t>
+    <t xml:space="preserve">3.76412963867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15717172622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11182022094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17228889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31345653533936</t>
   </si>
   <si>
     <t xml:space="preserve">4.22718667984009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12523221969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07817602157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08601903915405</t>
+    <t xml:space="preserve">4.1252326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07817649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08601951599121</t>
   </si>
   <si>
     <t xml:space="preserve">4.09386157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20365858078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26640033721924</t>
+    <t xml:space="preserve">4.20365905761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26639986038208</t>
   </si>
   <si>
     <t xml:space="preserve">4.27424240112305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25855779647827</t>
+    <t xml:space="preserve">4.25855731964111</t>
   </si>
   <si>
     <t xml:space="preserve">4.36835479736328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32914113998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34482622146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35266971588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30561304092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28992748260498</t>
+    <t xml:space="preserve">4.32914161682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34482669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35266923904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30561351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28992795944214</t>
   </si>
   <si>
     <t xml:space="preserve">4.28208541870117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19581651687622</t>
+    <t xml:space="preserve">4.19581604003906</t>
   </si>
   <si>
     <t xml:space="preserve">4.03896331787109</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">4.03112077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05464839935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93700885772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92132329940796</t>
+    <t xml:space="preserve">4.05464887619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93700861930847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92132353782654</t>
   </si>
   <si>
     <t xml:space="preserve">4.01543521881104</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">4.24287176132202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.211501121521</t>
+    <t xml:space="preserve">4.21150159835815</t>
   </si>
   <si>
     <t xml:space="preserve">4.39188241958618</t>
@@ -2360,13 +2360,13 @@
     <t xml:space="preserve">4.43109560012817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42325305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38403987884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39972543716431</t>
+    <t xml:space="preserve">4.42325258255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38404035568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39972496032715</t>
   </si>
   <si>
     <t xml:space="preserve">4.33698415756226</t>
@@ -2375,22 +2375,22 @@
     <t xml:space="preserve">4.36051177978516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46246671676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44678068161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4389386177063</t>
+    <t xml:space="preserve">4.46246576309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44678115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43893766403198</t>
   </si>
   <si>
     <t xml:space="preserve">4.47815179824829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48599433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50167989730835</t>
+    <t xml:space="preserve">4.4859938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50167942047119</t>
   </si>
   <si>
     <t xml:space="preserve">4.56442070007324</t>
@@ -2399,28 +2399,28 @@
     <t xml:space="preserve">4.60363388061523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62716197967529</t>
+    <t xml:space="preserve">4.62716150283813</t>
   </si>
   <si>
     <t xml:space="preserve">4.63500452041626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49383640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59579133987427</t>
+    <t xml:space="preserve">4.49383687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59579181671143</t>
   </si>
   <si>
     <t xml:space="preserve">4.66637516021729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68205976486206</t>
+    <t xml:space="preserve">4.68206024169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.72911643981934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64284706115723</t>
+    <t xml:space="preserve">4.64284753799438</t>
   </si>
   <si>
     <t xml:space="preserve">4.74480152130127</t>
@@ -2429,37 +2429,37 @@
     <t xml:space="preserve">4.86244106292725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90949726104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05850791931152</t>
+    <t xml:space="preserve">4.90949678421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05850744247437</t>
   </si>
   <si>
     <t xml:space="preserve">5.03497982025146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99576663970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95655345916748</t>
+    <t xml:space="preserve">4.99576616287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95655250549316</t>
   </si>
   <si>
     <t xml:space="preserve">4.9487099647522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97223806381226</t>
+    <t xml:space="preserve">4.97223854064941</t>
   </si>
   <si>
     <t xml:space="preserve">4.87028408050537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98008060455322</t>
+    <t xml:space="preserve">4.98008108139038</t>
   </si>
   <si>
     <t xml:space="preserve">5.0741925239563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05066442489624</t>
+    <t xml:space="preserve">5.0506649017334</t>
   </si>
   <si>
     <t xml:space="preserve">5.02713680267334</t>
@@ -2468,46 +2468,46 @@
     <t xml:space="preserve">5.08987760543823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19183254241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18399000167847</t>
+    <t xml:space="preserve">5.19183206558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18398952484131</t>
   </si>
   <si>
     <t xml:space="preserve">5.16830444335938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10556364059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14477682113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23888778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21536016464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19967555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25457334518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30162954330444</t>
+    <t xml:space="preserve">5.10556316375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14477634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23888826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21536064147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1996750831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25457382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3016300201416</t>
   </si>
   <si>
     <t xml:space="preserve">5.01929426193237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93302488327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7996997833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7604866027832</t>
+    <t xml:space="preserve">4.93302440643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79970026016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76048707962036</t>
   </si>
   <si>
     <t xml:space="preserve">4.76832962036133</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">4.68990325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69774580001831</t>
+    <t xml:space="preserve">4.69774532318115</t>
   </si>
   <si>
     <t xml:space="preserve">4.6114764213562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53305006027222</t>
+    <t xml:space="preserve">4.53305053710938</t>
   </si>
   <si>
     <t xml:space="preserve">4.50952196121216</t>
@@ -2546,64 +2546,64 @@
     <t xml:space="preserve">4.54089260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51736450195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58010578155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82322835922241</t>
+    <t xml:space="preserve">4.51736497879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58010625839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82322788238525</t>
   </si>
   <si>
     <t xml:space="preserve">4.87812662124634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88596868515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7840142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70558881759644</t>
+    <t xml:space="preserve">4.8859691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78401470184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558834075928</t>
   </si>
   <si>
     <t xml:space="preserve">4.65853261947632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77617263793945</t>
+    <t xml:space="preserve">4.77617216110229</t>
   </si>
   <si>
     <t xml:space="preserve">4.85459899902344</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94086837768555</t>
+    <t xml:space="preserve">4.94086790084839</t>
   </si>
   <si>
     <t xml:space="preserve">5.52122354507446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6623911857605</t>
+    <t xml:space="preserve">5.66239070892334</t>
   </si>
   <si>
     <t xml:space="preserve">5.73297500610352</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89767074584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6859188079834</t>
+    <t xml:space="preserve">5.89767026901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68591976165771</t>
   </si>
   <si>
     <t xml:space="preserve">5.70160484313965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59965038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53690958023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906656265259</t>
+    <t xml:space="preserve">5.59964990615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53690910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906608581543</t>
   </si>
   <si>
     <t xml:space="preserve">5.17614698410034</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">4.71343088150024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41541004180908</t>
+    <t xml:space="preserve">4.41541051864624</t>
   </si>
   <si>
     <t xml:space="preserve">4.89381170272827</t>
@@ -2624,70 +2624,70 @@
     <t xml:space="preserve">4.81538534164429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92518281936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.846755027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72127389907837</t>
+    <t xml:space="preserve">4.9251823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84675598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72127294540405</t>
   </si>
   <si>
     <t xml:space="preserve">4.5879487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61931943893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70558834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77163171768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73861026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69733333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63954448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7963981628418</t>
+    <t xml:space="preserve">4.61931896209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558786392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77163219451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.738609790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69733285903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63954496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79639768600464</t>
   </si>
   <si>
     <t xml:space="preserve">4.98627281188965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95325136184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312505722046</t>
+    <t xml:space="preserve">4.95325040817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312601089478</t>
   </si>
   <si>
     <t xml:space="preserve">5.07708263397217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11835908889771</t>
+    <t xml:space="preserve">5.11835956573486</t>
   </si>
   <si>
     <t xml:space="preserve">4.97801733016968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06057119369507</t>
+    <t xml:space="preserve">5.06057167053223</t>
   </si>
   <si>
     <t xml:space="preserve">4.9037184715271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96976184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87069702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82942008972168</t>
+    <t xml:space="preserve">4.96976137161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87069654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82941961288452</t>
   </si>
   <si>
     <t xml:space="preserve">4.62303400039673</t>
@@ -2699,28 +2699,31 @@
     <t xml:space="preserve">4.50745820999146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56524658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58175754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64779996871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61477899551392</t>
+    <t xml:space="preserve">4.56524610519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48269128799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58175706863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64780044555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54873609542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61477947235107</t>
   </si>
   <si>
     <t xml:space="preserve">4.57350158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51571321487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3340950012207</t>
+    <t xml:space="preserve">4.51571416854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33409452438354</t>
   </si>
   <si>
     <t xml:space="preserve">4.30932807922363</t>
@@ -2735,34 +2738,34 @@
     <t xml:space="preserve">4.26805114746094</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4661808013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42490386962891</t>
+    <t xml:space="preserve">4.46618127822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42490434646606</t>
   </si>
   <si>
     <t xml:space="preserve">4.3753719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27630662918091</t>
+    <t xml:space="preserve">4.27630615234375</t>
   </si>
   <si>
     <t xml:space="preserve">4.44967031478882</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34235000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41664886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55699062347412</t>
+    <t xml:space="preserve">4.34235048294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41664838790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55699110031128</t>
   </si>
   <si>
     <t xml:space="preserve">4.67256689071655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65605592727661</t>
+    <t xml:space="preserve">4.65605545043945</t>
   </si>
   <si>
     <t xml:space="preserve">4.71384382247925</t>
@@ -2771,28 +2774,25 @@
     <t xml:space="preserve">4.76337623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85418558120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8624415397644</t>
+    <t xml:space="preserve">4.85418605804443</t>
   </si>
   <si>
     <t xml:space="preserve">4.72209930419922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75512075424194</t>
+    <t xml:space="preserve">4.7551212310791</t>
   </si>
   <si>
     <t xml:space="preserve">4.77988719940186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73035430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82116413116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9284839630127</t>
+    <t xml:space="preserve">4.73035526275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82116460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92848491668701</t>
   </si>
   <si>
     <t xml:space="preserve">4.92022943496704</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">4.66431140899658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81290864944458</t>
+    <t xml:space="preserve">4.81290912628174</t>
   </si>
   <si>
     <t xml:space="preserve">4.88720750808716</t>
@@ -2834,13 +2834,13 @@
     <t xml:space="preserve">5.16789197921753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23393487930298</t>
+    <t xml:space="preserve">5.23393535614014</t>
   </si>
   <si>
     <t xml:space="preserve">5.19265794754028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22567939758301</t>
+    <t xml:space="preserve">5.22567987442017</t>
   </si>
   <si>
     <t xml:space="preserve">5.26695680618286</t>
@@ -2849,19 +2849,19 @@
     <t xml:space="preserve">5.27521181106567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29172325134277</t>
+    <t xml:space="preserve">5.29172277450562</t>
   </si>
   <si>
     <t xml:space="preserve">5.30823373794556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36602258682251</t>
+    <t xml:space="preserve">5.36602163314819</t>
   </si>
   <si>
     <t xml:space="preserve">5.43206548690796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47334289550781</t>
+    <t xml:space="preserve">5.47334241867065</t>
   </si>
   <si>
     <t xml:space="preserve">5.55589628219604</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">5.41555452346802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48985290527344</t>
+    <t xml:space="preserve">5.48985385894775</t>
   </si>
   <si>
     <t xml:space="preserve">5.46508693695068</t>
@@ -2888,19 +2888,19 @@
     <t xml:space="preserve">5.52287483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51461887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58891820907593</t>
+    <t xml:space="preserve">5.51461935043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58891868591309</t>
   </si>
   <si>
     <t xml:space="preserve">5.45683145523071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54764080047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6879825592041</t>
+    <t xml:space="preserve">5.54764127731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68798303604126</t>
   </si>
   <si>
     <t xml:space="preserve">5.63019561767578</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">5.65496110916138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77879238128662</t>
+    <t xml:space="preserve">5.77879285812378</t>
   </si>
   <si>
     <t xml:space="preserve">5.82007026672363</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">5.8118143081665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90262365341187</t>
+    <t xml:space="preserve">5.90262460708618</t>
   </si>
   <si>
     <t xml:space="preserve">5.80355930328369</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">6.52178049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57956790924072</t>
+    <t xml:space="preserve">6.57956838607788</t>
   </si>
   <si>
     <t xml:space="preserve">6.58782386779785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51352500915527</t>
+    <t xml:space="preserve">6.51352453231812</t>
   </si>
   <si>
     <t xml:space="preserve">6.56305742263794</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">6.72816514968872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6703782081604</t>
+    <t xml:space="preserve">6.67037773132324</t>
   </si>
   <si>
     <t xml:space="preserve">6.63735628128052</t>
@@ -2999,19 +2999,19 @@
     <t xml:space="preserve">6.79420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73642158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68688917160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53829145431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62084531784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64561223983765</t>
+    <t xml:space="preserve">6.73642110824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68688869476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53829097747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62084579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64561176300049</t>
   </si>
   <si>
     <t xml:space="preserve">6.71991062164307</t>
@@ -3020,31 +3020,31 @@
     <t xml:space="preserve">6.74467658996582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75293302536011</t>
+    <t xml:space="preserve">6.75293254852295</t>
   </si>
   <si>
     <t xml:space="preserve">6.78595399856567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96866750717163</t>
+    <t xml:space="preserve">5.96866703033447</t>
   </si>
   <si>
     <t xml:space="preserve">6.05122137069702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64670658111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85309171676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67972803115845</t>
+    <t xml:space="preserve">5.64670610427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8530912399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67972755432129</t>
   </si>
   <si>
     <t xml:space="preserve">5.39904356002808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38253259658813</t>
+    <t xml:space="preserve">5.38253211975098</t>
   </si>
   <si>
     <t xml:space="preserve">5.66321706771851</t>
@@ -3062,40 +3062,40 @@
     <t xml:space="preserve">5.88611316680908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79530334472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87785768508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97692251205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91087961196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91913461685181</t>
+    <t xml:space="preserve">5.79530382156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87785816192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9769229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91087913513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91913509368896</t>
   </si>
   <si>
     <t xml:space="preserve">5.63845062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78704881668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94390058517456</t>
+    <t xml:space="preserve">5.78704833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94390106201172</t>
   </si>
   <si>
     <t xml:space="preserve">5.96041202545166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8696026802063</t>
+    <t xml:space="preserve">5.86960220336914</t>
   </si>
   <si>
     <t xml:space="preserve">5.98917293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97186279296875</t>
+    <t xml:space="preserve">5.97186326980591</t>
   </si>
   <si>
     <t xml:space="preserve">5.98051786422729</t>
@@ -3128,19 +3128,19 @@
     <t xml:space="preserve">5.76414585113525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71221733093262</t>
+    <t xml:space="preserve">5.71221685409546</t>
   </si>
   <si>
     <t xml:space="preserve">5.82472991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80742073059082</t>
+    <t xml:space="preserve">5.80742025375366</t>
   </si>
   <si>
     <t xml:space="preserve">5.86800479888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88531398773193</t>
+    <t xml:space="preserve">5.88531446456909</t>
   </si>
   <si>
     <t xml:space="preserve">5.87665939331055</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">5.92858839035034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96320772171021</t>
+    <t xml:space="preserve">5.96320819854736</t>
   </si>
   <si>
     <t xml:space="preserve">5.94589853286743</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">5.91993379592896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15361547470093</t>
+    <t xml:space="preserve">6.15361499786377</t>
   </si>
   <si>
     <t xml:space="preserve">6.22285461425781</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">6.28343868255615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25747394561768</t>
+    <t xml:space="preserve">6.25747346878052</t>
   </si>
   <si>
     <t xml:space="preserve">6.24881887435913</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">6.24016380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23150873184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26612854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46519041061401</t>
+    <t xml:space="preserve">6.2315092086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26612901687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46519088745117</t>
   </si>
   <si>
     <t xml:space="preserve">6.54308462142944</t>
@@ -3194,43 +3194,43 @@
     <t xml:space="preserve">6.58635902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56904935836792</t>
+    <t xml:space="preserve">6.56904983520508</t>
   </si>
   <si>
     <t xml:space="preserve">6.6382884979248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56039476394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57770395278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62097883224487</t>
+    <t xml:space="preserve">6.56039381027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57770442962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62097835540771</t>
   </si>
   <si>
     <t xml:space="preserve">6.65559816360474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69021797180176</t>
+    <t xml:space="preserve">6.6902174949646</t>
   </si>
   <si>
     <t xml:space="preserve">6.73349189758301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64694309234619</t>
+    <t xml:space="preserve">6.64694261550903</t>
   </si>
   <si>
     <t xml:space="preserve">6.50846529006958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66425275802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11034107208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30940294265747</t>
+    <t xml:space="preserve">6.66425228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11034059524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30940341949463</t>
   </si>
   <si>
     <t xml:space="preserve">6.37864208221436</t>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">6.49981021881104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55174016952515</t>
+    <t xml:space="preserve">6.55173969268799</t>
   </si>
   <si>
     <t xml:space="preserve">6.5950140953064</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">6.62963342666626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74214649200439</t>
+    <t xml:space="preserve">6.74214696884155</t>
   </si>
   <si>
     <t xml:space="preserve">6.87196969985962</t>
@@ -3287,19 +3287,19 @@
     <t xml:space="preserve">6.77676630020142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7508020401001</t>
+    <t xml:space="preserve">6.75080156326294</t>
   </si>
   <si>
     <t xml:space="preserve">6.52577495574951</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42191696166992</t>
+    <t xml:space="preserve">6.42191648483276</t>
   </si>
   <si>
     <t xml:space="preserve">6.45653581619263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71618223190308</t>
+    <t xml:space="preserve">6.71618270874023</t>
   </si>
   <si>
     <t xml:space="preserve">6.72483682632446</t>
@@ -3308,10 +3308,10 @@
     <t xml:space="preserve">6.75945663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82869577407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82004117965698</t>
+    <t xml:space="preserve">6.82869529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82004070281982</t>
   </si>
   <si>
     <t xml:space="preserve">6.92389917373657</t>
@@ -3320,10 +3320,10 @@
     <t xml:space="preserve">7.01044797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05372190475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99313831329346</t>
+    <t xml:space="preserve">7.05372142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9931378364563</t>
   </si>
   <si>
     <t xml:space="preserve">7.001793384552</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">6.97582864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95851898193359</t>
+    <t xml:space="preserve">6.95851850509644</t>
   </si>
   <si>
     <t xml:space="preserve">6.94986343383789</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">6.88927984237671</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86331510543823</t>
+    <t xml:space="preserve">6.86331462860107</t>
   </si>
   <si>
     <t xml:space="preserve">6.93255424499512</t>
@@ -3383,28 +3383,28 @@
     <t xml:space="preserve">6.91524410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9412088394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96717405319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17489051818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27009344100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20085477828979</t>
+    <t xml:space="preserve">6.94120931625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96717357635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17489004135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27009391784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20085430145264</t>
   </si>
   <si>
     <t xml:space="preserve">7.22681999206543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16623592376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14892578125</t>
+    <t xml:space="preserve">7.16623544692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14892625808716</t>
   </si>
   <si>
     <t xml:space="preserve">7.08834171295166</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">7.26143932342529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31336832046509</t>
+    <t xml:space="preserve">7.31336784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.33933258056641</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">7.42588138580322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44319152832031</t>
+    <t xml:space="preserve">7.44319200515747</t>
   </si>
   <si>
     <t xml:space="preserve">7.48646545410156</t>
@@ -3434,19 +3434,19 @@
     <t xml:space="preserve">7.23547458648682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29605913162231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19220066070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45184659957886</t>
+    <t xml:space="preserve">7.29605865478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19220113754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4518461227417</t>
   </si>
   <si>
     <t xml:space="preserve">7.38260746002197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35664224624634</t>
+    <t xml:space="preserve">7.3566427230835</t>
   </si>
   <si>
     <t xml:space="preserve">7.52108478546143</t>
@@ -3455,28 +3455,28 @@
     <t xml:space="preserve">7.84997081756592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7288031578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7634220123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53839540481567</t>
+    <t xml:space="preserve">7.72880268096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76342248916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53839588165283</t>
   </si>
   <si>
     <t xml:space="preserve">7.55570507049561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4605016708374</t>
+    <t xml:space="preserve">7.46050119400024</t>
   </si>
   <si>
     <t xml:space="preserve">7.40857219696045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63359880447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72014808654785</t>
+    <t xml:space="preserve">7.63359785079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72014713287354</t>
   </si>
   <si>
     <t xml:space="preserve">7.88458967208862</t>
@@ -3485,64 +3485,64 @@
     <t xml:space="preserve">7.77207612991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65090847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66821765899658</t>
+    <t xml:space="preserve">7.65090894699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6682186126709</t>
   </si>
   <si>
     <t xml:space="preserve">7.78073120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83266162872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8240065574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75476694107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7028374671936</t>
+    <t xml:space="preserve">7.83266115188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82400560379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75476741790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70283794403076</t>
   </si>
   <si>
     <t xml:space="preserve">7.69418334960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67687368392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94517421722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01441383361816</t>
+    <t xml:space="preserve">7.67687273025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94517469406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01441287994385</t>
   </si>
   <si>
     <t xml:space="preserve">8.11827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05768775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12692737579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06634140014648</t>
+    <t xml:space="preserve">8.05768871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12692642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0663423538208</t>
   </si>
   <si>
     <t xml:space="preserve">8.02306842803955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10961723327637</t>
+    <t xml:space="preserve">8.10961627960205</t>
   </si>
   <si>
     <t xml:space="preserve">8.17885589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17020130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20481967926025</t>
+    <t xml:space="preserve">8.17020034790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20482063293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.07499694824219</t>
@@ -3554,25 +3554,25 @@
     <t xml:space="preserve">8.00575828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99710369110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87593555450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30867862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24809551239014</t>
+    <t xml:space="preserve">7.99710321426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87593650817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30867958068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24809455871582</t>
   </si>
   <si>
     <t xml:space="preserve">8.27406024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41253757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.576979637146</t>
+    <t xml:space="preserve">8.41253662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57698059082031</t>
   </si>
   <si>
     <t xml:space="preserve">8.58563423156738</t>
@@ -3581,19 +3581,19 @@
     <t xml:space="preserve">8.65487384796143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54236125946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62025451660156</t>
+    <t xml:space="preserve">8.54236030578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62025356292725</t>
   </si>
   <si>
     <t xml:space="preserve">8.81066226959229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82797145843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7068042755127</t>
+    <t xml:space="preserve">8.82797050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70680332183838</t>
   </si>
   <si>
     <t xml:space="preserve">8.87990093231201</t>
@@ -47474,7 +47474,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1648" t="s">
-        <v>840</v>
+        <v>899</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47500,7 +47500,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1649" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47526,7 +47526,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47552,7 +47552,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1651" t="s">
-        <v>840</v>
+        <v>899</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47578,7 +47578,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1652" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47604,7 +47604,7 @@
         <v>5.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47630,7 +47630,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1654" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47656,7 +47656,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1655" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47682,7 +47682,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1656" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47708,7 +47708,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1657" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47760,7 +47760,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1659" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47786,7 +47786,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1660" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47812,7 +47812,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1661" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47838,7 +47838,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1662" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47864,7 +47864,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1663" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47890,7 +47890,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1664" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47942,7 +47942,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1666" t="s">
-        <v>840</v>
+        <v>899</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48020,7 +48020,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1669" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48046,7 +48046,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1670" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48072,7 +48072,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1671" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48124,7 +48124,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1673" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48150,7 +48150,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1674" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48228,7 +48228,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1677" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48254,7 +48254,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1678" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48332,7 +48332,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48358,7 +48358,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1682" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48410,7 +48410,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1684" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48436,7 +48436,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G1685" t="s">
-        <v>920</v>
+        <v>804</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48514,7 +48514,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48670,7 +48670,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48722,7 +48722,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -48774,7 +48774,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1698" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48800,7 +48800,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48852,7 +48852,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -49320,7 +49320,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1719" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49398,7 +49398,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1722" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49424,7 +49424,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1723" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49502,7 +49502,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1726" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49580,7 +49580,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1729" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -69582,7 +69582,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6912268518</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>111511</v>
@@ -69603,6 +69603,32 @@
         <v>1412</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6909953704</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>201436</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>13.7399997711182</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>13.460000038147</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>13.7200002670288</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">CE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52814483642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46432065963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30644035339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2661304473877</t>
+    <t xml:space="preserve">4.52814531326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46432209014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30644130706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26613092422485</t>
   </si>
   <si>
     <t xml:space="preserve">4.31315946578979</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">4.31987714767456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36690521240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27284955978394</t>
+    <t xml:space="preserve">4.3669056892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27284908294678</t>
   </si>
   <si>
     <t xml:space="preserve">4.23589849472046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05114555358887</t>
+    <t xml:space="preserve">4.05114459991455</t>
   </si>
   <si>
     <t xml:space="preserve">4.08473634719849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74210262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91677808761597</t>
+    <t xml:space="preserve">3.74210238456726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91677904129028</t>
   </si>
   <si>
     <t xml:space="preserve">4.03099012374878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15527868270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12840557098389</t>
+    <t xml:space="preserve">4.1552791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12840509414673</t>
   </si>
   <si>
     <t xml:space="preserve">4.01419401168823</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">4.12504625320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12168741226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94701051712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80256700515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83615946769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86975026130676</t>
+    <t xml:space="preserve">4.1216869354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94701027870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80256676673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83615875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86975002288818</t>
   </si>
   <si>
     <t xml:space="preserve">3.5808629989624</t>
@@ -122,58 +122,58 @@
     <t xml:space="preserve">3.75217962265015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60773611068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84959483146667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96716618537903</t>
+    <t xml:space="preserve">3.6077356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84959530830383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9067018032074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96716570854187</t>
   </si>
   <si>
     <t xml:space="preserve">4.06458139419556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82944011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77233409881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90334177017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87982821464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72866559028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79584884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88318800926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95708870887756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13176441192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19558906555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18551158905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13848352432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22246217727661</t>
+    <t xml:space="preserve">3.8294403553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77233457565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90334153175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87982773780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72866582870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79584908485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88318657875061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95708847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13176488876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19558954238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18551111221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13848304748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22246170043945</t>
   </si>
   <si>
     <t xml:space="preserve">4.29972267150879</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">4.35682821273804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25605344772339</t>
+    <t xml:space="preserve">4.25605297088623</t>
   </si>
   <si>
     <t xml:space="preserve">4.27956771850586</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">4.14856052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3265962600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26949024200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16535663604736</t>
+    <t xml:space="preserve">4.32659578323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26948976516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16535520553589</t>
   </si>
   <si>
     <t xml:space="preserve">4.09817361831665</t>
@@ -206,25 +206,25 @@
     <t xml:space="preserve">4.04778575897217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04106760025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93021535873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91006112098694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81936240196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75889801979065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71187019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93357467651367</t>
+    <t xml:space="preserve">4.04106712341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93021512031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91006064414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81936311721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75889849662781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71186947822571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93357419967651</t>
   </si>
   <si>
     <t xml:space="preserve">3.82608103752136</t>
@@ -233,22 +233,22 @@
     <t xml:space="preserve">4.0813775062561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15863847732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17879247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21238470077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21574306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28292751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30308198928833</t>
+    <t xml:space="preserve">4.15863800048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17879295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21238374710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21574449539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2829270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30308246612549</t>
   </si>
   <si>
     <t xml:space="preserve">4.35346937179565</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">4.19894790649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07465934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08809566497803</t>
+    <t xml:space="preserve">4.07465839385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08809614181519</t>
   </si>
   <si>
     <t xml:space="preserve">4.06122255325317</t>
@@ -269,19 +269,19 @@
     <t xml:space="preserve">4.0242714881897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93693399429321</t>
+    <t xml:space="preserve">3.93693351745605</t>
   </si>
   <si>
     <t xml:space="preserve">4.21648979187012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14420652389526</t>
+    <t xml:space="preserve">4.14420747756958</t>
   </si>
   <si>
     <t xml:space="preserve">4.19927978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25435161590576</t>
+    <t xml:space="preserve">4.25435209274292</t>
   </si>
   <si>
     <t xml:space="preserve">4.23369979858398</t>
@@ -290,40 +290,40 @@
     <t xml:space="preserve">4.23714208602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49185228347778</t>
+    <t xml:space="preserve">4.49185180664062</t>
   </si>
   <si>
     <t xml:space="preserve">4.4987359046936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47120046615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45743179321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46431589126587</t>
+    <t xml:space="preserve">4.47119951248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45743227005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46431541442871</t>
   </si>
   <si>
     <t xml:space="preserve">4.37826538085938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31975030899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37138080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28188753128052</t>
+    <t xml:space="preserve">4.31975126266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3713812828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28188800811768</t>
   </si>
   <si>
     <t xml:space="preserve">4.42989587783813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34040260314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35072946548462</t>
+    <t xml:space="preserve">4.34040212631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3507285118103</t>
   </si>
   <si>
     <t xml:space="preserve">4.25090980529785</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">3.91703319549561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98243069648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884355545044</t>
+    <t xml:space="preserve">3.98243141174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884450912476</t>
   </si>
   <si>
     <t xml:space="preserve">4.13732290267944</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">4.33696126937866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38170671463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.423011302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52971458435059</t>
+    <t xml:space="preserve">4.38170719146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42301177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52971506118774</t>
   </si>
   <si>
     <t xml:space="preserve">3.74148893356323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75181531906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73116326332092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84130811691284</t>
+    <t xml:space="preserve">3.75181555747986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7311635017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84130764007568</t>
   </si>
   <si>
     <t xml:space="preserve">3.65199589729309</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">3.42826437950134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50743079185486</t>
+    <t xml:space="preserve">3.50743103027344</t>
   </si>
   <si>
     <t xml:space="preserve">3.65888023376465</t>
@@ -386,79 +386,79 @@
     <t xml:space="preserve">3.75525736808777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82065606117249</t>
+    <t xml:space="preserve">3.82065629959106</t>
   </si>
   <si>
     <t xml:space="preserve">3.78623557090759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90670657157898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96522188186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9514524936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0409460067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01340913772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94456839561462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98931479454041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.958336353302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79656267166138</t>
+    <t xml:space="preserve">3.90670680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9652214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95145297050476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04094648361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01340961456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9445686340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98931550979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9583375453949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79656147956848</t>
   </si>
   <si>
     <t xml:space="preserve">3.90326523780823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80000400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68641686439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70018482208252</t>
+    <t xml:space="preserve">3.80000376701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68641638755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70018529891968</t>
   </si>
   <si>
     <t xml:space="preserve">3.76558327674866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70362663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66576409339905</t>
+    <t xml:space="preserve">3.70362687110901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66576457023621</t>
   </si>
   <si>
     <t xml:space="preserve">3.6692066192627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55217742919922</t>
+    <t xml:space="preserve">3.5521776676178</t>
   </si>
   <si>
     <t xml:space="preserve">3.4867787361145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47989439964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37319207191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3718147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50054717063904</t>
+    <t xml:space="preserve">3.47989463806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37319183349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37181448936462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50054669380188</t>
   </si>
   <si>
     <t xml:space="preserve">3.68985819816589</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">3.45235824584961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47645282745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64511251449585</t>
+    <t xml:space="preserve">3.47645258903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64511275291443</t>
   </si>
   <si>
     <t xml:space="preserve">3.72083687782288</t>
@@ -485,91 +485,91 @@
     <t xml:space="preserve">3.77935099601746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80688762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61413335800171</t>
+    <t xml:space="preserve">3.80688810348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61413359642029</t>
   </si>
   <si>
     <t xml:space="preserve">3.61757612228394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57971405982971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5659453868866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49366235733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49022102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44891667366028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63822770118713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49710488319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38696002960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35804653167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37456822395325</t>
+    <t xml:space="preserve">3.57971358299255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56594562530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4936625957489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49022150039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4489164352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63822793960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49710464477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38695955276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35804629325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37456846237183</t>
   </si>
   <si>
     <t xml:space="preserve">3.31123518943787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32638001441956</t>
+    <t xml:space="preserve">3.32638025283813</t>
   </si>
   <si>
     <t xml:space="preserve">3.3552930355072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41587281227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51431512832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48333621025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51087260246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51775693893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47301077842712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57627177238464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53496742248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64855480194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67953276634216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59692430496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64167022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63134384155273</t>
+    <t xml:space="preserve">3.41587233543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51431488990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48333668708801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51087284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51775741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4730110168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57627153396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53496789932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64855456352234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.679532289505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59692335128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64166975021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63134431838989</t>
   </si>
   <si>
     <t xml:space="preserve">3.56250309944153</t>
@@ -578,22 +578,22 @@
     <t xml:space="preserve">3.53152513504028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45580053329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41174244880676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42964100837708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45924234390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4420325756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52808356285095</t>
+    <t xml:space="preserve">3.4558002948761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41174268722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42964124679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45924210548401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44203186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52808332443237</t>
   </si>
   <si>
     <t xml:space="preserve">3.6347861289978</t>
@@ -602,49 +602,49 @@
     <t xml:space="preserve">3.67609047889709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62790179252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58659744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54529333114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55906176567078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56938719749451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71739435195923</t>
+    <t xml:space="preserve">3.6279022693634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58659768104553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54529356956482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55906105041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56938695907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71739482879639</t>
   </si>
   <si>
     <t xml:space="preserve">3.94112706184387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00996732711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88605499267578</t>
+    <t xml:space="preserve">4.00996780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8860547542572</t>
   </si>
   <si>
     <t xml:space="preserve">3.97210550308228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83442401885986</t>
+    <t xml:space="preserve">3.83442378044128</t>
   </si>
   <si>
     <t xml:space="preserve">3.92735862731934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9858729839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05471467971802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93080139160156</t>
+    <t xml:space="preserve">3.98587393760681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05471324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93080067634583</t>
   </si>
   <si>
     <t xml:space="preserve">4.04438781738281</t>
@@ -653,58 +653,58 @@
     <t xml:space="preserve">4.06159830093384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91014838218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89982295036316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05815649032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07192420959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07880830764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03061962127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19583702087402</t>
+    <t xml:space="preserve">3.91014862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89982271194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05815553665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07192373275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07880878448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03062009811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19583749771118</t>
   </si>
   <si>
     <t xml:space="preserve">4.20960569381714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29565572738647</t>
+    <t xml:space="preserve">4.29565620422363</t>
   </si>
   <si>
     <t xml:space="preserve">4.27844619750977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24746799468994</t>
+    <t xml:space="preserve">4.24746704101562</t>
   </si>
   <si>
     <t xml:space="preserve">4.30254030227661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1269965171814</t>
+    <t xml:space="preserve">4.12699604034424</t>
   </si>
   <si>
     <t xml:space="preserve">4.13043832778931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20272159576416</t>
+    <t xml:space="preserve">4.202721118927</t>
   </si>
   <si>
     <t xml:space="preserve">4.10634469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12011289596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17862749099731</t>
+    <t xml:space="preserve">4.12011241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17862701416016</t>
   </si>
   <si>
     <t xml:space="preserve">4.2405834197998</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">4.14764881134033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16141653060913</t>
+    <t xml:space="preserve">4.16141748428345</t>
   </si>
   <si>
     <t xml:space="preserve">4.04783010482788</t>
@@ -722,37 +722,37 @@
     <t xml:space="preserve">4.14076471328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1510910987854</t>
+    <t xml:space="preserve">4.15109157562256</t>
   </si>
   <si>
     <t xml:space="preserve">4.15453290939331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18206977844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15797472000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21304750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32319259643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43333768844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44022178649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38514947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47464179992676</t>
+    <t xml:space="preserve">4.18206882476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15797519683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21304702758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32319211959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449718475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43333721160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44022226333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38514995574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47464227676392</t>
   </si>
   <si>
     <t xml:space="preserve">4.41956949234009</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">4.37482309341431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41268491744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34384489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30942440032959</t>
+    <t xml:space="preserve">4.41268539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34384441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30942487716675</t>
   </si>
   <si>
     <t xml:space="preserve">4.36793851852417</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">4.28532981872559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52627229690552</t>
+    <t xml:space="preserve">4.52627182006836</t>
   </si>
   <si>
     <t xml:space="preserve">4.40580129623413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48840951919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50906276702881</t>
+    <t xml:space="preserve">4.48840999603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50906181335449</t>
   </si>
   <si>
     <t xml:space="preserve">4.53659868240356</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">4.447105884552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67083740234375</t>
+    <t xml:space="preserve">4.67083787918091</t>
   </si>
   <si>
     <t xml:space="preserve">4.69899654388428</t>
@@ -809,28 +809,28 @@
     <t xml:space="preserve">4.8010721206665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7165961265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83627128601074</t>
+    <t xml:space="preserve">4.71659564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83627033233643</t>
   </si>
   <si>
     <t xml:space="preserve">4.86090993881226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85035037994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87850904464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7834734916687</t>
+    <t xml:space="preserve">4.85034990310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87850856781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78347253799438</t>
   </si>
   <si>
     <t xml:space="preserve">4.72011566162109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68491697311401</t>
+    <t xml:space="preserve">4.68491744995117</t>
   </si>
   <si>
     <t xml:space="preserve">4.7306752204895</t>
@@ -839,28 +839,28 @@
     <t xml:space="preserve">4.75179481506348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81515169143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81163167953491</t>
+    <t xml:space="preserve">4.81515121459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81163263320923</t>
   </si>
   <si>
     <t xml:space="preserve">4.9277868270874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93834686279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87498998641968</t>
+    <t xml:space="preserve">4.93834638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87498903274536</t>
   </si>
   <si>
     <t xml:space="preserve">4.80811166763306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8045916557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7869930267334</t>
+    <t xml:space="preserve">4.80459213256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78699350357056</t>
   </si>
   <si>
     <t xml:space="preserve">4.95946502685547</t>
@@ -881,22 +881,22 @@
     <t xml:space="preserve">4.97354459762573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97706460952759</t>
+    <t xml:space="preserve">4.97706508636475</t>
   </si>
   <si>
     <t xml:space="preserve">4.94538593292236</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11081886291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2586522102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06154108047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08617973327637</t>
+    <t xml:space="preserve">5.1108193397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25865268707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06154155731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08617925643921</t>
   </si>
   <si>
     <t xml:space="preserve">5.10377931594849</t>
@@ -905,22 +905,22 @@
     <t xml:space="preserve">5.09673976898193</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0509819984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08969974517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01930284500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04746198654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96650552749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91018724441528</t>
+    <t xml:space="preserve">5.05098104476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08970022201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01930379867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04746150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96650457382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91018772125244</t>
   </si>
   <si>
     <t xml:space="preserve">5.00874328613281</t>
@@ -929,61 +929,61 @@
     <t xml:space="preserve">5.10025930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06858062744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1319375038147</t>
+    <t xml:space="preserve">5.06858015060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13193845748901</t>
   </si>
   <si>
     <t xml:space="preserve">5.04042148590088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12489795684814</t>
+    <t xml:space="preserve">5.1248984336853</t>
   </si>
   <si>
     <t xml:space="preserve">5.20937442779541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36424732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21289443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03690195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16361618041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27273178100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23049402236938</t>
+    <t xml:space="preserve">5.36424827575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21289491653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03690242767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16361665725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2727313041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23049306869507</t>
   </si>
   <si>
     <t xml:space="preserve">5.15305709838867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20233535766602</t>
+    <t xml:space="preserve">5.20233488082886</t>
   </si>
   <si>
     <t xml:space="preserve">5.11433839797974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10729885101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00522375106812</t>
+    <t xml:space="preserve">5.10729932785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00522327423096</t>
   </si>
   <si>
     <t xml:space="preserve">4.9981837272644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01226282119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04394197463989</t>
+    <t xml:space="preserve">5.01226329803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04394149780273</t>
   </si>
   <si>
     <t xml:space="preserve">5.06506109237671</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">5.15657663345337</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3431282043457</t>
+    <t xml:space="preserve">5.34312868118286</t>
   </si>
   <si>
     <t xml:space="preserve">5.30089092254639</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">5.27977180480957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30793046951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25161266326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29385137557983</t>
+    <t xml:space="preserve">5.30792999267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25161218643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29385089874268</t>
   </si>
   <si>
     <t xml:space="preserve">5.29033088684082</t>
@@ -1016,28 +1016,28 @@
     <t xml:space="preserve">5.33608865737915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34664821624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36776733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35368871688843</t>
+    <t xml:space="preserve">5.34664869308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36776781082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35368824005127</t>
   </si>
   <si>
     <t xml:space="preserve">5.38536691665649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3994460105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26569271087646</t>
+    <t xml:space="preserve">5.39944648742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26569223403931</t>
   </si>
   <si>
     <t xml:space="preserve">5.31145048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32553005218506</t>
+    <t xml:space="preserve">5.3255295753479</t>
   </si>
   <si>
     <t xml:space="preserve">5.28329181671143</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">5.23401355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2164134979248</t>
+    <t xml:space="preserve">5.21641397476196</t>
   </si>
   <si>
     <t xml:space="preserve">5.14249753952026</t>
@@ -1058,67 +1058,67 @@
     <t xml:space="preserve">5.31497001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29737091064453</t>
+    <t xml:space="preserve">5.29737043380737</t>
   </si>
   <si>
     <t xml:space="preserve">5.19177484512329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35720825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07210063934326</t>
+    <t xml:space="preserve">5.35720872879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07210111618042</t>
   </si>
   <si>
     <t xml:space="preserve">4.98410415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94186544418335</t>
+    <t xml:space="preserve">4.94186687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.86794948577881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92426729202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98058414459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03338193893433</t>
+    <t xml:space="preserve">4.92426633834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98058462142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03338241577148</t>
   </si>
   <si>
     <t xml:space="preserve">5.0545015335083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18473482131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17417669296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21993350982666</t>
+    <t xml:space="preserve">5.18473529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17417573928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21993398666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.17769622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22697448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28681182861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02282333374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00170373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02986288070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05802202224731</t>
+    <t xml:space="preserve">5.22697401046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28681135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02282238006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0017032623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02986192703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.058021068573</t>
   </si>
   <si>
     <t xml:space="preserve">4.92074680328369</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">4.99114418029785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37128782272339</t>
+    <t xml:space="preserve">5.37128686904907</t>
   </si>
   <si>
     <t xml:space="preserve">5.47688293457031</t>
@@ -1136,16 +1136,16 @@
     <t xml:space="preserve">5.48392248153687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44168519973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43464422225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5261607170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51208114624023</t>
+    <t xml:space="preserve">5.44168472290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43464517593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52616119384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51208162307739</t>
   </si>
   <si>
     <t xml:space="preserve">5.46984338760376</t>
@@ -1157,19 +1157,19 @@
     <t xml:space="preserve">5.37832736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18825578689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13897800445557</t>
+    <t xml:space="preserve">5.18825531005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13897848129272</t>
   </si>
   <si>
     <t xml:space="preserve">5.32904958724976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14601755142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1952953338623</t>
+    <t xml:space="preserve">5.14601707458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19529485702515</t>
   </si>
   <si>
     <t xml:space="preserve">5.24457263946533</t>
@@ -1178,25 +1178,25 @@
     <t xml:space="preserve">5.22345399856567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23753356933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16009712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11785793304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97002506256104</t>
+    <t xml:space="preserve">5.23753309249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16009664535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11785888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97002458572388</t>
   </si>
   <si>
     <t xml:space="preserve">5.21899938583374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14661455154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98012685775757</t>
+    <t xml:space="preserve">5.14661407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98012733459473</t>
   </si>
   <si>
     <t xml:space="preserve">4.94393396377563</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">4.81364059448242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84259510040283</t>
+    <t xml:space="preserve">4.84259414672852</t>
   </si>
   <si>
     <t xml:space="preserve">4.85707187652588</t>
@@ -1220,25 +1220,25 @@
     <t xml:space="preserve">4.56029081344604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46618986129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21284103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4517126083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37208843231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52409839630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4082818031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3431339263916</t>
+    <t xml:space="preserve">4.46618938446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21284008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45171213150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37208795547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52409791946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40828132629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34313440322876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29246425628662</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">4.45895099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4372353553772</t>
+    <t xml:space="preserve">4.43723583221436</t>
   </si>
   <si>
     <t xml:space="preserve">4.53133678436279</t>
@@ -1259,52 +1259,52 @@
     <t xml:space="preserve">4.61096096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64715337753296</t>
+    <t xml:space="preserve">4.64715385437012</t>
   </si>
   <si>
     <t xml:space="preserve">4.69058513641357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57476854324341</t>
+    <t xml:space="preserve">4.57476806640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.58200645446777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48790502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54581356048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58924531936646</t>
+    <t xml:space="preserve">4.48790597915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.545814037323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58924579620361</t>
   </si>
   <si>
     <t xml:space="preserve">4.6037220954895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68334674835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6978235244751</t>
+    <t xml:space="preserve">4.68334627151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69782257080078</t>
   </si>
   <si>
     <t xml:space="preserve">4.62543773651123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63267707824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61819982528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56752920150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44447422027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42999649047852</t>
+    <t xml:space="preserve">4.63267612457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61819934844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56752967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44447374343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42999744415283</t>
   </si>
   <si>
     <t xml:space="preserve">4.59648370742798</t>
@@ -1313,40 +1313,40 @@
     <t xml:space="preserve">4.47342824935913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51685905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50962114334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17664766311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10426235198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04635381698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02463817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03187704086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05359172821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0680685043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97396731376648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00292205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85091209411621</t>
+    <t xml:space="preserve">4.51686000823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50962066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1766471862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10426187515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04635334014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02463722229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03187656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05359220504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06806898117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97396779060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00292253494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85091233253479</t>
   </si>
   <si>
     <t xml:space="preserve">3.87262773513794</t>
@@ -1355,16 +1355,16 @@
     <t xml:space="preserve">3.93053603172302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92329812049866</t>
+    <t xml:space="preserve">3.92329788208008</t>
   </si>
   <si>
     <t xml:space="preserve">4.11149978637695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22731733322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20560169219971</t>
+    <t xml:space="preserve">4.22731781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20560121536255</t>
   </si>
   <si>
     <t xml:space="preserve">4.22007894515991</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">4.23455572128296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25627183914185</t>
+    <t xml:space="preserve">4.25627136230469</t>
   </si>
   <si>
     <t xml:space="preserve">4.27798700332642</t>
@@ -1385,70 +1385,70 @@
     <t xml:space="preserve">4.36485004425049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35761117935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26351022720337</t>
+    <t xml:space="preserve">4.35761070251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26350975036621</t>
   </si>
   <si>
     <t xml:space="preserve">4.09702348709106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06083059310913</t>
+    <t xml:space="preserve">4.06083106994629</t>
   </si>
   <si>
     <t xml:space="preserve">4.12597751617432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90882062911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84367418289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78576493263245</t>
+    <t xml:space="preserve">3.90882086753845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84367394447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78576564788818</t>
   </si>
   <si>
     <t xml:space="preserve">3.87986660003662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94501376152039</t>
+    <t xml:space="preserve">3.94501352310181</t>
   </si>
   <si>
     <t xml:space="preserve">3.80748105049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72061848640442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68442583084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57946634292603</t>
+    <t xml:space="preserve">3.720618724823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68442535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5794665813446</t>
   </si>
   <si>
     <t xml:space="preserve">3.45641088485718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55051231384277</t>
+    <t xml:space="preserve">3.55051207542419</t>
   </si>
   <si>
     <t xml:space="preserve">3.81471967697144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76405000686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82919692993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83643579483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85815095901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74233436584473</t>
+    <t xml:space="preserve">3.7640495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82919645309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83643507957458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85815119743347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74233412742615</t>
   </si>
   <si>
     <t xml:space="preserve">3.75681138038635</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">3.70614123344421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67718696594238</t>
+    <t xml:space="preserve">3.6771867275238</t>
   </si>
   <si>
     <t xml:space="preserve">3.63375568389893</t>
@@ -1466,31 +1466,31 @@
     <t xml:space="preserve">3.66994857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6192786693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64099454879761</t>
+    <t xml:space="preserve">3.61927795410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64099502563477</t>
   </si>
   <si>
     <t xml:space="preserve">3.77128791809082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80024194717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6627094745636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72785711288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86538934707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60480165481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58670496940613</t>
+    <t xml:space="preserve">3.80024266242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66270995140076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72785687446594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86538910865784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60480117797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58670520782471</t>
   </si>
   <si>
     <t xml:space="preserve">3.57584714889526</t>
@@ -1499,10 +1499,10 @@
     <t xml:space="preserve">3.54327368736267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65547156333923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82195854187012</t>
+    <t xml:space="preserve">3.65547132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82195806503296</t>
   </si>
   <si>
     <t xml:space="preserve">3.71337962150574</t>
@@ -1511,76 +1511,76 @@
     <t xml:space="preserve">3.69890260696411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69166374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62651753425598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64823293685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5251772403717</t>
+    <t xml:space="preserve">3.69166421890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6265172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64823269844055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52517700195312</t>
   </si>
   <si>
     <t xml:space="preserve">3.60118222236633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54689335823059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50346159934998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60842108726501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79300355911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88710498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5649893283844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59394383430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7785267829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58308553695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53965425491333</t>
+    <t xml:space="preserve">3.54689311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5034613609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60842061042786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79300427436829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88710522651672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56498956680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59394431114197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77852630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58308577537537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53965449333191</t>
   </si>
   <si>
     <t xml:space="preserve">3.48174595832825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49622273445129</t>
+    <t xml:space="preserve">3.49622297286987</t>
   </si>
   <si>
     <t xml:space="preserve">3.452791929245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4202184677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43155598640442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43533539772034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41265964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33329558372498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841251373291</t>
+    <t xml:space="preserve">3.42021822929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43155574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43533515930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41265988349915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33329510688782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841275215149</t>
   </si>
   <si>
     <t xml:space="preserve">3.38620495796204</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">3.3824257850647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31062006950378</t>
+    <t xml:space="preserve">3.31062030792236</t>
   </si>
   <si>
     <t xml:space="preserve">3.32573699951172</t>
@@ -1607,106 +1607,106 @@
     <t xml:space="preserve">3.25393128395081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3143994808197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33707523345947</t>
+    <t xml:space="preserve">3.31439971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33707475662231</t>
   </si>
   <si>
     <t xml:space="preserve">3.27660703659058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28038644790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23503565788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20480132102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21613883972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23125576972961</t>
+    <t xml:space="preserve">3.28038620948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23503541946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20480108261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21613907814026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23125600814819</t>
   </si>
   <si>
     <t xml:space="preserve">3.21235966682434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24259376525879</t>
+    <t xml:space="preserve">3.24259352684021</t>
   </si>
   <si>
     <t xml:space="preserve">3.18212580680847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13677501678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15189218521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18968415260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20102214813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25015211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39376354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59784317016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65831089019775</t>
+    <t xml:space="preserve">3.13677477836609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15189146995544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18968439102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20102190971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25015234947205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39376330375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59784293174744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6583104133606</t>
   </si>
   <si>
     <t xml:space="preserve">3.55627083778381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5524914264679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56760859489441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57516717910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60540127754211</t>
+    <t xml:space="preserve">3.55249166488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56760883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57516741752625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60540151596069</t>
   </si>
   <si>
     <t xml:space="preserve">3.53359580039978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47690725326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59028434753418</t>
+    <t xml:space="preserve">3.47690677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5902841091156</t>
   </si>
   <si>
     <t xml:space="preserve">3.58272552490234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57138800621033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52603721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50336194038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43911457061768</t>
+    <t xml:space="preserve">3.57138824462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52603697776794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50336170196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43911504745483</t>
   </si>
   <si>
     <t xml:space="preserve">3.42777681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40132212638855</t>
+    <t xml:space="preserve">3.40132188796997</t>
   </si>
   <si>
     <t xml:space="preserve">3.36730885505676</t>
@@ -1715,25 +1715,25 @@
     <t xml:space="preserve">3.40888071060181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34085416793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4239981174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51469969749451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49958205223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54871249198914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63941431045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65453195571899</t>
+    <t xml:space="preserve">3.34085392951965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42399740219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51469945907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49958229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54871273040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6394145488739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65453171730042</t>
   </si>
   <si>
     <t xml:space="preserve">3.68098592758179</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">3.67342782020569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73011660575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78680515289307</t>
+    <t xml:space="preserve">3.73011636734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78680539131165</t>
   </si>
   <si>
     <t xml:space="preserve">3.92285823822021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86238956451416</t>
+    <t xml:space="preserve">3.86239004135132</t>
   </si>
   <si>
     <t xml:space="preserve">3.7452335357666</t>
@@ -1760,46 +1760,46 @@
     <t xml:space="preserve">3.76790904998779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83971452713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83215570449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168822288513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73767495155334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69232392311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70366239547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77924704551697</t>
+    <t xml:space="preserve">3.83971428871155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83215618133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73767518997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69232439994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70366191864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77924609184265</t>
   </si>
   <si>
     <t xml:space="preserve">3.68854451179504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66586947441101</t>
+    <t xml:space="preserve">3.66586923599243</t>
   </si>
   <si>
     <t xml:space="preserve">3.69610333442688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66964864730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73389601707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81703972816467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84727358818054</t>
+    <t xml:space="preserve">3.66964888572693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73389577865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81703925132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8472728729248</t>
   </si>
   <si>
     <t xml:space="preserve">3.90018248558044</t>
@@ -1808,22 +1808,22 @@
     <t xml:space="preserve">3.98332619667053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96065068244934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95309233665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93041634559631</t>
+    <t xml:space="preserve">3.96065044403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95309209823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93041658401489</t>
   </si>
   <si>
     <t xml:space="preserve">3.94553327560425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99088501930237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91529941558838</t>
+    <t xml:space="preserve">3.99088454246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9152991771698</t>
   </si>
   <si>
     <t xml:space="preserve">4.02111864089966</t>
@@ -1832,19 +1832,19 @@
     <t xml:space="preserve">4.09670352935791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03623580932617</t>
+    <t xml:space="preserve">4.03623533248901</t>
   </si>
   <si>
     <t xml:space="preserve">4.06646966934204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0815863609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13449573516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05135202407837</t>
+    <t xml:space="preserve">4.08158683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1344952583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05135250091553</t>
   </si>
   <si>
     <t xml:space="preserve">4.02867698669434</t>
@@ -1856,94 +1856,94 @@
     <t xml:space="preserve">4.04379367828369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1193790435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01355981826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96820831298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93797516822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97576761245728</t>
+    <t xml:space="preserve">4.11937856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96820902824402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93797492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97576785087585</t>
   </si>
   <si>
     <t xml:space="preserve">3.90774083137512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89262437820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88506555557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87750744819641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85483193397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.801922082901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5940637588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60162210464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65075182914734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877861022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99844312667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72255802154541</t>
+    <t xml:space="preserve">3.89262461662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88506627082825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87750720977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85483169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80192303657532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59406352043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6016218662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65075206756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877837181091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99844288825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72255825996399</t>
   </si>
   <si>
     <t xml:space="preserve">3.63185572624207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46556949615479</t>
+    <t xml:space="preserve">3.46556901931763</t>
   </si>
   <si>
     <t xml:space="preserve">3.44667315483093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28416538238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11032009124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0649688243866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83821415901184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8344349861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95915007591248</t>
+    <t xml:space="preserve">3.28416514396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11031985282898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06496906280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83821439743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83443522453308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95915031433105</t>
   </si>
   <si>
     <t xml:space="preserve">2.70971989631653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93269562721252</t>
+    <t xml:space="preserve">2.93269538879395</t>
   </si>
   <si>
     <t xml:space="preserve">3.00450110435486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97426724433899</t>
+    <t xml:space="preserve">2.97426700592041</t>
   </si>
   <si>
     <t xml:space="preserve">2.94403314590454</t>
@@ -1952,10 +1952,10 @@
     <t xml:space="preserve">2.91001963615417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96292924880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85333132743835</t>
+    <t xml:space="preserve">2.96292972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85333108901978</t>
   </si>
   <si>
     <t xml:space="preserve">2.89490294456482</t>
@@ -1964,25 +1964,25 @@
     <t xml:space="preserve">2.88734436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92135787010193</t>
+    <t xml:space="preserve">2.92135810852051</t>
   </si>
   <si>
     <t xml:space="preserve">2.85711050033569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90246152877808</t>
+    <t xml:space="preserve">2.9024612903595</t>
   </si>
   <si>
     <t xml:space="preserve">2.82687664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8911235332489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9969425201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9515917301178</t>
+    <t xml:space="preserve">2.89112377166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99694228172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95159149169922</t>
   </si>
   <si>
     <t xml:space="preserve">2.97804641723633</t>
@@ -1991,22 +1991,22 @@
     <t xml:space="preserve">2.99316334724426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.053631067276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03473472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02717685699463</t>
+    <t xml:space="preserve">3.05363154411316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03473496437073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02717661857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.12165784835815</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06119012832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09898233413696</t>
+    <t xml:space="preserve">3.06118988990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09898257255554</t>
   </si>
   <si>
     <t xml:space="preserve">3.16700887680054</t>
@@ -2015,19 +2015,19 @@
     <t xml:space="preserve">3.14433312416077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19346380233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21991848945618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26904797554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3219575881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15944981575012</t>
+    <t xml:space="preserve">3.19346332550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2199182510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26904821395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32195782661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15945029258728</t>
   </si>
   <si>
     <t xml:space="preserve">3.07252764701843</t>
@@ -2036,19 +2036,19 @@
     <t xml:space="preserve">3.06874823570251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10654067993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1632297039032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27282738685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28794479370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40510129928589</t>
+    <t xml:space="preserve">3.10654091835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16322946548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27282762527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28794455528259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40510153770447</t>
   </si>
   <si>
     <t xml:space="preserve">3.51092004776001</t>
@@ -2057,31 +2057,31 @@
     <t xml:space="preserve">3.4882447719574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45801043510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29550337791443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34463357925415</t>
+    <t xml:space="preserve">3.45801067352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29550290107727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34463334083557</t>
   </si>
   <si>
     <t xml:space="preserve">3.29928231239319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30684065818787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30306172370911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26149010658264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37864637374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37486743927002</t>
+    <t xml:space="preserve">3.30684113502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30306124687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26148986816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37864661216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37486720085144</t>
   </si>
   <si>
     <t xml:space="preserve">3.26526927947998</t>
@@ -2090,82 +2090,82 @@
     <t xml:space="preserve">3.39754295349121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48068642616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38998436927795</t>
+    <t xml:space="preserve">3.48068618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38998413085938</t>
   </si>
   <si>
     <t xml:space="preserve">3.31817841529846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25771069526672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2274763584137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18590474128723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24637317657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17456698417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14055442810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17834615707397</t>
+    <t xml:space="preserve">3.2577109336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22747659683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18590497970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24637293815613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17456722259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14055418968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17834639549255</t>
   </si>
   <si>
     <t xml:space="preserve">3.09142398834229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08008599281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04607319831848</t>
+    <t xml:space="preserve">3.08008575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0460729598999</t>
   </si>
   <si>
     <t xml:space="preserve">3.01583886146545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94025373458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95537090301514</t>
+    <t xml:space="preserve">2.9402539730072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95537066459656</t>
   </si>
   <si>
     <t xml:space="preserve">2.92513680458069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8835654258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80042147636414</t>
+    <t xml:space="preserve">2.88356518745422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80042171478271</t>
   </si>
   <si>
     <t xml:space="preserve">2.7890841960907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77018785476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75129175186157</t>
+    <t xml:space="preserve">2.77018761634827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75129151344299</t>
   </si>
   <si>
     <t xml:space="preserve">2.71727848052979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7210578918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67948627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55477118492126</t>
+    <t xml:space="preserve">2.72105741500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67948603630066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55477070808411</t>
   </si>
   <si>
     <t xml:space="preserve">2.44895195960999</t>
@@ -2174,82 +2174,82 @@
     <t xml:space="preserve">2.55099153518677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61523866653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69838213920593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9893844127655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53737449645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62807703018188</t>
+    <t xml:space="preserve">2.615238904953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69838237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98938393592834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5373752117157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62807679176331</t>
   </si>
   <si>
     <t xml:space="preserve">3.63563537597656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57894659042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56383037567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50714087486267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48446536064148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52225780487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41643857955933</t>
+    <t xml:space="preserve">3.57894682884216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56382989883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50714111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48446559906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52225756645203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41643881797791</t>
   </si>
   <si>
     <t xml:space="preserve">3.12543702125549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80948114395142</t>
+    <t xml:space="preserve">3.80948042869568</t>
   </si>
   <si>
     <t xml:space="preserve">3.76035070419312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64319372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68476533889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74901270866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79436349868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75657105445862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77546715736389</t>
+    <t xml:space="preserve">3.64319396018982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68476557731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74901223182678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7943639755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7565712928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77546739578247</t>
   </si>
   <si>
     <t xml:space="preserve">3.76412963867188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15717077255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11182022094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17228889465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31345558166504</t>
+    <t xml:space="preserve">4.15717172622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11182069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17228841781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31345653533936</t>
   </si>
   <si>
     <t xml:space="preserve">4.22718667984009</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">4.07817649841309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08601951599121</t>
+    <t xml:space="preserve">4.08601903915405</t>
   </si>
   <si>
     <t xml:space="preserve">4.09386157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20365858078003</t>
+    <t xml:space="preserve">4.20365905761719</t>
   </si>
   <si>
     <t xml:space="preserve">4.26640033721924</t>
@@ -2285,16 +2285,16 @@
     <t xml:space="preserve">4.32914113998413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34482622146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35266971588135</t>
+    <t xml:space="preserve">4.34482669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35266923904419</t>
   </si>
   <si>
     <t xml:space="preserve">4.30561351776123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28992795944214</t>
+    <t xml:space="preserve">4.28992748260498</t>
   </si>
   <si>
     <t xml:space="preserve">4.28208541870117</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">4.03896379470825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02327871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99974966049194</t>
+    <t xml:space="preserve">4.02327823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9997501373291</t>
   </si>
   <si>
     <t xml:space="preserve">4.00759267807007</t>
@@ -2318,28 +2318,28 @@
     <t xml:space="preserve">3.96053695678711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03112030029297</t>
+    <t xml:space="preserve">4.03112125396729</t>
   </si>
   <si>
     <t xml:space="preserve">4.05464839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93700933456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92132329940796</t>
+    <t xml:space="preserve">3.93700909614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92132306098938</t>
   </si>
   <si>
     <t xml:space="preserve">4.01543521881104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07033443450928</t>
+    <t xml:space="preserve">4.07033395767212</t>
   </si>
   <si>
     <t xml:space="preserve">3.97622227668762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18797397613525</t>
+    <t xml:space="preserve">4.1879734992981</t>
   </si>
   <si>
     <t xml:space="preserve">4.24287223815918</t>
@@ -2348,432 +2348,432 @@
     <t xml:space="preserve">4.21150159835815</t>
   </si>
   <si>
+    <t xml:space="preserve">4.39188194274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45462322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43109607696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42325258255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38403987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39972543716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33698415756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36051177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46246671676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44678115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43893814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47815179824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4859938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50167989730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56442070007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60363388061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62716150283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63500452041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49383687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59579181671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66637516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68206024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72911643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64284753799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74480199813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8624415397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90949726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05850744247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03497982025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99576616287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95655298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94871044158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97223854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87028408050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98008108139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0741925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0506649017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02713680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08987712860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19183206558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18398952484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830492019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10556316375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14477682113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23888826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21536064147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1996750831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25457334518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30162954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01929426193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93302488327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79970026016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76048707962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76832962036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68990278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69774580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61147689819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53305006027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50952243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47030878067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55657768249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54873561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57226324081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52520704269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54089260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51736497879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58010625839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82322788238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87812662124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8859691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78401470184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65853214263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77617216110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85459852218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94086790084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5212230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6623911857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73297500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89767074584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68591928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70160436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59965038299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53690910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906656265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1761474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29378700256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7134313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41541051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89381217956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81538486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9251823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84675598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72127294540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5879487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61931896209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77163171768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73861026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69733333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63954544067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79639768600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98627281188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95325088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07708215713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11835956573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97801733016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06057167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90371799468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96976137161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87069654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82941961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62303400039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40839338302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50745820999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56524658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48269128799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58175706863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64780044555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61477899551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57350158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51571369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33409452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30932807922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38362693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16898632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26805114746094</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.39188241958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45462322235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43109560012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42325305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38403940200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39972496032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33698415756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36051177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46246671676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44678115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43893814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47815179824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48599433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50167989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56442022323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60363388061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62716197967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63500452041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49383687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59579133987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66637468338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68206024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72911596298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64284753799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74480199813843</t>
+    <t xml:space="preserve">4.46618127822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42490434646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3753719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27630615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44966983795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34235048294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41664838790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55699062347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67256689071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65605545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71384382247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76337623596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85418605804443</t>
   </si>
   <si>
     <t xml:space="preserve">4.86244106292725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90949726104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05850696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03497982025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99576616287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95655298233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9487099647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97223901748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87028360366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98008060455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07419300079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0506649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02713680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08987760543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19183254241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18399000167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10556364059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14477634429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23888826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21536064147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19967460632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25457382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3016300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01929473876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93302488327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7996997833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7604866027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76832962036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68990325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69774580001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61147689819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53305006027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50952196121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47030878067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55657815933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54873561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57226371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52520751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54089260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51736497879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58010578155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82322788238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87812662124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88596963882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7840142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70558834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65853261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77617216110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85459899902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94086837768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52122402191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66239070892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73297500610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89767026901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68591928482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70160484313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59964990615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53690910339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906608581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17614698410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29378652572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71343088150024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41541051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89381122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81538486480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92518281936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84675550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72127389907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5879487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61931896209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77163171768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73861026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69733333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63954544067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7963981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98627281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95325088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312601089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07708215713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11835908889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97801685333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06057167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9037184715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96976184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87069702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82941961288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62303400039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40839385986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50745820999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56524658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48269176483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58175754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64780044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54873609542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61477851867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57350158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51571369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33409452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30932807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38362693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16898632049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26805114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39188289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46618127822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42490386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3753719329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27630615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44967031478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34235048294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41664838790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55699062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67256641387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65605592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71384382247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76337623596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85418605804443</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.72209930419922</t>
   </si>
   <si>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">4.73035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82116413116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92848443984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92022895812988</t>
+    <t xml:space="preserve">4.82116460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92848491668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92022943496704</t>
   </si>
   <si>
     <t xml:space="preserve">4.94499540328979</t>
@@ -2810,16 +2810,16 @@
     <t xml:space="preserve">4.60652351379395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66431140899658</t>
+    <t xml:space="preserve">4.66431188583374</t>
   </si>
   <si>
     <t xml:space="preserve">4.81290912628174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88720798492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93674039840698</t>
+    <t xml:space="preserve">4.88720750808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93673992156982</t>
   </si>
   <si>
     <t xml:space="preserve">5.0110387802124</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">5.16789197921753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23393583297729</t>
+    <t xml:space="preserve">5.23393535614014</t>
   </si>
   <si>
     <t xml:space="preserve">5.19265794754028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22567939758301</t>
+    <t xml:space="preserve">5.22567987442017</t>
   </si>
   <si>
     <t xml:space="preserve">5.26695680618286</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">5.27521181106567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29172325134277</t>
+    <t xml:space="preserve">5.29172277450562</t>
   </si>
   <si>
     <t xml:space="preserve">5.30823373794556</t>
@@ -2858,13 +2858,13 @@
     <t xml:space="preserve">5.43206548690796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4733419418335</t>
+    <t xml:space="preserve">5.47334241867065</t>
   </si>
   <si>
     <t xml:space="preserve">5.55589628219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41555404663086</t>
+    <t xml:space="preserve">5.41555452346802</t>
   </si>
   <si>
     <t xml:space="preserve">5.4898533821106</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">5.46508693695068</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57240676879883</t>
+    <t xml:space="preserve">5.57240724563599</t>
   </si>
   <si>
     <t xml:space="preserve">5.44857597351074</t>
@@ -2903,67 +2903,67 @@
     <t xml:space="preserve">5.63019514083862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61368417739868</t>
+    <t xml:space="preserve">5.61368465423584</t>
   </si>
   <si>
     <t xml:space="preserve">5.5971736907959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58066320419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65496158599854</t>
+    <t xml:space="preserve">5.58066272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65496110916138</t>
   </si>
   <si>
     <t xml:space="preserve">5.77879238128662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82006978988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84483623504639</t>
+    <t xml:space="preserve">5.82007026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84483575820923</t>
   </si>
   <si>
     <t xml:space="preserve">5.86134672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89436817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81181478500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90262413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80355882644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73751592636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00168943405151</t>
+    <t xml:space="preserve">5.89436864852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8118143081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90262460708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80355930328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73751544952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00168895721436</t>
   </si>
   <si>
     <t xml:space="preserve">6.30713939666748</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38969373703003</t>
+    <t xml:space="preserve">6.38969326019287</t>
   </si>
   <si>
     <t xml:space="preserve">6.39794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47224760055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43922662734985</t>
+    <t xml:space="preserve">6.47224807739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4392261505127</t>
   </si>
   <si>
     <t xml:space="preserve">6.45573711395264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59607934951782</t>
+    <t xml:space="preserve">6.59607887268066</t>
   </si>
   <si>
     <t xml:space="preserve">6.52178049087524</t>
@@ -2975,34 +2975,34 @@
     <t xml:space="preserve">6.58782386779785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51352453231812</t>
+    <t xml:space="preserve">6.51352500915527</t>
   </si>
   <si>
     <t xml:space="preserve">6.56305742263794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67863321304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72816514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67037773132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63735675811768</t>
+    <t xml:space="preserve">6.67863368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72816562652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6703782081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63735628128052</t>
   </si>
   <si>
     <t xml:space="preserve">6.79420900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73642158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68688917160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53829145431519</t>
+    <t xml:space="preserve">6.73642110824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68688869476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53829097747803</t>
   </si>
   <si>
     <t xml:space="preserve">6.62084579467773</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">6.64561176300049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71991062164307</t>
+    <t xml:space="preserve">6.71991014480591</t>
   </si>
   <si>
     <t xml:space="preserve">6.74467658996582</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">5.67972755432129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39904356002808</t>
+    <t xml:space="preserve">5.39904403686523</t>
   </si>
   <si>
     <t xml:space="preserve">5.38253259658813</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">5.66321706771851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60542917251587</t>
+    <t xml:space="preserve">5.60542964935303</t>
   </si>
   <si>
     <t xml:space="preserve">5.7457709312439</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">5.87785768508911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97692203521729</t>
+    <t xml:space="preserve">5.97692251205444</t>
   </si>
   <si>
     <t xml:space="preserve">5.91087913513184</t>
@@ -3074,16 +3074,16 @@
     <t xml:space="preserve">5.91913461685181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63845109939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78704833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94390106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9604115486145</t>
+    <t xml:space="preserve">5.63845062255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78704881668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94390058517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96041202545166</t>
   </si>
   <si>
     <t xml:space="preserve">5.8696026802063</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">5.79011058807373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78145551681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57373857498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67759704589844</t>
+    <t xml:space="preserve">5.78145599365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57373905181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6775975227356</t>
   </si>
   <si>
     <t xml:space="preserve">5.76414585113525</t>
@@ -3137,13 +3137,13 @@
     <t xml:space="preserve">5.86800479888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88531398773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87665939331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9285888671875</t>
+    <t xml:space="preserve">5.88531446456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87665987014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92858839035034</t>
   </si>
   <si>
     <t xml:space="preserve">5.96320819854736</t>
@@ -3164,25 +3164,25 @@
     <t xml:space="preserve">6.17092561721802</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28343868255615</t>
+    <t xml:space="preserve">6.28343915939331</t>
   </si>
   <si>
     <t xml:space="preserve">6.25747394561768</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24881839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24016427993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2315092086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2661280632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46519041061401</t>
+    <t xml:space="preserve">6.24881887435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24016380310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23150873184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26612854003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46519088745117</t>
   </si>
   <si>
     <t xml:space="preserve">6.54308462142944</t>
@@ -3194,22 +3194,22 @@
     <t xml:space="preserve">6.56904935836792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6382884979248</t>
+    <t xml:space="preserve">6.63828802108765</t>
   </si>
   <si>
     <t xml:space="preserve">6.56039428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57770395278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62097835540771</t>
+    <t xml:space="preserve">6.57770442962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62097883224487</t>
   </si>
   <si>
     <t xml:space="preserve">6.65559816360474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6902174949646</t>
+    <t xml:space="preserve">6.69021797180176</t>
   </si>
   <si>
     <t xml:space="preserve">6.73349189758301</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">6.64694309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50846481323242</t>
+    <t xml:space="preserve">6.50846529006958</t>
   </si>
   <si>
     <t xml:space="preserve">6.66425275802612</t>
@@ -3254,58 +3254,58 @@
     <t xml:space="preserve">6.68156242370605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60366916656494</t>
+    <t xml:space="preserve">6.60366868972778</t>
   </si>
   <si>
     <t xml:space="preserve">6.51712036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6296329498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74214696884155</t>
+    <t xml:space="preserve">6.62963342666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74214649200439</t>
   </si>
   <si>
     <t xml:space="preserve">6.87196969985962</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79407596588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85466051101685</t>
+    <t xml:space="preserve">6.79407644271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85466003417969</t>
   </si>
   <si>
     <t xml:space="preserve">6.61232376098633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7854208946228</t>
+    <t xml:space="preserve">6.78542137145996</t>
   </si>
   <si>
     <t xml:space="preserve">6.77676630020142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7508020401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52577447891235</t>
+    <t xml:space="preserve">6.75080156326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52577495574951</t>
   </si>
   <si>
     <t xml:space="preserve">6.42191648483276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45653629302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71618270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72483682632446</t>
+    <t xml:space="preserve">6.45653581619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71618223190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72483730316162</t>
   </si>
   <si>
     <t xml:space="preserve">6.75945663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82869529724121</t>
+    <t xml:space="preserve">6.82869577407837</t>
   </si>
   <si>
     <t xml:space="preserve">6.82004070281982</t>
@@ -3314,25 +3314,25 @@
     <t xml:space="preserve">6.92389917373657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01044845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05372142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9931378364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00179290771484</t>
+    <t xml:space="preserve">7.01044797897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05372190475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99313831329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.001793384552</t>
   </si>
   <si>
     <t xml:space="preserve">7.02775764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97582912445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95851898193359</t>
+    <t xml:space="preserve">6.97582864761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95851850509644</t>
   </si>
   <si>
     <t xml:space="preserve">6.94986343383789</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">7.07103204727173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06237745285034</t>
+    <t xml:space="preserve">7.06237697601318</t>
   </si>
   <si>
     <t xml:space="preserve">7.11430644989014</t>
@@ -3353,31 +3353,31 @@
     <t xml:space="preserve">7.01910257339478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04506778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13161563873291</t>
+    <t xml:space="preserve">7.04506731033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13161611557007</t>
   </si>
   <si>
     <t xml:space="preserve">7.18354558944702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1575813293457</t>
+    <t xml:space="preserve">7.15758085250854</t>
   </si>
   <si>
     <t xml:space="preserve">7.07968711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88927936553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86331510543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93255376815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91524457931519</t>
+    <t xml:space="preserve">6.88927984237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86331462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93255424499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91524410247803</t>
   </si>
   <si>
     <t xml:space="preserve">6.94120931625366</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">6.96717357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17489051818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27009391784668</t>
+    <t xml:space="preserve">7.17489004135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27009439468384</t>
   </si>
   <si>
     <t xml:space="preserve">7.20085477828979</t>
@@ -3404,10 +3404,10 @@
     <t xml:space="preserve">7.14892578125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0883412361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14027118682861</t>
+    <t xml:space="preserve">7.08834171295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14027070999146</t>
   </si>
   <si>
     <t xml:space="preserve">7.26143932342529</t>
@@ -3419,16 +3419,16 @@
     <t xml:space="preserve">7.33933305740356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42588186264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44319248199463</t>
+    <t xml:space="preserve">7.42588138580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44319200515747</t>
   </si>
   <si>
     <t xml:space="preserve">7.48646545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23547410964966</t>
+    <t xml:space="preserve">7.23547506332397</t>
   </si>
   <si>
     <t xml:space="preserve">7.29605865478516</t>
@@ -3437,10 +3437,10 @@
     <t xml:space="preserve">7.19220066070557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45184564590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38260793685913</t>
+    <t xml:space="preserve">7.4518461227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38260746002197</t>
   </si>
   <si>
     <t xml:space="preserve">7.3566427230835</t>
@@ -3449,55 +3449,55 @@
     <t xml:space="preserve">7.52108478546143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84997034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72880268096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76342248916626</t>
+    <t xml:space="preserve">7.84997081756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72880220413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7634220123291</t>
   </si>
   <si>
     <t xml:space="preserve">7.53839540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55570411682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46050119400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40857267379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63359880447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72014760971069</t>
+    <t xml:space="preserve">7.55570507049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4605016708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40857219696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63359785079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72014713287354</t>
   </si>
   <si>
     <t xml:space="preserve">7.88458967208862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77207660675049</t>
+    <t xml:space="preserve">7.77207612991333</t>
   </si>
   <si>
     <t xml:space="preserve">7.65090847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66821813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78073072433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83266162872314</t>
+    <t xml:space="preserve">7.6682186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78073215484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83266067504883</t>
   </si>
   <si>
     <t xml:space="preserve">7.82400560379028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75476741790771</t>
+    <t xml:space="preserve">7.75476694107056</t>
   </si>
   <si>
     <t xml:space="preserve">7.7028374671936</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">7.69418334960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67687320709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94517374038696</t>
+    <t xml:space="preserve">7.67687273025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94517421722412</t>
   </si>
   <si>
     <t xml:space="preserve">8.01441287994385</t>
@@ -3518,10 +3518,10 @@
     <t xml:space="preserve">8.11827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05768775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12692737579346</t>
+    <t xml:space="preserve">8.05768871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12692642211914</t>
   </si>
   <si>
     <t xml:space="preserve">8.0663423538208</t>
@@ -3533,10 +3533,10 @@
     <t xml:space="preserve">8.10961627960205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17885494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17020034790039</t>
+    <t xml:space="preserve">8.17885589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17020130157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.20481967926025</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">8.00575828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99710369110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87593555450439</t>
+    <t xml:space="preserve">7.99710273742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87593650817871</t>
   </si>
   <si>
     <t xml:space="preserve">8.30867862701416</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">8.41253757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.576979637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5856351852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65487384796143</t>
+    <t xml:space="preserve">8.57698059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58563423156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65487289428711</t>
   </si>
   <si>
     <t xml:space="preserve">8.54236030578613</t>
@@ -3584,16 +3584,16 @@
     <t xml:space="preserve">8.62025451660156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81066226959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82797050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70680332183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87990188598633</t>
+    <t xml:space="preserve">8.81066131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82797145843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7068042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87990093231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.834641456604</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">8.93421173095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86179637908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.753173828125</t>
+    <t xml:space="preserve">8.86179733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75317478179932</t>
   </si>
   <si>
     <t xml:space="preserve">8.72601890563965</t>
@@ -3626,22 +3626,22 @@
     <t xml:space="preserve">8.80748558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85274410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77127742767334</t>
+    <t xml:space="preserve">8.85274505615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77127838134766</t>
   </si>
   <si>
     <t xml:space="preserve">8.68981170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69886302947998</t>
+    <t xml:space="preserve">8.69886207580566</t>
   </si>
   <si>
     <t xml:space="preserve">8.73507022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59929275512695</t>
+    <t xml:space="preserve">8.59929180145264</t>
   </si>
   <si>
     <t xml:space="preserve">8.56308460235596</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">8.08333492279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27342414855957</t>
+    <t xml:space="preserve">8.27342510223389</t>
   </si>
   <si>
     <t xml:space="preserve">8.42730712890625</t>
@@ -3680,10 +3680,10 @@
     <t xml:space="preserve">8.4906702041626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40015125274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58118724822998</t>
+    <t xml:space="preserve">8.40015029907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5811882019043</t>
   </si>
   <si>
     <t xml:space="preserve">8.40920257568359</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">8.41825485229492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60834503173828</t>
+    <t xml:space="preserve">8.60834407806396</t>
   </si>
   <si>
     <t xml:space="preserve">8.48161697387695</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">8.68075942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65360355377197</t>
+    <t xml:space="preserve">8.65360450744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.870849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02473068237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91610908508301</t>
+    <t xml:space="preserve">9.02473163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91610813140869</t>
   </si>
   <si>
     <t xml:space="preserve">8.98852348327637</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">9.08809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01567935943604</t>
+    <t xml:space="preserve">9.01567840576172</t>
   </si>
   <si>
     <t xml:space="preserve">9.04283428192139</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">9.16050910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79843425750732</t>
+    <t xml:space="preserve">8.79843330383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.36394309997559</t>
@@ -3749,16 +3749,16 @@
     <t xml:space="preserve">8.29152774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23721694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26437282562256</t>
+    <t xml:space="preserve">8.23721790313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26437187194824</t>
   </si>
   <si>
     <t xml:space="preserve">8.47256565093994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97947216033936</t>
+    <t xml:space="preserve">8.97947120666504</t>
   </si>
   <si>
     <t xml:space="preserve">8.89800453186035</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">9.14240550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34154605865479</t>
+    <t xml:space="preserve">9.3415470123291</t>
   </si>
   <si>
     <t xml:space="preserve">9.28723621368408</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">9.19671630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2510290145874</t>
+    <t xml:space="preserve">9.25102806091309</t>
   </si>
   <si>
     <t xml:space="preserve">9.12430191040039</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">9.21482086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35965156555176</t>
+    <t xml:space="preserve">9.35965061187744</t>
   </si>
   <si>
     <t xml:space="preserve">9.17861366271973</t>
@@ -3815,10 +3815,10 @@
     <t xml:space="preserve">9.10619831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30533885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50448036193848</t>
+    <t xml:space="preserve">9.30533981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50448131561279</t>
   </si>
   <si>
     <t xml:space="preserve">9.65504741668701</t>
@@ -3896,9 +3896,6 @@
     <t xml:space="preserve">9.5797643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50448131561279</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.46683979034424</t>
   </si>
   <si>
@@ -4299,6 +4296,9 @@
   </si>
   <si>
     <t xml:space="preserve">13.8199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3599996566772</t>
   </si>
 </sst>
 </file>
@@ -47477,7 +47477,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1648" t="s">
-        <v>897</v>
+        <v>839</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47503,7 +47503,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1649" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47529,7 +47529,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47555,7 +47555,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1651" t="s">
-        <v>897</v>
+        <v>839</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47581,7 +47581,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1652" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47607,7 +47607,7 @@
         <v>5.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47633,7 +47633,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1654" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47659,7 +47659,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1655" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47685,7 +47685,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1656" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47711,7 +47711,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1657" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47737,7 +47737,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1658" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -47763,7 +47763,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1659" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47789,7 +47789,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1660" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47815,7 +47815,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1661" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47841,7 +47841,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1662" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47867,7 +47867,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1663" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47893,7 +47893,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1664" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47945,7 +47945,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1666" t="s">
-        <v>897</v>
+        <v>839</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48023,7 +48023,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1669" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48049,7 +48049,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1670" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48075,7 +48075,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1671" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48101,7 +48101,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1672" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -48127,7 +48127,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1673" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48153,7 +48153,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1674" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48231,7 +48231,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1677" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48257,7 +48257,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1678" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48335,7 +48335,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48361,7 +48361,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1682" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48413,7 +48413,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1684" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48439,7 +48439,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G1685" t="s">
-        <v>803</v>
+        <v>919</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -48517,7 +48517,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48673,7 +48673,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48725,7 +48725,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -48777,7 +48777,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1698" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48803,7 +48803,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48855,7 +48855,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -49323,7 +49323,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1719" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49401,7 +49401,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1722" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49427,7 +49427,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1723" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49505,7 +49505,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1726" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49583,7 +49583,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1729" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -63597,7 +63597,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>1294</v>
+        <v>1268</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63623,7 +63623,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2269" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63649,7 +63649,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2270" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63675,7 +63675,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2271" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63701,7 +63701,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2272" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63753,7 +63753,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2274" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63883,7 +63883,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2279" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63909,7 +63909,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2280" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63935,7 +63935,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2281" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63961,7 +63961,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2282" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63987,7 +63987,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2283" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64013,7 +64013,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64065,7 +64065,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2286" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64117,7 +64117,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2288" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64143,7 +64143,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2289" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64169,7 +64169,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2290" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64221,7 +64221,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2292" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64247,7 +64247,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2293" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64273,7 +64273,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2294" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64299,7 +64299,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2295" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64325,7 +64325,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2296" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64351,7 +64351,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2297" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64377,7 +64377,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2298" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64403,7 +64403,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2299" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64429,7 +64429,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2300" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64455,7 +64455,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2301" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64481,7 +64481,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2302" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64507,7 +64507,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2303" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64533,7 +64533,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2304" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64559,7 +64559,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2305" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64585,7 +64585,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2306" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64611,7 +64611,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64637,7 +64637,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2308" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64663,7 +64663,7 @@
         <v>11.5</v>
       </c>
       <c r="G2309" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64689,7 +64689,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2310" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64715,7 +64715,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2311" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64741,7 +64741,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2312" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64767,7 +64767,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2313" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64793,7 +64793,7 @@
         <v>11.5</v>
       </c>
       <c r="G2314" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64819,7 +64819,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2315" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64845,7 +64845,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2316" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64871,7 +64871,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2317" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64897,7 +64897,7 @@
         <v>12</v>
       </c>
       <c r="G2318" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64923,7 +64923,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2319" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64949,7 +64949,7 @@
         <v>12</v>
       </c>
       <c r="G2320" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64975,7 +64975,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2321" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65001,7 +65001,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2322" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65027,7 +65027,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2323" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65053,7 +65053,7 @@
         <v>12</v>
       </c>
       <c r="G2324" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65079,7 +65079,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2325" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65105,7 +65105,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2326" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65131,7 +65131,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2327" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65157,7 +65157,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2328" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65183,7 +65183,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2329" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65209,7 +65209,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2330" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65235,7 +65235,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2331" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65261,7 +65261,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2332" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65287,7 +65287,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2333" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65313,7 +65313,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2334" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65339,7 +65339,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65365,7 +65365,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65391,7 +65391,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2337" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65417,7 +65417,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2338" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65443,7 +65443,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2339" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65469,7 +65469,7 @@
         <v>12.5</v>
       </c>
       <c r="G2340" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65495,7 +65495,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2341" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65521,7 +65521,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65547,7 +65547,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2343" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65573,7 +65573,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2344" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65599,7 +65599,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2345" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65625,7 +65625,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2346" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65651,7 +65651,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2347" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65677,7 +65677,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2348" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65703,7 +65703,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2349" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65729,7 +65729,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2350" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65755,7 +65755,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2351" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65781,7 +65781,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2352" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65807,7 +65807,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2353" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65833,7 +65833,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2354" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65859,7 +65859,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2355" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65885,7 +65885,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2356" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65911,7 +65911,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2357" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65937,7 +65937,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2358" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65963,7 +65963,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2359" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65989,7 +65989,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2360" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66015,7 +66015,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2361" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66041,7 +66041,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2362" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66067,7 +66067,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2363" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66093,7 +66093,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2364" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66119,7 +66119,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2365" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66145,7 +66145,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2366" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66171,7 +66171,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2367" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66197,7 +66197,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G2368" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66223,7 +66223,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2369" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66249,7 +66249,7 @@
         <v>12</v>
       </c>
       <c r="G2370" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66275,7 +66275,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2371" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66301,7 +66301,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2372" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66327,7 +66327,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2373" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66353,7 +66353,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2374" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66379,7 +66379,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2375" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66405,7 +66405,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2376" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66431,7 +66431,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66457,7 +66457,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2378" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66483,7 +66483,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2379" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66509,7 +66509,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2380" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66535,7 +66535,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2381" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66561,7 +66561,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2382" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66587,7 +66587,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2383" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66613,7 +66613,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2384" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66639,7 +66639,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2385" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66665,7 +66665,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2386" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66691,7 +66691,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2387" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66717,7 +66717,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2388" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66743,7 +66743,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2389" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66769,7 +66769,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2390" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66795,7 +66795,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2391" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66821,7 +66821,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2392" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66847,7 +66847,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2393" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66873,7 +66873,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2394" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66899,7 +66899,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2395" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66925,7 +66925,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2396" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66951,7 +66951,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2397" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66977,7 +66977,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2398" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67003,7 +67003,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2399" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67029,7 +67029,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2400" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67055,7 +67055,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2401" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67081,7 +67081,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2402" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67107,7 +67107,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67133,7 +67133,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67159,7 +67159,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2405" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67185,7 +67185,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2406" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67211,7 +67211,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67237,7 +67237,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2408" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67263,7 +67263,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67289,7 +67289,7 @@
         <v>12.5</v>
       </c>
       <c r="G2410" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67315,7 +67315,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2411" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67341,7 +67341,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67367,7 +67367,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2413" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67393,7 +67393,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2414" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67419,7 +67419,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2415" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67445,7 +67445,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67471,7 +67471,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2417" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67497,7 +67497,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2418" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67523,7 +67523,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67549,7 +67549,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2420" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67575,7 +67575,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2421" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67601,7 +67601,7 @@
         <v>13</v>
       </c>
       <c r="G2422" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67627,7 +67627,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67653,7 +67653,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G2424" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67679,7 +67679,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2425" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67705,7 +67705,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2426" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67731,7 +67731,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67757,7 +67757,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2428" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67783,7 +67783,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2429" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67809,7 +67809,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2430" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67835,7 +67835,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2431" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67861,7 +67861,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2432" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67887,7 +67887,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2433" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67913,7 +67913,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2434" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67939,7 +67939,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2435" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67965,7 +67965,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2436" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67991,7 +67991,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2437" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68017,7 +68017,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2438" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68043,7 +68043,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2439" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68069,7 +68069,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2440" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68095,7 +68095,7 @@
         <v>13.5</v>
       </c>
       <c r="G2441" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68121,7 +68121,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2442" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68147,7 +68147,7 @@
         <v>13.5</v>
       </c>
       <c r="G2443" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68173,7 +68173,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2444" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68199,7 +68199,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68225,7 +68225,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2446" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68251,7 +68251,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2447" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68277,7 +68277,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2448" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68303,7 +68303,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2449" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68329,7 +68329,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2450" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68355,7 +68355,7 @@
         <v>14</v>
       </c>
       <c r="G2451" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68381,7 +68381,7 @@
         <v>14</v>
       </c>
       <c r="G2452" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68407,7 +68407,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2453" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68433,7 +68433,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2454" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68459,7 +68459,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2455" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68485,7 +68485,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2456" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68511,7 +68511,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2457" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68537,7 +68537,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2458" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68563,7 +68563,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G2459" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68589,7 +68589,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2460" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68615,7 +68615,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G2461" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68641,7 +68641,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2462" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68667,7 +68667,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G2463" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68693,7 +68693,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2464" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68719,7 +68719,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G2465" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68745,7 +68745,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2466" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68771,7 +68771,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2467" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68797,7 +68797,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68823,7 +68823,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2469" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68849,7 +68849,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68875,7 +68875,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68901,7 +68901,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2472" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68927,7 +68927,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2473" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68953,7 +68953,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2474" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68979,7 +68979,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69005,7 +69005,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G2476" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69031,7 +69031,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69057,7 +69057,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69083,7 +69083,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69109,7 +69109,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2480" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69135,7 +69135,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2481" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69161,7 +69161,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69187,7 +69187,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2483" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69213,7 +69213,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2484" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69239,7 +69239,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2485" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69265,7 +69265,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2486" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69291,7 +69291,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G2487" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69317,7 +69317,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2488" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69343,7 +69343,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2489" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69369,7 +69369,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2490" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69395,7 +69395,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2491" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69421,7 +69421,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2492" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69447,7 +69447,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2493" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69473,7 +69473,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69499,7 +69499,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69525,7 +69525,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G2496" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69551,7 +69551,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2497" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69577,7 +69577,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2498" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69603,7 +69603,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2499" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69629,7 +69629,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2500" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69655,7 +69655,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2501" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69681,7 +69681,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2502" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69707,7 +69707,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G2503" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69733,7 +69733,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2504" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69741,27 +69741,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6911458333</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
+        <v>216804</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>13.7600002288818</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>13.5200004577637</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>13.6800003051758</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>13.6999998092651</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>176361</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>13.8000001907349</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>13.5600004196167</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>13.6599998474121</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>13.6400003433228</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
         <v>324078</v>
       </c>
-      <c r="C2505" t="n">
+      <c r="C2507" t="n">
         <v>13.9200000762939</v>
       </c>
-      <c r="D2505" t="n">
+      <c r="D2507" t="n">
         <v>13.3400001525879</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2507" t="n">
         <v>13.5</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>13.9200000762939</v>
       </c>
-      <c r="G2505" t="s">
-        <v>1408</v>
-      </c>
-      <c r="H2505" t="s">
+      <c r="G2507" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6911689815</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>471903</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>14.0600004196167</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>14.0600004196167</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>14.3599996566772</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49119520187378</t>
+    <t xml:space="preserve">4.49119424819946</t>
   </si>
   <si>
     <t xml:space="preserve">CE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5281457901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46432161331177</t>
+    <t xml:space="preserve">4.52814531326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46432113647461</t>
   </si>
   <si>
     <t xml:space="preserve">4.30644083023071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26613092422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31315898895264</t>
+    <t xml:space="preserve">4.2661304473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31315946578979</t>
   </si>
   <si>
     <t xml:space="preserve">4.31987714767456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3669056892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27284955978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23589897155762</t>
+    <t xml:space="preserve">4.36690616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27284908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23589849472046</t>
   </si>
   <si>
     <t xml:space="preserve">4.05114555358887</t>
@@ -77,40 +77,40 @@
     <t xml:space="preserve">4.08473634719849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74210286140442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91677808761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03099060058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15527868270874</t>
+    <t xml:space="preserve">3.74210214614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91677904129028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03099012374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15527963638306</t>
   </si>
   <si>
     <t xml:space="preserve">4.12840509414673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01419448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12504577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12168788909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94701075553894</t>
+    <t xml:space="preserve">4.01419401168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1250467300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12168741226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9470112323761</t>
   </si>
   <si>
     <t xml:space="preserve">3.80256724357605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83615827560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86975002288818</t>
+    <t xml:space="preserve">3.83615875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8697509765625</t>
   </si>
   <si>
     <t xml:space="preserve">3.5808629989624</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">3.42970085144043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7521800994873</t>
+    <t xml:space="preserve">3.75217938423157</t>
   </si>
   <si>
     <t xml:space="preserve">3.6077356338501</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">3.84959554672241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90670084953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96716570854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06458187103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82944011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77233409881592</t>
+    <t xml:space="preserve">3.9067018032074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96716618537903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06458139419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82944059371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77233505249023</t>
   </si>
   <si>
     <t xml:space="preserve">3.9033420085907</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">3.72866582870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79584884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88318753242493</t>
+    <t xml:space="preserve">3.79584932327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88318705558777</t>
   </si>
   <si>
     <t xml:space="preserve">3.95708847045898</t>
@@ -167,43 +167,43 @@
     <t xml:space="preserve">4.1955885887146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18551111221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13848304748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22246217727661</t>
+    <t xml:space="preserve">4.18551158905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13848257064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22246170043945</t>
   </si>
   <si>
     <t xml:space="preserve">4.29972267150879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35682821273804</t>
+    <t xml:space="preserve">4.35682773590088</t>
   </si>
   <si>
     <t xml:space="preserve">4.25605392456055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2795672416687</t>
+    <t xml:space="preserve">4.27956771850586</t>
   </si>
   <si>
     <t xml:space="preserve">4.14856052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32659530639648</t>
+    <t xml:space="preserve">4.3265962600708</t>
   </si>
   <si>
     <t xml:space="preserve">4.26949024200439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16535615921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09817218780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04778575897217</t>
+    <t xml:space="preserve">4.16535568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09817266464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04778623580933</t>
   </si>
   <si>
     <t xml:space="preserve">4.04106760025024</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">3.93021512031555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91006016731262</t>
+    <t xml:space="preserve">3.91006064414978</t>
   </si>
   <si>
     <t xml:space="preserve">3.81936311721802</t>
@@ -221,28 +221,28 @@
     <t xml:space="preserve">3.75889801979065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71187043190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93357467651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8260817527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0813775062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15863800048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17879295349121</t>
+    <t xml:space="preserve">3.71186995506287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93357515335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82608199119568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08137702941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15863847732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17879390716553</t>
   </si>
   <si>
     <t xml:space="preserve">4.21238422393799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21574354171753</t>
+    <t xml:space="preserve">4.21574401855469</t>
   </si>
   <si>
     <t xml:space="preserve">4.28292751312256</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">4.30308198928833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35346937179565</t>
+    <t xml:space="preserve">4.35346841812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.1989483833313</t>
@@ -260,34 +260,34 @@
     <t xml:space="preserve">4.07465934753418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08809614181519</t>
+    <t xml:space="preserve">4.08809518814087</t>
   </si>
   <si>
     <t xml:space="preserve">4.06122303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02427101135254</t>
+    <t xml:space="preserve">4.02427196502686</t>
   </si>
   <si>
     <t xml:space="preserve">3.93693351745605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21649026870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14420652389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19927883148193</t>
+    <t xml:space="preserve">4.21648979187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14420700073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19927930831909</t>
   </si>
   <si>
     <t xml:space="preserve">4.25435209274292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23370027542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23714160919189</t>
+    <t xml:space="preserve">4.23369932174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23714208602905</t>
   </si>
   <si>
     <t xml:space="preserve">4.49185180664062</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">4.47119998931885</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45743179321289</t>
+    <t xml:space="preserve">4.45743131637573</t>
   </si>
   <si>
     <t xml:space="preserve">4.46431589126587</t>
@@ -311,28 +311,28 @@
     <t xml:space="preserve">4.31975078582764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3713812828064</t>
+    <t xml:space="preserve">4.37138080596924</t>
   </si>
   <si>
     <t xml:space="preserve">4.28188848495483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42989540100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34040212631226</t>
+    <t xml:space="preserve">4.42989635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34040260314941</t>
   </si>
   <si>
     <t xml:space="preserve">4.35072898864746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25091028213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03750371932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91703319549561</t>
+    <t xml:space="preserve">4.25090980529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03750419616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91703271865845</t>
   </si>
   <si>
     <t xml:space="preserve">3.98243093490601</t>
@@ -344,61 +344,61 @@
     <t xml:space="preserve">4.13732290267944</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3369607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38170719146729</t>
+    <t xml:space="preserve">4.33696126937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38170623779297</t>
   </si>
   <si>
     <t xml:space="preserve">4.42301177978516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52971458435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74148917198181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7518150806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73116302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84130835533142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65199661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5246410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42826342582703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50743103027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65888023376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75525736808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82065606117249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78623533248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670728683472</t>
+    <t xml:space="preserve">4.52971410751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74148988723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181531906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73116230964661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84130787849426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65199613571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52464127540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42826390266418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50743007659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65888071060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75525760650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82065582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78623557090759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9067063331604</t>
   </si>
   <si>
     <t xml:space="preserve">3.96522188186646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9514524936676</t>
+    <t xml:space="preserve">3.95145297050476</t>
   </si>
   <si>
     <t xml:space="preserve">4.04094552993774</t>
@@ -407,112 +407,112 @@
     <t xml:space="preserve">4.01341009140015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94456911087036</t>
+    <t xml:space="preserve">3.9445686340332</t>
   </si>
   <si>
     <t xml:space="preserve">3.98931550979614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9583375453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79656171798706</t>
+    <t xml:space="preserve">3.95833802223206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79656147956848</t>
   </si>
   <si>
     <t xml:space="preserve">3.90326476097107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80000352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68641638755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70018458366394</t>
+    <t xml:space="preserve">3.80000376701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68641662597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70018482208252</t>
   </si>
   <si>
     <t xml:space="preserve">3.7655827999115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70362734794617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66576385498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66920614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5521776676178</t>
+    <t xml:space="preserve">3.70362710952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66576409339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66920638084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55217719078064</t>
   </si>
   <si>
     <t xml:space="preserve">3.48677897453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47989439964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37319183349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37181448936462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50054669380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68985819816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561971664429</t>
+    <t xml:space="preserve">3.47989463806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37319159507751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3718147277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50054717063904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68985843658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561947822571</t>
   </si>
   <si>
     <t xml:space="preserve">3.45235848426819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47645282745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64511203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72083687782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70706868171692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77935171127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80688858032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61413383483887</t>
+    <t xml:space="preserve">3.47645258903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64511275291443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72083711624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7070689201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77935147285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80688810348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61413407325745</t>
   </si>
   <si>
     <t xml:space="preserve">3.61757588386536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57971382141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56594586372375</t>
+    <t xml:space="preserve">3.57971358299255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5659453868866</t>
   </si>
   <si>
     <t xml:space="preserve">3.49366283416748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49022150039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4489164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63822817802429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49710416793823</t>
+    <t xml:space="preserve">3.49022102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44891595840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63822770118713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49710512161255</t>
   </si>
   <si>
     <t xml:space="preserve">3.38696002960205</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">3.35804629325867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37456846237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31123542785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32637977600098</t>
+    <t xml:space="preserve">3.37456870079041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31123471260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32638001441956</t>
   </si>
   <si>
     <t xml:space="preserve">3.35529327392578</t>
@@ -542,16 +542,16 @@
     <t xml:space="preserve">3.48333668708801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51087331771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51775717735291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47301077842712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57627177238464</t>
+    <t xml:space="preserve">3.51087260246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51775789260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47301054000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57627153396606</t>
   </si>
   <si>
     <t xml:space="preserve">3.53496742248535</t>
@@ -560,43 +560,43 @@
     <t xml:space="preserve">3.64855480194092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67953252792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59692311286926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64166951179504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63134384155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56250309944153</t>
+    <t xml:space="preserve">3.67953205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59692358970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6416699886322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63134431838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56250333786011</t>
   </si>
   <si>
     <t xml:space="preserve">3.5315248966217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45580101013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4117419719696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4296407699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45924282073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44203233718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52808332443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63478636741638</t>
+    <t xml:space="preserve">3.45580053329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41174268722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42964124679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45924234390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44203209877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52808260917664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6347861289978</t>
   </si>
   <si>
     <t xml:space="preserve">3.67609071731567</t>
@@ -608,28 +608,28 @@
     <t xml:space="preserve">3.58659768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54529356956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5590615272522</t>
+    <t xml:space="preserve">3.54529333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55906128883362</t>
   </si>
   <si>
     <t xml:space="preserve">3.56938743591309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71739530563354</t>
+    <t xml:space="preserve">3.71739554405212</t>
   </si>
   <si>
     <t xml:space="preserve">3.94112753868103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00996780395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8860547542572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97210550308228</t>
+    <t xml:space="preserve">4.00996685028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88605523109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97210502624512</t>
   </si>
   <si>
     <t xml:space="preserve">3.83442378044128</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">3.92735862731934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98587346076965</t>
+    <t xml:space="preserve">3.98587250709534</t>
   </si>
   <si>
     <t xml:space="preserve">4.0547137260437</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">3.93080067634583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04438734054565</t>
+    <t xml:space="preserve">4.04438781738281</t>
   </si>
   <si>
     <t xml:space="preserve">4.06159830093384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91014862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89982318878174</t>
+    <t xml:space="preserve">3.91014909744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89982271194458</t>
   </si>
   <si>
     <t xml:space="preserve">4.05815601348877</t>
@@ -665,25 +665,25 @@
     <t xml:space="preserve">4.07192373275757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07880878448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03061962127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19583702087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20960521697998</t>
+    <t xml:space="preserve">4.07880830764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03062009811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19583749771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20960569381714</t>
   </si>
   <si>
     <t xml:space="preserve">4.29565572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27844619750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24746704101562</t>
+    <t xml:space="preserve">4.27844667434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24746799468994</t>
   </si>
   <si>
     <t xml:space="preserve">4.30254030227661</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">4.1269965171814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13043880462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20272159576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10634469985962</t>
+    <t xml:space="preserve">4.13043832778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.202721118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10634517669678</t>
   </si>
   <si>
     <t xml:space="preserve">4.12011241912842</t>
@@ -710,22 +710,22 @@
     <t xml:space="preserve">4.24058389663696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14764881134033</t>
+    <t xml:space="preserve">4.14764928817749</t>
   </si>
   <si>
     <t xml:space="preserve">4.16141748428345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04783010482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14076471328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1510910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15453290939331</t>
+    <t xml:space="preserve">4.04782962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14076519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15109157562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15453243255615</t>
   </si>
   <si>
     <t xml:space="preserve">4.18206882476807</t>
@@ -734,28 +734,28 @@
     <t xml:space="preserve">4.15797472000122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21304702758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32319307327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43333721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44022178649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38514995574951</t>
+    <t xml:space="preserve">4.21304750442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32319211959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43333768844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44022130966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3851490020752</t>
   </si>
   <si>
     <t xml:space="preserve">4.47464179992676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41956996917725</t>
+    <t xml:space="preserve">4.41956901550293</t>
   </si>
   <si>
     <t xml:space="preserve">4.37482357025146</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">4.41268587112427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34384441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30942535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36793851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35417079925537</t>
+    <t xml:space="preserve">4.34384489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30942487716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36793947219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35417032241821</t>
   </si>
   <si>
     <t xml:space="preserve">4.28533029556274</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">4.48840999603271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50906181335449</t>
+    <t xml:space="preserve">4.50906229019165</t>
   </si>
   <si>
     <t xml:space="preserve">4.53659868240356</t>
@@ -800,19 +800,19 @@
     <t xml:space="preserve">4.44710636138916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67083787918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69899654388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8010721206665</t>
+    <t xml:space="preserve">4.67083835601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69899749755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80107259750366</t>
   </si>
   <si>
     <t xml:space="preserve">4.71659564971924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83627033233643</t>
+    <t xml:space="preserve">4.83627080917358</t>
   </si>
   <si>
     <t xml:space="preserve">4.86090993881226</t>
@@ -821,34 +821,34 @@
     <t xml:space="preserve">4.85034990310669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87850904464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78347253799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72011661529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68491744995117</t>
+    <t xml:space="preserve">4.8785080909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78347301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72011566162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68491697311401</t>
   </si>
   <si>
     <t xml:space="preserve">4.7306752204895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75179433822632</t>
+    <t xml:space="preserve">4.75179386138916</t>
   </si>
   <si>
     <t xml:space="preserve">4.81515169143677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81163215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9277868270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93834638595581</t>
+    <t xml:space="preserve">4.81163167953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92778635025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93834590911865</t>
   </si>
   <si>
     <t xml:space="preserve">4.87498903274536</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">4.80459260940552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78699254989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95946550369263</t>
+    <t xml:space="preserve">4.7869930267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95946502685547</t>
   </si>
   <si>
     <t xml:space="preserve">4.86442947387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89258861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89610767364502</t>
+    <t xml:space="preserve">4.89258813858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89610815048218</t>
   </si>
   <si>
     <t xml:space="preserve">4.91370725631714</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">4.97706508636475</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94538593292236</t>
+    <t xml:space="preserve">4.94538545608521</t>
   </si>
   <si>
     <t xml:space="preserve">5.1108193397522</t>
@@ -902,40 +902,40 @@
     <t xml:space="preserve">5.10377883911133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09673976898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05098152160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08969974517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01930332183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04746246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96650505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91018772125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00874328613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10025882720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06858062744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13193798065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04042196273804</t>
+    <t xml:space="preserve">5.09673929214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05098104476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08970022201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01930284500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04746198654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96650409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91018724441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0087423324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10025930404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06858110427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13193845748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04042100906372</t>
   </si>
   <si>
     <t xml:space="preserve">5.1248984336853</t>
@@ -947,34 +947,34 @@
     <t xml:space="preserve">5.36424732208252</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21289443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03690195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16361665725708</t>
+    <t xml:space="preserve">5.21289491653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03690242767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16361618041992</t>
   </si>
   <si>
     <t xml:space="preserve">5.2727313041687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23049306869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15305757522583</t>
+    <t xml:space="preserve">5.23049354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15305709838867</t>
   </si>
   <si>
     <t xml:space="preserve">5.2023344039917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11433887481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10729932785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00522327423096</t>
+    <t xml:space="preserve">5.11433839797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10729885101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00522375106812</t>
   </si>
   <si>
     <t xml:space="preserve">4.9981837272644</t>
@@ -986,22 +986,22 @@
     <t xml:space="preserve">5.04394149780273</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06506061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15657711029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34312915802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30089139938354</t>
+    <t xml:space="preserve">5.06506109237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15657663345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34312868118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30089044570923</t>
   </si>
   <si>
     <t xml:space="preserve">5.27977132797241</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30793046951294</t>
+    <t xml:space="preserve">5.30792999267578</t>
   </si>
   <si>
     <t xml:space="preserve">5.25161266326904</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">5.29033088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33608913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3466477394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36776876449585</t>
+    <t xml:space="preserve">5.33608961105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34664869308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36776781082153</t>
   </si>
   <si>
     <t xml:space="preserve">5.35368824005127</t>
@@ -1028,10 +1028,10 @@
     <t xml:space="preserve">5.38536691665649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39944696426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26569175720215</t>
+    <t xml:space="preserve">5.39944648742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26569223403931</t>
   </si>
   <si>
     <t xml:space="preserve">5.31145048141479</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">5.3255295753479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28329181671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23401403427124</t>
+    <t xml:space="preserve">5.28329086303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23401355743408</t>
   </si>
   <si>
     <t xml:space="preserve">5.2164134979248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14249706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16713666915894</t>
+    <t xml:space="preserve">5.14249753952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16713619232178</t>
   </si>
   <si>
     <t xml:space="preserve">5.31497001647949</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">5.29737091064453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19177532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35720777511597</t>
+    <t xml:space="preserve">5.19177484512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35720825195312</t>
   </si>
   <si>
     <t xml:space="preserve">5.0721001625061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98410415649414</t>
+    <t xml:space="preserve">4.9841046333313</t>
   </si>
   <si>
     <t xml:space="preserve">4.94186639785767</t>
@@ -1082,46 +1082,46 @@
     <t xml:space="preserve">4.92426633834839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98058414459229</t>
+    <t xml:space="preserve">4.98058462142944</t>
   </si>
   <si>
     <t xml:space="preserve">5.03338241577148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05450105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1847357749939</t>
+    <t xml:space="preserve">5.0545015335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18473529815674</t>
   </si>
   <si>
     <t xml:space="preserve">5.17417621612549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21993494033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17769575119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22697401046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28681087493896</t>
+    <t xml:space="preserve">5.21993446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17769622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22697353363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28681135177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.02282285690308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0017032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02986192703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.058021068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92074680328369</t>
+    <t xml:space="preserve">5.00170373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02986240386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05802154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92074728012085</t>
   </si>
   <si>
     <t xml:space="preserve">4.99114418029785</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">5.37128782272339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47688341140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48392295837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44168519973755</t>
+    <t xml:space="preserve">5.47688293457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48392200469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44168424606323</t>
   </si>
   <si>
     <t xml:space="preserve">5.43464469909668</t>
@@ -1151,61 +1151,61 @@
     <t xml:space="preserve">5.46984338760376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40648555755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37832689285278</t>
+    <t xml:space="preserve">5.40648603439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37832736968994</t>
   </si>
   <si>
     <t xml:space="preserve">5.18825531005859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13897752761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32905006408691</t>
+    <t xml:space="preserve">5.13897800445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32904958724976</t>
   </si>
   <si>
     <t xml:space="preserve">5.14601755142212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19529581069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24457263946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22345399856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23753309249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16009712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11785888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97002506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21900033950806</t>
+    <t xml:space="preserve">5.19529485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24457311630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22345447540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23753261566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16009664535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11785936355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97002458572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2189998626709</t>
   </si>
   <si>
     <t xml:space="preserve">5.14661407470703</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98012733459473</t>
+    <t xml:space="preserve">4.98012781143188</t>
   </si>
   <si>
     <t xml:space="preserve">4.94393444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81364059448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84259414672852</t>
+    <t xml:space="preserve">4.81364011764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84259462356567</t>
   </si>
   <si>
     <t xml:space="preserve">4.85707187652588</t>
@@ -1220,13 +1220,13 @@
     <t xml:space="preserve">4.56029081344604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46618986129761</t>
+    <t xml:space="preserve">4.46619033813477</t>
   </si>
   <si>
     <t xml:space="preserve">4.21284008026123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45171356201172</t>
+    <t xml:space="preserve">4.4517126083374</t>
   </si>
   <si>
     <t xml:space="preserve">4.37208843231201</t>
@@ -1238,10 +1238,10 @@
     <t xml:space="preserve">4.40828132629395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34313440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29246377944946</t>
+    <t xml:space="preserve">4.34313488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29246473312378</t>
   </si>
   <si>
     <t xml:space="preserve">4.39380359649658</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">4.4372353553772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53133630752563</t>
+    <t xml:space="preserve">4.53133678436279</t>
   </si>
   <si>
     <t xml:space="preserve">4.61096096038818</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">4.69058513641357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57476806640625</t>
+    <t xml:space="preserve">4.57476854324341</t>
   </si>
   <si>
     <t xml:space="preserve">4.58200645446777</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">4.48790502548218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54581356048584</t>
+    <t xml:space="preserve">4.545814037323</t>
   </si>
   <si>
     <t xml:space="preserve">4.58924531936646</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">4.6037220954895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68334579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69782257080078</t>
+    <t xml:space="preserve">4.68334627151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69782304763794</t>
   </si>
   <si>
     <t xml:space="preserve">4.62543773651123</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">4.63267612457275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61819934844971</t>
+    <t xml:space="preserve">4.61819982528687</t>
   </si>
   <si>
     <t xml:space="preserve">4.56753015518188</t>
@@ -1307,52 +1307,52 @@
     <t xml:space="preserve">4.42999696731567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59648418426514</t>
+    <t xml:space="preserve">4.59648370742798</t>
   </si>
   <si>
     <t xml:space="preserve">4.47342777252197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51685953140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50962114334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17664766311646</t>
+    <t xml:space="preserve">4.51685905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50962066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1766471862793</t>
   </si>
   <si>
     <t xml:space="preserve">4.10426187515259</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04635381698608</t>
+    <t xml:space="preserve">4.04635334014893</t>
   </si>
   <si>
     <t xml:space="preserve">4.0246376991272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03187656402588</t>
+    <t xml:space="preserve">4.03187608718872</t>
   </si>
   <si>
     <t xml:space="preserve">4.05359220504761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0680685043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97396779060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00292253494263</t>
+    <t xml:space="preserve">4.06806898117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97396802902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00292205810547</t>
   </si>
   <si>
     <t xml:space="preserve">3.85091233253479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8726282119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93053650856018</t>
+    <t xml:space="preserve">3.87262773513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93053698539734</t>
   </si>
   <si>
     <t xml:space="preserve">3.92329788208008</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">4.20560169219971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22007846832275</t>
+    <t xml:space="preserve">4.22007894515991</t>
   </si>
   <si>
     <t xml:space="preserve">4.23455572128296</t>
@@ -1376,34 +1376,34 @@
     <t xml:space="preserve">4.25627136230469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27798652648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29970359802246</t>
+    <t xml:space="preserve">4.27798700332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2997031211853</t>
   </si>
   <si>
     <t xml:space="preserve">4.36484956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35761165618896</t>
+    <t xml:space="preserve">4.35761117935181</t>
   </si>
   <si>
     <t xml:space="preserve">4.26351022720337</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09702301025391</t>
+    <t xml:space="preserve">4.09702348709106</t>
   </si>
   <si>
     <t xml:space="preserve">4.06083059310913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12597703933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90882086753845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84367394447327</t>
+    <t xml:space="preserve">4.12597751617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90882039070129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84367346763611</t>
   </si>
   <si>
     <t xml:space="preserve">3.7857654094696</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">3.80748105049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72061896324158</t>
+    <t xml:space="preserve">3.72061800956726</t>
   </si>
   <si>
     <t xml:space="preserve">3.68442559242249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5794665813446</t>
+    <t xml:space="preserve">3.57946681976318</t>
   </si>
   <si>
     <t xml:space="preserve">3.45641088485718</t>
@@ -1433,34 +1433,34 @@
     <t xml:space="preserve">3.55051231384277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81471920013428</t>
+    <t xml:space="preserve">3.81471943855286</t>
   </si>
   <si>
     <t xml:space="preserve">3.76404929161072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82919645309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83643555641174</t>
+    <t xml:space="preserve">3.82919597625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83643531799316</t>
   </si>
   <si>
     <t xml:space="preserve">3.85815119743347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74233436584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75681114196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70614171028137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6771867275238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63375544548035</t>
+    <t xml:space="preserve">3.74233388900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75681090354919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70614099502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67718648910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63375616073608</t>
   </si>
   <si>
     <t xml:space="preserve">3.66994833946228</t>
@@ -1469,49 +1469,49 @@
     <t xml:space="preserve">3.61927843093872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64099407196045</t>
+    <t xml:space="preserve">3.64099454879761</t>
   </si>
   <si>
     <t xml:space="preserve">3.77128839492798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80024242401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6627094745636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72785687446594</t>
+    <t xml:space="preserve">3.80024266242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66271018981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72785711288452</t>
   </si>
   <si>
     <t xml:space="preserve">3.865389585495</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60480165481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58670496940613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57584714889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54327368736267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547132492065</t>
+    <t xml:space="preserve">3.60480117797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58670520782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57584667205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54327392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547180175781</t>
   </si>
   <si>
     <t xml:space="preserve">3.82195806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71337962150574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69890284538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69166398048401</t>
+    <t xml:space="preserve">3.71337914466858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69890308380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69166374206543</t>
   </si>
   <si>
     <t xml:space="preserve">3.6265172958374</t>
@@ -1520,19 +1520,19 @@
     <t xml:space="preserve">3.64823293685913</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52517747879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60118222236633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54689288139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5034613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60842061042786</t>
+    <t xml:space="preserve">3.5251772403717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60118198394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54689311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50346207618713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60842037200928</t>
   </si>
   <si>
     <t xml:space="preserve">3.79300379753113</t>
@@ -1541,31 +1541,31 @@
     <t xml:space="preserve">3.88710522651672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56498908996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59394359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77852654457092</t>
+    <t xml:space="preserve">3.56498980522156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59394383430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77852725982666</t>
   </si>
   <si>
     <t xml:space="preserve">3.58308553695679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53965449333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48174619674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49622368812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.452791929245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4202184677124</t>
+    <t xml:space="preserve">3.53965425491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48174595832825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49622344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45279169082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42021775245667</t>
   </si>
   <si>
     <t xml:space="preserve">3.43155574798584</t>
@@ -1577,28 +1577,28 @@
     <t xml:space="preserve">3.41265988349915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3332953453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841227531433</t>
+    <t xml:space="preserve">3.33329558372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841251373291</t>
   </si>
   <si>
     <t xml:space="preserve">3.38620519638062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3710880279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36352944374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3824257850647</t>
+    <t xml:space="preserve">3.37108826637268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.363529920578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38242554664612</t>
   </si>
   <si>
     <t xml:space="preserve">3.31062030792236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32573699951172</t>
+    <t xml:space="preserve">3.3257372379303</t>
   </si>
   <si>
     <t xml:space="preserve">3.29172372817993</t>
@@ -1610,16 +1610,16 @@
     <t xml:space="preserve">3.3143994808197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33707499504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27660703659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28038620948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23503541946411</t>
+    <t xml:space="preserve">3.33707475662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.276606798172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28038644790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23503518104553</t>
   </si>
   <si>
     <t xml:space="preserve">3.20480108261108</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">3.21235966682434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24259376525879</t>
+    <t xml:space="preserve">3.24259352684021</t>
   </si>
   <si>
     <t xml:space="preserve">3.18212580680847</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">3.15189170837402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18968391418457</t>
+    <t xml:space="preserve">3.18968439102173</t>
   </si>
   <si>
     <t xml:space="preserve">3.20102190971375</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">3.25015211105347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39376306533813</t>
+    <t xml:space="preserve">3.39376330375671</t>
   </si>
   <si>
     <t xml:space="preserve">3.59784317016602</t>
@@ -1664,31 +1664,31 @@
     <t xml:space="preserve">3.65831065177917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55627131462097</t>
+    <t xml:space="preserve">3.55627107620239</t>
   </si>
   <si>
     <t xml:space="preserve">3.5524914264679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56760835647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57516717910767</t>
+    <t xml:space="preserve">3.56760883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57516765594482</t>
   </si>
   <si>
     <t xml:space="preserve">3.60540151596069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53359580039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47690725326538</t>
+    <t xml:space="preserve">3.53359603881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47690677642822</t>
   </si>
   <si>
     <t xml:space="preserve">3.59028458595276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58272552490234</t>
+    <t xml:space="preserve">3.5827260017395</t>
   </si>
   <si>
     <t xml:space="preserve">3.57138824462891</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">3.52603697776794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50336170196533</t>
+    <t xml:space="preserve">3.50336194038391</t>
   </si>
   <si>
     <t xml:space="preserve">3.43911457061768</t>
@@ -1709,25 +1709,25 @@
     <t xml:space="preserve">3.42021822929382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40132212638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36730885505676</t>
+    <t xml:space="preserve">3.40132236480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36730861663818</t>
   </si>
   <si>
     <t xml:space="preserve">3.40888071060181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34085392951965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42399740219116</t>
+    <t xml:space="preserve">3.34085416793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42399764060974</t>
   </si>
   <si>
     <t xml:space="preserve">3.51469945907593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49958276748657</t>
+    <t xml:space="preserve">3.49958252906799</t>
   </si>
   <si>
     <t xml:space="preserve">3.54871249198914</t>
@@ -1739,94 +1739,94 @@
     <t xml:space="preserve">3.65453124046326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68098640441895</t>
+    <t xml:space="preserve">3.68098616600037</t>
   </si>
   <si>
     <t xml:space="preserve">3.67342782020569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73011636734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78680515289307</t>
+    <t xml:space="preserve">3.73011708259583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78680491447449</t>
   </si>
   <si>
     <t xml:space="preserve">3.92285823822021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86239004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7452335357666</t>
+    <t xml:space="preserve">3.86239051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74523329734802</t>
   </si>
   <si>
     <t xml:space="preserve">3.76790928840637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83971476554871</t>
+    <t xml:space="preserve">3.83971524238586</t>
   </si>
   <si>
     <t xml:space="preserve">3.83215641975403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77168798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73767495155334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69232392311096</t>
+    <t xml:space="preserve">3.77168774604797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73767518997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69232439994812</t>
   </si>
   <si>
     <t xml:space="preserve">3.70366191864014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77924656867981</t>
+    <t xml:space="preserve">3.77924633026123</t>
   </si>
   <si>
     <t xml:space="preserve">3.6885449886322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66586995124817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69610333442688</t>
+    <t xml:space="preserve">3.66586971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6961030960083</t>
   </si>
   <si>
     <t xml:space="preserve">3.66964840888977</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73389530181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81703901290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84727334976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90018248558044</t>
+    <t xml:space="preserve">3.73389554023743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81703948974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84727382659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9001829624176</t>
   </si>
   <si>
     <t xml:space="preserve">3.98332571983337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9606499671936</t>
+    <t xml:space="preserve">3.96065044403076</t>
   </si>
   <si>
     <t xml:space="preserve">3.95309209823608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93041610717773</t>
+    <t xml:space="preserve">3.93041658401489</t>
   </si>
   <si>
     <t xml:space="preserve">3.94553327560425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99088501930237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91529965400696</t>
+    <t xml:space="preserve">3.99088454246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91530013084412</t>
   </si>
   <si>
     <t xml:space="preserve">4.0211181640625</t>
@@ -1835,19 +1835,19 @@
     <t xml:space="preserve">4.09670400619507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03623580932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06646919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08158683776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13449573516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05135250091553</t>
+    <t xml:space="preserve">4.03623533248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06646966934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08158731460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1344952583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05135202407837</t>
   </si>
   <si>
     <t xml:space="preserve">4.02867698669434</t>
@@ -1859,16 +1859,16 @@
     <t xml:space="preserve">4.04379367828369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1193790435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01356029510498</t>
+    <t xml:space="preserve">4.11937856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01355981826782</t>
   </si>
   <si>
     <t xml:space="preserve">3.96820902824402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93797540664673</t>
+    <t xml:space="preserve">3.93797492980957</t>
   </si>
   <si>
     <t xml:space="preserve">3.97576785087585</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">3.89262413978577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88506579399109</t>
+    <t xml:space="preserve">3.88506627082825</t>
   </si>
   <si>
     <t xml:space="preserve">3.87750720977783</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">3.59406352043152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60162210464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65075278282166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877861022949</t>
+    <t xml:space="preserve">3.6016218662262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65075254440308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877813339233</t>
   </si>
   <si>
     <t xml:space="preserve">3.99844288825989</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">3.72255802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63185596466064</t>
+    <t xml:space="preserve">3.63185572624207</t>
   </si>
   <si>
     <t xml:space="preserve">3.46556949615479</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">3.28416538238525</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11032009124756</t>
+    <t xml:space="preserve">3.11031985282898</t>
   </si>
   <si>
     <t xml:space="preserve">3.06496906280518</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">2.70971989631653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93269538879395</t>
+    <t xml:space="preserve">2.93269562721252</t>
   </si>
   <si>
     <t xml:space="preserve">3.00450110435486</t>
@@ -1952,28 +1952,28 @@
     <t xml:space="preserve">2.94403314590454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91001963615417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96292972564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85333156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89490294456482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88734436035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92135787010193</t>
+    <t xml:space="preserve">2.91001987457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96292948722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85333132743835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8949031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88734483718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92135763168335</t>
   </si>
   <si>
     <t xml:space="preserve">2.85711026191711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90246105194092</t>
+    <t xml:space="preserve">2.90246152877808</t>
   </si>
   <si>
     <t xml:space="preserve">2.82687664031982</t>
@@ -1985,22 +1985,22 @@
     <t xml:space="preserve">2.9969425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9515917301178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97804641723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99316358566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05363154411316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03473472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02717661857605</t>
+    <t xml:space="preserve">2.95159149169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97804665565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99316334724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05363130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03473520278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02717685699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.12165760993958</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">3.09898209571838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16700863838196</t>
+    <t xml:space="preserve">3.16700887680054</t>
   </si>
   <si>
     <t xml:space="preserve">3.14433312416077</t>
@@ -2021,31 +2021,31 @@
     <t xml:space="preserve">3.19346356391907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2199182510376</t>
+    <t xml:space="preserve">3.21991801261902</t>
   </si>
   <si>
     <t xml:space="preserve">3.26904845237732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32195782661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15944981575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07252740859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06874799728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10654091835022</t>
+    <t xml:space="preserve">3.32195806503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1594500541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07252764701843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06874823570251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10654067993164</t>
   </si>
   <si>
     <t xml:space="preserve">3.16322946548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27282738685608</t>
+    <t xml:space="preserve">3.27282762527466</t>
   </si>
   <si>
     <t xml:space="preserve">3.28794455528259</t>
@@ -2054,13 +2054,13 @@
     <t xml:space="preserve">3.40510129928589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51092004776001</t>
+    <t xml:space="preserve">3.51092028617859</t>
   </si>
   <si>
     <t xml:space="preserve">3.48824453353882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45801019668579</t>
+    <t xml:space="preserve">3.45801067352295</t>
   </si>
   <si>
     <t xml:space="preserve">3.29550337791443</t>
@@ -2069,55 +2069,55 @@
     <t xml:space="preserve">3.34463334083557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29928207397461</t>
+    <t xml:space="preserve">3.29928183555603</t>
   </si>
   <si>
     <t xml:space="preserve">3.30684089660645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30306124687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26148962974548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3786461353302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3748676776886</t>
+    <t xml:space="preserve">3.30306148529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26148986816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37864637374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37486720085144</t>
   </si>
   <si>
     <t xml:space="preserve">3.26526927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48068618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38998436927795</t>
+    <t xml:space="preserve">3.39754271507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48068642616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38998413085938</t>
   </si>
   <si>
     <t xml:space="preserve">3.31817865371704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25771069526672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22747707366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18590521812439</t>
+    <t xml:space="preserve">3.25771045684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22747683525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18590497970581</t>
   </si>
   <si>
     <t xml:space="preserve">3.24637269973755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17456698417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14055418968201</t>
+    <t xml:space="preserve">3.17456722259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14055442810059</t>
   </si>
   <si>
     <t xml:space="preserve">3.17834639549255</t>
@@ -2132,22 +2132,22 @@
     <t xml:space="preserve">3.0460729598999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01583909988403</t>
+    <t xml:space="preserve">3.01583886146545</t>
   </si>
   <si>
     <t xml:space="preserve">2.9402539730072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95537090301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92513680458069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8835654258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80042147636414</t>
+    <t xml:space="preserve">2.95537066459656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92513704299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88356518745422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80042171478271</t>
   </si>
   <si>
     <t xml:space="preserve">2.7890841960907</t>
@@ -2162,16 +2162,16 @@
     <t xml:space="preserve">2.71727848052979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72105765342712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67948579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55477046966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44895219802856</t>
+    <t xml:space="preserve">2.72105741500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67948603630066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55477070808411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44895195960999</t>
   </si>
   <si>
     <t xml:space="preserve">2.55099153518677</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">2.69838237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98938369750977</t>
+    <t xml:space="preserve">2.98938393592834</t>
   </si>
   <si>
     <t xml:space="preserve">3.53737449645996</t>
@@ -2192,46 +2192,46 @@
     <t xml:space="preserve">3.62807679176331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63563561439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57894659042358</t>
+    <t xml:space="preserve">3.63563537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.578946352005</t>
   </si>
   <si>
     <t xml:space="preserve">3.56382942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50714135169983</t>
+    <t xml:space="preserve">3.50714087486267</t>
   </si>
   <si>
     <t xml:space="preserve">3.48446559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52225780487061</t>
+    <t xml:space="preserve">3.52225732803345</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643929481506</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12543725967407</t>
+    <t xml:space="preserve">3.12543702125549</t>
   </si>
   <si>
     <t xml:space="preserve">3.80948090553284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76035070419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64319372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68476533889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74901294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7943639755249</t>
+    <t xml:space="preserve">3.76035022735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64319396018982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68476557731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74901247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79436326026917</t>
   </si>
   <si>
     <t xml:space="preserve">3.75657105445862</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">4.15717124938965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11182069778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17228889465332</t>
+    <t xml:space="preserve">4.11182117462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17228841781616</t>
   </si>
   <si>
     <t xml:space="preserve">4.3134560585022</t>
@@ -2261,43 +2261,43 @@
     <t xml:space="preserve">4.1252326965332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07817602157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08601951599121</t>
+    <t xml:space="preserve">4.07817649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08601903915405</t>
   </si>
   <si>
     <t xml:space="preserve">4.09386157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20365905761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26640033721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27424287796021</t>
+    <t xml:space="preserve">4.20365858078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2664008140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27424240112305</t>
   </si>
   <si>
     <t xml:space="preserve">4.25855731964111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36835479736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32914161682129</t>
+    <t xml:space="preserve">4.36835432052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32914113998413</t>
   </si>
   <si>
     <t xml:space="preserve">4.34482669830322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35266971588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30561351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28992795944214</t>
+    <t xml:space="preserve">4.35266923904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30561304092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28992748260498</t>
   </si>
   <si>
     <t xml:space="preserve">4.28208541870117</t>
@@ -2315,25 +2315,25 @@
     <t xml:space="preserve">3.99975037574768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00759267807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96053671836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03112077713013</t>
+    <t xml:space="preserve">4.00759315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96053719520569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03112125396729</t>
   </si>
   <si>
     <t xml:space="preserve">4.05464839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93700909614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92132353782654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01543569564819</t>
+    <t xml:space="preserve">3.93700838088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92132329940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01543521881104</t>
   </si>
   <si>
     <t xml:space="preserve">4.07033395767212</t>
@@ -2342,418 +2342,418 @@
     <t xml:space="preserve">3.9762225151062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18797397613525</t>
+    <t xml:space="preserve">4.1879734992981</t>
   </si>
   <si>
     <t xml:space="preserve">4.24287176132202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21150207519531</t>
+    <t xml:space="preserve">4.21150159835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39188194274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45462369918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43109560012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42325305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38403987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39972496032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33698415756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36051177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46246671676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44678068161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43893814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47815179824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4859938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50167942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56442070007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60363388061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62716197967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6350040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49383687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59579086303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66637468338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68205976486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72911643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64284706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74480199813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8624415397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90949726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05850696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03497982025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99576616287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95655298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9487099647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97223854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87028360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98008108139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07419204711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05066537857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02713680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08987760543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19183254241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18398952484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10556364059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14477634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23888874053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21536016464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1996750831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25457382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30162954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01929473876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93302536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7996997833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76048707962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76832962036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68990278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69774532318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61147689819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53305006027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50952243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47030925750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55657815933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54873561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57226371765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52520799636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54089307785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51736497879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58010578155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82322835922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87812662124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8859691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7840142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558786392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65853261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77617263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85459852218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94086790084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52122354507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66239070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73297500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89767074584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68591928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70160436630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59965038299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5369086265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906703948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17614698410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29378700256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7134313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41541051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89381170272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81538534164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9251823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84675645828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72127342224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5879487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61931943893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77163219451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.738609790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69733238220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63954496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79639768600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98627233505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95325088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07708168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11835956573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97801733016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06057119369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90371799468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96976184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87069654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82941961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62303447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40839338302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50745820999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56524658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58175754547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6478009223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61477947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57350158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51571369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3340950012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30932760238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38362693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16898632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2680516242981</t>
   </si>
   <si>
     <t xml:space="preserve">4.39188241958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45462322235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43109560012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42325258255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38403987884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39972543716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33698415756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36051177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46246671676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44678068161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43893814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47815179824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48599338531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50167942047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5644211769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60363435745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62716245651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63500356674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49383687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59579133987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66637468338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68205976486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72911596298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64284753799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74480152130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86244058609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90949678421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05850696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03497934341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99576616287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95655298233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94871044158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97223854064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87028408050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98008108139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07419204711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05066442489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02713680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08987808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19183254241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18399000167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10556364059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14477682113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23888778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21536064147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1996750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25457334518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30162906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01929426193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93302536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7996997833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7604866027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76832962036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68990325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69774532318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6114764213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53305006027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50952243804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47030830383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55657815933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54873561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57226324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52520799636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54089260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51736450195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58010625839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82322835922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87812662124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8859691619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78401470184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70558834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65853261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77617216110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85459899902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94086790084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52122354507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6623911857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73297548294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89767122268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68591928482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70160436630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59965038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5369086265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906656265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1761474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29378700256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7134313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4154109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89381122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81538534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9251823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84675550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72127389907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5879487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61931896209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77163171768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.738609790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69733333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63954496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7963981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98627281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95325088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312553405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07708168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11835908889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97801733016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06057167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9037184715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96976137161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87069702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82941961288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62303400039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40839385986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50745868682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56524658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48269176483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58175754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64780044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61477899551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5735011100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51571369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33409452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30932807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38362693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16898679733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26805114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39188289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4661808013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42490386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37537145614624</t>
+    <t xml:space="preserve">4.46618127822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42490482330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3753719329834</t>
   </si>
   <si>
     <t xml:space="preserve">4.27630662918091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44966983795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34235048294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41664886474609</t>
+    <t xml:space="preserve">4.44967031478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34235000610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41664838790894</t>
   </si>
   <si>
     <t xml:space="preserve">4.55699062347412</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">4.77988719940186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73035430908203</t>
+    <t xml:space="preserve">4.73035478591919</t>
   </si>
   <si>
     <t xml:space="preserve">4.82116460800171</t>
@@ -2798,25 +2798,25 @@
     <t xml:space="preserve">4.94499540328979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83767461776733</t>
+    <t xml:space="preserve">4.83767509460449</t>
   </si>
   <si>
     <t xml:space="preserve">4.78814268112183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87895202636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60652351379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66431093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81290864944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88720798492432</t>
+    <t xml:space="preserve">4.87895154953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60652303695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66431188583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81290912628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88720703125</t>
   </si>
   <si>
     <t xml:space="preserve">4.93673992156982</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">5.11010408401489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16789150238037</t>
+    <t xml:space="preserve">5.16789197921753</t>
   </si>
   <si>
     <t xml:space="preserve">5.23393535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19265842437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22567939758301</t>
+    <t xml:space="preserve">5.19265794754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22567987442017</t>
   </si>
   <si>
     <t xml:space="preserve">5.26695680618286</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27521228790283</t>
+    <t xml:space="preserve">5.27521181106567</t>
   </si>
   <si>
     <t xml:space="preserve">5.29172277450562</t>
@@ -2852,43 +2852,43 @@
     <t xml:space="preserve">5.30823373794556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36602163314819</t>
+    <t xml:space="preserve">5.36602210998535</t>
   </si>
   <si>
     <t xml:space="preserve">5.43206548690796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47334241867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55589628219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41555404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48985290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46508646011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57240772247314</t>
+    <t xml:space="preserve">5.4733419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5558967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41555452346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4898533821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46508693695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57240724563599</t>
   </si>
   <si>
     <t xml:space="preserve">5.44857597351074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49810886383057</t>
+    <t xml:space="preserve">5.49810838699341</t>
   </si>
   <si>
     <t xml:space="preserve">5.52287483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51461887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58891820907593</t>
+    <t xml:space="preserve">5.51461935043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58891868591309</t>
   </si>
   <si>
     <t xml:space="preserve">5.45683145523071</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">5.61368465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5971736907959</t>
+    <t xml:space="preserve">5.59717416763306</t>
   </si>
   <si>
     <t xml:space="preserve">5.58066272735596</t>
@@ -2921,10 +2921,10 @@
     <t xml:space="preserve">5.82006978988647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84483623504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86134672164917</t>
+    <t xml:space="preserve">5.84483575820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86134624481201</t>
   </si>
   <si>
     <t xml:space="preserve">5.89436864852905</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">5.8118143081665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90262413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80355930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73751592636108</t>
+    <t xml:space="preserve">5.90262460708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80355978012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73751544952393</t>
   </si>
   <si>
     <t xml:space="preserve">6.00168943405151</t>
@@ -2948,22 +2948,22 @@
     <t xml:space="preserve">6.30713939666748</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38969373703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39794921875</t>
+    <t xml:space="preserve">6.38969421386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39794874191284</t>
   </si>
   <si>
     <t xml:space="preserve">6.47224807739258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43922662734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45573711395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59607887268066</t>
+    <t xml:space="preserve">6.4392261505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45573663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59607839584351</t>
   </si>
   <si>
     <t xml:space="preserve">6.52178049087524</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">6.51352500915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5630578994751</t>
+    <t xml:space="preserve">6.56305742263794</t>
   </si>
   <si>
     <t xml:space="preserve">6.67863368988037</t>
@@ -2999,13 +2999,13 @@
     <t xml:space="preserve">6.73642110824585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68688917160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53829097747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62084531784058</t>
+    <t xml:space="preserve">6.6868896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53829145431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62084579467773</t>
   </si>
   <si>
     <t xml:space="preserve">6.64561128616333</t>
@@ -3017,13 +3017,13 @@
     <t xml:space="preserve">6.74467658996582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75293207168579</t>
+    <t xml:space="preserve">6.75293254852295</t>
   </si>
   <si>
     <t xml:space="preserve">6.78595399856567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96866750717163</t>
+    <t xml:space="preserve">5.96866703033447</t>
   </si>
   <si>
     <t xml:space="preserve">6.05122137069702</t>
@@ -3032,34 +3032,34 @@
     <t xml:space="preserve">5.64670610427856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8530912399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67972803115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39904356002808</t>
+    <t xml:space="preserve">5.85309171676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67972755432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39904403686523</t>
   </si>
   <si>
     <t xml:space="preserve">5.38253259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66321706771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60542917251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7457709312439</t>
+    <t xml:space="preserve">5.66321659088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60542964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74577140808105</t>
   </si>
   <si>
     <t xml:space="preserve">5.83658075332642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88611316680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79530334472656</t>
+    <t xml:space="preserve">5.88611364364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79530382156372</t>
   </si>
   <si>
     <t xml:space="preserve">5.87785768508911</t>
@@ -3068,25 +3068,25 @@
     <t xml:space="preserve">5.9769229888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91087961196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91913461685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63845062255859</t>
+    <t xml:space="preserve">5.91087913513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91913509368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63845014572144</t>
   </si>
   <si>
     <t xml:space="preserve">5.78704881668091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94390058517456</t>
+    <t xml:space="preserve">5.94390106201172</t>
   </si>
   <si>
     <t xml:space="preserve">5.9604115486145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8696026802063</t>
+    <t xml:space="preserve">5.86960220336914</t>
   </si>
   <si>
     <t xml:space="preserve">5.98917293548584</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">5.79011058807373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78145551681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57373857498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67759704589844</t>
+    <t xml:space="preserve">5.78145599365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57373905181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6775975227356</t>
   </si>
   <si>
     <t xml:space="preserve">5.76414585113525</t>
@@ -3131,76 +3131,76 @@
     <t xml:space="preserve">5.82472991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80742073059082</t>
+    <t xml:space="preserve">5.80742025375366</t>
   </si>
   <si>
     <t xml:space="preserve">5.86800479888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88531398773193</t>
+    <t xml:space="preserve">5.88531446456909</t>
   </si>
   <si>
     <t xml:space="preserve">5.87665939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9285888671875</t>
+    <t xml:space="preserve">5.92858839035034</t>
   </si>
   <si>
     <t xml:space="preserve">5.96320819854736</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94589805603027</t>
+    <t xml:space="preserve">5.94589853286743</t>
   </si>
   <si>
     <t xml:space="preserve">5.91993379592896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15361547470093</t>
+    <t xml:space="preserve">6.15361499786377</t>
   </si>
   <si>
     <t xml:space="preserve">6.22285461425781</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17092561721802</t>
+    <t xml:space="preserve">6.17092514038086</t>
   </si>
   <si>
     <t xml:space="preserve">6.28343868255615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25747394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24881839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24016427993774</t>
+    <t xml:space="preserve">6.25747346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24881887435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24016380310059</t>
   </si>
   <si>
     <t xml:space="preserve">6.2315092086792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2661280632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46519041061401</t>
+    <t xml:space="preserve">6.26612901687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46519088745117</t>
   </si>
   <si>
     <t xml:space="preserve">6.54308462142944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58635950088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56904935836792</t>
+    <t xml:space="preserve">6.58635902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56904983520508</t>
   </si>
   <si>
     <t xml:space="preserve">6.6382884979248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56039428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57770395278931</t>
+    <t xml:space="preserve">6.56039381027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57770442962646</t>
   </si>
   <si>
     <t xml:space="preserve">6.62097835540771</t>
@@ -3215,19 +3215,19 @@
     <t xml:space="preserve">6.73349189758301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64694309234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50846481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66425275802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11034107208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30940294265747</t>
+    <t xml:space="preserve">6.64694261550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50846529006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66425228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11034059524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30940341949463</t>
   </si>
   <si>
     <t xml:space="preserve">6.37864208221436</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">6.49115562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49981069564819</t>
+    <t xml:space="preserve">6.49981021881104</t>
   </si>
   <si>
     <t xml:space="preserve">6.55173969268799</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">6.70752716064453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68156242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60366916656494</t>
+    <t xml:space="preserve">6.68156290054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60366868972778</t>
   </si>
   <si>
     <t xml:space="preserve">6.51712036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6296329498291</t>
+    <t xml:space="preserve">6.62963342666626</t>
   </si>
   <si>
     <t xml:space="preserve">6.74214696884155</t>
@@ -3272,28 +3272,28 @@
     <t xml:space="preserve">6.79407596588135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85466051101685</t>
+    <t xml:space="preserve">6.85466003417969</t>
   </si>
   <si>
     <t xml:space="preserve">6.61232376098633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7854208946228</t>
+    <t xml:space="preserve">6.78542137145996</t>
   </si>
   <si>
     <t xml:space="preserve">6.77676630020142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7508020401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52577447891235</t>
+    <t xml:space="preserve">6.75080156326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52577495574951</t>
   </si>
   <si>
     <t xml:space="preserve">6.42191648483276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45653629302979</t>
+    <t xml:space="preserve">6.45653581619263</t>
   </si>
   <si>
     <t xml:space="preserve">6.71618270874023</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">6.92389917373657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01044845581055</t>
+    <t xml:space="preserve">7.01044797897339</t>
   </si>
   <si>
     <t xml:space="preserve">7.05372142791748</t>
@@ -3323,16 +3323,16 @@
     <t xml:space="preserve">6.9931378364563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00179290771484</t>
+    <t xml:space="preserve">7.001793384552</t>
   </si>
   <si>
     <t xml:space="preserve">7.02775764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97582912445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95851898193359</t>
+    <t xml:space="preserve">6.97582864761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95851850509644</t>
   </si>
   <si>
     <t xml:space="preserve">6.94986343383789</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">7.07103204727173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06237745285034</t>
+    <t xml:space="preserve">7.06237697601318</t>
   </si>
   <si>
     <t xml:space="preserve">7.11430644989014</t>
@@ -3356,28 +3356,28 @@
     <t xml:space="preserve">7.04506778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13161563873291</t>
+    <t xml:space="preserve">7.13161611557007</t>
   </si>
   <si>
     <t xml:space="preserve">7.18354558944702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1575813293457</t>
+    <t xml:space="preserve">7.15758085250854</t>
   </si>
   <si>
     <t xml:space="preserve">7.07968711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88927936553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86331510543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93255376815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91524457931519</t>
+    <t xml:space="preserve">6.88927984237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86331462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93255424499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91524410247803</t>
   </si>
   <si>
     <t xml:space="preserve">6.94120931625366</t>
@@ -3386,13 +3386,13 @@
     <t xml:space="preserve">6.96717357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17489051818848</t>
+    <t xml:space="preserve">7.17489004135132</t>
   </si>
   <si>
     <t xml:space="preserve">7.27009391784668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20085477828979</t>
+    <t xml:space="preserve">7.20085430145264</t>
   </si>
   <si>
     <t xml:space="preserve">7.22681999206543</t>
@@ -3401,13 +3401,13 @@
     <t xml:space="preserve">7.16623544692993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0883412361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14027118682861</t>
+    <t xml:space="preserve">7.14892625808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08834171295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14027070999146</t>
   </si>
   <si>
     <t xml:space="preserve">7.26143932342529</t>
@@ -3416,31 +3416,31 @@
     <t xml:space="preserve">7.31336784362793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33933305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42588186264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44319248199463</t>
+    <t xml:space="preserve">7.33933258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42588138580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44319200515747</t>
   </si>
   <si>
     <t xml:space="preserve">7.48646545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23547410964966</t>
+    <t xml:space="preserve">7.23547458648682</t>
   </si>
   <si>
     <t xml:space="preserve">7.29605865478516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19220066070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45184564590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38260793685913</t>
+    <t xml:space="preserve">7.19220113754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4518461227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38260746002197</t>
   </si>
   <si>
     <t xml:space="preserve">7.3566427230835</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">7.52108478546143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84997034072876</t>
+    <t xml:space="preserve">7.84997081756592</t>
   </si>
   <si>
     <t xml:space="preserve">7.72880268096924</t>
@@ -3458,40 +3458,40 @@
     <t xml:space="preserve">7.76342248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53839540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55570411682129</t>
+    <t xml:space="preserve">7.53839588165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55570507049561</t>
   </si>
   <si>
     <t xml:space="preserve">7.46050119400024</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40857267379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63359880447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72014760971069</t>
+    <t xml:space="preserve">7.40857219696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63359785079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72014713287354</t>
   </si>
   <si>
     <t xml:space="preserve">7.88458967208862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77207660675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65090847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66821813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78073072433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83266162872314</t>
+    <t xml:space="preserve">7.77207612991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65090894699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6682186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78073120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83266115188599</t>
   </si>
   <si>
     <t xml:space="preserve">7.82400560379028</t>
@@ -3500,16 +3500,16 @@
     <t xml:space="preserve">7.75476741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7028374671936</t>
+    <t xml:space="preserve">7.70283794403076</t>
   </si>
   <si>
     <t xml:space="preserve">7.69418334960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67687320709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94517374038696</t>
+    <t xml:space="preserve">7.67687273025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94517469406128</t>
   </si>
   <si>
     <t xml:space="preserve">8.01441287994385</t>
@@ -3518,10 +3518,10 @@
     <t xml:space="preserve">8.11827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05768775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12692737579346</t>
+    <t xml:space="preserve">8.05768871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12692642211914</t>
   </si>
   <si>
     <t xml:space="preserve">8.0663423538208</t>
@@ -3533,13 +3533,13 @@
     <t xml:space="preserve">8.10961627960205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17885494232178</t>
+    <t xml:space="preserve">8.17885589599609</t>
   </si>
   <si>
     <t xml:space="preserve">8.17020034790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20481967926025</t>
+    <t xml:space="preserve">8.20482063293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.07499694824219</t>
@@ -3551,13 +3551,13 @@
     <t xml:space="preserve">8.00575828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99710369110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87593555450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30867862701416</t>
+    <t xml:space="preserve">7.99710321426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87593650817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30867958068848</t>
   </si>
   <si>
     <t xml:space="preserve">8.24809455871582</t>
@@ -3566,13 +3566,13 @@
     <t xml:space="preserve">8.27406024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41253757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.576979637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5856351852417</t>
+    <t xml:space="preserve">8.41253662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57698059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58563423156738</t>
   </si>
   <si>
     <t xml:space="preserve">8.65487384796143</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">8.54236030578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62025451660156</t>
+    <t xml:space="preserve">8.62025356292725</t>
   </si>
   <si>
     <t xml:space="preserve">8.81066226959229</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">8.70680332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87990188598633</t>
+    <t xml:space="preserve">8.87990093231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.834641456604</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">8.93421173095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86179637908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.753173828125</t>
+    <t xml:space="preserve">8.86179733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75317478179932</t>
   </si>
   <si>
     <t xml:space="preserve">8.72601890563965</t>
@@ -3626,22 +3626,22 @@
     <t xml:space="preserve">8.80748558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85274410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77127742767334</t>
+    <t xml:space="preserve">8.85274505615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77127838134766</t>
   </si>
   <si>
     <t xml:space="preserve">8.68981170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69886302947998</t>
+    <t xml:space="preserve">8.69886207580566</t>
   </si>
   <si>
     <t xml:space="preserve">8.73507022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59929275512695</t>
+    <t xml:space="preserve">8.59929180145264</t>
   </si>
   <si>
     <t xml:space="preserve">8.56308460235596</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">8.08333492279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27342414855957</t>
+    <t xml:space="preserve">8.27342510223389</t>
   </si>
   <si>
     <t xml:space="preserve">8.42730712890625</t>
@@ -3680,10 +3680,10 @@
     <t xml:space="preserve">8.4906702041626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40015125274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58118724822998</t>
+    <t xml:space="preserve">8.40015029907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5811882019043</t>
   </si>
   <si>
     <t xml:space="preserve">8.40920257568359</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">8.41825485229492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60834503173828</t>
+    <t xml:space="preserve">8.60834407806396</t>
   </si>
   <si>
     <t xml:space="preserve">8.48161697387695</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">8.68075942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65360355377197</t>
+    <t xml:space="preserve">8.65360450744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.870849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02473068237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91610908508301</t>
+    <t xml:space="preserve">9.02473163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91610813140869</t>
   </si>
   <si>
     <t xml:space="preserve">8.98852348327637</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">9.08809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01567935943604</t>
+    <t xml:space="preserve">9.01567840576172</t>
   </si>
   <si>
     <t xml:space="preserve">9.04283428192139</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">9.16050910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79843425750732</t>
+    <t xml:space="preserve">8.79843330383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.36394309997559</t>
@@ -3749,16 +3749,16 @@
     <t xml:space="preserve">8.29152774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23721694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26437282562256</t>
+    <t xml:space="preserve">8.23721790313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26437187194824</t>
   </si>
   <si>
     <t xml:space="preserve">8.47256565093994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97947216033936</t>
+    <t xml:space="preserve">8.97947120666504</t>
   </si>
   <si>
     <t xml:space="preserve">8.89800453186035</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">9.14240550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34154605865479</t>
+    <t xml:space="preserve">9.3415470123291</t>
   </si>
   <si>
     <t xml:space="preserve">9.28723621368408</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">9.19671630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2510290145874</t>
+    <t xml:space="preserve">9.25102806091309</t>
   </si>
   <si>
     <t xml:space="preserve">9.12430191040039</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">9.21482086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35965156555176</t>
+    <t xml:space="preserve">9.35965061187744</t>
   </si>
   <si>
     <t xml:space="preserve">9.17861366271973</t>
@@ -3815,10 +3815,10 @@
     <t xml:space="preserve">9.10619831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30533885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50448036193848</t>
+    <t xml:space="preserve">9.30533981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50448131561279</t>
   </si>
   <si>
     <t xml:space="preserve">9.65504741668701</t>
@@ -3896,9 +3896,6 @@
     <t xml:space="preserve">9.5797643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50448131561279</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.46683979034424</t>
   </si>
   <si>
@@ -4326,6 +4323,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.1999998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.460000038147</t>
   </si>
 </sst>
 </file>
@@ -63624,7 +63624,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>1294</v>
+        <v>1268</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63650,7 +63650,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2269" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63676,7 +63676,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2270" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63702,7 +63702,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2271" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63728,7 +63728,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2272" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63780,7 +63780,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2274" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63910,7 +63910,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2279" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63936,7 +63936,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2280" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63962,7 +63962,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2281" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63988,7 +63988,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2282" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64014,7 +64014,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2283" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64040,7 +64040,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64092,7 +64092,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2286" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64144,7 +64144,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2288" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64170,7 +64170,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2289" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64196,7 +64196,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2290" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64248,7 +64248,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2292" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64274,7 +64274,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2293" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64300,7 +64300,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2294" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64326,7 +64326,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2295" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64352,7 +64352,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2296" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64378,7 +64378,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2297" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64404,7 +64404,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2298" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64430,7 +64430,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2299" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64456,7 +64456,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2300" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64482,7 +64482,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2301" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64508,7 +64508,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2302" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64534,7 +64534,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2303" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64560,7 +64560,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2304" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64586,7 +64586,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2305" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64612,7 +64612,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2306" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64638,7 +64638,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64664,7 +64664,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2308" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64690,7 +64690,7 @@
         <v>11.5</v>
       </c>
       <c r="G2309" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64716,7 +64716,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2310" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64742,7 +64742,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2311" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64768,7 +64768,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2312" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64794,7 +64794,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2313" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64820,7 +64820,7 @@
         <v>11.5</v>
       </c>
       <c r="G2314" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64846,7 +64846,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2315" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64872,7 +64872,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2316" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64898,7 +64898,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2317" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64924,7 +64924,7 @@
         <v>12</v>
       </c>
       <c r="G2318" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64950,7 +64950,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2319" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64976,7 +64976,7 @@
         <v>12</v>
       </c>
       <c r="G2320" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -65002,7 +65002,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2321" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65028,7 +65028,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2322" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65054,7 +65054,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2323" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65080,7 +65080,7 @@
         <v>12</v>
       </c>
       <c r="G2324" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65106,7 +65106,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2325" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65132,7 +65132,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2326" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65158,7 +65158,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2327" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65184,7 +65184,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2328" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65210,7 +65210,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2329" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65236,7 +65236,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2330" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65262,7 +65262,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2331" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65288,7 +65288,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2332" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65314,7 +65314,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2333" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65340,7 +65340,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2334" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65366,7 +65366,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65392,7 +65392,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65418,7 +65418,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2337" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65444,7 +65444,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2338" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65470,7 +65470,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2339" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65496,7 +65496,7 @@
         <v>12.5</v>
       </c>
       <c r="G2340" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65522,7 +65522,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2341" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65548,7 +65548,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65574,7 +65574,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2343" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65600,7 +65600,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2344" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65626,7 +65626,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2345" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65652,7 +65652,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2346" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65678,7 +65678,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2347" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65704,7 +65704,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2348" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65730,7 +65730,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2349" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65756,7 +65756,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2350" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65782,7 +65782,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2351" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65808,7 +65808,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2352" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65834,7 +65834,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2353" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65860,7 +65860,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2354" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65886,7 +65886,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2355" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65912,7 +65912,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2356" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65938,7 +65938,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2357" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65964,7 +65964,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2358" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65990,7 +65990,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2359" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -66016,7 +66016,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2360" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66042,7 +66042,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2361" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66068,7 +66068,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2362" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66094,7 +66094,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2363" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66120,7 +66120,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2364" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66146,7 +66146,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2365" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66172,7 +66172,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2366" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66198,7 +66198,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2367" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66224,7 +66224,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G2368" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66250,7 +66250,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2369" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66276,7 +66276,7 @@
         <v>12</v>
       </c>
       <c r="G2370" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66302,7 +66302,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2371" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66328,7 +66328,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2372" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66354,7 +66354,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2373" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66380,7 +66380,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2374" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66406,7 +66406,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2375" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66432,7 +66432,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2376" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66458,7 +66458,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66484,7 +66484,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2378" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66510,7 +66510,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2379" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66536,7 +66536,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2380" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66562,7 +66562,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2381" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66588,7 +66588,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2382" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66614,7 +66614,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2383" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66640,7 +66640,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2384" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66666,7 +66666,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2385" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66692,7 +66692,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2386" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66718,7 +66718,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2387" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66744,7 +66744,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2388" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66770,7 +66770,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2389" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66796,7 +66796,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2390" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66822,7 +66822,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2391" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66848,7 +66848,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2392" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66874,7 +66874,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2393" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66900,7 +66900,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2394" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66926,7 +66926,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2395" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66952,7 +66952,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2396" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66978,7 +66978,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2397" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -67004,7 +67004,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2398" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67030,7 +67030,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2399" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67056,7 +67056,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2400" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67082,7 +67082,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2401" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67108,7 +67108,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2402" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67134,7 +67134,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67160,7 +67160,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67186,7 +67186,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2405" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67212,7 +67212,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2406" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67238,7 +67238,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67264,7 +67264,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2408" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67290,7 +67290,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67316,7 +67316,7 @@
         <v>12.5</v>
       </c>
       <c r="G2410" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67342,7 +67342,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2411" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67368,7 +67368,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67394,7 +67394,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2413" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67420,7 +67420,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2414" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67446,7 +67446,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2415" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67472,7 +67472,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67498,7 +67498,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2417" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67524,7 +67524,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2418" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67550,7 +67550,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67576,7 +67576,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2420" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67602,7 +67602,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2421" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67628,7 +67628,7 @@
         <v>13</v>
       </c>
       <c r="G2422" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67654,7 +67654,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67680,7 +67680,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G2424" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67706,7 +67706,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2425" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67732,7 +67732,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2426" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67758,7 +67758,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67784,7 +67784,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2428" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67810,7 +67810,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2429" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67836,7 +67836,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2430" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67862,7 +67862,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2431" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67888,7 +67888,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2432" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67914,7 +67914,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2433" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67940,7 +67940,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2434" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67966,7 +67966,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2435" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67992,7 +67992,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2436" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -68018,7 +68018,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2437" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68044,7 +68044,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2438" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68070,7 +68070,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2439" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68096,7 +68096,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2440" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68122,7 +68122,7 @@
         <v>13.5</v>
       </c>
       <c r="G2441" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68148,7 +68148,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2442" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68174,7 +68174,7 @@
         <v>13.5</v>
       </c>
       <c r="G2443" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68200,7 +68200,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2444" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68226,7 +68226,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68252,7 +68252,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2446" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68278,7 +68278,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2447" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68304,7 +68304,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2448" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68330,7 +68330,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2449" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68356,7 +68356,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2450" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68382,7 +68382,7 @@
         <v>14</v>
       </c>
       <c r="G2451" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68408,7 +68408,7 @@
         <v>14</v>
       </c>
       <c r="G2452" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68434,7 +68434,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2453" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68460,7 +68460,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2454" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68486,7 +68486,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2455" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68512,7 +68512,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2456" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68538,7 +68538,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2457" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68564,7 +68564,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2458" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68590,7 +68590,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G2459" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68616,7 +68616,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2460" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68642,7 +68642,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G2461" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68668,7 +68668,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2462" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68694,7 +68694,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G2463" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68720,7 +68720,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2464" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68746,7 +68746,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G2465" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68772,7 +68772,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2466" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68798,7 +68798,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2467" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68824,7 +68824,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68850,7 +68850,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2469" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68876,7 +68876,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68902,7 +68902,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68928,7 +68928,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2472" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68954,7 +68954,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2473" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68980,7 +68980,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2474" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -69006,7 +69006,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69032,7 +69032,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G2476" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69058,7 +69058,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69084,7 +69084,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69110,7 +69110,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69136,7 +69136,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2480" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69162,7 +69162,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2481" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69188,7 +69188,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69214,7 +69214,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2483" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69240,7 +69240,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2484" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69266,7 +69266,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2485" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69292,7 +69292,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2486" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69318,7 +69318,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G2487" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69344,7 +69344,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2488" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69370,7 +69370,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2489" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69396,7 +69396,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2490" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69422,7 +69422,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2491" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69448,7 +69448,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2492" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69474,7 +69474,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2493" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69500,7 +69500,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69526,7 +69526,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69552,7 +69552,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G2496" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69578,7 +69578,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2497" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69604,7 +69604,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2498" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69630,7 +69630,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2499" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69656,7 +69656,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2500" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69682,7 +69682,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2501" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69708,7 +69708,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2502" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69734,7 +69734,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G2503" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69760,7 +69760,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2504" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69786,7 +69786,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2505" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -69812,7 +69812,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2506" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -69838,7 +69838,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2507" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -69864,7 +69864,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G2508" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -69890,7 +69890,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2509" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -69916,7 +69916,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G2510" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -69942,7 +69942,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G2511" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -69968,7 +69968,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2512" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -69994,7 +69994,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2513" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -70020,7 +70020,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2514" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -70046,7 +70046,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G2515" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -70072,7 +70072,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2516" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -70080,7 +70080,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6911574074</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>211109</v>
@@ -70098,9 +70098,35 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2517" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6912962963</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>702759</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>14.460000038147</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>14.1999998092651</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>14.3800001144409</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>14.460000038147</v>
+      </c>
+      <c r="G2518" t="s">
         <v>1437</v>
       </c>
-      <c r="H2517" t="s">
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="1437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="1438">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49119567871094</t>
+    <t xml:space="preserve">4.49119520187378</t>
   </si>
   <si>
     <t xml:space="preserve">CE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52814531326294</t>
+    <t xml:space="preserve">4.52814483642578</t>
   </si>
   <si>
     <t xml:space="preserve">4.46432161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30644083023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26613140106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31315994262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3198766708374</t>
+    <t xml:space="preserve">4.30644035339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26613092422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31315898895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31987714767456</t>
   </si>
   <si>
     <t xml:space="preserve">4.36690521240234</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">4.27284908294678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23589849472046</t>
+    <t xml:space="preserve">4.23589897155762</t>
   </si>
   <si>
     <t xml:space="preserve">4.05114507675171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08473587036133</t>
+    <t xml:space="preserve">4.08473634719849</t>
   </si>
   <si>
     <t xml:space="preserve">3.74210214614868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91677856445312</t>
+    <t xml:space="preserve">3.91677904129028</t>
   </si>
   <si>
     <t xml:space="preserve">4.03099012374878</t>
@@ -89,79 +89,79 @@
     <t xml:space="preserve">4.15527868270874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12840509414673</t>
+    <t xml:space="preserve">4.12840461730957</t>
   </si>
   <si>
     <t xml:space="preserve">4.01419401168823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1250467300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12168645858765</t>
+    <t xml:space="preserve">4.12504577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1216869354248</t>
   </si>
   <si>
     <t xml:space="preserve">3.94701051712036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80256748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83615875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86975073814392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5808629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42970108985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75218081474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60773587226868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84959554672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670084953308</t>
+    <t xml:space="preserve">3.80256652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83615851402283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86975026130676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58086276054382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42970061302185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7521800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60773611068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84959530830383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670156478882</t>
   </si>
   <si>
     <t xml:space="preserve">3.96716642379761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06458139419556</t>
+    <t xml:space="preserve">4.06458234786987</t>
   </si>
   <si>
     <t xml:space="preserve">3.82944011688232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7723343372345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90334177017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87982892990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72866535186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79584932327271</t>
+    <t xml:space="preserve">3.77233457565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90334272384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87982773780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72866582870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79584884643555</t>
   </si>
   <si>
     <t xml:space="preserve">3.88318705558777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95708870887756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13176488876343</t>
+    <t xml:space="preserve">3.95708775520325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13176441192627</t>
   </si>
   <si>
     <t xml:space="preserve">4.1955885887146</t>
@@ -173,16 +173,16 @@
     <t xml:space="preserve">4.13848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22246217727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29972219467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35682821273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25605344772339</t>
+    <t xml:space="preserve">4.22246265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29972267150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35682916641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25605297088623</t>
   </si>
   <si>
     <t xml:space="preserve">4.27956771850586</t>
@@ -194,10 +194,10 @@
     <t xml:space="preserve">4.32659578323364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26949024200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16535568237305</t>
+    <t xml:space="preserve">4.26948976516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16535615921021</t>
   </si>
   <si>
     <t xml:space="preserve">4.09817314147949</t>
@@ -209,37 +209,37 @@
     <t xml:space="preserve">4.04106712341309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93021512031555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91006016731262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81936264038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75889849662781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71186995506287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93357396125793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82608151435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08137702941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15863752365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17879247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21238422393799</t>
+    <t xml:space="preserve">3.93021488189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91006064414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81936287879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75889825820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71187019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93357467651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82608103752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08137655258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15863800048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17879295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21238470077515</t>
   </si>
   <si>
     <t xml:space="preserve">4.21574354171753</t>
@@ -248,19 +248,19 @@
     <t xml:space="preserve">4.2829270362854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30308198928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35346984863281</t>
+    <t xml:space="preserve">4.30308151245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35346937179565</t>
   </si>
   <si>
     <t xml:space="preserve">4.19894790649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07465887069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08809614181519</t>
+    <t xml:space="preserve">4.07465934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08809566497803</t>
   </si>
   <si>
     <t xml:space="preserve">4.06122255325317</t>
@@ -269,46 +269,46 @@
     <t xml:space="preserve">4.02427196502686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93693423271179</t>
+    <t xml:space="preserve">3.93693351745605</t>
   </si>
   <si>
     <t xml:space="preserve">4.21648931503296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14420700073242</t>
+    <t xml:space="preserve">4.14420652389526</t>
   </si>
   <si>
     <t xml:space="preserve">4.19927930831909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25435209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23369979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23714208602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49185180664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49873638153076</t>
+    <t xml:space="preserve">4.25435161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23369932174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23714256286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49185228347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4987359046936</t>
   </si>
   <si>
     <t xml:space="preserve">4.47119951248169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45743227005005</t>
+    <t xml:space="preserve">4.45743179321289</t>
   </si>
   <si>
     <t xml:space="preserve">4.46431589126587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37826490402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31975030899048</t>
+    <t xml:space="preserve">4.37826538085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31975078582764</t>
   </si>
   <si>
     <t xml:space="preserve">4.37138080596924</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">4.28188800811768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42989587783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34040307998657</t>
+    <t xml:space="preserve">4.42989540100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34040260314941</t>
   </si>
   <si>
     <t xml:space="preserve">4.35072898864746</t>
@@ -332,40 +332,40 @@
     <t xml:space="preserve">4.03750371932983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91703319549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98243117332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884379386902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1373233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3369607925415</t>
+    <t xml:space="preserve">3.91703271865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98243069648743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884427070618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13732242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33696174621582</t>
   </si>
   <si>
     <t xml:space="preserve">4.38170671463013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42301225662231</t>
+    <t xml:space="preserve">4.42301177978516</t>
   </si>
   <si>
     <t xml:space="preserve">4.52971410751343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74148917198181</t>
+    <t xml:space="preserve">3.74148893356323</t>
   </si>
   <si>
     <t xml:space="preserve">3.7518150806427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7311635017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84130787849426</t>
+    <t xml:space="preserve">3.73116254806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84130859375</t>
   </si>
   <si>
     <t xml:space="preserve">3.65199565887451</t>
@@ -374,166 +374,166 @@
     <t xml:space="preserve">3.52464079856873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42826342582703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50743126869202</t>
+    <t xml:space="preserve">3.42826437950134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50743079185486</t>
   </si>
   <si>
     <t xml:space="preserve">3.65888071060181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75525736808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82065558433533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78623604774475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670680999756</t>
+    <t xml:space="preserve">3.75525760650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82065606117249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78623533248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670657157898</t>
   </si>
   <si>
     <t xml:space="preserve">3.96522092819214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9514524936676</t>
+    <t xml:space="preserve">3.95145297050476</t>
   </si>
   <si>
     <t xml:space="preserve">4.04094552993774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01340961456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94456911087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98931550979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9583375453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79656147956848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90326476097107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80000376701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68641662597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70018434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76558256149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362710952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66576457023621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66920685768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55217719078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48677849769592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47989439964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37319207191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3718147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50054669380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68985867500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561947822571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45235872268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47645330429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64511179924011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72083687782288</t>
+    <t xml:space="preserve">4.01341009140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94456934928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98931622505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95833683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7965612411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90326428413391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80000400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6864173412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70018482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76558327674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362663269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66576480865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66920638084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55217695236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4867787361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47989463806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37319159507751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37181496620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50054693222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68985843658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561852455139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45235824584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47645211219788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64511203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7208366394043</t>
   </si>
   <si>
     <t xml:space="preserve">3.70706844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77935147285461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80688858032227</t>
+    <t xml:space="preserve">3.77935123443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80688738822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.61413383483887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61757564544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57971382141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5659453868866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4936625957489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49022150039673</t>
+    <t xml:space="preserve">3.61757636070251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57971334457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56594491004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49366283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49022054672241</t>
   </si>
   <si>
     <t xml:space="preserve">3.44891667366028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63822817802429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49710440635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38695979118347</t>
+    <t xml:space="preserve">3.63822793960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49710488319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38695955276489</t>
   </si>
   <si>
     <t xml:space="preserve">3.35804653167725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37456846237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31123495101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3263795375824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35529351234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41587233543396</t>
+    <t xml:space="preserve">3.37456822395325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31123471260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32637977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35529327392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41587281227112</t>
   </si>
   <si>
     <t xml:space="preserve">3.514315366745</t>
@@ -542,46 +542,46 @@
     <t xml:space="preserve">3.48333621025085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51087307929993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51775693893433</t>
+    <t xml:space="preserve">3.51087284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51775717735291</t>
   </si>
   <si>
     <t xml:space="preserve">3.47301054000854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57627177238464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53496742248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64855456352234</t>
+    <t xml:space="preserve">3.57627129554749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53496718406677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6485538482666</t>
   </si>
   <si>
     <t xml:space="preserve">3.67953252792358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59692358970642</t>
+    <t xml:space="preserve">3.596923828125</t>
   </si>
   <si>
     <t xml:space="preserve">3.6416699886322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63134431838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56250357627869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5315248966217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45580053329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41174221038818</t>
+    <t xml:space="preserve">3.63134384155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56250309944153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53152537345886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4558002948761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41174244880676</t>
   </si>
   <si>
     <t xml:space="preserve">3.4296407699585</t>
@@ -596,97 +596,97 @@
     <t xml:space="preserve">3.52808284759521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63478660583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67609095573425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6279022693634</t>
+    <t xml:space="preserve">3.63478589057922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67609071731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62790155410767</t>
   </si>
   <si>
     <t xml:space="preserve">3.58659768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54529356956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55906200408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56938719749451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71739554405212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94112730026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00996732711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88605499267578</t>
+    <t xml:space="preserve">3.5452926158905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55906105041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56938695907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71739411354065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94112706184387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00996780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88605403900146</t>
   </si>
   <si>
     <t xml:space="preserve">3.97210502624512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83442354202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92735886573792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98587346076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05471420288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93080115318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04438734054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06159830093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91014862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89982295036316</t>
+    <t xml:space="preserve">3.83442401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92735862731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9858729839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05471324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93080139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04438781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06159782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91014885902405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.899822473526</t>
   </si>
   <si>
     <t xml:space="preserve">4.05815601348877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07192420959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07880830764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03062009811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19583749771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20960521697998</t>
+    <t xml:space="preserve">4.07192373275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07880878448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03061962127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19583654403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20960474014282</t>
   </si>
   <si>
     <t xml:space="preserve">4.29565620422363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27844619750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24746799468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30253982543945</t>
+    <t xml:space="preserve">4.27844667434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2474684715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30254030227661</t>
   </si>
   <si>
     <t xml:space="preserve">4.1269965171814</t>
@@ -695,61 +695,61 @@
     <t xml:space="preserve">4.13043880462646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20272207260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10634517669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12011241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17862701416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24058389663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14764881134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16141700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04783010482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14076519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1510910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15453243255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18206882476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15797472000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21304750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32319259643555</t>
+    <t xml:space="preserve">4.202721118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10634469985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12011289596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17862749099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2405834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14764928817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16141748428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04782962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1407642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15109062194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15453290939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18206834793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15797519683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21304702758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32319307327271</t>
   </si>
   <si>
     <t xml:space="preserve">4.36449670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43333721160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44022130966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38514947891235</t>
+    <t xml:space="preserve">4.43333768844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44022178649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38514852523804</t>
   </si>
   <si>
     <t xml:space="preserve">4.47464179992676</t>
@@ -758,43 +758,43 @@
     <t xml:space="preserve">4.41956996917725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37482309341431</t>
+    <t xml:space="preserve">4.37482261657715</t>
   </si>
   <si>
     <t xml:space="preserve">4.41268491744995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34384489059448</t>
+    <t xml:space="preserve">4.34384441375732</t>
   </si>
   <si>
     <t xml:space="preserve">4.30942487716675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36793851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35417079925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28533029556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52627229690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40580081939697</t>
+    <t xml:space="preserve">4.36793899536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35417032241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28532981872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52627277374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40580129623413</t>
   </si>
   <si>
     <t xml:space="preserve">4.48840999603271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50906181335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53659868240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54348278045654</t>
+    <t xml:space="preserve">4.50906276702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53659820556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54348182678223</t>
   </si>
   <si>
     <t xml:space="preserve">4.447105884552</t>
@@ -806,55 +806,55 @@
     <t xml:space="preserve">4.69899702072144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8010721206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71659564971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83627033233643</t>
+    <t xml:space="preserve">4.80107259750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7165961265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83627128601074</t>
   </si>
   <si>
     <t xml:space="preserve">4.86090993881226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85034990310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87850856781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78347253799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72011566162109</t>
+    <t xml:space="preserve">4.85035037994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87850904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78347301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72011613845825</t>
   </si>
   <si>
     <t xml:space="preserve">4.68491744995117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7306752204895</t>
+    <t xml:space="preserve">4.73067474365234</t>
   </si>
   <si>
     <t xml:space="preserve">4.75179481506348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81515216827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81163215637207</t>
+    <t xml:space="preserve">4.81515169143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81163167953491</t>
   </si>
   <si>
     <t xml:space="preserve">4.92778730392456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93834638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87498903274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8081111907959</t>
+    <t xml:space="preserve">4.93834686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87498950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80811214447021</t>
   </si>
   <si>
     <t xml:space="preserve">4.8045916557312</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">4.78699350357056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95946502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86442995071411</t>
+    <t xml:space="preserve">4.95946550369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86442947387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.89258813858032</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">4.91370725631714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97354507446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97706508636475</t>
+    <t xml:space="preserve">4.97354555130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97706460952759</t>
   </si>
   <si>
     <t xml:space="preserve">4.94538640975952</t>
@@ -890,19 +890,19 @@
     <t xml:space="preserve">5.11081886291504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2586522102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06154108047485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08617973327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10377883911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09673929214478</t>
+    <t xml:space="preserve">5.25865316390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06154155731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08618021011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10377979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09673976898193</t>
   </si>
   <si>
     <t xml:space="preserve">5.0509819984436</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">5.01930332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04746198654175</t>
+    <t xml:space="preserve">5.04746150970459</t>
   </si>
   <si>
     <t xml:space="preserve">4.96650505065918</t>
@@ -923,19 +923,19 @@
     <t xml:space="preserve">4.91018724441528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00874328613281</t>
+    <t xml:space="preserve">5.00874376296997</t>
   </si>
   <si>
     <t xml:space="preserve">5.10025978088379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06857967376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13193798065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04042100906372</t>
+    <t xml:space="preserve">5.06858015060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13193845748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0404224395752</t>
   </si>
   <si>
     <t xml:space="preserve">5.1248984336853</t>
@@ -944,34 +944,34 @@
     <t xml:space="preserve">5.20937490463257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36424779891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21289443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03690242767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16361665725708</t>
+    <t xml:space="preserve">5.36424732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21289491653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0369029045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16361618041992</t>
   </si>
   <si>
     <t xml:space="preserve">5.27273178100586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23049306869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15305757522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2023344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11433792114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1072998046875</t>
+    <t xml:space="preserve">5.23049402236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15305709838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20233488082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11433839797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10729932785034</t>
   </si>
   <si>
     <t xml:space="preserve">5.00522375106812</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">5.01226282119751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04394197463989</t>
+    <t xml:space="preserve">5.04394149780273</t>
   </si>
   <si>
     <t xml:space="preserve">5.06506156921387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15657615661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34312915802002</t>
+    <t xml:space="preserve">5.15657663345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34312868118286</t>
   </si>
   <si>
     <t xml:space="preserve">5.30089092254639</t>
@@ -1004,82 +1004,82 @@
     <t xml:space="preserve">5.30793046951294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2516131401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29385089874268</t>
+    <t xml:space="preserve">5.25161266326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29385137557983</t>
   </si>
   <si>
     <t xml:space="preserve">5.29033136367798</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33608818054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34664821624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36776828765869</t>
+    <t xml:space="preserve">5.33608865737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34664869308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36776781082153</t>
   </si>
   <si>
     <t xml:space="preserve">5.35368871688843</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38536691665649</t>
+    <t xml:space="preserve">5.38536739349365</t>
   </si>
   <si>
     <t xml:space="preserve">5.39944648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26569223403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31145000457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32553005218506</t>
+    <t xml:space="preserve">5.26569271087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31145048141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3255295753479</t>
   </si>
   <si>
     <t xml:space="preserve">5.28329181671143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23401355743408</t>
+    <t xml:space="preserve">5.23401308059692</t>
   </si>
   <si>
     <t xml:space="preserve">5.21641445159912</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14249753952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16713714599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31497049331665</t>
+    <t xml:space="preserve">5.14249706268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16713666915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31497001647949</t>
   </si>
   <si>
     <t xml:space="preserve">5.29737043380737</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19177532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35720777511597</t>
+    <t xml:space="preserve">5.19177579879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35720825195312</t>
   </si>
   <si>
     <t xml:space="preserve">5.07210063934326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98410415649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94186592102051</t>
+    <t xml:space="preserve">4.98410367965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94186639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.86794948577881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92426633834839</t>
+    <t xml:space="preserve">4.92426729202271</t>
   </si>
   <si>
     <t xml:space="preserve">4.98058414459229</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">5.03338241577148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05450105667114</t>
+    <t xml:space="preserve">5.0545015335083</t>
   </si>
   <si>
     <t xml:space="preserve">5.18473529815674</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">5.17417621612549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21993350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17769575119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22697353363037</t>
+    <t xml:space="preserve">5.21993446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17769622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22697401046753</t>
   </si>
   <si>
     <t xml:space="preserve">5.28681182861328</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">5.02282285690308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0017032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02986192703247</t>
+    <t xml:space="preserve">5.00170373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02986288070679</t>
   </si>
   <si>
     <t xml:space="preserve">5.05802154541016</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">4.92074680328369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99114465713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37128734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47688388824463</t>
+    <t xml:space="preserve">4.99114370346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37128782272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47688341140747</t>
   </si>
   <si>
     <t xml:space="preserve">5.48392295837402</t>
@@ -1139,58 +1139,58 @@
     <t xml:space="preserve">5.44168519973755</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43464517593384</t>
+    <t xml:space="preserve">5.43464469909668</t>
   </si>
   <si>
     <t xml:space="preserve">5.5261607170105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51208114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4698429107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40648603439331</t>
+    <t xml:space="preserve">5.51208209991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46984338760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40648555755615</t>
   </si>
   <si>
     <t xml:space="preserve">5.37832736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18825531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13897800445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32904958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14601707458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1952953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24457263946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22345399856567</t>
+    <t xml:space="preserve">5.18825578689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13897752761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3290491104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14601755142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19529581069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24457311630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22345447540283</t>
   </si>
   <si>
     <t xml:space="preserve">5.23753356933594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16009664535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11785793304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97002458572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2189998626709</t>
+    <t xml:space="preserve">5.16009616851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11785840988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97002506256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21899938583374</t>
   </si>
   <si>
     <t xml:space="preserve">5.14661407470703</t>
@@ -1205,49 +1205,49 @@
     <t xml:space="preserve">4.81364011764526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84259414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85707139968872</t>
+    <t xml:space="preserve">4.84259510040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85707187652588</t>
   </si>
   <si>
     <t xml:space="preserve">4.82087898254395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80640125274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5602912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46618938446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21284008026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45171308517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37208843231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52409839630127</t>
+    <t xml:space="preserve">4.80640172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56029081344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46618986129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21284055709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45171213150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37208795547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52409791946411</t>
   </si>
   <si>
     <t xml:space="preserve">4.40828132629395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34313344955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29246377944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3938045501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45895099639893</t>
+    <t xml:space="preserve">4.3431339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29246425628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39380407333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45895147323608</t>
   </si>
   <si>
     <t xml:space="preserve">4.4372353553772</t>
@@ -1256,25 +1256,25 @@
     <t xml:space="preserve">4.53133678436279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61096048355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64715337753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69058561325073</t>
+    <t xml:space="preserve">4.61096000671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64715385437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69058465957642</t>
   </si>
   <si>
     <t xml:space="preserve">4.57476806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58200693130493</t>
+    <t xml:space="preserve">4.58200597763062</t>
   </si>
   <si>
     <t xml:space="preserve">4.48790550231934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54581356048584</t>
+    <t xml:space="preserve">4.545814037323</t>
   </si>
   <si>
     <t xml:space="preserve">4.58924531936646</t>
@@ -1286,46 +1286,46 @@
     <t xml:space="preserve">4.68334627151489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69782304763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62543773651123</t>
+    <t xml:space="preserve">4.6978235244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62543821334839</t>
   </si>
   <si>
     <t xml:space="preserve">4.63267707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61819982528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56752872467041</t>
+    <t xml:space="preserve">4.61819934844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56752920150757</t>
   </si>
   <si>
     <t xml:space="preserve">4.44447374343872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42999649047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59648370742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47342872619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51685953140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50962066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17664766311646</t>
+    <t xml:space="preserve">4.42999744415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59648323059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47342777252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51685905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50962114334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1766471862793</t>
   </si>
   <si>
     <t xml:space="preserve">4.10426139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04635286331177</t>
+    <t xml:space="preserve">4.04635429382324</t>
   </si>
   <si>
     <t xml:space="preserve">4.0246376991272</t>
@@ -1337,37 +1337,37 @@
     <t xml:space="preserve">4.05359172821045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0680685043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97396731376648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00292205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85091185569763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87262797355652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93053650856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92329883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11150026321411</t>
+    <t xml:space="preserve">4.06806898117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97396779060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00292253494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85091304779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87262773513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93053603172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9232976436615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11150074005127</t>
   </si>
   <si>
     <t xml:space="preserve">4.22731733322144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20560169219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22007894515991</t>
+    <t xml:space="preserve">4.20560216903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22007942199707</t>
   </si>
   <si>
     <t xml:space="preserve">4.23455572128296</t>
@@ -1379,16 +1379,16 @@
     <t xml:space="preserve">4.27798700332642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29970264434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36485052108765</t>
+    <t xml:space="preserve">4.2997031211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36484956741333</t>
   </si>
   <si>
     <t xml:space="preserve">4.35761117935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26351022720337</t>
+    <t xml:space="preserve">4.26350927352905</t>
   </si>
   <si>
     <t xml:space="preserve">4.09702301025391</t>
@@ -1397,118 +1397,118 @@
     <t xml:space="preserve">4.06083059310913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12597751617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90882110595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84367370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78576564788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87986612319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94501304626465</t>
+    <t xml:space="preserve">4.12597703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90882062911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84367322921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78576493263245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87986660003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94501328468323</t>
   </si>
   <si>
     <t xml:space="preserve">3.80748105049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72061848640442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68442630767822</t>
+    <t xml:space="preserve">3.72061824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68442606925964</t>
   </si>
   <si>
     <t xml:space="preserve">3.5794665813446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45641136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55051255226135</t>
+    <t xml:space="preserve">3.45641088485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55051231384277</t>
   </si>
   <si>
     <t xml:space="preserve">3.81471967697144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76404976844788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8291962146759</t>
+    <t xml:space="preserve">3.76405000686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82919692993164</t>
   </si>
   <si>
     <t xml:space="preserve">3.83643531799316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85815048217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74233388900757</t>
+    <t xml:space="preserve">3.85815143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74233341217041</t>
   </si>
   <si>
     <t xml:space="preserve">3.75681090354919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70614171028137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67718744277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63375520706177</t>
+    <t xml:space="preserve">3.70614123344421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67718696594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63375544548035</t>
   </si>
   <si>
     <t xml:space="preserve">3.66994857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61927795410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64099383354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7712881565094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80024194717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66270971298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72785663604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86538934707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60480141639709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58670473098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57584691047668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54327392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547204017639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82195830345154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71337962150574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69890308380127</t>
+    <t xml:space="preserve">3.61927890777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64099431037903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77128791809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80024266242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66270995140076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72785687446594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86538982391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60480165481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58670496940613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57584714889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54327344894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547156333923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82195854187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71337985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69890284538269</t>
   </si>
   <si>
     <t xml:space="preserve">3.69166398048401</t>
@@ -1517,43 +1517,43 @@
     <t xml:space="preserve">3.6265172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64823293685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52517700195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60118246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54689288139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5034613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60842061042786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79300403594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8871054649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5649893283844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59394407272339</t>
+    <t xml:space="preserve">3.64823269844055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52517747879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60118198394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54689311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50346207618713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60842108726501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79300355911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88710451126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56498885154724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59394383430481</t>
   </si>
   <si>
     <t xml:space="preserve">3.77852654457092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58308577537537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53965449333191</t>
+    <t xml:space="preserve">3.58308529853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53965401649475</t>
   </si>
   <si>
     <t xml:space="preserve">3.48174595832825</t>
@@ -1562,70 +1562,70 @@
     <t xml:space="preserve">3.49622321128845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.452791929245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42021822929382</t>
+    <t xml:space="preserve">3.45279169082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4202184677124</t>
   </si>
   <si>
     <t xml:space="preserve">3.43155598640442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43533515930176</t>
+    <t xml:space="preserve">3.43533539772034</t>
   </si>
   <si>
     <t xml:space="preserve">3.41265964508057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33329558372498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841275215149</t>
+    <t xml:space="preserve">3.33329510688782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841227531433</t>
   </si>
   <si>
     <t xml:space="preserve">3.38620495796204</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37108826637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36352968215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3824257850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31062030792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32573699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29172396659851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393152236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3143994808197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33707475662231</t>
+    <t xml:space="preserve">3.37108778953552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36352920532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38242554664612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31062054634094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32573747634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29172348976135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393128395081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31439995765686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33707451820374</t>
   </si>
   <si>
     <t xml:space="preserve">3.276606798172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28038644790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23503518104553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20480108261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21613907814026</t>
+    <t xml:space="preserve">3.28038620948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23503541946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20480132102966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21613931655884</t>
   </si>
   <si>
     <t xml:space="preserve">3.23125624656677</t>
@@ -1634,40 +1634,40 @@
     <t xml:space="preserve">3.21235966682434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24259376525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18212556838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13677501678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15189170837402</t>
+    <t xml:space="preserve">3.24259352684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18212580680847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13677477836609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1518919467926</t>
   </si>
   <si>
     <t xml:space="preserve">3.18968415260315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20102214813232</t>
+    <t xml:space="preserve">3.20102190971375</t>
   </si>
   <si>
     <t xml:space="preserve">3.25015234947205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39376330375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59784293174744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65831089019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55627131462097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5524914264679</t>
+    <t xml:space="preserve">3.39376354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59784317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65831136703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55627107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55249166488647</t>
   </si>
   <si>
     <t xml:space="preserve">3.56760883331299</t>
@@ -1676,124 +1676,124 @@
     <t xml:space="preserve">3.57516741752625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60540151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53359580039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47690677642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59028458595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5827260017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57138824462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52603721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50336194038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43911480903625</t>
+    <t xml:space="preserve">3.60540127754211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53359532356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47690749168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59028434753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58272576332092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57138848304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52603673934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50336217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43911457061768</t>
   </si>
   <si>
     <t xml:space="preserve">3.4277765750885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40132212638855</t>
+    <t xml:space="preserve">3.40132188796997</t>
   </si>
   <si>
     <t xml:space="preserve">3.36730861663818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40888071060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34085416793823</t>
+    <t xml:space="preserve">3.40888094902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34085392951965</t>
   </si>
   <si>
     <t xml:space="preserve">3.42399764060974</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51469945907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49958252906799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54871225357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63941502571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65453147888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68098616600037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67342782020569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73011684417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78680515289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285799980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86239075660706</t>
+    <t xml:space="preserve">3.51469922065735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49958276748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54871249198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6394145488739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65453171730042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6809868812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67342805862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73011612892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78680562973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285776138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86239051818848</t>
   </si>
   <si>
     <t xml:space="preserve">3.74523329734802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76790904998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83971476554871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83215665817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168750762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7376754283905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69232392311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70366191864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77924656867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6885449886322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66586923599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69610285758972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66964817047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73389554023743</t>
+    <t xml:space="preserve">3.76790928840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83971500396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83215570449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168846130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73767471313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69232439994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70366144180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77924680709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68854475021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66586971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6961030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66964888572693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73389530181885</t>
   </si>
   <si>
     <t xml:space="preserve">3.81703925132751</t>
@@ -1802,16 +1802,16 @@
     <t xml:space="preserve">3.84727358818054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90018272399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98332571983337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96065044403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95309209823608</t>
+    <t xml:space="preserve">3.90018248558044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98332619667053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96065068244934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9530918598175</t>
   </si>
   <si>
     <t xml:space="preserve">3.93041634559631</t>
@@ -1820,25 +1820,25 @@
     <t xml:space="preserve">3.94553327560425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99088478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91530013084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0211181640625</t>
+    <t xml:space="preserve">3.99088454246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91529893875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02111864089966</t>
   </si>
   <si>
     <t xml:space="preserve">4.09670352935791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03623580932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0664701461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08158683776855</t>
+    <t xml:space="preserve">4.03623628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06646966934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0815863609314</t>
   </si>
   <si>
     <t xml:space="preserve">4.13449573516846</t>
@@ -1862,25 +1862,25 @@
     <t xml:space="preserve">4.01355981826782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96820902824402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93797540664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97576785087585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90774130821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89262437820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88506603240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87750720977783</t>
+    <t xml:space="preserve">3.9682092666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93797516822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97576808929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90774083137512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89262390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88506531715393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87750744819641</t>
   </si>
   <si>
     <t xml:space="preserve">3.85483193397522</t>
@@ -1889,91 +1889,91 @@
     <t xml:space="preserve">3.801922082901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59406352043152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60162162780762</t>
+    <t xml:space="preserve">3.5940637588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60162210464478</t>
   </si>
   <si>
     <t xml:space="preserve">3.65075254440308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71877837181091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99844264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72255802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63185572624207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46556973457336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44667291641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28416538238525</t>
+    <t xml:space="preserve">3.71877861022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99844312667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72255825996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63185548782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46556925773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44667315483093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28416514396667</t>
   </si>
   <si>
     <t xml:space="preserve">3.11031985282898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06496906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83821439743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83443522453308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95915007591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70972013473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93269538879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00450110435486</t>
+    <t xml:space="preserve">3.0649688243866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83821415901184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8344349861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95915031433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70971989631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93269562721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00450134277344</t>
   </si>
   <si>
     <t xml:space="preserve">2.97426724433899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94403290748596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91001987457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96292924880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85333132743835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8949031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88734459877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92135787010193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85711026191711</t>
+    <t xml:space="preserve">2.94403314590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91002011299133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96292948722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85333108901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89490294456482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88734436035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92135763168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85711050033569</t>
   </si>
   <si>
     <t xml:space="preserve">2.9024612903595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82687664031982</t>
+    <t xml:space="preserve">2.8268768787384</t>
   </si>
   <si>
     <t xml:space="preserve">2.89112401008606</t>
@@ -1982,31 +1982,31 @@
     <t xml:space="preserve">2.9969425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9515917301178</t>
+    <t xml:space="preserve">2.95159149169922</t>
   </si>
   <si>
     <t xml:space="preserve">2.97804641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99316310882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.053631067276</t>
+    <t xml:space="preserve">2.99316334724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05363154411316</t>
   </si>
   <si>
     <t xml:space="preserve">3.03473496437073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02717685699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12165760993958</t>
+    <t xml:space="preserve">3.02717661857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12165784835815</t>
   </si>
   <si>
     <t xml:space="preserve">3.06118988990784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09898209571838</t>
+    <t xml:space="preserve">3.09898233413696</t>
   </si>
   <si>
     <t xml:space="preserve">3.16700887680054</t>
@@ -2015,16 +2015,16 @@
     <t xml:space="preserve">3.14433312416077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19346380233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2199182510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26904845237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32195782661438</t>
+    <t xml:space="preserve">3.19346332550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21991848945618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26904821395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32195806503296</t>
   </si>
   <si>
     <t xml:space="preserve">3.1594500541687</t>
@@ -2033,85 +2033,85 @@
     <t xml:space="preserve">3.07252764701843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06874823570251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10654067993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1632297039032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27282738685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28794455528259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40510129928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51092004776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48824429512024</t>
+    <t xml:space="preserve">3.06874847412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10654091835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16322946548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27282762527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28794431686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40510153770447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51091980934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4882447719574</t>
   </si>
   <si>
     <t xml:space="preserve">3.45801067352295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29550313949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34463357925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29928183555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30684089660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30306148529053</t>
+    <t xml:space="preserve">3.29550361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34463334083557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29928278923035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30684113502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30306196212769</t>
   </si>
   <si>
     <t xml:space="preserve">3.26148986816406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37864637374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37486743927002</t>
+    <t xml:space="preserve">3.3786461353302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37486720085144</t>
   </si>
   <si>
     <t xml:space="preserve">3.26526927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4806866645813</t>
+    <t xml:space="preserve">3.39754271507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48068642616272</t>
   </si>
   <si>
     <t xml:space="preserve">3.38998436927795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31817889213562</t>
+    <t xml:space="preserve">3.31817865371704</t>
   </si>
   <si>
     <t xml:space="preserve">3.25771069526672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22747683525085</t>
+    <t xml:space="preserve">3.22747659683228</t>
   </si>
   <si>
     <t xml:space="preserve">3.18590497970581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24637246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17456722259521</t>
+    <t xml:space="preserve">3.24637317657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17456698417664</t>
   </si>
   <si>
     <t xml:space="preserve">3.14055418968201</t>
@@ -2123,16 +2123,16 @@
     <t xml:space="preserve">3.09142398834229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08008599281311</t>
+    <t xml:space="preserve">3.08008575439453</t>
   </si>
   <si>
     <t xml:space="preserve">3.0460729598999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01583909988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94025421142578</t>
+    <t xml:space="preserve">3.01583862304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9402539730072</t>
   </si>
   <si>
     <t xml:space="preserve">2.95537090301514</t>
@@ -2141,16 +2141,16 @@
     <t xml:space="preserve">2.92513704299927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88356494903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80042195320129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78908443450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77018809318542</t>
+    <t xml:space="preserve">2.8835654258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80042171478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7890841960907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77018785476685</t>
   </si>
   <si>
     <t xml:space="preserve">2.75129151344299</t>
@@ -2159,22 +2159,22 @@
     <t xml:space="preserve">2.71727824211121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72105717658997</t>
+    <t xml:space="preserve">2.72105765342712</t>
   </si>
   <si>
     <t xml:space="preserve">2.67948603630066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55477070808411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44895195960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55099153518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61523842811584</t>
+    <t xml:space="preserve">2.55477094650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44895172119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55099177360535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.615238904953</t>
   </si>
   <si>
     <t xml:space="preserve">2.69838213920593</t>
@@ -2183,16 +2183,16 @@
     <t xml:space="preserve">2.98938417434692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53737449645996</t>
+    <t xml:space="preserve">3.53737473487854</t>
   </si>
   <si>
     <t xml:space="preserve">3.62807679176331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63563561439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.578946352005</t>
+    <t xml:space="preserve">3.63563513755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57894682884216</t>
   </si>
   <si>
     <t xml:space="preserve">3.56382942199707</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">3.50714087486267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48446536064148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52225756645203</t>
+    <t xml:space="preserve">3.48446583747864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52225732803345</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643905639648</t>
@@ -2213,43 +2213,43 @@
     <t xml:space="preserve">3.12543702125549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80948090553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76035046577454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64319372177124</t>
+    <t xml:space="preserve">3.80948066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76035094261169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64319396018982</t>
   </si>
   <si>
     <t xml:space="preserve">3.68476557731628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74901247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79436326026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75657105445862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77546739578247</t>
+    <t xml:space="preserve">3.7490131855011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79436349868774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7565712928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77546763420105</t>
   </si>
   <si>
     <t xml:space="preserve">3.76412963867188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15717172622681</t>
+    <t xml:space="preserve">4.15717077255249</t>
   </si>
   <si>
     <t xml:space="preserve">4.11182069778442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.172287940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3134560585022</t>
+    <t xml:space="preserve">4.17228889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31345558166504</t>
   </si>
   <si>
     <t xml:space="preserve">4.22718667984009</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">4.1252326965332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07817649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08601903915405</t>
+    <t xml:space="preserve">4.07817602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08601951599121</t>
   </si>
   <si>
     <t xml:space="preserve">4.09386157989502</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">4.20365858078003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2664008140564</t>
+    <t xml:space="preserve">4.26640033721924</t>
   </si>
   <si>
     <t xml:space="preserve">4.27424240112305</t>
@@ -2279,28 +2279,28 @@
     <t xml:space="preserve">4.25855731964111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36835432052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32914113998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34482669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35266923904419</t>
+    <t xml:space="preserve">4.36835479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32914161682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34482622146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35266971588135</t>
   </si>
   <si>
     <t xml:space="preserve">4.30561304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28992748260498</t>
+    <t xml:space="preserve">4.28992795944214</t>
   </si>
   <si>
     <t xml:space="preserve">4.28208541870117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19581604003906</t>
+    <t xml:space="preserve">4.19581651687622</t>
   </si>
   <si>
     <t xml:space="preserve">4.03896331787109</t>
@@ -2315,49 +2315,49 @@
     <t xml:space="preserve">4.00759315490723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96053719520569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03112125396729</t>
+    <t xml:space="preserve">3.96053695678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03112030029297</t>
   </si>
   <si>
     <t xml:space="preserve">4.05464839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93700838088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92132329940796</t>
+    <t xml:space="preserve">3.93700885772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92132377624512</t>
   </si>
   <si>
     <t xml:space="preserve">4.01543521881104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07033395767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9762225151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1879734992981</t>
+    <t xml:space="preserve">4.07033348083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97622179985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18797397613525</t>
   </si>
   <si>
     <t xml:space="preserve">4.24287176132202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21150159835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39188194274902</t>
+    <t xml:space="preserve">4.21150064468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39188241958618</t>
   </si>
   <si>
     <t xml:space="preserve">4.45462369918823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43109560012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42325305938721</t>
+    <t xml:space="preserve">4.43109512329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42325258255005</t>
   </si>
   <si>
     <t xml:space="preserve">4.38403987884521</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">4.33698415756226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36051177978516</t>
+    <t xml:space="preserve">4.36051225662231</t>
   </si>
   <si>
     <t xml:space="preserve">4.46246671676636</t>
@@ -2384,34 +2384,34 @@
     <t xml:space="preserve">4.47815179824829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4859938621521</t>
+    <t xml:space="preserve">4.48599433898926</t>
   </si>
   <si>
     <t xml:space="preserve">4.50167942047119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56442070007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60363388061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62716197967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6350040435791</t>
+    <t xml:space="preserve">4.5644211769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60363340377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62716150283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63500452041626</t>
   </si>
   <si>
     <t xml:space="preserve">4.49383687973022</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59579086303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66637468338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68205976486206</t>
+    <t xml:space="preserve">4.59579133987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66637516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68206024169922</t>
   </si>
   <si>
     <t xml:space="preserve">4.72911643981934</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">4.74480199813843</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8624415397644</t>
+    <t xml:space="preserve">4.86244106292725</t>
   </si>
   <si>
     <t xml:space="preserve">4.90949726104736</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05850696563721</t>
+    <t xml:space="preserve">5.05850744247437</t>
   </si>
   <si>
     <t xml:space="preserve">5.03497982025146</t>
@@ -2444,28 +2444,28 @@
     <t xml:space="preserve">4.9487099647522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97223854064941</t>
+    <t xml:space="preserve">4.97223806381226</t>
   </si>
   <si>
     <t xml:space="preserve">4.87028360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98008108139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07419204711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05066537857056</t>
+    <t xml:space="preserve">4.98008060455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0741925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0506649017334</t>
   </si>
   <si>
     <t xml:space="preserve">5.02713680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08987760543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19183254241943</t>
+    <t xml:space="preserve">5.08987808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19183206558228</t>
   </si>
   <si>
     <t xml:space="preserve">5.18398952484131</t>
@@ -2480,22 +2480,22 @@
     <t xml:space="preserve">5.14477634429932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23888874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21536016464233</t>
+    <t xml:space="preserve">5.23888826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21536064147949</t>
   </si>
   <si>
     <t xml:space="preserve">5.1996750831604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25457382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30162954330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01929473876953</t>
+    <t xml:space="preserve">5.25457334518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3016300201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01929426193237</t>
   </si>
   <si>
     <t xml:space="preserve">4.93302536010742</t>
@@ -2504,31 +2504,31 @@
     <t xml:space="preserve">4.7996997833252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76048707962036</t>
+    <t xml:space="preserve">4.7604866027832</t>
   </si>
   <si>
     <t xml:space="preserve">4.76832962036133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68990278244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69774532318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61147689819336</t>
+    <t xml:space="preserve">4.68990325927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69774580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6114764213562</t>
   </si>
   <si>
     <t xml:space="preserve">4.53305006027222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50952243804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47030925750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55657815933228</t>
+    <t xml:space="preserve">4.50952196121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47030878067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55657863616943</t>
   </si>
   <si>
     <t xml:space="preserve">4.54873561859131</t>
@@ -2537,19 +2537,19 @@
     <t xml:space="preserve">4.57226371765137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52520799636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54089307785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51736497879028</t>
+    <t xml:space="preserve">4.52520751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54089212417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51736450195312</t>
   </si>
   <si>
     <t xml:space="preserve">4.58010578155518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82322835922241</t>
+    <t xml:space="preserve">4.82322788238525</t>
   </si>
   <si>
     <t xml:space="preserve">4.87812662124634</t>
@@ -2561,25 +2561,25 @@
     <t xml:space="preserve">4.7840142250061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70558786392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65853261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77617263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85459852218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94086790084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52122354507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66239070892334</t>
+    <t xml:space="preserve">4.70558834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65853309631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77617216110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85459899902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94086837768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5212230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6623911857605</t>
   </si>
   <si>
     <t xml:space="preserve">5.73297500610352</t>
@@ -2597,61 +2597,61 @@
     <t xml:space="preserve">5.59965038299561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5369086265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906703948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17614698410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29378700256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7134313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41541051864624</t>
+    <t xml:space="preserve">5.53690910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906656265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17614650726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29378747940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71343088150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41541004180908</t>
   </si>
   <si>
     <t xml:space="preserve">4.89381170272827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81538534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9251823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84675645828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72127342224121</t>
+    <t xml:space="preserve">4.81538486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92518329620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84675550460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72127389907837</t>
   </si>
   <si>
     <t xml:space="preserve">4.5879487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61931943893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77163219451904</t>
+    <t xml:space="preserve">4.61931896209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77163171768188</t>
   </si>
   <si>
     <t xml:space="preserve">4.738609790802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69733238220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63954496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79639768600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98627233505249</t>
+    <t xml:space="preserve">4.69733333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63954448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79639863967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98627281188965</t>
   </si>
   <si>
     <t xml:space="preserve">4.95325088500977</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">5.14312553405762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07708168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11835956573486</t>
+    <t xml:space="preserve">5.07708215713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11835908889771</t>
   </si>
   <si>
     <t xml:space="preserve">4.97801733016968</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">5.06057119369507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90371799468994</t>
+    <t xml:space="preserve">4.90371894836426</t>
   </si>
   <si>
     <t xml:space="preserve">4.96976184844971</t>
@@ -2684,10 +2684,10 @@
     <t xml:space="preserve">4.82941961288452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62303447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40839338302612</t>
+    <t xml:space="preserve">4.62303400039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40839385986328</t>
   </si>
   <si>
     <t xml:space="preserve">4.50745820999146</t>
@@ -2696,16 +2696,16 @@
     <t xml:space="preserve">4.56524658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4826922416687</t>
+    <t xml:space="preserve">4.48269176483154</t>
   </si>
   <si>
     <t xml:space="preserve">4.58175754547119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6478009223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61477947235107</t>
+    <t xml:space="preserve">4.64779996871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61477899551392</t>
   </si>
   <si>
     <t xml:space="preserve">4.57350158691406</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">4.3340950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30932760238647</t>
+    <t xml:space="preserve">4.30932807922363</t>
   </si>
   <si>
     <t xml:space="preserve">4.38362693786621</t>
@@ -2726,40 +2726,40 @@
     <t xml:space="preserve">4.16898632049561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2680516242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39188241958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46618127822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42490482330322</t>
+    <t xml:space="preserve">4.26805114746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39188289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4661808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42490386962891</t>
   </si>
   <si>
     <t xml:space="preserve">4.3753719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27630662918091</t>
+    <t xml:space="preserve">4.27630615234375</t>
   </si>
   <si>
     <t xml:space="preserve">4.44967031478882</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34235000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41664838790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55699062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67256689071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65605592727661</t>
+    <t xml:space="preserve">4.34235048294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41664886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55699110031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67256641387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65605545043945</t>
   </si>
   <si>
     <t xml:space="preserve">4.71384382247925</t>
@@ -2768,22 +2768,22 @@
     <t xml:space="preserve">4.76337623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85418605804443</t>
+    <t xml:space="preserve">4.85418558120728</t>
   </si>
   <si>
     <t xml:space="preserve">4.72209930419922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7551212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77988719940186</t>
+    <t xml:space="preserve">4.75512075424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7798867225647</t>
   </si>
   <si>
     <t xml:space="preserve">4.73035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82116460800171</t>
+    <t xml:space="preserve">4.82116413116455</t>
   </si>
   <si>
     <t xml:space="preserve">4.92848443984985</t>
@@ -2801,25 +2801,25 @@
     <t xml:space="preserve">4.78814268112183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87895154953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60652303695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66431188583374</t>
+    <t xml:space="preserve">4.87895202636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60652351379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66431093215942</t>
   </si>
   <si>
     <t xml:space="preserve">4.81290912628174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93673992156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01103925704956</t>
+    <t xml:space="preserve">4.88720750808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93674039840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0110387802124</t>
   </si>
   <si>
     <t xml:space="preserve">5.11010408401489</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">5.16789197921753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23393535614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19265794754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22567987442017</t>
+    <t xml:space="preserve">5.23393487930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19265842437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22567939758301</t>
   </si>
   <si>
     <t xml:space="preserve">5.26695680618286</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27521181106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29172277450562</t>
+    <t xml:space="preserve">5.27521228790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29172325134277</t>
   </si>
   <si>
     <t xml:space="preserve">5.30823373794556</t>
@@ -2852,28 +2852,28 @@
     <t xml:space="preserve">5.36602210998535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43206548690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4733419418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5558967590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41555452346802</t>
+    <t xml:space="preserve">5.4320650100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47334241867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55589628219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41555404663086</t>
   </si>
   <si>
     <t xml:space="preserve">5.4898533821106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46508693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57240724563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44857597351074</t>
+    <t xml:space="preserve">5.46508646011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57240772247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44857549667358</t>
   </si>
   <si>
     <t xml:space="preserve">5.49810838699341</t>
@@ -2885,10 +2885,10 @@
     <t xml:space="preserve">5.51461935043335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58891868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45683145523071</t>
+    <t xml:space="preserve">5.58891820907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45683097839355</t>
   </si>
   <si>
     <t xml:space="preserve">5.54764080047607</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">5.61368465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59717416763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58066272735596</t>
+    <t xml:space="preserve">5.5971736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58066320419312</t>
   </si>
   <si>
     <t xml:space="preserve">5.65496110916138</t>
@@ -2915,40 +2915,40 @@
     <t xml:space="preserve">5.77879285812378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82006978988647</t>
+    <t xml:space="preserve">5.82007026672363</t>
   </si>
   <si>
     <t xml:space="preserve">5.84483575820923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86134624481201</t>
+    <t xml:space="preserve">5.86134672164917</t>
   </si>
   <si>
     <t xml:space="preserve">5.89436864852905</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8118143081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90262460708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80355978012085</t>
+    <t xml:space="preserve">5.81181383132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90262413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80355882644653</t>
   </si>
   <si>
     <t xml:space="preserve">5.73751544952393</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00168943405151</t>
+    <t xml:space="preserve">6.00168895721436</t>
   </si>
   <si>
     <t xml:space="preserve">6.30713939666748</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38969421386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39794874191284</t>
+    <t xml:space="preserve">6.38969373703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39794921875</t>
   </si>
   <si>
     <t xml:space="preserve">6.47224807739258</t>
@@ -2957,10 +2957,10 @@
     <t xml:space="preserve">6.4392261505127</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45573663711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59607839584351</t>
+    <t xml:space="preserve">6.45573711395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59607887268066</t>
   </si>
   <si>
     <t xml:space="preserve">6.52178049087524</t>
@@ -2969,19 +2969,19 @@
     <t xml:space="preserve">6.57956838607788</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58782386779785</t>
+    <t xml:space="preserve">6.58782339096069</t>
   </si>
   <si>
     <t xml:space="preserve">6.51352500915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56305742263794</t>
+    <t xml:space="preserve">6.5630578994751</t>
   </si>
   <si>
     <t xml:space="preserve">6.67863368988037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72816562652588</t>
+    <t xml:space="preserve">6.72816514968872</t>
   </si>
   <si>
     <t xml:space="preserve">6.6703782081604</t>
@@ -2996,22 +2996,22 @@
     <t xml:space="preserve">6.73642110824585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6868896484375</t>
+    <t xml:space="preserve">6.68688917160034</t>
   </si>
   <si>
     <t xml:space="preserve">6.53829145431519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62084579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64561128616333</t>
+    <t xml:space="preserve">6.62084531784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64561176300049</t>
   </si>
   <si>
     <t xml:space="preserve">6.71991062164307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74467658996582</t>
+    <t xml:space="preserve">6.74467706680298</t>
   </si>
   <si>
     <t xml:space="preserve">6.75293254852295</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">6.78595399856567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96866703033447</t>
+    <t xml:space="preserve">5.96866798400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.05122137069702</t>
@@ -3032,28 +3032,28 @@
     <t xml:space="preserve">5.85309171676636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67972755432129</t>
+    <t xml:space="preserve">5.67972803115845</t>
   </si>
   <si>
     <t xml:space="preserve">5.39904403686523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38253259658813</t>
+    <t xml:space="preserve">5.38253307342529</t>
   </si>
   <si>
     <t xml:space="preserve">5.66321659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60542964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74577140808105</t>
+    <t xml:space="preserve">5.60542917251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7457709312439</t>
   </si>
   <si>
     <t xml:space="preserve">5.83658075332642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88611364364624</t>
+    <t xml:space="preserve">5.88611316680908</t>
   </si>
   <si>
     <t xml:space="preserve">5.79530382156372</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">5.91087913513184</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91913509368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63845014572144</t>
+    <t xml:space="preserve">5.91913461685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63845062255859</t>
   </si>
   <si>
     <t xml:space="preserve">5.78704881668091</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">5.94390106201172</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9604115486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86960220336914</t>
+    <t xml:space="preserve">5.96041202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8696026802063</t>
   </si>
   <si>
     <t xml:space="preserve">5.98917293548584</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">5.82472991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80742025375366</t>
+    <t xml:space="preserve">5.80742073059082</t>
   </si>
   <si>
     <t xml:space="preserve">5.86800479888916</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">5.88531446456909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87665939331055</t>
+    <t xml:space="preserve">5.87665987014771</t>
   </si>
   <si>
     <t xml:space="preserve">5.92858839035034</t>
@@ -3146,25 +3146,25 @@
     <t xml:space="preserve">5.96320819854736</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94589853286743</t>
+    <t xml:space="preserve">5.94589805603027</t>
   </si>
   <si>
     <t xml:space="preserve">5.91993379592896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15361499786377</t>
+    <t xml:space="preserve">6.15361547470093</t>
   </si>
   <si>
     <t xml:space="preserve">6.22285461425781</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17092514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28343868255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25747346878052</t>
+    <t xml:space="preserve">6.17092561721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28343915939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25747394561768</t>
   </si>
   <si>
     <t xml:space="preserve">6.24881887435913</t>
@@ -3173,10 +3173,10 @@
     <t xml:space="preserve">6.24016380310059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2315092086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26612901687622</t>
+    <t xml:space="preserve">6.23150873184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26612854003906</t>
   </si>
   <si>
     <t xml:space="preserve">6.46519088745117</t>
@@ -3185,46 +3185,46 @@
     <t xml:space="preserve">6.54308462142944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58635902404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56904983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6382884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56039381027222</t>
+    <t xml:space="preserve">6.58635950088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56904935836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63828802108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56039428710938</t>
   </si>
   <si>
     <t xml:space="preserve">6.57770442962646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62097835540771</t>
+    <t xml:space="preserve">6.62097883224487</t>
   </si>
   <si>
     <t xml:space="preserve">6.65559816360474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6902174949646</t>
+    <t xml:space="preserve">6.69021797180176</t>
   </si>
   <si>
     <t xml:space="preserve">6.73349189758301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64694261550903</t>
+    <t xml:space="preserve">6.64694309234619</t>
   </si>
   <si>
     <t xml:space="preserve">6.50846529006958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66425228118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11034059524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30940341949463</t>
+    <t xml:space="preserve">6.66425275802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11034107208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30940294265747</t>
   </si>
   <si>
     <t xml:space="preserve">6.37864208221436</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">6.49115562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49981021881104</t>
+    <t xml:space="preserve">6.49981069564819</t>
   </si>
   <si>
     <t xml:space="preserve">6.55173969268799</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">6.70752716064453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68156290054321</t>
+    <t xml:space="preserve">6.68156242370605</t>
   </si>
   <si>
     <t xml:space="preserve">6.60366868972778</t>
@@ -3260,13 +3260,13 @@
     <t xml:space="preserve">6.62963342666626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74214696884155</t>
+    <t xml:space="preserve">6.74214649200439</t>
   </si>
   <si>
     <t xml:space="preserve">6.87196969985962</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79407596588135</t>
+    <t xml:space="preserve">6.79407644271851</t>
   </si>
   <si>
     <t xml:space="preserve">6.85466003417969</t>
@@ -3293,16 +3293,16 @@
     <t xml:space="preserve">6.45653581619263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71618270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72483682632446</t>
+    <t xml:space="preserve">6.71618223190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72483730316162</t>
   </si>
   <si>
     <t xml:space="preserve">6.75945663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82869529724121</t>
+    <t xml:space="preserve">6.82869577407837</t>
   </si>
   <si>
     <t xml:space="preserve">6.82004070281982</t>
@@ -3314,10 +3314,10 @@
     <t xml:space="preserve">7.01044797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05372142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9931378364563</t>
+    <t xml:space="preserve">7.05372190475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99313831329346</t>
   </si>
   <si>
     <t xml:space="preserve">7.001793384552</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">7.01910257339478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04506778717041</t>
+    <t xml:space="preserve">7.04506731033325</t>
   </si>
   <si>
     <t xml:space="preserve">7.13161611557007</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">7.17489004135132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27009391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20085430145264</t>
+    <t xml:space="preserve">7.27009439468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20085477828979</t>
   </si>
   <si>
     <t xml:space="preserve">7.22681999206543</t>
@@ -3398,7 +3398,7 @@
     <t xml:space="preserve">7.16623544692993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14892625808716</t>
+    <t xml:space="preserve">7.14892578125</t>
   </si>
   <si>
     <t xml:space="preserve">7.08834171295166</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">7.31336784362793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33933258056641</t>
+    <t xml:space="preserve">7.33933305740356</t>
   </si>
   <si>
     <t xml:space="preserve">7.42588138580322</t>
@@ -3425,13 +3425,13 @@
     <t xml:space="preserve">7.48646545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23547458648682</t>
+    <t xml:space="preserve">7.23547506332397</t>
   </si>
   <si>
     <t xml:space="preserve">7.29605865478516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19220113754272</t>
+    <t xml:space="preserve">7.19220066070557</t>
   </si>
   <si>
     <t xml:space="preserve">7.4518461227417</t>
@@ -3449,19 +3449,19 @@
     <t xml:space="preserve">7.84997081756592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72880268096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76342248916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53839588165283</t>
+    <t xml:space="preserve">7.72880220413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7634220123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53839540481567</t>
   </si>
   <si>
     <t xml:space="preserve">7.55570507049561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46050119400024</t>
+    <t xml:space="preserve">7.4605016708374</t>
   </si>
   <si>
     <t xml:space="preserve">7.40857219696045</t>
@@ -3479,25 +3479,25 @@
     <t xml:space="preserve">7.77207612991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65090894699097</t>
+    <t xml:space="preserve">7.65090847015381</t>
   </si>
   <si>
     <t xml:space="preserve">7.6682186126709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78073120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83266115188599</t>
+    <t xml:space="preserve">7.78073215484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83266067504883</t>
   </si>
   <si>
     <t xml:space="preserve">7.82400560379028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75476741790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70283794403076</t>
+    <t xml:space="preserve">7.75476694107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7028374671936</t>
   </si>
   <si>
     <t xml:space="preserve">7.69418334960938</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">7.67687273025513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94517469406128</t>
+    <t xml:space="preserve">7.94517421722412</t>
   </si>
   <si>
     <t xml:space="preserve">8.01441287994385</t>
@@ -3533,10 +3533,10 @@
     <t xml:space="preserve">8.17885589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17020034790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20482063293457</t>
+    <t xml:space="preserve">8.17020130157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20481967926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.07499694824219</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">8.00575828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99710321426392</t>
+    <t xml:space="preserve">7.99710273742676</t>
   </si>
   <si>
     <t xml:space="preserve">7.87593650817871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30867958068848</t>
+    <t xml:space="preserve">8.30867862701416</t>
   </si>
   <si>
     <t xml:space="preserve">8.24809455871582</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">8.27406024932861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41253662109375</t>
+    <t xml:space="preserve">8.41253757476807</t>
   </si>
   <si>
     <t xml:space="preserve">8.57698059082031</t>
@@ -3572,22 +3572,22 @@
     <t xml:space="preserve">8.58563423156738</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65487384796143</t>
+    <t xml:space="preserve">8.65487289428711</t>
   </si>
   <si>
     <t xml:space="preserve">8.54236030578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62025356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81066226959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82797050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70680332183838</t>
+    <t xml:space="preserve">8.62025451660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81066131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82797145843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7068042755127</t>
   </si>
   <si>
     <t xml:space="preserve">8.87990093231201</t>
@@ -4323,6 +4323,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.460000038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6199998855591</t>
   </si>
 </sst>
 </file>
@@ -70129,7 +70132,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6911921296</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>108847</v>
@@ -70150,6 +70153,32 @@
         <v>1436</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6911805556</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>143088</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>14.6800003051758</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>14.3999996185303</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>14.5200004577637</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>14.6199998855591</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="1444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="1445">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49119472503662</t>
+    <t xml:space="preserve">4.49119424819946</t>
   </si>
   <si>
     <t xml:space="preserve">CE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52814531326294</t>
+    <t xml:space="preserve">4.52814626693726</t>
   </si>
   <si>
     <t xml:space="preserve">4.46432161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30644035339355</t>
+    <t xml:space="preserve">4.30644083023071</t>
   </si>
   <si>
     <t xml:space="preserve">4.26613140106201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31315851211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31987810134888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36690521240234</t>
+    <t xml:space="preserve">4.31315946578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3198766708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3669056892395</t>
   </si>
   <si>
     <t xml:space="preserve">4.27284955978394</t>
@@ -71,121 +71,121 @@
     <t xml:space="preserve">4.23589849472046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05114507675171</t>
+    <t xml:space="preserve">4.05114459991455</t>
   </si>
   <si>
     <t xml:space="preserve">4.08473682403564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74210286140442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91677856445312</t>
+    <t xml:space="preserve">3.74210214614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91677832603455</t>
   </si>
   <si>
     <t xml:space="preserve">4.03099012374878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1552791595459</t>
+    <t xml:space="preserve">4.15527868270874</t>
   </si>
   <si>
     <t xml:space="preserve">4.12840604782104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01419448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1250467300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12168741226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94701075553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80256652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83615851402283</t>
+    <t xml:space="preserve">4.01419401168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12504577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1216869354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94701099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80256772041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83615922927856</t>
   </si>
   <si>
     <t xml:space="preserve">3.86975121498108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58086276054382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42970061302185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7521800994873</t>
+    <t xml:space="preserve">3.58086252212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42970085144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75217986106873</t>
   </si>
   <si>
     <t xml:space="preserve">3.60773611068726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84959506988525</t>
+    <t xml:space="preserve">3.84959530830383</t>
   </si>
   <si>
     <t xml:space="preserve">3.90670132637024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96716594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06458139419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8294403553009</t>
+    <t xml:space="preserve">3.96716690063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06458234786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82943964004517</t>
   </si>
   <si>
     <t xml:space="preserve">3.77233481407166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90334153175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87982821464539</t>
+    <t xml:space="preserve">3.90334224700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87982797622681</t>
   </si>
   <si>
     <t xml:space="preserve">3.72866582870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79584860801697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88318777084351</t>
+    <t xml:space="preserve">3.79584932327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88318705558777</t>
   </si>
   <si>
     <t xml:space="preserve">3.95708823204041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13176536560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1955885887146</t>
+    <t xml:space="preserve">4.13176488876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19558906555176</t>
   </si>
   <si>
     <t xml:space="preserve">4.18551111221313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13848304748535</t>
+    <t xml:space="preserve">4.13848257064819</t>
   </si>
   <si>
     <t xml:space="preserve">4.22246217727661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29972219467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35682773590088</t>
+    <t xml:space="preserve">4.29972267150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3568286895752</t>
   </si>
   <si>
     <t xml:space="preserve">4.25605344772339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27956819534302</t>
+    <t xml:space="preserve">4.2795672416687</t>
   </si>
   <si>
     <t xml:space="preserve">4.14856100082397</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">4.26949024200439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16535663604736</t>
+    <t xml:space="preserve">4.16535615921021</t>
   </si>
   <si>
     <t xml:space="preserve">4.09817266464233</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04778528213501</t>
+    <t xml:space="preserve">4.04778575897217</t>
   </si>
   <si>
     <t xml:space="preserve">4.04106712341309</t>
@@ -215,19 +215,19 @@
     <t xml:space="preserve">3.91006064414978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8193621635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75889825820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71186947822571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93357419967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82608151435852</t>
+    <t xml:space="preserve">3.8193633556366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75889778137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71187043190002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93357491493225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8260817527771</t>
   </si>
   <si>
     <t xml:space="preserve">4.0813775062561</t>
@@ -236,16 +236,16 @@
     <t xml:space="preserve">4.15863800048828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17879295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21238470077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21574401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2829270362854</t>
+    <t xml:space="preserve">4.17879343032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21238422393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21574354171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28292751312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.30308198928833</t>
@@ -254,55 +254,55 @@
     <t xml:space="preserve">4.35346937179565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19894790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07465934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08809518814087</t>
+    <t xml:space="preserve">4.1989483833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07465887069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08809614181519</t>
   </si>
   <si>
     <t xml:space="preserve">4.06122207641602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02427101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693399429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21648931503296</t>
+    <t xml:space="preserve">4.0242714881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693375587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21648979187012</t>
   </si>
   <si>
     <t xml:space="preserve">4.14420652389526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19927883148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25435256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23370027542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23714256286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49185228347778</t>
+    <t xml:space="preserve">4.19927930831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25435161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23369979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23714160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49185180664062</t>
   </si>
   <si>
     <t xml:space="preserve">4.4987359046936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47119951248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45743179321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46431541442871</t>
+    <t xml:space="preserve">4.47119998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45743227005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46431589126587</t>
   </si>
   <si>
     <t xml:space="preserve">4.37826538085938</t>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">4.3713812828064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28188800811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42989587783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34040260314941</t>
+    <t xml:space="preserve">4.28188848495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42989540100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34040212631226</t>
   </si>
   <si>
     <t xml:space="preserve">4.35072946548462</t>
@@ -335,16 +335,16 @@
     <t xml:space="preserve">3.91703271865845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98243188858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8688440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13732290267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33696031570435</t>
+    <t xml:space="preserve">3.98243165016174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884427070618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13732242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3369607925415</t>
   </si>
   <si>
     <t xml:space="preserve">4.38170719146729</t>
@@ -353,55 +353,55 @@
     <t xml:space="preserve">4.423011302948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52971458435059</t>
+    <t xml:space="preserve">4.52971410751343</t>
   </si>
   <si>
     <t xml:space="preserve">3.74148893356323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75181531906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73116302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65199542045593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52464079856873</t>
+    <t xml:space="preserve">3.75181460380554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73116278648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84130692481995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65199565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5246410369873</t>
   </si>
   <si>
     <t xml:space="preserve">3.42826414108276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50743126869202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65887975692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75525760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82065606117249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78623509407043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670704841614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96522212028503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95145320892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0409460067749</t>
+    <t xml:space="preserve">3.50743103027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65887999534607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75525712966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82065582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78623580932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670585632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9652214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95145344734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04094552993774</t>
   </si>
   <si>
     <t xml:space="preserve">4.01340961456299</t>
@@ -410,10 +410,10 @@
     <t xml:space="preserve">3.9445686340332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98931527137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95833730697632</t>
+    <t xml:space="preserve">3.98931503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95833706855774</t>
   </si>
   <si>
     <t xml:space="preserve">3.79656147956848</t>
@@ -422,85 +422,85 @@
     <t xml:space="preserve">3.90326428413391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80000329017639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68641662597656</t>
+    <t xml:space="preserve">3.80000400543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68641638755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.70018458366394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76558375358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362710952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66576457023621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66920638084412</t>
+    <t xml:space="preserve">3.76558327674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362639427185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66576433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6692066192627</t>
   </si>
   <si>
     <t xml:space="preserve">3.55217719078064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48677825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47989463806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37319207191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3718147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50054693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68985915184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561923980713</t>
+    <t xml:space="preserve">3.4867787361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47989511489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37319183349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37181496620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50054669380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68985843658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561900138855</t>
   </si>
   <si>
     <t xml:space="preserve">3.45235848426819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47645282745361</t>
+    <t xml:space="preserve">3.47645330429077</t>
   </si>
   <si>
     <t xml:space="preserve">3.64511203765869</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72083687782288</t>
+    <t xml:space="preserve">3.72083735466003</t>
   </si>
   <si>
     <t xml:space="preserve">3.70706915855408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77935123443604</t>
+    <t xml:space="preserve">3.77935099601746</t>
   </si>
   <si>
     <t xml:space="preserve">3.80688810348511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61413359642029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757612228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57971334457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56594514846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49366235733032</t>
+    <t xml:space="preserve">3.61413431167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757588386536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57971358299255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5659453868866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49366307258606</t>
   </si>
   <si>
     <t xml:space="preserve">3.49022078514099</t>
@@ -509,28 +509,28 @@
     <t xml:space="preserve">3.4489164352417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63822817802429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49710512161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38696002960205</t>
+    <t xml:space="preserve">3.63822746276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49710488319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38695979118347</t>
   </si>
   <si>
     <t xml:space="preserve">3.35804629325867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37456798553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31123471260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32638001441956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35529327392578</t>
+    <t xml:space="preserve">3.37456846237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31123495101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3263795375824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3552930355072</t>
   </si>
   <si>
     <t xml:space="preserve">3.41587281227112</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">3.48333644866943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51087260246277</t>
+    <t xml:space="preserve">3.51087307929993</t>
   </si>
   <si>
     <t xml:space="preserve">3.51775717735291</t>
@@ -551,19 +551,19 @@
     <t xml:space="preserve">3.47301077842712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57627177238464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53496742248535</t>
+    <t xml:space="preserve">3.57627201080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53496718406677</t>
   </si>
   <si>
     <t xml:space="preserve">3.64855432510376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67953276634216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.596923828125</t>
+    <t xml:space="preserve">3.67953300476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59692358970642</t>
   </si>
   <si>
     <t xml:space="preserve">3.6416699886322</t>
@@ -572,103 +572,103 @@
     <t xml:space="preserve">3.63134431838989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56250405311584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53152537345886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4558002948761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41174268722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4296407699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45924282073975</t>
+    <t xml:space="preserve">3.56250381469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5315248966217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45580005645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41174221038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42964053153992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45924258232117</t>
   </si>
   <si>
     <t xml:space="preserve">3.44203186035156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52808284759521</t>
+    <t xml:space="preserve">3.52808308601379</t>
   </si>
   <si>
     <t xml:space="preserve">3.63478636741638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67609095573425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62790179252625</t>
+    <t xml:space="preserve">3.67609071731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62790203094482</t>
   </si>
   <si>
     <t xml:space="preserve">3.58659768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5452938079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55906128883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56938695907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71739482879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94112658500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00996780395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88605403900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9721052646637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83442449569702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92735862731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98587369918823</t>
+    <t xml:space="preserve">3.54529333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55906105041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56938767433167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71739506721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94112682342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00996732711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88605451583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97210597991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83442425727844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92735838890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98587346076965</t>
   </si>
   <si>
     <t xml:space="preserve">4.0547137260437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93080067634583</t>
+    <t xml:space="preserve">3.93080115318298</t>
   </si>
   <si>
     <t xml:space="preserve">4.04438781738281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06159782409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91014790534973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89982223510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05815601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07192373275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07880783081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03061962127686</t>
+    <t xml:space="preserve">4.061598777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91014862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.899822473526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05815649032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07192420959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07880830764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03062009811401</t>
   </si>
   <si>
     <t xml:space="preserve">4.19583702087402</t>
@@ -677,10 +677,10 @@
     <t xml:space="preserve">4.20960521697998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29565620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27844572067261</t>
+    <t xml:space="preserve">4.29565572738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27844667434692</t>
   </si>
   <si>
     <t xml:space="preserve">4.24746751785278</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">4.13043880462646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.202721118927</t>
+    <t xml:space="preserve">4.20272207260132</t>
   </si>
   <si>
     <t xml:space="preserve">4.10634469985962</t>
@@ -704,28 +704,28 @@
     <t xml:space="preserve">4.12011289596558</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17862796783447</t>
+    <t xml:space="preserve">4.17862701416016</t>
   </si>
   <si>
     <t xml:space="preserve">4.24058389663696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14764833450317</t>
+    <t xml:space="preserve">4.14764928817749</t>
   </si>
   <si>
     <t xml:space="preserve">4.16141653060913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04783010482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14076471328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1510910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15453243255615</t>
+    <t xml:space="preserve">4.04782962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1407642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15109157562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15453290939331</t>
   </si>
   <si>
     <t xml:space="preserve">4.18206930160522</t>
@@ -734,28 +734,28 @@
     <t xml:space="preserve">4.15797472000122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21304702758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32319307327271</t>
+    <t xml:space="preserve">4.21304750442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32319259643555</t>
   </si>
   <si>
     <t xml:space="preserve">4.36449670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43333768844604</t>
+    <t xml:space="preserve">4.43333721160889</t>
   </si>
   <si>
     <t xml:space="preserve">4.44022178649902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38514947891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4746413230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41956853866577</t>
+    <t xml:space="preserve">4.3851490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47464227676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41956996917725</t>
   </si>
   <si>
     <t xml:space="preserve">4.37482309341431</t>
@@ -764,25 +764,25 @@
     <t xml:space="preserve">4.41268491744995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34384536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30942487716675</t>
+    <t xml:space="preserve">4.34384441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30942440032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.36793947219849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35417127609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28533029556274</t>
+    <t xml:space="preserve">4.35417079925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28532981872559</t>
   </si>
   <si>
     <t xml:space="preserve">4.52627229690552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40580081939697</t>
+    <t xml:space="preserve">4.40580129623413</t>
   </si>
   <si>
     <t xml:space="preserve">4.48840999603271</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">4.50906276702881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53659820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54348278045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44710540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67083692550659</t>
+    <t xml:space="preserve">4.53659868240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54348230361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.447105884552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67083787918091</t>
   </si>
   <si>
     <t xml:space="preserve">4.69899702072144</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">4.71659564971924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83627080917358</t>
+    <t xml:space="preserve">4.83627033233643</t>
   </si>
   <si>
     <t xml:space="preserve">4.86091041564941</t>
@@ -821,16 +821,16 @@
     <t xml:space="preserve">4.85035037994385</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87850904464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78347253799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72011518478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68491792678833</t>
+    <t xml:space="preserve">4.87850856781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7834734916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72011566162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68491744995117</t>
   </si>
   <si>
     <t xml:space="preserve">4.7306752204895</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">4.75179433822632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81515121459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81163167953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9277868270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93834638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87498950958252</t>
+    <t xml:space="preserve">4.81515169143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81163215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92778635025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93834590911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87498903274536</t>
   </si>
   <si>
     <t xml:space="preserve">4.80811166763306</t>
@@ -860,37 +860,37 @@
     <t xml:space="preserve">4.80459213256836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78699254989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95946502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86442947387695</t>
+    <t xml:space="preserve">4.7869930267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95946550369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86442995071411</t>
   </si>
   <si>
     <t xml:space="preserve">4.89258861541748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89610767364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91370725631714</t>
+    <t xml:space="preserve">4.89610815048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9137077331543</t>
   </si>
   <si>
     <t xml:space="preserve">4.97354507446289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97706460952759</t>
+    <t xml:space="preserve">4.97706508636475</t>
   </si>
   <si>
     <t xml:space="preserve">4.94538593292236</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11081886291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25865268707275</t>
+    <t xml:space="preserve">5.1108193397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2586522102356</t>
   </si>
   <si>
     <t xml:space="preserve">5.06154108047485</t>
@@ -899,25 +899,25 @@
     <t xml:space="preserve">5.08617973327637</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10377883911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09673976898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05098104476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08969926834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01930236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04746198654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96650552749634</t>
+    <t xml:space="preserve">5.10377931594849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09673881530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0509819984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08970022201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01930332183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04746150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96650505065918</t>
   </si>
   <si>
     <t xml:space="preserve">4.91018772125244</t>
@@ -926,49 +926,49 @@
     <t xml:space="preserve">5.00874280929565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10025930404663</t>
+    <t xml:space="preserve">5.10025882720947</t>
   </si>
   <si>
     <t xml:space="preserve">5.06858062744141</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1319375038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04042100906372</t>
+    <t xml:space="preserve">5.13193798065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04042196273804</t>
   </si>
   <si>
     <t xml:space="preserve">5.1248984336853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20937490463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36424827575684</t>
+    <t xml:space="preserve">5.20937442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36424779891968</t>
   </si>
   <si>
     <t xml:space="preserve">5.21289443969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03690242767334</t>
+    <t xml:space="preserve">5.03690147399902</t>
   </si>
   <si>
     <t xml:space="preserve">5.16361665725708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27273225784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23049402236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15305662155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2023344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11433887481689</t>
+    <t xml:space="preserve">5.27273178100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23049306869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15305757522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20233488082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11433839797974</t>
   </si>
   <si>
     <t xml:space="preserve">5.10729932785034</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">5.00522327423096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9981837272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01226329803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04394149780273</t>
+    <t xml:space="preserve">4.99818420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01226234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04394197463989</t>
   </si>
   <si>
     <t xml:space="preserve">5.06506109237671</t>
@@ -992,37 +992,37 @@
     <t xml:space="preserve">5.15657711029053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34312868118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30089092254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27977132797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30792999267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25161266326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29385042190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29033088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33608913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34664821624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36776733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35368871688843</t>
+    <t xml:space="preserve">5.34312915802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30089044570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27977180480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30793046951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2516131401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29385089874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29033136367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33608865737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34664869308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36776828765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35368824005127</t>
   </si>
   <si>
     <t xml:space="preserve">5.38536739349365</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">5.39944648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26569175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31145048141479</t>
+    <t xml:space="preserve">5.26569223403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31145000457764</t>
   </si>
   <si>
     <t xml:space="preserve">5.3255295753479</t>
@@ -1046,55 +1046,55 @@
     <t xml:space="preserve">5.23401355743408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21641397476196</t>
+    <t xml:space="preserve">5.2164134979248</t>
   </si>
   <si>
     <t xml:space="preserve">5.14249753952026</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16713619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31497001647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29736995697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19177532196045</t>
+    <t xml:space="preserve">5.16713666915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31497049331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29737138748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19177579879761</t>
   </si>
   <si>
     <t xml:space="preserve">5.35720777511597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0721001625061</t>
+    <t xml:space="preserve">5.07210111618042</t>
   </si>
   <si>
     <t xml:space="preserve">4.9841046333313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94186639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86794900894165</t>
+    <t xml:space="preserve">4.94186544418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86794996261597</t>
   </si>
   <si>
     <t xml:space="preserve">4.92426681518555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98058462142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03338193893433</t>
+    <t xml:space="preserve">4.98058414459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03338146209717</t>
   </si>
   <si>
     <t xml:space="preserve">5.05450105667114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1847357749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17417621612549</t>
+    <t xml:space="preserve">5.18473482131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17417573928833</t>
   </si>
   <si>
     <t xml:space="preserve">5.21993398666382</t>
@@ -1106,22 +1106,22 @@
     <t xml:space="preserve">5.22697401046753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28681087493896</t>
+    <t xml:space="preserve">5.28681135177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.02282285690308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0017032623291</t>
+    <t xml:space="preserve">5.00170373916626</t>
   </si>
   <si>
     <t xml:space="preserve">5.02986192703247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.058021068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92074775695801</t>
+    <t xml:space="preserve">5.05802059173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92074680328369</t>
   </si>
   <si>
     <t xml:space="preserve">4.99114370346069</t>
@@ -1133,19 +1133,19 @@
     <t xml:space="preserve">5.47688341140747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48392295837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44168472290039</t>
+    <t xml:space="preserve">5.48392248153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44168424606323</t>
   </si>
   <si>
     <t xml:space="preserve">5.43464469909668</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5261607170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51208162307739</t>
+    <t xml:space="preserve">5.52616024017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51208114624023</t>
   </si>
   <si>
     <t xml:space="preserve">5.46984338760376</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">5.40648603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37832641601562</t>
+    <t xml:space="preserve">5.37832736968994</t>
   </si>
   <si>
     <t xml:space="preserve">5.18825578689575</t>
@@ -1163,52 +1163,52 @@
     <t xml:space="preserve">5.13897800445557</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32904863357544</t>
+    <t xml:space="preserve">5.3290491104126</t>
   </si>
   <si>
     <t xml:space="preserve">5.14601755142212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1952953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24457311630249</t>
+    <t xml:space="preserve">5.19529485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24457359313965</t>
   </si>
   <si>
     <t xml:space="preserve">5.22345447540283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23753356933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16009664535522</t>
+    <t xml:space="preserve">5.23753261566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16009712219238</t>
   </si>
   <si>
     <t xml:space="preserve">5.11785888671875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97002506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21899938583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14661359786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98012733459473</t>
+    <t xml:space="preserve">4.97002458572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2189998626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14661407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98012781143188</t>
   </si>
   <si>
     <t xml:space="preserve">4.94393396377563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81364011764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84259510040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85707139968872</t>
+    <t xml:space="preserve">4.81363964080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84259462356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85707187652588</t>
   </si>
   <si>
     <t xml:space="preserve">4.82087898254395</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">4.8064022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5602912902832</t>
+    <t xml:space="preserve">4.56029081344604</t>
   </si>
   <si>
     <t xml:space="preserve">4.46618938446045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21284055709839</t>
+    <t xml:space="preserve">4.21283960342407</t>
   </si>
   <si>
     <t xml:space="preserve">4.45171308517456</t>
@@ -1232,16 +1232,16 @@
     <t xml:space="preserve">4.37208843231201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52409887313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40828132629395</t>
+    <t xml:space="preserve">4.52409839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4082818031311</t>
   </si>
   <si>
     <t xml:space="preserve">4.34313440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29246425628662</t>
+    <t xml:space="preserve">4.29246473312378</t>
   </si>
   <si>
     <t xml:space="preserve">4.3938045501709</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">4.45895099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4372353553772</t>
+    <t xml:space="preserve">4.43723487854004</t>
   </si>
   <si>
     <t xml:space="preserve">4.53133678436279</t>
@@ -1259,31 +1259,31 @@
     <t xml:space="preserve">4.61096048355103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6471529006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69058465957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57476806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58200645446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48790550231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54581451416016</t>
+    <t xml:space="preserve">4.64715337753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69058513641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57476854324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58200693130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48790454864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.545814037323</t>
   </si>
   <si>
     <t xml:space="preserve">4.5892448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60372161865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68334627151489</t>
+    <t xml:space="preserve">4.6037220954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68334674835205</t>
   </si>
   <si>
     <t xml:space="preserve">4.69782304763794</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">4.61819934844971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56752920150757</t>
+    <t xml:space="preserve">4.56752967834473</t>
   </si>
   <si>
     <t xml:space="preserve">4.44447374343872</t>
@@ -1313,34 +1313,34 @@
     <t xml:space="preserve">4.47342824935913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51685953140259</t>
+    <t xml:space="preserve">4.51686000823975</t>
   </si>
   <si>
     <t xml:space="preserve">4.50962066650391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1766471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10426139831543</t>
+    <t xml:space="preserve">4.17664766311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10426187515259</t>
   </si>
   <si>
     <t xml:space="preserve">4.04635334014893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0246376991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03187608718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05359172821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0680685043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97396755218506</t>
+    <t xml:space="preserve">4.02463722229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03187656402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05359220504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06806945800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97396731376648</t>
   </si>
   <si>
     <t xml:space="preserve">4.00292205810547</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">3.85091233253479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87262773513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93053650856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9232976436615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11149978637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22731781005859</t>
+    <t xml:space="preserve">3.87262749671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9305362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92329740524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11150074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22731733322144</t>
   </si>
   <si>
     <t xml:space="preserve">4.20560169219971</t>
@@ -1388,28 +1388,28 @@
     <t xml:space="preserve">4.35761117935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26351070404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09702348709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06083106994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12597751617432</t>
+    <t xml:space="preserve">4.26350975036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09702301025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06083059310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12597703933716</t>
   </si>
   <si>
     <t xml:space="preserve">3.90882062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84367299079895</t>
+    <t xml:space="preserve">3.84367370605469</t>
   </si>
   <si>
     <t xml:space="preserve">3.7857654094696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8798668384552</t>
+    <t xml:space="preserve">3.87986660003662</t>
   </si>
   <si>
     <t xml:space="preserve">3.94501352310181</t>
@@ -1418,70 +1418,70 @@
     <t xml:space="preserve">3.80748105049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72061824798584</t>
+    <t xml:space="preserve">3.72061848640442</t>
   </si>
   <si>
     <t xml:space="preserve">3.68442583084106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57946610450745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45641136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55051231384277</t>
+    <t xml:space="preserve">3.57946634292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45641088485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55051207542419</t>
   </si>
   <si>
     <t xml:space="preserve">3.81471967697144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76404976844788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82919645309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83643555641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85815119743347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74233388900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75681066513062</t>
+    <t xml:space="preserve">3.7640495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82919669151306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83643531799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85815095901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74233365058899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75681114196777</t>
   </si>
   <si>
     <t xml:space="preserve">3.70614099502563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67718720436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63375568389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66994857788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61927843093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64099478721619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77128767967224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80024218559265</t>
+    <t xml:space="preserve">3.67718696594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63375544548035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66994833946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61927819252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64099383354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7712881565094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80024266242981</t>
   </si>
   <si>
     <t xml:space="preserve">3.66270995140076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7278573513031</t>
+    <t xml:space="preserve">3.72785663604736</t>
   </si>
   <si>
     <t xml:space="preserve">3.86538982391357</t>
@@ -1490,31 +1490,31 @@
     <t xml:space="preserve">3.60480141639709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58670520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57584691047668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54327368736267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547156333923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82195806503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71338057518005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69890284538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69166398048401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62651705741882</t>
+    <t xml:space="preserve">3.58670496940613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57584738731384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54327392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82195830345154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71338033676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69890260696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69166374206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6265172958374</t>
   </si>
   <si>
     <t xml:space="preserve">3.64823269844055</t>
@@ -1526,43 +1526,43 @@
     <t xml:space="preserve">3.60118174552917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54689359664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50346231460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60842084884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79300308227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88710474967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56498980522156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59394407272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7785267829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58308553695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53965377807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48174595832825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49622249603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.452791929245</t>
+    <t xml:space="preserve">3.54689311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50346183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60842108726501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79300332069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88710498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56498956680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59394359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77852702140808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58308601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53965425491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48174571990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49622297286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45279169082642</t>
   </si>
   <si>
     <t xml:space="preserve">3.42021822929382</t>
@@ -1571,31 +1571,31 @@
     <t xml:space="preserve">3.431556224823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43533539772034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41265964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33329582214355</t>
+    <t xml:space="preserve">3.43533563613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41265940666199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33329558372498</t>
   </si>
   <si>
     <t xml:space="preserve">3.34841251373291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38620519638062</t>
+    <t xml:space="preserve">3.38620495796204</t>
   </si>
   <si>
     <t xml:space="preserve">3.3710880279541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36352968215942</t>
+    <t xml:space="preserve">3.36352944374084</t>
   </si>
   <si>
     <t xml:space="preserve">3.3824257850647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31062006950378</t>
+    <t xml:space="preserve">3.31062030792236</t>
   </si>
   <si>
     <t xml:space="preserve">3.32573676109314</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">3.29172396659851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25393104553223</t>
+    <t xml:space="preserve">3.25393128395081</t>
   </si>
   <si>
     <t xml:space="preserve">3.3143994808197</t>
@@ -1613,16 +1613,16 @@
     <t xml:space="preserve">3.33707523345947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27660655975342</t>
+    <t xml:space="preserve">3.276606798172</t>
   </si>
   <si>
     <t xml:space="preserve">3.28038644790649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23503565788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20480108261108</t>
+    <t xml:space="preserve">3.23503541946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2048008441925</t>
   </si>
   <si>
     <t xml:space="preserve">3.21613883972168</t>
@@ -1631,16 +1631,16 @@
     <t xml:space="preserve">3.23125576972961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21235990524292</t>
+    <t xml:space="preserve">3.21235966682434</t>
   </si>
   <si>
     <t xml:space="preserve">3.24259376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18212556838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13677477836609</t>
+    <t xml:space="preserve">3.18212532997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13677501678467</t>
   </si>
   <si>
     <t xml:space="preserve">3.1518919467926</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">3.25015234947205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39376330375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59784293174744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65831089019775</t>
+    <t xml:space="preserve">3.39376354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59784269332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65831065177917</t>
   </si>
   <si>
     <t xml:space="preserve">3.55627059936523</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">3.5524914264679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56760907173157</t>
+    <t xml:space="preserve">3.56760883331299</t>
   </si>
   <si>
     <t xml:space="preserve">3.57516741752625</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">3.43911457061768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4277765750885</t>
+    <t xml:space="preserve">3.42777681350708</t>
   </si>
   <si>
     <t xml:space="preserve">3.40132212638855</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">3.36730885505676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40888047218323</t>
+    <t xml:space="preserve">3.40888071060181</t>
   </si>
   <si>
     <t xml:space="preserve">3.34085440635681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4239981174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51469969749451</t>
+    <t xml:space="preserve">3.42399787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51469945907593</t>
   </si>
   <si>
     <t xml:space="preserve">3.49958229064941</t>
@@ -1733,40 +1733,40 @@
     <t xml:space="preserve">3.63941431045532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65453147888184</t>
+    <t xml:space="preserve">3.65453195571899</t>
   </si>
   <si>
     <t xml:space="preserve">3.68098640441895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67342782020569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73011660575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78680539131165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285823822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86239004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74523305892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76790904998779</t>
+    <t xml:space="preserve">3.67342829704285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73011636734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78680515289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285847663879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8623902797699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7452335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76790928840637</t>
   </si>
   <si>
     <t xml:space="preserve">3.83971476554871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83215618133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168774604797</t>
+    <t xml:space="preserve">3.83215570449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168798446655</t>
   </si>
   <si>
     <t xml:space="preserve">3.73767495155334</t>
@@ -1775,13 +1775,13 @@
     <t xml:space="preserve">3.69232368469238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70366215705872</t>
+    <t xml:space="preserve">3.70366191864014</t>
   </si>
   <si>
     <t xml:space="preserve">3.77924680709839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68854451179504</t>
+    <t xml:space="preserve">3.68854475021362</t>
   </si>
   <si>
     <t xml:space="preserve">3.66586923599243</t>
@@ -1790,40 +1790,40 @@
     <t xml:space="preserve">3.69610285758972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66964888572693</t>
+    <t xml:space="preserve">3.66964864730835</t>
   </si>
   <si>
     <t xml:space="preserve">3.73389577865601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81703948974609</t>
+    <t xml:space="preserve">3.81703925132751</t>
   </si>
   <si>
     <t xml:space="preserve">3.84727311134338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90018248558044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98332595825195</t>
+    <t xml:space="preserve">3.90018272399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98332619667053</t>
   </si>
   <si>
     <t xml:space="preserve">3.96065044403076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95309209823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93041610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94553351402283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99088478088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91529941558838</t>
+    <t xml:space="preserve">3.95309257507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93041634559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94553327560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99088454246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9152991771698</t>
   </si>
   <si>
     <t xml:space="preserve">4.02111864089966</t>
@@ -1835,40 +1835,40 @@
     <t xml:space="preserve">4.03623580932617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06646966934204</t>
+    <t xml:space="preserve">4.06646919250488</t>
   </si>
   <si>
     <t xml:space="preserve">4.0815863609314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1344952583313</t>
+    <t xml:space="preserve">4.13449573516846</t>
   </si>
   <si>
     <t xml:space="preserve">4.05135250091553</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02867650985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00600147247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04379415512085</t>
+    <t xml:space="preserve">4.02867698669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0060019493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04379367828369</t>
   </si>
   <si>
     <t xml:space="preserve">4.1193790435791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01356029510498</t>
+    <t xml:space="preserve">4.01355981826782</t>
   </si>
   <si>
     <t xml:space="preserve">3.96820902824402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93797516822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9757673740387</t>
+    <t xml:space="preserve">3.93797492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97576785087585</t>
   </si>
   <si>
     <t xml:space="preserve">3.90774130821228</t>
@@ -1880,64 +1880,64 @@
     <t xml:space="preserve">3.88506555557251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87750697135925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85483169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.801922082901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59406352043152</t>
+    <t xml:space="preserve">3.87750673294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85483193397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80192232131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5940637588501</t>
   </si>
   <si>
     <t xml:space="preserve">3.60162162780762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65075206756592</t>
+    <t xml:space="preserve">3.65075182914734</t>
   </si>
   <si>
     <t xml:space="preserve">3.71877884864807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99844288825989</t>
+    <t xml:space="preserve">3.99844264984131</t>
   </si>
   <si>
     <t xml:space="preserve">3.72255778312683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63185596466064</t>
+    <t xml:space="preserve">3.63185572624207</t>
   </si>
   <si>
     <t xml:space="preserve">3.46556949615479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44667315483093</t>
+    <t xml:space="preserve">3.44667291641235</t>
   </si>
   <si>
     <t xml:space="preserve">3.28416562080383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11031985282898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06496906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83821415901184</t>
+    <t xml:space="preserve">3.11032009124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0649688243866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83821439743042</t>
   </si>
   <si>
     <t xml:space="preserve">2.83443522453308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95915007591248</t>
+    <t xml:space="preserve">2.95915031433105</t>
   </si>
   <si>
     <t xml:space="preserve">2.70972013473511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93269538879395</t>
+    <t xml:space="preserve">2.93269562721252</t>
   </si>
   <si>
     <t xml:space="preserve">3.00450086593628</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">2.94403314590454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91001987457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96292948722839</t>
+    <t xml:space="preserve">2.91001963615417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96292924880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.85333132743835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8949031829834</t>
+    <t xml:space="preserve">2.89490294456482</t>
   </si>
   <si>
     <t xml:space="preserve">2.88734436035156</t>
@@ -1976,10 +1976,10 @@
     <t xml:space="preserve">2.82687664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8911235332489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99694275856018</t>
+    <t xml:space="preserve">2.89112377166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9969425201416</t>
   </si>
   <si>
     <t xml:space="preserve">2.9515917301178</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">3.03473496437073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02717685699463</t>
+    <t xml:space="preserve">3.02717661857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.12165760993958</t>
@@ -2006,31 +2006,31 @@
     <t xml:space="preserve">3.06118988990784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09898209571838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16700887680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14433336257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19346356391907</t>
+    <t xml:space="preserve">3.09898233413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16700911521912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14433312416077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19346380233765</t>
   </si>
   <si>
     <t xml:space="preserve">3.21991848945618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26904821395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3219575881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15944981575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07252740859985</t>
+    <t xml:space="preserve">3.26904797554016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32195782661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1594500541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07252764701843</t>
   </si>
   <si>
     <t xml:space="preserve">3.06874847412109</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">3.1632297039032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27282738685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28794479370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40510129928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51091957092285</t>
+    <t xml:space="preserve">3.2728271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28794503211975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40510153770447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51091980934143</t>
   </si>
   <si>
     <t xml:space="preserve">3.48824453353882</t>
@@ -2060,16 +2060,16 @@
     <t xml:space="preserve">3.45801043510437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29550337791443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34463334083557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29928207397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30684089660645</t>
+    <t xml:space="preserve">3.29550313949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34463381767273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29928183555603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30684065818787</t>
   </si>
   <si>
     <t xml:space="preserve">3.30306148529053</t>
@@ -2084,40 +2084,40 @@
     <t xml:space="preserve">3.3748676776886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26526927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39754295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4806866645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38998436927795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31817841529846</t>
+    <t xml:space="preserve">3.2652690410614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39754271507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48068642616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38998413085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31817865371704</t>
   </si>
   <si>
     <t xml:space="preserve">3.25771045684814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2274763584137</t>
+    <t xml:space="preserve">3.22747659683228</t>
   </si>
   <si>
     <t xml:space="preserve">3.18590474128723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24637317657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17456674575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14055466651917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17834663391113</t>
+    <t xml:space="preserve">3.24637293815613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17456698417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14055442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17834615707397</t>
   </si>
   <si>
     <t xml:space="preserve">3.09142398834229</t>
@@ -2129,16 +2129,16 @@
     <t xml:space="preserve">3.04607319831848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01583886146545</t>
+    <t xml:space="preserve">3.01583909988403</t>
   </si>
   <si>
     <t xml:space="preserve">2.94025373458862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95537066459656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92513680458069</t>
+    <t xml:space="preserve">2.95537090301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92513704299927</t>
   </si>
   <si>
     <t xml:space="preserve">2.88356518745422</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">2.80042171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78908395767212</t>
+    <t xml:space="preserve">2.7890841960907</t>
   </si>
   <si>
     <t xml:space="preserve">2.77018761634827</t>
@@ -2156,16 +2156,16 @@
     <t xml:space="preserve">2.75129175186157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71727848052979</t>
+    <t xml:space="preserve">2.71727824211121</t>
   </si>
   <si>
     <t xml:space="preserve">2.72105741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67948627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55477070808411</t>
+    <t xml:space="preserve">2.67948603630066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55477094650269</t>
   </si>
   <si>
     <t xml:space="preserve">2.44895172119141</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">2.61523866653442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69838190078735</t>
+    <t xml:space="preserve">2.69838213920593</t>
   </si>
   <si>
     <t xml:space="preserve">2.98938417434692</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">3.53737473487854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62807679176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63563513755798</t>
+    <t xml:space="preserve">3.62807703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6356348991394</t>
   </si>
   <si>
     <t xml:space="preserve">3.57894682884216</t>
@@ -2201,64 +2201,64 @@
     <t xml:space="preserve">3.50714063644409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48446583747864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52225780487061</t>
+    <t xml:space="preserve">3.48446559906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52225804328918</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12543702125549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80948114395142</t>
+    <t xml:space="preserve">3.12543725967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80948066711426</t>
   </si>
   <si>
     <t xml:space="preserve">3.76035070419312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64319396018982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68476557731628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74901247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79436349868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75657153129578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77546691894531</t>
+    <t xml:space="preserve">3.64319372177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68476533889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74901270866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79436373710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7565712928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77546739578247</t>
   </si>
   <si>
     <t xml:space="preserve">3.76412987709045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15717124938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11182069778442</t>
+    <t xml:space="preserve">4.15717172622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11182022094727</t>
   </si>
   <si>
     <t xml:space="preserve">4.17228841781616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3134560585022</t>
+    <t xml:space="preserve">4.31345558166504</t>
   </si>
   <si>
     <t xml:space="preserve">4.22718667984009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12523317337036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07817602157593</t>
+    <t xml:space="preserve">4.1252326965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07817649841309</t>
   </si>
   <si>
     <t xml:space="preserve">4.08601951599121</t>
@@ -2270,16 +2270,16 @@
     <t xml:space="preserve">4.20365905761719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26639986038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27424287796021</t>
+    <t xml:space="preserve">4.26640033721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27424240112305</t>
   </si>
   <si>
     <t xml:space="preserve">4.25855731964111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36835432052612</t>
+    <t xml:space="preserve">4.36835479736328</t>
   </si>
   <si>
     <t xml:space="preserve">4.32914113998413</t>
@@ -2288,25 +2288,25 @@
     <t xml:space="preserve">4.34482622146606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35266971588135</t>
+    <t xml:space="preserve">4.35267019271851</t>
   </si>
   <si>
     <t xml:space="preserve">4.30561304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28992795944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28208494186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19581604003906</t>
+    <t xml:space="preserve">4.28992748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28208541870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19581651687622</t>
   </si>
   <si>
     <t xml:space="preserve">4.03896331787109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02327871322632</t>
+    <t xml:space="preserve">4.023277759552</t>
   </si>
   <si>
     <t xml:space="preserve">3.99974989891052</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">4.00759315490723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96053719520569</t>
+    <t xml:space="preserve">3.96053671836853</t>
   </si>
   <si>
     <t xml:space="preserve">4.03112030029297</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">4.05464887619019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93700861930847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9213240146637</t>
+    <t xml:space="preserve">3.93700885772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92132377624512</t>
   </si>
   <si>
     <t xml:space="preserve">4.01543521881104</t>
@@ -2336,10 +2336,10 @@
     <t xml:space="preserve">4.07033395767212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97622203826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18797397613525</t>
+    <t xml:space="preserve">3.9762225151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1879734992981</t>
   </si>
   <si>
     <t xml:space="preserve">4.24287176132202</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">4.43109560012817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42325258255005</t>
+    <t xml:space="preserve">4.42325305938721</t>
   </si>
   <si>
     <t xml:space="preserve">4.38403940200806</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">4.39972543716431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33698463439941</t>
+    <t xml:space="preserve">4.33698415756226</t>
   </si>
   <si>
     <t xml:space="preserve">4.36051177978516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46246671676636</t>
+    <t xml:space="preserve">4.4624662399292</t>
   </si>
   <si>
     <t xml:space="preserve">4.44678068161011</t>
@@ -2381,25 +2381,25 @@
     <t xml:space="preserve">4.4389386177063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47815179824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4859938621521</t>
+    <t xml:space="preserve">4.47815132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48599433898926</t>
   </si>
   <si>
     <t xml:space="preserve">4.50167989730835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5644211769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60363435745239</t>
+    <t xml:space="preserve">4.56442070007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60363388061523</t>
   </si>
   <si>
     <t xml:space="preserve">4.62716197967529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6350040435791</t>
+    <t xml:space="preserve">4.63500452041626</t>
   </si>
   <si>
     <t xml:space="preserve">4.49383640289307</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">4.59579086303711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66637516021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68206024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72911643981934</t>
+    <t xml:space="preserve">4.66637468338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68205976486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72911691665649</t>
   </si>
   <si>
     <t xml:space="preserve">4.64284753799438</t>
@@ -2423,10 +2423,10 @@
     <t xml:space="preserve">4.74480152130127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86244106292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90949726104736</t>
+    <t xml:space="preserve">4.8624415397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90949773788452</t>
   </si>
   <si>
     <t xml:space="preserve">5.05850744247437</t>
@@ -2441,13 +2441,13 @@
     <t xml:space="preserve">4.95655298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94870948791504</t>
+    <t xml:space="preserve">4.9487099647522</t>
   </si>
   <si>
     <t xml:space="preserve">4.97223854064941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87028455734253</t>
+    <t xml:space="preserve">4.87028408050537</t>
   </si>
   <si>
     <t xml:space="preserve">4.98008108139038</t>
@@ -2456,19 +2456,19 @@
     <t xml:space="preserve">5.0741925239563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05066394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02713680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08987808227539</t>
+    <t xml:space="preserve">5.05066442489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02713632583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08987760543823</t>
   </si>
   <si>
     <t xml:space="preserve">5.19183254241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18399000167847</t>
+    <t xml:space="preserve">5.18398952484131</t>
   </si>
   <si>
     <t xml:space="preserve">5.16830492019653</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">5.14477634429932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23888778686523</t>
+    <t xml:space="preserve">5.23888826370239</t>
   </si>
   <si>
     <t xml:space="preserve">5.21536064147949</t>
@@ -2498,31 +2498,31 @@
     <t xml:space="preserve">5.01929473876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93302488327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79969930648804</t>
+    <t xml:space="preserve">4.93302536010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7996997833252</t>
   </si>
   <si>
     <t xml:space="preserve">4.76048707962036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76833009719849</t>
+    <t xml:space="preserve">4.76832962036133</t>
   </si>
   <si>
     <t xml:space="preserve">4.68990325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69774484634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6114764213562</t>
+    <t xml:space="preserve">4.69774532318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61147689819336</t>
   </si>
   <si>
     <t xml:space="preserve">4.53305006027222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50952196121216</t>
+    <t xml:space="preserve">4.50952243804932</t>
   </si>
   <si>
     <t xml:space="preserve">4.47030878067017</t>
@@ -2534,25 +2534,25 @@
     <t xml:space="preserve">4.54873514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57226324081421</t>
+    <t xml:space="preserve">4.57226371765137</t>
   </si>
   <si>
     <t xml:space="preserve">4.52520751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54089307785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51736497879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58010625839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82322788238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87812662124634</t>
+    <t xml:space="preserve">4.54089260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51736450195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58010578155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82322835922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87812614440918</t>
   </si>
   <si>
     <t xml:space="preserve">4.8859691619873</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">4.77617263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85459899902344</t>
+    <t xml:space="preserve">4.85459852218628</t>
   </si>
   <si>
     <t xml:space="preserve">4.94086790084839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52122402191162</t>
+    <t xml:space="preserve">5.52122354507446</t>
   </si>
   <si>
     <t xml:space="preserve">5.66239070892334</t>
@@ -2591,13 +2591,13 @@
     <t xml:space="preserve">5.68591928482056</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70160436630249</t>
+    <t xml:space="preserve">5.70160484313965</t>
   </si>
   <si>
     <t xml:space="preserve">5.59964990615845</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53690910339355</t>
+    <t xml:space="preserve">5.5369086265564</t>
   </si>
   <si>
     <t xml:space="preserve">5.52906656265259</t>
@@ -2615,25 +2615,25 @@
     <t xml:space="preserve">4.41541051864624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89381170272827</t>
+    <t xml:space="preserve">4.89381122589111</t>
   </si>
   <si>
     <t xml:space="preserve">4.81538534164429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9251823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84675550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72127342224121</t>
+    <t xml:space="preserve">4.92518281936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84675598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72127389907837</t>
   </si>
   <si>
     <t xml:space="preserve">4.5879487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61931896209717</t>
+    <t xml:space="preserve">4.61931943893433</t>
   </si>
   <si>
     <t xml:space="preserve">4.70558834075928</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">4.73861026763916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69733333587646</t>
+    <t xml:space="preserve">4.69733285903931</t>
   </si>
   <si>
     <t xml:space="preserve">4.63954496383667</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">4.7963981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98627281188965</t>
+    <t xml:space="preserve">4.98627233505249</t>
   </si>
   <si>
     <t xml:space="preserve">4.95325136184692</t>
@@ -2666,19 +2666,19 @@
     <t xml:space="preserve">5.07708215713501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11835908889771</t>
+    <t xml:space="preserve">5.11835956573486</t>
   </si>
   <si>
     <t xml:space="preserve">4.97801733016968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06057214736938</t>
+    <t xml:space="preserve">5.06057167053223</t>
   </si>
   <si>
     <t xml:space="preserve">4.9037184715271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96976184844971</t>
+    <t xml:space="preserve">4.96976232528687</t>
   </si>
   <si>
     <t xml:space="preserve">4.87069702148438</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">4.62303400039673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40839385986328</t>
+    <t xml:space="preserve">4.40839338302612</t>
   </si>
   <si>
     <t xml:space="preserve">4.50745820999146</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">4.61477851867676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5735011100769</t>
+    <t xml:space="preserve">4.57350158691406</t>
   </si>
   <si>
     <t xml:space="preserve">4.51571369171143</t>
@@ -2729,31 +2729,31 @@
     <t xml:space="preserve">4.38362693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16898679733276</t>
+    <t xml:space="preserve">4.16898632049561</t>
   </si>
   <si>
     <t xml:space="preserve">4.2680516242981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39188289642334</t>
+    <t xml:space="preserve">4.39188241958618</t>
   </si>
   <si>
     <t xml:space="preserve">4.4661808013916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42490434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3753719329834</t>
+    <t xml:space="preserve">4.42490482330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37537240982056</t>
   </si>
   <si>
     <t xml:space="preserve">4.27630662918091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44966983795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34235048294067</t>
+    <t xml:space="preserve">4.44967031478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34235000610352</t>
   </si>
   <si>
     <t xml:space="preserve">4.41664886474609</t>
@@ -2780,19 +2780,19 @@
     <t xml:space="preserve">4.72209930419922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7551212310791</t>
+    <t xml:space="preserve">4.75512075424194</t>
   </si>
   <si>
     <t xml:space="preserve">4.77988719940186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73035430908203</t>
+    <t xml:space="preserve">4.73035478591919</t>
   </si>
   <si>
     <t xml:space="preserve">4.82116460800171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92848443984985</t>
+    <t xml:space="preserve">4.9284839630127</t>
   </si>
   <si>
     <t xml:space="preserve">4.92022943496704</t>
@@ -2810,13 +2810,13 @@
     <t xml:space="preserve">4.87895202636719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60652351379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66431093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81290864944458</t>
+    <t xml:space="preserve">4.60652303695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66431140899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81290912628174</t>
   </si>
   <si>
     <t xml:space="preserve">4.88720750808716</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">5.11010408401489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16789197921753</t>
+    <t xml:space="preserve">5.16789245605469</t>
   </si>
   <si>
     <t xml:space="preserve">5.23393535614014</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">5.22567939758301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26695680618286</t>
+    <t xml:space="preserve">5.26695728302002</t>
   </si>
   <si>
     <t xml:space="preserve">5.27521228790283</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">5.36602163314819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43206548690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47334241867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55589628219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41555404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48985290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46508646011353</t>
+    <t xml:space="preserve">5.4320650100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4733419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5558967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41555452346802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4898533821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46508693695068</t>
   </si>
   <si>
     <t xml:space="preserve">5.57240724563599</t>
@@ -2885,13 +2885,13 @@
     <t xml:space="preserve">5.49810886383057</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52287483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51461887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58891820907593</t>
+    <t xml:space="preserve">5.52287435531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51461935043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58891773223877</t>
   </si>
   <si>
     <t xml:space="preserve">5.45683145523071</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">5.63019514083862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61368465423584</t>
+    <t xml:space="preserve">5.61368417739868</t>
   </si>
   <si>
     <t xml:space="preserve">5.5971736907959</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">5.89436817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81181478500366</t>
+    <t xml:space="preserve">5.8118143081665</t>
   </si>
   <si>
     <t xml:space="preserve">5.90262413024902</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">5.80355882644653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73751592636108</t>
+    <t xml:space="preserve">5.73751544952393</t>
   </si>
   <si>
     <t xml:space="preserve">6.00168943405151</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">6.39794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47224760055542</t>
+    <t xml:space="preserve">6.47224807739258</t>
   </si>
   <si>
     <t xml:space="preserve">6.43922662734985</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">6.51352500915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5630578994751</t>
+    <t xml:space="preserve">6.56305742263794</t>
   </si>
   <si>
     <t xml:space="preserve">6.67863368988037</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">6.73642158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68688917160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53829097747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62084579467773</t>
+    <t xml:space="preserve">6.6868896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53829145431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62084627151489</t>
   </si>
   <si>
     <t xml:space="preserve">6.64561128616333</t>
@@ -3032,10 +3032,10 @@
     <t xml:space="preserve">6.05122137069702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64670610427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8530912399292</t>
+    <t xml:space="preserve">5.64670658111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85309171676636</t>
   </si>
   <si>
     <t xml:space="preserve">5.67972755432129</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">5.38253259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66321706771851</t>
+    <t xml:space="preserve">5.66321659088135</t>
   </si>
   <si>
     <t xml:space="preserve">5.60542917251587</t>
@@ -3062,16 +3062,16 @@
     <t xml:space="preserve">5.88611316680908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79530334472656</t>
+    <t xml:space="preserve">5.79530382156372</t>
   </si>
   <si>
     <t xml:space="preserve">5.87785768508911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9769229888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91087961196899</t>
+    <t xml:space="preserve">5.97692251205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91087913513184</t>
   </si>
   <si>
     <t xml:space="preserve">5.91913509368896</t>
@@ -3083,10 +3083,10 @@
     <t xml:space="preserve">5.78704833984375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94390058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9604115486145</t>
+    <t xml:space="preserve">5.94390106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96041107177734</t>
   </si>
   <si>
     <t xml:space="preserve">5.8696026802063</t>
@@ -3134,13 +3134,13 @@
     <t xml:space="preserve">5.82472991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80742073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86800479888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88531398773193</t>
+    <t xml:space="preserve">5.80742025375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.868004322052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88531446456909</t>
   </si>
   <si>
     <t xml:space="preserve">5.87665939331055</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">5.9285888671875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96320819854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94589805603027</t>
+    <t xml:space="preserve">5.96320772171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94589853286743</t>
   </si>
   <si>
     <t xml:space="preserve">5.91993379592896</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">6.22285461425781</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17092561721802</t>
+    <t xml:space="preserve">6.17092514038086</t>
   </si>
   <si>
     <t xml:space="preserve">6.28343868255615</t>
@@ -3173,31 +3173,31 @@
     <t xml:space="preserve">6.25747394561768</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24881839752197</t>
+    <t xml:space="preserve">6.24881887435913</t>
   </si>
   <si>
     <t xml:space="preserve">6.24016427993774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2315092086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2661280632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46519041061401</t>
+    <t xml:space="preserve">6.23150873184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26612854003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46519088745117</t>
   </si>
   <si>
     <t xml:space="preserve">6.54308462142944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58635950088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56904935836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6382884979248</t>
+    <t xml:space="preserve">6.58635902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56904983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63828802108765</t>
   </si>
   <si>
     <t xml:space="preserve">6.56039428710938</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">6.64694309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50846481323242</t>
+    <t xml:space="preserve">6.50846529006958</t>
   </si>
   <si>
     <t xml:space="preserve">6.66425275802612</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">6.11034107208252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30940294265747</t>
+    <t xml:space="preserve">6.30940341949463</t>
   </si>
   <si>
     <t xml:space="preserve">6.37864208221436</t>
@@ -3239,16 +3239,16 @@
     <t xml:space="preserve">6.44788074493408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49115562438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49981069564819</t>
+    <t xml:space="preserve">6.49115514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49981021881104</t>
   </si>
   <si>
     <t xml:space="preserve">6.55173969268799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5950140953064</t>
+    <t xml:space="preserve">6.59501361846924</t>
   </si>
   <si>
     <t xml:space="preserve">6.70752716064453</t>
@@ -3263,40 +3263,40 @@
     <t xml:space="preserve">6.51712036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6296329498291</t>
+    <t xml:space="preserve">6.62963342666626</t>
   </si>
   <si>
     <t xml:space="preserve">6.74214696884155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87196969985962</t>
+    <t xml:space="preserve">6.87197017669678</t>
   </si>
   <si>
     <t xml:space="preserve">6.79407596588135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85466051101685</t>
+    <t xml:space="preserve">6.85466003417969</t>
   </si>
   <si>
     <t xml:space="preserve">6.61232376098633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7854208946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77676630020142</t>
+    <t xml:space="preserve">6.78542137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77676582336426</t>
   </si>
   <si>
     <t xml:space="preserve">6.7508020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52577447891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42191648483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45653629302979</t>
+    <t xml:space="preserve">6.52577495574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42191696166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45653581619263</t>
   </si>
   <si>
     <t xml:space="preserve">6.71618270874023</t>
@@ -3308,10 +3308,10 @@
     <t xml:space="preserve">6.75945663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82869529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82004070281982</t>
+    <t xml:space="preserve">6.82869577407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82004022598267</t>
   </si>
   <si>
     <t xml:space="preserve">6.92389917373657</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">7.01044845581055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05372142791748</t>
+    <t xml:space="preserve">7.05372190475464</t>
   </si>
   <si>
     <t xml:space="preserve">6.9931378364563</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">6.97582912445068</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95851898193359</t>
+    <t xml:space="preserve">6.95851850509644</t>
   </si>
   <si>
     <t xml:space="preserve">6.94986343383789</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">7.13161563873291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18354558944702</t>
+    <t xml:space="preserve">7.18354511260986</t>
   </si>
   <si>
     <t xml:space="preserve">7.1575813293457</t>
@@ -3371,16 +3371,16 @@
     <t xml:space="preserve">7.07968711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88927936553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86331510543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93255376815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91524457931519</t>
+    <t xml:space="preserve">6.88927984237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86331462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93255424499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91524410247803</t>
   </si>
   <si>
     <t xml:space="preserve">6.94120931625366</t>
@@ -3392,25 +3392,25 @@
     <t xml:space="preserve">7.17489051818848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27009391784668</t>
+    <t xml:space="preserve">7.27009344100952</t>
   </si>
   <si>
     <t xml:space="preserve">7.20085477828979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22681999206543</t>
+    <t xml:space="preserve">7.22681951522827</t>
   </si>
   <si>
     <t xml:space="preserve">7.16623544692993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14892578125</t>
+    <t xml:space="preserve">7.14892625808716</t>
   </si>
   <si>
     <t xml:space="preserve">7.0883412361145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14027118682861</t>
+    <t xml:space="preserve">7.14027070999146</t>
   </si>
   <si>
     <t xml:space="preserve">7.26143932342529</t>
@@ -3425,19 +3425,19 @@
     <t xml:space="preserve">7.42588186264038</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44319248199463</t>
+    <t xml:space="preserve">7.44319200515747</t>
   </si>
   <si>
     <t xml:space="preserve">7.48646545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23547410964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29605865478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19220066070557</t>
+    <t xml:space="preserve">7.23547458648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29605913162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19220113754272</t>
   </si>
   <si>
     <t xml:space="preserve">7.45184564590454</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">7.52108478546143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84997034072876</t>
+    <t xml:space="preserve">7.84997081756592</t>
   </si>
   <si>
     <t xml:space="preserve">7.72880268096924</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">7.53839540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55570411682129</t>
+    <t xml:space="preserve">7.55570459365845</t>
   </si>
   <si>
     <t xml:space="preserve">7.46050119400024</t>
@@ -3473,28 +3473,28 @@
     <t xml:space="preserve">7.40857267379761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63359880447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72014760971069</t>
+    <t xml:space="preserve">7.63359832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72014713287354</t>
   </si>
   <si>
     <t xml:space="preserve">7.88458967208862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77207660675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65090847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66821813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78073072433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83266162872314</t>
+    <t xml:space="preserve">7.77207708358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65090799331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6682186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78073120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83266115188599</t>
   </si>
   <si>
     <t xml:space="preserve">7.82400560379028</t>
@@ -3503,16 +3503,16 @@
     <t xml:space="preserve">7.75476741790771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7028374671936</t>
+    <t xml:space="preserve">7.70283794403076</t>
   </si>
   <si>
     <t xml:space="preserve">7.69418334960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67687320709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94517374038696</t>
+    <t xml:space="preserve">7.67687368392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94517469406128</t>
   </si>
   <si>
     <t xml:space="preserve">8.01441287994385</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">8.11827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05768775939941</t>
+    <t xml:space="preserve">8.05768871307373</t>
   </si>
   <si>
     <t xml:space="preserve">8.12692737579346</t>
@@ -3551,28 +3551,28 @@
     <t xml:space="preserve">8.18751049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00575828552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99710369110107</t>
+    <t xml:space="preserve">8.00575733184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99710321426392</t>
   </si>
   <si>
     <t xml:space="preserve">7.87593555450439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30867862701416</t>
+    <t xml:space="preserve">8.30867958068848</t>
   </si>
   <si>
     <t xml:space="preserve">8.24809455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27406024932861</t>
+    <t xml:space="preserve">8.2740592956543</t>
   </si>
   <si>
     <t xml:space="preserve">8.41253757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.576979637146</t>
+    <t xml:space="preserve">8.57698059082031</t>
   </si>
   <si>
     <t xml:space="preserve">8.5856351852417</t>
@@ -3596,7 +3596,7 @@
     <t xml:space="preserve">8.70680332183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87990188598633</t>
+    <t xml:space="preserve">8.87990093231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.834641456604</t>
@@ -4344,6 +4344,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.6400003433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5200004577637</t>
   </si>
 </sst>
 </file>
@@ -70306,7 +70309,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6911805556</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>92886</v>
@@ -70327,6 +70330,32 @@
         <v>1443</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6934375</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>75569</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>14.7600002288818</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>14.4399995803833</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>14.7600002288818</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>14.5200004577637</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -44,46 +44,46 @@
     <t xml:space="preserve">CE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52814483642578</t>
+    <t xml:space="preserve">4.52814531326294</t>
   </si>
   <si>
     <t xml:space="preserve">4.46432161331177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30644083023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26613092422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31315898895264</t>
+    <t xml:space="preserve">4.30644035339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2661304473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31315946578979</t>
   </si>
   <si>
     <t xml:space="preserve">4.31987762451172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36690616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27284955978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23589897155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05114459991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08473587036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74210214614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91677904129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03099012374878</t>
+    <t xml:space="preserve">4.36690521240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27284860610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23589849472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05114507675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08473634719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74210262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91677856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03099060058594</t>
   </si>
   <si>
     <t xml:space="preserve">4.15527868270874</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">4.12840557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01419401168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1250467300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1216869354248</t>
+    <t xml:space="preserve">4.01419496536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12504625320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12168741226196</t>
   </si>
   <si>
     <t xml:space="preserve">3.94701075553894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80256676673889</t>
+    <t xml:space="preserve">3.80256724357605</t>
   </si>
   <si>
     <t xml:space="preserve">3.83615851402283</t>
@@ -116,52 +116,52 @@
     <t xml:space="preserve">3.5808629989624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42970061302185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75217962265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6077356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84959411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670037269592</t>
+    <t xml:space="preserve">3.42970085144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75218033790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60773515701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84959602355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670132637024</t>
   </si>
   <si>
     <t xml:space="preserve">3.96716594696045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06458187103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82943987846375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77233409881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90334129333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87982678413391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72866582870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79584908485413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88318681716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95708775520325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13176488876343</t>
+    <t xml:space="preserve">4.06458234786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82944083213806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77233457565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90334177017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87982821464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72866630554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79584956169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88318777084351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95708870887756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13176441192627</t>
   </si>
   <si>
     <t xml:space="preserve">4.1955885887146</t>
@@ -170,70 +170,70 @@
     <t xml:space="preserve">4.18551111221313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13848257064819</t>
+    <t xml:space="preserve">4.13848304748535</t>
   </si>
   <si>
     <t xml:space="preserve">4.22246170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29972267150879</t>
+    <t xml:space="preserve">4.29972219467163</t>
   </si>
   <si>
     <t xml:space="preserve">4.35682821273804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25605344772339</t>
+    <t xml:space="preserve">4.25605297088623</t>
   </si>
   <si>
     <t xml:space="preserve">4.27956771850586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14856052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32659578323364</t>
+    <t xml:space="preserve">4.14856004714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3265962600708</t>
   </si>
   <si>
     <t xml:space="preserve">4.26949071884155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16535615921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09817314147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04778575897217</t>
+    <t xml:space="preserve">4.16535568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09817361831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04778671264648</t>
   </si>
   <si>
     <t xml:space="preserve">4.04106760025024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93021464347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91005992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81936240196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75889754295349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71186995506287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93357372283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82608079910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08137702941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15863847732544</t>
+    <t xml:space="preserve">3.93021512031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9100604057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81936287879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75889825820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71187019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93357467651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82608127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08137798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15863800048828</t>
   </si>
   <si>
     <t xml:space="preserve">4.17879247665405</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">4.21238422393799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21574401855469</t>
+    <t xml:space="preserve">4.21574354171753</t>
   </si>
   <si>
     <t xml:space="preserve">4.28292655944824</t>
@@ -251,25 +251,25 @@
     <t xml:space="preserve">4.30308198928833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35346937179565</t>
+    <t xml:space="preserve">4.3534688949585</t>
   </si>
   <si>
     <t xml:space="preserve">4.19894742965698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07465934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08809518814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06122207641602</t>
+    <t xml:space="preserve">4.07465887069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08809566497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06122303009033</t>
   </si>
   <si>
     <t xml:space="preserve">4.0242714881897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93693351745605</t>
+    <t xml:space="preserve">3.93693375587463</t>
   </si>
   <si>
     <t xml:space="preserve">4.21648931503296</t>
@@ -281,37 +281,37 @@
     <t xml:space="preserve">4.19927930831909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2543511390686</t>
+    <t xml:space="preserve">4.25435209274292</t>
   </si>
   <si>
     <t xml:space="preserve">4.23369979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23714208602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49185228347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4987359046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47119951248169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45743179321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46431589126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37826538085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31975078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3713812828064</t>
+    <t xml:space="preserve">4.23714160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49185180664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49873685836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47120046615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45743131637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46431541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37826490402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31975030899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37138080596924</t>
   </si>
   <si>
     <t xml:space="preserve">4.28188848495483</t>
@@ -320,28 +320,28 @@
     <t xml:space="preserve">4.42989540100098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34040307998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35072946548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25090980529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03750371932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91703271865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98243188858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8688440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1373233795166</t>
+    <t xml:space="preserve">4.34040260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35072898864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25090932846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03750324249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91703224182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98243117332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884427070618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13732290267944</t>
   </si>
   <si>
     <t xml:space="preserve">4.3369607925415</t>
@@ -350,28 +350,28 @@
     <t xml:space="preserve">4.38170671463013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42301177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52971458435059</t>
+    <t xml:space="preserve">4.42301225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52971410751343</t>
   </si>
   <si>
     <t xml:space="preserve">3.74148917198181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7518150806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73116326332092</t>
+    <t xml:space="preserve">3.75181531906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73116278648376</t>
   </si>
   <si>
     <t xml:space="preserve">3.84130811691284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65199589729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5246410369873</t>
+    <t xml:space="preserve">3.65199565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52464127540588</t>
   </si>
   <si>
     <t xml:space="preserve">3.42826390266418</t>
@@ -380,16 +380,16 @@
     <t xml:space="preserve">3.50743079185486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65887999534607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75525689125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82065606117249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78623604774475</t>
+    <t xml:space="preserve">3.65888023376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75525784492493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82065558433533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78623509407043</t>
   </si>
   <si>
     <t xml:space="preserve">3.90670657157898</t>
@@ -404,67 +404,67 @@
     <t xml:space="preserve">4.04094552993774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01341009140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94456839561462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98931622505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95833778381348</t>
+    <t xml:space="preserve">4.01340961456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94456887245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98931550979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95833706855774</t>
   </si>
   <si>
     <t xml:space="preserve">3.79656147956848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90326499938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80000329017639</t>
+    <t xml:space="preserve">3.90326452255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80000376701355</t>
   </si>
   <si>
     <t xml:space="preserve">3.68641662597656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70018434524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76558327674866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362782478333</t>
+    <t xml:space="preserve">3.70018482208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76558351516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362663269043</t>
   </si>
   <si>
     <t xml:space="preserve">3.66576409339905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66920638084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55217695236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4867787361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47989463806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37319159507751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37181448936462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50054740905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68985819816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561971664429</t>
+    <t xml:space="preserve">3.6692066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55217719078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48677825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47989439964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37319207191467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37181496620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50054669380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68985915184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561900138855</t>
   </si>
   <si>
     <t xml:space="preserve">3.45235848426819</t>
@@ -473,40 +473,40 @@
     <t xml:space="preserve">3.47645282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64511203765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72083687782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70706915855408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77935123443604</t>
+    <t xml:space="preserve">3.64511275291443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7208366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706820487976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77935075759888</t>
   </si>
   <si>
     <t xml:space="preserve">3.80688762664795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61413335800171</t>
+    <t xml:space="preserve">3.61413383483887</t>
   </si>
   <si>
     <t xml:space="preserve">3.61757612228394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57971405982971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5659453868866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49366307258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49022030830383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4489164352417</t>
+    <t xml:space="preserve">3.57971382141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56594491004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49366283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49022102355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44891691207886</t>
   </si>
   <si>
     <t xml:space="preserve">3.63822793960571</t>
@@ -518,70 +518,70 @@
     <t xml:space="preserve">3.38695979118347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3580470085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37456846237183</t>
+    <t xml:space="preserve">3.35804677009583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37456870079041</t>
   </si>
   <si>
     <t xml:space="preserve">3.31123471260071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32638049125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35529351234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41587209701538</t>
+    <t xml:space="preserve">3.32638025283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3552930355072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41587281227112</t>
   </si>
   <si>
     <t xml:space="preserve">3.51431488990784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48333668708801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51087284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51775717735291</t>
+    <t xml:space="preserve">3.48333621025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51087260246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51775741577148</t>
   </si>
   <si>
     <t xml:space="preserve">3.47301030158997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57627201080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53496670722961</t>
+    <t xml:space="preserve">3.57627153396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53496742248535</t>
   </si>
   <si>
     <t xml:space="preserve">3.64855456352234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67953276634216</t>
+    <t xml:space="preserve">3.67953252792358</t>
   </si>
   <si>
     <t xml:space="preserve">3.59692335128784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64167046546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63134431838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56250381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53152513504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45580101013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41174173355103</t>
+    <t xml:space="preserve">3.6416699886322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63134407997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56250357627869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53152537345886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45580005645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41174244880676</t>
   </si>
   <si>
     <t xml:space="preserve">3.42964124679565</t>
@@ -590,37 +590,37 @@
     <t xml:space="preserve">3.45924258232117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44203209877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52808332443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63478636741638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67609047889709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62790179252625</t>
+    <t xml:space="preserve">3.44203186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52808284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63478708267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67609071731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62790203094482</t>
   </si>
   <si>
     <t xml:space="preserve">3.58659744262695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54529356956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55906057357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56938767433167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71739482879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94112682342529</t>
+    <t xml:space="preserve">3.54529404640198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55906176567078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56938743591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71739459037781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94112706184387</t>
   </si>
   <si>
     <t xml:space="preserve">4.00996732711792</t>
@@ -632,67 +632,67 @@
     <t xml:space="preserve">3.97210502624512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83442378044128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92735910415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98587369918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05471324920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93080067634583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04438829421997</t>
+    <t xml:space="preserve">3.83442425727844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92735862731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98587274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05471420288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93080019950867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04438781738281</t>
   </si>
   <si>
     <t xml:space="preserve">4.06159830093384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91014885902405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89982271194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05815649032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07192373275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07880783081055</t>
+    <t xml:space="preserve">3.91014838218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89982223510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05815601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07192420959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07880878448486</t>
   </si>
   <si>
     <t xml:space="preserve">4.0306191444397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19583797454834</t>
+    <t xml:space="preserve">4.19583702087402</t>
   </si>
   <si>
     <t xml:space="preserve">4.20960569381714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29565572738647</t>
+    <t xml:space="preserve">4.29565620422363</t>
   </si>
   <si>
     <t xml:space="preserve">4.27844572067261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24746751785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30253982543945</t>
+    <t xml:space="preserve">4.24746704101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30254030227661</t>
   </si>
   <si>
     <t xml:space="preserve">4.12699604034424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13043832778931</t>
+    <t xml:space="preserve">4.13043880462646</t>
   </si>
   <si>
     <t xml:space="preserve">4.20272159576416</t>
@@ -701,31 +701,31 @@
     <t xml:space="preserve">4.10634469985962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12011337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17862701416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2405834197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14764928817749</t>
+    <t xml:space="preserve">4.12011241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17862796783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24058389663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14764881134033</t>
   </si>
   <si>
     <t xml:space="preserve">4.16141700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04782962799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14076471328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15109062194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15453243255615</t>
+    <t xml:space="preserve">4.04783058166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1407642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1510910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15453338623047</t>
   </si>
   <si>
     <t xml:space="preserve">4.18206930160522</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">4.21304702758789</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32319307327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3644962310791</t>
+    <t xml:space="preserve">4.32319259643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449718475342</t>
   </si>
   <si>
     <t xml:space="preserve">4.43333768844604</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">4.41956901550293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37482357025146</t>
+    <t xml:space="preserve">4.37482309341431</t>
   </si>
   <si>
     <t xml:space="preserve">4.41268539428711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34384536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30942440032959</t>
+    <t xml:space="preserve">4.34384441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30942487716675</t>
   </si>
   <si>
     <t xml:space="preserve">4.36793899536133</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">4.35417079925537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28532981872559</t>
+    <t xml:space="preserve">4.2853307723999</t>
   </si>
   <si>
     <t xml:space="preserve">4.52627229690552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40580177307129</t>
+    <t xml:space="preserve">4.40580081939697</t>
   </si>
   <si>
     <t xml:space="preserve">4.48840999603271</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">4.53659820556641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54348278045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44710636138916</t>
+    <t xml:space="preserve">4.54348230361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44710540771484</t>
   </si>
   <si>
     <t xml:space="preserve">4.67083740234375</t>
@@ -806,25 +806,25 @@
     <t xml:space="preserve">4.69899654388428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8010721206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71659564971924</t>
+    <t xml:space="preserve">4.80107259750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7165961265564</t>
   </si>
   <si>
     <t xml:space="preserve">4.83627080917358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8609094619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85034942626953</t>
+    <t xml:space="preserve">4.86090993881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85034990310669</t>
   </si>
   <si>
     <t xml:space="preserve">4.87850904464722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7834734916687</t>
+    <t xml:space="preserve">4.78347301483154</t>
   </si>
   <si>
     <t xml:space="preserve">4.72011566162109</t>
@@ -833,28 +833,28 @@
     <t xml:space="preserve">4.68491744995117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7306752204895</t>
+    <t xml:space="preserve">4.73067474365234</t>
   </si>
   <si>
     <t xml:space="preserve">4.75179433822632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81515216827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81163215637207</t>
+    <t xml:space="preserve">4.81515121459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81163167953491</t>
   </si>
   <si>
     <t xml:space="preserve">4.9277868270874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93834638595581</t>
+    <t xml:space="preserve">4.93834686279297</t>
   </si>
   <si>
     <t xml:space="preserve">4.87498903274536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80811262130737</t>
+    <t xml:space="preserve">4.80811166763306</t>
   </si>
   <si>
     <t xml:space="preserve">4.80459213256836</t>
@@ -866,37 +866,37 @@
     <t xml:space="preserve">4.95946550369263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86442947387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89258813858032</t>
+    <t xml:space="preserve">4.86442899703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89258861541748</t>
   </si>
   <si>
     <t xml:space="preserve">4.89610862731934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97354507446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97706460952759</t>
+    <t xml:space="preserve">4.91370725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97354459762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97706508636475</t>
   </si>
   <si>
     <t xml:space="preserve">4.94538593292236</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11081886291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25865268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0615406036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08617973327637</t>
+    <t xml:space="preserve">5.1108193397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2586522102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06154108047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08617925643921</t>
   </si>
   <si>
     <t xml:space="preserve">5.10377931594849</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">5.05098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08970022201538</t>
+    <t xml:space="preserve">5.08969926834106</t>
   </si>
   <si>
     <t xml:space="preserve">5.01930332183838</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">4.91018772125244</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00874280929565</t>
+    <t xml:space="preserve">5.00874328613281</t>
   </si>
   <si>
     <t xml:space="preserve">5.10025930404663</t>
@@ -941,16 +941,16 @@
     <t xml:space="preserve">5.1248984336853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20937490463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36424779891968</t>
+    <t xml:space="preserve">5.20937442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36424827575684</t>
   </si>
   <si>
     <t xml:space="preserve">5.21289443969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03690195083618</t>
+    <t xml:space="preserve">5.03690242767334</t>
   </si>
   <si>
     <t xml:space="preserve">5.16361665725708</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">5.2727313041687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23049354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15305709838867</t>
+    <t xml:space="preserve">5.23049306869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15305662155151</t>
   </si>
   <si>
     <t xml:space="preserve">5.2023344039917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11433887481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10729885101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00522327423096</t>
+    <t xml:space="preserve">5.11433839797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10729932785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00522422790527</t>
   </si>
   <si>
     <t xml:space="preserve">4.9981837272644</t>
@@ -983,10 +983,10 @@
     <t xml:space="preserve">5.01226329803467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04394197463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06506109237671</t>
+    <t xml:space="preserve">5.04394149780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06506061553955</t>
   </si>
   <si>
     <t xml:space="preserve">5.15657711029053</t>
@@ -995,16 +995,16 @@
     <t xml:space="preserve">5.34312868118286</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30089092254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27977132797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30793046951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25161266326904</t>
+    <t xml:space="preserve">5.30089044570923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27977180480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30792999267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25161218643188</t>
   </si>
   <si>
     <t xml:space="preserve">5.29385042190552</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">5.33608913421631</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34664821624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36776733398438</t>
+    <t xml:space="preserve">5.34664869308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36776781082153</t>
   </si>
   <si>
     <t xml:space="preserve">5.35368824005127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38536739349365</t>
+    <t xml:space="preserve">5.38536643981934</t>
   </si>
   <si>
     <t xml:space="preserve">5.39944648742676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26569223403931</t>
+    <t xml:space="preserve">5.26569271087646</t>
   </si>
   <si>
     <t xml:space="preserve">5.31145048141479</t>
@@ -1040,22 +1040,22 @@
     <t xml:space="preserve">5.3255295753479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28329181671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2340145111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2164134979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14249658584595</t>
+    <t xml:space="preserve">5.28329133987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23401403427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21641397476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14249753952026</t>
   </si>
   <si>
     <t xml:space="preserve">5.16713619232178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31497049331665</t>
+    <t xml:space="preserve">5.31496953964233</t>
   </si>
   <si>
     <t xml:space="preserve">5.29737091064453</t>
@@ -1064,22 +1064,22 @@
     <t xml:space="preserve">5.19177532196045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35720777511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0721001625061</t>
+    <t xml:space="preserve">5.35720872879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07209968566895</t>
   </si>
   <si>
     <t xml:space="preserve">4.98410415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94186639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86794996261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92426681518555</t>
+    <t xml:space="preserve">4.94186592102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86794900894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92426729202271</t>
   </si>
   <si>
     <t xml:space="preserve">4.98058414459229</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">5.0545015335083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18473625183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17417573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21993398666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17769622802734</t>
+    <t xml:space="preserve">5.18473529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17417526245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21993446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1776967048645</t>
   </si>
   <si>
     <t xml:space="preserve">5.22697401046753</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">5.28681087493896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02282285690308</t>
+    <t xml:space="preserve">5.02282333374023</t>
   </si>
   <si>
     <t xml:space="preserve">5.0017032623291</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">5.02986192703247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05802059173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92074680328369</t>
+    <t xml:space="preserve">5.058021068573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92074728012085</t>
   </si>
   <si>
     <t xml:space="preserve">4.99114370346069</t>
@@ -1133,22 +1133,22 @@
     <t xml:space="preserve">5.47688341140747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48392248153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44168472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43464469909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52616119384766</t>
+    <t xml:space="preserve">5.48392295837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44168519973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43464517593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5261607170105</t>
   </si>
   <si>
     <t xml:space="preserve">5.51208114624023</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46984386444092</t>
+    <t xml:space="preserve">5.46984338760376</t>
   </si>
   <si>
     <t xml:space="preserve">5.40648603439331</t>
@@ -1163,34 +1163,34 @@
     <t xml:space="preserve">5.13897752761841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32905006408691</t>
+    <t xml:space="preserve">5.3290491104126</t>
   </si>
   <si>
     <t xml:space="preserve">5.14601707458496</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1952953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24457263946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22345352172852</t>
+    <t xml:space="preserve">5.19529485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24457311630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22345447540283</t>
   </si>
   <si>
     <t xml:space="preserve">5.23753356933594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16009664535522</t>
+    <t xml:space="preserve">5.16009616851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.11785888671875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97002506256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21899938583374</t>
+    <t xml:space="preserve">4.97002458572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2189998626709</t>
   </si>
   <si>
     <t xml:space="preserve">5.14661455154419</t>
@@ -1205,19 +1205,19 @@
     <t xml:space="preserve">4.81364011764526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84259414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85707139968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82087850570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80640125274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5602912902832</t>
+    <t xml:space="preserve">4.84259462356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85707187652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82087898254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80640172958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56029081344604</t>
   </si>
   <si>
     <t xml:space="preserve">4.46618938446045</t>
@@ -1232,46 +1232,46 @@
     <t xml:space="preserve">4.37208843231201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52409791946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40828132629395</t>
+    <t xml:space="preserve">4.52409839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4082818031311</t>
   </si>
   <si>
     <t xml:space="preserve">4.34313440322876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29246425628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3938045501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45895099639893</t>
+    <t xml:space="preserve">4.29246377944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39380502700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45895051956177</t>
   </si>
   <si>
     <t xml:space="preserve">4.43723583221436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53133678436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61096048355103</t>
+    <t xml:space="preserve">4.53133726119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61096096038818</t>
   </si>
   <si>
     <t xml:space="preserve">4.64715337753296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69058513641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57476854324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58200597763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48790550231934</t>
+    <t xml:space="preserve">4.69058465957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57476806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58200645446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48790597915649</t>
   </si>
   <si>
     <t xml:space="preserve">4.545814037323</t>
@@ -1280,19 +1280,19 @@
     <t xml:space="preserve">4.58924531936646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60372304916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68334627151489</t>
+    <t xml:space="preserve">4.6037220954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68334674835205</t>
   </si>
   <si>
     <t xml:space="preserve">4.69782304763794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62543773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63267707824707</t>
+    <t xml:space="preserve">4.62543821334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63267612457275</t>
   </si>
   <si>
     <t xml:space="preserve">4.61819934844971</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">4.44447422027588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42999744415283</t>
+    <t xml:space="preserve">4.42999649047852</t>
   </si>
   <si>
     <t xml:space="preserve">4.59648370742798</t>
@@ -1316,19 +1316,19 @@
     <t xml:space="preserve">4.51685905456543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50962018966675</t>
+    <t xml:space="preserve">4.50962066650391</t>
   </si>
   <si>
     <t xml:space="preserve">4.1766471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10426235198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04635381698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02463722229004</t>
+    <t xml:space="preserve">4.10426187515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04635429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0246376991272</t>
   </si>
   <si>
     <t xml:space="preserve">4.03187656402588</t>
@@ -1340,19 +1340,19 @@
     <t xml:space="preserve">4.06806898117065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97396779060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00292253494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85091257095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87262797355652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93053650856018</t>
+    <t xml:space="preserve">3.97396731376648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00292205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85091209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87262749671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93053603172302</t>
   </si>
   <si>
     <t xml:space="preserve">3.9232976436615</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">4.20560169219971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2200779914856</t>
+    <t xml:space="preserve">4.22007846832275</t>
   </si>
   <si>
     <t xml:space="preserve">4.2345552444458</t>
@@ -1382,22 +1382,22 @@
     <t xml:space="preserve">4.2997031211853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36485004425049</t>
+    <t xml:space="preserve">4.36485052108765</t>
   </si>
   <si>
     <t xml:space="preserve">4.35761117935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26350975036621</t>
+    <t xml:space="preserve">4.26351022720337</t>
   </si>
   <si>
     <t xml:space="preserve">4.09702301025391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06083059310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12597703933716</t>
+    <t xml:space="preserve">4.06083106994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12597799301147</t>
   </si>
   <si>
     <t xml:space="preserve">3.90882110595703</t>
@@ -1406,37 +1406,37 @@
     <t xml:space="preserve">3.84367370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7857654094696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87986731529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94501304626465</t>
+    <t xml:space="preserve">3.78576588630676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8798668384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94501352310181</t>
   </si>
   <si>
     <t xml:space="preserve">3.80748128890991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72061800956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68442583084106</t>
+    <t xml:space="preserve">3.72061824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68442630767822</t>
   </si>
   <si>
     <t xml:space="preserve">3.57946634292603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45641136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55051207542419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81471920013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7640495300293</t>
+    <t xml:space="preserve">3.45641088485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55051231384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81471943855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76404976844788</t>
   </si>
   <si>
     <t xml:space="preserve">3.82919669151306</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">3.74233388900757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75681161880493</t>
+    <t xml:space="preserve">3.75681042671204</t>
   </si>
   <si>
     <t xml:space="preserve">3.70614123344421</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">3.67718696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63375568389893</t>
+    <t xml:space="preserve">3.63375520706177</t>
   </si>
   <si>
     <t xml:space="preserve">3.66994857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6192786693573</t>
+    <t xml:space="preserve">3.61927819252014</t>
   </si>
   <si>
     <t xml:space="preserve">3.64099454879761</t>
@@ -1478,46 +1478,46 @@
     <t xml:space="preserve">3.80024242401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6627094745636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72785687446594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86539006233215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60480141639709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58670473098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57584714889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54327368736267</t>
+    <t xml:space="preserve">3.66270995140076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72785758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.865389585495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60480117797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58670496940613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57584691047668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54327392578125</t>
   </si>
   <si>
     <t xml:space="preserve">3.65547156333923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82195830345154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71337985992432</t>
+    <t xml:space="preserve">3.8219587802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71337962150574</t>
   </si>
   <si>
     <t xml:space="preserve">3.69890284538269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69166421890259</t>
+    <t xml:space="preserve">3.69166374206543</t>
   </si>
   <si>
     <t xml:space="preserve">3.6265172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64823246002197</t>
+    <t xml:space="preserve">3.64823317527771</t>
   </si>
   <si>
     <t xml:space="preserve">3.5251772403717</t>
@@ -1526,265 +1526,265 @@
     <t xml:space="preserve">3.60118222236633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54689264297485</t>
+    <t xml:space="preserve">3.54689335823059</t>
   </si>
   <si>
     <t xml:space="preserve">3.50346183776855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6084201335907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79300403594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88710474967957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56499004364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59394359588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77852606773376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58308553695679</t>
+    <t xml:space="preserve">3.60842108726501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79300355911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88710498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56498956680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59394407272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77852702140808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58308529853821</t>
   </si>
   <si>
     <t xml:space="preserve">3.53965401649475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48174571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49622297286987</t>
+    <t xml:space="preserve">3.48174548149109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49622273445129</t>
   </si>
   <si>
     <t xml:space="preserve">3.452791929245</t>
   </si>
   <si>
+    <t xml:space="preserve">3.42021799087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43155598640442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43533539772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41265940666199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33329558372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38620519638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37108778953552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36352968215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3824257850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31062030792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32573699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29172396659851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393104553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3143994808197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33707499504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.276606798172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28038644790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23503565788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2048008441925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21613907814026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23125576972961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21235966682434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24259376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18212556838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13677501678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15189170837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18968415260315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20102214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25015234947205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39376330375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59784293174744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65831089019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55627131462097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55249166488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56760883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57516741752625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60540151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53359603881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47690653800964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59028434753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58272576332092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57138800621033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52603721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50336146354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43911480903625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42777681350708</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.4202184677124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43155598640442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43533515930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41265964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33329558372498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841227531433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38620543479919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37108826637268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36352944374084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3824257850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31062030792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3257372379303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29172372817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393152236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31439971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33707475662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.276606798172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28038620948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23503541946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20480108261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21613907814026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23125576972961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21235918998718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24259376525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18212580680847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13677477836609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1518919467926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18968415260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20102214813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25015234947205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39376330375671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59784340858459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65831112861633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55627107620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5524914264679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56760883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57516765594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60540151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53359580039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47690677642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59028387069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58272552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57138824462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52603721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50336217880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43911457061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42777681350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42021870613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40132188796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36730885505676</t>
+    <t xml:space="preserve">3.40132212638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36730861663818</t>
   </si>
   <si>
     <t xml:space="preserve">3.40888023376465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34085416793823</t>
+    <t xml:space="preserve">3.34085440635681</t>
   </si>
   <si>
     <t xml:space="preserve">3.42399787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51469922065735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49958276748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54871273040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63941431045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65453100204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68098640441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67342805862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73011612892151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78680539131165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285823822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86239004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74523329734802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76790833473206</t>
+    <t xml:space="preserve">3.51469945907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49958229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54871296882629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63941478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65453147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68098616600037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67342758178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73011636734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78680491447449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285752296448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86239051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7452335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76790881156921</t>
   </si>
   <si>
     <t xml:space="preserve">3.83971476554871</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83215641975403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168750762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73767518997192</t>
+    <t xml:space="preserve">3.83215594291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73767495155334</t>
   </si>
   <si>
     <t xml:space="preserve">3.69232392311096</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70366144180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77924728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68854475021362</t>
+    <t xml:space="preserve">3.70366191864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77924680709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68854451179504</t>
   </si>
   <si>
     <t xml:space="preserve">3.66586923599243</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">3.69610285758972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66964840888977</t>
+    <t xml:space="preserve">3.66964817047119</t>
   </si>
   <si>
     <t xml:space="preserve">3.73389577865601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81703948974609</t>
+    <t xml:space="preserve">3.81703996658325</t>
   </si>
   <si>
     <t xml:space="preserve">3.84727334976196</t>
@@ -1808,19 +1808,19 @@
     <t xml:space="preserve">3.90018272399902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98332595825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96065068244934</t>
+    <t xml:space="preserve">3.98332619667053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96065020561218</t>
   </si>
   <si>
     <t xml:space="preserve">3.9530918598175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93041658401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94553279876709</t>
+    <t xml:space="preserve">3.93041610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94553327560425</t>
   </si>
   <si>
     <t xml:space="preserve">3.99088454246521</t>
@@ -1838,22 +1838,22 @@
     <t xml:space="preserve">4.03623580932617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0664701461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0815863609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1344952583313</t>
+    <t xml:space="preserve">4.06646966934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08158683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13449573516846</t>
   </si>
   <si>
     <t xml:space="preserve">4.05135297775269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02867698669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00600147247314</t>
+    <t xml:space="preserve">4.02867746353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0060019493103</t>
   </si>
   <si>
     <t xml:space="preserve">4.04379367828369</t>
@@ -1865,61 +1865,61 @@
     <t xml:space="preserve">4.01355981826782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9682092666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93797492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97576761245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90774083137512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89262390136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88506555557251</t>
+    <t xml:space="preserve">3.96820878982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93797540664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97576713562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90774130821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89262437820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88506603240967</t>
   </si>
   <si>
     <t xml:space="preserve">3.87750697135925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85483169555664</t>
+    <t xml:space="preserve">3.85483121871948</t>
   </si>
   <si>
     <t xml:space="preserve">3.80192255973816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5940637588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60162234306335</t>
+    <t xml:space="preserve">3.59406352043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6016218662262</t>
   </si>
   <si>
     <t xml:space="preserve">3.65075206756592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71877932548523</t>
+    <t xml:space="preserve">3.71877861022949</t>
   </si>
   <si>
     <t xml:space="preserve">3.99844336509705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72255849838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63185572624207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46556925773621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44667267799377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28416514396667</t>
+    <t xml:space="preserve">3.72255825996399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63185620307922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46556949615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44667291641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28416562080383</t>
   </si>
   <si>
     <t xml:space="preserve">3.11031985282898</t>
@@ -1928,19 +1928,19 @@
     <t xml:space="preserve">3.06496906280518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83821439743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83443474769592</t>
+    <t xml:space="preserve">2.83821415901184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8344349861145</t>
   </si>
   <si>
     <t xml:space="preserve">2.95915007591248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70972037315369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93269538879395</t>
+    <t xml:space="preserve">2.70971989631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93269515037537</t>
   </si>
   <si>
     <t xml:space="preserve">3.00450110435486</t>
@@ -1952,16 +1952,16 @@
     <t xml:space="preserve">2.94403314590454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91001987457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96292972564697</t>
+    <t xml:space="preserve">2.91002011299133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96292948722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.85333132743835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89490294456482</t>
+    <t xml:space="preserve">2.89490270614624</t>
   </si>
   <si>
     <t xml:space="preserve">2.88734459877014</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">2.85711050033569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9024612903595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82687664031982</t>
+    <t xml:space="preserve">2.90246152877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8268768787384</t>
   </si>
   <si>
     <t xml:space="preserve">2.89112377166748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9969425201416</t>
+    <t xml:space="preserve">2.99694275856018</t>
   </si>
   <si>
     <t xml:space="preserve">2.95159149169922</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">2.97804641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99316310882568</t>
+    <t xml:space="preserve">2.99316334724426</t>
   </si>
   <si>
     <t xml:space="preserve">3.05363130569458</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">3.02717661857605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12165760993958</t>
+    <t xml:space="preserve">3.12165784835815</t>
   </si>
   <si>
     <t xml:space="preserve">3.06118988990784</t>
@@ -2015,25 +2015,25 @@
     <t xml:space="preserve">3.16700887680054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14433312416077</t>
+    <t xml:space="preserve">3.14433336257935</t>
   </si>
   <si>
     <t xml:space="preserve">3.19346332550049</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21991872787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26904821395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32195782661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15945029258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07252764701843</t>
+    <t xml:space="preserve">3.2199182510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26904845237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3219575881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1594500541687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07252740859985</t>
   </si>
   <si>
     <t xml:space="preserve">3.06874823570251</t>
@@ -2045,28 +2045,28 @@
     <t xml:space="preserve">3.16322946548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27282738685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28794431686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40510129928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51091980934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4882447719574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45801067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29550361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34463357925415</t>
+    <t xml:space="preserve">3.27282762527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28794479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40510153770447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51092004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48824429512024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45801043510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29550337791443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34463381767273</t>
   </si>
   <si>
     <t xml:space="preserve">3.29928231239319</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">3.30306172370911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26149010658264</t>
+    <t xml:space="preserve">3.26148986816406</t>
   </si>
   <si>
     <t xml:space="preserve">3.37864661216736</t>
@@ -2087,19 +2087,19 @@
     <t xml:space="preserve">3.37486743927002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26526927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39754247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48068618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38998413085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31817841529846</t>
+    <t xml:space="preserve">3.2652690410614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39754271507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48068594932556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38998436927795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31817865371704</t>
   </si>
   <si>
     <t xml:space="preserve">3.25771069526672</t>
@@ -2108,52 +2108,52 @@
     <t xml:space="preserve">3.22747683525085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18590521812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24637293815613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17456674575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14055418968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17834663391113</t>
+    <t xml:space="preserve">3.18590497970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24637317657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17456698417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14055466651917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17834615707397</t>
   </si>
   <si>
     <t xml:space="preserve">3.09142398834229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08008599281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0460729598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01583909988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9402539730072</t>
+    <t xml:space="preserve">3.08008575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04607319831848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01583862304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94025373458862</t>
   </si>
   <si>
     <t xml:space="preserve">2.95537090301514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92513680458069</t>
+    <t xml:space="preserve">2.92513704299927</t>
   </si>
   <si>
     <t xml:space="preserve">2.88356518745422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80042171478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78908395767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77018809318542</t>
+    <t xml:space="preserve">2.80042147636414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7890841960907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77018785476685</t>
   </si>
   <si>
     <t xml:space="preserve">2.75129175186157</t>
@@ -2168,28 +2168,28 @@
     <t xml:space="preserve">2.67948579788208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55477070808411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44895195960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55099153518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61523866653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69838190078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98938417434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5373752117157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62807655334473</t>
+    <t xml:space="preserve">2.55477094650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44895172119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55099177360535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.615238904953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69838213920593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9893844127655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53737497329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62807726860046</t>
   </si>
   <si>
     <t xml:space="preserve">3.63563513755798</t>
@@ -2198,25 +2198,25 @@
     <t xml:space="preserve">3.57894682884216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56383013725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50714087486267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48446559906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52225756645203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41643929481506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12543725967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8094801902771</t>
+    <t xml:space="preserve">3.56382989883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50714063644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48446536064148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52225828170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41643857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12543749809265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80948066711426</t>
   </si>
   <si>
     <t xml:space="preserve">3.76035070419312</t>
@@ -2225,13 +2225,13 @@
     <t xml:space="preserve">3.6431941986084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68476581573486</t>
+    <t xml:space="preserve">3.68476510047913</t>
   </si>
   <si>
     <t xml:space="preserve">3.74901270866394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79436373710632</t>
+    <t xml:space="preserve">3.79436421394348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75657105445862</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">3.77546763420105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76412963867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15717172622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11182069778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.172287940979</t>
+    <t xml:space="preserve">3.76412987709045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15717124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11182022094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17228889465332</t>
   </si>
   <si>
     <t xml:space="preserve">4.3134560585022</t>
@@ -2267,43 +2267,43 @@
     <t xml:space="preserve">4.08601951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09386110305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20365905761719</t>
+    <t xml:space="preserve">4.09386157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20365953445435</t>
   </si>
   <si>
     <t xml:space="preserve">4.26640033721924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27424240112305</t>
+    <t xml:space="preserve">4.27424192428589</t>
   </si>
   <si>
     <t xml:space="preserve">4.25855731964111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36835479736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32914066314697</t>
+    <t xml:space="preserve">4.36835432052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32914113998413</t>
   </si>
   <si>
     <t xml:space="preserve">4.34482622146606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35266971588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30561351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28992748260498</t>
+    <t xml:space="preserve">4.35266923904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30561304092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28992795944214</t>
   </si>
   <si>
     <t xml:space="preserve">4.28208541870117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19581604003906</t>
+    <t xml:space="preserve">4.1958155632019</t>
   </si>
   <si>
     <t xml:space="preserve">4.03896331787109</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">4.03112077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05464839935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93700933456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92132377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01543521881104</t>
+    <t xml:space="preserve">4.05464887619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93700885772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92132329940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01543569564819</t>
   </si>
   <si>
     <t xml:space="preserve">4.07033395767212</t>
@@ -2342,13 +2342,13 @@
     <t xml:space="preserve">3.97622203826904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18797397613525</t>
+    <t xml:space="preserve">4.1879734992981</t>
   </si>
   <si>
     <t xml:space="preserve">4.24287176132202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21150064468384</t>
+    <t xml:space="preserve">4.211501121521</t>
   </si>
   <si>
     <t xml:space="preserve">4.39188241958618</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">4.43109607696533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42325353622437</t>
+    <t xml:space="preserve">4.42325258255005</t>
   </si>
   <si>
     <t xml:space="preserve">4.38404035568237</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">4.39972496032715</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33698415756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36051177978516</t>
+    <t xml:space="preserve">4.3369836807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.360511302948</t>
   </si>
   <si>
     <t xml:space="preserve">4.4624662399292</t>
@@ -2384,34 +2384,34 @@
     <t xml:space="preserve">4.43893814086914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47815084457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48599433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50167989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5644211769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60363340377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62716197967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63500452041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49383687973022</t>
+    <t xml:space="preserve">4.47815179824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4859938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50167942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56442070007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60363388061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62716150283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6350040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49383735656738</t>
   </si>
   <si>
     <t xml:space="preserve">4.59579133987427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66637468338013</t>
+    <t xml:space="preserve">4.66637516021729</t>
   </si>
   <si>
     <t xml:space="preserve">4.68206071853638</t>
@@ -2432,25 +2432,25 @@
     <t xml:space="preserve">4.90949726104736</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05850744247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03497934341431</t>
+    <t xml:space="preserve">5.05850696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03497982025146</t>
   </si>
   <si>
     <t xml:space="preserve">4.99576616287231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95655345916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94871091842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97223806381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87028408050537</t>
+    <t xml:space="preserve">4.95655298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94871044158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97223854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87028360366821</t>
   </si>
   <si>
     <t xml:space="preserve">4.98008108139038</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">5.07419204711914</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0506649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02713680267334</t>
+    <t xml:space="preserve">5.05066537857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02713632583618</t>
   </si>
   <si>
     <t xml:space="preserve">5.08987760543823</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">5.19183206558228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18399000167847</t>
+    <t xml:space="preserve">5.18398952484131</t>
   </si>
   <si>
     <t xml:space="preserve">5.16830444335938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10556364059448</t>
+    <t xml:space="preserve">5.10556316375732</t>
   </si>
   <si>
     <t xml:space="preserve">5.14477682113647</t>
@@ -2495,16 +2495,16 @@
     <t xml:space="preserve">5.25457382202148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3016300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01929473876953</t>
+    <t xml:space="preserve">5.30162954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01929426193237</t>
   </si>
   <si>
     <t xml:space="preserve">4.93302488327026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79970026016235</t>
+    <t xml:space="preserve">4.7996997833252</t>
   </si>
   <si>
     <t xml:space="preserve">4.76048707962036</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">4.76832962036133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68990325927734</t>
+    <t xml:space="preserve">4.68990278244019</t>
   </si>
   <si>
     <t xml:space="preserve">4.69774580001831</t>
@@ -2522,202 +2522,205 @@
     <t xml:space="preserve">4.6114764213562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53305006027222</t>
+    <t xml:space="preserve">4.53305053710938</t>
   </si>
   <si>
     <t xml:space="preserve">4.50952196121216</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47030830383301</t>
+    <t xml:space="preserve">4.47030878067017</t>
   </si>
   <si>
     <t xml:space="preserve">4.55657815933228</t>
   </si>
   <si>
+    <t xml:space="preserve">4.54873514175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57226324081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52520751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54089260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51736497879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58010625839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82322788238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87812662124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8859691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78401470184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65853214263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77617216110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85459899902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94086837768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52122354507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6623911857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73297500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89767122268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68591928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70160484313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59964990615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5369086265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906656265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17614698410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29378652572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7134313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4154109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89381170272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81538534164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9251823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84675645828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72127294540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5879487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61931943893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558786392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77163171768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.738609790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69733285903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63954496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7963981628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98627233505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95325088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07708215713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11835908889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97801733016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06057119369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9037184715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96976184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87069654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82942008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62303447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40839338302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50745820999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56524658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58175754547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64780044555664</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.54873561859131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57226324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52520704269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54089260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51736497879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58010625839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82322835922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87812662124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8859691619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78401470184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70558834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65853214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77617216110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85459804534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94086790084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52122354507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6623911857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73297452926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89767122268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68591928482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70160484313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59964990615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5369086265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906608581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1761474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29378652572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7134313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41541051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89381122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81538581848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9251823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84675550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72127342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58794832229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61931943893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70558786392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77163171768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73861026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69733333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63954448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7963981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98627281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95325088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312505722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07708263397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11835956573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97801733016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06057119369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9037184715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96976184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87069702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82941961288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62303447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40839385986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50745820999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56524658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58175754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64779996871948</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.61477899551392</t>
   </si>
   <si>
     <t xml:space="preserve">4.57350158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51571321487427</t>
+    <t xml:space="preserve">4.51571369171143</t>
   </si>
   <si>
     <t xml:space="preserve">4.3340950012207</t>
@@ -2732,10 +2735,10 @@
     <t xml:space="preserve">4.16898632049561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26805114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4661808013916</t>
+    <t xml:space="preserve">4.2680516242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46618127822876</t>
   </si>
   <si>
     <t xml:space="preserve">4.42490434646606</t>
@@ -2747,25 +2750,25 @@
     <t xml:space="preserve">4.27630662918091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44967031478882</t>
+    <t xml:space="preserve">4.44967079162598</t>
   </si>
   <si>
     <t xml:space="preserve">4.34235048294067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41664886474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55699062347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67256641387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65605640411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71384334564209</t>
+    <t xml:space="preserve">4.41664838790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55699110031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67256689071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65605592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71384382247925</t>
   </si>
   <si>
     <t xml:space="preserve">4.76337623596191</t>
@@ -2780,13 +2783,13 @@
     <t xml:space="preserve">4.75512075424194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77988719940186</t>
+    <t xml:space="preserve">4.7798867225647</t>
   </si>
   <si>
     <t xml:space="preserve">4.73035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82116413116455</t>
+    <t xml:space="preserve">4.82116460800171</t>
   </si>
   <si>
     <t xml:space="preserve">4.92848443984985</t>
@@ -2798,25 +2801,25 @@
     <t xml:space="preserve">4.94499540328979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83767509460449</t>
+    <t xml:space="preserve">4.83767557144165</t>
   </si>
   <si>
     <t xml:space="preserve">4.78814268112183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87895202636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60652351379395</t>
+    <t xml:space="preserve">4.87895154953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60652303695679</t>
   </si>
   <si>
     <t xml:space="preserve">4.66431140899658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81290864944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88720750808716</t>
+    <t xml:space="preserve">4.81290912628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88720703125</t>
   </si>
   <si>
     <t xml:space="preserve">4.93674039840698</t>
@@ -2825,19 +2828,19 @@
     <t xml:space="preserve">5.01103925704956</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11010360717773</t>
+    <t xml:space="preserve">5.11010408401489</t>
   </si>
   <si>
     <t xml:space="preserve">5.16789197921753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23393487930298</t>
+    <t xml:space="preserve">5.23393535614014</t>
   </si>
   <si>
     <t xml:space="preserve">5.19265794754028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22567939758301</t>
+    <t xml:space="preserve">5.22567987442017</t>
   </si>
   <si>
     <t xml:space="preserve">5.26695680618286</t>
@@ -2846,16 +2849,16 @@
     <t xml:space="preserve">5.27521181106567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29172325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3082332611084</t>
+    <t xml:space="preserve">5.29172277450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30823373794556</t>
   </si>
   <si>
     <t xml:space="preserve">5.36602210998535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4320650100708</t>
+    <t xml:space="preserve">5.43206548690796</t>
   </si>
   <si>
     <t xml:space="preserve">5.47334241867065</t>
@@ -2867,16 +2870,16 @@
     <t xml:space="preserve">5.41555452346802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48985290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46508693695068</t>
+    <t xml:space="preserve">5.4898533821106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46508646011353</t>
   </si>
   <si>
     <t xml:space="preserve">5.57240724563599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4485764503479</t>
+    <t xml:space="preserve">5.44857549667358</t>
   </si>
   <si>
     <t xml:space="preserve">5.49810838699341</t>
@@ -2891,7 +2894,7 @@
     <t xml:space="preserve">5.58891820907593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45683145523071</t>
+    <t xml:space="preserve">5.45683097839355</t>
   </si>
   <si>
     <t xml:space="preserve">5.54764080047607</t>
@@ -2903,25 +2906,25 @@
     <t xml:space="preserve">5.63019514083862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61368465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5971736907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58066320419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65496158599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77879238128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82006978988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84483623504639</t>
+    <t xml:space="preserve">5.613685131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59717416763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58066272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65496110916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77879285812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82007026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84483575820923</t>
   </si>
   <si>
     <t xml:space="preserve">5.86134672164917</t>
@@ -2933,13 +2936,13 @@
     <t xml:space="preserve">5.8118143081665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90262365341187</t>
+    <t xml:space="preserve">5.90262413024902</t>
   </si>
   <si>
     <t xml:space="preserve">5.80355930328369</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73751497268677</t>
+    <t xml:space="preserve">5.73751544952393</t>
   </si>
   <si>
     <t xml:space="preserve">6.00168943405151</t>
@@ -2957,22 +2960,22 @@
     <t xml:space="preserve">6.47224807739258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43922662734985</t>
+    <t xml:space="preserve">6.4392261505127</t>
   </si>
   <si>
     <t xml:space="preserve">6.45573711395264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59607934951782</t>
+    <t xml:space="preserve">6.59607887268066</t>
   </si>
   <si>
     <t xml:space="preserve">6.52178049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57956790924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58782386779785</t>
+    <t xml:space="preserve">6.57956838607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58782339096069</t>
   </si>
   <si>
     <t xml:space="preserve">6.51352500915527</t>
@@ -2984,40 +2987,40 @@
     <t xml:space="preserve">6.67863368988037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72816562652588</t>
+    <t xml:space="preserve">6.72816514968872</t>
   </si>
   <si>
     <t xml:space="preserve">6.6703782081604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63735675811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79420900344849</t>
+    <t xml:space="preserve">6.63735628128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79420852661133</t>
   </si>
   <si>
     <t xml:space="preserve">6.73642110824585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68688869476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53829097747803</t>
+    <t xml:space="preserve">6.68688917160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53829145431519</t>
   </si>
   <si>
     <t xml:space="preserve">6.62084531784058</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64561223983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71991109848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74467658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75293254852295</t>
+    <t xml:space="preserve">6.64561176300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71991062164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74467706680298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75293302536011</t>
   </si>
   <si>
     <t xml:space="preserve">6.78595399856567</t>
@@ -3026,25 +3029,25 @@
     <t xml:space="preserve">5.96866750717163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05122184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64670658111572</t>
+    <t xml:space="preserve">6.05122137069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64670610427856</t>
   </si>
   <si>
     <t xml:space="preserve">5.85309171676636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67972803115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39904356002808</t>
+    <t xml:space="preserve">5.67972755432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39904403686523</t>
   </si>
   <si>
     <t xml:space="preserve">5.38253259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66321706771851</t>
+    <t xml:space="preserve">5.66321659088135</t>
   </si>
   <si>
     <t xml:space="preserve">5.60542917251587</t>
@@ -3065,13 +3068,13 @@
     <t xml:space="preserve">5.87785768508911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97692251205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91087961196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91913509368896</t>
+    <t xml:space="preserve">5.9769229888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91087913513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91913461685181</t>
   </si>
   <si>
     <t xml:space="preserve">5.63845062255859</t>
@@ -3080,19 +3083,19 @@
     <t xml:space="preserve">5.78704881668091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94390058517456</t>
+    <t xml:space="preserve">5.94390106201172</t>
   </si>
   <si>
     <t xml:space="preserve">5.96041202545166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8696026802063</t>
+    <t xml:space="preserve">5.86960220336914</t>
   </si>
   <si>
     <t xml:space="preserve">5.98917293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97186279296875</t>
+    <t xml:space="preserve">5.97186326980591</t>
   </si>
   <si>
     <t xml:space="preserve">5.98051786422729</t>
@@ -3125,7 +3128,7 @@
     <t xml:space="preserve">5.76414585113525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71221733093262</t>
+    <t xml:space="preserve">5.71221685409546</t>
   </si>
   <si>
     <t xml:space="preserve">5.82472991943359</t>
@@ -3137,19 +3140,19 @@
     <t xml:space="preserve">5.86800479888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88531398773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87665939331055</t>
+    <t xml:space="preserve">5.88531446456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87665987014771</t>
   </si>
   <si>
     <t xml:space="preserve">5.92858839035034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96320772171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94589853286743</t>
+    <t xml:space="preserve">5.96320819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94589805603027</t>
   </si>
   <si>
     <t xml:space="preserve">5.91993379592896</t>
@@ -3161,10 +3164,10 @@
     <t xml:space="preserve">6.22285461425781</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17092514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28343868255615</t>
+    <t xml:space="preserve">6.17092561721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28343915939331</t>
   </si>
   <si>
     <t xml:space="preserve">6.25747394561768</t>
@@ -3182,25 +3185,25 @@
     <t xml:space="preserve">6.26612854003906</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46519041061401</t>
+    <t xml:space="preserve">6.46519088745117</t>
   </si>
   <si>
     <t xml:space="preserve">6.54308462142944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58635902404785</t>
+    <t xml:space="preserve">6.58635950088501</t>
   </si>
   <si>
     <t xml:space="preserve">6.56904935836792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6382884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56039476394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57770395278931</t>
+    <t xml:space="preserve">6.63828802108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56039428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57770442962646</t>
   </si>
   <si>
     <t xml:space="preserve">6.62097883224487</t>
@@ -3239,13 +3242,10 @@
     <t xml:space="preserve">6.49115562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4392261505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49981021881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55174016952515</t>
+    <t xml:space="preserve">6.49981069564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55173969268799</t>
   </si>
   <si>
     <t xml:space="preserve">6.5950140953064</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">6.70752716064453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68156290054321</t>
+    <t xml:space="preserve">6.68156242370605</t>
   </si>
   <si>
     <t xml:space="preserve">6.60366868972778</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">6.87196969985962</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79407596588135</t>
+    <t xml:space="preserve">6.79407644271851</t>
   </si>
   <si>
     <t xml:space="preserve">6.85466003417969</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">6.77676630020142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7508020401001</t>
+    <t xml:space="preserve">6.75080156326294</t>
   </si>
   <si>
     <t xml:space="preserve">6.52577495574951</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42191696166992</t>
+    <t xml:space="preserve">6.42191648483276</t>
   </si>
   <si>
     <t xml:space="preserve">6.45653581619263</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">6.71618223190308</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72483682632446</t>
+    <t xml:space="preserve">6.72483730316162</t>
   </si>
   <si>
     <t xml:space="preserve">6.75945663452148</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">6.82869577407837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82004117965698</t>
+    <t xml:space="preserve">6.82004070281982</t>
   </si>
   <si>
     <t xml:space="preserve">6.92389917373657</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">6.97582864761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95851898193359</t>
+    <t xml:space="preserve">6.95851850509644</t>
   </si>
   <si>
     <t xml:space="preserve">6.94986343383789</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">7.01910257339478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04506778717041</t>
+    <t xml:space="preserve">7.04506731033325</t>
   </si>
   <si>
     <t xml:space="preserve">7.13161611557007</t>
@@ -3374,7 +3374,7 @@
     <t xml:space="preserve">6.88927984237671</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86331510543823</t>
+    <t xml:space="preserve">6.86331462860107</t>
   </si>
   <si>
     <t xml:space="preserve">6.93255424499512</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">6.91524410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9412088394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96717405319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17489051818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27009344100952</t>
+    <t xml:space="preserve">6.94120931625366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96717357635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17489004135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27009439468384</t>
   </si>
   <si>
     <t xml:space="preserve">7.20085477828979</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">7.22681999206543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16623592376709</t>
+    <t xml:space="preserve">7.16623544692993</t>
   </si>
   <si>
     <t xml:space="preserve">7.14892578125</t>
@@ -3416,37 +3416,37 @@
     <t xml:space="preserve">7.26143932342529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31336832046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33933258056641</t>
+    <t xml:space="preserve">7.31336784362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33933305740356</t>
   </si>
   <si>
     <t xml:space="preserve">7.42588138580322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44319152832031</t>
+    <t xml:space="preserve">7.44319200515747</t>
   </si>
   <si>
     <t xml:space="preserve">7.48646545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23547458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29605913162231</t>
+    <t xml:space="preserve">7.23547506332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29605865478516</t>
   </si>
   <si>
     <t xml:space="preserve">7.19220066070557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45184659957886</t>
+    <t xml:space="preserve">7.4518461227417</t>
   </si>
   <si>
     <t xml:space="preserve">7.38260746002197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35664224624634</t>
+    <t xml:space="preserve">7.3566427230835</t>
   </si>
   <si>
     <t xml:space="preserve">7.52108478546143</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">7.84997081756592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7288031578064</t>
+    <t xml:space="preserve">7.72880220413208</t>
   </si>
   <si>
     <t xml:space="preserve">7.7634220123291</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">7.40857219696045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63359880447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72014808654785</t>
+    <t xml:space="preserve">7.63359785079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72014713287354</t>
   </si>
   <si>
     <t xml:space="preserve">7.88458967208862</t>
@@ -3488,16 +3488,16 @@
     <t xml:space="preserve">7.65090847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66821765899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78073120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83266162872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8240065574646</t>
+    <t xml:space="preserve">7.6682186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78073215484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83266067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82400560379028</t>
   </si>
   <si>
     <t xml:space="preserve">7.75476694107056</t>
@@ -3509,31 +3509,31 @@
     <t xml:space="preserve">7.69418334960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67687368392944</t>
+    <t xml:space="preserve">7.67687273025513</t>
   </si>
   <si>
     <t xml:space="preserve">7.94517421722412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01441383361816</t>
+    <t xml:space="preserve">8.01441287994385</t>
   </si>
   <si>
     <t xml:space="preserve">8.11827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05768775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12692737579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06634140014648</t>
+    <t xml:space="preserve">8.05768871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12692642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0663423538208</t>
   </si>
   <si>
     <t xml:space="preserve">8.02306842803955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10961723327637</t>
+    <t xml:space="preserve">8.10961627960205</t>
   </si>
   <si>
     <t xml:space="preserve">8.17885589599609</t>
@@ -3554,16 +3554,16 @@
     <t xml:space="preserve">8.00575828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99710369110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87593555450439</t>
+    <t xml:space="preserve">7.99710273742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87593650817871</t>
   </si>
   <si>
     <t xml:space="preserve">8.30867862701416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24809551239014</t>
+    <t xml:space="preserve">8.24809455871582</t>
   </si>
   <si>
     <t xml:space="preserve">8.27406024932861</t>
@@ -3572,22 +3572,22 @@
     <t xml:space="preserve">8.41253757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.576979637146</t>
+    <t xml:space="preserve">8.57698059082031</t>
   </si>
   <si>
     <t xml:space="preserve">8.58563423156738</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65487384796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54236125946045</t>
+    <t xml:space="preserve">8.65487289428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54236030578613</t>
   </si>
   <si>
     <t xml:space="preserve">8.62025451660156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81066226959229</t>
+    <t xml:space="preserve">8.81066131591797</t>
   </si>
   <si>
     <t xml:space="preserve">8.82797145843506</t>
@@ -47525,7 +47525,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1648" t="s">
-        <v>840</v>
+        <v>899</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47551,7 +47551,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G1649" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -47577,7 +47577,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1650" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -47603,7 +47603,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1651" t="s">
-        <v>840</v>
+        <v>899</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47629,7 +47629,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1652" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -47655,7 +47655,7 @@
         <v>5.25</v>
       </c>
       <c r="G1653" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -47681,7 +47681,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1654" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -47707,7 +47707,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1655" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -47733,7 +47733,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1656" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -47759,7 +47759,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1657" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -47811,7 +47811,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1659" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -47837,7 +47837,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1660" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -47863,7 +47863,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1661" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -47889,7 +47889,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1662" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -47915,7 +47915,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1663" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -47941,7 +47941,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1664" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -47993,7 +47993,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1666" t="s">
-        <v>840</v>
+        <v>899</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48071,7 +48071,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1669" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -48097,7 +48097,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1670" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -48123,7 +48123,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1671" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -48175,7 +48175,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1673" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -48201,7 +48201,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1674" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -48279,7 +48279,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1677" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -48305,7 +48305,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1678" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -48383,7 +48383,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1681" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -48409,7 +48409,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1682" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -48461,7 +48461,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1684" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -48565,7 +48565,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1688" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -48591,7 +48591,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1689" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -48617,7 +48617,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1690" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -48643,7 +48643,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1691" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -48669,7 +48669,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1692" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -48721,7 +48721,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1694" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -48773,7 +48773,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1696" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -48825,7 +48825,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1698" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -48851,7 +48851,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1699" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -48903,7 +48903,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1701" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -48929,7 +48929,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1702" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -48955,7 +48955,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G1703" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -49033,7 +49033,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1706" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -49059,7 +49059,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G1707" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -49111,7 +49111,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G1709" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -49163,7 +49163,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1711" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -49189,7 +49189,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1712" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -49241,7 +49241,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G1714" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -49267,7 +49267,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1715" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -49293,7 +49293,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1716" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -49345,7 +49345,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1718" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -49371,7 +49371,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1719" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -49397,7 +49397,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G1720" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -49449,7 +49449,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1722" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -49475,7 +49475,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1723" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -49501,7 +49501,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1724" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -49553,7 +49553,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1726" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -49579,7 +49579,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1727" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -49631,7 +49631,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1729" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -49683,7 +49683,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1731" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -49709,7 +49709,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1732" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -49735,7 +49735,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -49761,7 +49761,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1734" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -49839,7 +49839,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1737" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -49865,7 +49865,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1738" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -49917,7 +49917,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1740" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -49943,7 +49943,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G1741" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -49969,7 +49969,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1742" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -49995,7 +49995,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G1743" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -50021,7 +50021,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G1744" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -50047,7 +50047,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -50073,7 +50073,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G1746" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -50099,7 +50099,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1747" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -50125,7 +50125,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1748" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -50151,7 +50151,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1749" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -50177,7 +50177,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1750" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -50203,7 +50203,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1751" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -50229,7 +50229,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G1752" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -50255,7 +50255,7 @@
         <v>6.5</v>
       </c>
       <c r="G1753" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -50281,7 +50281,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1754" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -50307,7 +50307,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1755" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -50333,7 +50333,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1756" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -50359,7 +50359,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G1757" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -50385,7 +50385,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1758" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -50411,7 +50411,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1759" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -50437,7 +50437,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1760" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -50463,7 +50463,7 @@
         <v>6.75</v>
       </c>
       <c r="G1761" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -50489,7 +50489,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1762" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -50515,7 +50515,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1763" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -50541,7 +50541,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1764" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -50567,7 +50567,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1765" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -50593,7 +50593,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1766" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -50619,7 +50619,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1767" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -50645,7 +50645,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1768" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -50671,7 +50671,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1769" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -50697,7 +50697,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1770" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -50723,7 +50723,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1771" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -50749,7 +50749,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G1772" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -50775,7 +50775,7 @@
         <v>6.75</v>
       </c>
       <c r="G1773" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -50801,7 +50801,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1774" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -50827,7 +50827,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1775" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -50853,7 +50853,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1776" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -50879,7 +50879,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1777" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -50905,7 +50905,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1778" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -50931,7 +50931,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1779" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -50957,7 +50957,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1780" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -50983,7 +50983,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1781" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -51009,7 +51009,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G1782" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -51035,7 +51035,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1783" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -51061,7 +51061,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1784" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -51087,7 +51087,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1785" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -51113,7 +51113,7 @@
         <v>7</v>
       </c>
       <c r="G1786" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -51139,7 +51139,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1787" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -51165,7 +51165,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1788" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -51191,7 +51191,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1789" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -51217,7 +51217,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G1790" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -51243,7 +51243,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1791" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -51269,7 +51269,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1792" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -51295,7 +51295,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G1793" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -51321,7 +51321,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1794" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -51347,7 +51347,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1795" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -51373,7 +51373,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1796" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -51399,7 +51399,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1797" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -51425,7 +51425,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1798" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -51451,7 +51451,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1799" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -51477,7 +51477,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G1800" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -51503,7 +51503,7 @@
         <v>7.75</v>
       </c>
       <c r="G1801" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -51529,7 +51529,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1802" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -51555,7 +51555,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1803" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -51581,7 +51581,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1804" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -51607,7 +51607,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G1805" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -51633,7 +51633,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1806" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -51659,7 +51659,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -51685,7 +51685,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G1808" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -51711,7 +51711,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1809" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -51737,7 +51737,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1810" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -51763,7 +51763,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1811" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -51789,7 +51789,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G1812" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -51815,7 +51815,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1813" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -51841,7 +51841,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1814" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -51867,7 +51867,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G1815" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -51893,7 +51893,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1816" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -51919,7 +51919,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1817" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -51945,7 +51945,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1818" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -51971,7 +51971,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1819" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51997,7 +51997,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1820" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -52023,7 +52023,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1821" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -52049,7 +52049,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1822" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -52075,7 +52075,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1823" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -52101,7 +52101,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1824" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -52127,7 +52127,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1825" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -52153,7 +52153,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G1826" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -52179,7 +52179,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1827" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -52205,7 +52205,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1828" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -52231,7 +52231,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1829" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -52257,7 +52257,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1830" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -52283,7 +52283,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1831" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -52309,7 +52309,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G1832" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -52335,7 +52335,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G1833" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -52361,7 +52361,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1834" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -52387,7 +52387,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1835" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -52413,7 +52413,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1836" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -52439,7 +52439,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G1837" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -52465,7 +52465,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1838" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -52491,7 +52491,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G1839" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -52517,7 +52517,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G1840" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -52543,7 +52543,7 @@
         <v>6.75</v>
       </c>
       <c r="G1841" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -52569,7 +52569,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1842" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -52595,7 +52595,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G1843" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -52621,7 +52621,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1844" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -52647,7 +52647,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1845" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -52673,7 +52673,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1846" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -52699,7 +52699,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G1847" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -52725,7 +52725,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1848" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -52751,7 +52751,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1849" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -52777,7 +52777,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1850" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -52803,7 +52803,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1851" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -52829,7 +52829,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1852" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -52855,7 +52855,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1853" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -52881,7 +52881,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G1854" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -52907,7 +52907,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1855" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -52933,7 +52933,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1856" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -52959,7 +52959,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1857" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -52985,7 +52985,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1858" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -53011,7 +53011,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -53037,7 +53037,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1860" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -53063,7 +53063,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1861" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -53089,7 +53089,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G1862" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -53115,7 +53115,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1863" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -53141,7 +53141,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1864" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -53167,7 +53167,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1865" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -53193,7 +53193,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1866" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -53219,7 +53219,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1867" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -53245,7 +53245,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G1868" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -53271,7 +53271,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G1869" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -53297,7 +53297,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1870" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -53323,7 +53323,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1871" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -53349,7 +53349,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1872" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -53375,7 +53375,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G1873" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53401,7 +53401,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G1874" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53427,7 +53427,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1875" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53453,7 +53453,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1876" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53479,7 +53479,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1877" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53505,7 +53505,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1878" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -53531,7 +53531,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G1879" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -53557,7 +53557,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1880" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53583,7 +53583,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1881" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -53609,7 +53609,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1882" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -53635,7 +53635,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1883" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -53661,7 +53661,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1884" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -53687,7 +53687,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1885" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -53713,7 +53713,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G1886" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -53739,7 +53739,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G1887" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -53765,7 +53765,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G1888" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -53791,7 +53791,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G1889" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -53817,7 +53817,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1890" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -53843,7 +53843,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1891" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -53869,7 +53869,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G1892" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -53895,7 +53895,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1893" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -53921,7 +53921,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G1894" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -53947,7 +53947,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1895" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -53973,7 +53973,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G1896" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53999,7 +53999,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1897" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -54025,7 +54025,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1898" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -54051,7 +54051,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1899" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -54077,7 +54077,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1900" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -54103,7 +54103,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1901" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -54129,7 +54129,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1902" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -54155,7 +54155,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1903" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -54181,7 +54181,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1904" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -54207,7 +54207,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G1905" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -54233,7 +54233,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G1906" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -54259,7 +54259,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1907" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -54285,7 +54285,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1908" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -54311,7 +54311,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1909" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -54337,7 +54337,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1910" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -54363,7 +54363,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G1911" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -54389,7 +54389,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G1912" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -54415,7 +54415,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G1913" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -54441,7 +54441,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1914" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -54467,7 +54467,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G1915" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -54493,7 +54493,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1916" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -54519,7 +54519,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1917" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54545,7 +54545,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G1918" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54571,7 +54571,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1919" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54597,7 +54597,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G1920" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -54623,7 +54623,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1921" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -54649,7 +54649,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1922" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -54675,7 +54675,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G1923" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -54701,7 +54701,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1924" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -54727,7 +54727,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1925" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -54753,7 +54753,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1926" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -54779,7 +54779,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1927" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -54805,7 +54805,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1928" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -54831,7 +54831,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1929" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -54857,7 +54857,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1930" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54883,7 +54883,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1931" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -54909,7 +54909,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1932" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -54935,7 +54935,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1933" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -54961,7 +54961,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1934" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -54987,7 +54987,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1935" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -55013,7 +55013,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1936" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -55039,7 +55039,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -55065,7 +55065,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1938" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -55091,7 +55091,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1939" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -55117,7 +55117,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G1940" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -55143,7 +55143,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G1941" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -55169,7 +55169,7 @@
         <v>7.5</v>
       </c>
       <c r="G1942" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -55195,7 +55195,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1943" t="s">
-        <v>1075</v>
+        <v>982</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -55325,7 +55325,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1948" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -55351,7 +55351,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1949" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -55377,7 +55377,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1950" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -55455,7 +55455,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1953" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -55533,7 +55533,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1956" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55585,7 +55585,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1958" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -55663,7 +55663,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1961" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -55689,7 +55689,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1962" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -55715,7 +55715,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G1963" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -55923,7 +55923,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1971" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -55975,7 +55975,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1973" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -56053,7 +56053,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1976" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -56105,7 +56105,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1978" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -56131,7 +56131,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1979" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -56235,7 +56235,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -56365,7 +56365,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G1988" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -56443,7 +56443,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1991" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -56547,7 +56547,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1995" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -70361,7 +70361,7 @@
     </row>
     <row r="2527">
       <c r="A2527" s="1" t="n">
-        <v>45996.6910648148</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2527" t="n">
         <v>150105</v>
@@ -70382,6 +70382,32 @@
         <v>1444</v>
       </c>
       <c r="H2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="1" t="n">
+        <v>45999.6912268518</v>
+      </c>
+      <c r="B2528" t="n">
+        <v>75964</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>14.6000003814697</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>14.3800001144409</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>14.3800001144409</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>14.539999961853</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H2528" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49119520187378</t>
+    <t xml:space="preserve">4.49119472503662</t>
   </si>
   <si>
     <t xml:space="preserve">CE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52814531326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46432209014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30644035339355</t>
+    <t xml:space="preserve">4.52814483642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46432113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30644083023071</t>
   </si>
   <si>
     <t xml:space="preserve">4.26613092422485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31315946578979</t>
+    <t xml:space="preserve">4.31315898895264</t>
   </si>
   <si>
     <t xml:space="preserve">4.31987762451172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36690521240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27284955978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23589849472046</t>
+    <t xml:space="preserve">4.3669056892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27284860610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2358980178833</t>
   </si>
   <si>
     <t xml:space="preserve">4.05114507675171</t>
@@ -77,31 +77,31 @@
     <t xml:space="preserve">4.08473682403564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74210214614868</t>
+    <t xml:space="preserve">3.74210238456726</t>
   </si>
   <si>
     <t xml:space="preserve">3.91677856445312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03099012374878</t>
+    <t xml:space="preserve">4.03098964691162</t>
   </si>
   <si>
     <t xml:space="preserve">4.15527868270874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12840509414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01419448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12504577636719</t>
+    <t xml:space="preserve">4.1284065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01419401168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12504625320435</t>
   </si>
   <si>
     <t xml:space="preserve">4.12168741226196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94701099395752</t>
+    <t xml:space="preserve">3.94701075553894</t>
   </si>
   <si>
     <t xml:space="preserve">3.80256700515747</t>
@@ -110,76 +110,76 @@
     <t xml:space="preserve">3.83615899085999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86975073814392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58086228370667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42970061302185</t>
+    <t xml:space="preserve">3.86975002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58086276054382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42970108985901</t>
   </si>
   <si>
     <t xml:space="preserve">3.75217962265015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60773634910583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84959578514099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670156478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96716642379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0645809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82944011688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77233409881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90334224700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87982869148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72866606712341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79584932327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88318705558777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95708775520325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13176441192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1955885887146</t>
+    <t xml:space="preserve">3.6077356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84959530830383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670132637024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96716690063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06458187103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8294403553009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77233481407166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90334153175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87982821464539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72866582870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79584860801697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88318657875061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95708847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13176488876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19558811187744</t>
   </si>
   <si>
     <t xml:space="preserve">4.18551158905029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13848352432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22246217727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29972267150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35682916641235</t>
+    <t xml:space="preserve">4.13848304748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22246170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29972219467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3568286895752</t>
   </si>
   <si>
     <t xml:space="preserve">4.25605344772339</t>
@@ -191,19 +191,19 @@
     <t xml:space="preserve">4.14856052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32659578323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26948928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16535615921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09817266464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04778623580933</t>
+    <t xml:space="preserve">4.3265962600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26949119567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16535663604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09817361831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04778575897217</t>
   </si>
   <si>
     <t xml:space="preserve">4.04106760025024</t>
@@ -212,64 +212,64 @@
     <t xml:space="preserve">3.93021535873413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91006064414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81936240196228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75889825820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71186947822571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93357467651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82608151435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0813775062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15863752365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17879295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21238422393799</t>
+    <t xml:space="preserve">3.91005969047546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81936264038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75889801979065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71187043190002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93357396125793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82608127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08137702941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15863800048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17879390716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21238374710083</t>
   </si>
   <si>
     <t xml:space="preserve">4.21574401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28292751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30308103561401</t>
+    <t xml:space="preserve">4.2829270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30308198928833</t>
   </si>
   <si>
     <t xml:space="preserve">4.3534688949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19894790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07465934753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08809566497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06122207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02427101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93693399429321</t>
+    <t xml:space="preserve">4.1989483833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07465887069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08809518814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06122255325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0242714881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93693375587463</t>
   </si>
   <si>
     <t xml:space="preserve">4.21648979187012</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">4.14420700073242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19927930831909</t>
+    <t xml:space="preserve">4.19927978515625</t>
   </si>
   <si>
     <t xml:space="preserve">4.25435161590576</t>
@@ -287,25 +287,25 @@
     <t xml:space="preserve">4.23369979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23714160919189</t>
+    <t xml:space="preserve">4.23714113235474</t>
   </si>
   <si>
     <t xml:space="preserve">4.49185180664062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4987359046936</t>
+    <t xml:space="preserve">4.49873638153076</t>
   </si>
   <si>
     <t xml:space="preserve">4.47119998931885</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45743179321289</t>
+    <t xml:space="preserve">4.45743227005005</t>
   </si>
   <si>
     <t xml:space="preserve">4.46431636810303</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37826538085938</t>
+    <t xml:space="preserve">4.37826442718506</t>
   </si>
   <si>
     <t xml:space="preserve">4.31975078582764</t>
@@ -314,43 +314,43 @@
     <t xml:space="preserve">4.37138080596924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28188800811768</t>
+    <t xml:space="preserve">4.28188896179199</t>
   </si>
   <si>
     <t xml:space="preserve">4.42989540100098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34040212631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35072898864746</t>
+    <t xml:space="preserve">4.34040260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35072946548462</t>
   </si>
   <si>
     <t xml:space="preserve">4.25090980529785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03750419616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91703319549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98243069648743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884379386902</t>
+    <t xml:space="preserve">4.03750324249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91703271865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98243117332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884450912476</t>
   </si>
   <si>
     <t xml:space="preserve">4.1373233795166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3369607925415</t>
+    <t xml:space="preserve">4.33696126937866</t>
   </si>
   <si>
     <t xml:space="preserve">4.38170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42301177978516</t>
+    <t xml:space="preserve">4.423011302948</t>
   </si>
   <si>
     <t xml:space="preserve">4.52971458435059</t>
@@ -359,214 +359,214 @@
     <t xml:space="preserve">3.74148941040039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75181531906128</t>
+    <t xml:space="preserve">3.75181484222412</t>
   </si>
   <si>
     <t xml:space="preserve">3.73116326332092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84130811691284</t>
+    <t xml:space="preserve">3.84130764007568</t>
   </si>
   <si>
     <t xml:space="preserve">3.65199613571167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5246410369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42826437950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50743055343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65887975692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75525712966919</t>
+    <t xml:space="preserve">3.52464127540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42826414108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50743079185486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65888047218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75525784492493</t>
   </si>
   <si>
     <t xml:space="preserve">3.82065606117249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78623509407043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670657157898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96522188186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95145297050476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04094552993774</t>
+    <t xml:space="preserve">3.78623580932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670704841614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96522116661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95145273208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04094648361206</t>
   </si>
   <si>
     <t xml:space="preserve">4.01340961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94456934928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98931574821472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95833730697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79656076431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90326428413391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80000352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68641638755798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70018482208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76558303833008</t>
+    <t xml:space="preserve">3.94456887245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98931550979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95833659172058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7965612411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90326452255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80000376701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68641686439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7001850605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76558375358582</t>
   </si>
   <si>
     <t xml:space="preserve">3.70362734794617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66576480865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66920614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55217719078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4867787361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4798948764801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37319207191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37181520462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50054693222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68985867500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561971664429</t>
+    <t xml:space="preserve">3.66576385498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66920638084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55217695236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48677897453308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47989392280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37319183349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3718147277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50054669380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68985843658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561923980713</t>
   </si>
   <si>
     <t xml:space="preserve">3.45235824584961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47645258903503</t>
+    <t xml:space="preserve">3.47645306587219</t>
   </si>
   <si>
     <t xml:space="preserve">3.64511227607727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7208366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7070689201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77935171127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80688762664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61413359642029</t>
+    <t xml:space="preserve">3.72083735466003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706820487976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77935147285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80688810348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61413431167603</t>
   </si>
   <si>
     <t xml:space="preserve">3.61757636070251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57971334457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56594514846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49366307258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49022150039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44891691207886</t>
+    <t xml:space="preserve">3.57971382141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56594562530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49366331100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49022078514099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4489164352417</t>
   </si>
   <si>
     <t xml:space="preserve">3.63822817802429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49710440635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38696026802063</t>
+    <t xml:space="preserve">3.49710488319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38695979118347</t>
   </si>
   <si>
     <t xml:space="preserve">3.35804653167725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37456798553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31123518943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32638001441956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3552930355072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41587233543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51431488990784</t>
+    <t xml:space="preserve">3.37456870079041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31123447418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3263795375824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35529327392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41587281227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51431560516357</t>
   </si>
   <si>
     <t xml:space="preserve">3.48333621025085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51087236404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51775717735291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47301030158997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57627153396606</t>
+    <t xml:space="preserve">3.51087260246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51775693893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47301054000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5762722492218</t>
   </si>
   <si>
     <t xml:space="preserve">3.53496718406677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64855432510376</t>
+    <t xml:space="preserve">3.64855456352234</t>
   </si>
   <si>
     <t xml:space="preserve">3.67953252792358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59692430496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64167046546936</t>
+    <t xml:space="preserve">3.59692406654358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6416699886322</t>
   </si>
   <si>
     <t xml:space="preserve">3.63134431838989</t>
@@ -575,19 +575,19 @@
     <t xml:space="preserve">3.56250333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53152537345886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45580077171326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41174244880676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42964100837708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45924282073975</t>
+    <t xml:space="preserve">3.53152561187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45580053329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41174221038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42964124679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45924210548401</t>
   </si>
   <si>
     <t xml:space="preserve">3.44203209877014</t>
@@ -599,52 +599,52 @@
     <t xml:space="preserve">3.6347861289978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67609095573425</t>
+    <t xml:space="preserve">3.67609047889709</t>
   </si>
   <si>
     <t xml:space="preserve">3.62790179252625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58659815788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54529333114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55906200408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56938719749451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71739459037781</t>
+    <t xml:space="preserve">3.58659768104553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54529356956482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5590615272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56938767433167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71739530563354</t>
   </si>
   <si>
     <t xml:space="preserve">3.94112706184387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00996732711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88605499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97210502624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83442354202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92735862731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98587393760681</t>
+    <t xml:space="preserve">4.00996780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88605427742004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97210550308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83442401885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92735886573792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98587274551392</t>
   </si>
   <si>
     <t xml:space="preserve">4.0547137260437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93080043792725</t>
+    <t xml:space="preserve">3.9308009147644</t>
   </si>
   <si>
     <t xml:space="preserve">4.04438781738281</t>
@@ -653,19 +653,19 @@
     <t xml:space="preserve">4.06159830093384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91014885902405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.899822473526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05815601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07192420959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07880830764771</t>
+    <t xml:space="preserve">3.91014862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89982271194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05815649032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07192468643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07880878448486</t>
   </si>
   <si>
     <t xml:space="preserve">4.03061962127686</t>
@@ -674,34 +674,34 @@
     <t xml:space="preserve">4.19583702087402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2096061706543</t>
+    <t xml:space="preserve">4.20960569381714</t>
   </si>
   <si>
     <t xml:space="preserve">4.29565620422363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27844572067261</t>
+    <t xml:space="preserve">4.27844619750977</t>
   </si>
   <si>
     <t xml:space="preserve">4.2474684715271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30254077911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1269965171814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13043880462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20272159576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10634422302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12011289596558</t>
+    <t xml:space="preserve">4.30254125595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12699699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13043832778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20272064208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10634469985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12011337280273</t>
   </si>
   <si>
     <t xml:space="preserve">4.17862749099731</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">4.04783010482788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14076471328735</t>
+    <t xml:space="preserve">4.14076519012451</t>
   </si>
   <si>
     <t xml:space="preserve">4.1510910987854</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">4.15453290939331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18206930160522</t>
+    <t xml:space="preserve">4.18206882476807</t>
   </si>
   <si>
     <t xml:space="preserve">4.15797519683838</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">4.21304750442505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32319307327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449670791626</t>
+    <t xml:space="preserve">4.32319211959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449718475342</t>
   </si>
   <si>
     <t xml:space="preserve">4.43333768844604</t>
@@ -752,28 +752,28 @@
     <t xml:space="preserve">4.3851490020752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47464227676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41956996917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37482261657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41268491744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34384441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30942440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36793899536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35417079925537</t>
+    <t xml:space="preserve">4.47464179992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41956901550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37482404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41268539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34384489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30942487716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36793851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35417127609253</t>
   </si>
   <si>
     <t xml:space="preserve">4.28533029556274</t>
@@ -785,22 +785,22 @@
     <t xml:space="preserve">4.40580129623413</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4884090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50906276702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53659820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5434832572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44710540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67083787918091</t>
+    <t xml:space="preserve">4.48840999603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50906229019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53659915924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54348230361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.447105884552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67083740234375</t>
   </si>
   <si>
     <t xml:space="preserve">4.69899606704712</t>
@@ -809,40 +809,40 @@
     <t xml:space="preserve">4.80107259750366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7165961265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83627080917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8609094619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85034990310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87850856781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7834734916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72011518478394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68491697311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7306752204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75179481506348</t>
+    <t xml:space="preserve">4.71659564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83627128601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86091041564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85035037994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87850904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78347253799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72011470794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68491744995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73067569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75179386138916</t>
   </si>
   <si>
     <t xml:space="preserve">4.81515169143677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81163167953491</t>
+    <t xml:space="preserve">4.81163263320923</t>
   </si>
   <si>
     <t xml:space="preserve">4.9277868270874</t>
@@ -851,49 +851,49 @@
     <t xml:space="preserve">4.93834638595581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87498950958252</t>
+    <t xml:space="preserve">4.87498903274536</t>
   </si>
   <si>
     <t xml:space="preserve">4.80811166763306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8045916557312</t>
+    <t xml:space="preserve">4.80459213256836</t>
   </si>
   <si>
     <t xml:space="preserve">4.78699350357056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95946502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86442995071411</t>
+    <t xml:space="preserve">4.95946598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86442947387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.89258813858032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89610862731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91370725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97354459762573</t>
+    <t xml:space="preserve">4.89610815048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91370677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97354507446289</t>
   </si>
   <si>
     <t xml:space="preserve">4.97706460952759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94538640975952</t>
+    <t xml:space="preserve">4.94538593292236</t>
   </si>
   <si>
     <t xml:space="preserve">5.1108193397522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25865268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06154155731201</t>
+    <t xml:space="preserve">5.2586522102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0615406036377</t>
   </si>
   <si>
     <t xml:space="preserve">5.08618021011353</t>
@@ -902,16 +902,16 @@
     <t xml:space="preserve">5.10377931594849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09673929214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0509819984436</t>
+    <t xml:space="preserve">5.09674024581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05098152160645</t>
   </si>
   <si>
     <t xml:space="preserve">5.08969974517822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01930284500122</t>
+    <t xml:space="preserve">5.01930236816406</t>
   </si>
   <si>
     <t xml:space="preserve">5.04746150970459</t>
@@ -923,22 +923,22 @@
     <t xml:space="preserve">4.91018724441528</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00874328613281</t>
+    <t xml:space="preserve">5.00874376296997</t>
   </si>
   <si>
     <t xml:space="preserve">5.10025930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06858015060425</t>
+    <t xml:space="preserve">5.06857967376709</t>
   </si>
   <si>
     <t xml:space="preserve">5.13193798065186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04042148590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1248984336853</t>
+    <t xml:space="preserve">5.04042196273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12489795684814</t>
   </si>
   <si>
     <t xml:space="preserve">5.20937442779541</t>
@@ -950,13 +950,13 @@
     <t xml:space="preserve">5.21289443969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0369029045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16361618041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27273225784302</t>
+    <t xml:space="preserve">5.03690147399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16361665725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27273178100586</t>
   </si>
   <si>
     <t xml:space="preserve">5.23049354553223</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">5.15305709838867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20233488082886</t>
+    <t xml:space="preserve">5.20233535766602</t>
   </si>
   <si>
     <t xml:space="preserve">5.11433839797974</t>
@@ -974,34 +974,34 @@
     <t xml:space="preserve">5.10729885101318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00522375106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99818277359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01226329803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04394197463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06506109237671</t>
+    <t xml:space="preserve">5.00522327423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99818325042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01226282119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04394149780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06506156921387</t>
   </si>
   <si>
     <t xml:space="preserve">5.15657663345337</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34312915802002</t>
+    <t xml:space="preserve">5.34312868118286</t>
   </si>
   <si>
     <t xml:space="preserve">5.30089092254639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27977132797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30792999267578</t>
+    <t xml:space="preserve">5.27977180480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30793046951294</t>
   </si>
   <si>
     <t xml:space="preserve">5.25161266326904</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">5.29033088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33608913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34664869308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36776828765869</t>
+    <t xml:space="preserve">5.33608865737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34664821624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36776733398438</t>
   </si>
   <si>
     <t xml:space="preserve">5.35368871688843</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">5.31145000457764</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3255295753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28329086303711</t>
+    <t xml:space="preserve">5.32553005218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28329133987427</t>
   </si>
   <si>
     <t xml:space="preserve">5.23401355743408</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">5.31497001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29737091064453</t>
+    <t xml:space="preserve">5.29737043380737</t>
   </si>
   <si>
     <t xml:space="preserve">5.19177532196045</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35720777511597</t>
+    <t xml:space="preserve">5.35720825195312</t>
   </si>
   <si>
     <t xml:space="preserve">5.07210111618042</t>
@@ -1076,70 +1076,70 @@
     <t xml:space="preserve">4.94186639785767</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86794900894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92426681518555</t>
+    <t xml:space="preserve">4.86794948577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92426729202271</t>
   </si>
   <si>
     <t xml:space="preserve">4.98058414459229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03338193893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05450105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18473529815674</t>
+    <t xml:space="preserve">5.03338289260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0545015335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1847357749939</t>
   </si>
   <si>
     <t xml:space="preserve">5.17417573928833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21993398666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17769527435303</t>
+    <t xml:space="preserve">5.21993446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17769575119019</t>
   </si>
   <si>
     <t xml:space="preserve">5.22697401046753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28681135177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02282285690308</t>
+    <t xml:space="preserve">5.28681182861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02282333374023</t>
   </si>
   <si>
     <t xml:space="preserve">5.00170373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02986240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.058021068573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99114322662354</t>
+    <t xml:space="preserve">5.02986288070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05802154541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92074632644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99114465713501</t>
   </si>
   <si>
     <t xml:space="preserve">5.37128782272339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47688293457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48392295837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44168424606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43464469909668</t>
+    <t xml:space="preserve">5.47688341140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48392343521118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44168472290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43464517593384</t>
   </si>
   <si>
     <t xml:space="preserve">5.5261607170105</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">5.46984243392944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40648603439331</t>
+    <t xml:space="preserve">5.40648508071899</t>
   </si>
   <si>
     <t xml:space="preserve">5.37832736968994</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">5.18825531005859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13897752761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3290491104126</t>
+    <t xml:space="preserve">5.13897800445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32904958724976</t>
   </si>
   <si>
     <t xml:space="preserve">5.14601707458496</t>
@@ -1175,37 +1175,37 @@
     <t xml:space="preserve">5.24457311630249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22345495223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2375340461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16009664535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11785888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97002458572388</t>
+    <t xml:space="preserve">5.22345399856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23753356933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16009712219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11785840988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97002506256104</t>
   </si>
   <si>
     <t xml:space="preserve">5.21899938583374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14661455154419</t>
+    <t xml:space="preserve">5.14661359786987</t>
   </si>
   <si>
     <t xml:space="preserve">4.98012685775757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94393444061279</t>
+    <t xml:space="preserve">4.94393396377563</t>
   </si>
   <si>
     <t xml:space="preserve">4.81364011764526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84259462356567</t>
+    <t xml:space="preserve">4.84259510040283</t>
   </si>
   <si>
     <t xml:space="preserve">4.85707187652588</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">4.82087898254395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80640172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5602912902832</t>
+    <t xml:space="preserve">4.80640125274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56029081344604</t>
   </si>
   <si>
     <t xml:space="preserve">4.46618986129761</t>
@@ -1226,13 +1226,13 @@
     <t xml:space="preserve">4.21284008026123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45171308517456</t>
+    <t xml:space="preserve">4.4517126083374</t>
   </si>
   <si>
     <t xml:space="preserve">4.37208843231201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52409791946411</t>
+    <t xml:space="preserve">4.52409839630127</t>
   </si>
   <si>
     <t xml:space="preserve">4.40828132629395</t>
@@ -1244,10 +1244,10 @@
     <t xml:space="preserve">4.29246377944946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39380407333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45895147323608</t>
+    <t xml:space="preserve">4.3938045501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45895099639893</t>
   </si>
   <si>
     <t xml:space="preserve">4.43723583221436</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">4.61096096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64715433120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69058513641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57476806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58200645446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48790502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.545814037323</t>
+    <t xml:space="preserve">4.64715385437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69058465957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57476854324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58200597763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48790550231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54581356048584</t>
   </si>
   <si>
     <t xml:space="preserve">4.58924531936646</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">4.6037220954895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68334579467773</t>
+    <t xml:space="preserve">4.68334627151489</t>
   </si>
   <si>
     <t xml:space="preserve">4.6978235244751</t>
@@ -1292,16 +1292,16 @@
     <t xml:space="preserve">4.62543773651123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63267707824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61819982528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56752920150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44447374343872</t>
+    <t xml:space="preserve">4.63267660140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61819934844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56752967834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44447422027588</t>
   </si>
   <si>
     <t xml:space="preserve">4.42999696731567</t>
@@ -1316,55 +1316,55 @@
     <t xml:space="preserve">4.51685905456543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50962162017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1766471862793</t>
+    <t xml:space="preserve">4.50962114334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17664766311646</t>
   </si>
   <si>
     <t xml:space="preserve">4.10426187515259</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04635381698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02463817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03187561035156</t>
+    <t xml:space="preserve">4.04635429382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0246376991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03187656402588</t>
   </si>
   <si>
     <t xml:space="preserve">4.05359220504761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06806898117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9739682674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00292205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85091257095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87262725830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93053603172302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9232976436615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11149978637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22731733322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20560216903687</t>
+    <t xml:space="preserve">4.06806945800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97396779060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00292253494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85091304779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8726282119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93053650856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92329812049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11150026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22731781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20560169219971</t>
   </si>
   <si>
     <t xml:space="preserve">4.22007894515991</t>
@@ -1373,73 +1373,73 @@
     <t xml:space="preserve">4.23455619812012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25627183914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27798748016357</t>
+    <t xml:space="preserve">4.25627136230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27798652648926</t>
   </si>
   <si>
     <t xml:space="preserve">4.29970264434814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36485004425049</t>
+    <t xml:space="preserve">4.36484956741333</t>
   </si>
   <si>
     <t xml:space="preserve">4.35761117935181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26350975036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09702348709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06083011627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12597751617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90882062911987</t>
+    <t xml:space="preserve">4.26351022720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09702301025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06083059310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12597703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90882110595703</t>
   </si>
   <si>
     <t xml:space="preserve">3.84367370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78576517105103</t>
+    <t xml:space="preserve">3.78576588630676</t>
   </si>
   <si>
     <t xml:space="preserve">3.87986660003662</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94501376152039</t>
+    <t xml:space="preserve">3.94501328468323</t>
   </si>
   <si>
     <t xml:space="preserve">3.80748152732849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72061800956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68442583084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57946634292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45641088485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55051302909851</t>
+    <t xml:space="preserve">3.72061848640442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68442535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5794665813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4564106464386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55051231384277</t>
   </si>
   <si>
     <t xml:space="preserve">3.81471967697144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7640495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82919645309448</t>
+    <t xml:space="preserve">3.76405000686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82919692993164</t>
   </si>
   <si>
     <t xml:space="preserve">3.83643579483032</t>
@@ -1451,31 +1451,31 @@
     <t xml:space="preserve">3.74233412742615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75681161880493</t>
+    <t xml:space="preserve">3.75681090354919</t>
   </si>
   <si>
     <t xml:space="preserve">3.70614147186279</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6771867275238</t>
+    <t xml:space="preserve">3.67718696594238</t>
   </si>
   <si>
     <t xml:space="preserve">3.6337559223175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66994857788086</t>
+    <t xml:space="preserve">3.66994833946228</t>
   </si>
   <si>
     <t xml:space="preserve">3.61927819252014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64099407196045</t>
+    <t xml:space="preserve">3.64099478721619</t>
   </si>
   <si>
     <t xml:space="preserve">3.7712881565094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80024194717407</t>
+    <t xml:space="preserve">3.80024266242981</t>
   </si>
   <si>
     <t xml:space="preserve">3.66270971298218</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">3.72785711288452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86539030075073</t>
+    <t xml:space="preserve">3.86538934707642</t>
   </si>
   <si>
     <t xml:space="preserve">3.60480141639709</t>
@@ -1493,232 +1493,232 @@
     <t xml:space="preserve">3.58670520782471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57584762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54327297210693</t>
+    <t xml:space="preserve">3.57584714889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54327344894409</t>
   </si>
   <si>
     <t xml:space="preserve">3.65547156333923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82195806503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7133800983429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69890260696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69166350364685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62651753425598</t>
+    <t xml:space="preserve">3.82195854187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71338033676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69890284538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69166398048401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62651705741882</t>
   </si>
   <si>
     <t xml:space="preserve">3.64823269844055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52517771720886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60118269920349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54689359664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50346183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60842061042786</t>
+    <t xml:space="preserve">3.52517676353455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60118246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54689288139343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50346159934998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60842108726501</t>
   </si>
   <si>
     <t xml:space="preserve">3.79300379753113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8871054649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5649893283844</t>
+    <t xml:space="preserve">3.88710498809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56498956680298</t>
   </si>
   <si>
     <t xml:space="preserve">3.59394335746765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77852702140808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58308529853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53965401649475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48174595832825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49622321128845</t>
+    <t xml:space="preserve">3.77852654457092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58308553695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53965425491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48174548149109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49622344970703</t>
   </si>
   <si>
     <t xml:space="preserve">3.452791929245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42021775245667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.431556224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43533563613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41265964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3332953453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841275215149</t>
+    <t xml:space="preserve">3.42021822929382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43155598640442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43533539772034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41265988349915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33329510688782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841251373291</t>
   </si>
   <si>
     <t xml:space="preserve">3.38620495796204</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37108778953552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36352968215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38242554664612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31062006950378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3257372379303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29172372817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393104553223</t>
+    <t xml:space="preserve">3.3710880279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36352920532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38242602348328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31062030792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32573699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29172396659851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393152236938</t>
   </si>
   <si>
     <t xml:space="preserve">3.3143994808197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33707499504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.276606798172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28038668632507</t>
+    <t xml:space="preserve">3.33707475662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27660703659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28038620948792</t>
   </si>
   <si>
     <t xml:space="preserve">3.23503541946411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20480132102966</t>
+    <t xml:space="preserve">3.20480108261108</t>
   </si>
   <si>
     <t xml:space="preserve">3.21613907814026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23125600814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21235966682434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24259376525879</t>
+    <t xml:space="preserve">3.23125624656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21235942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24259352684021</t>
   </si>
   <si>
     <t xml:space="preserve">3.18212580680847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13677477836609</t>
+    <t xml:space="preserve">3.13677501678467</t>
   </si>
   <si>
     <t xml:space="preserve">3.15189170837402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18968415260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20102214813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25015211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39376378059387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59784293174744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65831089019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55627131462097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55249214172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56760859489441</t>
+    <t xml:space="preserve">3.18968391418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20102167129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25015234947205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39376354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59784317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65831065177917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55627107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55249166488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56760835647583</t>
   </si>
   <si>
     <t xml:space="preserve">3.57516717910767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60540151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5335955619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47690725326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59028458595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58272552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57138776779175</t>
+    <t xml:space="preserve">3.60540175437927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53359580039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47690677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59028434753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5827260017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57138824462891</t>
   </si>
   <si>
     <t xml:space="preserve">3.52603697776794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50336194038391</t>
+    <t xml:space="preserve">3.50336217880249</t>
   </si>
   <si>
     <t xml:space="preserve">3.43911457061768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42777681350708</t>
+    <t xml:space="preserve">3.4277765750885</t>
   </si>
   <si>
     <t xml:space="preserve">3.4202184677124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40132212638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36730861663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40888094902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34085392951965</t>
+    <t xml:space="preserve">3.40132188796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36730885505676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40888047218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34085416793823</t>
   </si>
   <si>
     <t xml:space="preserve">3.42399740219116</t>
@@ -1727,31 +1727,31 @@
     <t xml:space="preserve">3.51469969749451</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49958229064941</t>
+    <t xml:space="preserve">3.49958205223083</t>
   </si>
   <si>
     <t xml:space="preserve">3.54871273040771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6394145488739</t>
+    <t xml:space="preserve">3.63941431045532</t>
   </si>
   <si>
     <t xml:space="preserve">3.65453147888184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6809868812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67342758178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73011660575867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78680562973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285871505737</t>
+    <t xml:space="preserve">3.68098592758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67342782020569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73011589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78680539131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285776138306</t>
   </si>
   <si>
     <t xml:space="preserve">3.86239004135132</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">3.74523377418518</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76790881156921</t>
+    <t xml:space="preserve">3.76790928840637</t>
   </si>
   <si>
     <t xml:space="preserve">3.83971452713013</t>
@@ -1769,16 +1769,16 @@
     <t xml:space="preserve">3.83215618133545</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77168798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73767495155334</t>
+    <t xml:space="preserve">3.77168750762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73767518997192</t>
   </si>
   <si>
     <t xml:space="preserve">3.69232439994812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70366239547729</t>
+    <t xml:space="preserve">3.70366191864014</t>
   </si>
   <si>
     <t xml:space="preserve">3.77924633026123</t>
@@ -1787,46 +1787,46 @@
     <t xml:space="preserve">3.68854475021362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66586971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6961030960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66964840888977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73389625549316</t>
+    <t xml:space="preserve">3.66586947441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69610333442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66964864730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73389601707458</t>
   </si>
   <si>
     <t xml:space="preserve">3.81703925132751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84727358818054</t>
+    <t xml:space="preserve">3.84727263450623</t>
   </si>
   <si>
     <t xml:space="preserve">3.90018248558044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98332619667053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96065068244934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9530918598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93041634559631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94553375244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99088454246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91529893875122</t>
+    <t xml:space="preserve">3.98332571983337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96065020561218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95309233665466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93041682243347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94553327560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99088501930237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91529941558838</t>
   </si>
   <si>
     <t xml:space="preserve">4.02111864089966</t>
@@ -1835,13 +1835,13 @@
     <t xml:space="preserve">4.09670305252075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03623628616333</t>
+    <t xml:space="preserve">4.03623533248901</t>
   </si>
   <si>
     <t xml:space="preserve">4.06646966934204</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0815863609314</t>
+    <t xml:space="preserve">4.08158683776855</t>
   </si>
   <si>
     <t xml:space="preserve">4.13449573516846</t>
@@ -1856,16 +1856,16 @@
     <t xml:space="preserve">4.0060019493103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04379320144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1193790435791</t>
+    <t xml:space="preserve">4.04379367828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11937856674194</t>
   </si>
   <si>
     <t xml:space="preserve">4.01355981826782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96820831298828</t>
+    <t xml:space="preserve">3.9682092666626</t>
   </si>
   <si>
     <t xml:space="preserve">3.93797516822815</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">3.97576808929443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90774130821228</t>
+    <t xml:space="preserve">3.90774083137512</t>
   </si>
   <si>
     <t xml:space="preserve">3.89262437820435</t>
@@ -1883,25 +1883,25 @@
     <t xml:space="preserve">3.88506531715393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87750744819641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8548309803009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.801922082901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59406423568726</t>
+    <t xml:space="preserve">3.87750792503357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85483145713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80192279815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59406352043152</t>
   </si>
   <si>
     <t xml:space="preserve">3.60162210464478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6507523059845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877908706665</t>
+    <t xml:space="preserve">3.65075278282166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877884864807</t>
   </si>
   <si>
     <t xml:space="preserve">3.99844264984131</t>
@@ -1910,10 +1910,10 @@
     <t xml:space="preserve">3.72255825996399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63185620307922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46556925773621</t>
+    <t xml:space="preserve">3.63185548782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46556901931763</t>
   </si>
   <si>
     <t xml:space="preserve">3.44667315483093</t>
@@ -1922,13 +1922,13 @@
     <t xml:space="preserve">3.28416514396667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11032009124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06496906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83821415901184</t>
+    <t xml:space="preserve">3.11031985282898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0649688243866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.838214635849</t>
   </si>
   <si>
     <t xml:space="preserve">2.8344349861145</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">2.70971989631653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9326958656311</t>
+    <t xml:space="preserve">2.93269562721252</t>
   </si>
   <si>
     <t xml:space="preserve">3.00450110435486</t>
@@ -1955,40 +1955,40 @@
     <t xml:space="preserve">2.91001987457275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96292948722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85333132743835</t>
+    <t xml:space="preserve">2.96292972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85333108901978</t>
   </si>
   <si>
     <t xml:space="preserve">2.89490294456482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88734436035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92135763168335</t>
+    <t xml:space="preserve">2.88734459877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92135787010193</t>
   </si>
   <si>
     <t xml:space="preserve">2.85711050033569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90246152877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82687640190125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89112377166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9969425201416</t>
+    <t xml:space="preserve">2.90246105194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82687664031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8911235332489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99694228172302</t>
   </si>
   <si>
     <t xml:space="preserve">2.9515917301178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97804617881775</t>
+    <t xml:space="preserve">2.97804665565491</t>
   </si>
   <si>
     <t xml:space="preserve">2.99316334724426</t>
@@ -2000,25 +2000,25 @@
     <t xml:space="preserve">3.03473472595215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02717685699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12165808677673</t>
+    <t xml:space="preserve">3.02717661857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12165784835815</t>
   </si>
   <si>
     <t xml:space="preserve">3.06118988990784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09898209571838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16700887680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14433312416077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19346308708191</t>
+    <t xml:space="preserve">3.09898233413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16700911521912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14433264732361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19346332550049</t>
   </si>
   <si>
     <t xml:space="preserve">3.21991848945618</t>
@@ -2027,7 +2027,7 @@
     <t xml:space="preserve">3.26904821395874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32195806503296</t>
+    <t xml:space="preserve">3.32195782661438</t>
   </si>
   <si>
     <t xml:space="preserve">3.15945029258728</t>
@@ -2036,67 +2036,67 @@
     <t xml:space="preserve">3.07252764701843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06874847412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10654091835022</t>
+    <t xml:space="preserve">3.06874823570251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10654067993164</t>
   </si>
   <si>
     <t xml:space="preserve">3.16322946548462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27282762527466</t>
+    <t xml:space="preserve">3.27282786369324</t>
   </si>
   <si>
     <t xml:space="preserve">3.28794455528259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40510153770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51092004776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48824453353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45801043510437</t>
+    <t xml:space="preserve">3.40510129928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51092028617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48824501037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45801019668579</t>
   </si>
   <si>
     <t xml:space="preserve">3.29550290107727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34463334083557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29928231239319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30684113502502</t>
+    <t xml:space="preserve">3.34463357925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29928255081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30684089660645</t>
   </si>
   <si>
     <t xml:space="preserve">3.30306148529053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26149010658264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37864637374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37486743927002</t>
+    <t xml:space="preserve">3.26148986816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37864661216736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37486720085144</t>
   </si>
   <si>
     <t xml:space="preserve">3.26526927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48068618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38998460769653</t>
+    <t xml:space="preserve">3.39754271507263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48068642616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38998436927795</t>
   </si>
   <si>
     <t xml:space="preserve">3.31817841529846</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">3.25771069526672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22747659683228</t>
+    <t xml:space="preserve">3.2274763584137</t>
   </si>
   <si>
     <t xml:space="preserve">3.18590521812439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24637293815613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17456698417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14055442810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17834663391113</t>
+    <t xml:space="preserve">3.24637269973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17456722259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14055418968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17834639549255</t>
   </si>
   <si>
     <t xml:space="preserve">3.09142398834229</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">3.04607319831848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01583862304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94025373458862</t>
+    <t xml:space="preserve">3.01583886146545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9402539730072</t>
   </si>
   <si>
     <t xml:space="preserve">2.95537090301514</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">2.8835654258728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80042147636414</t>
+    <t xml:space="preserve">2.80042195320129</t>
   </si>
   <si>
     <t xml:space="preserve">2.7890841960907</t>
@@ -2165,49 +2165,49 @@
     <t xml:space="preserve">2.72105741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67948579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55477094650269</t>
+    <t xml:space="preserve">2.67948603630066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55477070808411</t>
   </si>
   <si>
     <t xml:space="preserve">2.44895195960999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55099153518677</t>
+    <t xml:space="preserve">2.55099129676819</t>
   </si>
   <si>
     <t xml:space="preserve">2.61523866653442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69838190078735</t>
+    <t xml:space="preserve">2.69838213920593</t>
   </si>
   <si>
     <t xml:space="preserve">2.98938417434692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53737473487854</t>
+    <t xml:space="preserve">3.53737497329712</t>
   </si>
   <si>
     <t xml:space="preserve">3.62807703018188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63563537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57894682884216</t>
+    <t xml:space="preserve">3.6356348991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57894706726074</t>
   </si>
   <si>
     <t xml:space="preserve">3.56382989883423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50714087486267</t>
+    <t xml:space="preserve">3.50714063644409</t>
   </si>
   <si>
     <t xml:space="preserve">3.48446559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52225780487061</t>
+    <t xml:space="preserve">3.52225804328918</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643881797791</t>
@@ -2222,28 +2222,28 @@
     <t xml:space="preserve">3.76035094261169</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64319396018982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68476510047913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74901294708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7943639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7565712928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77546715736389</t>
+    <t xml:space="preserve">3.64319372177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68476533889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74901247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79436373710632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75657081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77546739578247</t>
   </si>
   <si>
     <t xml:space="preserve">3.76412963867188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15717077255249</t>
+    <t xml:space="preserve">4.15717172622681</t>
   </si>
   <si>
     <t xml:space="preserve">4.11182069778442</t>
@@ -2267,13 +2267,13 @@
     <t xml:space="preserve">4.08601951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09386205673218</t>
+    <t xml:space="preserve">4.09386110305786</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365905761719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26640033721924</t>
+    <t xml:space="preserve">4.26639986038208</t>
   </si>
   <si>
     <t xml:space="preserve">4.27424240112305</t>
@@ -2285,10 +2285,10 @@
     <t xml:space="preserve">4.36835432052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32914113998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34482622146606</t>
+    <t xml:space="preserve">4.32914161682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34482669830322</t>
   </si>
   <si>
     <t xml:space="preserve">4.35266971588135</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">4.30561351776123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28992795944214</t>
+    <t xml:space="preserve">4.2899284362793</t>
   </si>
   <si>
     <t xml:space="preserve">4.28208541870117</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">4.19581604003906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03896379470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02327823638916</t>
+    <t xml:space="preserve">4.03896331787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02327871322632</t>
   </si>
   <si>
     <t xml:space="preserve">3.99974966049194</t>
@@ -2321,16 +2321,16 @@
     <t xml:space="preserve">3.96053695678711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03112030029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05464887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93700933456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92132329940796</t>
+    <t xml:space="preserve">4.03112077713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05464839935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93700885772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92132377624512</t>
   </si>
   <si>
     <t xml:space="preserve">4.01543521881104</t>
@@ -2339,10 +2339,10 @@
     <t xml:space="preserve">4.07033443450928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97622227668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18797397613525</t>
+    <t xml:space="preserve">3.97622275352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1879734992981</t>
   </si>
   <si>
     <t xml:space="preserve">4.24287223815918</t>
@@ -2351,393 +2351,393 @@
     <t xml:space="preserve">4.21150159835815</t>
   </si>
   <si>
+    <t xml:space="preserve">4.39188289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45462322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43109560012817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42325258255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38404035568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39972543716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33698415756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.360511302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46246576309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44678115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4389386177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47815179824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48599433898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50167942047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56442070007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60363388061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62716150283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6350040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49383687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59579133987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66637516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68206024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72911596298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64284706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74480152130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8624415397644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90949726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05850696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03497982025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99576616287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95655345916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94871044158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97223854064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87028360366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98008060455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0741925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05066537857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02713680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08987808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19183254241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18399000167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10556316375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14477682113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23888826370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21536064147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1996750831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25457382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30162954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01929378509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93302488327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7996997833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76048707962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76833009719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68990278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69774580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61147689819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53305053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50952243804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47030830383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55657768249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54873561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57226324081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52520751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54089260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51736450195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58010625839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82322788238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87812662124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88596963882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7840142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65853261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77617216110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85459899902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94086837768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52122354507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66239070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73297548294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89767074584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68591928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70160484313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59965038299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5369086265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906608581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17614698410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29378700256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7134313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41541051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89381122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81538534164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9251823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84675598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72127389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5879487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61931943893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558786392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77163219451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.738609790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69733238220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63954496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79639768600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98627233505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95325088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312601089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07708215713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11835956573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97801685333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06057167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9037184715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96976184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87069654464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82941961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62303447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40839338302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50745820999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56524658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48269176483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58175754547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64780044555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61477947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57350206375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51571416854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3340950012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30932760238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38362693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16898632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26805114746094</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.39188241958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45462322235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43109560012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42325305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38403987884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39972496032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33698415756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36051177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46246671676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44678068161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4389386177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47815179824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48599433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50167989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56442022323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60363388061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62716197967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63500499725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49383687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59579133987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66637468338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68206024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72911643981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64284706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74480152130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86244106292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90949726104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05850744247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03497982025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99576616287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95655298233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9487099647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97223854064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87028408050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98008060455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0741925239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0506649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02713680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08987760543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19183254241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18399000167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10556364059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14477634429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23888826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21536064147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1996750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25457382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3016300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01929473876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93302488327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7996997833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7604866027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76833009719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68990325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69774532318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61147689819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53305006027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50952196121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47030878067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55657815933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54873561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57226371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52520751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54089260101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51736497879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58010578155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82322835922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87812662124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88596963882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7840142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70558834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65853261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77617216110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85459899902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94086837768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52122354507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6623911857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73297500610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89767074584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6859188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70160484313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59964990615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53690910339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906656265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17614698410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29378700256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7134313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41541051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89381122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81538486480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92518281936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84675550460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72127389907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5879487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61931896209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77163171768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73861026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69733333587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63954496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7963981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98627281188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95325088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312601089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07708263397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11835908889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97801733016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06057167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9037184715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96976184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87069702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82941961288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62303400039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40839385986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50745820999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56524658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48269176483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58175754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64780044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54873609542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61477899551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57350158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51571369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33409404754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30932855606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38362693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16898632049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2680516242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39188289642334</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.46618127822876</t>
   </si>
   <si>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">4.3753719329834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27630615234375</t>
+    <t xml:space="preserve">4.27630662918091</t>
   </si>
   <si>
     <t xml:space="preserve">4.44967031478882</t>
@@ -2759,13 +2759,13 @@
     <t xml:space="preserve">4.41664838790894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55699062347412</t>
+    <t xml:space="preserve">4.55699110031128</t>
   </si>
   <si>
     <t xml:space="preserve">4.67256689071655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65605592727661</t>
+    <t xml:space="preserve">4.65605545043945</t>
   </si>
   <si>
     <t xml:space="preserve">4.71384382247925</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">4.72209930419922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7551212310791</t>
+    <t xml:space="preserve">4.75512075424194</t>
   </si>
   <si>
     <t xml:space="preserve">4.77988719940186</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">4.73035478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82116413116455</t>
+    <t xml:space="preserve">4.82116460800171</t>
   </si>
   <si>
     <t xml:space="preserve">4.92848443984985</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">4.92022943496704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94499492645264</t>
+    <t xml:space="preserve">4.94499540328979</t>
   </si>
   <si>
     <t xml:space="preserve">4.83767509460449</t>
@@ -2807,25 +2807,25 @@
     <t xml:space="preserve">4.78814268112183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87895250320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60652351379395</t>
+    <t xml:space="preserve">4.87895154953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60652303695679</t>
   </si>
   <si>
     <t xml:space="preserve">4.66431140899658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81290912628174</t>
+    <t xml:space="preserve">4.81290864944458</t>
   </si>
   <si>
     <t xml:space="preserve">4.88720750808716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93674039840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0110387802124</t>
+    <t xml:space="preserve">4.93673992156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01103925704956</t>
   </si>
   <si>
     <t xml:space="preserve">5.11010408401489</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">5.19265794754028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22567987442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26695728302002</t>
+    <t xml:space="preserve">5.22567939758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26695680618286</t>
   </si>
   <si>
     <t xml:space="preserve">5.27521181106567</t>
@@ -2852,13 +2852,13 @@
     <t xml:space="preserve">5.29172277450562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30823373794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36602163314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43206548690796</t>
+    <t xml:space="preserve">5.30823421478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36602210998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4320650100708</t>
   </si>
   <si>
     <t xml:space="preserve">5.47334241867065</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">5.55589628219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41555404663086</t>
+    <t xml:space="preserve">5.41555452346802</t>
   </si>
   <si>
     <t xml:space="preserve">5.4898533821106</t>
@@ -2891,37 +2891,37 @@
     <t xml:space="preserve">5.51461935043335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58891820907593</t>
+    <t xml:space="preserve">5.58891868591309</t>
   </si>
   <si>
     <t xml:space="preserve">5.45683145523071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54764127731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6879825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63019514083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61368465423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59717321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58066320419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65496158599854</t>
+    <t xml:space="preserve">5.54764080047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68798351287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63019561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61368417739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5971736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58066272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65496110916138</t>
   </si>
   <si>
     <t xml:space="preserve">5.77879285812378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82007026672363</t>
+    <t xml:space="preserve">5.82006978988647</t>
   </si>
   <si>
     <t xml:space="preserve">5.84483623504639</t>
@@ -2930,19 +2930,19 @@
     <t xml:space="preserve">5.86134672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89436817169189</t>
+    <t xml:space="preserve">5.89436864852905</t>
   </si>
   <si>
     <t xml:space="preserve">5.8118143081665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90262413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80355882644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73751592636108</t>
+    <t xml:space="preserve">5.90262460708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80355978012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73751544952393</t>
   </si>
   <si>
     <t xml:space="preserve">6.00168943405151</t>
@@ -2954,16 +2954,16 @@
     <t xml:space="preserve">6.38969373703003</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39794921875</t>
+    <t xml:space="preserve">6.39794874191284</t>
   </si>
   <si>
     <t xml:space="preserve">6.47224807739258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43922662734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45573711395264</t>
+    <t xml:space="preserve">6.4392261505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45573663711548</t>
   </si>
   <si>
     <t xml:space="preserve">6.59607887268066</t>
@@ -2975,19 +2975,19 @@
     <t xml:space="preserve">6.57956838607788</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58782339096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51352500915527</t>
+    <t xml:space="preserve">6.58782434463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51352453231812</t>
   </si>
   <si>
     <t xml:space="preserve">6.56305742263794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67863321304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72816562652588</t>
+    <t xml:space="preserve">6.67863368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72816514968872</t>
   </si>
   <si>
     <t xml:space="preserve">6.67037773132324</t>
@@ -2996,16 +2996,16 @@
     <t xml:space="preserve">6.63735628128052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79420900344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73642158508301</t>
+    <t xml:space="preserve">6.79420852661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73642110824585</t>
   </si>
   <si>
     <t xml:space="preserve">6.68688917160034</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53829097747803</t>
+    <t xml:space="preserve">6.53829145431519</t>
   </si>
   <si>
     <t xml:space="preserve">6.62084579467773</t>
@@ -3026,16 +3026,16 @@
     <t xml:space="preserve">6.78595399856567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96866750717163</t>
+    <t xml:space="preserve">5.96866703033447</t>
   </si>
   <si>
     <t xml:space="preserve">6.05122137069702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64670610427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8530912399292</t>
+    <t xml:space="preserve">5.64670658111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85309171676636</t>
   </si>
   <si>
     <t xml:space="preserve">5.67972755432129</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">5.38253211975098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66321706771851</t>
+    <t xml:space="preserve">5.66321659088135</t>
   </si>
   <si>
     <t xml:space="preserve">5.60542917251587</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7457709312439</t>
+    <t xml:space="preserve">5.74577140808105</t>
   </si>
   <si>
     <t xml:space="preserve">5.83658075332642</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">5.79530382156372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87785816192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97692251205444</t>
+    <t xml:space="preserve">5.87785768508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9769229888916</t>
   </si>
   <si>
     <t xml:space="preserve">5.91087913513184</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">5.78704833984375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94390058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96041202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8696026802063</t>
+    <t xml:space="preserve">5.94390106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9604115486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86960220336914</t>
   </si>
   <si>
     <t xml:space="preserve">5.98917293548584</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">5.79011058807373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78145551681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57373857498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67759704589844</t>
+    <t xml:space="preserve">5.78145599365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57373905181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6775975227356</t>
   </si>
   <si>
     <t xml:space="preserve">5.76414585113525</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">5.80742025375366</t>
   </si>
   <si>
-    <t xml:space="preserve">5.868004322052</t>
+    <t xml:space="preserve">5.86800479888916</t>
   </si>
   <si>
     <t xml:space="preserve">5.88531446456909</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">5.87665939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9285888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96320772171021</t>
+    <t xml:space="preserve">5.92858839035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96320819854736</t>
   </si>
   <si>
     <t xml:space="preserve">5.94589853286743</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">5.91993379592896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15361547470093</t>
+    <t xml:space="preserve">6.15361499786377</t>
   </si>
   <si>
     <t xml:space="preserve">6.22285461425781</t>
@@ -3170,19 +3170,19 @@
     <t xml:space="preserve">6.28343868255615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25747394561768</t>
+    <t xml:space="preserve">6.25747346878052</t>
   </si>
   <si>
     <t xml:space="preserve">6.24881887435913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24016427993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23150873184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26612854003906</t>
+    <t xml:space="preserve">6.24016380310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2315092086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26612901687622</t>
   </si>
   <si>
     <t xml:space="preserve">6.46519088745117</t>
@@ -3197,13 +3197,13 @@
     <t xml:space="preserve">6.56904983520508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63828802108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56039428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57770395278931</t>
+    <t xml:space="preserve">6.6382884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56039381027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57770442962646</t>
   </si>
   <si>
     <t xml:space="preserve">6.62097835540771</t>
@@ -3218,16 +3218,16 @@
     <t xml:space="preserve">6.73349189758301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64694309234619</t>
+    <t xml:space="preserve">6.64694261550903</t>
   </si>
   <si>
     <t xml:space="preserve">6.50846529006958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66425275802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11034107208252</t>
+    <t xml:space="preserve">6.66425228118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11034059524536</t>
   </si>
   <si>
     <t xml:space="preserve">6.30940341949463</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">6.44788074493408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49115514755249</t>
+    <t xml:space="preserve">6.49115562438965</t>
   </si>
   <si>
     <t xml:space="preserve">6.49981021881104</t>
@@ -3248,16 +3248,16 @@
     <t xml:space="preserve">6.55173969268799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59501361846924</t>
+    <t xml:space="preserve">6.5950140953064</t>
   </si>
   <si>
     <t xml:space="preserve">6.70752716064453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68156242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60366916656494</t>
+    <t xml:space="preserve">6.68156290054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60366868972778</t>
   </si>
   <si>
     <t xml:space="preserve">6.51712036132812</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">6.74214696884155</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87197017669678</t>
+    <t xml:space="preserve">6.87196969985962</t>
   </si>
   <si>
     <t xml:space="preserve">6.79407596588135</t>
@@ -3284,16 +3284,16 @@
     <t xml:space="preserve">6.78542137145996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77676582336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7508020401001</t>
+    <t xml:space="preserve">6.77676630020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75080156326294</t>
   </si>
   <si>
     <t xml:space="preserve">6.52577495574951</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42191696166992</t>
+    <t xml:space="preserve">6.42191648483276</t>
   </si>
   <si>
     <t xml:space="preserve">6.45653581619263</t>
@@ -3308,31 +3308,31 @@
     <t xml:space="preserve">6.75945663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82869577407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82004022598267</t>
+    <t xml:space="preserve">6.82869529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82004070281982</t>
   </si>
   <si>
     <t xml:space="preserve">6.92389917373657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01044845581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05372190475464</t>
+    <t xml:space="preserve">7.01044797897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05372142791748</t>
   </si>
   <si>
     <t xml:space="preserve">6.9931378364563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00179290771484</t>
+    <t xml:space="preserve">7.001793384552</t>
   </si>
   <si>
     <t xml:space="preserve">7.02775764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97582912445068</t>
+    <t xml:space="preserve">6.97582864761353</t>
   </si>
   <si>
     <t xml:space="preserve">6.95851850509644</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">7.07103204727173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06237745285034</t>
+    <t xml:space="preserve">7.06237697601318</t>
   </si>
   <si>
     <t xml:space="preserve">7.11430644989014</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">7.04506778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13161563873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18354511260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1575813293457</t>
+    <t xml:space="preserve">7.13161611557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18354558944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15758085250854</t>
   </si>
   <si>
     <t xml:space="preserve">7.07968711853027</t>
@@ -3389,16 +3389,16 @@
     <t xml:space="preserve">6.96717357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17489051818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27009344100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20085477828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22681951522827</t>
+    <t xml:space="preserve">7.17489004135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27009391784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20085430145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22681999206543</t>
   </si>
   <si>
     <t xml:space="preserve">7.16623544692993</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">7.14892625808716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0883412361145</t>
+    <t xml:space="preserve">7.08834171295166</t>
   </si>
   <si>
     <t xml:space="preserve">7.14027070999146</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">7.31336784362793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33933305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42588186264038</t>
+    <t xml:space="preserve">7.33933258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42588138580322</t>
   </si>
   <si>
     <t xml:space="preserve">7.44319200515747</t>
@@ -3434,16 +3434,16 @@
     <t xml:space="preserve">7.23547458648682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29605913162231</t>
+    <t xml:space="preserve">7.29605865478516</t>
   </si>
   <si>
     <t xml:space="preserve">7.19220113754272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45184564590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38260793685913</t>
+    <t xml:space="preserve">7.4518461227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38260746002197</t>
   </si>
   <si>
     <t xml:space="preserve">7.3566427230835</t>
@@ -3461,19 +3461,19 @@
     <t xml:space="preserve">7.76342248916626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53839540481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55570459365845</t>
+    <t xml:space="preserve">7.53839588165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55570507049561</t>
   </si>
   <si>
     <t xml:space="preserve">7.46050119400024</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40857267379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63359832763672</t>
+    <t xml:space="preserve">7.40857219696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63359785079956</t>
   </si>
   <si>
     <t xml:space="preserve">7.72014713287354</t>
@@ -3482,10 +3482,10 @@
     <t xml:space="preserve">7.88458967208862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77207708358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65090799331665</t>
+    <t xml:space="preserve">7.77207612991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65090894699097</t>
   </si>
   <si>
     <t xml:space="preserve">7.6682186126709</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">7.69418334960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67687368392944</t>
+    <t xml:space="preserve">7.67687273025513</t>
   </si>
   <si>
     <t xml:space="preserve">7.94517469406128</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">8.05768871307373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12692737579346</t>
+    <t xml:space="preserve">8.12692642211914</t>
   </si>
   <si>
     <t xml:space="preserve">8.0663423538208</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">8.10961627960205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17885494232178</t>
+    <t xml:space="preserve">8.17885589599609</t>
   </si>
   <si>
     <t xml:space="preserve">8.17020034790039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20481967926025</t>
+    <t xml:space="preserve">8.20482063293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.07499694824219</t>
@@ -3551,13 +3551,13 @@
     <t xml:space="preserve">8.18751049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00575733184814</t>
+    <t xml:space="preserve">8.00575828552246</t>
   </si>
   <si>
     <t xml:space="preserve">7.99710321426392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87593555450439</t>
+    <t xml:space="preserve">7.87593650817871</t>
   </si>
   <si>
     <t xml:space="preserve">8.30867958068848</t>
@@ -3566,16 +3566,16 @@
     <t xml:space="preserve">8.24809455871582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2740592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41253757476807</t>
+    <t xml:space="preserve">8.27406024932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41253662109375</t>
   </si>
   <si>
     <t xml:space="preserve">8.57698059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5856351852417</t>
+    <t xml:space="preserve">8.58563423156738</t>
   </si>
   <si>
     <t xml:space="preserve">8.65487384796143</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">8.54236030578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62025451660156</t>
+    <t xml:space="preserve">8.62025356292725</t>
   </si>
   <si>
     <t xml:space="preserve">8.81066226959229</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">8.93421173095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86179637908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.753173828125</t>
+    <t xml:space="preserve">8.86179733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75317478179932</t>
   </si>
   <si>
     <t xml:space="preserve">8.72601890563965</t>
@@ -3629,22 +3629,22 @@
     <t xml:space="preserve">8.80748558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85274410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77127742767334</t>
+    <t xml:space="preserve">8.85274505615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77127838134766</t>
   </si>
   <si>
     <t xml:space="preserve">8.68981170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69886302947998</t>
+    <t xml:space="preserve">8.69886207580566</t>
   </si>
   <si>
     <t xml:space="preserve">8.73507022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59929275512695</t>
+    <t xml:space="preserve">8.59929180145264</t>
   </si>
   <si>
     <t xml:space="preserve">8.56308460235596</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">8.08333492279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27342414855957</t>
+    <t xml:space="preserve">8.27342510223389</t>
   </si>
   <si>
     <t xml:space="preserve">8.42730712890625</t>
@@ -3683,10 +3683,10 @@
     <t xml:space="preserve">8.4906702041626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40015125274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58118724822998</t>
+    <t xml:space="preserve">8.40015029907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5811882019043</t>
   </si>
   <si>
     <t xml:space="preserve">8.40920257568359</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">8.41825485229492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60834503173828</t>
+    <t xml:space="preserve">8.60834407806396</t>
   </si>
   <si>
     <t xml:space="preserve">8.48161697387695</t>
@@ -3710,16 +3710,16 @@
     <t xml:space="preserve">8.68075942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65360355377197</t>
+    <t xml:space="preserve">8.65360450744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.870849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02473068237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91610908508301</t>
+    <t xml:space="preserve">9.02473163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91610813140869</t>
   </si>
   <si>
     <t xml:space="preserve">8.98852348327637</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">9.08809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01567935943604</t>
+    <t xml:space="preserve">9.01567840576172</t>
   </si>
   <si>
     <t xml:space="preserve">9.04283428192139</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">9.16050910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79843425750732</t>
+    <t xml:space="preserve">8.79843330383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.36394309997559</t>
@@ -3752,16 +3752,16 @@
     <t xml:space="preserve">8.29152774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23721694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26437282562256</t>
+    <t xml:space="preserve">8.23721790313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26437187194824</t>
   </si>
   <si>
     <t xml:space="preserve">8.47256565093994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97947216033936</t>
+    <t xml:space="preserve">8.97947120666504</t>
   </si>
   <si>
     <t xml:space="preserve">8.89800453186035</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">9.14240550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34154605865479</t>
+    <t xml:space="preserve">9.3415470123291</t>
   </si>
   <si>
     <t xml:space="preserve">9.28723621368408</t>
@@ -3794,7 +3794,7 @@
     <t xml:space="preserve">9.19671630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2510290145874</t>
+    <t xml:space="preserve">9.25102806091309</t>
   </si>
   <si>
     <t xml:space="preserve">9.12430191040039</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">9.21482086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35965156555176</t>
+    <t xml:space="preserve">9.35965061187744</t>
   </si>
   <si>
     <t xml:space="preserve">9.17861366271973</t>
@@ -3818,10 +3818,10 @@
     <t xml:space="preserve">9.10619831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30533885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50448036193848</t>
+    <t xml:space="preserve">9.30533981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50448131561279</t>
   </si>
   <si>
     <t xml:space="preserve">9.65504741668701</t>
@@ -3899,9 +3899,6 @@
     <t xml:space="preserve">9.5797643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50448131561279</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.46683979034424</t>
   </si>
   <si>
@@ -4353,6 +4350,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.8400001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7600002288818</t>
   </si>
 </sst>
 </file>
@@ -46803,7 +46803,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1620" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -46829,7 +46829,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1621" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -46855,7 +46855,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1622" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -46881,7 +46881,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1623" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -46907,7 +46907,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1624" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -46933,7 +46933,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1625" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -46959,7 +46959,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1626" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -46985,7 +46985,7 @@
         <v>6</v>
       </c>
       <c r="G1627" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -47011,7 +47011,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G1628" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -47037,7 +47037,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G1629" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -47063,7 +47063,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1630" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -47089,7 +47089,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1631" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -47115,7 +47115,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G1632" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -47141,7 +47141,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1633" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -47167,7 +47167,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1634" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -47193,7 +47193,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1635" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -47219,7 +47219,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1636" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -47245,7 +47245,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1637" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -47271,7 +47271,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1638" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -47297,7 +47297,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1639" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -47323,7 +47323,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1640" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -47349,7 +47349,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1641" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -47375,7 +47375,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1642" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -47401,7 +47401,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1643" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -47427,7 +47427,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1644" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -47453,7 +47453,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1645" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -47479,7 +47479,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1646" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -47505,7 +47505,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1647" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -47531,7 +47531,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1648" t="s">
-        <v>898</v>
+        <v>840</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -47609,7 +47609,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1651" t="s">
-        <v>898</v>
+        <v>840</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -47973,7 +47973,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1665" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -47999,7 +47999,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1666" t="s">
-        <v>898</v>
+        <v>840</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -48025,7 +48025,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1667" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -48051,7 +48051,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1668" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -48233,7 +48233,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1675" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -48259,7 +48259,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1676" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -48337,7 +48337,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1679" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -48363,7 +48363,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G1680" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -48441,7 +48441,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1683" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -48519,7 +48519,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1686" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -48545,7 +48545,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G1687" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -48701,7 +48701,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1693" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -48753,7 +48753,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1695" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -48805,7 +48805,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1697" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -48883,7 +48883,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1700" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -48987,7 +48987,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1704" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -49013,7 +49013,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G1705" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -49091,7 +49091,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1708" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -49143,7 +49143,7 @@
         <v>6</v>
       </c>
       <c r="G1710" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -49221,7 +49221,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1713" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -49325,7 +49325,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1717" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -49429,7 +49429,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1721" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -49533,7 +49533,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1725" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -49611,7 +49611,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G1728" t="s">
-        <v>850</v>
+        <v>875</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -49663,7 +49663,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G1730" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -49793,7 +49793,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G1735" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -49819,7 +49819,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1736" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -49897,7 +49897,7 @@
         <v>6</v>
       </c>
       <c r="G1739" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -63651,7 +63651,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>1295</v>
+        <v>1269</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63677,7 +63677,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2269" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63703,7 +63703,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2270" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63729,7 +63729,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2271" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63755,7 +63755,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2272" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63807,7 +63807,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2274" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63937,7 +63937,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2279" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63963,7 +63963,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2280" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -63989,7 +63989,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2281" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64015,7 +64015,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2282" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64041,7 +64041,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2283" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64067,7 +64067,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64119,7 +64119,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2286" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64171,7 +64171,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2288" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64197,7 +64197,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2289" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64223,7 +64223,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2290" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64275,7 +64275,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2292" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64301,7 +64301,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2293" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64327,7 +64327,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2294" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64353,7 +64353,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2295" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64379,7 +64379,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2296" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64405,7 +64405,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2297" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64431,7 +64431,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2298" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64457,7 +64457,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2299" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64483,7 +64483,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2300" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64509,7 +64509,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2301" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64535,7 +64535,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2302" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64561,7 +64561,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2303" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64587,7 +64587,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2304" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64613,7 +64613,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2305" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64639,7 +64639,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2306" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64665,7 +64665,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64691,7 +64691,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2308" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64717,7 +64717,7 @@
         <v>11.5</v>
       </c>
       <c r="G2309" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64743,7 +64743,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2310" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64769,7 +64769,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2311" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64795,7 +64795,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2312" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64821,7 +64821,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2313" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64847,7 +64847,7 @@
         <v>11.5</v>
       </c>
       <c r="G2314" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64873,7 +64873,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2315" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64899,7 +64899,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2316" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64925,7 +64925,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2317" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64951,7 +64951,7 @@
         <v>12</v>
       </c>
       <c r="G2318" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64977,7 +64977,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2319" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -65003,7 +65003,7 @@
         <v>12</v>
       </c>
       <c r="G2320" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -65029,7 +65029,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2321" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65055,7 +65055,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2322" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65081,7 +65081,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2323" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65107,7 +65107,7 @@
         <v>12</v>
       </c>
       <c r="G2324" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65133,7 +65133,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2325" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65159,7 +65159,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2326" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65185,7 +65185,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2327" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65211,7 +65211,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2328" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65237,7 +65237,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2329" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65263,7 +65263,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2330" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65289,7 +65289,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2331" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65315,7 +65315,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2332" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65341,7 +65341,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2333" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65367,7 +65367,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2334" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65393,7 +65393,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65419,7 +65419,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65445,7 +65445,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2337" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65471,7 +65471,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2338" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65497,7 +65497,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2339" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65523,7 +65523,7 @@
         <v>12.5</v>
       </c>
       <c r="G2340" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65549,7 +65549,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2341" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65575,7 +65575,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65601,7 +65601,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2343" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65627,7 +65627,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2344" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65653,7 +65653,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2345" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65679,7 +65679,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2346" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65705,7 +65705,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2347" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65731,7 +65731,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2348" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65757,7 +65757,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2349" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65783,7 +65783,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2350" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65809,7 +65809,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2351" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65835,7 +65835,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2352" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65861,7 +65861,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2353" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65887,7 +65887,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2354" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65913,7 +65913,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2355" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65939,7 +65939,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2356" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65965,7 +65965,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2357" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -65991,7 +65991,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2358" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -66017,7 +66017,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2359" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -66043,7 +66043,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2360" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66069,7 +66069,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2361" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66095,7 +66095,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2362" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66121,7 +66121,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2363" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66147,7 +66147,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2364" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66173,7 +66173,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2365" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66199,7 +66199,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2366" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66225,7 +66225,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2367" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66251,7 +66251,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G2368" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66277,7 +66277,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2369" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66303,7 +66303,7 @@
         <v>12</v>
       </c>
       <c r="G2370" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66329,7 +66329,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2371" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66355,7 +66355,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2372" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66381,7 +66381,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2373" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66407,7 +66407,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2374" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66433,7 +66433,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2375" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66459,7 +66459,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2376" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66485,7 +66485,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66511,7 +66511,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2378" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66537,7 +66537,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2379" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66563,7 +66563,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2380" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66589,7 +66589,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2381" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66615,7 +66615,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2382" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66641,7 +66641,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2383" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66667,7 +66667,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2384" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66693,7 +66693,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2385" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66719,7 +66719,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2386" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66745,7 +66745,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2387" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66771,7 +66771,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2388" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66797,7 +66797,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2389" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66823,7 +66823,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2390" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66849,7 +66849,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2391" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66875,7 +66875,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2392" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66901,7 +66901,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2393" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66927,7 +66927,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2394" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66953,7 +66953,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2395" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66979,7 +66979,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2396" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -67005,7 +67005,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2397" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -67031,7 +67031,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2398" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67057,7 +67057,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2399" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67083,7 +67083,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2400" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67109,7 +67109,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2401" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67135,7 +67135,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2402" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67161,7 +67161,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67187,7 +67187,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67213,7 +67213,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2405" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67239,7 +67239,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2406" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67265,7 +67265,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67291,7 +67291,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2408" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67317,7 +67317,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67343,7 +67343,7 @@
         <v>12.5</v>
       </c>
       <c r="G2410" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67369,7 +67369,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2411" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67395,7 +67395,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67421,7 +67421,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2413" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67447,7 +67447,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2414" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67473,7 +67473,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2415" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67499,7 +67499,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67525,7 +67525,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2417" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67551,7 +67551,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2418" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67577,7 +67577,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67603,7 +67603,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2420" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67629,7 +67629,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2421" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67655,7 +67655,7 @@
         <v>13</v>
       </c>
       <c r="G2422" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67681,7 +67681,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67707,7 +67707,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G2424" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67733,7 +67733,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2425" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67759,7 +67759,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2426" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67785,7 +67785,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67811,7 +67811,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2428" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67837,7 +67837,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2429" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67863,7 +67863,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2430" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67889,7 +67889,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2431" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67915,7 +67915,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2432" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67941,7 +67941,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2433" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67967,7 +67967,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2434" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -67993,7 +67993,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2435" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -68019,7 +68019,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2436" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -68045,7 +68045,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2437" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68071,7 +68071,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2438" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68097,7 +68097,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2439" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68123,7 +68123,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2440" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68149,7 +68149,7 @@
         <v>13.5</v>
       </c>
       <c r="G2441" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68175,7 +68175,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2442" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68201,7 +68201,7 @@
         <v>13.5</v>
       </c>
       <c r="G2443" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68227,7 +68227,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2444" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68253,7 +68253,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68279,7 +68279,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2446" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68305,7 +68305,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2447" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68331,7 +68331,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2448" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68357,7 +68357,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2449" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68383,7 +68383,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2450" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68409,7 +68409,7 @@
         <v>14</v>
       </c>
       <c r="G2451" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68435,7 +68435,7 @@
         <v>14</v>
       </c>
       <c r="G2452" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68461,7 +68461,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2453" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68487,7 +68487,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2454" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68513,7 +68513,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2455" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68539,7 +68539,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2456" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68565,7 +68565,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2457" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68591,7 +68591,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2458" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68617,7 +68617,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G2459" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68643,7 +68643,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2460" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68669,7 +68669,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G2461" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68695,7 +68695,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2462" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68721,7 +68721,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G2463" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68747,7 +68747,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2464" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68773,7 +68773,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G2465" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68799,7 +68799,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2466" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68825,7 +68825,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2467" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68851,7 +68851,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68877,7 +68877,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2469" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68903,7 +68903,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68929,7 +68929,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68955,7 +68955,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2472" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68981,7 +68981,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2473" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -69007,7 +69007,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2474" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -69033,7 +69033,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69059,7 +69059,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G2476" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69085,7 +69085,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69111,7 +69111,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69137,7 +69137,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69163,7 +69163,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2480" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69189,7 +69189,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2481" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69215,7 +69215,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69241,7 +69241,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2483" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69267,7 +69267,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2484" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69293,7 +69293,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2485" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69319,7 +69319,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2486" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69345,7 +69345,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G2487" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69371,7 +69371,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2488" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69397,7 +69397,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2489" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69423,7 +69423,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2490" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69449,7 +69449,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2491" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69475,7 +69475,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2492" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69501,7 +69501,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2493" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69527,7 +69527,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69553,7 +69553,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69579,7 +69579,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G2496" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69605,7 +69605,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2497" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69631,7 +69631,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2498" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69657,7 +69657,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2499" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69683,7 +69683,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2500" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69709,7 +69709,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2501" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69735,7 +69735,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2502" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69761,7 +69761,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G2503" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69787,7 +69787,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2504" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69813,7 +69813,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2505" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -69839,7 +69839,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2506" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -69865,7 +69865,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2507" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -69891,7 +69891,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G2508" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -69917,7 +69917,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2509" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -69943,7 +69943,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G2510" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -69969,7 +69969,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G2511" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -69995,7 +69995,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2512" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -70021,7 +70021,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2513" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -70047,7 +70047,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2514" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -70073,7 +70073,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G2515" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -70099,7 +70099,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2516" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -70125,7 +70125,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2517" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -70151,7 +70151,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2518" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -70177,7 +70177,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2519" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -70203,7 +70203,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G2520" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -70229,7 +70229,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G2521" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -70255,7 +70255,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2522" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -70281,7 +70281,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G2523" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -70307,7 +70307,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G2524" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -70333,7 +70333,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G2525" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -70359,7 +70359,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G2526" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -70385,7 +70385,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G2527" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -70411,7 +70411,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2528" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -70437,7 +70437,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G2529" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -70463,7 +70463,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2530" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -70471,7 +70471,7 @@
     </row>
     <row r="2531">
       <c r="A2531" s="1" t="n">
-        <v>46002.6910300926</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2531" t="n">
         <v>137761</v>
@@ -70489,9 +70489,35 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G2531" t="s">
+        <v>1445</v>
+      </c>
+      <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.691087963</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>104963</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>14.960000038147</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>14.6999998092651</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>14.8400001525879</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>14.7600002288818</v>
+      </c>
+      <c r="G2532" t="s">
         <v>1446</v>
       </c>
-      <c r="H2531" t="s">
+      <c r="H2532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="1447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1448" uniqueCount="1448">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">4.52814483642578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46432113647461</t>
+    <t xml:space="preserve">4.46432161331177</t>
   </si>
   <si>
     <t xml:space="preserve">4.30644083023071</t>
@@ -56,22 +56,22 @@
     <t xml:space="preserve">4.26613092422485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31315898895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31987762451172</t>
+    <t xml:space="preserve">4.31315946578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31987714767456</t>
   </si>
   <si>
     <t xml:space="preserve">4.3669056892395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27284860610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2358980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05114507675171</t>
+    <t xml:space="preserve">4.27284955978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23589897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05114555358887</t>
   </si>
   <si>
     <t xml:space="preserve">4.08473682403564</t>
@@ -80,28 +80,28 @@
     <t xml:space="preserve">3.74210238456726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91677856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03098964691162</t>
+    <t xml:space="preserve">3.91677927970886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03099012374878</t>
   </si>
   <si>
     <t xml:space="preserve">4.15527868270874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1284065246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01419401168823</t>
+    <t xml:space="preserve">4.12840557098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01419353485107</t>
   </si>
   <si>
     <t xml:space="preserve">4.12504625320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12168741226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94701075553894</t>
+    <t xml:space="preserve">4.1216869354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9470112323761</t>
   </si>
   <si>
     <t xml:space="preserve">3.80256700515747</t>
@@ -110,100 +110,100 @@
     <t xml:space="preserve">3.83615899085999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86975002288818</t>
+    <t xml:space="preserve">3.86975026130676</t>
   </si>
   <si>
     <t xml:space="preserve">3.58086276054382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42970108985901</t>
+    <t xml:space="preserve">3.42970037460327</t>
   </si>
   <si>
     <t xml:space="preserve">3.75217962265015</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6077356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84959530830383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670132637024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96716690063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06458187103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8294403553009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77233481407166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90334153175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87982821464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72866582870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79584860801697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88318657875061</t>
+    <t xml:space="preserve">3.60773587226868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84959554672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670084953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96716642379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06458139419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82943964004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77233409881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90334129333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87982773780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72866606712341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79584908485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88318705558777</t>
   </si>
   <si>
     <t xml:space="preserve">3.95708847045898</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13176488876343</t>
+    <t xml:space="preserve">4.13176441192627</t>
   </si>
   <si>
     <t xml:space="preserve">4.19558811187744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18551158905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13848304748535</t>
+    <t xml:space="preserve">4.18551015853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13848209381104</t>
   </si>
   <si>
     <t xml:space="preserve">4.22246170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29972219467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3568286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25605344772339</t>
+    <t xml:space="preserve">4.29972267150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35682916641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25605392456055</t>
   </si>
   <si>
     <t xml:space="preserve">4.27956771850586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14856052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3265962600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26949119567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16535663604736</t>
+    <t xml:space="preserve">4.14856100082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32659578323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26948976516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16535568237305</t>
   </si>
   <si>
     <t xml:space="preserve">4.09817361831665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04778575897217</t>
+    <t xml:space="preserve">4.04778623580933</t>
   </si>
   <si>
     <t xml:space="preserve">4.04106760025024</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">3.93021535873413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91005969047546</t>
+    <t xml:space="preserve">3.91006064414978</t>
   </si>
   <si>
     <t xml:space="preserve">3.81936264038086</t>
@@ -221,28 +221,28 @@
     <t xml:space="preserve">3.75889801979065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71187043190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93357396125793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82608127593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08137702941895</t>
+    <t xml:space="preserve">3.71186995506287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93357419967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82608103752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08137655258179</t>
   </si>
   <si>
     <t xml:space="preserve">4.15863800048828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17879390716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21238374710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21574401855469</t>
+    <t xml:space="preserve">4.17879295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21238422393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21574354171753</t>
   </si>
   <si>
     <t xml:space="preserve">4.2829270362854</t>
@@ -254,28 +254,28 @@
     <t xml:space="preserve">4.3534688949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1989483833313</t>
+    <t xml:space="preserve">4.19894742965698</t>
   </si>
   <si>
     <t xml:space="preserve">4.07465887069702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08809518814087</t>
+    <t xml:space="preserve">4.08809566497803</t>
   </si>
   <si>
     <t xml:space="preserve">4.06122255325317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0242714881897</t>
+    <t xml:space="preserve">4.02427196502686</t>
   </si>
   <si>
     <t xml:space="preserve">3.93693375587463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21648979187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14420700073242</t>
+    <t xml:space="preserve">4.21649026870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14420747756958</t>
   </si>
   <si>
     <t xml:space="preserve">4.19927978515625</t>
@@ -287,40 +287,40 @@
     <t xml:space="preserve">4.23369979858398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23714113235474</t>
+    <t xml:space="preserve">4.23714208602905</t>
   </si>
   <si>
     <t xml:space="preserve">4.49185180664062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49873638153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47119998931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45743227005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46431636810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37826442718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31975078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37138080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28188896179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42989540100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34040260314941</t>
+    <t xml:space="preserve">4.4987359046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47119951248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45743131637573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46431541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37826490402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31975030899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37138175964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28188848495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42989587783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34040212631226</t>
   </si>
   <si>
     <t xml:space="preserve">4.35072946548462</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">3.91703271865845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98243117332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884450912476</t>
+    <t xml:space="preserve">3.98243045806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884427070618</t>
   </si>
   <si>
     <t xml:space="preserve">4.1373233795166</t>
@@ -350,16 +350,16 @@
     <t xml:space="preserve">4.38170719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.423011302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52971458435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74148941040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181484222412</t>
+    <t xml:space="preserve">4.42301225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52971506118774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74148917198181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181436538696</t>
   </si>
   <si>
     <t xml:space="preserve">3.73116326332092</t>
@@ -371,136 +371,136 @@
     <t xml:space="preserve">3.65199613571167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52464127540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42826414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50743079185486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65888047218323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75525784492493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82065606117249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78623580932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670704841614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96522116661072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95145273208618</t>
+    <t xml:space="preserve">3.52464079856873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42826390266418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50743126869202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65887999534607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75525736808777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82065582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78623509407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670728683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96522164344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95145297050476</t>
   </si>
   <si>
     <t xml:space="preserve">4.04094648361206</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01340961456299</t>
+    <t xml:space="preserve">4.01341009140015</t>
   </si>
   <si>
     <t xml:space="preserve">3.94456887245178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98931550979614</t>
+    <t xml:space="preserve">3.9893159866333</t>
   </si>
   <si>
     <t xml:space="preserve">3.95833659172058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7965612411499</t>
+    <t xml:space="preserve">3.79656171798706</t>
   </si>
   <si>
     <t xml:space="preserve">3.90326452255249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80000376701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68641686439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7001850605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76558375358582</t>
+    <t xml:space="preserve">3.80000305175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68641591072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70018458366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76558351516724</t>
   </si>
   <si>
     <t xml:space="preserve">3.70362734794617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66576385498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66920638084412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55217695236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48677897453308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47989392280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37319183349609</t>
+    <t xml:space="preserve">3.66576433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66920590400696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55217742919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48677921295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47989463806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37319231033325</t>
   </si>
   <si>
     <t xml:space="preserve">3.3718147277832</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50054669380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68985843658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561923980713</t>
+    <t xml:space="preserve">3.50054693222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68985915184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561900138855</t>
   </si>
   <si>
     <t xml:space="preserve">3.45235824584961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47645306587219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64511227607727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72083735466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70706820487976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77935147285461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80688810348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61413431167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757636070251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57971382141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56594562530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49366331100464</t>
+    <t xml:space="preserve">3.47645258903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64511275291443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7208366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7070689201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77935171127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80688762664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61413407325745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757588386536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57971358299255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5659453868866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49366307258606</t>
   </si>
   <si>
     <t xml:space="preserve">3.49022078514099</t>
@@ -512,61 +512,61 @@
     <t xml:space="preserve">3.63822817802429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49710488319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38695979118347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35804653167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37456870079041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31123447418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3263795375824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35529327392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41587281227112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51431560516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48333621025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51087260246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51775693893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47301054000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5762722492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53496718406677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64855456352234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67953252792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59692406654358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6416699886322</t>
+    <t xml:space="preserve">3.49710536003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38696002960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35804629325867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37456846237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31123495101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32637977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35529351234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41587233543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51431488990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48333692550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51087307929993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51775717735291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47301077842712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57627177238464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53496742248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64855432510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67953205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.596923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64167046546936</t>
   </si>
   <si>
     <t xml:space="preserve">3.63134431838989</t>
@@ -575,58 +575,58 @@
     <t xml:space="preserve">3.56250333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53152561187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45580053329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41174221038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42964124679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45924210548401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44203209877014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52808332443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6347861289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67609047889709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62790179252625</t>
+    <t xml:space="preserve">3.53152537345886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45580077171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41174268722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42964100837708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45924234390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44203186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52808284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63478660583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67609071731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62790203094482</t>
   </si>
   <si>
     <t xml:space="preserve">3.58659768104553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54529356956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5590615272522</t>
+    <t xml:space="preserve">3.54529333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55906128883362</t>
   </si>
   <si>
     <t xml:space="preserve">3.56938767433167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71739530563354</t>
+    <t xml:space="preserve">3.71739506721497</t>
   </si>
   <si>
     <t xml:space="preserve">3.94112706184387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00996780395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88605427742004</t>
+    <t xml:space="preserve">4.00996685028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8860547542572</t>
   </si>
   <si>
     <t xml:space="preserve">3.97210550308228</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">3.83442401885986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92735886573792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98587274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0547137260437</t>
+    <t xml:space="preserve">3.92735862731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98587322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05471420288086</t>
   </si>
   <si>
     <t xml:space="preserve">3.9308009147644</t>
@@ -650,76 +650,76 @@
     <t xml:space="preserve">4.04438781738281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06159830093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91014862060547</t>
+    <t xml:space="preserve">4.06159782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91014814376831</t>
   </si>
   <si>
     <t xml:space="preserve">3.89982271194458</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05815649032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07192468643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07880878448486</t>
+    <t xml:space="preserve">4.05815601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07192420959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07880830764771</t>
   </si>
   <si>
     <t xml:space="preserve">4.03061962127686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19583702087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20960569381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29565620422363</t>
+    <t xml:space="preserve">4.19583654403687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20960521697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29565668106079</t>
   </si>
   <si>
     <t xml:space="preserve">4.27844619750977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2474684715271</t>
+    <t xml:space="preserve">4.24746751785278</t>
   </si>
   <si>
     <t xml:space="preserve">4.30254125595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12699699401855</t>
+    <t xml:space="preserve">4.1269965171814</t>
   </si>
   <si>
     <t xml:space="preserve">4.13043832778931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20272064208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10634469985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12011337280273</t>
+    <t xml:space="preserve">4.202721118927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10634422302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12011289596558</t>
   </si>
   <si>
     <t xml:space="preserve">4.17862749099731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24058389663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14764881134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16141700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04783010482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14076519012451</t>
+    <t xml:space="preserve">4.2405834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14764976501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16141748428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04782962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1407642364502</t>
   </si>
   <si>
     <t xml:space="preserve">4.1510910987854</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">4.15453290939331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18206882476807</t>
+    <t xml:space="preserve">4.18206930160522</t>
   </si>
   <si>
     <t xml:space="preserve">4.15797519683838</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">4.36449718475342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43333768844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44022130966187</t>
+    <t xml:space="preserve">4.4333381652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44022178649902</t>
   </si>
   <si>
     <t xml:space="preserve">4.3851490020752</t>
@@ -755,31 +755,31 @@
     <t xml:space="preserve">4.47464179992676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41956901550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37482404708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41268539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34384489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30942487716675</t>
+    <t xml:space="preserve">4.41956996917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37482309341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41268491744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34384441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30942440032959</t>
   </si>
   <si>
     <t xml:space="preserve">4.36793851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35417127609253</t>
+    <t xml:space="preserve">4.35417032241821</t>
   </si>
   <si>
     <t xml:space="preserve">4.28533029556274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52627182006836</t>
+    <t xml:space="preserve">4.52627229690552</t>
   </si>
   <si>
     <t xml:space="preserve">4.40580129623413</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">4.48840999603271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50906229019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53659915924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54348230361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.447105884552</t>
+    <t xml:space="preserve">4.50906276702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53659820556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54348278045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44710540771484</t>
   </si>
   <si>
     <t xml:space="preserve">4.67083740234375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69899606704712</t>
+    <t xml:space="preserve">4.69899654388428</t>
   </si>
   <si>
     <t xml:space="preserve">4.80107259750366</t>
@@ -812,37 +812,37 @@
     <t xml:space="preserve">4.71659564971924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83627128601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86091041564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85035037994385</t>
+    <t xml:space="preserve">4.83626985549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8609094619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85034942626953</t>
   </si>
   <si>
     <t xml:space="preserve">4.87850904464722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78347253799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72011470794678</t>
+    <t xml:space="preserve">4.78347301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72011566162109</t>
   </si>
   <si>
     <t xml:space="preserve">4.68491744995117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73067569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75179386138916</t>
+    <t xml:space="preserve">4.73067474365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75179433822632</t>
   </si>
   <si>
     <t xml:space="preserve">4.81515169143677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81163263320923</t>
+    <t xml:space="preserve">4.81163215637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.9277868270874</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">4.78699350357056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95946598052979</t>
+    <t xml:space="preserve">4.95946502685547</t>
   </si>
   <si>
     <t xml:space="preserve">4.86442947387695</t>
@@ -875,22 +875,22 @@
     <t xml:space="preserve">4.89610815048218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97354507446289</t>
+    <t xml:space="preserve">4.9137077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97354459762573</t>
   </si>
   <si>
     <t xml:space="preserve">4.97706460952759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94538593292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1108193397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2586522102356</t>
+    <t xml:space="preserve">4.94538640975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11081981658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25865268707275</t>
   </si>
   <si>
     <t xml:space="preserve">5.0615406036377</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">5.08618021011353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10377931594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09674024581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05098152160645</t>
+    <t xml:space="preserve">5.10377883911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09673929214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05098104476929</t>
   </si>
   <si>
     <t xml:space="preserve">5.08969974517822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01930236816406</t>
+    <t xml:space="preserve">5.01930332183838</t>
   </si>
   <si>
     <t xml:space="preserve">5.04746150970459</t>
@@ -920,43 +920,43 @@
     <t xml:space="preserve">4.96650505065918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91018724441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00874376296997</t>
+    <t xml:space="preserve">4.91018772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00874280929565</t>
   </si>
   <si>
     <t xml:space="preserve">5.10025930404663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06857967376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13193798065186</t>
+    <t xml:space="preserve">5.06858062744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1319375038147</t>
   </si>
   <si>
     <t xml:space="preserve">5.04042196273804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12489795684814</t>
+    <t xml:space="preserve">5.1248984336853</t>
   </si>
   <si>
     <t xml:space="preserve">5.20937442779541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36424732208252</t>
+    <t xml:space="preserve">5.36424779891968</t>
   </si>
   <si>
     <t xml:space="preserve">5.21289443969727</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03690147399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16361665725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27273178100586</t>
+    <t xml:space="preserve">5.03690195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16361713409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27273225784302</t>
   </si>
   <si>
     <t xml:space="preserve">5.23049354553223</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">5.10729885101318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00522327423096</t>
+    <t xml:space="preserve">5.00522375106812</t>
   </si>
   <si>
     <t xml:space="preserve">4.99818325042725</t>
@@ -983,22 +983,22 @@
     <t xml:space="preserve">5.01226282119751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04394149780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06506156921387</t>
+    <t xml:space="preserve">5.04394197463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06506109237671</t>
   </si>
   <si>
     <t xml:space="preserve">5.15657663345337</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34312868118286</t>
+    <t xml:space="preserve">5.34312963485718</t>
   </si>
   <si>
     <t xml:space="preserve">5.30089092254639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27977180480957</t>
+    <t xml:space="preserve">5.27977132797241</t>
   </si>
   <si>
     <t xml:space="preserve">5.30793046951294</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">5.25161266326904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29385089874268</t>
+    <t xml:space="preserve">5.29385042190552</t>
   </si>
   <si>
     <t xml:space="preserve">5.29033088684082</t>
@@ -1019,22 +1019,22 @@
     <t xml:space="preserve">5.34664821624756</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36776733398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35368871688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38536691665649</t>
+    <t xml:space="preserve">5.36776781082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35368919372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38536643981934</t>
   </si>
   <si>
     <t xml:space="preserve">5.3994460105896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26569271087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31145000457764</t>
+    <t xml:space="preserve">5.26569223403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31145048141479</t>
   </si>
   <si>
     <t xml:space="preserve">5.32553005218506</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">5.21641445159912</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14249706268311</t>
+    <t xml:space="preserve">5.14249753952026</t>
   </si>
   <si>
     <t xml:space="preserve">5.16713666915894</t>
@@ -1058,22 +1058,22 @@
     <t xml:space="preserve">5.31497001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29737043380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19177532196045</t>
+    <t xml:space="preserve">5.29737091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19177579879761</t>
   </si>
   <si>
     <t xml:space="preserve">5.35720825195312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07210111618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98410415649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94186639785767</t>
+    <t xml:space="preserve">5.07210063934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98410367965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94186592102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.86794948577881</t>
@@ -1082,58 +1082,58 @@
     <t xml:space="preserve">4.92426729202271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98058414459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03338289260864</t>
+    <t xml:space="preserve">4.98058462142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03338241577148</t>
   </si>
   <si>
     <t xml:space="preserve">5.0545015335083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1847357749939</t>
+    <t xml:space="preserve">5.18473529815674</t>
   </si>
   <si>
     <t xml:space="preserve">5.17417573928833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21993446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17769575119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22697401046753</t>
+    <t xml:space="preserve">5.21993494033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1776967048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22697353363037</t>
   </si>
   <si>
     <t xml:space="preserve">5.28681182861328</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02282333374023</t>
+    <t xml:space="preserve">5.02282285690308</t>
   </si>
   <si>
     <t xml:space="preserve">5.00170373916626</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02986288070679</t>
+    <t xml:space="preserve">5.02986240386963</t>
   </si>
   <si>
     <t xml:space="preserve">5.05802154541016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92074632644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99114465713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37128782272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47688341140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48392343521118</t>
+    <t xml:space="preserve">4.92074680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99114418029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37128734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47688293457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48392295837402</t>
   </si>
   <si>
     <t xml:space="preserve">5.44168472290039</t>
@@ -1148,10 +1148,10 @@
     <t xml:space="preserve">5.51208114624023</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46984243392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40648508071899</t>
+    <t xml:space="preserve">5.4698429107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40648603439331</t>
   </si>
   <si>
     <t xml:space="preserve">5.37832736968994</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">5.18825531005859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13897800445557</t>
+    <t xml:space="preserve">5.13897752761841</t>
   </si>
   <si>
     <t xml:space="preserve">5.32904958724976</t>
@@ -1172,58 +1172,58 @@
     <t xml:space="preserve">5.1952953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24457311630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22345399856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23753356933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16009712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11785840988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97002506256104</t>
+    <t xml:space="preserve">5.24457263946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22345352172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23753309249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16009616851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11785793304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97002458572388</t>
   </si>
   <si>
     <t xml:space="preserve">5.21899938583374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14661359786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98012685775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94393396377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81364011764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84259510040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85707187652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82087898254395</t>
+    <t xml:space="preserve">5.14661407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98012733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94393444061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81364107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84259462356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85707139968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82087850570679</t>
   </si>
   <si>
     <t xml:space="preserve">4.80640125274658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56029081344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46618986129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21284008026123</t>
+    <t xml:space="preserve">4.5602912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46618938446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21284055709839</t>
   </si>
   <si>
     <t xml:space="preserve">4.4517126083374</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">4.45895099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43723583221436</t>
+    <t xml:space="preserve">4.4372353553772</t>
   </si>
   <si>
     <t xml:space="preserve">4.53133678436279</t>
@@ -1262,19 +1262,19 @@
     <t xml:space="preserve">4.64715385437012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69058465957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57476854324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58200597763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48790550231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54581356048584</t>
+    <t xml:space="preserve">4.69058513641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57476806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58200645446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48790597915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54581308364868</t>
   </si>
   <si>
     <t xml:space="preserve">4.58924531936646</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">4.6037220954895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68334627151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6978235244751</t>
+    <t xml:space="preserve">4.68334579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69782304763794</t>
   </si>
   <si>
     <t xml:space="preserve">4.62543773651123</t>
@@ -1295,25 +1295,25 @@
     <t xml:space="preserve">4.63267660140991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61819934844971</t>
+    <t xml:space="preserve">4.61819982528687</t>
   </si>
   <si>
     <t xml:space="preserve">4.56752967834473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44447422027588</t>
+    <t xml:space="preserve">4.44447374343872</t>
   </si>
   <si>
     <t xml:space="preserve">4.42999696731567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59648323059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47342777252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51685905456543</t>
+    <t xml:space="preserve">4.59648370742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47342824935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51685953140259</t>
   </si>
   <si>
     <t xml:space="preserve">4.50962114334106</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">4.17664766311646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10426187515259</t>
+    <t xml:space="preserve">4.10426139831543</t>
   </si>
   <si>
     <t xml:space="preserve">4.04635429382324</t>
@@ -1331,25 +1331,25 @@
     <t xml:space="preserve">4.0246376991272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03187656402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05359220504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06806945800781</t>
+    <t xml:space="preserve">4.03187608718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05359172821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06806898117065</t>
   </si>
   <si>
     <t xml:space="preserve">3.97396779060364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00292253494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85091304779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8726282119751</t>
+    <t xml:space="preserve">4.00292205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85091209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87262725830078</t>
   </si>
   <si>
     <t xml:space="preserve">3.93053650856018</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">3.92329812049866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11150026321411</t>
+    <t xml:space="preserve">4.11149978637695</t>
   </si>
   <si>
     <t xml:space="preserve">4.22731781005859</t>
@@ -1370,31 +1370,31 @@
     <t xml:space="preserve">4.22007894515991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23455619812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25627136230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27798652648926</t>
+    <t xml:space="preserve">4.23455572128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25627183914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27798700332642</t>
   </si>
   <si>
     <t xml:space="preserve">4.29970264434814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36484956741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35761117935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26351022720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09702301025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06083059310913</t>
+    <t xml:space="preserve">4.36485004425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35761165618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26350975036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09702348709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06083106994629</t>
   </si>
   <si>
     <t xml:space="preserve">4.12597703933716</t>
@@ -1406,10 +1406,10 @@
     <t xml:space="preserve">3.84367370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78576588630676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87986660003662</t>
+    <t xml:space="preserve">3.78576517105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87986707687378</t>
   </si>
   <si>
     <t xml:space="preserve">3.94501328468323</t>
@@ -1418,49 +1418,49 @@
     <t xml:space="preserve">3.80748152732849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72061848640442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68442535400391</t>
+    <t xml:space="preserve">3.72061800956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68442559242249</t>
   </si>
   <si>
     <t xml:space="preserve">3.5794665813446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4564106464386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55051231384277</t>
+    <t xml:space="preserve">3.45641112327576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55051255226135</t>
   </si>
   <si>
     <t xml:space="preserve">3.81471967697144</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76405000686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82919692993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83643579483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85815095901489</t>
+    <t xml:space="preserve">3.7640495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82919669151306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83643555641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85815048217773</t>
   </si>
   <si>
     <t xml:space="preserve">3.74233412742615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75681090354919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70614147186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67718696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6337559223175</t>
+    <t xml:space="preserve">3.75681114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70614099502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67718720436096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63375568389893</t>
   </si>
   <si>
     <t xml:space="preserve">3.66994833946228</t>
@@ -1469,16 +1469,16 @@
     <t xml:space="preserve">3.61927819252014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64099478721619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7712881565094</t>
+    <t xml:space="preserve">3.64099454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77128839492798</t>
   </si>
   <si>
     <t xml:space="preserve">3.80024266242981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66270971298218</t>
+    <t xml:space="preserve">3.66271018981934</t>
   </si>
   <si>
     <t xml:space="preserve">3.72785711288452</t>
@@ -1487,85 +1487,85 @@
     <t xml:space="preserve">3.86538934707642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60480141639709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58670520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57584714889526</t>
+    <t xml:space="preserve">3.60480117797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58670473098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57584738731384</t>
   </si>
   <si>
     <t xml:space="preserve">3.54327344894409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65547156333923</t>
+    <t xml:space="preserve">3.65547132492065</t>
   </si>
   <si>
     <t xml:space="preserve">3.82195854187012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71338033676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69890284538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69166398048401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62651705741882</t>
+    <t xml:space="preserve">3.7133800983429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69890308380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69166445732117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6265172958374</t>
   </si>
   <si>
     <t xml:space="preserve">3.64823269844055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52517676353455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60118246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54689288139343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50346159934998</t>
+    <t xml:space="preserve">3.52517747879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60118222236633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54689359664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5034613609314</t>
   </si>
   <si>
     <t xml:space="preserve">3.60842108726501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79300379753113</t>
+    <t xml:space="preserve">3.79300355911255</t>
   </si>
   <si>
     <t xml:space="preserve">3.88710498809814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56498956680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59394335746765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77852654457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58308553695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53965425491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48174548149109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49622344970703</t>
+    <t xml:space="preserve">3.5649893283844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59394359588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77852606773376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58308529853821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53965473175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48174595832825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49622297286987</t>
   </si>
   <si>
     <t xml:space="preserve">3.452791929245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42021822929382</t>
+    <t xml:space="preserve">3.42021799087524</t>
   </si>
   <si>
     <t xml:space="preserve">3.43155598640442</t>
@@ -1574,22 +1574,22 @@
     <t xml:space="preserve">3.43533539772034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41265988349915</t>
+    <t xml:space="preserve">3.41265964508057</t>
   </si>
   <si>
     <t xml:space="preserve">3.33329510688782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34841251373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38620495796204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3710880279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36352920532227</t>
+    <t xml:space="preserve">3.34841275215149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38620519638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37108826637268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36352944374084</t>
   </si>
   <si>
     <t xml:space="preserve">3.38242602348328</t>
@@ -1604,13 +1604,13 @@
     <t xml:space="preserve">3.29172396659851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25393152236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3143994808197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33707475662231</t>
+    <t xml:space="preserve">3.25393128395081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31439971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33707451820374</t>
   </si>
   <si>
     <t xml:space="preserve">3.27660703659058</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">3.23125624656677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21235942840576</t>
+    <t xml:space="preserve">3.21235966682434</t>
   </si>
   <si>
     <t xml:space="preserve">3.24259352684021</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">3.15189170837402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18968391418457</t>
+    <t xml:space="preserve">3.18968415260315</t>
   </si>
   <si>
     <t xml:space="preserve">3.20102167129517</t>
@@ -1655,28 +1655,28 @@
     <t xml:space="preserve">3.25015234947205</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39376354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59784317016602</t>
+    <t xml:space="preserve">3.39376330375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59784269332886</t>
   </si>
   <si>
     <t xml:space="preserve">3.65831065177917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55627107620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55249166488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56760835647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57516717910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60540175437927</t>
+    <t xml:space="preserve">3.55627059936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55249190330505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56760907173157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57516741752625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60540151596069</t>
   </si>
   <si>
     <t xml:space="preserve">3.53359580039978</t>
@@ -1685,19 +1685,19 @@
     <t xml:space="preserve">3.47690677642822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59028434753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5827260017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57138824462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52603697776794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50336217880249</t>
+    <t xml:space="preserve">3.5902841091156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58272552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57138800621033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52603673934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50336194038391</t>
   </si>
   <si>
     <t xml:space="preserve">3.43911457061768</t>
@@ -1712,13 +1712,13 @@
     <t xml:space="preserve">3.40132188796997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36730885505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40888047218323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34085416793823</t>
+    <t xml:space="preserve">3.36730861663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40888023376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34085440635681</t>
   </si>
   <si>
     <t xml:space="preserve">3.42399740219116</t>
@@ -1727,19 +1727,19 @@
     <t xml:space="preserve">3.51469969749451</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49958205223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54871273040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63941431045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65453147888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68098592758179</t>
+    <t xml:space="preserve">3.49958252906799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54871249198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63941478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65453195571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68098640441895</t>
   </si>
   <si>
     <t xml:space="preserve">3.67342782020569</t>
@@ -1751,19 +1751,19 @@
     <t xml:space="preserve">3.78680539131165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92285776138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86239004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74523377418518</t>
+    <t xml:space="preserve">3.92285823822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86239051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74523329734802</t>
   </si>
   <si>
     <t xml:space="preserve">3.76790928840637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83971452713013</t>
+    <t xml:space="preserve">3.83971500396729</t>
   </si>
   <si>
     <t xml:space="preserve">3.83215618133545</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">3.69232439994812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70366191864014</t>
+    <t xml:space="preserve">3.70366239547729</t>
   </si>
   <si>
     <t xml:space="preserve">3.77924633026123</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">3.66586947441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69610333442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66964864730835</t>
+    <t xml:space="preserve">3.69610357284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66964840888977</t>
   </si>
   <si>
     <t xml:space="preserve">3.73389601707458</t>
@@ -1802,25 +1802,25 @@
     <t xml:space="preserve">3.81703925132751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84727263450623</t>
+    <t xml:space="preserve">3.84727311134338</t>
   </si>
   <si>
     <t xml:space="preserve">3.90018248558044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98332571983337</t>
+    <t xml:space="preserve">3.98332619667053</t>
   </si>
   <si>
     <t xml:space="preserve">3.96065020561218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95309233665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93041682243347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94553327560425</t>
+    <t xml:space="preserve">3.9530918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93041634559631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94553279876709</t>
   </si>
   <si>
     <t xml:space="preserve">3.99088501930237</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">3.91529941558838</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02111864089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09670305252075</t>
+    <t xml:space="preserve">4.0211181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09670352935791</t>
   </si>
   <si>
     <t xml:space="preserve">4.03623533248901</t>
@@ -1847,16 +1847,16 @@
     <t xml:space="preserve">4.13449573516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05135250091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02867698669434</t>
+    <t xml:space="preserve">4.05135297775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02867650985718</t>
   </si>
   <si>
     <t xml:space="preserve">4.0060019493103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04379367828369</t>
+    <t xml:space="preserve">4.04379320144653</t>
   </si>
   <si>
     <t xml:space="preserve">4.11937856674194</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">3.97576808929443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90774083137512</t>
+    <t xml:space="preserve">3.90774130821228</t>
   </si>
   <si>
     <t xml:space="preserve">3.89262437820435</t>
@@ -1883,40 +1883,40 @@
     <t xml:space="preserve">3.88506531715393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87750792503357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85483145713806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80192279815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59406352043152</t>
+    <t xml:space="preserve">3.87750744819641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85483193397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80192255973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59406399726868</t>
   </si>
   <si>
     <t xml:space="preserve">3.60162210464478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65075278282166</t>
+    <t xml:space="preserve">3.6507523059845</t>
   </si>
   <si>
     <t xml:space="preserve">3.71877884864807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99844264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72255825996399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63185548782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46556901931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44667315483093</t>
+    <t xml:space="preserve">3.99844312667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72255802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63185572624207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46556925773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44667291641235</t>
   </si>
   <si>
     <t xml:space="preserve">3.28416514396667</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">3.0649688243866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.838214635849</t>
+    <t xml:space="preserve">2.83821439743042</t>
   </si>
   <si>
     <t xml:space="preserve">2.8344349861145</t>
@@ -1940,31 +1940,31 @@
     <t xml:space="preserve">2.70971989631653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93269562721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00450110435486</t>
+    <t xml:space="preserve">2.93269538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00450134277344</t>
   </si>
   <si>
     <t xml:space="preserve">2.97426724433899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94403338432312</t>
+    <t xml:space="preserve">2.94403314590454</t>
   </si>
   <si>
     <t xml:space="preserve">2.91001987457275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96292972564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85333108901978</t>
+    <t xml:space="preserve">2.96292948722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85333132743835</t>
   </si>
   <si>
     <t xml:space="preserve">2.89490294456482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88734459877014</t>
+    <t xml:space="preserve">2.88734436035156</t>
   </si>
   <si>
     <t xml:space="preserve">2.92135787010193</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">2.85711050033569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90246105194092</t>
+    <t xml:space="preserve">2.9024612903595</t>
   </si>
   <si>
     <t xml:space="preserve">2.82687664031982</t>
@@ -1982,13 +1982,13 @@
     <t xml:space="preserve">2.8911235332489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99694228172302</t>
+    <t xml:space="preserve">2.9969425201416</t>
   </si>
   <si>
     <t xml:space="preserve">2.9515917301178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97804665565491</t>
+    <t xml:space="preserve">2.97804641723633</t>
   </si>
   <si>
     <t xml:space="preserve">2.99316334724426</t>
@@ -2000,34 +2000,34 @@
     <t xml:space="preserve">3.03473472595215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02717661857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12165784835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06118988990784</t>
+    <t xml:space="preserve">3.02717638015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12165760993958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06119012832642</t>
   </si>
   <si>
     <t xml:space="preserve">3.09898233413696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16700911521912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14433264732361</t>
+    <t xml:space="preserve">3.1670093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14433288574219</t>
   </si>
   <si>
     <t xml:space="preserve">3.19346332550049</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21991848945618</t>
+    <t xml:space="preserve">3.2199182510376</t>
   </si>
   <si>
     <t xml:space="preserve">3.26904821395874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32195782661438</t>
+    <t xml:space="preserve">3.3219575881958</t>
   </si>
   <si>
     <t xml:space="preserve">3.15945029258728</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">3.07252764701843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06874823570251</t>
+    <t xml:space="preserve">3.06874847412109</t>
   </si>
   <si>
     <t xml:space="preserve">3.10654067993164</t>
@@ -2051,34 +2051,34 @@
     <t xml:space="preserve">3.28794455528259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40510129928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51092028617859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48824501037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45801019668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29550290107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34463357925415</t>
+    <t xml:space="preserve">3.40510153770447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51091980934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4882447719574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45801043510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29550313949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34463334083557</t>
   </si>
   <si>
     <t xml:space="preserve">3.29928255081177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30684089660645</t>
+    <t xml:space="preserve">3.30684113502502</t>
   </si>
   <si>
     <t xml:space="preserve">3.30306148529053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26148986816406</t>
+    <t xml:space="preserve">3.26149010658264</t>
   </si>
   <si>
     <t xml:space="preserve">3.37864661216736</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">3.26526927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754271507263</t>
+    <t xml:space="preserve">3.39754295349121</t>
   </si>
   <si>
     <t xml:space="preserve">3.48068642616272</t>
@@ -2108,10 +2108,10 @@
     <t xml:space="preserve">3.2274763584137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18590521812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24637269973755</t>
+    <t xml:space="preserve">3.18590497970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24637293815613</t>
   </si>
   <si>
     <t xml:space="preserve">3.17456722259521</t>
@@ -2129,22 +2129,22 @@
     <t xml:space="preserve">3.08008599281311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04607319831848</t>
+    <t xml:space="preserve">3.0460729598999</t>
   </si>
   <si>
     <t xml:space="preserve">3.01583886146545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9402539730072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95537090301514</t>
+    <t xml:space="preserve">2.94025373458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95537066459656</t>
   </si>
   <si>
     <t xml:space="preserve">2.92513704299927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8835654258728</t>
+    <t xml:space="preserve">2.88356518745422</t>
   </si>
   <si>
     <t xml:space="preserve">2.80042195320129</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">2.7890841960907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77018785476685</t>
+    <t xml:space="preserve">2.77018761634827</t>
   </si>
   <si>
     <t xml:space="preserve">2.75129151344299</t>
@@ -2162,19 +2162,19 @@
     <t xml:space="preserve">2.71727848052979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72105741500854</t>
+    <t xml:space="preserve">2.72105765342712</t>
   </si>
   <si>
     <t xml:space="preserve">2.67948603630066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55477070808411</t>
+    <t xml:space="preserve">2.55477094650269</t>
   </si>
   <si>
     <t xml:space="preserve">2.44895195960999</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55099129676819</t>
+    <t xml:space="preserve">2.55099153518677</t>
   </si>
   <si>
     <t xml:space="preserve">2.61523866653442</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">3.62807703018188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6356348991394</t>
+    <t xml:space="preserve">3.63563537597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.57894706726074</t>
@@ -2201,16 +2201,16 @@
     <t xml:space="preserve">3.56382989883423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50714063644409</t>
+    <t xml:space="preserve">3.50714087486267</t>
   </si>
   <si>
     <t xml:space="preserve">3.48446559906006</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52225804328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41643881797791</t>
+    <t xml:space="preserve">3.52225828170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41643857955933</t>
   </si>
   <si>
     <t xml:space="preserve">3.12543725967407</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">3.80948066711426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76035094261169</t>
+    <t xml:space="preserve">3.76035046577454</t>
   </si>
   <si>
     <t xml:space="preserve">3.64319372177124</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">3.68476533889771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74901247024536</t>
+    <t xml:space="preserve">3.74901294708252</t>
   </si>
   <si>
     <t xml:space="preserve">3.79436373710632</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">3.77546739578247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76412963867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15717172622681</t>
+    <t xml:space="preserve">3.7641294002533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15717077255249</t>
   </si>
   <si>
     <t xml:space="preserve">4.11182069778442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17228841781616</t>
+    <t xml:space="preserve">4.172287940979</t>
   </si>
   <si>
     <t xml:space="preserve">4.31345558166504</t>
@@ -2258,37 +2258,37 @@
     <t xml:space="preserve">4.22718667984009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1252326965332</t>
+    <t xml:space="preserve">4.12523221969604</t>
   </si>
   <si>
     <t xml:space="preserve">4.07817602157593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08601951599121</t>
+    <t xml:space="preserve">4.08601903915405</t>
   </si>
   <si>
     <t xml:space="preserve">4.09386110305786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20365905761719</t>
+    <t xml:space="preserve">4.20365953445435</t>
   </si>
   <si>
     <t xml:space="preserve">4.26639986038208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27424240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25855731964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36835432052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32914161682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34482669830322</t>
+    <t xml:space="preserve">4.27424192428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25855779647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36835479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32914113998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34482622146606</t>
   </si>
   <si>
     <t xml:space="preserve">4.35266971588135</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">4.30561351776123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2899284362793</t>
+    <t xml:space="preserve">4.28992795944214</t>
   </si>
   <si>
     <t xml:space="preserve">4.28208541870117</t>
@@ -2306,13 +2306,13 @@
     <t xml:space="preserve">4.19581604003906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03896331787109</t>
+    <t xml:space="preserve">4.03896379470825</t>
   </si>
   <si>
     <t xml:space="preserve">4.02327871322632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99974966049194</t>
+    <t xml:space="preserve">3.9997501373291</t>
   </si>
   <si>
     <t xml:space="preserve">4.00759267807007</t>
@@ -2321,16 +2321,16 @@
     <t xml:space="preserve">3.96053695678711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03112077713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05464839935303</t>
+    <t xml:space="preserve">4.03112030029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05464887619019</t>
   </si>
   <si>
     <t xml:space="preserve">3.93700885772705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92132377624512</t>
+    <t xml:space="preserve">3.92132329940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.01543521881104</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">4.07033443450928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97622275352478</t>
+    <t xml:space="preserve">3.97622227668762</t>
   </si>
   <si>
     <t xml:space="preserve">4.1879734992981</t>
@@ -2357,10 +2357,10 @@
     <t xml:space="preserve">4.45462322235107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43109560012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42325258255005</t>
+    <t xml:space="preserve">4.43109607696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42325305938721</t>
   </si>
   <si>
     <t xml:space="preserve">4.38404035568237</t>
@@ -2417,10 +2417,10 @@
     <t xml:space="preserve">4.68206024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72911596298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64284706115723</t>
+    <t xml:space="preserve">4.72911643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64284658432007</t>
   </si>
   <si>
     <t xml:space="preserve">4.74480152130127</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">4.95655345916748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94871044158936</t>
+    <t xml:space="preserve">4.94871091842651</t>
   </si>
   <si>
     <t xml:space="preserve">4.97223854064941</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">4.87028360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98008060455322</t>
+    <t xml:space="preserve">4.98008108139038</t>
   </si>
   <si>
     <t xml:space="preserve">5.0741925239563</t>
@@ -2465,7 +2465,7 @@
     <t xml:space="preserve">5.02713680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08987808227539</t>
+    <t xml:space="preserve">5.08987760543823</t>
   </si>
   <si>
     <t xml:space="preserve">5.19183254241943</t>
@@ -2489,10 +2489,10 @@
     <t xml:space="preserve">5.21536064147949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1996750831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25457382202148</t>
+    <t xml:space="preserve">5.19967460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25457334518433</t>
   </si>
   <si>
     <t xml:space="preserve">5.30162954330444</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">4.93302488327026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7996997833252</t>
+    <t xml:space="preserve">4.79970026016235</t>
   </si>
   <si>
     <t xml:space="preserve">4.76048707962036</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">4.53305053710938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50952243804932</t>
+    <t xml:space="preserve">4.50952196121216</t>
   </si>
   <si>
     <t xml:space="preserve">4.47030830383301</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">4.54873561859131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57226324081421</t>
+    <t xml:space="preserve">4.57226371765137</t>
   </si>
   <si>
     <t xml:space="preserve">4.52520751953125</t>
@@ -2546,28 +2546,28 @@
     <t xml:space="preserve">4.54089260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51736450195312</t>
+    <t xml:space="preserve">4.51736497879028</t>
   </si>
   <si>
     <t xml:space="preserve">4.58010625839233</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82322788238525</t>
+    <t xml:space="preserve">4.8232274055481</t>
   </si>
   <si>
     <t xml:space="preserve">4.87812662124634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88596963882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7840142250061</t>
+    <t xml:space="preserve">4.8859691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78401470184326</t>
   </si>
   <si>
     <t xml:space="preserve">4.70558834075928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65853261947632</t>
+    <t xml:space="preserve">4.65853214263916</t>
   </si>
   <si>
     <t xml:space="preserve">4.77617216110229</t>
@@ -2585,10 +2585,10 @@
     <t xml:space="preserve">5.66239070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73297548294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89767074584961</t>
+    <t xml:space="preserve">5.73297500610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89767026901245</t>
   </si>
   <si>
     <t xml:space="preserve">5.68591928482056</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">4.7134313583374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41541051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89381122589111</t>
+    <t xml:space="preserve">4.4154109954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89381170272827</t>
   </si>
   <si>
     <t xml:space="preserve">4.81538534164429</t>
@@ -2663,22 +2663,22 @@
     <t xml:space="preserve">4.95325088500977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14312601089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07708215713501</t>
+    <t xml:space="preserve">5.14312553405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07708168029785</t>
   </si>
   <si>
     <t xml:space="preserve">5.11835956573486</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97801685333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06057167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9037184715271</t>
+    <t xml:space="preserve">4.97801733016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06057119369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90371799468994</t>
   </si>
   <si>
     <t xml:space="preserve">4.96976184844971</t>
@@ -2702,22 +2702,22 @@
     <t xml:space="preserve">4.56524658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48269176483154</t>
+    <t xml:space="preserve">4.4826922416687</t>
   </si>
   <si>
     <t xml:space="preserve">4.58175754547119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64780044555664</t>
+    <t xml:space="preserve">4.6478009223938</t>
   </si>
   <si>
     <t xml:space="preserve">4.61477947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57350206375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51571416854858</t>
+    <t xml:space="preserve">4.57350158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51571369171143</t>
   </si>
   <si>
     <t xml:space="preserve">4.3340950012207</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">4.16898632049561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26805114746094</t>
+    <t xml:space="preserve">4.2680516242981</t>
   </si>
   <si>
     <t xml:space="preserve">4.39188241958618</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">4.46618127822876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42490434646606</t>
+    <t xml:space="preserve">4.42490482330322</t>
   </si>
   <si>
     <t xml:space="preserve">4.3753719329834</t>
@@ -2753,19 +2753,19 @@
     <t xml:space="preserve">4.44967031478882</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34235048294067</t>
+    <t xml:space="preserve">4.34235000610352</t>
   </si>
   <si>
     <t xml:space="preserve">4.41664838790894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55699110031128</t>
+    <t xml:space="preserve">4.55699062347412</t>
   </si>
   <si>
     <t xml:space="preserve">4.67256689071655</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65605545043945</t>
+    <t xml:space="preserve">4.65605592727661</t>
   </si>
   <si>
     <t xml:space="preserve">4.71384382247925</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">4.72209930419922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75512075424194</t>
+    <t xml:space="preserve">4.7551212310791</t>
   </si>
   <si>
     <t xml:space="preserve">4.77988719940186</t>
@@ -2813,13 +2813,13 @@
     <t xml:space="preserve">4.60652303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66431140899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81290864944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88720750808716</t>
+    <t xml:space="preserve">4.66431188583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81290912628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88720703125</t>
   </si>
   <si>
     <t xml:space="preserve">4.93673992156982</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">5.19265794754028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22567939758301</t>
+    <t xml:space="preserve">5.22567987442017</t>
   </si>
   <si>
     <t xml:space="preserve">5.26695680618286</t>
@@ -2852,19 +2852,19 @@
     <t xml:space="preserve">5.29172277450562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30823421478271</t>
+    <t xml:space="preserve">5.30823373794556</t>
   </si>
   <si>
     <t xml:space="preserve">5.36602210998535</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4320650100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47334241867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55589628219604</t>
+    <t xml:space="preserve">5.43206548690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4733419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5558967590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.41555452346802</t>
@@ -2900,16 +2900,16 @@
     <t xml:space="preserve">5.54764080047607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68798351287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63019561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61368417739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5971736907959</t>
+    <t xml:space="preserve">5.68798303604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63019514083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61368465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59717416763306</t>
   </si>
   <si>
     <t xml:space="preserve">5.58066272735596</t>
@@ -2924,10 +2924,10 @@
     <t xml:space="preserve">5.82006978988647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84483623504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86134672164917</t>
+    <t xml:space="preserve">5.84483575820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86134624481201</t>
   </si>
   <si>
     <t xml:space="preserve">5.89436864852905</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">6.30713939666748</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38969373703003</t>
+    <t xml:space="preserve">6.38969421386719</t>
   </si>
   <si>
     <t xml:space="preserve">6.39794874191284</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">6.45573663711548</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59607887268066</t>
+    <t xml:space="preserve">6.59607839584351</t>
   </si>
   <si>
     <t xml:space="preserve">6.52178049087524</t>
@@ -2975,10 +2975,10 @@
     <t xml:space="preserve">6.57956838607788</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58782434463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51352453231812</t>
+    <t xml:space="preserve">6.58782386779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51352500915527</t>
   </si>
   <si>
     <t xml:space="preserve">6.56305742263794</t>
@@ -2987,10 +2987,10 @@
     <t xml:space="preserve">6.67863368988037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72816514968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67037773132324</t>
+    <t xml:space="preserve">6.72816562652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6703782081604</t>
   </si>
   <si>
     <t xml:space="preserve">6.63735628128052</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">6.73642110824585</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68688917160034</t>
+    <t xml:space="preserve">6.6868896484375</t>
   </si>
   <si>
     <t xml:space="preserve">6.53829145431519</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">6.62084579467773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64561176300049</t>
+    <t xml:space="preserve">6.64561128616333</t>
   </si>
   <si>
     <t xml:space="preserve">6.71991062164307</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">6.05122137069702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64670658111572</t>
+    <t xml:space="preserve">5.64670610427856</t>
   </si>
   <si>
     <t xml:space="preserve">5.85309171676636</t>
@@ -3041,16 +3041,16 @@
     <t xml:space="preserve">5.67972755432129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39904356002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38253211975098</t>
+    <t xml:space="preserve">5.39904403686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38253259658813</t>
   </si>
   <si>
     <t xml:space="preserve">5.66321659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60542917251587</t>
+    <t xml:space="preserve">5.60542964935303</t>
   </si>
   <si>
     <t xml:space="preserve">5.74577140808105</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">5.83658075332642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88611316680908</t>
+    <t xml:space="preserve">5.88611364364624</t>
   </si>
   <si>
     <t xml:space="preserve">5.79530382156372</t>
@@ -3077,10 +3077,10 @@
     <t xml:space="preserve">5.91913509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63845062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78704833984375</t>
+    <t xml:space="preserve">5.63845014572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78704881668091</t>
   </si>
   <si>
     <t xml:space="preserve">5.94390106201172</t>
@@ -4353,6 +4353,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.7600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.960000038147</t>
   </si>
 </sst>
 </file>
@@ -70497,7 +70500,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.691087963</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>104963</v>
@@ -70518,6 +70521,32 @@
         <v>1446</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6912152778</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>130421</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>14.7799997329712</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>14.8000001907349</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>14.960000038147</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="1454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="1453">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">CE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52814626693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46432209014893</t>
+    <t xml:space="preserve">4.52814483642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46432161331177</t>
   </si>
   <si>
     <t xml:space="preserve">4.30644035339355</t>
@@ -56,31 +56,31 @@
     <t xml:space="preserve">4.26613092422485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31315946578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31987762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3669056892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27284955978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23589849472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05114507675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08473682403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7421019077301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91677784919739</t>
+    <t xml:space="preserve">4.31315898895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31987714767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36690664291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27284908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23589897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05114459991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08473634719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74210262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91677856445312</t>
   </si>
   <si>
     <t xml:space="preserve">4.03099012374878</t>
@@ -92,73 +92,73 @@
     <t xml:space="preserve">4.12840557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01419401168823</t>
+    <t xml:space="preserve">4.01419353485107</t>
   </si>
   <si>
     <t xml:space="preserve">4.12504625320435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12168741226196</t>
+    <t xml:space="preserve">4.1216869354248</t>
   </si>
   <si>
     <t xml:space="preserve">3.9470112323761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80256700515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83615946769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86975002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58086252212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42970037460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75217962265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60773587226868</t>
+    <t xml:space="preserve">3.80256724357605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83615851402283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86975026130676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58086228370667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42970085144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75217986106873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60773611068726</t>
   </si>
   <si>
     <t xml:space="preserve">3.84959506988525</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9067018032074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96716642379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0645809173584</t>
+    <t xml:space="preserve">3.90670132637024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96716570854187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06458139419556</t>
   </si>
   <si>
     <t xml:space="preserve">3.8294403553009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77233481407166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90334177017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87982821464539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72866606712341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79584836959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88318729400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95708847045898</t>
+    <t xml:space="preserve">3.77233409881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9033420085907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87982773780823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72866582870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79584908485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88318681716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95708775520325</t>
   </si>
   <si>
     <t xml:space="preserve">4.13176536560059</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">4.1955885887146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18551206588745</t>
+    <t xml:space="preserve">4.18551111221313</t>
   </si>
   <si>
     <t xml:space="preserve">4.13848304748535</t>
@@ -176,31 +176,31 @@
     <t xml:space="preserve">4.22246170043945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29972314834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3568286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25605440139771</t>
+    <t xml:space="preserve">4.29972267150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35682821273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25605344772339</t>
   </si>
   <si>
     <t xml:space="preserve">4.27956771850586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14856052398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32659530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26948976516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16535568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09817218780518</t>
+    <t xml:space="preserve">4.14856100082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32659578323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26949071884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16535615921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09817266464233</t>
   </si>
   <si>
     <t xml:space="preserve">4.04778575897217</t>
@@ -209,40 +209,40 @@
     <t xml:space="preserve">4.04106760025024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93021535873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91006016731262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81936264038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75889825820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71187019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93357372283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82608151435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0813775062561</t>
+    <t xml:space="preserve">3.93021512031555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9100604057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81936287879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75889801979065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71186971664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93357467651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82608127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08137702941895</t>
   </si>
   <si>
     <t xml:space="preserve">4.15863800048828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17879295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21238374710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21574354171753</t>
+    <t xml:space="preserve">4.17879199981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21238470077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21574306488037</t>
   </si>
   <si>
     <t xml:space="preserve">4.28292655944824</t>
@@ -251,226 +251,226 @@
     <t xml:space="preserve">4.30308198928833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35346937179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19894790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07465887069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08809566497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06122207641602</t>
+    <t xml:space="preserve">4.3534688949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19894742965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07465934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08809518814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06122303009033</t>
   </si>
   <si>
     <t xml:space="preserve">4.0242714881897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93693423271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21648979187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14420747756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19927883148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25435209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23370027542114</t>
+    <t xml:space="preserve">3.93693375587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21648931503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14420700073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19927930831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25435161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23369979858398</t>
   </si>
   <si>
     <t xml:space="preserve">4.23714208602905</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49185228347778</t>
+    <t xml:space="preserve">4.49185180664062</t>
   </si>
   <si>
     <t xml:space="preserve">4.49873638153076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47120046615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45743227005005</t>
+    <t xml:space="preserve">4.47119951248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45743179321289</t>
   </si>
   <si>
     <t xml:space="preserve">4.46431589126587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37826538085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31975030899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3713812828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28188848495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42989587783813</t>
+    <t xml:space="preserve">4.37826490402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31974983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37138080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28188800811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42989540100098</t>
   </si>
   <si>
     <t xml:space="preserve">4.34040260314941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35072946548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25090932846069</t>
+    <t xml:space="preserve">4.35072898864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25091028213501</t>
   </si>
   <si>
     <t xml:space="preserve">4.03750371932983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91703271865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98243093490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884379386902</t>
+    <t xml:space="preserve">3.91703295707703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98243165016174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8688440322876</t>
   </si>
   <si>
     <t xml:space="preserve">4.13732290267944</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33696031570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38170719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42301177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52971458435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74148893356323</t>
+    <t xml:space="preserve">4.33696126937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38170671463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42301225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52971410751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74148941040039</t>
   </si>
   <si>
     <t xml:space="preserve">3.7518150806427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73116230964661</t>
+    <t xml:space="preserve">3.73116302490234</t>
   </si>
   <si>
     <t xml:space="preserve">3.84130811691284</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65199613571167</t>
+    <t xml:space="preserve">3.65199589729309</t>
   </si>
   <si>
     <t xml:space="preserve">3.52464127540588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42826461791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50743055343628</t>
+    <t xml:space="preserve">3.42826437950134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50743103027344</t>
   </si>
   <si>
     <t xml:space="preserve">3.65887999534607</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75525712966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82065606117249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78623509407043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96522068977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95145344734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0409460067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01340961456299</t>
+    <t xml:space="preserve">3.75525736808777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82065558433533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78623557090759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670657157898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96522116661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95145320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04094552993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01341009140015</t>
   </si>
   <si>
     <t xml:space="preserve">3.94456839561462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9893159866333</t>
+    <t xml:space="preserve">3.98931550979614</t>
   </si>
   <si>
     <t xml:space="preserve">3.9583375453949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79656100273132</t>
+    <t xml:space="preserve">3.79656195640564</t>
   </si>
   <si>
     <t xml:space="preserve">3.90326452255249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80000352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68641662597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70018458366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76558303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362758636475</t>
+    <t xml:space="preserve">3.80000329017639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6864161491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70018434524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7655827999115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362663269043</t>
   </si>
   <si>
     <t xml:space="preserve">3.66576457023621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6692066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5521764755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48677897453308</t>
+    <t xml:space="preserve">3.66920638084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55217790603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4867787361145</t>
   </si>
   <si>
     <t xml:space="preserve">3.47989439964294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37319183349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37181496620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50054717063904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68985843658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561971664429</t>
+    <t xml:space="preserve">3.37319159507751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37181448936462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50054669380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68985795974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561876296997</t>
   </si>
   <si>
     <t xml:space="preserve">3.45235848426819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47645282745361</t>
+    <t xml:space="preserve">3.47645258903503</t>
   </si>
   <si>
     <t xml:space="preserve">3.64511227607727</t>
@@ -479,109 +479,109 @@
     <t xml:space="preserve">3.72083711624146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7070689201355</t>
+    <t xml:space="preserve">3.70706939697266</t>
   </si>
   <si>
     <t xml:space="preserve">3.77935123443604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80688834190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61413359642029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757612228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57971334457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5659453868866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4936625957489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49022102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44891667366028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63822793960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49710440635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38696026802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35804677009583</t>
+    <t xml:space="preserve">3.80688810348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61413407325745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57971382141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56594562530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49366307258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49022054672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4489164352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63822770118713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49710488319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38695979118347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35804653167725</t>
   </si>
   <si>
     <t xml:space="preserve">3.37456846237183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31123495101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32638001441956</t>
+    <t xml:space="preserve">3.31123471260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32637977600098</t>
   </si>
   <si>
     <t xml:space="preserve">3.3552930355072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41587233543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51431488990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48333668708801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51087284088135</t>
+    <t xml:space="preserve">3.41587281227112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.514315366745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48333644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51087260246277</t>
   </si>
   <si>
     <t xml:space="preserve">3.51775717735291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47301054000854</t>
+    <t xml:space="preserve">3.47301077842712</t>
   </si>
   <si>
     <t xml:space="preserve">3.57627177238464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53496742248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64855408668518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67953181266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59692430496216</t>
+    <t xml:space="preserve">3.53496694564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6485538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67953252792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59692406654358</t>
   </si>
   <si>
     <t xml:space="preserve">3.64167022705078</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63134431838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56250333786011</t>
+    <t xml:space="preserve">3.63134407997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56250357627869</t>
   </si>
   <si>
     <t xml:space="preserve">3.53152513504028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4558002948761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41174244880676</t>
+    <t xml:space="preserve">3.45580053329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41174221038818</t>
   </si>
   <si>
     <t xml:space="preserve">3.42964124679565</t>
@@ -590,49 +590,49 @@
     <t xml:space="preserve">3.45924234390259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44203233718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52808308601379</t>
+    <t xml:space="preserve">3.44203209877014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52808356285095</t>
   </si>
   <si>
     <t xml:space="preserve">3.6347861289978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67609095573425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62790179252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58659791946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54529333114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55906128883362</t>
+    <t xml:space="preserve">3.67609000205994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6279022693634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58659696578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54529309272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55906105041504</t>
   </si>
   <si>
     <t xml:space="preserve">3.56938767433167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71739530563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94112658500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00996732711792</t>
+    <t xml:space="preserve">3.71739506721497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94112682342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00996685028076</t>
   </si>
   <si>
     <t xml:space="preserve">3.8860547542572</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97210550308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83442354202271</t>
+    <t xml:space="preserve">3.97210502624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83442378044128</t>
   </si>
   <si>
     <t xml:space="preserve">3.92735910415649</t>
@@ -641,34 +641,34 @@
     <t xml:space="preserve">3.98587369918823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05471420288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93080139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04438829421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06159782409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91014814376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.899822473526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05815553665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07192420959473</t>
+    <t xml:space="preserve">4.05471324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93080115318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04438781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06159830093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91014838218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89982271194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05815649032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07192468643188</t>
   </si>
   <si>
     <t xml:space="preserve">4.07880830764771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0306191444397</t>
+    <t xml:space="preserve">4.03062009811401</t>
   </si>
   <si>
     <t xml:space="preserve">4.19583749771118</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">4.1269965171814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13043928146362</t>
+    <t xml:space="preserve">4.13043880462646</t>
   </si>
   <si>
     <t xml:space="preserve">4.20272159576416</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.10634422302246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12011289596558</t>
+    <t xml:space="preserve">4.12011241912842</t>
   </si>
   <si>
     <t xml:space="preserve">4.17862701416016</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">4.16141700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04783010482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14076566696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1510910987854</t>
+    <t xml:space="preserve">4.04782962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14076471328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15109062194824</t>
   </si>
   <si>
     <t xml:space="preserve">4.15453290939331</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.18206930160522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15797472000122</t>
+    <t xml:space="preserve">4.15797567367554</t>
   </si>
   <si>
     <t xml:space="preserve">4.21304750442505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32319211959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449718475342</t>
+    <t xml:space="preserve">4.32319259643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449670791626</t>
   </si>
   <si>
     <t xml:space="preserve">4.43333721160889</t>
@@ -749,94 +749,94 @@
     <t xml:space="preserve">4.44022130966187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3851490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47464179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41956996917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37482309341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41268491744995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34384393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30942440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36793947219849</t>
+    <t xml:space="preserve">4.38514947891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47464275360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41956949234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37482357025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41268587112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34384489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30942487716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36793899536133</t>
   </si>
   <si>
     <t xml:space="preserve">4.35417127609253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28533029556274</t>
+    <t xml:space="preserve">4.28532981872559</t>
   </si>
   <si>
     <t xml:space="preserve">4.52627229690552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40580177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48840951919556</t>
+    <t xml:space="preserve">4.40580129623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48841047286987</t>
   </si>
   <si>
     <t xml:space="preserve">4.50906276702881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53659868240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54348230361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44710540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67083787918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69899654388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8010721206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71659564971924</t>
+    <t xml:space="preserve">4.53659820556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54348278045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.447105884552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67083740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69899702072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80107259750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7165961265564</t>
   </si>
   <si>
     <t xml:space="preserve">4.83627080917358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8609094619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85035037994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87850856781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7834734916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72011613845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68491697311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7306752204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75179386138916</t>
+    <t xml:space="preserve">4.86090993881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85034942626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87850904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78347301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72011566162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68491744995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73067474365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75179433822632</t>
   </si>
   <si>
     <t xml:space="preserve">4.81515169143677</t>
@@ -845,22 +845,22 @@
     <t xml:space="preserve">4.81163215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9277868270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93834638595581</t>
+    <t xml:space="preserve">4.92778635025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93834686279297</t>
   </si>
   <si>
     <t xml:space="preserve">4.87498903274536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80811214447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8045916557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78699350357056</t>
+    <t xml:space="preserve">4.80811166763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80459213256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7869930267334</t>
   </si>
   <si>
     <t xml:space="preserve">4.95946550369263</t>
@@ -869,31 +869,31 @@
     <t xml:space="preserve">4.86442947387695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89258861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89610862731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91370677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97354459762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97706460952759</t>
+    <t xml:space="preserve">4.89258766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89610815048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91370725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97354507446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97706508636475</t>
   </si>
   <si>
     <t xml:space="preserve">4.94538640975952</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11081886291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2586522102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0615406036377</t>
+    <t xml:space="preserve">5.1108193397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25865268707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06154108047485</t>
   </si>
   <si>
     <t xml:space="preserve">5.08617973327637</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">5.0509819984436</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08969974517822</t>
+    <t xml:space="preserve">5.08970022201538</t>
   </si>
   <si>
     <t xml:space="preserve">5.01930284500122</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">5.04746150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96650505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91018724441528</t>
+    <t xml:space="preserve">4.96650457382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91018772125244</t>
   </si>
   <si>
     <t xml:space="preserve">5.00874328613281</t>
@@ -932,25 +932,25 @@
     <t xml:space="preserve">5.06858062744141</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1319375038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04042196273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12489891052246</t>
+    <t xml:space="preserve">5.13193798065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0404224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1248984336853</t>
   </si>
   <si>
     <t xml:space="preserve">5.20937442779541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36424732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21289443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03690242767334</t>
+    <t xml:space="preserve">5.36424827575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21289491653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03690195083618</t>
   </si>
   <si>
     <t xml:space="preserve">5.16361665725708</t>
@@ -968,31 +968,31 @@
     <t xml:space="preserve">5.20233488082886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11433887481689</t>
+    <t xml:space="preserve">5.11433839797974</t>
   </si>
   <si>
     <t xml:space="preserve">5.10729885101318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00522422790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9981837272644</t>
+    <t xml:space="preserve">5.00522375106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99818325042725</t>
   </si>
   <si>
     <t xml:space="preserve">5.01226282119751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04394197463989</t>
+    <t xml:space="preserve">5.04394149780273</t>
   </si>
   <si>
     <t xml:space="preserve">5.06506109237671</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15657663345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34312963485718</t>
+    <t xml:space="preserve">5.15657711029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34312868118286</t>
   </si>
   <si>
     <t xml:space="preserve">5.30089092254639</t>
@@ -1010,31 +1010,31 @@
     <t xml:space="preserve">5.29385042190552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29033088684082</t>
+    <t xml:space="preserve">5.29033136367798</t>
   </si>
   <si>
     <t xml:space="preserve">5.33608913421631</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34664869308472</t>
+    <t xml:space="preserve">5.34664821624756</t>
   </si>
   <si>
     <t xml:space="preserve">5.36776781082153</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35368824005127</t>
+    <t xml:space="preserve">5.35368776321411</t>
   </si>
   <si>
     <t xml:space="preserve">5.38536691665649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3994460105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26569223403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31145000457764</t>
+    <t xml:space="preserve">5.39944648742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26569175720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31145048141479</t>
   </si>
   <si>
     <t xml:space="preserve">5.3255295753479</t>
@@ -1043,40 +1043,40 @@
     <t xml:space="preserve">5.28329133987427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23401403427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21641397476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14249706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16713714599609</t>
+    <t xml:space="preserve">5.23401355743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2164134979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14249753952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16713666915894</t>
   </si>
   <si>
     <t xml:space="preserve">5.31497001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29737138748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19177579879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35720825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07210063934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98410415649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94186639785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86794900894165</t>
+    <t xml:space="preserve">5.29737091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19177484512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35720872879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0721001625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9841046333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94186592102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86794948577881</t>
   </si>
   <si>
     <t xml:space="preserve">4.92426681518555</t>
@@ -1088,16 +1088,16 @@
     <t xml:space="preserve">5.03338193893433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05450105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18473529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17417573928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21993398666382</t>
+    <t xml:space="preserve">5.05450057983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1847357749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17417526245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21993446350098</t>
   </si>
   <si>
     <t xml:space="preserve">5.17769622802734</t>
@@ -1106,19 +1106,19 @@
     <t xml:space="preserve">5.22697401046753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28681182861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02282238006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00170373916626</t>
+    <t xml:space="preserve">5.28681135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02282333374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0017032623291</t>
   </si>
   <si>
     <t xml:space="preserve">5.02986192703247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05802154541016</t>
+    <t xml:space="preserve">5.058021068573</t>
   </si>
   <si>
     <t xml:space="preserve">4.92074632644653</t>
@@ -1130,37 +1130,37 @@
     <t xml:space="preserve">5.37128782272339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47688293457031</t>
+    <t xml:space="preserve">5.47688341140747</t>
   </si>
   <si>
     <t xml:space="preserve">5.48392295837402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44168472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43464469909668</t>
+    <t xml:space="preserve">5.44168424606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43464517593384</t>
   </si>
   <si>
     <t xml:space="preserve">5.5261607170105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51208114624023</t>
+    <t xml:space="preserve">5.51208162307739</t>
   </si>
   <si>
     <t xml:space="preserve">5.46984338760376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40648603439331</t>
+    <t xml:space="preserve">5.40648651123047</t>
   </si>
   <si>
     <t xml:space="preserve">5.37832736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18825578689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13897800445557</t>
+    <t xml:space="preserve">5.18825483322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13897752761841</t>
   </si>
   <si>
     <t xml:space="preserve">5.32905006408691</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">5.1952953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24457263946533</t>
+    <t xml:space="preserve">5.24457359313965</t>
   </si>
   <si>
     <t xml:space="preserve">5.22345447540283</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">5.11785888671875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97002458572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21899938583374</t>
+    <t xml:space="preserve">4.97002506256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2189998626709</t>
   </si>
   <si>
     <t xml:space="preserve">5.14661455154419</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">4.98012733459473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94393491744995</t>
+    <t xml:space="preserve">4.94393396377563</t>
   </si>
   <si>
     <t xml:space="preserve">4.81364011764526</t>
@@ -1208,16 +1208,16 @@
     <t xml:space="preserve">4.84259510040283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85707139968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82087898254395</t>
+    <t xml:space="preserve">4.85707235336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8208794593811</t>
   </si>
   <si>
     <t xml:space="preserve">4.80640172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56029081344604</t>
+    <t xml:space="preserve">4.5602912902832</t>
   </si>
   <si>
     <t xml:space="preserve">4.46618986129761</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">4.21284055709839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45171308517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37208795547485</t>
+    <t xml:space="preserve">4.4517126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37208843231201</t>
   </si>
   <si>
     <t xml:space="preserve">4.52409791946411</t>
@@ -1238,19 +1238,19 @@
     <t xml:space="preserve">4.40828132629395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34313440322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29246377944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39380407333374</t>
+    <t xml:space="preserve">4.34313488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29246473312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39380359649658</t>
   </si>
   <si>
     <t xml:space="preserve">4.45895099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4372353553772</t>
+    <t xml:space="preserve">4.43723583221436</t>
   </si>
   <si>
     <t xml:space="preserve">4.53133678436279</t>
@@ -1259,79 +1259,79 @@
     <t xml:space="preserve">4.61096096038818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64715433120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69058465957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57476806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58200597763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48790502548218</t>
+    <t xml:space="preserve">4.64715337753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69058513641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57476854324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58200645446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48790550231934</t>
   </si>
   <si>
     <t xml:space="preserve">4.545814037323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58924531936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60372257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68334579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6978235244751</t>
+    <t xml:space="preserve">4.5892448425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6037220954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68334674835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69782304763794</t>
   </si>
   <si>
     <t xml:space="preserve">4.62543773651123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63267660140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61819982528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56752872467041</t>
+    <t xml:space="preserve">4.63267707824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61819934844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56752967834473</t>
   </si>
   <si>
     <t xml:space="preserve">4.44447422027588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42999649047852</t>
+    <t xml:space="preserve">4.42999696731567</t>
   </si>
   <si>
     <t xml:space="preserve">4.59648370742798</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47342824935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51685905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50962162017822</t>
+    <t xml:space="preserve">4.47342777252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51685953140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50962018966675</t>
   </si>
   <si>
     <t xml:space="preserve">4.1766471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10426139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04635334014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02463722229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03187608718872</t>
+    <t xml:space="preserve">4.10426187515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04635381698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0246376991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03187656402588</t>
   </si>
   <si>
     <t xml:space="preserve">4.05359172821045</t>
@@ -1340,28 +1340,28 @@
     <t xml:space="preserve">4.06806898117065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97396779060364</t>
+    <t xml:space="preserve">3.97396731376648</t>
   </si>
   <si>
     <t xml:space="preserve">4.00292253494263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85091304779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87262773513794</t>
+    <t xml:space="preserve">3.85091209411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87262797355652</t>
   </si>
   <si>
     <t xml:space="preserve">3.93053650856018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9232976436615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11149978637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22731637954712</t>
+    <t xml:space="preserve">3.92329812049866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11150026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22731733322144</t>
   </si>
   <si>
     <t xml:space="preserve">4.20560169219971</t>
@@ -1382,133 +1382,133 @@
     <t xml:space="preserve">4.2997031211853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36485004425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35761165618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26351022720337</t>
+    <t xml:space="preserve">4.36484956741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35761117935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26350975036621</t>
   </si>
   <si>
     <t xml:space="preserve">4.09702348709106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06083059310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12597751617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90882062911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84367370605469</t>
+    <t xml:space="preserve">4.06083106994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12597703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90882110595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84367322921753</t>
   </si>
   <si>
     <t xml:space="preserve">3.7857654094696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87986612319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94501328468323</t>
+    <t xml:space="preserve">3.87986588478088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94501352310181</t>
   </si>
   <si>
     <t xml:space="preserve">3.80748128890991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72061824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68442559242249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57946634292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45641136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55051279067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81471967697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7640495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8291962146759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83643531799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85815095901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74233412742615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75681138038635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70614123344421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67718648910522</t>
+    <t xml:space="preserve">3.72061848640442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68442583084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5794665813446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4564106464386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55051207542419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81471943855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76404976844788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82919669151306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83643555641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85815143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74233341217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75681114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70614099502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67718696594238</t>
   </si>
   <si>
     <t xml:space="preserve">3.63375568389893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66994881629944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6192786693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64099431037903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77128863334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80024194717407</t>
+    <t xml:space="preserve">3.66994833946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61927843093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64099502563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7712881565094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80024290084839</t>
   </si>
   <si>
     <t xml:space="preserve">3.66270995140076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72785711288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86538982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60480189323425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58670496940613</t>
+    <t xml:space="preserve">3.72785663604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86538910865784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60480141639709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58670473098755</t>
   </si>
   <si>
     <t xml:space="preserve">3.57584691047668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54327321052551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547108650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82195806503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71337985992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69890332221985</t>
+    <t xml:space="preserve">3.54327368736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547132492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82195830345154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71337962150574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69890284538269</t>
   </si>
   <si>
     <t xml:space="preserve">3.69166398048401</t>
@@ -1517,43 +1517,43 @@
     <t xml:space="preserve">3.6265172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64823293685913</t>
+    <t xml:space="preserve">3.64823269844055</t>
   </si>
   <si>
     <t xml:space="preserve">3.5251772403717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60118198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54689311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5034613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60842084884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79300379753113</t>
+    <t xml:space="preserve">3.60118246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54689335823059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50346183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60842061042786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79300403594971</t>
   </si>
   <si>
     <t xml:space="preserve">3.88710498809814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56498956680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59394359588623</t>
+    <t xml:space="preserve">3.5649893283844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59394383430481</t>
   </si>
   <si>
     <t xml:space="preserve">3.77852654457092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58308506011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53965377807617</t>
+    <t xml:space="preserve">3.58308553695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53965401649475</t>
   </si>
   <si>
     <t xml:space="preserve">3.48174571990967</t>
@@ -1562,28 +1562,28 @@
     <t xml:space="preserve">3.49622297286987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45279169082642</t>
+    <t xml:space="preserve">3.452791929245</t>
   </si>
   <si>
     <t xml:space="preserve">3.42021775245667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.431556224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43533539772034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41265940666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33329558372498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841275215149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38620519638062</t>
+    <t xml:space="preserve">3.43155550956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43533515930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41265988349915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3332953453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38620495796204</t>
   </si>
   <si>
     <t xml:space="preserve">3.3710880279541</t>
@@ -1592,37 +1592,37 @@
     <t xml:space="preserve">3.36352944374084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38242554664612</t>
+    <t xml:space="preserve">3.38242602348328</t>
   </si>
   <si>
     <t xml:space="preserve">3.31062006950378</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32573699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29172396659851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393104553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31439924240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33707475662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27660703659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28038644790649</t>
+    <t xml:space="preserve">3.3257372379303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29172372817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393152236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3143994808197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33707499504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.276606798172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28038620948792</t>
   </si>
   <si>
     <t xml:space="preserve">3.23503541946411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20480132102966</t>
+    <t xml:space="preserve">3.20480108261108</t>
   </si>
   <si>
     <t xml:space="preserve">3.21613883972168</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">3.23125600814819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21235966682434</t>
+    <t xml:space="preserve">3.21235942840576</t>
   </si>
   <si>
     <t xml:space="preserve">3.24259352684021</t>
@@ -1652,43 +1652,43 @@
     <t xml:space="preserve">3.20102214813232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25015258789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39376354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59784293174744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65831065177917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55627107620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55249214172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56760883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57516741752625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60540127754211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53359580039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4769070148468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59028458595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58272504806519</t>
+    <t xml:space="preserve">3.25015211105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39376330375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59784245491028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65831089019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55627083778381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5524914264679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56760859489441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57516765594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60540175437927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53359627723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47690677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59028434753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58272576332092</t>
   </si>
   <si>
     <t xml:space="preserve">3.57138776779175</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">3.52603721618652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50336194038391</t>
+    <t xml:space="preserve">3.50336217880249</t>
   </si>
   <si>
     <t xml:space="preserve">3.43911457061768</t>
@@ -1706,121 +1706,121 @@
     <t xml:space="preserve">3.42777681350708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42021799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40132212638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3673083782196</t>
+    <t xml:space="preserve">3.42021870613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40132188796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36730861663818</t>
   </si>
   <si>
     <t xml:space="preserve">3.40888071060181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34085392951965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42399716377258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51469969749451</t>
+    <t xml:space="preserve">3.34085416793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42399787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51469922065735</t>
   </si>
   <si>
     <t xml:space="preserve">3.49958229064941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54871296882629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63941431045532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65453147888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68098616600037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67342829704285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73011660575867</t>
+    <t xml:space="preserve">3.54871273040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6394145488739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65453171730042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68098640441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67342758178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73011636734009</t>
   </si>
   <si>
     <t xml:space="preserve">3.78680539131165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92285847663879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86239075660706</t>
+    <t xml:space="preserve">3.92285799980164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86239004135132</t>
   </si>
   <si>
     <t xml:space="preserve">3.7452335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76790904998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83971405029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83215665817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77168774604797</t>
+    <t xml:space="preserve">3.76790881156921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83971476554871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83215594291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77168798446655</t>
   </si>
   <si>
     <t xml:space="preserve">3.73767495155334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69232416152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70366191864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77924680709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68854475021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66586947441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69610261917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66964864730835</t>
+    <t xml:space="preserve">3.6923246383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70366215705872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77924633026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68854522705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66586923599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6961030960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66964793205261</t>
   </si>
   <si>
     <t xml:space="preserve">3.73389554023743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81703901290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84727311134338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90018177032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98332619667053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96065044403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95309209823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93041634559631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94553327560425</t>
+    <t xml:space="preserve">3.81703948974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84727334976196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90018272399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98332595825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96065068244934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9530918598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93041610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94553351402283</t>
   </si>
   <si>
     <t xml:space="preserve">3.99088454246521</t>
@@ -1829,31 +1829,31 @@
     <t xml:space="preserve">3.91529965400696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02111911773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09670305252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03623580932617</t>
+    <t xml:space="preserve">4.02111864089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09670352935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03623533248901</t>
   </si>
   <si>
     <t xml:space="preserve">4.0664701461792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0815863609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13449573516846</t>
+    <t xml:space="preserve">4.08158683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1344952583313</t>
   </si>
   <si>
     <t xml:space="preserve">4.05135202407837</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02867698669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00600147247314</t>
+    <t xml:space="preserve">4.02867746353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0060019493103</t>
   </si>
   <si>
     <t xml:space="preserve">4.04379367828369</t>
@@ -1865,61 +1865,61 @@
     <t xml:space="preserve">4.01355981826782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96820855140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93797540664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97576785087585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90774130821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89262437820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88506555557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87750720977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85483145713806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80192232131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59406399726868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6016218662262</t>
+    <t xml:space="preserve">3.9682092666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93797492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97576761245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90774083137512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89262390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88506603240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87750744819641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85483121871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80192255973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5940637588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60162234306335</t>
   </si>
   <si>
     <t xml:space="preserve">3.6507523059845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71877908706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99844264984131</t>
+    <t xml:space="preserve">3.71877884864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99844288825989</t>
   </si>
   <si>
     <t xml:space="preserve">3.72255825996399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63185572624207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46556901931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44667291641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2841649055481</t>
+    <t xml:space="preserve">3.63185620307922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46556925773621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44667315483093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28416514396667</t>
   </si>
   <si>
     <t xml:space="preserve">3.11031985282898</t>
@@ -1955,31 +1955,31 @@
     <t xml:space="preserve">2.91001987457275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96292948722839</t>
+    <t xml:space="preserve">2.96292972564697</t>
   </si>
   <si>
     <t xml:space="preserve">2.85333132743835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89490294456482</t>
+    <t xml:space="preserve">2.89490270614624</t>
   </si>
   <si>
     <t xml:space="preserve">2.88734459877014</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92135787010193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85711050033569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90246152877808</t>
+    <t xml:space="preserve">2.92135739326477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85711026191711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90246176719666</t>
   </si>
   <si>
     <t xml:space="preserve">2.82687664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89112377166748</t>
+    <t xml:space="preserve">2.8911235332489</t>
   </si>
   <si>
     <t xml:space="preserve">2.9969425201416</t>
@@ -1988,22 +1988,22 @@
     <t xml:space="preserve">2.95159149169922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97804641723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99316334724426</t>
+    <t xml:space="preserve">2.97804665565491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99316358566284</t>
   </si>
   <si>
     <t xml:space="preserve">3.05363130569458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03473472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02717638015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12165784835815</t>
+    <t xml:space="preserve">3.03473520278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02717685699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12165808677673</t>
   </si>
   <si>
     <t xml:space="preserve">3.06119012832642</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">3.09898233413696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16700887680054</t>
+    <t xml:space="preserve">3.16700863838196</t>
   </si>
   <si>
     <t xml:space="preserve">3.14433312416077</t>
@@ -2021,28 +2021,28 @@
     <t xml:space="preserve">3.19346332550049</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21991872787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26904797554016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32195830345154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15945029258728</t>
+    <t xml:space="preserve">3.21991848945618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26904821395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32195806503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1594500541687</t>
   </si>
   <si>
     <t xml:space="preserve">3.07252764701843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06874847412109</t>
+    <t xml:space="preserve">3.06874823570251</t>
   </si>
   <si>
     <t xml:space="preserve">3.10654091835022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16322922706604</t>
+    <t xml:space="preserve">3.16322946548462</t>
   </si>
   <si>
     <t xml:space="preserve">3.27282738685608</t>
@@ -2051,67 +2051,67 @@
     <t xml:space="preserve">3.28794455528259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40510153770447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51092004776001</t>
+    <t xml:space="preserve">3.40510129928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51091980934143</t>
   </si>
   <si>
     <t xml:space="preserve">3.48824453353882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45801043510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29550290107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34463334083557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29928207397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30684113502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30306148529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26149010658264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37864637374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37486743927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26526951789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39754271507263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48068642616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38998436927795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31817865371704</t>
+    <t xml:space="preserve">3.45801067352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29550337791443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34463357925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29928231239319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30684089660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30306172370911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26149034500122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37864685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37486720085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26526927947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39754247665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48068618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38998413085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31817817687988</t>
   </si>
   <si>
     <t xml:space="preserve">3.25771069526672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22747659683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18590497970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24637317657471</t>
+    <t xml:space="preserve">3.22747683525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18590545654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24637293815613</t>
   </si>
   <si>
     <t xml:space="preserve">3.17456698417664</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">3.17834639549255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09142374992371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08008599281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04607319831848</t>
+    <t xml:space="preserve">3.09142422676086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08008575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0460729598999</t>
   </si>
   <si>
     <t xml:space="preserve">3.01583886146545</t>
@@ -2138,94 +2138,94 @@
     <t xml:space="preserve">2.9402539730072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95537090301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92513704299927</t>
+    <t xml:space="preserve">2.95537066459656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92513680458069</t>
   </si>
   <si>
     <t xml:space="preserve">2.8835654258728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80042147636414</t>
+    <t xml:space="preserve">2.80042171478271</t>
   </si>
   <si>
     <t xml:space="preserve">2.7890841960907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77018761634827</t>
+    <t xml:space="preserve">2.77018785476685</t>
   </si>
   <si>
     <t xml:space="preserve">2.75129175186157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71727824211121</t>
+    <t xml:space="preserve">2.71727848052979</t>
   </si>
   <si>
     <t xml:space="preserve">2.72105741500854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67948579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55477094650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44895172119141</t>
+    <t xml:space="preserve">2.67948603630066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55477070808411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44895195960999</t>
   </si>
   <si>
     <t xml:space="preserve">2.55099153518677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61523866653442</t>
+    <t xml:space="preserve">2.615238904953</t>
   </si>
   <si>
     <t xml:space="preserve">2.69838190078735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98938417434692</t>
+    <t xml:space="preserve">2.98938393592834</t>
   </si>
   <si>
     <t xml:space="preserve">3.53737473487854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62807726860046</t>
+    <t xml:space="preserve">3.62807679176331</t>
   </si>
   <si>
     <t xml:space="preserve">3.63563513755798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57894659042358</t>
+    <t xml:space="preserve">3.57894706726074</t>
   </si>
   <si>
     <t xml:space="preserve">3.56383013725281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50714111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48446536064148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52225828170776</t>
+    <t xml:space="preserve">3.50714087486267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48446559906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52225780487061</t>
   </si>
   <si>
     <t xml:space="preserve">3.41643881797791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12543749809265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80948090553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76035022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64319396018982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68476533889771</t>
+    <t xml:space="preserve">3.12543725967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80948066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76035070419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6431941986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68476581573486</t>
   </si>
   <si>
     <t xml:space="preserve">3.74901270866394</t>
@@ -2234,37 +2234,37 @@
     <t xml:space="preserve">3.79436373710632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75657081604004</t>
+    <t xml:space="preserve">3.75657153129578</t>
   </si>
   <si>
     <t xml:space="preserve">3.77546763420105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76413011550903</t>
+    <t xml:space="preserve">3.76412987709045</t>
   </si>
   <si>
     <t xml:space="preserve">4.15717124938965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11182022094727</t>
+    <t xml:space="preserve">4.11182069778442</t>
   </si>
   <si>
     <t xml:space="preserve">4.172287940979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31345558166504</t>
+    <t xml:space="preserve">4.3134560585022</t>
   </si>
   <si>
     <t xml:space="preserve">4.22718667984009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1252326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07817649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08601951599121</t>
+    <t xml:space="preserve">4.12523221969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07817602157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08601903915405</t>
   </si>
   <si>
     <t xml:space="preserve">4.09386157989502</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">4.25855731964111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36835432052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32914113998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34482669830322</t>
+    <t xml:space="preserve">4.36835479736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32914066314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34482622146606</t>
   </si>
   <si>
     <t xml:space="preserve">4.35266971588135</t>
@@ -2312,25 +2312,25 @@
     <t xml:space="preserve">4.02327823638916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99974989891052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00759315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96053671836853</t>
+    <t xml:space="preserve">3.99974942207336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00759267807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96053695678711</t>
   </si>
   <si>
     <t xml:space="preserve">4.03112077713013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05464887619019</t>
+    <t xml:space="preserve">4.05464839935303</t>
   </si>
   <si>
     <t xml:space="preserve">3.93700885772705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92132377624512</t>
+    <t xml:space="preserve">3.92132329940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.01543521881104</t>
@@ -2339,409 +2339,409 @@
     <t xml:space="preserve">4.07033395767212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9762225151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18797397613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24287223815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21150159835815</t>
+    <t xml:space="preserve">3.97622203826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1879734992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24287176132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.211501121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39188194274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45462322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43109607696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42325305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38404035568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39972543716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33698415756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36051177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4624662399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44678115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4389386177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47815132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48599433898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50167989730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5644211769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60363388061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62716197967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63500452041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49383640289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59579133987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66637516021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68206024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72911643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64284706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74480104446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86244106292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90949726104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05850744247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03497982025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99576663970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95655345916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94871044158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97223806381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87028408050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98008108139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07419204711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05066442489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02713680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08987760543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19183206558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18399000167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16830444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10556364059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14477682113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23888778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21536064147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19967555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25457334518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30162954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01929473876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93302488327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7996997833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7604866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76832962036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68990325927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69774580001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61147594451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53305006027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50952196121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47030878067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55657815933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54873561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57226324081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52520704269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54089260101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51736497879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58010625839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82322835922241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87812662124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8859691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78401470184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558881759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65853214263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77617263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85459852218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94086790084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52122354507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6623911857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73297452926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89767074584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68591928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70160484313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59964990615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53690910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52906656265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17614698410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29378652572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7134313583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41541051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89381170272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81538581848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9251823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84675550460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72127342224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5879487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61931943893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70558834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77163171768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73861026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69733333587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63954448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7963981628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98627281188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95325136184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14312505722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07708263397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11835908889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97801733016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06057119369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9037184715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96976184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87069702148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82942008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62303400039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40839338302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50745820999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56524658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58175754547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64779996871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61477899551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57350158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51571321487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3340950012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30932807922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38362693786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16898632049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26805114746094</t>
   </si>
   <si>
     <t xml:space="preserve">4.39188241958618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45462369918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43109560012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42325305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38403987884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39972543716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33698463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.360511302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4624662399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44678068161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4389386177063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47815132141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48599433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50167989730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56442070007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60363388061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62716197967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63500452041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49383640289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59579133987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66637516021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68205976486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72911643981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64284753799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74480152130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86244106292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90949726104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05850696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03498029708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99576616287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95655345916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9487099647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97223854064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87028408050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98008108139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07419204711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05066442489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02713632583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08987808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19183254241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18398952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16830492019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10556364059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14477634429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23888826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21536016464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19967555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25457382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3016300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01929473876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93302536010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7996997833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76048707962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76832962036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68990325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69774532318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61147689819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53305006027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50952243804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47030878067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55657815933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54873561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57226324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52520751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54089307785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51736450195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58010530471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82322835922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87812662124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88596963882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78401374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70558881759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65853261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77617263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85459852218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94086742401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52122354507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6623911857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73297548294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89767074584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68591928482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70160484313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59964990615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5369086265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52906656265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17614698410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29378700256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7134313583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41541004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89381122589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81538534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92518281936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84675598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72127389907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5879487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61931943893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70558834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77163171768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73861026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69733285903931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63954496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7963981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98627233505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95325136184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14312601089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07708215713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11835908889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97801685333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06057167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9037184715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96976232528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87069702148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82941961288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62303447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40839385986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50745820999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56524705886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58175754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64779996871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61477899551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57350206375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51571369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33409452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30932807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38362693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16898632049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2680516242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39188289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46618127822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42490434646606</t>
+    <t xml:space="preserve">4.4661808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42490386962891</t>
   </si>
   <si>
     <t xml:space="preserve">4.3753719329834</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">4.34235000610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41664838790894</t>
+    <t xml:space="preserve">4.41664886474609</t>
   </si>
   <si>
     <t xml:space="preserve">4.55699062347412</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">4.76337623596191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85418605804443</t>
+    <t xml:space="preserve">4.85418558120728</t>
   </si>
   <si>
     <t xml:space="preserve">4.8624415397644</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">4.77988719940186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73035478591919</t>
+    <t xml:space="preserve">4.73035430908203</t>
   </si>
   <si>
     <t xml:space="preserve">4.82116413116455</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">4.92022943496704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94499492645264</t>
+    <t xml:space="preserve">4.94499540328979</t>
   </si>
   <si>
     <t xml:space="preserve">4.83767509460449</t>
@@ -2825,10 +2825,10 @@
     <t xml:space="preserve">4.88720750808716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93673992156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01103925704956</t>
+    <t xml:space="preserve">4.93674039840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0110387802124</t>
   </si>
   <si>
     <t xml:space="preserve">5.11010408401489</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">5.16789197921753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23393535614014</t>
+    <t xml:space="preserve">5.23393487930298</t>
   </si>
   <si>
     <t xml:space="preserve">5.19265794754028</t>
@@ -2846,25 +2846,25 @@
     <t xml:space="preserve">5.22567939758301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26695728302002</t>
+    <t xml:space="preserve">5.26695680618286</t>
   </si>
   <si>
     <t xml:space="preserve">5.27521181106567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29172277450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30823421478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36602210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4320650100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47334241867065</t>
+    <t xml:space="preserve">5.29172325134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30823373794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36602258682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43206548690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47334289550781</t>
   </si>
   <si>
     <t xml:space="preserve">5.55589628219604</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">5.52287483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51461935043335</t>
+    <t xml:space="preserve">5.51461887359619</t>
   </si>
   <si>
     <t xml:space="preserve">5.58891820907593</t>
@@ -2903,28 +2903,28 @@
     <t xml:space="preserve">5.54764080047607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68798303604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63019514083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61368417739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59717321395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58066320419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65496158599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77879285812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82006978988647</t>
+    <t xml:space="preserve">5.6879825592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63019561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61368465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5971736907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58066272735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65496110916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77879238128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82007026672363</t>
   </si>
   <si>
     <t xml:space="preserve">5.84483623504639</t>
@@ -2933,19 +2933,19 @@
     <t xml:space="preserve">5.86134672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89436817169189</t>
+    <t xml:space="preserve">5.89436864852905</t>
   </si>
   <si>
     <t xml:space="preserve">5.8118143081665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90262413024902</t>
+    <t xml:space="preserve">5.90262365341187</t>
   </si>
   <si>
     <t xml:space="preserve">5.80355930328369</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73751592636108</t>
+    <t xml:space="preserve">5.73751544952393</t>
   </si>
   <si>
     <t xml:space="preserve">6.00168943405151</t>
@@ -2957,16 +2957,16 @@
     <t xml:space="preserve">6.38969373703003</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39794874191284</t>
+    <t xml:space="preserve">6.39794921875</t>
   </si>
   <si>
     <t xml:space="preserve">6.47224807739258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43922662734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45573663711548</t>
+    <t xml:space="preserve">6.4392261505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45573711395264</t>
   </si>
   <si>
     <t xml:space="preserve">6.59607887268066</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">6.52178049087524</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57956838607788</t>
+    <t xml:space="preserve">6.57956790924072</t>
   </si>
   <si>
     <t xml:space="preserve">6.58782386779785</t>
@@ -2987,34 +2987,34 @@
     <t xml:space="preserve">6.56305742263794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67863321304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72816562652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67037773132324</t>
+    <t xml:space="preserve">6.67863368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72816514968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6703782081604</t>
   </si>
   <si>
     <t xml:space="preserve">6.63735628128052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79420852661133</t>
+    <t xml:space="preserve">6.79420900344849</t>
   </si>
   <si>
     <t xml:space="preserve">6.73642158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6868896484375</t>
+    <t xml:space="preserve">6.68688917160034</t>
   </si>
   <si>
     <t xml:space="preserve">6.53829145431519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62084579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64561176300049</t>
+    <t xml:space="preserve">6.62084531784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64561223983765</t>
   </si>
   <si>
     <t xml:space="preserve">6.71991062164307</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">6.74467658996582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75293207168579</t>
+    <t xml:space="preserve">6.75293302536011</t>
   </si>
   <si>
     <t xml:space="preserve">6.78595399856567</t>
@@ -3041,22 +3041,22 @@
     <t xml:space="preserve">5.85309171676636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67972755432129</t>
+    <t xml:space="preserve">5.67972803115845</t>
   </si>
   <si>
     <t xml:space="preserve">5.39904356002808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38253211975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66321659088135</t>
+    <t xml:space="preserve">5.38253259658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66321706771851</t>
   </si>
   <si>
     <t xml:space="preserve">5.60542917251587</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74577140808105</t>
+    <t xml:space="preserve">5.7457709312439</t>
   </si>
   <si>
     <t xml:space="preserve">5.83658075332642</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">5.88611316680908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79530382156372</t>
+    <t xml:space="preserve">5.79530334472656</t>
   </si>
   <si>
     <t xml:space="preserve">5.87785768508911</t>
@@ -3074,22 +3074,22 @@
     <t xml:space="preserve">5.97692251205444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91087913513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91913509368896</t>
+    <t xml:space="preserve">5.91087961196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91913461685181</t>
   </si>
   <si>
     <t xml:space="preserve">5.63845062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78704833984375</t>
+    <t xml:space="preserve">5.78704881668091</t>
   </si>
   <si>
     <t xml:space="preserve">5.94390058517456</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9604115486145</t>
+    <t xml:space="preserve">5.96041202545166</t>
   </si>
   <si>
     <t xml:space="preserve">5.8696026802063</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">5.98917293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97186326980591</t>
+    <t xml:space="preserve">5.97186279296875</t>
   </si>
   <si>
     <t xml:space="preserve">5.98051786422729</t>
@@ -3119,37 +3119,37 @@
     <t xml:space="preserve">5.79011058807373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78145551681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57373857498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67759704589844</t>
+    <t xml:space="preserve">5.78145599365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57373905181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6775975227356</t>
   </si>
   <si>
     <t xml:space="preserve">5.76414585113525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71221685409546</t>
+    <t xml:space="preserve">5.71221733093262</t>
   </si>
   <si>
     <t xml:space="preserve">5.82472991943359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80742025375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.868004322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88531446456909</t>
+    <t xml:space="preserve">5.80742073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86800479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88531398773193</t>
   </si>
   <si>
     <t xml:space="preserve">5.87665939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9285888671875</t>
+    <t xml:space="preserve">5.92858839035034</t>
   </si>
   <si>
     <t xml:space="preserve">5.96320772171021</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">6.24881887435913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24016427993774</t>
+    <t xml:space="preserve">6.24016380310059</t>
   </si>
   <si>
     <t xml:space="preserve">6.23150873184204</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">6.26612854003906</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46519088745117</t>
+    <t xml:space="preserve">6.46519041061401</t>
   </si>
   <si>
     <t xml:space="preserve">6.54308462142944</t>
@@ -3197,25 +3197,25 @@
     <t xml:space="preserve">6.58635902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56904983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63828802108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56039428710938</t>
+    <t xml:space="preserve">6.56904935836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6382884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56039476394653</t>
   </si>
   <si>
     <t xml:space="preserve">6.57770395278931</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62097835540771</t>
+    <t xml:space="preserve">6.62097883224487</t>
   </si>
   <si>
     <t xml:space="preserve">6.65559816360474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6902174949646</t>
+    <t xml:space="preserve">6.69021797180176</t>
   </si>
   <si>
     <t xml:space="preserve">6.73349189758301</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">6.11034107208252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30940341949463</t>
+    <t xml:space="preserve">6.30940294265747</t>
   </si>
   <si>
     <t xml:space="preserve">6.37864208221436</t>
@@ -3242,25 +3242,25 @@
     <t xml:space="preserve">6.44788074493408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49115514755249</t>
+    <t xml:space="preserve">6.49115562438965</t>
   </si>
   <si>
     <t xml:space="preserve">6.49981021881104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55173969268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59501361846924</t>
+    <t xml:space="preserve">6.55174016952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5950140953064</t>
   </si>
   <si>
     <t xml:space="preserve">6.70752716064453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68156242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60366916656494</t>
+    <t xml:space="preserve">6.68156290054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60366868972778</t>
   </si>
   <si>
     <t xml:space="preserve">6.51712036132812</t>
@@ -3269,10 +3269,10 @@
     <t xml:space="preserve">6.62963342666626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74214696884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87197017669678</t>
+    <t xml:space="preserve">6.74214649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87196969985962</t>
   </si>
   <si>
     <t xml:space="preserve">6.79407596588135</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">6.78542137145996</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77676582336426</t>
+    <t xml:space="preserve">6.77676630020142</t>
   </si>
   <si>
     <t xml:space="preserve">6.7508020401001</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">6.45653581619263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71618270874023</t>
+    <t xml:space="preserve">6.71618223190308</t>
   </si>
   <si>
     <t xml:space="preserve">6.72483682632446</t>
@@ -3314,31 +3314,31 @@
     <t xml:space="preserve">6.82869577407837</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82004022598267</t>
+    <t xml:space="preserve">6.82004117965698</t>
   </si>
   <si>
     <t xml:space="preserve">6.92389917373657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01044845581055</t>
+    <t xml:space="preserve">7.01044797897339</t>
   </si>
   <si>
     <t xml:space="preserve">7.05372190475464</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9931378364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00179290771484</t>
+    <t xml:space="preserve">6.99313831329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.001793384552</t>
   </si>
   <si>
     <t xml:space="preserve">7.02775764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97582912445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95851850509644</t>
+    <t xml:space="preserve">6.97582864761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95851898193359</t>
   </si>
   <si>
     <t xml:space="preserve">6.94986343383789</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">7.07103204727173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06237745285034</t>
+    <t xml:space="preserve">7.06237697601318</t>
   </si>
   <si>
     <t xml:space="preserve">7.11430644989014</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">7.04506778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13161563873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18354511260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1575813293457</t>
+    <t xml:space="preserve">7.13161611557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18354558944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15758085250854</t>
   </si>
   <si>
     <t xml:space="preserve">7.07968711853027</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">6.88927984237671</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86331462860107</t>
+    <t xml:space="preserve">6.86331510543823</t>
   </si>
   <si>
     <t xml:space="preserve">6.93255424499512</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">6.91524410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94120931625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96717357635498</t>
+    <t xml:space="preserve">6.9412088394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96717405319214</t>
   </si>
   <si>
     <t xml:space="preserve">7.17489051818848</t>
@@ -3401,16 +3401,16 @@
     <t xml:space="preserve">7.20085477828979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22681951522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16623544692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14892625808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0883412361145</t>
+    <t xml:space="preserve">7.22681999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16623592376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08834171295166</t>
   </si>
   <si>
     <t xml:space="preserve">7.14027070999146</t>
@@ -3419,16 +3419,16 @@
     <t xml:space="preserve">7.26143932342529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31336784362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33933305740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42588186264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44319200515747</t>
+    <t xml:space="preserve">7.31336832046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33933258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42588138580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44319152832031</t>
   </si>
   <si>
     <t xml:space="preserve">7.48646545410156</t>
@@ -3440,16 +3440,16 @@
     <t xml:space="preserve">7.29605913162231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19220113754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45184564590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38260793685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3566427230835</t>
+    <t xml:space="preserve">7.19220066070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45184659957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38260746002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35664224624634</t>
   </si>
   <si>
     <t xml:space="preserve">7.52108478546143</t>
@@ -3458,55 +3458,55 @@
     <t xml:space="preserve">7.84997081756592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72880268096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76342248916626</t>
+    <t xml:space="preserve">7.7288031578064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7634220123291</t>
   </si>
   <si>
     <t xml:space="preserve">7.53839540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55570459365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46050119400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40857267379761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63359832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72014713287354</t>
+    <t xml:space="preserve">7.55570507049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4605016708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40857219696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63359880447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72014808654785</t>
   </si>
   <si>
     <t xml:space="preserve">7.88458967208862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77207708358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65090799331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6682186126709</t>
+    <t xml:space="preserve">7.77207612991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65090847015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">7.78073120117188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83266115188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82400560379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75476741790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70283794403076</t>
+    <t xml:space="preserve">7.83266162872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8240065574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75476694107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7028374671936</t>
   </si>
   <si>
     <t xml:space="preserve">7.69418334960938</t>
@@ -3515,34 +3515,34 @@
     <t xml:space="preserve">7.67687368392944</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94517469406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01441287994385</t>
+    <t xml:space="preserve">7.94517421722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01441383361816</t>
   </si>
   <si>
     <t xml:space="preserve">8.11827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05768871307373</t>
+    <t xml:space="preserve">8.05768775939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.12692737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0663423538208</t>
+    <t xml:space="preserve">8.06634140014648</t>
   </si>
   <si>
     <t xml:space="preserve">8.02306842803955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10961627960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17885494232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17020034790039</t>
+    <t xml:space="preserve">8.10961723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17885589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17020130157471</t>
   </si>
   <si>
     <t xml:space="preserve">8.20481967926025</t>
@@ -3554,37 +3554,37 @@
     <t xml:space="preserve">8.18751049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00575733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99710321426392</t>
+    <t xml:space="preserve">8.00575828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99710369110107</t>
   </si>
   <si>
     <t xml:space="preserve">7.87593555450439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30867958068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24809455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2740592956543</t>
+    <t xml:space="preserve">8.30867862701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24809551239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27406024932861</t>
   </si>
   <si>
     <t xml:space="preserve">8.41253757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57698059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5856351852417</t>
+    <t xml:space="preserve">8.576979637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58563423156738</t>
   </si>
   <si>
     <t xml:space="preserve">8.65487384796143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54236030578613</t>
+    <t xml:space="preserve">8.54236125946045</t>
   </si>
   <si>
     <t xml:space="preserve">8.62025451660156</t>
@@ -3593,10 +3593,10 @@
     <t xml:space="preserve">8.81066226959229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82797050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70680332183838</t>
+    <t xml:space="preserve">8.82797145843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7068042755127</t>
   </si>
   <si>
     <t xml:space="preserve">8.87990093231201</t>
@@ -3620,10 +3620,10 @@
     <t xml:space="preserve">8.93421173095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86179637908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.753173828125</t>
+    <t xml:space="preserve">8.86179733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75317478179932</t>
   </si>
   <si>
     <t xml:space="preserve">8.72601890563965</t>
@@ -3632,22 +3632,22 @@
     <t xml:space="preserve">8.80748558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85274410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77127742767334</t>
+    <t xml:space="preserve">8.85274505615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77127838134766</t>
   </si>
   <si>
     <t xml:space="preserve">8.68981170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69886302947998</t>
+    <t xml:space="preserve">8.69886207580566</t>
   </si>
   <si>
     <t xml:space="preserve">8.73507022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59929275512695</t>
+    <t xml:space="preserve">8.59929180145264</t>
   </si>
   <si>
     <t xml:space="preserve">8.56308460235596</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">8.08333492279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27342414855957</t>
+    <t xml:space="preserve">8.27342510223389</t>
   </si>
   <si>
     <t xml:space="preserve">8.42730712890625</t>
@@ -3686,10 +3686,10 @@
     <t xml:space="preserve">8.4906702041626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40015125274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58118724822998</t>
+    <t xml:space="preserve">8.40015029907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5811882019043</t>
   </si>
   <si>
     <t xml:space="preserve">8.40920257568359</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">8.41825485229492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60834503173828</t>
+    <t xml:space="preserve">8.60834407806396</t>
   </si>
   <si>
     <t xml:space="preserve">8.48161697387695</t>
@@ -3713,16 +3713,16 @@
     <t xml:space="preserve">8.68075942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65360355377197</t>
+    <t xml:space="preserve">8.65360450744629</t>
   </si>
   <si>
     <t xml:space="preserve">8.870849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02473068237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91610908508301</t>
+    <t xml:space="preserve">9.02473163604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91610813140869</t>
   </si>
   <si>
     <t xml:space="preserve">8.98852348327637</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">9.08809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01567935943604</t>
+    <t xml:space="preserve">9.01567840576172</t>
   </si>
   <si>
     <t xml:space="preserve">9.04283428192139</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">9.16050910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79843425750732</t>
+    <t xml:space="preserve">8.79843330383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.36394309997559</t>
@@ -3755,16 +3755,16 @@
     <t xml:space="preserve">8.29152774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23721694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26437282562256</t>
+    <t xml:space="preserve">8.23721790313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26437187194824</t>
   </si>
   <si>
     <t xml:space="preserve">8.47256565093994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97947216033936</t>
+    <t xml:space="preserve">8.97947120666504</t>
   </si>
   <si>
     <t xml:space="preserve">8.89800453186035</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">9.14240550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34154605865479</t>
+    <t xml:space="preserve">9.3415470123291</t>
   </si>
   <si>
     <t xml:space="preserve">9.28723621368408</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">9.19671630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2510290145874</t>
+    <t xml:space="preserve">9.25102806091309</t>
   </si>
   <si>
     <t xml:space="preserve">9.12430191040039</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">9.21482086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35965156555176</t>
+    <t xml:space="preserve">9.35965061187744</t>
   </si>
   <si>
     <t xml:space="preserve">9.17861366271973</t>
@@ -3821,10 +3821,10 @@
     <t xml:space="preserve">9.10619831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30533885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50448036193848</t>
+    <t xml:space="preserve">9.30533981323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50448131561279</t>
   </si>
   <si>
     <t xml:space="preserve">9.65504741668701</t>
@@ -3900,9 +3900,6 @@
   </si>
   <si>
     <t xml:space="preserve">9.5797643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50448131561279</t>
   </si>
   <si>
     <t xml:space="preserve">9.46683979034424</t>
@@ -63672,7 +63669,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>1296</v>
+        <v>1270</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63698,7 +63695,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2269" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63724,7 +63721,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2270" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63750,7 +63747,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2271" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63776,7 +63773,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2272" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63828,7 +63825,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2274" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63958,7 +63955,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2279" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63984,7 +63981,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2280" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64010,7 +64007,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2281" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64036,7 +64033,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2282" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64062,7 +64059,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2283" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64088,7 +64085,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64140,7 +64137,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2286" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64192,7 +64189,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2288" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64218,7 +64215,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2289" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64244,7 +64241,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2290" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64296,7 +64293,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2292" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64322,7 +64319,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2293" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64348,7 +64345,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2294" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64374,7 +64371,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2295" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64400,7 +64397,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2296" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64426,7 +64423,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2297" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64452,7 +64449,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2298" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64478,7 +64475,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2299" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64504,7 +64501,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2300" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64530,7 +64527,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2301" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64556,7 +64553,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2302" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64582,7 +64579,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2303" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64608,7 +64605,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2304" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64634,7 +64631,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2305" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64660,7 +64657,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2306" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64686,7 +64683,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64712,7 +64709,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2308" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64738,7 +64735,7 @@
         <v>11.5</v>
       </c>
       <c r="G2309" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64764,7 +64761,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2310" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64790,7 +64787,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2311" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64816,7 +64813,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2312" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64842,7 +64839,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2313" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64868,7 +64865,7 @@
         <v>11.5</v>
       </c>
       <c r="G2314" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64894,7 +64891,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2315" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64920,7 +64917,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2316" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64946,7 +64943,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2317" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64972,7 +64969,7 @@
         <v>12</v>
       </c>
       <c r="G2318" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64998,7 +64995,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2319" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -65024,7 +65021,7 @@
         <v>12</v>
       </c>
       <c r="G2320" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -65050,7 +65047,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2321" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65076,7 +65073,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2322" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65102,7 +65099,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2323" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65128,7 +65125,7 @@
         <v>12</v>
       </c>
       <c r="G2324" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65154,7 +65151,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2325" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65180,7 +65177,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2326" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65206,7 +65203,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2327" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65232,7 +65229,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2328" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65258,7 +65255,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2329" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65284,7 +65281,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2330" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65310,7 +65307,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2331" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65336,7 +65333,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2332" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65362,7 +65359,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2333" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65388,7 +65385,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2334" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65414,7 +65411,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65440,7 +65437,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65466,7 +65463,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2337" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65492,7 +65489,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2338" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65518,7 +65515,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2339" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65544,7 +65541,7 @@
         <v>12.5</v>
       </c>
       <c r="G2340" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65570,7 +65567,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2341" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65596,7 +65593,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65622,7 +65619,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2343" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65648,7 +65645,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2344" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65674,7 +65671,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2345" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65700,7 +65697,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2346" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65726,7 +65723,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2347" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65752,7 +65749,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2348" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65778,7 +65775,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2349" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65804,7 +65801,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2350" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65830,7 +65827,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2351" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65856,7 +65853,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2352" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65882,7 +65879,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2353" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65908,7 +65905,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2354" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65934,7 +65931,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2355" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65960,7 +65957,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2356" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65986,7 +65983,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2357" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -66012,7 +66009,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2358" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -66038,7 +66035,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2359" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -66064,7 +66061,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2360" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66090,7 +66087,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2361" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66116,7 +66113,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2362" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66142,7 +66139,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2363" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66168,7 +66165,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2364" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66194,7 +66191,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2365" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66220,7 +66217,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2366" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66246,7 +66243,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2367" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66272,7 +66269,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G2368" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66298,7 +66295,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2369" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66324,7 +66321,7 @@
         <v>12</v>
       </c>
       <c r="G2370" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66350,7 +66347,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2371" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66376,7 +66373,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2372" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66402,7 +66399,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2373" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66428,7 +66425,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2374" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66454,7 +66451,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2375" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66480,7 +66477,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2376" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66506,7 +66503,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66532,7 +66529,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2378" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66558,7 +66555,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2379" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66584,7 +66581,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2380" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66610,7 +66607,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2381" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66636,7 +66633,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2382" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66662,7 +66659,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2383" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66688,7 +66685,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2384" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66714,7 +66711,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2385" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66740,7 +66737,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2386" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66766,7 +66763,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2387" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66792,7 +66789,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2388" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66818,7 +66815,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2389" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66844,7 +66841,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2390" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66870,7 +66867,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2391" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66896,7 +66893,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2392" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66922,7 +66919,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2393" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66948,7 +66945,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2394" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66974,7 +66971,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2395" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -67000,7 +66997,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2396" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -67026,7 +67023,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2397" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -67052,7 +67049,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2398" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67078,7 +67075,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2399" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67104,7 +67101,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2400" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67130,7 +67127,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2401" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67156,7 +67153,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2402" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67182,7 +67179,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67208,7 +67205,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67234,7 +67231,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2405" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67260,7 +67257,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2406" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67286,7 +67283,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67312,7 +67309,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2408" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67338,7 +67335,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67364,7 +67361,7 @@
         <v>12.5</v>
       </c>
       <c r="G2410" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67390,7 +67387,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2411" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67416,7 +67413,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67442,7 +67439,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2413" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67468,7 +67465,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2414" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67494,7 +67491,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2415" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67520,7 +67517,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67546,7 +67543,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2417" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67572,7 +67569,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2418" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67598,7 +67595,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67624,7 +67621,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2420" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67650,7 +67647,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2421" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67676,7 +67673,7 @@
         <v>13</v>
       </c>
       <c r="G2422" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67702,7 +67699,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67728,7 +67725,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G2424" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67754,7 +67751,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2425" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67780,7 +67777,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2426" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67806,7 +67803,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67832,7 +67829,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2428" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67858,7 +67855,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2429" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67884,7 +67881,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2430" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67910,7 +67907,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2431" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67936,7 +67933,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2432" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67962,7 +67959,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2433" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67988,7 +67985,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2434" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -68014,7 +68011,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2435" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -68040,7 +68037,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2436" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -68066,7 +68063,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2437" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68092,7 +68089,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2438" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68118,7 +68115,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2439" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68144,7 +68141,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2440" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68170,7 +68167,7 @@
         <v>13.5</v>
       </c>
       <c r="G2441" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68196,7 +68193,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2442" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68222,7 +68219,7 @@
         <v>13.5</v>
       </c>
       <c r="G2443" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68248,7 +68245,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2444" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68274,7 +68271,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68300,7 +68297,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2446" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68326,7 +68323,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2447" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68352,7 +68349,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2448" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68378,7 +68375,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2449" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68404,7 +68401,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2450" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68430,7 +68427,7 @@
         <v>14</v>
       </c>
       <c r="G2451" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68456,7 +68453,7 @@
         <v>14</v>
       </c>
       <c r="G2452" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68482,7 +68479,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2453" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68508,7 +68505,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2454" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68534,7 +68531,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2455" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68560,7 +68557,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2456" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68586,7 +68583,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2457" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68612,7 +68609,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2458" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68638,7 +68635,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G2459" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68664,7 +68661,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2460" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68690,7 +68687,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G2461" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68716,7 +68713,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2462" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68742,7 +68739,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G2463" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68768,7 +68765,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2464" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68794,7 +68791,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G2465" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68820,7 +68817,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2466" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68846,7 +68843,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2467" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68872,7 +68869,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68898,7 +68895,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2469" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68924,7 +68921,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68950,7 +68947,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68976,7 +68973,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2472" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -69002,7 +68999,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2473" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -69028,7 +69025,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2474" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -69054,7 +69051,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69080,7 +69077,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G2476" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69106,7 +69103,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69132,7 +69129,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69158,7 +69155,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69184,7 +69181,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2480" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69210,7 +69207,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2481" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69236,7 +69233,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69262,7 +69259,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2483" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69288,7 +69285,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2484" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69314,7 +69311,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2485" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69340,7 +69337,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2486" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69366,7 +69363,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G2487" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69392,7 +69389,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2488" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69418,7 +69415,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2489" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69444,7 +69441,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2490" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69470,7 +69467,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2491" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69496,7 +69493,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2492" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69522,7 +69519,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2493" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69548,7 +69545,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69574,7 +69571,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69600,7 +69597,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G2496" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69626,7 +69623,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2497" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69652,7 +69649,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2498" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69678,7 +69675,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2499" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69704,7 +69701,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2500" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69730,7 +69727,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2501" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69756,7 +69753,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2502" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69782,7 +69779,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G2503" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69808,7 +69805,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2504" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69834,7 +69831,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2505" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -69860,7 +69857,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2506" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -69886,7 +69883,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2507" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -69912,7 +69909,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G2508" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -69938,7 +69935,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2509" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -69964,7 +69961,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G2510" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -69990,7 +69987,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G2511" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -70016,7 +70013,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2512" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -70042,7 +70039,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2513" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -70068,7 +70065,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2514" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -70094,7 +70091,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G2515" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -70120,7 +70117,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2516" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -70146,7 +70143,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2517" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -70172,7 +70169,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2518" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -70198,7 +70195,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2519" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -70224,7 +70221,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G2520" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -70250,7 +70247,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G2521" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -70276,7 +70273,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2522" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -70302,7 +70299,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G2523" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -70328,7 +70325,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G2524" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -70354,7 +70351,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G2525" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -70380,7 +70377,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G2526" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -70406,7 +70403,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G2527" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -70432,7 +70429,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2528" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -70458,7 +70455,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G2529" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -70484,7 +70481,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2530" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -70510,7 +70507,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G2531" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -70536,7 +70533,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2532" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -70562,7 +70559,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G2533" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -70588,7 +70585,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2534" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -70614,7 +70611,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G2535" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -70640,7 +70637,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2536" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -70648,7 +70645,7 @@
     </row>
     <row r="2537">
       <c r="A2537" s="1" t="n">
-        <v>46010.6910069444</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2537" t="n">
         <v>240553</v>
@@ -70666,9 +70663,35 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G2537" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2537" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" s="1" t="n">
+        <v>46013.6912152778</v>
+      </c>
+      <c r="B2538" t="n">
+        <v>202931</v>
+      </c>
+      <c r="C2538" t="n">
+        <v>15.3999996185303</v>
+      </c>
+      <c r="D2538" t="n">
+        <v>15.1999998092651</v>
+      </c>
+      <c r="E2538" t="n">
+        <v>15.3999996185303</v>
+      </c>
+      <c r="F2538" t="n">
+        <v>15.3000001907349</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>1451</v>
+      </c>
+      <c r="H2538" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="1452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1453" uniqueCount="1453">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,121 +38,121 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49119472503662</t>
+    <t xml:space="preserve">4.49119424819946</t>
   </si>
   <si>
     <t xml:space="preserve">CE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52814531326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46432161331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30644083023071</t>
+    <t xml:space="preserve">4.52814435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46432113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30644035339355</t>
   </si>
   <si>
     <t xml:space="preserve">4.26613092422485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31315946578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31987762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36690521240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27284955978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23589849472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05114459991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08473634719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74210214614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91677832603455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03099060058594</t>
+    <t xml:space="preserve">4.31315994262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31987810134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3669056892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27284908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23589897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05114507675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08473587036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74210238456726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91677856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03099012374878</t>
   </si>
   <si>
     <t xml:space="preserve">4.1552791595459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12840557098389</t>
+    <t xml:space="preserve">4.12840509414673</t>
   </si>
   <si>
     <t xml:space="preserve">4.01419401168823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1250467300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12168741226196</t>
+    <t xml:space="preserve">4.12504625320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1216869354248</t>
   </si>
   <si>
     <t xml:space="preserve">3.94701075553894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80256700515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83615851402283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86975073814392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58086252212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42970085144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75217962265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60773611068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84959554672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670084953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96716642379761</t>
+    <t xml:space="preserve">3.80256748199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83615946769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86975049972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58086276054382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42970037460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7521800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60773587226868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84959578514099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670132637024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96716594696045</t>
   </si>
   <si>
     <t xml:space="preserve">4.06458139419556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82944059371948</t>
+    <t xml:space="preserve">3.8294403553009</t>
   </si>
   <si>
     <t xml:space="preserve">3.77233505249023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90334177017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87982773780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72866582870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79584884643555</t>
+    <t xml:space="preserve">3.9033420085907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87982845306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72866606712341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79584932327271</t>
   </si>
   <si>
     <t xml:space="preserve">3.88318729400635</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">3.95708894729614</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13176488876343</t>
+    <t xml:space="preserve">4.13176441192627</t>
   </si>
   <si>
     <t xml:space="preserve">4.1955885887146</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">4.18551111221313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13848304748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22246217727661</t>
+    <t xml:space="preserve">4.13848257064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22246170043945</t>
   </si>
   <si>
     <t xml:space="preserve">4.29972219467163</t>
@@ -185,49 +185,49 @@
     <t xml:space="preserve">4.25605392456055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27956819534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1485595703125</t>
+    <t xml:space="preserve">4.27956771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14856100082397</t>
   </si>
   <si>
     <t xml:space="preserve">4.32659578323364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26949024200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16535615921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09817314147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04778575897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04106760025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93021488189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91006064414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81936240196228</t>
+    <t xml:space="preserve">4.26949071884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16535568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09817361831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04778623580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04106664657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93021535873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91006016731262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81936311721802</t>
   </si>
   <si>
     <t xml:space="preserve">3.75889825820923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71186995506287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93357443809509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82608199119568</t>
+    <t xml:space="preserve">3.71186971664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93357396125793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82608103752136</t>
   </si>
   <si>
     <t xml:space="preserve">4.0813775062561</t>
@@ -245,46 +245,46 @@
     <t xml:space="preserve">4.21574354171753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2829270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30308198928833</t>
+    <t xml:space="preserve">4.28292655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30308246612549</t>
   </si>
   <si>
     <t xml:space="preserve">4.35346937179565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19894790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07465887069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08809566497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06122207641602</t>
+    <t xml:space="preserve">4.1989483833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07465934753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08809518814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06122255325317</t>
   </si>
   <si>
     <t xml:space="preserve">4.0242714881897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93693327903748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21649026870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14420700073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19927883148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25435161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23370027542114</t>
+    <t xml:space="preserve">3.93693375587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21648931503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14420604705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19927978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2543511390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23369932174683</t>
   </si>
   <si>
     <t xml:space="preserve">4.23714160919189</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">4.49185228347778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4987359046936</t>
+    <t xml:space="preserve">4.49873638153076</t>
   </si>
   <si>
     <t xml:space="preserve">4.47119998931885</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">4.37826490402222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31975030899048</t>
+    <t xml:space="preserve">4.31975078582764</t>
   </si>
   <si>
     <t xml:space="preserve">4.3713812828064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28188848495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42989540100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34040260314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35072946548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25090980529785</t>
+    <t xml:space="preserve">4.28188800811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42989635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34040307998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3507285118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25091028213501</t>
   </si>
   <si>
     <t xml:space="preserve">4.03750371932983</t>
@@ -335,70 +335,70 @@
     <t xml:space="preserve">3.91703319549561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98243093490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884379386902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13732290267944</t>
+    <t xml:space="preserve">3.98243165016174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8688440322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1373233795166</t>
   </si>
   <si>
     <t xml:space="preserve">4.3369607925415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38170671463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42301177978516</t>
+    <t xml:space="preserve">4.38170719146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.423011302948</t>
   </si>
   <si>
     <t xml:space="preserve">4.52971458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74148941040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181531906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73116302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84130764007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65199613571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52464079856873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42826437950134</t>
+    <t xml:space="preserve">3.74148893356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75181412696838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7311635017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84130787849426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65199637413025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52464151382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42826390266418</t>
   </si>
   <si>
     <t xml:space="preserve">3.50743055343628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65887999534607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75525712966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82065606117249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78623533248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670728683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96522164344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95145297050476</t>
+    <t xml:space="preserve">3.65888047218323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75525760650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82065677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78623580932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670657157898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96522116661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95145273208618</t>
   </si>
   <si>
     <t xml:space="preserve">4.0409460067749</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">4.01340961456299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94456887245178</t>
+    <t xml:space="preserve">3.94456934928894</t>
   </si>
   <si>
     <t xml:space="preserve">3.98931550979614</t>
@@ -416,58 +416,58 @@
     <t xml:space="preserve">3.9583375453949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7965612411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90326452255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80000329017639</t>
+    <t xml:space="preserve">3.79656147956848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90326428413391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80000400543213</t>
   </si>
   <si>
     <t xml:space="preserve">3.68641638755798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70018529891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7655827999115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362639427185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66576385498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66920614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5521776676178</t>
+    <t xml:space="preserve">3.70018434524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76558327674866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362710952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66576457023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66920638084412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55217719078064</t>
   </si>
   <si>
     <t xml:space="preserve">3.4867787361145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47989439964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37319207191467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37181448936462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50054717063904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68985867500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561947822571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45235800743103</t>
+    <t xml:space="preserve">3.47989463806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37319135665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37181496620178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50054669380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68985915184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561923980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45235824584961</t>
   </si>
   <si>
     <t xml:space="preserve">3.47645282745361</t>
@@ -476,25 +476,25 @@
     <t xml:space="preserve">3.64511227607727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72083711624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70706915855408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77935194969177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80688714981079</t>
+    <t xml:space="preserve">3.72083783149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706868171692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77935171127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80688810348511</t>
   </si>
   <si>
     <t xml:space="preserve">3.61413407325745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61757564544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5797131061554</t>
+    <t xml:space="preserve">3.61757588386536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57971334457397</t>
   </si>
   <si>
     <t xml:space="preserve">3.5659453868866</t>
@@ -506,58 +506,58 @@
     <t xml:space="preserve">3.49022030830383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44891595840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63822793960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49710464477539</t>
+    <t xml:space="preserve">3.44891619682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63822817802429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49710488319397</t>
   </si>
   <si>
     <t xml:space="preserve">3.38695979118347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35804677009583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37456822395325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31123471260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3263795375824</t>
+    <t xml:space="preserve">3.35804653167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37456774711609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31123495101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32638001441956</t>
   </si>
   <si>
     <t xml:space="preserve">3.35529279708862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41587257385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51431512832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48333668708801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51087260246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51775717735291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47301030158997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57627153396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53496742248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64855480194092</t>
+    <t xml:space="preserve">3.41587233543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51431488990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48333692550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51087284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51775670051575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47301077842712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57627129554749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53496718406677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64855432510376</t>
   </si>
   <si>
     <t xml:space="preserve">3.67953252792358</t>
@@ -566,16 +566,16 @@
     <t xml:space="preserve">3.596923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64167046546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63134407997131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56250381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5315248966217</t>
+    <t xml:space="preserve">3.6416699886322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63134431838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56250333786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53152513504028</t>
   </si>
   <si>
     <t xml:space="preserve">3.4558002948761</t>
@@ -584,127 +584,127 @@
     <t xml:space="preserve">3.41174244880676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42964100837708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45924258232117</t>
+    <t xml:space="preserve">3.42964053153992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45924305915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.44203209877014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52808332443237</t>
+    <t xml:space="preserve">3.52808284759521</t>
   </si>
   <si>
     <t xml:space="preserve">3.6347861289978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67609047889709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62790155410767</t>
+    <t xml:space="preserve">3.67609071731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62790203094482</t>
   </si>
   <si>
     <t xml:space="preserve">3.58659791946411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54529356956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55906128883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56938743591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71739459037781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94112658500671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00996732711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88605427742004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9721052646637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83442354202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92735862731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98587322235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05471420288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9308009147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04438781738281</t>
+    <t xml:space="preserve">3.54529309272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5590615272522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56938767433167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71739530563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94112706184387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00996780395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8860547542572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97210550308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83442425727844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92735886573792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98587369918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05471324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93080139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04438734054565</t>
   </si>
   <si>
     <t xml:space="preserve">4.06159830093384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91014862060547</t>
+    <t xml:space="preserve">3.91014909744263</t>
   </si>
   <si>
     <t xml:space="preserve">3.899822473526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05815601348877</t>
+    <t xml:space="preserve">4.05815553665161</t>
   </si>
   <si>
     <t xml:space="preserve">4.07192373275757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07880878448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0306191444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19583702087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20960521697998</t>
+    <t xml:space="preserve">4.07880783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03062009811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19583749771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20960569381714</t>
   </si>
   <si>
     <t xml:space="preserve">4.29565572738647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27844619750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24746751785278</t>
+    <t xml:space="preserve">4.27844715118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24746799468994</t>
   </si>
   <si>
     <t xml:space="preserve">4.30254077911377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12699699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13043832778931</t>
+    <t xml:space="preserve">4.1269965171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13043880462646</t>
   </si>
   <si>
     <t xml:space="preserve">4.20272159576416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10634422302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12011241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17862749099731</t>
+    <t xml:space="preserve">4.10634469985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12011289596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17862796783447</t>
   </si>
   <si>
     <t xml:space="preserve">4.2405834197998</t>
@@ -716,94 +716,94 @@
     <t xml:space="preserve">4.16141748428345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04783010482788</t>
+    <t xml:space="preserve">4.04783058166504</t>
   </si>
   <si>
     <t xml:space="preserve">4.14076471328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1510910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15453338623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18206882476807</t>
+    <t xml:space="preserve">4.15109157562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15453243255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18206930160522</t>
   </si>
   <si>
     <t xml:space="preserve">4.15797472000122</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21304798126221</t>
+    <t xml:space="preserve">4.21304750442505</t>
   </si>
   <si>
     <t xml:space="preserve">4.32319259643555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36449718475342</t>
+    <t xml:space="preserve">4.36449670791626</t>
   </si>
   <si>
     <t xml:space="preserve">4.43333721160889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44022226333618</t>
+    <t xml:space="preserve">4.44022178649902</t>
   </si>
   <si>
     <t xml:space="preserve">4.3851490020752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4746413230896</t>
+    <t xml:space="preserve">4.47464179992676</t>
   </si>
   <si>
     <t xml:space="preserve">4.41956949234009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37482309341431</t>
+    <t xml:space="preserve">4.37482357025146</t>
   </si>
   <si>
     <t xml:space="preserve">4.41268539428711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34384393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30942440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36793899536133</t>
+    <t xml:space="preserve">4.34384489059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30942487716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36793947219849</t>
   </si>
   <si>
     <t xml:space="preserve">4.35417127609253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28533029556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52627277374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40580081939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48841047286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50906276702881</t>
+    <t xml:space="preserve">4.28532981872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52627229690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40580129623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48840951919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50906229019165</t>
   </si>
   <si>
     <t xml:space="preserve">4.53659868240356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54348230361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.447105884552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67083740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69899702072144</t>
+    <t xml:space="preserve">4.54348278045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44710540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67083787918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69899654388428</t>
   </si>
   <si>
     <t xml:space="preserve">4.80107259750366</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">4.78347301483154</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72011613845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68491649627686</t>
+    <t xml:space="preserve">4.72011518478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68491792678833</t>
   </si>
   <si>
     <t xml:space="preserve">4.7306752204895</t>
@@ -839,49 +839,49 @@
     <t xml:space="preserve">4.75179433822632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81515169143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81163215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9277868270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93834638595581</t>
+    <t xml:space="preserve">4.81515216827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81163167953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92778635025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93834590911865</t>
   </si>
   <si>
     <t xml:space="preserve">4.87498950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80811166763306</t>
+    <t xml:space="preserve">4.80811214447021</t>
   </si>
   <si>
     <t xml:space="preserve">4.8045916557312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7869930267334</t>
+    <t xml:space="preserve">4.78699350357056</t>
   </si>
   <si>
     <t xml:space="preserve">4.95946550369263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86442995071411</t>
+    <t xml:space="preserve">4.86442947387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.89258813858032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89610767364502</t>
+    <t xml:space="preserve">4.89610815048218</t>
   </si>
   <si>
     <t xml:space="preserve">4.91370725631714</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97354459762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97706508636475</t>
+    <t xml:space="preserve">4.97354507446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97706460952759</t>
   </si>
   <si>
     <t xml:space="preserve">4.94538593292236</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">5.11081886291504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2586522102356</t>
+    <t xml:space="preserve">5.25865268707275</t>
   </si>
   <si>
     <t xml:space="preserve">5.0615406036377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08618068695068</t>
+    <t xml:space="preserve">5.08617973327637</t>
   </si>
   <si>
     <t xml:space="preserve">5.10377883911133</t>
@@ -911,22 +911,22 @@
     <t xml:space="preserve">5.08969974517822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01930332183838</t>
+    <t xml:space="preserve">5.01930236816406</t>
   </si>
   <si>
     <t xml:space="preserve">5.04746150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96650505065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91018724441528</t>
+    <t xml:space="preserve">4.96650457382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91018772125244</t>
   </si>
   <si>
     <t xml:space="preserve">5.00874328613281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10025978088379</t>
+    <t xml:space="preserve">5.10025882720947</t>
   </si>
   <si>
     <t xml:space="preserve">5.06858062744141</t>
@@ -935,13 +935,13 @@
     <t xml:space="preserve">5.13193798065186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04042148590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1248984336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20937442779541</t>
+    <t xml:space="preserve">5.04042196273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12489795684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20937538146973</t>
   </si>
   <si>
     <t xml:space="preserve">5.36424827575684</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">5.27273178100586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23049402236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15305805206299</t>
+    <t xml:space="preserve">5.23049354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15305662155151</t>
   </si>
   <si>
     <t xml:space="preserve">5.2023344039917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11433839797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10729932785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00522422790527</t>
+    <t xml:space="preserve">5.11433887481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10729885101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00522327423096</t>
   </si>
   <si>
     <t xml:space="preserve">4.99818420410156</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">5.01226329803467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04394149780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06506061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15657663345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34312915802002</t>
+    <t xml:space="preserve">5.04394245147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06506156921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15657711029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34312963485718</t>
   </si>
   <si>
     <t xml:space="preserve">5.30089092254639</t>
@@ -1001,52 +1001,52 @@
     <t xml:space="preserve">5.27977132797241</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30793046951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25161266326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29385089874268</t>
+    <t xml:space="preserve">5.30792999267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2516131401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29385042190552</t>
   </si>
   <si>
     <t xml:space="preserve">5.29033088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33608865737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34664821624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36776828765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35368824005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38536643981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3994460105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26569175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31145000457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32553005218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28329181671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2340145111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21641397476196</t>
+    <t xml:space="preserve">5.33608913421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3466477394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36776781082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35368871688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38536691665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39944648742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26569223403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31145095825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3255295753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28329133987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23401308059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2164134979248</t>
   </si>
   <si>
     <t xml:space="preserve">5.14249753952026</t>
@@ -1058,46 +1058,46 @@
     <t xml:space="preserve">5.31497049331665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29737138748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19177532196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35720825195312</t>
+    <t xml:space="preserve">5.29737091064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19177484512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35720872879028</t>
   </si>
   <si>
     <t xml:space="preserve">5.07210063934326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98410367965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94186544418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86794948577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92426681518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98058414459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03338241577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05450057983398</t>
+    <t xml:space="preserve">4.9841046333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94186639785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86794996261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92426633834839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98058462142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03338193893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05450201034546</t>
   </si>
   <si>
     <t xml:space="preserve">5.18473529815674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17417526245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21993446350098</t>
+    <t xml:space="preserve">5.17417573928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21993494033813</t>
   </si>
   <si>
     <t xml:space="preserve">5.17769622802734</t>
@@ -1106,46 +1106,46 @@
     <t xml:space="preserve">5.22697401046753</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28681182861328</t>
+    <t xml:space="preserve">5.28681135177612</t>
   </si>
   <si>
     <t xml:space="preserve">5.02282285690308</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00170373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02986240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05802154541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99114418029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37128734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47688341140747</t>
+    <t xml:space="preserve">5.00170421600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02986288070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.058021068573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92074728012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99114370346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37128782272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47688293457031</t>
   </si>
   <si>
     <t xml:space="preserve">5.48392248153687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44168472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43464469909668</t>
+    <t xml:space="preserve">5.44168519973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43464517593384</t>
   </si>
   <si>
     <t xml:space="preserve">5.5261607170105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51208209991455</t>
+    <t xml:space="preserve">5.51208162307739</t>
   </si>
   <si>
     <t xml:space="preserve">5.46984338760376</t>
@@ -1154,16 +1154,16 @@
     <t xml:space="preserve">5.40648603439331</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3783278465271</t>
+    <t xml:space="preserve">5.37832736968994</t>
   </si>
   <si>
     <t xml:space="preserve">5.18825531005859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13897800445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32905006408691</t>
+    <t xml:space="preserve">5.13897752761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32904958724976</t>
   </si>
   <si>
     <t xml:space="preserve">5.14601707458496</t>
@@ -1172,31 +1172,31 @@
     <t xml:space="preserve">5.1952953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24457359313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22345399856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23753261566162</t>
+    <t xml:space="preserve">5.24457263946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22345447540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23753356933594</t>
   </si>
   <si>
     <t xml:space="preserve">5.16009664535522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11785793304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97002410888672</t>
+    <t xml:space="preserve">5.11785840988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97002458572388</t>
   </si>
   <si>
     <t xml:space="preserve">5.2189998626709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14661455154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98012733459473</t>
+    <t xml:space="preserve">5.14661359786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98012781143188</t>
   </si>
   <si>
     <t xml:space="preserve">4.94393444061279</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">4.81364059448242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84259462356567</t>
+    <t xml:space="preserve">4.84259510040283</t>
   </si>
   <si>
     <t xml:space="preserve">4.85707139968872</t>
@@ -1217,25 +1217,25 @@
     <t xml:space="preserve">4.8064022064209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56029081344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46618986129761</t>
+    <t xml:space="preserve">4.5602912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46618938446045</t>
   </si>
   <si>
     <t xml:space="preserve">4.21284008026123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45171308517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37208843231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52409791946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40828132629395</t>
+    <t xml:space="preserve">4.4517126083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37208795547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52409839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4082818031311</t>
   </si>
   <si>
     <t xml:space="preserve">4.34313440322876</t>
@@ -1244,28 +1244,28 @@
     <t xml:space="preserve">4.29246473312378</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39380407333374</t>
+    <t xml:space="preserve">4.3938045501709</t>
   </si>
   <si>
     <t xml:space="preserve">4.45895099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43723583221436</t>
+    <t xml:space="preserve">4.4372353553772</t>
   </si>
   <si>
     <t xml:space="preserve">4.53133726119995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61096096038818</t>
+    <t xml:space="preserve">4.61096048355103</t>
   </si>
   <si>
     <t xml:space="preserve">4.64715385437012</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69058513641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57476854324341</t>
+    <t xml:space="preserve">4.69058561325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57476806640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.58200645446777</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">4.48790550231934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.545814037323</t>
+    <t xml:space="preserve">4.54581451416016</t>
   </si>
   <si>
     <t xml:space="preserve">4.58924531936646</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">4.6037220954895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68334674835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6978235244751</t>
+    <t xml:space="preserve">4.68334627151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69782304763794</t>
   </si>
   <si>
     <t xml:space="preserve">4.62543773651123</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">4.63267660140991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61820030212402</t>
+    <t xml:space="preserve">4.61819934844971</t>
   </si>
   <si>
     <t xml:space="preserve">4.56752920150757</t>
@@ -1307,25 +1307,25 @@
     <t xml:space="preserve">4.42999696731567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59648323059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47342824935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51685905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50962114334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17664766311646</t>
+    <t xml:space="preserve">4.59648370742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47342777252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51685953140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50962066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1766471862793</t>
   </si>
   <si>
     <t xml:space="preserve">4.10426139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04635381698608</t>
+    <t xml:space="preserve">4.04635334014893</t>
   </si>
   <si>
     <t xml:space="preserve">4.0246376991272</t>
@@ -1337,22 +1337,22 @@
     <t xml:space="preserve">4.05359172821045</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06806898117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9739682674408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00292205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85091257095337</t>
+    <t xml:space="preserve">4.0680685043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97396802902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00292253494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85091233253479</t>
   </si>
   <si>
     <t xml:space="preserve">3.87262773513794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93053698539734</t>
+    <t xml:space="preserve">3.93053650856018</t>
   </si>
   <si>
     <t xml:space="preserve">3.92329812049866</t>
@@ -1364,88 +1364,88 @@
     <t xml:space="preserve">4.22731733322144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20560169219971</t>
+    <t xml:space="preserve">4.20560216903687</t>
   </si>
   <si>
     <t xml:space="preserve">4.22007846832275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23455572128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25627136230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27798700332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29970359802246</t>
+    <t xml:space="preserve">4.23455619812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25627183914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27798748016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2997031211853</t>
   </si>
   <si>
     <t xml:space="preserve">4.36484956741333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35761117935181</t>
+    <t xml:space="preserve">4.35761070251465</t>
   </si>
   <si>
     <t xml:space="preserve">4.26350975036621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09702301025391</t>
+    <t xml:space="preserve">4.09702348709106</t>
   </si>
   <si>
     <t xml:space="preserve">4.06083059310913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12597799301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90882062911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84367370605469</t>
+    <t xml:space="preserve">4.12597751617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90882110595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84367394447327</t>
   </si>
   <si>
     <t xml:space="preserve">3.78576564788818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87986707687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94501328468323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80748105049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72061824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68442630767822</t>
+    <t xml:space="preserve">3.87986636161804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94501304626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80748081207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72061848640442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68442559242249</t>
   </si>
   <si>
     <t xml:space="preserve">3.57946634292603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45641136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55051231384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81471943855286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76404929161072</t>
+    <t xml:space="preserve">3.45641112327576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55051279067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81471967697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7640495300293</t>
   </si>
   <si>
     <t xml:space="preserve">3.82919645309448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83643555641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85815095901489</t>
+    <t xml:space="preserve">3.83643531799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85815119743347</t>
   </si>
   <si>
     <t xml:space="preserve">3.74233412742615</t>
@@ -1454,67 +1454,67 @@
     <t xml:space="preserve">3.75681114196777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70614123344421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6771867275238</t>
+    <t xml:space="preserve">3.70614194869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67718696594238</t>
   </si>
   <si>
     <t xml:space="preserve">3.63375568389893</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66994857788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6192786693573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64099454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77128863334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80024218559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6627094745636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72785711288452</t>
+    <t xml:space="preserve">3.66994786262512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61927843093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64099431037903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7712881565094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80024266242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66270971298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72785687446594</t>
   </si>
   <si>
     <t xml:space="preserve">3.86538934707642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60480165481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58670496940613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57584714889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54327416419983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65547156333923</t>
+    <t xml:space="preserve">3.60480141639709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58670520782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57584691047668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54327392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65547132492065</t>
   </si>
   <si>
     <t xml:space="preserve">3.82195806503296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71337962150574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69890332221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69166374206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62651681900024</t>
+    <t xml:space="preserve">3.71337985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69890260696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69166398048401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62651705741882</t>
   </si>
   <si>
     <t xml:space="preserve">3.64823269844055</t>
@@ -1523,40 +1523,40 @@
     <t xml:space="preserve">3.5251772403717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60118246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54689311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50346159934998</t>
+    <t xml:space="preserve">3.60118174552917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54689288139343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50346183776855</t>
   </si>
   <si>
     <t xml:space="preserve">3.60842061042786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79300403594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88710498809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56498956680298</t>
+    <t xml:space="preserve">3.79300379753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88710474967957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5649893283844</t>
   </si>
   <si>
     <t xml:space="preserve">3.59394359588623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77852654457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58308529853821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53965449333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48174571990967</t>
+    <t xml:space="preserve">3.7785267829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58308601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53965425491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48174595832825</t>
   </si>
   <si>
     <t xml:space="preserve">3.49622321128845</t>
@@ -1565,130 +1565,130 @@
     <t xml:space="preserve">3.452791929245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42021799087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43155574798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43533539772034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41265988349915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3332953453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34841227531433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38620519638062</t>
+    <t xml:space="preserve">3.42021775245667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43155598640442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43533492088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41266012191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33329558372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34841251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38620543479919</t>
   </si>
   <si>
     <t xml:space="preserve">3.3710880279541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36352968215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38242554664612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31062054634094</t>
+    <t xml:space="preserve">3.36352920532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38242530822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31062030792236</t>
   </si>
   <si>
     <t xml:space="preserve">3.32573699951172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29172372817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25393104553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31439924240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33707499504089</t>
+    <t xml:space="preserve">3.29172348976135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25393128395081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31439971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33707475662231</t>
   </si>
   <si>
     <t xml:space="preserve">3.276606798172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28038644790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23503518104553</t>
+    <t xml:space="preserve">3.28038620948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23503541946411</t>
   </si>
   <si>
     <t xml:space="preserve">3.20480108261108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21613907814026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23125600814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21235942840576</t>
+    <t xml:space="preserve">3.21613931655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23125624656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21235990524292</t>
   </si>
   <si>
     <t xml:space="preserve">3.24259352684021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18212580680847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13677501678467</t>
+    <t xml:space="preserve">3.18212556838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13677477836609</t>
   </si>
   <si>
     <t xml:space="preserve">3.15189170837402</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18968415260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2010223865509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25015211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39376306533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59784293174744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65831089019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55627131462097</t>
+    <t xml:space="preserve">3.18968367576599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20102190971375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25015234947205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39376330375671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59784317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65831112861633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55627107620239</t>
   </si>
   <si>
     <t xml:space="preserve">3.55249166488647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56760883331299</t>
+    <t xml:space="preserve">3.56760907173157</t>
   </si>
   <si>
     <t xml:space="preserve">3.57516741752625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60540151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53359603881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4769070148468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59028434753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58272576332092</t>
+    <t xml:space="preserve">3.60540127754211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5335955619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47690677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5902841091156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5827260017395</t>
   </si>
   <si>
     <t xml:space="preserve">3.57138800621033</t>
@@ -1697,148 +1697,148 @@
     <t xml:space="preserve">3.52603697776794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50336194038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43911480903625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42777681350708</t>
+    <t xml:space="preserve">3.50336217880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43911457061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4277765750885</t>
   </si>
   <si>
     <t xml:space="preserve">3.42021822929382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40132212638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36730885505676</t>
+    <t xml:space="preserve">3.40132236480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36730861663818</t>
   </si>
   <si>
     <t xml:space="preserve">3.40888071060181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34085392951965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42399787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51469945907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49958229064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54871249198914</t>
+    <t xml:space="preserve">3.34085416793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42399740219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51469969749451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49958300590515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54871273040771</t>
   </si>
   <si>
     <t xml:space="preserve">3.63941478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65453147888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68098616600037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67342758178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73011636734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78680491447449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92285799980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86239075660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7452335357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76790881156921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83971428871155</t>
+    <t xml:space="preserve">3.65453124046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68098640441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67342782020569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73011612892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78680539131165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92285776138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86239051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74523329734802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76790928840637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83971476554871</t>
   </si>
   <si>
     <t xml:space="preserve">3.83215641975403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77168750762939</t>
+    <t xml:space="preserve">3.77168774604797</t>
   </si>
   <si>
     <t xml:space="preserve">3.73767495155334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69232392311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70366191864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77924680709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68854451179504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66586923599243</t>
+    <t xml:space="preserve">3.69232439994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70366144180298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77924656867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6885449886322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66586947441101</t>
   </si>
   <si>
     <t xml:space="preserve">3.69610333442688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66964817047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73389577865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81703948974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84727382659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90018272399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98332595825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96065068244934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95309233665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93041610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94553327560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99088454246521</t>
+    <t xml:space="preserve">3.66964888572693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73389554023743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81703925132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84727311134338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9001829624176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98332643508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9606499671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95309162139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93041658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94553351402283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99088430404663</t>
   </si>
   <si>
     <t xml:space="preserve">3.91529965400696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02111864089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09670352935791</t>
+    <t xml:space="preserve">4.02111911773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09670400619507</t>
   </si>
   <si>
     <t xml:space="preserve">4.03623533248901</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06646966934204</t>
+    <t xml:space="preserve">4.06646871566772</t>
   </si>
   <si>
     <t xml:space="preserve">4.0815863609314</t>
@@ -1847,85 +1847,85 @@
     <t xml:space="preserve">4.13449573516846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05135297775269</t>
+    <t xml:space="preserve">4.05135250091553</t>
   </si>
   <si>
     <t xml:space="preserve">4.02867698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0060019493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04379367828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11937856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01355981826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96820878982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93797540664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97576761245728</t>
+    <t xml:space="preserve">4.00600147247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04379415512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1193790435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01356029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96820902824402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93797516822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97576785087585</t>
   </si>
   <si>
     <t xml:space="preserve">3.90774130821228</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89262437820435</t>
+    <t xml:space="preserve">3.89262390136719</t>
   </si>
   <si>
     <t xml:space="preserve">3.88506555557251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87750697135925</t>
+    <t xml:space="preserve">3.87750744819641</t>
   </si>
   <si>
     <t xml:space="preserve">3.85483121871948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80192255973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59406352043152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6016218662262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65075254440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71877861022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99844288825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72255825996399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63185620307922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46556949615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44667291641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28416538238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11031985282898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06496930122375</t>
+    <t xml:space="preserve">3.80192279815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59406399726868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60162210464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6507523059845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71877884864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99844312667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72255778312683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63185596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46556901931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44667315483093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28416514396667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11032009124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06496906280518</t>
   </si>
   <si>
     <t xml:space="preserve">2.83821439743042</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">2.8344349861145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95915031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70972013473511</t>
+    <t xml:space="preserve">2.95915007591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70971989631653</t>
   </si>
   <si>
     <t xml:space="preserve">2.93269538879395</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">2.94403314590454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91002011299133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96292948722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85333132743835</t>
+    <t xml:space="preserve">2.91001987457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96292972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85333108901978</t>
   </si>
   <si>
     <t xml:space="preserve">2.89490294456482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88734483718872</t>
+    <t xml:space="preserve">2.88734436035156</t>
   </si>
   <si>
     <t xml:space="preserve">2.92135787010193</t>
@@ -1973,25 +1973,25 @@
     <t xml:space="preserve">2.85711026191711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90246152877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82687664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89112377166748</t>
+    <t xml:space="preserve">2.9024612903595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8268768787384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8911235332489</t>
   </si>
   <si>
     <t xml:space="preserve">2.9969425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9515917301178</t>
+    <t xml:space="preserve">2.95159149169922</t>
   </si>
   <si>
     <t xml:space="preserve">2.97804641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99316334724426</t>
+    <t xml:space="preserve">2.99316358566284</t>
   </si>
   <si>
     <t xml:space="preserve">3.05363130569458</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">3.03473472595215</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02717661857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12165784835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06118988990784</t>
+    <t xml:space="preserve">3.02717685699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12165808677673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.061190366745</t>
   </si>
   <si>
     <t xml:space="preserve">3.09898209571838</t>
@@ -2018,46 +2018,46 @@
     <t xml:space="preserve">3.14433312416077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19346356391907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2199182510376</t>
+    <t xml:space="preserve">3.19346332550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21991872787476</t>
   </si>
   <si>
     <t xml:space="preserve">3.26904845237732</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32195806503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1594500541687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07252764701843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06874823570251</t>
+    <t xml:space="preserve">3.32195782661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15945029258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07252740859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06874847412109</t>
   </si>
   <si>
     <t xml:space="preserve">3.10654091835022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16322946548462</t>
+    <t xml:space="preserve">3.1632297039032</t>
   </si>
   <si>
     <t xml:space="preserve">3.27282738685608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28794455528259</t>
+    <t xml:space="preserve">3.28794431686401</t>
   </si>
   <si>
     <t xml:space="preserve">3.40510153770447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51092004776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48824429512024</t>
+    <t xml:space="preserve">3.51092028617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48824453353882</t>
   </si>
   <si>
     <t xml:space="preserve">3.45801043510437</t>
@@ -2066,43 +2066,43 @@
     <t xml:space="preserve">3.29550337791443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34463357925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29928183555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30684113502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30306148529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26148986816406</t>
+    <t xml:space="preserve">3.34463310241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29928255081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30684089660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30306196212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26149010658264</t>
   </si>
   <si>
     <t xml:space="preserve">3.37864637374878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37486743927002</t>
+    <t xml:space="preserve">3.37486720085144</t>
   </si>
   <si>
     <t xml:space="preserve">3.26526927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39754247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48068642616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38998436927795</t>
+    <t xml:space="preserve">3.39754319190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48068618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38998460769653</t>
   </si>
   <si>
     <t xml:space="preserve">3.31817865371704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2577109336853</t>
+    <t xml:space="preserve">3.25771045684814</t>
   </si>
   <si>
     <t xml:space="preserve">3.22747683525085</t>
@@ -2114,16 +2114,16 @@
     <t xml:space="preserve">3.24637293815613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17456722259521</t>
+    <t xml:space="preserve">3.17456698417664</t>
   </si>
   <si>
     <t xml:space="preserve">3.14055418968201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17834615707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09142398834229</t>
+    <t xml:space="preserve">3.17834663391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09142351150513</t>
   </si>
   <si>
     <t xml:space="preserve">3.08008599281311</t>
@@ -2132,19 +2132,19 @@
     <t xml:space="preserve">3.0460729598999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01583862304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9402539730072</t>
+    <t xml:space="preserve">3.01583886146545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94025421142578</t>
   </si>
   <si>
     <t xml:space="preserve">2.95537090301514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92513704299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88356518745422</t>
+    <t xml:space="preserve">2.92513680458069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8835654258728</t>
   </si>
   <si>
     <t xml:space="preserve">2.80042147636414</t>
@@ -2156,19 +2156,19 @@
     <t xml:space="preserve">2.77018785476685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75129175186157</t>
+    <t xml:space="preserve">2.75129151344299</t>
   </si>
   <si>
     <t xml:space="preserve">2.71727848052979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72105741500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67948579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55477070808411</t>
+    <t xml:space="preserve">2.72105765342712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67948603630066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55477094650269</t>
   </si>
   <si>
     <t xml:space="preserve">2.44895195960999</t>
@@ -2177,46 +2177,46 @@
     <t xml:space="preserve">2.55099177360535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.615238904953</t>
+    <t xml:space="preserve">2.61523866653442</t>
   </si>
   <si>
     <t xml:space="preserve">2.69838213920593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98938417434692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53737449645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62807679176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63563513755798</t>
+    <t xml:space="preserve">2.98938393592834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53737473487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62807655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63563537597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.57894682884216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56382989883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50714111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48446536064148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52225780487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41643929481506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12543749809265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80948066711426</t>
+    <t xml:space="preserve">3.56382966041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50714063644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48446583747864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52225804328918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41643905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12543702125549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8094801902771</t>
   </si>
   <si>
     <t xml:space="preserve">3.76035070419312</t>
@@ -2225,31 +2225,31 @@
     <t xml:space="preserve">3.64319372177124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68476510047913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7490131855011</t>
+    <t xml:space="preserve">3.68476557731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74901342391968</t>
   </si>
   <si>
     <t xml:space="preserve">3.79436373710632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75657105445862</t>
+    <t xml:space="preserve">3.7565712928772</t>
   </si>
   <si>
     <t xml:space="preserve">3.77546763420105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76412987709045</t>
+    <t xml:space="preserve">3.76413011550903</t>
   </si>
   <si>
     <t xml:space="preserve">4.15717124938965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11182069778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17228841781616</t>
+    <t xml:space="preserve">4.11182117462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17228746414185</t>
   </si>
   <si>
     <t xml:space="preserve">4.3134560585022</t>
@@ -2261,28 +2261,28 @@
     <t xml:space="preserve">4.1252326965332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07817602157593</t>
+    <t xml:space="preserve">4.07817649841309</t>
   </si>
   <si>
     <t xml:space="preserve">4.08601951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09386157989502</t>
+    <t xml:space="preserve">4.09386205673218</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365905761719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2664008140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27424240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25855731964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36835432052612</t>
+    <t xml:space="preserve">4.26640033721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27424287796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25855684280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36835479736328</t>
   </si>
   <si>
     <t xml:space="preserve">4.32914113998413</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">4.34482622146606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35266923904419</t>
+    <t xml:space="preserve">4.35266971588135</t>
   </si>
   <si>
     <t xml:space="preserve">4.30561304092407</t>
@@ -2300,61 +2300,61 @@
     <t xml:space="preserve">4.28992795944214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28208541870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1958155632019</t>
+    <t xml:space="preserve">4.28208589553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19581604003906</t>
   </si>
   <si>
     <t xml:space="preserve">4.03896331787109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02327823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99975037574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00759315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96053695678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03112077713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05464887619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93700885772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92132329940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01543569564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07033395767212</t>
+    <t xml:space="preserve">4.02327871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99974989891052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00759267807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96053671836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03112030029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05464839935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93700909614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92132353782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01543521881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07033348083496</t>
   </si>
   <si>
     <t xml:space="preserve">3.9762225151062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1879734992981</t>
+    <t xml:space="preserve">4.18797397613525</t>
   </si>
   <si>
     <t xml:space="preserve">4.24287176132202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21150159835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39188194274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45462322235107</t>
+    <t xml:space="preserve">4.21150207519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39188241958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45462369918823</t>
   </si>
   <si>
     <t xml:space="preserve">4.43109560012817</t>
@@ -2366,22 +2366,22 @@
     <t xml:space="preserve">4.38403987884521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39972496032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3369836807251</t>
+    <t xml:space="preserve">4.39972543716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33698415756226</t>
   </si>
   <si>
     <t xml:space="preserve">4.36051177978516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4624662399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44678115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43893814086914</t>
+    <t xml:space="preserve">4.46246671676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44678020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4389386177063</t>
   </si>
   <si>
     <t xml:space="preserve">4.47815179824829</t>
@@ -2393,43 +2393,43 @@
     <t xml:space="preserve">4.50167942047119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5644211769104</t>
+    <t xml:space="preserve">4.56442070007324</t>
   </si>
   <si>
     <t xml:space="preserve">4.60363388061523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62716150283813</t>
+    <t xml:space="preserve">4.62716245651245</t>
   </si>
   <si>
     <t xml:space="preserve">4.6350040435791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49383735656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59579133987427</t>
+    <t xml:space="preserve">4.49383640289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59579086303711</t>
   </si>
   <si>
     <t xml:space="preserve">4.66637516021729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68206024169922</t>
+    <t xml:space="preserve">4.68205976486206</t>
   </si>
   <si>
     <t xml:space="preserve">4.72911643981934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64284706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74480152130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8624415397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90949726104736</t>
+    <t xml:space="preserve">4.64284753799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74480199813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86244058609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90949678421021</t>
   </si>
   <si>
     <t xml:space="preserve">5.05850696563721</t>
@@ -2438,61 +2438,61 @@
     <t xml:space="preserve">5.03497982025146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99576663970947</t>
+    <t xml:space="preserve">4.99576616287231</t>
   </si>
   <si>
     <t xml:space="preserve">4.95655298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9487099647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97223854064941</t>
+    <t xml:space="preserve">4.94871044158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97223806381226</t>
   </si>
   <si>
     <t xml:space="preserve">4.87028360366821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98008108139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07419204711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05066537857056</t>
+    <t xml:space="preserve">4.98008060455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0741925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05066442489624</t>
   </si>
   <si>
     <t xml:space="preserve">5.02713680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08987760543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19183206558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18398952484131</t>
+    <t xml:space="preserve">5.08987808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19183254241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18399000167847</t>
   </si>
   <si>
     <t xml:space="preserve">5.16830444335938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10556316375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14477682113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23888826370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21536016464233</t>
+    <t xml:space="preserve">5.10556364059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14477634429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23888778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21536064147949</t>
   </si>
   <si>
     <t xml:space="preserve">5.1996750831604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25457382202148</t>
+    <t xml:space="preserve">5.25457334518433</t>
   </si>
   <si>
     <t xml:space="preserve">5.30162954330444</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">5.01929473876953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93302536010742</t>
+    <t xml:space="preserve">4.93302488327026</t>
   </si>
   <si>
     <t xml:space="preserve">4.7996997833252</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">4.76832962036133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68990230560303</t>
+    <t xml:space="preserve">4.68990325927734</t>
   </si>
   <si>
     <t xml:space="preserve">4.69774580001831</t>
@@ -2522,13 +2522,13 @@
     <t xml:space="preserve">4.6114764213562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53305053710938</t>
+    <t xml:space="preserve">4.53305006027222</t>
   </si>
   <si>
     <t xml:space="preserve">4.50952243804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47030925750732</t>
+    <t xml:space="preserve">4.47030878067017</t>
   </si>
   <si>
     <t xml:space="preserve">4.55657815933228</t>
@@ -2540,19 +2540,19 @@
     <t xml:space="preserve">4.57226324081421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52520799636841</t>
+    <t xml:space="preserve">4.52520751953125</t>
   </si>
   <si>
     <t xml:space="preserve">4.54089260101318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51736497879028</t>
+    <t xml:space="preserve">4.51736450195312</t>
   </si>
   <si>
     <t xml:space="preserve">4.58010625839233</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82322835922241</t>
+    <t xml:space="preserve">4.8232274055481</t>
   </si>
   <si>
     <t xml:space="preserve">4.87812662124634</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">4.78401470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70558786392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65853214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77617216110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85459852218628</t>
+    <t xml:space="preserve">4.70558834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65853261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77617263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85459899902344</t>
   </si>
   <si>
     <t xml:space="preserve">4.94086790084839</t>
@@ -2582,52 +2582,52 @@
     <t xml:space="preserve">5.52122354507446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6623911857605</t>
+    <t xml:space="preserve">5.66239070892334</t>
   </si>
   <si>
     <t xml:space="preserve">5.73297500610352</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89767122268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6859188079834</t>
+    <t xml:space="preserve">5.89767074584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68591976165771</t>
   </si>
   <si>
     <t xml:space="preserve">5.70160436630249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59964990615845</t>
+    <t xml:space="preserve">5.59965038299561</t>
   </si>
   <si>
     <t xml:space="preserve">5.5369086265564</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52906703948975</t>
+    <t xml:space="preserve">5.52906656265259</t>
   </si>
   <si>
     <t xml:space="preserve">5.17614698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29378700256348</t>
+    <t xml:space="preserve">5.29378747940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.7134313583374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4154109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89381122589111</t>
+    <t xml:space="preserve">4.41541051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89381170272827</t>
   </si>
   <si>
     <t xml:space="preserve">4.81538534164429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9251823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84675645828247</t>
+    <t xml:space="preserve">4.92518281936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84675598144531</t>
   </si>
   <si>
     <t xml:space="preserve">4.72127342224121</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">4.5879487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61931943893433</t>
+    <t xml:space="preserve">4.61931896209717</t>
   </si>
   <si>
     <t xml:space="preserve">4.77163171768188</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">4.738609790802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69733285903931</t>
+    <t xml:space="preserve">4.69733333587646</t>
   </si>
   <si>
     <t xml:space="preserve">4.63954496383667</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">4.7963981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98627233505249</t>
+    <t xml:space="preserve">4.98627281188965</t>
   </si>
   <si>
     <t xml:space="preserve">4.95325088500977</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">5.14312553405762</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07708215713501</t>
+    <t xml:space="preserve">5.07708168029785</t>
   </si>
   <si>
     <t xml:space="preserve">5.11835908889771</t>
@@ -2672,34 +2672,34 @@
     <t xml:space="preserve">4.97801733016968</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06057119369507</t>
+    <t xml:space="preserve">5.06057167053223</t>
   </si>
   <si>
     <t xml:space="preserve">4.9037184715271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96976184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87069654464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82942008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62303447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40839338302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50745820999146</t>
+    <t xml:space="preserve">4.96976137161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87069702148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82941961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62303400039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40839385986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50745868682861</t>
   </si>
   <si>
     <t xml:space="preserve">4.56524658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4826922416687</t>
+    <t xml:space="preserve">4.48269176483154</t>
   </si>
   <si>
     <t xml:space="preserve">4.58175754547119</t>
@@ -2711,52 +2711,52 @@
     <t xml:space="preserve">4.61477899551392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57350158691406</t>
+    <t xml:space="preserve">4.5735011100769</t>
   </si>
   <si>
     <t xml:space="preserve">4.51571369171143</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3340950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30932760238647</t>
+    <t xml:space="preserve">4.33409452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30932807922363</t>
   </si>
   <si>
     <t xml:space="preserve">4.38362693786621</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16898632049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2680516242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39188241958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46618127822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42490434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3753719329834</t>
+    <t xml:space="preserve">4.16898679733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26805114746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39188289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4661808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42490386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37537145614624</t>
   </si>
   <si>
     <t xml:space="preserve">4.27630662918091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44967079162598</t>
+    <t xml:space="preserve">4.44966983795166</t>
   </si>
   <si>
     <t xml:space="preserve">4.34235048294067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41664838790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55699110031128</t>
+    <t xml:space="preserve">4.41664886474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55699062347412</t>
   </si>
   <si>
     <t xml:space="preserve">4.67256689071655</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">4.72209930419922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75512075424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7798867225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73035478591919</t>
+    <t xml:space="preserve">4.7551212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77988719940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73035430908203</t>
   </si>
   <si>
     <t xml:space="preserve">4.82116460800171</t>
@@ -2798,28 +2798,28 @@
     <t xml:space="preserve">4.94499540328979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83767557144165</t>
+    <t xml:space="preserve">4.83767461776733</t>
   </si>
   <si>
     <t xml:space="preserve">4.78814268112183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87895154953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60652303695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66431140899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81290912628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93674039840698</t>
+    <t xml:space="preserve">4.87895202636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60652351379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66431093215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81290864944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88720798492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93673992156982</t>
   </si>
   <si>
     <t xml:space="preserve">5.01103925704956</t>
@@ -2828,22 +2828,22 @@
     <t xml:space="preserve">5.11010408401489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16789197921753</t>
+    <t xml:space="preserve">5.16789150238037</t>
   </si>
   <si>
     <t xml:space="preserve">5.23393535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19265794754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22567987442017</t>
+    <t xml:space="preserve">5.19265842437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22567939758301</t>
   </si>
   <si>
     <t xml:space="preserve">5.26695680618286</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27521181106567</t>
+    <t xml:space="preserve">5.27521228790283</t>
   </si>
   <si>
     <t xml:space="preserve">5.29172277450562</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">5.30823373794556</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36602210998535</t>
+    <t xml:space="preserve">5.36602163314819</t>
   </si>
   <si>
     <t xml:space="preserve">5.43206548690796</t>
@@ -2864,34 +2864,34 @@
     <t xml:space="preserve">5.55589628219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41555452346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4898533821106</t>
+    <t xml:space="preserve">5.41555404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48985290527344</t>
   </si>
   <si>
     <t xml:space="preserve">5.46508646011353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57240724563599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44857549667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49810838699341</t>
+    <t xml:space="preserve">5.57240772247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44857597351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49810886383057</t>
   </si>
   <si>
     <t xml:space="preserve">5.52287483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51461935043335</t>
+    <t xml:space="preserve">5.51461887359619</t>
   </si>
   <si>
     <t xml:space="preserve">5.58891820907593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45683097839355</t>
+    <t xml:space="preserve">5.45683145523071</t>
   </si>
   <si>
     <t xml:space="preserve">5.54764080047607</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">5.63019514083862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.613685131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59717416763306</t>
+    <t xml:space="preserve">5.61368465423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5971736907959</t>
   </si>
   <si>
     <t xml:space="preserve">5.58066272735596</t>
@@ -2918,10 +2918,10 @@
     <t xml:space="preserve">5.77879285812378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82007026672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84483575820923</t>
+    <t xml:space="preserve">5.82006978988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84483623504639</t>
   </si>
   <si>
     <t xml:space="preserve">5.86134672164917</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">5.80355930328369</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73751544952393</t>
+    <t xml:space="preserve">5.73751592636108</t>
   </si>
   <si>
     <t xml:space="preserve">6.00168943405151</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">6.47224807739258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4392261505127</t>
+    <t xml:space="preserve">6.43922662734985</t>
   </si>
   <si>
     <t xml:space="preserve">6.45573711395264</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">6.57956838607788</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58782339096069</t>
+    <t xml:space="preserve">6.58782386779785</t>
   </si>
   <si>
     <t xml:space="preserve">6.51352500915527</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">6.67863368988037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72816514968872</t>
+    <t xml:space="preserve">6.72816562652588</t>
   </si>
   <si>
     <t xml:space="preserve">6.6703782081604</t>
@@ -3002,22 +3002,22 @@
     <t xml:space="preserve">6.68688917160034</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53829145431519</t>
+    <t xml:space="preserve">6.53829097747803</t>
   </si>
   <si>
     <t xml:space="preserve">6.62084531784058</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64561176300049</t>
+    <t xml:space="preserve">6.64561128616333</t>
   </si>
   <si>
     <t xml:space="preserve">6.71991062164307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74467706680298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75293302536011</t>
+    <t xml:space="preserve">6.74467658996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75293207168579</t>
   </si>
   <si>
     <t xml:space="preserve">6.78595399856567</t>
@@ -3032,19 +3032,19 @@
     <t xml:space="preserve">5.64670610427856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85309171676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67972755432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39904403686523</t>
+    <t xml:space="preserve">5.8530912399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67972803115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39904356002808</t>
   </si>
   <si>
     <t xml:space="preserve">5.38253259658813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66321659088135</t>
+    <t xml:space="preserve">5.66321706771851</t>
   </si>
   <si>
     <t xml:space="preserve">5.60542917251587</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">5.88611316680908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79530382156372</t>
+    <t xml:space="preserve">5.79530334472656</t>
   </si>
   <si>
     <t xml:space="preserve">5.87785768508911</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">5.9769229888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91087913513184</t>
+    <t xml:space="preserve">5.91087961196899</t>
   </si>
   <si>
     <t xml:space="preserve">5.91913461685181</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">5.78704881668091</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94390106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96041202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86960220336914</t>
+    <t xml:space="preserve">5.94390058517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9604115486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8696026802063</t>
   </si>
   <si>
     <t xml:space="preserve">5.98917293548584</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">5.79011058807373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78145599365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57373905181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6775975227356</t>
+    <t xml:space="preserve">5.78145551681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57373857498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67759704589844</t>
   </si>
   <si>
     <t xml:space="preserve">5.76414585113525</t>
@@ -3137,13 +3137,13 @@
     <t xml:space="preserve">5.86800479888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88531446456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87665987014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92858839035034</t>
+    <t xml:space="preserve">5.88531398773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87665939331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9285888671875</t>
   </si>
   <si>
     <t xml:space="preserve">5.96320819854736</t>
@@ -3164,25 +3164,25 @@
     <t xml:space="preserve">6.17092561721802</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28343915939331</t>
+    <t xml:space="preserve">6.28343868255615</t>
   </si>
   <si>
     <t xml:space="preserve">6.25747394561768</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24881887435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24016380310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23150873184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26612854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46519088745117</t>
+    <t xml:space="preserve">6.24881839752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24016427993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2315092086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2661280632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46519041061401</t>
   </si>
   <si>
     <t xml:space="preserve">6.54308462142944</t>
@@ -3194,22 +3194,22 @@
     <t xml:space="preserve">6.56904935836792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63828802108765</t>
+    <t xml:space="preserve">6.6382884979248</t>
   </si>
   <si>
     <t xml:space="preserve">6.56039428710938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57770442962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62097883224487</t>
+    <t xml:space="preserve">6.57770395278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62097835540771</t>
   </si>
   <si>
     <t xml:space="preserve">6.65559816360474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69021797180176</t>
+    <t xml:space="preserve">6.6902174949646</t>
   </si>
   <si>
     <t xml:space="preserve">6.73349189758301</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">6.64694309234619</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50846529006958</t>
+    <t xml:space="preserve">6.50846481323242</t>
   </si>
   <si>
     <t xml:space="preserve">6.66425275802612</t>
@@ -3254,58 +3254,58 @@
     <t xml:space="preserve">6.68156242370605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60366868972778</t>
+    <t xml:space="preserve">6.60366916656494</t>
   </si>
   <si>
     <t xml:space="preserve">6.51712036132812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62963342666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74214649200439</t>
+    <t xml:space="preserve">6.6296329498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74214696884155</t>
   </si>
   <si>
     <t xml:space="preserve">6.87196969985962</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79407644271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85466003417969</t>
+    <t xml:space="preserve">6.79407596588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85466051101685</t>
   </si>
   <si>
     <t xml:space="preserve">6.61232376098633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78542137145996</t>
+    <t xml:space="preserve">6.7854208946228</t>
   </si>
   <si>
     <t xml:space="preserve">6.77676630020142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75080156326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52577495574951</t>
+    <t xml:space="preserve">6.7508020401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52577447891235</t>
   </si>
   <si>
     <t xml:space="preserve">6.42191648483276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45653581619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71618223190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72483730316162</t>
+    <t xml:space="preserve">6.45653629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71618270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72483682632446</t>
   </si>
   <si>
     <t xml:space="preserve">6.75945663452148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82869577407837</t>
+    <t xml:space="preserve">6.82869529724121</t>
   </si>
   <si>
     <t xml:space="preserve">6.82004070281982</t>
@@ -3314,25 +3314,25 @@
     <t xml:space="preserve">6.92389917373657</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01044797897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05372190475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99313831329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.001793384552</t>
+    <t xml:space="preserve">7.01044845581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05372142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9931378364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00179290771484</t>
   </si>
   <si>
     <t xml:space="preserve">7.02775764465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97582864761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95851850509644</t>
+    <t xml:space="preserve">6.97582912445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95851898193359</t>
   </si>
   <si>
     <t xml:space="preserve">6.94986343383789</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">7.07103204727173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06237697601318</t>
+    <t xml:space="preserve">7.06237745285034</t>
   </si>
   <si>
     <t xml:space="preserve">7.11430644989014</t>
@@ -3353,31 +3353,31 @@
     <t xml:space="preserve">7.01910257339478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04506731033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13161611557007</t>
+    <t xml:space="preserve">7.04506778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13161563873291</t>
   </si>
   <si>
     <t xml:space="preserve">7.18354558944702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15758085250854</t>
+    <t xml:space="preserve">7.1575813293457</t>
   </si>
   <si>
     <t xml:space="preserve">7.07968711853027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88927984237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86331462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93255424499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91524410247803</t>
+    <t xml:space="preserve">6.88927936553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86331510543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93255376815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91524457931519</t>
   </si>
   <si>
     <t xml:space="preserve">6.94120931625366</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">6.96717357635498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17489004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27009439468384</t>
+    <t xml:space="preserve">7.17489051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27009391784668</t>
   </si>
   <si>
     <t xml:space="preserve">7.20085477828979</t>
@@ -3404,10 +3404,10 @@
     <t xml:space="preserve">7.14892578125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08834171295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14027070999146</t>
+    <t xml:space="preserve">7.0883412361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14027118682861</t>
   </si>
   <si>
     <t xml:space="preserve">7.26143932342529</t>
@@ -3419,16 +3419,16 @@
     <t xml:space="preserve">7.33933305740356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42588138580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44319200515747</t>
+    <t xml:space="preserve">7.42588186264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44319248199463</t>
   </si>
   <si>
     <t xml:space="preserve">7.48646545410156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23547506332397</t>
+    <t xml:space="preserve">7.23547410964966</t>
   </si>
   <si>
     <t xml:space="preserve">7.29605865478516</t>
@@ -3437,10 +3437,10 @@
     <t xml:space="preserve">7.19220066070557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4518461227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38260746002197</t>
+    <t xml:space="preserve">7.45184564590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38260793685913</t>
   </si>
   <si>
     <t xml:space="preserve">7.3566427230835</t>
@@ -3449,55 +3449,55 @@
     <t xml:space="preserve">7.52108478546143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84997081756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72880220413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7634220123291</t>
+    <t xml:space="preserve">7.84997034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72880268096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76342248916626</t>
   </si>
   <si>
     <t xml:space="preserve">7.53839540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55570507049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4605016708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40857219696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63359785079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72014713287354</t>
+    <t xml:space="preserve">7.55570411682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46050119400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40857267379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63359880447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72014760971069</t>
   </si>
   <si>
     <t xml:space="preserve">7.88458967208862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77207612991333</t>
+    <t xml:space="preserve">7.77207660675049</t>
   </si>
   <si>
     <t xml:space="preserve">7.65090847015381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6682186126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78073215484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83266067504883</t>
+    <t xml:space="preserve">7.66821813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78073072433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83266162872314</t>
   </si>
   <si>
     <t xml:space="preserve">7.82400560379028</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75476694107056</t>
+    <t xml:space="preserve">7.75476741790771</t>
   </si>
   <si>
     <t xml:space="preserve">7.7028374671936</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">7.69418334960938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67687273025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94517421722412</t>
+    <t xml:space="preserve">7.67687320709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94517374038696</t>
   </si>
   <si>
     <t xml:space="preserve">8.01441287994385</t>
@@ -3518,10 +3518,10 @@
     <t xml:space="preserve">8.11827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05768871307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12692642211914</t>
+    <t xml:space="preserve">8.05768775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12692737579346</t>
   </si>
   <si>
     <t xml:space="preserve">8.0663423538208</t>
@@ -3533,10 +3533,10 @@
     <t xml:space="preserve">8.10961627960205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17885589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17020130157471</t>
+    <t xml:space="preserve">8.17885494232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17020034790039</t>
   </si>
   <si>
     <t xml:space="preserve">8.20481967926025</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">8.00575828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99710273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87593650817871</t>
+    <t xml:space="preserve">7.99710369110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87593555450439</t>
   </si>
   <si>
     <t xml:space="preserve">8.30867862701416</t>
@@ -3569,13 +3569,13 @@
     <t xml:space="preserve">8.41253757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57698059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58563423156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65487289428711</t>
+    <t xml:space="preserve">8.576979637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5856351852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65487384796143</t>
   </si>
   <si>
     <t xml:space="preserve">8.54236030578613</t>
@@ -3584,16 +3584,16 @@
     <t xml:space="preserve">8.62025451660156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81066131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82797145843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7068042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87990093231201</t>
+    <t xml:space="preserve">8.81066226959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82797050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70680332183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87990188598633</t>
   </si>
   <si>
     <t xml:space="preserve">8.834641456604</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">8.93421173095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86179733276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75317478179932</t>
+    <t xml:space="preserve">8.86179637908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.753173828125</t>
   </si>
   <si>
     <t xml:space="preserve">8.72601890563965</t>
@@ -3626,22 +3626,22 @@
     <t xml:space="preserve">8.80748558044434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85274505615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77127838134766</t>
+    <t xml:space="preserve">8.85274410247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77127742767334</t>
   </si>
   <si>
     <t xml:space="preserve">8.68981170654297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69886207580566</t>
+    <t xml:space="preserve">8.69886302947998</t>
   </si>
   <si>
     <t xml:space="preserve">8.73507022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59929180145264</t>
+    <t xml:space="preserve">8.59929275512695</t>
   </si>
   <si>
     <t xml:space="preserve">8.56308460235596</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">8.08333492279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27342510223389</t>
+    <t xml:space="preserve">8.27342414855957</t>
   </si>
   <si>
     <t xml:space="preserve">8.42730712890625</t>
@@ -3680,10 +3680,10 @@
     <t xml:space="preserve">8.4906702041626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40015029907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5811882019043</t>
+    <t xml:space="preserve">8.40015125274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58118724822998</t>
   </si>
   <si>
     <t xml:space="preserve">8.40920257568359</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">8.41825485229492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60834407806396</t>
+    <t xml:space="preserve">8.60834503173828</t>
   </si>
   <si>
     <t xml:space="preserve">8.48161697387695</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">8.68075942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65360450744629</t>
+    <t xml:space="preserve">8.65360355377197</t>
   </si>
   <si>
     <t xml:space="preserve">8.870849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02473163604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91610813140869</t>
+    <t xml:space="preserve">9.02473068237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91610908508301</t>
   </si>
   <si>
     <t xml:space="preserve">8.98852348327637</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">9.08809471130371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01567840576172</t>
+    <t xml:space="preserve">9.01567935943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.04283428192139</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">9.16050910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79843330383301</t>
+    <t xml:space="preserve">8.79843425750732</t>
   </si>
   <si>
     <t xml:space="preserve">8.36394309997559</t>
@@ -3749,16 +3749,16 @@
     <t xml:space="preserve">8.29152774810791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23721790313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26437187194824</t>
+    <t xml:space="preserve">8.23721694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26437282562256</t>
   </si>
   <si>
     <t xml:space="preserve">8.47256565093994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97947120666504</t>
+    <t xml:space="preserve">8.97947216033936</t>
   </si>
   <si>
     <t xml:space="preserve">8.89800453186035</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">9.14240550994873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3415470123291</t>
+    <t xml:space="preserve">9.34154605865479</t>
   </si>
   <si>
     <t xml:space="preserve">9.28723621368408</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">9.19671630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25102806091309</t>
+    <t xml:space="preserve">9.2510290145874</t>
   </si>
   <si>
     <t xml:space="preserve">9.12430191040039</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">9.21482086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35965061187744</t>
+    <t xml:space="preserve">9.35965156555176</t>
   </si>
   <si>
     <t xml:space="preserve">9.17861366271973</t>
@@ -3815,85 +3815,88 @@
     <t xml:space="preserve">9.10619831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30533981323242</t>
+    <t xml:space="preserve">9.30533885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50448036193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65504741668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78679180145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73033046722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67386722564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52330112457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48566055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40096664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34450435638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29745292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35391426086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38214588165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26922225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41037750244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39155578613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91853713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93735885620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80561351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0314617156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84325408935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95617866516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97500038146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89971733093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61740589141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69268894195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5797643661499</t>
   </si>
   <si>
     <t xml:space="preserve">9.50448131561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65504741668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78679180145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73033046722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67386722564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52330112457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48566055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40096664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34450435638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29745292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35391426086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38214588165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26922225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41037750244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39155578613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91853713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93735885620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80561351776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0314617156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84325408935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95617866516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97500038146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89971733093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61740589141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69268894195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5797643661499</t>
   </si>
   <si>
     <t xml:space="preserve">9.46683979034424</t>
@@ -63666,7 +63669,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G2268" t="s">
-        <v>1268</v>
+        <v>1294</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -63692,7 +63695,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2269" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -63718,7 +63721,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G2270" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -63744,7 +63747,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G2271" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -63770,7 +63773,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G2272" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -63822,7 +63825,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G2274" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -63952,7 +63955,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G2279" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -63978,7 +63981,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2280" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64004,7 +64007,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2281" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64030,7 +64033,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2282" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64056,7 +64059,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G2283" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64082,7 +64085,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2284" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64134,7 +64137,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G2286" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64186,7 +64189,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2288" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64212,7 +64215,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G2289" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64238,7 +64241,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G2290" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64290,7 +64293,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2292" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64316,7 +64319,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G2293" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64342,7 +64345,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G2294" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64368,7 +64371,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G2295" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64394,7 +64397,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G2296" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64420,7 +64423,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G2297" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64446,7 +64449,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2298" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64472,7 +64475,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2299" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64498,7 +64501,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2300" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64524,7 +64527,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2301" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64550,7 +64553,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2302" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64576,7 +64579,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G2303" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64602,7 +64605,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G2304" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -64628,7 +64631,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2305" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -64654,7 +64657,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G2306" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -64680,7 +64683,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2307" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -64706,7 +64709,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2308" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -64732,7 +64735,7 @@
         <v>11.5</v>
       </c>
       <c r="G2309" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -64758,7 +64761,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G2310" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -64784,7 +64787,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G2311" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -64810,7 +64813,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2312" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -64836,7 +64839,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G2313" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -64862,7 +64865,7 @@
         <v>11.5</v>
       </c>
       <c r="G2314" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -64888,7 +64891,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G2315" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -64914,7 +64917,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G2316" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -64940,7 +64943,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G2317" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -64966,7 +64969,7 @@
         <v>12</v>
       </c>
       <c r="G2318" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -64992,7 +64995,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2319" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -65018,7 +65021,7 @@
         <v>12</v>
       </c>
       <c r="G2320" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -65044,7 +65047,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2321" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65070,7 +65073,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2322" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65096,7 +65099,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2323" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65122,7 +65125,7 @@
         <v>12</v>
       </c>
       <c r="G2324" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65148,7 +65151,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G2325" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65174,7 +65177,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G2326" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65200,7 +65203,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G2327" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65226,7 +65229,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2328" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65252,7 +65255,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2329" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65278,7 +65281,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2330" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65304,7 +65307,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2331" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65330,7 +65333,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2332" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65356,7 +65359,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G2333" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65382,7 +65385,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2334" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65408,7 +65411,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2335" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65434,7 +65437,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2336" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65460,7 +65463,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2337" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65486,7 +65489,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2338" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65512,7 +65515,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2339" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65538,7 +65541,7 @@
         <v>12.5</v>
       </c>
       <c r="G2340" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65564,7 +65567,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2341" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65590,7 +65593,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2342" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65616,7 +65619,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G2343" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -65642,7 +65645,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G2344" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -65668,7 +65671,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2345" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -65694,7 +65697,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2346" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -65720,7 +65723,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2347" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -65746,7 +65749,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G2348" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -65772,7 +65775,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2349" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -65798,7 +65801,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G2350" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -65824,7 +65827,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G2351" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -65850,7 +65853,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2352" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -65876,7 +65879,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G2353" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -65902,7 +65905,7 @@
         <v>12.7600002288818</v>
       </c>
       <c r="G2354" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -65928,7 +65931,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2355" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -65954,7 +65957,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G2356" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -65980,7 +65983,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G2357" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -66006,7 +66009,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G2358" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -66032,7 +66035,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G2359" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -66058,7 +66061,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G2360" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66084,7 +66087,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G2361" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66110,7 +66113,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G2362" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66136,7 +66139,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G2363" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66162,7 +66165,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G2364" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66188,7 +66191,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2365" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66214,7 +66217,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G2366" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66240,7 +66243,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G2367" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66266,7 +66269,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G2368" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66292,7 +66295,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G2369" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66318,7 +66321,7 @@
         <v>12</v>
       </c>
       <c r="G2370" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66344,7 +66347,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2371" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66370,7 +66373,7 @@
         <v>12.0799999237061</v>
       </c>
       <c r="G2372" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66396,7 +66399,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G2373" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66422,7 +66425,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2374" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66448,7 +66451,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2375" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66474,7 +66477,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2376" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66500,7 +66503,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G2377" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66526,7 +66529,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G2378" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66552,7 +66555,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2379" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66578,7 +66581,7 @@
         <v>12.4200000762939</v>
       </c>
       <c r="G2380" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66604,7 +66607,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G2381" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -66630,7 +66633,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2382" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -66656,7 +66659,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G2383" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -66682,7 +66685,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2384" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -66708,7 +66711,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2385" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -66734,7 +66737,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2386" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -66760,7 +66763,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2387" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -66786,7 +66789,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2388" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -66812,7 +66815,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2389" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -66838,7 +66841,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G2390" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -66864,7 +66867,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2391" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -66890,7 +66893,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G2392" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -66916,7 +66919,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2393" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -66942,7 +66945,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2394" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -66968,7 +66971,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G2395" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -66994,7 +66997,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G2396" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -67020,7 +67023,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2397" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -67046,7 +67049,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G2398" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67072,7 +67075,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2399" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67098,7 +67101,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2400" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67124,7 +67127,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G2401" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67150,7 +67153,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G2402" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67176,7 +67179,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2403" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67202,7 +67205,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G2404" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67228,7 +67231,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2405" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67254,7 +67257,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2406" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67280,7 +67283,7 @@
         <v>12</v>
       </c>
       <c r="G2407" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67306,7 +67309,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G2408" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67332,7 +67335,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G2409" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67358,7 +67361,7 @@
         <v>12.5</v>
       </c>
       <c r="G2410" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67384,7 +67387,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2411" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67410,7 +67413,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G2412" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67436,7 +67439,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2413" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67462,7 +67465,7 @@
         <v>12.539999961853</v>
       </c>
       <c r="G2414" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67488,7 +67491,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G2415" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67514,7 +67517,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G2416" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67540,7 +67543,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G2417" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67566,7 +67569,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G2418" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67592,7 +67595,7 @@
         <v>12.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67618,7 +67621,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2420" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -67644,7 +67647,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G2421" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -67670,7 +67673,7 @@
         <v>13</v>
       </c>
       <c r="G2422" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -67696,7 +67699,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2423" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -67722,7 +67725,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G2424" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -67748,7 +67751,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G2425" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -67774,7 +67777,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G2426" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -67800,7 +67803,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2427" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -67826,7 +67829,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G2428" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -67852,7 +67855,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G2429" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -67878,7 +67881,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G2430" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -67904,7 +67907,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2431" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -67930,7 +67933,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G2432" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -67956,7 +67959,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G2433" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -67982,7 +67985,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G2434" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -68008,7 +68011,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2435" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -68034,7 +68037,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2436" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -68060,7 +68063,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2437" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68086,7 +68089,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G2438" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68112,7 +68115,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2439" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68138,7 +68141,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2440" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68164,7 +68167,7 @@
         <v>13.5</v>
       </c>
       <c r="G2441" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68190,7 +68193,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2442" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68216,7 +68219,7 @@
         <v>13.5</v>
       </c>
       <c r="G2443" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68242,7 +68245,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2444" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68268,7 +68271,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2445" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68294,7 +68297,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2446" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68320,7 +68323,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2447" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68346,7 +68349,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G2448" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68372,7 +68375,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2449" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68398,7 +68401,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2450" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68424,7 +68427,7 @@
         <v>14</v>
       </c>
       <c r="G2451" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68450,7 +68453,7 @@
         <v>14</v>
       </c>
       <c r="G2452" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68476,7 +68479,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G2453" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68502,7 +68505,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2454" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68528,7 +68531,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2455" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68554,7 +68557,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2456" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68580,7 +68583,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2457" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68606,7 +68609,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2458" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -68632,7 +68635,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G2459" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -68658,7 +68661,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2460" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -68684,7 +68687,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G2461" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -68710,7 +68713,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2462" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -68736,7 +68739,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G2463" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -68762,7 +68765,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2464" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -68788,7 +68791,7 @@
         <v>13.5200004577637</v>
       </c>
       <c r="G2465" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -68814,7 +68817,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G2466" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -68840,7 +68843,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2467" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -68866,7 +68869,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G2468" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -68892,7 +68895,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2469" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -68918,7 +68921,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2470" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -68944,7 +68947,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G2471" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -68970,7 +68973,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2472" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -68996,7 +68999,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G2473" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -69022,7 +69025,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2474" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -69048,7 +69051,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2475" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69074,7 +69077,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G2476" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69100,7 +69103,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2477" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69126,7 +69129,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69152,7 +69155,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2479" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69178,7 +69181,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2480" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69204,7 +69207,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2481" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69230,7 +69233,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G2482" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69256,7 +69259,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2483" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69282,7 +69285,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G2484" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69308,7 +69311,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2485" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69334,7 +69337,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G2486" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69360,7 +69363,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G2487" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69386,7 +69389,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2488" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69412,7 +69415,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G2489" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69438,7 +69441,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G2490" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69464,7 +69467,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G2491" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69490,7 +69493,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G2492" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69516,7 +69519,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G2493" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69542,7 +69545,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2494" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69568,7 +69571,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G2495" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69594,7 +69597,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G2496" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69620,7 +69623,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G2497" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -69646,7 +69649,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G2498" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -69672,7 +69675,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G2499" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -69698,7 +69701,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2500" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -69724,7 +69727,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2501" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -69750,7 +69753,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G2502" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -69776,7 +69779,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G2503" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -69802,7 +69805,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G2504" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -69828,7 +69831,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G2505" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -69854,7 +69857,7 @@
         <v>13.6400003433228</v>
       </c>
       <c r="G2506" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -69880,7 +69883,7 @@
         <v>13.9200000762939</v>
       </c>
       <c r="G2507" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -69906,7 +69909,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G2508" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -69932,7 +69935,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2509" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -69958,7 +69961,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G2510" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -69984,7 +69987,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G2511" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -70010,7 +70013,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2512" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -70036,7 +70039,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2513" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -70062,7 +70065,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G2514" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -70088,7 +70091,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G2515" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -70114,7 +70117,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G2516" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -70140,7 +70143,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G2517" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -70166,7 +70169,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2518" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -70192,7 +70195,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G2519" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -70218,7 +70221,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G2520" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -70244,7 +70247,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G2521" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -70270,7 +70273,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2522" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -70296,7 +70299,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G2523" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -70322,7 +70325,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G2524" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -70348,7 +70351,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G2525" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -70374,7 +70377,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G2526" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -70400,7 +70403,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G2527" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -70426,7 +70429,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G2528" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -70452,7 +70455,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G2529" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -70478,7 +70481,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G2530" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -70504,7 +70507,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G2531" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -70530,7 +70533,7 @@
         <v>14.7600002288818</v>
       </c>
       <c r="G2532" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -70556,7 +70559,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G2533" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -70582,7 +70585,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G2534" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -70608,7 +70611,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G2535" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -70634,7 +70637,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2536" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -70660,7 +70663,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G2537" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -70686,7 +70689,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G2538" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -70712,7 +70715,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G2539" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>

--- a/data/CE.MI.xlsx
+++ b/data/CE.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49119424819946</t>
+    <t xml:space="preserve">4.49119472503662</t>
   </si>
   <si>
     <t xml:space="preserve">CE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52814531326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46432065963745</t>
+    <t xml:space="preserve">4.5281457901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46432161331177</t>
   </si>
   <si>
     <t xml:space="preserve">4.30644083023071</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">4.26613092422485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31315851211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31987714767456</t>
+    <t xml:space="preserve">4.31315898895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31987762451172</t>
   </si>
   <si>
     <t xml:space="preserve">4.3669056892395</t>
@@ -71,70 +71,70 @@
     <t xml:space="preserve">4.2358980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05114507675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08473587036133</t>
+    <t xml:space="preserve">4.05114555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08473682403564</t>
   </si>
   <si>
     <t xml:space="preserve">3.74210238456726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91677832603455</t>
+    <t xml:space="preserve">3.91677904129028</t>
   </si>
   <si>
     <t xml:space="preserve">4.03099012374878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15527820587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12840509414673</t>
+    <t xml:space="preserve">4.15527868270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12840557098389</t>
   </si>
   <si>
     <t xml:space="preserve">4.01419401168823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12504577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1216869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9470112323761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80256628990173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83615875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86975073814392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58086252212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42970061302185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7521800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60773611068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84959554672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90670037269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96716570854187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06458187103271</t>
+    <t xml:space="preserve">4.12504625320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12168741226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94701051712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80256772041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83615851402283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8697509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58086276054382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42970037460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75217986106873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60773587226868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84959506988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90670108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96716594696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06458139419556</t>
   </si>
   <si>
     <t xml:space="preserve">3.8294403553009</t>
@@ -143,40 +143,40 @@
     <t xml:space="preserve">3.7723343372345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9033420085907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87982773780823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72866559028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79584884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88318705558777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95708823204041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13176536560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1955885887146</t>
+    <t xml:space="preserve">3.90334224700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87982797622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72866582870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79584956169128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88318681716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95708847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13176393508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19558906555176</t>
   </si>
   <si>
     <t xml:space="preserve">4.18551111221313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13848304748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22246122360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29972267150879</t>
+    <t xml:space="preserve">4.13848257064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22246170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29972219467163</t>
   </si>
   <si>
     <t xml:space="preserve">4.35682773590088</t>
@@ -185,76 +185,76 @@
     <t xml:space="preserve">4.25605344772339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27956771850586</t>
+    <t xml:space="preserve">4.27956819534302</t>
   </si>
   <si>
     <t xml:space="preserve">4.14856052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32659530639648</t>
+    <t xml:space="preserve">4.32659578323364</t>
   </si>
   <si>
     <t xml:space="preserve">4.26949024200439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16535615921021</t>
+    <t xml:space="preserve">4.16535568237305</t>
   </si>
   <si>
     <t xml:space="preserve">4.09817266464233</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04778623580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04106712341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93021464347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91006064414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8193621635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75889754295349</t>
+    <t xml:space="preserve">4.04778575897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04106760025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93021535873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9100604057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81936287879944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75889778137207</t>
   </si>
   <si>
     <t xml:space="preserve">3.71187019348145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93357348442078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82608103752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08137702941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15863847732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17879199981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21238422393799</t>
+    <t xml:space="preserve">3.93357467651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82608151435852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0813775062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15863752365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17879295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2123851776123</t>
   </si>
   <si>
     <t xml:space="preserve">4.21574354171753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2829270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30308198928833</t>
+    <t xml:space="preserve">4.28292655944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30308151245117</t>
   </si>
   <si>
     <t xml:space="preserve">4.3534688949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19894742965698</t>
+    <t xml:space="preserve">4.1989483833313</t>
   </si>
   <si>
     <t xml:space="preserve">4.07465887069702</t>
@@ -263,49 +263,49 @@
     <t xml:space="preserve">4.08809566497803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06122255325317</t>
+    <t xml:space="preserve">4.06122207641602</t>
   </si>
   <si>
     <t xml:space="preserve">4.02427196502686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93693375587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21648979187012</t>
+    <t xml:space="preserve">3.93693351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21648931503296</t>
   </si>
   <si>
     <t xml:space="preserve">4.14420700073242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19927883148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25435161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23370027542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23714256286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49185180664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4987359046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47120094299316</t>
+    <t xml:space="preserve">4.19927930831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25435209274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23369979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23714160919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49185228347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49873638153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47119998931885</t>
   </si>
   <si>
     <t xml:space="preserve">4.45743179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46431589126587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37826442718506</t>
+    <t xml:space="preserve">4.46431541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37826538085938</t>
   </si>
   <si>
     <t xml:space="preserve">4.31975078582764</t>
@@ -326,133 +326,133 @@
     <t xml:space="preserve">4.35072898864746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25090932846069</t>
+    <t xml:space="preserve">4.25090980529785</t>
   </si>
   <si>
     <t xml:space="preserve">4.03750371932983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91703248023987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98243093490601</t>
+    <t xml:space="preserve">3.91703271865845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98243141174316</t>
   </si>
   <si>
     <t xml:space="preserve">3.86884450912476</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13732290267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3369607925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38170719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42301177978516</t>
+    <t xml:space="preserve">4.1373233795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33696031570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38170671463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.423011302948</t>
   </si>
   <si>
     <t xml:space="preserve">4.52971410751343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74148893356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75181555747986</t>
+    <t xml:space="preserve">3.74148845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7518150806427</t>
   </si>
   <si>
     <t xml:space="preserve">3.73116326332092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84130787849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65199613571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52464079856873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42826437950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50743103027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65888094902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75525736808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82065582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78623557090759</t>
+    <t xml:space="preserve">3.84130835533142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65199637413025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52464127540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42826414108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50743079185486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65888071060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75525712966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82065606117249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78623533248901</t>
   </si>
   <si>
     <t xml:space="preserve">3.90670704841614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9652214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95145297050476</t>
+    <t xml:space="preserve">3.96522116661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95145320892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.0409460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01340913772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94456887245178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98931527137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9583375453949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7965612411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90326404571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80000352859497</t>
+    <t xml:space="preserve">4.01341009140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94456911087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98931574821472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95833706855774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79656147956848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90326476097107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80000376701355</t>
   </si>
   <si>
     <t xml:space="preserve">3.68641662597656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70018458366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76558303833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70362663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66576361656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66920590400696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55217719078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48677849769592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47989463806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37319159507751</t>
+    <t xml:space="preserve">3.70018410682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76558375358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70362687110901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66576433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66920614242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5521776676178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4867787361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47989511489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37319231033325</t>
   </si>
   <si>
     <t xml:space="preserve">3.37181448936462</t>
@@ -461,118 +461,118 @@
     <t xml:space="preserve">3.50054717063904</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68985819816589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55561947822571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45235848426819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47645258903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64511227607727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72083711624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70706868171692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7793505191803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80688810348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61413383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61757612228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5797131061554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56594491004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4936625957489</t>
+    <t xml:space="preserve">3.68985867500305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55561900138855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45235896110535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47645282745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64511251449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72083783149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70706915855408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77935147285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80688786506653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61413407325745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61757588386536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57971382141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5659453868866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49366283416748</t>
   </si>
   <si>
     <t xml:space="preserve">3.49022102355957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44891595840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63822841644287</t>
+    <t xml:space="preserve">3.4489164352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63822793960571</t>
   </si>
   <si>
     <t xml:space="preserve">3.49710488319397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38695979118347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35804677009583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37456870079041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31123518943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32638001441956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35529327392578</t>
+    <t xml:space="preserve">3.38696002960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35804581642151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37456846237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31123471260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32637977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35529351234436</t>
   </si>
   <si>
     <t xml:space="preserve">3.41587281227112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51431512832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48333692550659</t>
+    <t xml:space="preserve">3.51431488990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48333644866943</t>
   </si>
   <si>
     <t xml:space="preserve">3.51087260246277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51775741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47301054000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57627129554749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53496766090393</t>
+    <t xml:space="preserve">3.51775717735291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4730110168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57627105712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53496742248535</t>
   </si>
   <si>
     <t xml:space="preserve">3.64855456352234</t>
   </si>
  